--- a/apps/workspace-web/i18n.xlsx
+++ b/apps/workspace-web/i18n.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1461" uniqueCount="1339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1482" uniqueCount="1356">
   <si>
     <t>key</t>
   </si>
@@ -667,15 +667,6 @@
     <t>Actions</t>
   </si>
   <si>
-    <t>stores.noDescription</t>
-  </si>
-  <si>
-    <t>尚未填寫商店描述</t>
-  </si>
-  <si>
-    <t>No store description yet</t>
-  </si>
-  <si>
     <t>stores.emptyTitle</t>
   </si>
   <si>
@@ -1078,22 +1069,16 @@
     <t>Result</t>
   </si>
   <si>
-    <t>reviewHistory.rejectReasonPrefix</t>
-  </si>
-  <si>
-    <t>駁回原因：{reason}</t>
-  </si>
-  <si>
-    <t>Rejection reason: {reason}</t>
-  </si>
-  <si>
-    <t>reviewHistory.reviewed</t>
-  </si>
-  <si>
-    <t>審核完成</t>
-  </si>
-  <si>
-    <t>Review complete</t>
+    <t>reviewHistory.viewReason</t>
+  </si>
+  <si>
+    <t>查看駁回原因</t>
+  </si>
+  <si>
+    <t>View rejection reason</t>
+  </si>
+  <si>
+    <t>reviewHistory.reasonModalTitle</t>
   </si>
   <si>
     <t>reviewHistory.emptyTitle</t>
@@ -1933,6 +1918,15 @@
     <t>Update failed</t>
   </si>
   <si>
+    <t>catalogCategories.searchPlaceholder</t>
+  </si>
+  <si>
+    <t>搜尋分類名稱或 slug</t>
+  </si>
+  <si>
+    <t>Search category name or slug</t>
+  </si>
+  <si>
     <t>catalogCategories.childSub</t>
   </si>
   <si>
@@ -3145,6 +3139,15 @@
     <t>Order status</t>
   </si>
   <si>
+    <t>orders.orderStatusPlaceholder</t>
+  </si>
+  <si>
+    <t>請選擇狀態</t>
+  </si>
+  <si>
+    <t>Select a status</t>
+  </si>
+  <si>
     <t>orders.colOrderNumber</t>
   </si>
   <si>
@@ -4028,6 +4031,54 @@
   </si>
   <si>
     <t>This product version has no downloadable files.</t>
+  </si>
+  <si>
+    <t>notifications.title</t>
+  </si>
+  <si>
+    <t>notifications.empty</t>
+  </si>
+  <si>
+    <t>目前沒有通知</t>
+  </si>
+  <si>
+    <t>No notifications yet</t>
+  </si>
+  <si>
+    <t>notifications.markAllRead</t>
+  </si>
+  <si>
+    <t>全部標為已讀</t>
+  </si>
+  <si>
+    <t>Mark all as read</t>
+  </si>
+  <si>
+    <t>notifications.justNow</t>
+  </si>
+  <si>
+    <t>剛剛</t>
+  </si>
+  <si>
+    <t>Just now</t>
+  </si>
+  <si>
+    <t>notifications.catalogPublished</t>
+  </si>
+  <si>
+    <t>{storeName} 上架了新商品「{catalogName}」</t>
+  </si>
+  <si>
+    <t>{storeName} released a new product "{catalogName}"</t>
+  </si>
+  <si>
+    <t>notifications.storeAnnouncement</t>
+  </si>
+  <si>
+    <t>{storeName}：{title}</t>
+  </si>
+  <si>
+    <t>{storeName}: {title}</t>
   </si>
 </sst>
 </file>
@@ -4413,7 +4464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C487"/>
+  <dimension ref="A1:C494"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -5316,21 +5367,21 @@
         <v>239</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>240</v>
+        <v>28</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>241</v>
+        <v>29</v>
       </c>
     </row>
     <row r="83" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C83" s="2" t="s">
         <v>242</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="84" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5470,21 +5521,21 @@
         <v>279</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>280</v>
+        <v>216</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>281</v>
+        <v>217</v>
       </c>
     </row>
     <row r="97" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C97" s="2" t="s">
         <v>282</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="98" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5756,1203 +5807,1203 @@
         <v>355</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>356</v>
+        <v>302</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>357</v>
+        <v>303</v>
       </c>
     </row>
     <row r="123" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C123" s="2" t="s">
         <v>358</v>
-      </c>
-      <c r="B123" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="C123" s="2" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="124" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="C124" s="2" t="s">
         <v>361</v>
-      </c>
-      <c r="B124" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="C124" s="2" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="125" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C125" s="2" t="s">
         <v>364</v>
-      </c>
-      <c r="B125" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="C125" s="2" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="126" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>368</v>
+        <v>228</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>369</v>
+        <v>229</v>
       </c>
     </row>
     <row r="127" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>231</v>
+        <v>367</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>232</v>
+        <v>368</v>
       </c>
     </row>
     <row r="128" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="C128" s="2" t="s">
         <v>371</v>
-      </c>
-      <c r="B128" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="129" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C129" s="2" t="s">
         <v>374</v>
-      </c>
-      <c r="B129" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="C129" s="2" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="130" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="C130" s="2" t="s">
         <v>377</v>
-      </c>
-      <c r="B130" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="C130" s="2" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="131" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="C131" s="2" t="s">
         <v>380</v>
-      </c>
-      <c r="B131" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="C131" s="2" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="132" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="C132" s="2" t="s">
         <v>383</v>
-      </c>
-      <c r="B132" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="C132" s="2" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="133" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C133" s="2" t="s">
         <v>386</v>
-      </c>
-      <c r="B133" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="134" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="C134" s="2" t="s">
         <v>389</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="135" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C135" s="2" t="s">
         <v>392</v>
-      </c>
-      <c r="B135" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="136" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="C136" s="2" t="s">
         <v>395</v>
-      </c>
-      <c r="B136" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="137" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="C137" s="2" t="s">
         <v>398</v>
-      </c>
-      <c r="B137" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="C137" s="2" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="138" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="C138" s="2" t="s">
         <v>401</v>
-      </c>
-      <c r="B138" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="C139" s="2" t="s">
         <v>404</v>
-      </c>
-      <c r="B139" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="C139" s="2" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="140" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="C140" s="2" t="s">
         <v>407</v>
-      </c>
-      <c r="B140" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="C140" s="2" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="141" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="C141" s="2" t="s">
         <v>410</v>
-      </c>
-      <c r="B141" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="C141" s="2" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="142" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="C142" s="2" t="s">
         <v>413</v>
-      </c>
-      <c r="B142" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="C142" s="2" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="143" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="C143" s="2" t="s">
         <v>416</v>
-      </c>
-      <c r="B143" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="C143" s="2" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="144" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="C144" s="2" t="s">
         <v>419</v>
-      </c>
-      <c r="B144" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="C144" s="2" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="145" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="C145" s="2" t="s">
         <v>422</v>
-      </c>
-      <c r="B145" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="C145" s="2" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="146" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="C146" s="2" t="s">
         <v>425</v>
-      </c>
-      <c r="B146" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="C146" s="2" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="147" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="C147" s="2" t="s">
         <v>428</v>
-      </c>
-      <c r="B147" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="C147" s="2" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="148" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="C148" s="2" t="s">
         <v>431</v>
-      </c>
-      <c r="B148" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="C148" s="2" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="149" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="C149" s="2" t="s">
         <v>434</v>
-      </c>
-      <c r="B149" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="C149" s="2" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="150" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C150" s="2" t="s">
         <v>437</v>
-      </c>
-      <c r="B150" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="C150" s="2" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="151" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="C151" s="2" t="s">
         <v>440</v>
-      </c>
-      <c r="B151" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="C151" s="2" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="152" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="C152" s="2" t="s">
         <v>443</v>
-      </c>
-      <c r="B152" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="C152" s="2" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="153" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="C153" s="2" t="s">
         <v>446</v>
-      </c>
-      <c r="B153" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="C153" s="2" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="154" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="C154" s="2" t="s">
         <v>449</v>
-      </c>
-      <c r="B154" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="C154" s="2" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="155" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>454</v>
+        <v>389</v>
       </c>
     </row>
     <row r="156" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>456</v>
+        <v>400</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
     </row>
     <row r="157" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>406</v>
+        <v>173</v>
       </c>
     </row>
     <row r="158" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>414</v>
+        <v>455</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>173</v>
+        <v>456</v>
       </c>
     </row>
     <row r="159" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="C159" s="2" t="s">
         <v>459</v>
-      </c>
-      <c r="B159" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="C159" s="2" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="160" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="C160" s="2" t="s">
         <v>462</v>
-      </c>
-      <c r="B160" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="C160" s="2" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="161" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="C161" s="2" t="s">
         <v>465</v>
-      </c>
-      <c r="B161" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="C161" s="2" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="162" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="C162" s="2" t="s">
         <v>468</v>
-      </c>
-      <c r="B162" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="C162" s="2" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="163" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="C163" s="2" t="s">
         <v>471</v>
-      </c>
-      <c r="B163" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="C163" s="2" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="164" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>475</v>
+        <v>22</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>476</v>
+        <v>23</v>
       </c>
     </row>
     <row r="165" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>22</v>
+        <v>474</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>23</v>
+        <v>475</v>
       </c>
     </row>
     <row r="166" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="C166" s="2" t="s">
         <v>478</v>
-      </c>
-      <c r="B166" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="C166" s="2" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="167" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="C167" s="2" t="s">
         <v>481</v>
-      </c>
-      <c r="B167" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="C167" s="2" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="168" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="C168" s="2" t="s">
         <v>484</v>
-      </c>
-      <c r="B168" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="C168" s="2" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="169" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="C169" s="2" t="s">
         <v>487</v>
-      </c>
-      <c r="B169" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="C169" s="2" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="170" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>491</v>
+        <v>400</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="171" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>405</v>
+        <v>491</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="172" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="C172" s="2" t="s">
         <v>495</v>
-      </c>
-      <c r="B172" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="C172" s="2" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="173" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="C173" s="2" t="s">
         <v>498</v>
-      </c>
-      <c r="B173" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="C173" s="2" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="174" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="C174" s="2" t="s">
         <v>501</v>
-      </c>
-      <c r="B174" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="C174" s="2" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="175" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="C175" s="2" t="s">
         <v>504</v>
-      </c>
-      <c r="B175" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="C175" s="2" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="176" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C176" s="2" t="s">
         <v>507</v>
-      </c>
-      <c r="B176" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="C176" s="2" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="177" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="C177" s="2" t="s">
         <v>510</v>
-      </c>
-      <c r="B177" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="C177" s="2" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="178" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="C178" s="2" t="s">
         <v>513</v>
-      </c>
-      <c r="B178" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="C178" s="2" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="179" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="C179" s="2" t="s">
         <v>516</v>
-      </c>
-      <c r="B179" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="C179" s="2" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="180" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="C180" s="2" t="s">
         <v>519</v>
-      </c>
-      <c r="B180" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="C180" s="2" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="181" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C181" s="2" t="s">
         <v>522</v>
-      </c>
-      <c r="B181" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="C181" s="2" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="182" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="C182" s="2" t="s">
         <v>525</v>
-      </c>
-      <c r="B182" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="C182" s="2" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="183" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>529</v>
+        <v>158</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>530</v>
+        <v>158</v>
       </c>
     </row>
     <row r="184" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>158</v>
+        <v>528</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>158</v>
+        <v>529</v>
       </c>
     </row>
     <row r="185" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>533</v>
+        <v>155</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>534</v>
+        <v>156</v>
       </c>
     </row>
     <row r="186" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>155</v>
+        <v>532</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>156</v>
+        <v>533</v>
       </c>
     </row>
     <row r="187" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="C187" s="2" t="s">
         <v>536</v>
-      </c>
-      <c r="B187" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="C187" s="2" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="188" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="C188" s="2" t="s">
         <v>539</v>
-      </c>
-      <c r="B188" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="C188" s="2" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="189" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="C189" s="2" t="s">
         <v>542</v>
-      </c>
-      <c r="B189" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="C189" s="2" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="190" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="C190" s="2" t="s">
         <v>545</v>
-      </c>
-      <c r="B190" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="C190" s="2" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="191" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="C191" s="2" t="s">
         <v>548</v>
-      </c>
-      <c r="B191" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="C191" s="2" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="192" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="C192" s="2" t="s">
         <v>551</v>
-      </c>
-      <c r="B192" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="C192" s="2" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="193" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="C193" s="2" t="s">
         <v>554</v>
-      </c>
-      <c r="B193" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="C193" s="2" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="194" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>558</v>
+        <v>268</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>559</v>
+        <v>269</v>
       </c>
     </row>
     <row r="195" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>271</v>
+        <v>557</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>272</v>
+        <v>558</v>
       </c>
     </row>
     <row r="196" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>562</v>
+        <v>271</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>563</v>
+        <v>272</v>
       </c>
     </row>
     <row r="197" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>274</v>
+        <v>561</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>275</v>
+        <v>562</v>
       </c>
     </row>
     <row r="198" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="C198" s="2" t="s">
         <v>565</v>
-      </c>
-      <c r="B198" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="C198" s="2" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="199" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="C199" s="2" t="s">
         <v>568</v>
-      </c>
-      <c r="B199" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="C199" s="2" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="200" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="C200" s="2" t="s">
         <v>571</v>
-      </c>
-      <c r="B200" s="2" t="s">
-        <v>572</v>
-      </c>
-      <c r="C200" s="2" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="201" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="C201" s="2" t="s">
         <v>574</v>
-      </c>
-      <c r="B201" s="2" t="s">
-        <v>575</v>
-      </c>
-      <c r="C201" s="2" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="202" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="C202" s="2" t="s">
         <v>577</v>
-      </c>
-      <c r="B202" s="2" t="s">
-        <v>578</v>
-      </c>
-      <c r="C202" s="2" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="203" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="C203" s="2" t="s">
         <v>580</v>
-      </c>
-      <c r="B203" s="2" t="s">
-        <v>581</v>
-      </c>
-      <c r="C203" s="2" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="204" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="C204" s="2" t="s">
         <v>583</v>
-      </c>
-      <c r="B204" s="2" t="s">
-        <v>584</v>
-      </c>
-      <c r="C204" s="2" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="205" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="C205" s="2" t="s">
         <v>586</v>
-      </c>
-      <c r="B205" s="2" t="s">
-        <v>587</v>
-      </c>
-      <c r="C205" s="2" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="206" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="C206" s="2" t="s">
         <v>589</v>
-      </c>
-      <c r="B206" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="C206" s="2" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="207" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="C207" s="2" t="s">
         <v>592</v>
-      </c>
-      <c r="B207" s="2" t="s">
-        <v>593</v>
-      </c>
-      <c r="C207" s="2" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="208" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="C208" s="2" t="s">
         <v>595</v>
-      </c>
-      <c r="B208" s="2" t="s">
-        <v>596</v>
-      </c>
-      <c r="C208" s="2" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="209" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="C209" s="2" t="s">
         <v>598</v>
-      </c>
-      <c r="B209" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="C209" s="2" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="210" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="C210" s="2" t="s">
         <v>601</v>
-      </c>
-      <c r="B210" s="2" t="s">
-        <v>602</v>
-      </c>
-      <c r="C210" s="2" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="211" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>605</v>
+        <v>268</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>606</v>
+        <v>269</v>
       </c>
     </row>
     <row r="212" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>271</v>
+        <v>557</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>272</v>
+        <v>558</v>
       </c>
     </row>
     <row r="213" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>562</v>
+        <v>271</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>563</v>
+        <v>272</v>
       </c>
     </row>
     <row r="214" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>274</v>
+        <v>606</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>275</v>
+        <v>607</v>
       </c>
     </row>
     <row r="215" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="C215" s="2" t="s">
         <v>610</v>
-      </c>
-      <c r="B215" s="2" t="s">
-        <v>611</v>
-      </c>
-      <c r="C215" s="2" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="216" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="C216" s="2" t="s">
         <v>613</v>
-      </c>
-      <c r="B216" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="C216" s="2" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="217" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="B217" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="C217" s="2" t="s">
         <v>616</v>
-      </c>
-      <c r="B217" s="2" t="s">
-        <v>617</v>
-      </c>
-      <c r="C217" s="2" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="218" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="C218" s="2" t="s">
         <v>619</v>
-      </c>
-      <c r="B218" s="2" t="s">
-        <v>620</v>
-      </c>
-      <c r="C218" s="2" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="219" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="C219" s="2" t="s">
         <v>622</v>
-      </c>
-      <c r="B219" s="2" t="s">
-        <v>623</v>
-      </c>
-      <c r="C219" s="2" t="s">
-        <v>624</v>
       </c>
     </row>
     <row r="220" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="C220" s="2" t="s">
         <v>625</v>
-      </c>
-      <c r="B220" s="2" t="s">
-        <v>626</v>
-      </c>
-      <c r="C220" s="2" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="221" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="C221" s="2" t="s">
         <v>628</v>
-      </c>
-      <c r="B221" s="2" t="s">
-        <v>629</v>
-      </c>
-      <c r="C221" s="2" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="222" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="C222" s="2" t="s">
         <v>631</v>
-      </c>
-      <c r="B222" s="2" t="s">
-        <v>632</v>
-      </c>
-      <c r="C222" s="2" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="223" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="C223" s="2" t="s">
         <v>634</v>
-      </c>
-      <c r="B223" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="C223" s="2" t="s">
-        <v>636</v>
       </c>
     </row>
     <row r="224" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="C224" s="2" t="s">
         <v>637</v>
-      </c>
-      <c r="B224" s="2" t="s">
-        <v>638</v>
-      </c>
-      <c r="C224" s="2" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="225" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="C225" s="2" t="s">
         <v>640</v>
-      </c>
-      <c r="B225" s="2" t="s">
-        <v>641</v>
-      </c>
-      <c r="C225" s="2" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="226" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="C226" s="2" t="s">
         <v>643</v>
-      </c>
-      <c r="B226" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="C226" s="2" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="227" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="C227" s="2" t="s">
         <v>646</v>
-      </c>
-      <c r="B227" s="2" t="s">
-        <v>647</v>
-      </c>
-      <c r="C227" s="2" t="s">
-        <v>648</v>
       </c>
     </row>
     <row r="228" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="C228" s="2" t="s">
         <v>649</v>
-      </c>
-      <c r="B228" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="C228" s="2" t="s">
-        <v>651</v>
       </c>
     </row>
     <row r="229" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
     </row>
     <row r="230" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="C230" s="2" t="s">
         <v>653</v>
-      </c>
-      <c r="B230" s="2" t="s">
-        <v>654</v>
-      </c>
-      <c r="C230" s="2" t="s">
-        <v>655</v>
       </c>
     </row>
     <row r="231" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B231" s="2" t="s">
         <v>216</v>
@@ -6963,260 +7014,260 @@
     </row>
     <row r="232" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="C232" s="2" t="s">
         <v>657</v>
-      </c>
-      <c r="B232" s="2" t="s">
-        <v>658</v>
-      </c>
-      <c r="C232" s="2" t="s">
-        <v>659</v>
       </c>
     </row>
     <row r="233" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="C233" s="2" t="s">
         <v>660</v>
-      </c>
-      <c r="B233" s="2" t="s">
-        <v>661</v>
-      </c>
-      <c r="C233" s="2" t="s">
-        <v>662</v>
       </c>
     </row>
     <row r="234" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="C234" s="2" t="s">
         <v>663</v>
-      </c>
-      <c r="B234" s="2" t="s">
-        <v>664</v>
-      </c>
-      <c r="C234" s="2" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="235" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="C235" s="2" t="s">
         <v>666</v>
-      </c>
-      <c r="B235" s="2" t="s">
-        <v>667</v>
-      </c>
-      <c r="C235" s="2" t="s">
-        <v>668</v>
       </c>
     </row>
     <row r="236" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="C236" s="2" t="s">
         <v>669</v>
-      </c>
-      <c r="B236" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="C236" s="2" t="s">
-        <v>671</v>
       </c>
     </row>
     <row r="237" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="C237" s="2" t="s">
         <v>672</v>
-      </c>
-      <c r="B237" s="2" t="s">
-        <v>673</v>
-      </c>
-      <c r="C237" s="2" t="s">
-        <v>674</v>
       </c>
     </row>
     <row r="238" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="B238" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="C238" s="2" t="s">
         <v>675</v>
-      </c>
-      <c r="B238" s="2" t="s">
-        <v>676</v>
-      </c>
-      <c r="C238" s="2" t="s">
-        <v>677</v>
       </c>
     </row>
     <row r="239" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="B239" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="C239" s="2" t="s">
         <v>678</v>
-      </c>
-      <c r="B239" s="2" t="s">
-        <v>679</v>
-      </c>
-      <c r="C239" s="2" t="s">
-        <v>680</v>
       </c>
     </row>
     <row r="240" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="C240" s="2" t="s">
         <v>681</v>
-      </c>
-      <c r="B240" s="2" t="s">
-        <v>682</v>
-      </c>
-      <c r="C240" s="2" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="241" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="242" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="C242" s="2" t="s">
         <v>685</v>
-      </c>
-      <c r="B242" s="2" t="s">
-        <v>686</v>
-      </c>
-      <c r="C242" s="2" t="s">
-        <v>687</v>
       </c>
     </row>
     <row r="243" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="C243" s="2" t="s">
         <v>688</v>
-      </c>
-      <c r="B243" s="2" t="s">
-        <v>689</v>
-      </c>
-      <c r="C243" s="2" t="s">
-        <v>690</v>
       </c>
     </row>
     <row r="244" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="C244" s="2" t="s">
         <v>691</v>
-      </c>
-      <c r="B244" s="2" t="s">
-        <v>692</v>
-      </c>
-      <c r="C244" s="2" t="s">
-        <v>693</v>
       </c>
     </row>
     <row r="245" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="B245" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="C245" s="2" t="s">
         <v>694</v>
-      </c>
-      <c r="B245" s="2" t="s">
-        <v>695</v>
-      </c>
-      <c r="C245" s="2" t="s">
-        <v>696</v>
       </c>
     </row>
     <row r="246" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="B246" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="C246" s="2" t="s">
         <v>697</v>
-      </c>
-      <c r="B246" s="2" t="s">
-        <v>698</v>
-      </c>
-      <c r="C246" s="2" t="s">
-        <v>699</v>
       </c>
     </row>
     <row r="247" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="B247" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="C247" s="2" t="s">
         <v>700</v>
-      </c>
-      <c r="B247" s="2" t="s">
-        <v>701</v>
-      </c>
-      <c r="C247" s="2" t="s">
-        <v>702</v>
       </c>
     </row>
     <row r="248" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="C248" s="2" t="s">
         <v>703</v>
-      </c>
-      <c r="B248" s="2" t="s">
-        <v>704</v>
-      </c>
-      <c r="C248" s="2" t="s">
-        <v>705</v>
       </c>
     </row>
     <row r="249" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
     </row>
     <row r="250" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="B250" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="C250" s="2" t="s">
         <v>707</v>
-      </c>
-      <c r="B250" s="2" t="s">
-        <v>708</v>
-      </c>
-      <c r="C250" s="2" t="s">
-        <v>709</v>
       </c>
     </row>
     <row r="251" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="B251" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="C251" s="2" t="s">
         <v>710</v>
-      </c>
-      <c r="B251" s="2" t="s">
-        <v>711</v>
-      </c>
-      <c r="C251" s="2" t="s">
-        <v>712</v>
       </c>
     </row>
     <row r="252" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="B252" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="C252" s="2" t="s">
         <v>713</v>
-      </c>
-      <c r="B252" s="2" t="s">
-        <v>714</v>
-      </c>
-      <c r="C252" s="2" t="s">
-        <v>715</v>
       </c>
     </row>
     <row r="253" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="B253" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="C253" s="2" t="s">
         <v>716</v>
-      </c>
-      <c r="B253" s="2" t="s">
-        <v>717</v>
-      </c>
-      <c r="C253" s="2" t="s">
-        <v>718</v>
       </c>
     </row>
     <row r="254" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="B254" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="C254" s="2" t="s">
         <v>719</v>
-      </c>
-      <c r="B254" s="2" t="s">
-        <v>720</v>
-      </c>
-      <c r="C254" s="2" t="s">
-        <v>721</v>
       </c>
     </row>
     <row r="255" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="B255" s="2" t="s">
         <v>46</v>
@@ -7227,689 +7278,689 @@
     </row>
     <row r="256" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="B256" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="C256" s="2" t="s">
         <v>723</v>
-      </c>
-      <c r="B256" s="2" t="s">
-        <v>724</v>
-      </c>
-      <c r="C256" s="2" t="s">
-        <v>725</v>
       </c>
     </row>
     <row r="257" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="B257" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="C257" s="2" t="s">
         <v>726</v>
-      </c>
-      <c r="B257" s="2" t="s">
-        <v>727</v>
-      </c>
-      <c r="C257" s="2" t="s">
-        <v>728</v>
       </c>
     </row>
     <row r="258" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="B258" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="C258" s="2" t="s">
         <v>729</v>
-      </c>
-      <c r="B258" s="2" t="s">
-        <v>730</v>
-      </c>
-      <c r="C258" s="2" t="s">
-        <v>731</v>
       </c>
     </row>
     <row r="259" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="B259" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="C259" s="2" t="s">
         <v>732</v>
-      </c>
-      <c r="B259" s="2" t="s">
-        <v>733</v>
-      </c>
-      <c r="C259" s="2" t="s">
-        <v>734</v>
       </c>
     </row>
     <row r="260" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="B260" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="C260" s="2" t="s">
         <v>735</v>
-      </c>
-      <c r="B260" s="2" t="s">
-        <v>736</v>
-      </c>
-      <c r="C260" s="2" t="s">
-        <v>737</v>
       </c>
     </row>
     <row r="261" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="B261" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="C261" s="2" t="s">
         <v>738</v>
-      </c>
-      <c r="B261" s="2" t="s">
-        <v>739</v>
-      </c>
-      <c r="C261" s="2" t="s">
-        <v>740</v>
       </c>
     </row>
     <row r="262" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="B262" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="C262" s="2" t="s">
         <v>741</v>
-      </c>
-      <c r="B262" s="2" t="s">
-        <v>742</v>
-      </c>
-      <c r="C262" s="2" t="s">
-        <v>743</v>
       </c>
     </row>
     <row r="263" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="B263" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="C263" s="2" t="s">
         <v>744</v>
-      </c>
-      <c r="B263" s="2" t="s">
-        <v>745</v>
-      </c>
-      <c r="C263" s="2" t="s">
-        <v>746</v>
       </c>
     </row>
     <row r="264" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
+        <v>745</v>
+      </c>
+      <c r="B264" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="C264" s="2" t="s">
         <v>747</v>
-      </c>
-      <c r="B264" s="2" t="s">
-        <v>748</v>
-      </c>
-      <c r="C264" s="2" t="s">
-        <v>749</v>
       </c>
     </row>
     <row r="265" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="B265" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="C265" s="2" t="s">
         <v>750</v>
-      </c>
-      <c r="B265" s="2" t="s">
-        <v>751</v>
-      </c>
-      <c r="C265" s="2" t="s">
-        <v>752</v>
       </c>
     </row>
     <row r="266" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="B266" s="2" t="s">
+        <v>752</v>
+      </c>
+      <c r="C266" s="2" t="s">
         <v>753</v>
-      </c>
-      <c r="B266" s="2" t="s">
-        <v>754</v>
-      </c>
-      <c r="C266" s="2" t="s">
-        <v>755</v>
       </c>
     </row>
     <row r="267" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
+        <v>754</v>
+      </c>
+      <c r="B267" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="C267" s="2" t="s">
         <v>756</v>
-      </c>
-      <c r="B267" s="2" t="s">
-        <v>757</v>
-      </c>
-      <c r="C267" s="2" t="s">
-        <v>758</v>
       </c>
     </row>
     <row r="268" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="B268" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="C268" s="2" t="s">
         <v>759</v>
-      </c>
-      <c r="B268" s="2" t="s">
-        <v>760</v>
-      </c>
-      <c r="C268" s="2" t="s">
-        <v>761</v>
       </c>
     </row>
     <row r="269" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="B269" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="C269" s="2" t="s">
         <v>762</v>
-      </c>
-      <c r="B269" s="2" t="s">
-        <v>763</v>
-      </c>
-      <c r="C269" s="2" t="s">
-        <v>764</v>
       </c>
     </row>
     <row r="270" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="B270" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="C270" s="2" t="s">
         <v>765</v>
-      </c>
-      <c r="B270" s="2" t="s">
-        <v>766</v>
-      </c>
-      <c r="C270" s="2" t="s">
-        <v>767</v>
       </c>
     </row>
     <row r="271" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
+        <v>766</v>
+      </c>
+      <c r="B271" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="C271" s="2" t="s">
         <v>768</v>
-      </c>
-      <c r="B271" s="2" t="s">
-        <v>769</v>
-      </c>
-      <c r="C271" s="2" t="s">
-        <v>770</v>
       </c>
     </row>
     <row r="272" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
     </row>
     <row r="273" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="274" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
+        <v>772</v>
+      </c>
+      <c r="B274" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="C274" s="2" t="s">
         <v>774</v>
-      </c>
-      <c r="B274" s="2" t="s">
-        <v>775</v>
-      </c>
-      <c r="C274" s="2" t="s">
-        <v>776</v>
       </c>
     </row>
     <row r="275" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="B275" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="C275" s="2" t="s">
         <v>777</v>
-      </c>
-      <c r="B275" s="2" t="s">
-        <v>778</v>
-      </c>
-      <c r="C275" s="2" t="s">
-        <v>779</v>
       </c>
     </row>
     <row r="276" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="B276" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="C276" s="2" t="s">
         <v>780</v>
-      </c>
-      <c r="B276" s="2" t="s">
-        <v>781</v>
-      </c>
-      <c r="C276" s="2" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="277" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="B277" s="2" t="s">
+        <v>782</v>
+      </c>
+      <c r="C277" s="2" t="s">
         <v>783</v>
-      </c>
-      <c r="B277" s="2" t="s">
-        <v>784</v>
-      </c>
-      <c r="C277" s="2" t="s">
-        <v>785</v>
       </c>
     </row>
     <row r="278" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="B278" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="C278" s="2" t="s">
         <v>786</v>
-      </c>
-      <c r="B278" s="2" t="s">
-        <v>787</v>
-      </c>
-      <c r="C278" s="2" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="279" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="B279" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="C279" s="2" t="s">
         <v>789</v>
-      </c>
-      <c r="B279" s="2" t="s">
-        <v>790</v>
-      </c>
-      <c r="C279" s="2" t="s">
-        <v>791</v>
       </c>
     </row>
     <row r="280" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="B280" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="C280" s="2" t="s">
         <v>792</v>
-      </c>
-      <c r="B280" s="2" t="s">
-        <v>793</v>
-      </c>
-      <c r="C280" s="2" t="s">
-        <v>794</v>
       </c>
     </row>
     <row r="281" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="B281" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="C281" s="2" t="s">
         <v>795</v>
-      </c>
-      <c r="B281" s="2" t="s">
-        <v>796</v>
-      </c>
-      <c r="C281" s="2" t="s">
-        <v>797</v>
       </c>
     </row>
     <row r="282" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="B282" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="C282" s="2" t="s">
         <v>798</v>
-      </c>
-      <c r="B282" s="2" t="s">
-        <v>799</v>
-      </c>
-      <c r="C282" s="2" t="s">
-        <v>800</v>
       </c>
     </row>
     <row r="283" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
     </row>
     <row r="284" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="B284" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="C284" s="2" t="s">
         <v>803</v>
-      </c>
-      <c r="B284" s="2" t="s">
-        <v>804</v>
-      </c>
-      <c r="C284" s="2" t="s">
-        <v>805</v>
       </c>
     </row>
     <row r="285" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="B285" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="C285" s="2" t="s">
         <v>806</v>
-      </c>
-      <c r="B285" s="2" t="s">
-        <v>807</v>
-      </c>
-      <c r="C285" s="2" t="s">
-        <v>808</v>
       </c>
     </row>
     <row r="286" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="B286" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="C286" s="2" t="s">
         <v>809</v>
-      </c>
-      <c r="B286" s="2" t="s">
-        <v>810</v>
-      </c>
-      <c r="C286" s="2" t="s">
-        <v>811</v>
       </c>
     </row>
     <row r="287" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="B287" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="C287" s="2" t="s">
         <v>812</v>
-      </c>
-      <c r="B287" s="2" t="s">
-        <v>813</v>
-      </c>
-      <c r="C287" s="2" t="s">
-        <v>814</v>
       </c>
     </row>
     <row r="288" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="B288" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="C288" s="2" t="s">
         <v>815</v>
-      </c>
-      <c r="B288" s="2" t="s">
-        <v>816</v>
-      </c>
-      <c r="C288" s="2" t="s">
-        <v>817</v>
       </c>
     </row>
     <row r="289" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="B289" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="C289" s="2" t="s">
         <v>818</v>
-      </c>
-      <c r="B289" s="2" t="s">
-        <v>819</v>
-      </c>
-      <c r="C289" s="2" t="s">
-        <v>820</v>
       </c>
     </row>
     <row r="290" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="B290" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="C290" s="2" t="s">
         <v>821</v>
-      </c>
-      <c r="B290" s="2" t="s">
-        <v>822</v>
-      </c>
-      <c r="C290" s="2" t="s">
-        <v>823</v>
       </c>
     </row>
     <row r="291" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="B291" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="C291" s="2" t="s">
         <v>824</v>
-      </c>
-      <c r="B291" s="2" t="s">
-        <v>825</v>
-      </c>
-      <c r="C291" s="2" t="s">
-        <v>826</v>
       </c>
     </row>
     <row r="292" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="B292" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="C292" s="2" t="s">
         <v>827</v>
-      </c>
-      <c r="B292" s="2" t="s">
-        <v>828</v>
-      </c>
-      <c r="C292" s="2" t="s">
-        <v>829</v>
       </c>
     </row>
     <row r="293" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="B293" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="C293" s="2" t="s">
         <v>830</v>
-      </c>
-      <c r="B293" s="2" t="s">
-        <v>831</v>
-      </c>
-      <c r="C293" s="2" t="s">
-        <v>832</v>
       </c>
     </row>
     <row r="294" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="B294" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="C294" s="2" t="s">
         <v>833</v>
-      </c>
-      <c r="B294" s="2" t="s">
-        <v>834</v>
-      </c>
-      <c r="C294" s="2" t="s">
-        <v>835</v>
       </c>
     </row>
     <row r="295" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="B295" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="C295" s="2" t="s">
         <v>836</v>
-      </c>
-      <c r="B295" s="2" t="s">
-        <v>837</v>
-      </c>
-      <c r="C295" s="2" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="296" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="B296" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="C296" s="2" t="s">
         <v>839</v>
-      </c>
-      <c r="B296" s="2" t="s">
-        <v>840</v>
-      </c>
-      <c r="C296" s="2" t="s">
-        <v>841</v>
       </c>
     </row>
     <row r="297" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="B297" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="C297" s="2" t="s">
         <v>842</v>
-      </c>
-      <c r="B297" s="2" t="s">
-        <v>843</v>
-      </c>
-      <c r="C297" s="2" t="s">
-        <v>844</v>
       </c>
     </row>
     <row r="298" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="B298" s="2" t="s">
+        <v>844</v>
+      </c>
+      <c r="C298" s="2" t="s">
         <v>845</v>
-      </c>
-      <c r="B298" s="2" t="s">
-        <v>846</v>
-      </c>
-      <c r="C298" s="2" t="s">
-        <v>847</v>
       </c>
     </row>
     <row r="299" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="B299" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="C299" s="2" t="s">
         <v>848</v>
-      </c>
-      <c r="B299" s="2" t="s">
-        <v>849</v>
-      </c>
-      <c r="C299" s="2" t="s">
-        <v>850</v>
       </c>
     </row>
     <row r="300" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
+        <v>849</v>
+      </c>
+      <c r="B300" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="C300" s="2" t="s">
         <v>851</v>
-      </c>
-      <c r="B300" s="2" t="s">
-        <v>852</v>
-      </c>
-      <c r="C300" s="2" t="s">
-        <v>853</v>
       </c>
     </row>
     <row r="301" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
+        <v>852</v>
+      </c>
+      <c r="B301" s="2" t="s">
+        <v>853</v>
+      </c>
+      <c r="C301" s="2" t="s">
         <v>854</v>
-      </c>
-      <c r="B301" s="2" t="s">
-        <v>855</v>
-      </c>
-      <c r="C301" s="2" t="s">
-        <v>856</v>
       </c>
     </row>
     <row r="302" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="B302" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="C302" s="2" t="s">
         <v>857</v>
-      </c>
-      <c r="B302" s="2" t="s">
-        <v>858</v>
-      </c>
-      <c r="C302" s="2" t="s">
-        <v>859</v>
       </c>
     </row>
     <row r="303" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="B303" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="C303" s="2" t="s">
         <v>860</v>
-      </c>
-      <c r="B303" s="2" t="s">
-        <v>861</v>
-      </c>
-      <c r="C303" s="2" t="s">
-        <v>862</v>
       </c>
     </row>
     <row r="304" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
+        <v>861</v>
+      </c>
+      <c r="B304" s="2" t="s">
+        <v>862</v>
+      </c>
+      <c r="C304" s="2" t="s">
         <v>863</v>
-      </c>
-      <c r="B304" s="2" t="s">
-        <v>864</v>
-      </c>
-      <c r="C304" s="2" t="s">
-        <v>865</v>
       </c>
     </row>
     <row r="305" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
+        <v>864</v>
+      </c>
+      <c r="B305" s="2" t="s">
+        <v>865</v>
+      </c>
+      <c r="C305" s="2" t="s">
         <v>866</v>
-      </c>
-      <c r="B305" s="2" t="s">
-        <v>867</v>
-      </c>
-      <c r="C305" s="2" t="s">
-        <v>868</v>
       </c>
     </row>
     <row r="306" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="B306" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="C306" s="2" t="s">
         <v>869</v>
-      </c>
-      <c r="B306" s="2" t="s">
-        <v>870</v>
-      </c>
-      <c r="C306" s="2" t="s">
-        <v>871</v>
       </c>
     </row>
     <row r="307" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="B307" s="2" t="s">
+        <v>871</v>
+      </c>
+      <c r="C307" s="2" t="s">
         <v>872</v>
-      </c>
-      <c r="B307" s="2" t="s">
-        <v>873</v>
-      </c>
-      <c r="C307" s="2" t="s">
-        <v>874</v>
       </c>
     </row>
     <row r="308" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
+        <v>873</v>
+      </c>
+      <c r="B308" s="2" t="s">
+        <v>874</v>
+      </c>
+      <c r="C308" s="2" t="s">
         <v>875</v>
-      </c>
-      <c r="B308" s="2" t="s">
-        <v>876</v>
-      </c>
-      <c r="C308" s="2" t="s">
-        <v>877</v>
       </c>
     </row>
     <row r="309" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
+        <v>876</v>
+      </c>
+      <c r="B309" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="C309" s="2" t="s">
         <v>878</v>
-      </c>
-      <c r="B309" s="2" t="s">
-        <v>879</v>
-      </c>
-      <c r="C309" s="2" t="s">
-        <v>880</v>
       </c>
     </row>
     <row r="310" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="B310" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="C310" s="2" t="s">
         <v>881</v>
-      </c>
-      <c r="B310" s="2" t="s">
-        <v>882</v>
-      </c>
-      <c r="C310" s="2" t="s">
-        <v>883</v>
       </c>
     </row>
     <row r="311" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="B311" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="C311" s="2" t="s">
         <v>884</v>
-      </c>
-      <c r="B311" s="2" t="s">
-        <v>885</v>
-      </c>
-      <c r="C311" s="2" t="s">
-        <v>886</v>
       </c>
     </row>
     <row r="312" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
+        <v>885</v>
+      </c>
+      <c r="B312" s="2" t="s">
+        <v>886</v>
+      </c>
+      <c r="C312" s="2" t="s">
         <v>887</v>
-      </c>
-      <c r="B312" s="2" t="s">
-        <v>888</v>
-      </c>
-      <c r="C312" s="2" t="s">
-        <v>889</v>
       </c>
     </row>
     <row r="313" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
+        <v>888</v>
+      </c>
+      <c r="B313" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="C313" s="2" t="s">
         <v>890</v>
-      </c>
-      <c r="B313" s="2" t="s">
-        <v>891</v>
-      </c>
-      <c r="C313" s="2" t="s">
-        <v>892</v>
       </c>
     </row>
     <row r="314" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="315" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
     </row>
     <row r="316" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="B316" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="C316" s="2" t="s">
         <v>896</v>
-      </c>
-      <c r="B316" s="2" t="s">
-        <v>897</v>
-      </c>
-      <c r="C316" s="2" t="s">
-        <v>898</v>
       </c>
     </row>
     <row r="317" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="B317" s="2" t="s">
+        <v>898</v>
+      </c>
+      <c r="C317" s="2" t="s">
         <v>899</v>
-      </c>
-      <c r="B317" s="2" t="s">
-        <v>900</v>
-      </c>
-      <c r="C317" s="2" t="s">
-        <v>901</v>
       </c>
     </row>
     <row r="318" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="B318" s="2" t="s">
         <v>155</v>
@@ -7920,95 +7971,95 @@
     </row>
     <row r="319" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
+        <v>901</v>
+      </c>
+      <c r="B319" s="2" t="s">
+        <v>902</v>
+      </c>
+      <c r="C319" s="2" t="s">
         <v>903</v>
-      </c>
-      <c r="B319" s="2" t="s">
-        <v>904</v>
-      </c>
-      <c r="C319" s="2" t="s">
-        <v>905</v>
       </c>
     </row>
     <row r="320" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
+        <v>904</v>
+      </c>
+      <c r="B320" s="2" t="s">
+        <v>905</v>
+      </c>
+      <c r="C320" s="2" t="s">
         <v>906</v>
-      </c>
-      <c r="B320" s="2" t="s">
-        <v>907</v>
-      </c>
-      <c r="C320" s="2" t="s">
-        <v>908</v>
       </c>
     </row>
     <row r="321" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
+        <v>907</v>
+      </c>
+      <c r="B321" s="2" t="s">
+        <v>908</v>
+      </c>
+      <c r="C321" s="2" t="s">
         <v>909</v>
-      </c>
-      <c r="B321" s="2" t="s">
-        <v>910</v>
-      </c>
-      <c r="C321" s="2" t="s">
-        <v>911</v>
       </c>
     </row>
     <row r="322" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
+        <v>910</v>
+      </c>
+      <c r="B322" s="2" t="s">
+        <v>911</v>
+      </c>
+      <c r="C322" s="2" t="s">
         <v>912</v>
-      </c>
-      <c r="B322" s="2" t="s">
-        <v>913</v>
-      </c>
-      <c r="C322" s="2" t="s">
-        <v>914</v>
       </c>
     </row>
     <row r="323" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
+        <v>913</v>
+      </c>
+      <c r="B323" s="2" t="s">
+        <v>914</v>
+      </c>
+      <c r="C323" s="2" t="s">
         <v>915</v>
-      </c>
-      <c r="B323" s="2" t="s">
-        <v>916</v>
-      </c>
-      <c r="C323" s="2" t="s">
-        <v>917</v>
       </c>
     </row>
     <row r="324" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
+        <v>916</v>
+      </c>
+      <c r="B324" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="C324" s="2" t="s">
         <v>918</v>
-      </c>
-      <c r="B324" s="2" t="s">
-        <v>919</v>
-      </c>
-      <c r="C324" s="2" t="s">
-        <v>920</v>
       </c>
     </row>
     <row r="325" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="B325" s="2" t="s">
+        <v>920</v>
+      </c>
+      <c r="C325" s="2" t="s">
         <v>921</v>
-      </c>
-      <c r="B325" s="2" t="s">
-        <v>922</v>
-      </c>
-      <c r="C325" s="2" t="s">
-        <v>923</v>
       </c>
     </row>
     <row r="326" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
+        <v>922</v>
+      </c>
+      <c r="B326" s="2" t="s">
+        <v>923</v>
+      </c>
+      <c r="C326" s="2" t="s">
         <v>924</v>
-      </c>
-      <c r="B326" s="2" t="s">
-        <v>925</v>
-      </c>
-      <c r="C326" s="2" t="s">
-        <v>926</v>
       </c>
     </row>
     <row r="327" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="B327" s="2" t="s">
         <v>210</v>
@@ -8019,497 +8070,497 @@
     </row>
     <row r="328" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
     </row>
     <row r="329" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
+        <v>928</v>
+      </c>
+      <c r="B329" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="C329" s="2" t="s">
         <v>930</v>
-      </c>
-      <c r="B329" s="2" t="s">
-        <v>931</v>
-      </c>
-      <c r="C329" s="2" t="s">
-        <v>932</v>
       </c>
     </row>
     <row r="330" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
+        <v>931</v>
+      </c>
+      <c r="B330" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="C330" s="2" t="s">
         <v>933</v>
-      </c>
-      <c r="B330" s="2" t="s">
-        <v>934</v>
-      </c>
-      <c r="C330" s="2" t="s">
-        <v>935</v>
       </c>
     </row>
     <row r="331" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="B331" s="2" t="s">
+        <v>935</v>
+      </c>
+      <c r="C331" s="2" t="s">
         <v>936</v>
-      </c>
-      <c r="B331" s="2" t="s">
-        <v>937</v>
-      </c>
-      <c r="C331" s="2" t="s">
-        <v>938</v>
       </c>
     </row>
     <row r="332" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="B332" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="C332" s="2" t="s">
         <v>939</v>
-      </c>
-      <c r="B332" s="2" t="s">
-        <v>940</v>
-      </c>
-      <c r="C332" s="2" t="s">
-        <v>941</v>
       </c>
     </row>
     <row r="333" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="B333" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="C333" s="2" t="s">
         <v>942</v>
-      </c>
-      <c r="B333" s="2" t="s">
-        <v>943</v>
-      </c>
-      <c r="C333" s="2" t="s">
-        <v>944</v>
       </c>
     </row>
     <row r="334" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="335" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
+        <v>944</v>
+      </c>
+      <c r="B335" s="2" t="s">
+        <v>945</v>
+      </c>
+      <c r="C335" s="2" t="s">
         <v>946</v>
-      </c>
-      <c r="B335" s="2" t="s">
-        <v>947</v>
-      </c>
-      <c r="C335" s="2" t="s">
-        <v>948</v>
       </c>
     </row>
     <row r="336" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
+        <v>947</v>
+      </c>
+      <c r="B336" s="2" t="s">
+        <v>948</v>
+      </c>
+      <c r="C336" s="2" t="s">
         <v>949</v>
-      </c>
-      <c r="B336" s="2" t="s">
-        <v>950</v>
-      </c>
-      <c r="C336" s="2" t="s">
-        <v>951</v>
       </c>
     </row>
     <row r="337" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
+        <v>950</v>
+      </c>
+      <c r="B337" s="2" t="s">
+        <v>951</v>
+      </c>
+      <c r="C337" s="2" t="s">
         <v>952</v>
-      </c>
-      <c r="B337" s="2" t="s">
-        <v>953</v>
-      </c>
-      <c r="C337" s="2" t="s">
-        <v>954</v>
       </c>
     </row>
     <row r="338" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
+        <v>953</v>
+      </c>
+      <c r="B338" s="2" t="s">
+        <v>954</v>
+      </c>
+      <c r="C338" s="2" t="s">
         <v>955</v>
-      </c>
-      <c r="B338" s="2" t="s">
-        <v>956</v>
-      </c>
-      <c r="C338" s="2" t="s">
-        <v>957</v>
       </c>
     </row>
     <row r="339" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
+        <v>956</v>
+      </c>
+      <c r="B339" s="2" t="s">
+        <v>957</v>
+      </c>
+      <c r="C339" s="2" t="s">
         <v>958</v>
-      </c>
-      <c r="B339" s="2" t="s">
-        <v>959</v>
-      </c>
-      <c r="C339" s="2" t="s">
-        <v>960</v>
       </c>
     </row>
     <row r="340" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
+        <v>959</v>
+      </c>
+      <c r="B340" s="2" t="s">
+        <v>960</v>
+      </c>
+      <c r="C340" s="2" t="s">
         <v>961</v>
-      </c>
-      <c r="B340" s="2" t="s">
-        <v>962</v>
-      </c>
-      <c r="C340" s="2" t="s">
-        <v>963</v>
       </c>
     </row>
     <row r="341" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
+        <v>962</v>
+      </c>
+      <c r="B341" s="2" t="s">
+        <v>963</v>
+      </c>
+      <c r="C341" s="2" t="s">
         <v>964</v>
-      </c>
-      <c r="B341" s="2" t="s">
-        <v>965</v>
-      </c>
-      <c r="C341" s="2" t="s">
-        <v>966</v>
       </c>
     </row>
     <row r="342" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
+        <v>965</v>
+      </c>
+      <c r="B342" s="2" t="s">
+        <v>966</v>
+      </c>
+      <c r="C342" s="2" t="s">
         <v>967</v>
-      </c>
-      <c r="B342" s="2" t="s">
-        <v>968</v>
-      </c>
-      <c r="C342" s="2" t="s">
-        <v>969</v>
       </c>
     </row>
     <row r="343" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="B343" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="C343" s="2" t="s">
         <v>970</v>
-      </c>
-      <c r="B343" s="2" t="s">
-        <v>971</v>
-      </c>
-      <c r="C343" s="2" t="s">
-        <v>972</v>
       </c>
     </row>
     <row r="344" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="B344" s="2" t="s">
+        <v>972</v>
+      </c>
+      <c r="C344" s="2" t="s">
         <v>973</v>
-      </c>
-      <c r="B344" s="2" t="s">
-        <v>974</v>
-      </c>
-      <c r="C344" s="2" t="s">
-        <v>975</v>
       </c>
     </row>
     <row r="345" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
+        <v>974</v>
+      </c>
+      <c r="B345" s="2" t="s">
+        <v>975</v>
+      </c>
+      <c r="C345" s="2" t="s">
         <v>976</v>
-      </c>
-      <c r="B345" s="2" t="s">
-        <v>977</v>
-      </c>
-      <c r="C345" s="2" t="s">
-        <v>978</v>
       </c>
     </row>
     <row r="346" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
+        <v>977</v>
+      </c>
+      <c r="B346" s="2" t="s">
+        <v>978</v>
+      </c>
+      <c r="C346" s="2" t="s">
         <v>979</v>
-      </c>
-      <c r="B346" s="2" t="s">
-        <v>980</v>
-      </c>
-      <c r="C346" s="2" t="s">
-        <v>981</v>
       </c>
     </row>
     <row r="347" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
+        <v>980</v>
+      </c>
+      <c r="B347" s="2" t="s">
+        <v>981</v>
+      </c>
+      <c r="C347" s="2" t="s">
         <v>982</v>
-      </c>
-      <c r="B347" s="2" t="s">
-        <v>983</v>
-      </c>
-      <c r="C347" s="2" t="s">
-        <v>984</v>
       </c>
     </row>
     <row r="348" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
+        <v>983</v>
+      </c>
+      <c r="B348" s="2" t="s">
+        <v>984</v>
+      </c>
+      <c r="C348" s="2" t="s">
         <v>985</v>
-      </c>
-      <c r="B348" s="2" t="s">
-        <v>986</v>
-      </c>
-      <c r="C348" s="2" t="s">
-        <v>987</v>
       </c>
     </row>
     <row r="349" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
+        <v>986</v>
+      </c>
+      <c r="B349" s="2" t="s">
+        <v>987</v>
+      </c>
+      <c r="C349" s="2" t="s">
         <v>988</v>
-      </c>
-      <c r="B349" s="2" t="s">
-        <v>989</v>
-      </c>
-      <c r="C349" s="2" t="s">
-        <v>990</v>
       </c>
     </row>
     <row r="350" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
+        <v>989</v>
+      </c>
+      <c r="B350" s="2" t="s">
+        <v>990</v>
+      </c>
+      <c r="C350" s="2" t="s">
         <v>991</v>
-      </c>
-      <c r="B350" s="2" t="s">
-        <v>992</v>
-      </c>
-      <c r="C350" s="2" t="s">
-        <v>993</v>
       </c>
     </row>
     <row r="351" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="352" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="B352" s="2" t="s">
+        <v>995</v>
+      </c>
+      <c r="C352" s="2" t="s">
         <v>996</v>
-      </c>
-      <c r="B352" s="2" t="s">
-        <v>997</v>
-      </c>
-      <c r="C352" s="2" t="s">
-        <v>998</v>
       </c>
     </row>
     <row r="353" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
+        <v>997</v>
+      </c>
+      <c r="B353" s="2" t="s">
+        <v>998</v>
+      </c>
+      <c r="C353" s="2" t="s">
         <v>999</v>
-      </c>
-      <c r="B353" s="2" t="s">
-        <v>1000</v>
-      </c>
-      <c r="C353" s="2" t="s">
-        <v>1001</v>
       </c>
     </row>
     <row r="354" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B354" s="2" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C354" s="2" t="s">
         <v>1002</v>
-      </c>
-      <c r="B354" s="2" t="s">
-        <v>1003</v>
-      </c>
-      <c r="C354" s="2" t="s">
-        <v>1004</v>
       </c>
     </row>
     <row r="355" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B355" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C355" s="2" t="s">
         <v>1005</v>
-      </c>
-      <c r="B355" s="2" t="s">
-        <v>1006</v>
-      </c>
-      <c r="C355" s="2" t="s">
-        <v>1007</v>
       </c>
     </row>
     <row r="356" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B356" s="2" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C356" s="2" t="s">
         <v>1008</v>
-      </c>
-      <c r="B356" s="2" t="s">
-        <v>1009</v>
-      </c>
-      <c r="C356" s="2" t="s">
-        <v>1010</v>
       </c>
     </row>
     <row r="357" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B357" s="2" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C357" s="2" t="s">
         <v>1011</v>
-      </c>
-      <c r="B357" s="2" t="s">
-        <v>1012</v>
-      </c>
-      <c r="C357" s="2" t="s">
-        <v>1013</v>
       </c>
     </row>
     <row r="358" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B358" s="2" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C358" s="2" t="s">
         <v>1014</v>
-      </c>
-      <c r="B358" s="2" t="s">
-        <v>1015</v>
-      </c>
-      <c r="C358" s="2" t="s">
-        <v>1016</v>
       </c>
     </row>
     <row r="359" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B359" s="2" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C359" s="2" t="s">
         <v>1017</v>
-      </c>
-      <c r="B359" s="2" t="s">
-        <v>1018</v>
-      </c>
-      <c r="C359" s="2" t="s">
-        <v>1019</v>
       </c>
     </row>
     <row r="360" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B360" s="2" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C360" s="2" t="s">
         <v>1020</v>
-      </c>
-      <c r="B360" s="2" t="s">
-        <v>1021</v>
-      </c>
-      <c r="C360" s="2" t="s">
-        <v>1022</v>
       </c>
     </row>
     <row r="361" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B361" s="2" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C361" s="2" t="s">
         <v>1023</v>
-      </c>
-      <c r="B361" s="2" t="s">
-        <v>1024</v>
-      </c>
-      <c r="C361" s="2" t="s">
-        <v>1025</v>
       </c>
     </row>
     <row r="362" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B362" s="2" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C362" s="2" t="s">
         <v>1026</v>
-      </c>
-      <c r="B362" s="2" t="s">
-        <v>1027</v>
-      </c>
-      <c r="C362" s="2" t="s">
-        <v>1028</v>
       </c>
     </row>
     <row r="363" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B363" s="2" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C363" s="2" t="s">
         <v>1029</v>
-      </c>
-      <c r="B363" s="2" t="s">
-        <v>1030</v>
-      </c>
-      <c r="C363" s="2" t="s">
-        <v>1031</v>
       </c>
     </row>
     <row r="364" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B364" s="2" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C364" s="2" t="s">
         <v>1032</v>
-      </c>
-      <c r="B364" s="2" t="s">
-        <v>1033</v>
-      </c>
-      <c r="C364" s="2" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="365" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B365" s="2" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C365" s="2" t="s">
         <v>1035</v>
-      </c>
-      <c r="B365" s="2" t="s">
-        <v>1036</v>
-      </c>
-      <c r="C365" s="2" t="s">
-        <v>1037</v>
       </c>
     </row>
     <row r="366" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B366" s="2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C366" s="2" t="s">
         <v>1038</v>
-      </c>
-      <c r="B366" s="2" t="s">
-        <v>1039</v>
-      </c>
-      <c r="C366" s="2" t="s">
-        <v>1040</v>
       </c>
     </row>
     <row r="367" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B367" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C367" s="2" t="s">
         <v>1041</v>
-      </c>
-      <c r="B367" s="2" t="s">
-        <v>1042</v>
-      </c>
-      <c r="C367" s="2" t="s">
-        <v>1043</v>
       </c>
     </row>
     <row r="368" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B368" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C368" s="2" t="s">
         <v>1044</v>
-      </c>
-      <c r="B368" s="2" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C368" s="2" t="s">
-        <v>1046</v>
       </c>
     </row>
     <row r="369" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B369" s="2" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C369" s="2" t="s">
         <v>1047</v>
-      </c>
-      <c r="B369" s="2" t="s">
-        <v>1048</v>
-      </c>
-      <c r="C369" s="2" t="s">
-        <v>1049</v>
       </c>
     </row>
     <row r="370" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B370" s="2" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C370" s="2" t="s">
         <v>1050</v>
-      </c>
-      <c r="B370" s="2" t="s">
-        <v>1051</v>
-      </c>
-      <c r="C370" s="2" t="s">
-        <v>1052</v>
       </c>
     </row>
     <row r="371" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B371" s="2" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C371" s="2" t="s">
         <v>1053</v>
-      </c>
-      <c r="B371" s="2" t="s">
-        <v>1054</v>
-      </c>
-      <c r="C371" s="2" t="s">
-        <v>1055</v>
       </c>
     </row>
     <row r="372" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B372" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C372" s="2" t="s">
         <v>1056</v>
-      </c>
-      <c r="B372" s="2" t="s">
-        <v>775</v>
-      </c>
-      <c r="C372" s="2" t="s">
-        <v>776</v>
       </c>
     </row>
     <row r="373" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8517,43 +8568,43 @@
         <v>1057</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>1058</v>
+        <v>773</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>1059</v>
+        <v>774</v>
       </c>
     </row>
     <row r="374" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B374" s="2" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C374" s="2" t="s">
         <v>1060</v>
-      </c>
-      <c r="B374" s="2" t="s">
-        <v>1061</v>
-      </c>
-      <c r="C374" s="2" t="s">
-        <v>1062</v>
       </c>
     </row>
     <row r="375" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B375" s="2" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C375" s="2" t="s">
         <v>1063</v>
-      </c>
-      <c r="B375" s="2" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C375" s="2" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="376" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A376" s="2" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B376" s="2" t="s">
         <v>1065</v>
       </c>
-      <c r="B376" s="2" t="s">
-        <v>149</v>
-      </c>
       <c r="C376" s="2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="377" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8561,21 +8612,21 @@
         <v>1066</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>1067</v>
+        <v>149</v>
       </c>
       <c r="C377" s="2" t="s">
-        <v>1068</v>
+        <v>150</v>
       </c>
     </row>
     <row r="378" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B378" s="2" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C378" s="2" t="s">
         <v>1069</v>
-      </c>
-      <c r="B378" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C378" s="2" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="379" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8583,21 +8634,21 @@
         <v>1070</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>1071</v>
+        <v>155</v>
       </c>
       <c r="C379" s="2" t="s">
-        <v>1072</v>
+        <v>156</v>
       </c>
     </row>
     <row r="380" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A380" s="2" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B380" s="2" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C380" s="2" t="s">
         <v>1073</v>
-      </c>
-      <c r="B380" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="C380" s="2" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="381" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8605,32 +8656,32 @@
         <v>1074</v>
       </c>
       <c r="B381" s="2" t="s">
-        <v>1075</v>
+        <v>216</v>
       </c>
       <c r="C381" s="2" t="s">
-        <v>1076</v>
+        <v>217</v>
       </c>
     </row>
     <row r="382" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A382" s="2" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B382" s="2" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C382" s="2" t="s">
         <v>1077</v>
-      </c>
-      <c r="B382" s="2" t="s">
-        <v>888</v>
-      </c>
-      <c r="C382" s="2" t="s">
-        <v>1078</v>
       </c>
     </row>
     <row r="383" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A383" s="2" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B383" s="2" t="s">
+        <v>886</v>
+      </c>
+      <c r="C383" s="2" t="s">
         <v>1079</v>
-      </c>
-      <c r="B383" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="C383" s="2" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="384" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8638,10 +8689,10 @@
         <v>1080</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="385" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8649,32 +8700,32 @@
         <v>1081</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>1082</v>
+        <v>231</v>
       </c>
       <c r="C385" s="2" t="s">
-        <v>1083</v>
+        <v>232</v>
       </c>
     </row>
     <row r="386" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A386" s="2" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B386" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C386" s="2" t="s">
         <v>1084</v>
-      </c>
-      <c r="B386" s="2" t="s">
-        <v>1085</v>
-      </c>
-      <c r="C386" s="2" t="s">
-        <v>1086</v>
       </c>
     </row>
     <row r="387" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A387" s="2" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B387" s="2" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C387" s="2" t="s">
         <v>1087</v>
-      </c>
-      <c r="B387" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="C387" s="2" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="388" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8682,21 +8733,21 @@
         <v>1088</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>1089</v>
+        <v>247</v>
       </c>
       <c r="C388" s="2" t="s">
-        <v>1090</v>
+        <v>248</v>
       </c>
     </row>
     <row r="389" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A389" s="2" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B389" s="2" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C389" s="2" t="s">
         <v>1091</v>
-      </c>
-      <c r="B389" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="C389" s="2" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="390" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8704,54 +8755,54 @@
         <v>1092</v>
       </c>
       <c r="B390" s="2" t="s">
-        <v>1093</v>
+        <v>253</v>
       </c>
       <c r="C390" s="2" t="s">
-        <v>1094</v>
+        <v>254</v>
       </c>
     </row>
     <row r="391" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A391" s="2" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B391" s="2" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C391" s="2" t="s">
         <v>1095</v>
-      </c>
-      <c r="B391" s="2" t="s">
-        <v>1096</v>
-      </c>
-      <c r="C391" s="2" t="s">
-        <v>1096</v>
       </c>
     </row>
     <row r="392" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A392" s="2" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B392" s="2" t="s">
         <v>1097</v>
       </c>
-      <c r="B392" s="2" t="s">
-        <v>1098</v>
-      </c>
       <c r="C392" s="2" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="393" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A393" s="2" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B393" s="2" t="s">
         <v>1099</v>
       </c>
-      <c r="B393" s="2" t="s">
-        <v>1100</v>
-      </c>
       <c r="C393" s="2" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="394" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A394" s="2" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B394" s="2" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C394" s="2" t="s">
         <v>1102</v>
-      </c>
-      <c r="B394" s="2" t="s">
-        <v>1100</v>
-      </c>
-      <c r="C394" s="2" t="s">
-        <v>1101</v>
       </c>
     </row>
     <row r="395" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8759,186 +8810,186 @@
         <v>1103</v>
       </c>
       <c r="B395" s="2" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="C395" s="2" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="396" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A396" s="2" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B396" s="2" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C396" s="2" t="s">
         <v>1106</v>
-      </c>
-      <c r="B396" s="2" t="s">
-        <v>1107</v>
-      </c>
-      <c r="C396" s="2" t="s">
-        <v>1108</v>
       </c>
     </row>
     <row r="397" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A397" s="2" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B397" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C397" s="2" t="s">
         <v>1109</v>
-      </c>
-      <c r="B397" s="2" t="s">
-        <v>1110</v>
-      </c>
-      <c r="C397" s="2" t="s">
-        <v>1111</v>
       </c>
     </row>
     <row r="398" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A398" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B398" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C398" s="2" t="s">
         <v>1112</v>
-      </c>
-      <c r="B398" s="2" t="s">
-        <v>1113</v>
-      </c>
-      <c r="C398" s="2" t="s">
-        <v>1114</v>
       </c>
     </row>
     <row r="399" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A399" s="2" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B399" s="2" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C399" s="2" t="s">
         <v>1115</v>
-      </c>
-      <c r="B399" s="2" t="s">
-        <v>1116</v>
-      </c>
-      <c r="C399" s="2" t="s">
-        <v>1117</v>
       </c>
     </row>
     <row r="400" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A400" s="2" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B400" s="2" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C400" s="2" t="s">
         <v>1118</v>
-      </c>
-      <c r="B400" s="2" t="s">
-        <v>1119</v>
-      </c>
-      <c r="C400" s="2" t="s">
-        <v>1120</v>
       </c>
     </row>
     <row r="401" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A401" s="2" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B401" s="2" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C401" s="2" t="s">
         <v>1121</v>
-      </c>
-      <c r="B401" s="2" t="s">
-        <v>1122</v>
-      </c>
-      <c r="C401" s="2" t="s">
-        <v>1123</v>
       </c>
     </row>
     <row r="402" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A402" s="2" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B402" s="2" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C402" s="2" t="s">
         <v>1124</v>
-      </c>
-      <c r="B402" s="2" t="s">
-        <v>1125</v>
-      </c>
-      <c r="C402" s="2" t="s">
-        <v>1126</v>
       </c>
     </row>
     <row r="403" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A403" s="2" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B403" s="2" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C403" s="2" t="s">
         <v>1127</v>
-      </c>
-      <c r="B403" s="2" t="s">
-        <v>1128</v>
-      </c>
-      <c r="C403" s="2" t="s">
-        <v>1129</v>
       </c>
     </row>
     <row r="404" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A404" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B404" s="2" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C404" s="2" t="s">
         <v>1130</v>
-      </c>
-      <c r="B404" s="2" t="s">
-        <v>1131</v>
-      </c>
-      <c r="C404" s="2" t="s">
-        <v>1132</v>
       </c>
     </row>
     <row r="405" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A405" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B405" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C405" s="2" t="s">
         <v>1133</v>
-      </c>
-      <c r="B405" s="2" t="s">
-        <v>1134</v>
-      </c>
-      <c r="C405" s="2" t="s">
-        <v>1135</v>
       </c>
     </row>
     <row r="406" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A406" s="2" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B406" s="2" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C406" s="2" t="s">
         <v>1136</v>
-      </c>
-      <c r="B406" s="2" t="s">
-        <v>1137</v>
-      </c>
-      <c r="C406" s="2" t="s">
-        <v>1120</v>
       </c>
     </row>
     <row r="407" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A407" s="2" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B407" s="2" t="s">
         <v>1138</v>
       </c>
-      <c r="B407" s="2" t="s">
-        <v>1139</v>
-      </c>
       <c r="C407" s="2" t="s">
-        <v>1140</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="408" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A408" s="2" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B408" s="2" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C408" s="2" t="s">
         <v>1141</v>
-      </c>
-      <c r="B408" s="2" t="s">
-        <v>1142</v>
-      </c>
-      <c r="C408" s="2" t="s">
-        <v>1126</v>
       </c>
     </row>
     <row r="409" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A409" s="2" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B409" s="2" t="s">
         <v>1143</v>
       </c>
-      <c r="B409" s="2" t="s">
-        <v>1144</v>
-      </c>
       <c r="C409" s="2" t="s">
-        <v>1145</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="410" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A410" s="2" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B410" s="2" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C410" s="2" t="s">
         <v>1146</v>
-      </c>
-      <c r="B410" s="2" t="s">
-        <v>1147</v>
-      </c>
-      <c r="C410" s="2" t="s">
-        <v>1148</v>
       </c>
     </row>
     <row r="411" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A411" s="2" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B411" s="2" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C411" s="2" t="s">
         <v>1149</v>
-      </c>
-      <c r="B411" s="2" t="s">
-        <v>1016</v>
-      </c>
-      <c r="C411" s="2" t="s">
-        <v>1016</v>
       </c>
     </row>
     <row r="412" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8946,76 +8997,76 @@
         <v>1150</v>
       </c>
       <c r="B412" s="2" t="s">
-        <v>1151</v>
+        <v>1014</v>
       </c>
       <c r="C412" s="2" t="s">
-        <v>1152</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="413" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A413" s="2" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B413" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C413" s="2" t="s">
         <v>1153</v>
-      </c>
-      <c r="B413" s="2" t="s">
-        <v>1154</v>
-      </c>
-      <c r="C413" s="2" t="s">
-        <v>1155</v>
       </c>
     </row>
     <row r="414" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A414" s="2" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B414" s="2" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C414" s="2" t="s">
         <v>1156</v>
-      </c>
-      <c r="B414" s="2" t="s">
-        <v>1157</v>
-      </c>
-      <c r="C414" s="2" t="s">
-        <v>1158</v>
       </c>
     </row>
     <row r="415" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A415" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B415" s="2" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C415" s="2" t="s">
         <v>1159</v>
-      </c>
-      <c r="B415" s="2" t="s">
-        <v>1160</v>
-      </c>
-      <c r="C415" s="2" t="s">
-        <v>1161</v>
       </c>
     </row>
     <row r="416" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A416" s="2" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B416" s="2" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C416" s="2" t="s">
         <v>1162</v>
-      </c>
-      <c r="B416" s="2" t="s">
-        <v>1163</v>
-      </c>
-      <c r="C416" s="2" t="s">
-        <v>1164</v>
       </c>
     </row>
     <row r="417" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A417" s="2" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B417" s="2" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C417" s="2" t="s">
         <v>1165</v>
-      </c>
-      <c r="B417" s="2" t="s">
-        <v>1166</v>
-      </c>
-      <c r="C417" s="2" t="s">
-        <v>1167</v>
       </c>
     </row>
     <row r="418" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A418" s="2" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B418" s="2" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C418" s="2" t="s">
         <v>1168</v>
-      </c>
-      <c r="B418" s="2" t="s">
-        <v>1048</v>
-      </c>
-      <c r="C418" s="2" t="s">
-        <v>1049</v>
       </c>
     </row>
     <row r="419" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9023,87 +9074,87 @@
         <v>1169</v>
       </c>
       <c r="B419" s="2" t="s">
-        <v>1170</v>
+        <v>1049</v>
       </c>
       <c r="C419" s="2" t="s">
-        <v>1171</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="420" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A420" s="2" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B420" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C420" s="2" t="s">
         <v>1172</v>
-      </c>
-      <c r="B420" s="2" t="s">
-        <v>1173</v>
-      </c>
-      <c r="C420" s="2" t="s">
-        <v>1174</v>
       </c>
     </row>
     <row r="421" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A421" s="2" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B421" s="2" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C421" s="2" t="s">
         <v>1175</v>
-      </c>
-      <c r="B421" s="2" t="s">
-        <v>1176</v>
-      </c>
-      <c r="C421" s="2" t="s">
-        <v>1177</v>
       </c>
     </row>
     <row r="422" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A422" s="2" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B422" s="2" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C422" s="2" t="s">
         <v>1178</v>
-      </c>
-      <c r="B422" s="2" t="s">
-        <v>1179</v>
-      </c>
-      <c r="C422" s="2" t="s">
-        <v>1180</v>
       </c>
     </row>
     <row r="423" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A423" s="2" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B423" s="2" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C423" s="2" t="s">
         <v>1181</v>
-      </c>
-      <c r="B423" s="2" t="s">
-        <v>1182</v>
-      </c>
-      <c r="C423" s="2" t="s">
-        <v>1183</v>
       </c>
     </row>
     <row r="424" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A424" s="2" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B424" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C424" s="2" t="s">
         <v>1184</v>
-      </c>
-      <c r="B424" s="2" t="s">
-        <v>1185</v>
-      </c>
-      <c r="C424" s="2" t="s">
-        <v>1186</v>
       </c>
     </row>
     <row r="425" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A425" s="2" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B425" s="2" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C425" s="2" t="s">
         <v>1187</v>
-      </c>
-      <c r="B425" s="2" t="s">
-        <v>1188</v>
-      </c>
-      <c r="C425" s="2" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="426" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A426" s="2" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B426" s="2" t="s">
         <v>1189</v>
       </c>
-      <c r="B426" s="2" t="s">
-        <v>149</v>
-      </c>
       <c r="C426" s="2" t="s">
-        <v>150</v>
+        <v>181</v>
       </c>
     </row>
     <row r="427" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9111,10 +9162,10 @@
         <v>1190</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C427" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="428" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9122,10 +9173,10 @@
         <v>1191</v>
       </c>
       <c r="B428" s="2" t="s">
-        <v>520</v>
+        <v>152</v>
       </c>
       <c r="C428" s="2" t="s">
-        <v>521</v>
+        <v>153</v>
       </c>
     </row>
     <row r="429" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9133,219 +9184,219 @@
         <v>1192</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>1193</v>
+        <v>515</v>
       </c>
       <c r="C429" s="2" t="s">
-        <v>1194</v>
+        <v>516</v>
       </c>
     </row>
     <row r="430" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A430" s="2" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B430" s="2" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C430" s="2" t="s">
         <v>1195</v>
-      </c>
-      <c r="B430" s="2" t="s">
-        <v>1196</v>
-      </c>
-      <c r="C430" s="2" t="s">
-        <v>1197</v>
       </c>
     </row>
     <row r="431" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A431" s="2" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B431" s="2" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C431" s="2" t="s">
         <v>1198</v>
-      </c>
-      <c r="B431" s="2" t="s">
-        <v>1199</v>
-      </c>
-      <c r="C431" s="2" t="s">
-        <v>1200</v>
       </c>
     </row>
     <row r="432" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A432" s="2" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B432" s="2" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C432" s="2" t="s">
         <v>1201</v>
-      </c>
-      <c r="B432" s="2" t="s">
-        <v>1202</v>
-      </c>
-      <c r="C432" s="2" t="s">
-        <v>1203</v>
       </c>
     </row>
     <row r="433" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A433" s="2" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B433" s="2" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C433" s="2" t="s">
         <v>1204</v>
-      </c>
-      <c r="B433" s="2" t="s">
-        <v>1205</v>
-      </c>
-      <c r="C433" s="2" t="s">
-        <v>1206</v>
       </c>
     </row>
     <row r="434" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A434" s="2" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B434" s="2" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C434" s="2" t="s">
         <v>1207</v>
-      </c>
-      <c r="B434" s="2" t="s">
-        <v>1208</v>
-      </c>
-      <c r="C434" s="2" t="s">
-        <v>1209</v>
       </c>
     </row>
     <row r="435" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A435" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B435" s="2" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C435" s="2" t="s">
         <v>1210</v>
-      </c>
-      <c r="B435" s="2" t="s">
-        <v>1211</v>
-      </c>
-      <c r="C435" s="2" t="s">
-        <v>1212</v>
       </c>
     </row>
     <row r="436" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A436" s="2" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B436" s="2" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C436" s="2" t="s">
         <v>1213</v>
-      </c>
-      <c r="B436" s="2" t="s">
-        <v>1214</v>
-      </c>
-      <c r="C436" s="2" t="s">
-        <v>1215</v>
       </c>
     </row>
     <row r="437" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A437" s="2" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B437" s="2" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C437" s="2" t="s">
         <v>1216</v>
-      </c>
-      <c r="B437" s="2" t="s">
-        <v>1217</v>
-      </c>
-      <c r="C437" s="2" t="s">
-        <v>1218</v>
       </c>
     </row>
     <row r="438" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A438" s="2" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B438" s="2" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C438" s="2" t="s">
         <v>1219</v>
-      </c>
-      <c r="B438" s="2" t="s">
-        <v>1220</v>
-      </c>
-      <c r="C438" s="2" t="s">
-        <v>1221</v>
       </c>
     </row>
     <row r="439" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A439" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B439" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C439" s="2" t="s">
         <v>1222</v>
-      </c>
-      <c r="B439" s="2" t="s">
-        <v>1223</v>
-      </c>
-      <c r="C439" s="2" t="s">
-        <v>1224</v>
       </c>
     </row>
     <row r="440" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A440" s="2" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B440" s="2" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C440" s="2" t="s">
         <v>1225</v>
-      </c>
-      <c r="B440" s="2" t="s">
-        <v>1226</v>
-      </c>
-      <c r="C440" s="2" t="s">
-        <v>1227</v>
       </c>
     </row>
     <row r="441" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A441" s="2" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B441" s="2" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C441" s="2" t="s">
         <v>1228</v>
-      </c>
-      <c r="B441" s="2" t="s">
-        <v>1229</v>
-      </c>
-      <c r="C441" s="2" t="s">
-        <v>1230</v>
       </c>
     </row>
     <row r="442" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A442" s="2" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B442" s="2" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C442" s="2" t="s">
         <v>1231</v>
-      </c>
-      <c r="B442" s="2" t="s">
-        <v>1232</v>
-      </c>
-      <c r="C442" s="2" t="s">
-        <v>1233</v>
       </c>
     </row>
     <row r="443" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A443" s="2" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B443" s="2" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C443" s="2" t="s">
         <v>1234</v>
-      </c>
-      <c r="B443" s="2" t="s">
-        <v>1235</v>
-      </c>
-      <c r="C443" s="2" t="s">
-        <v>1236</v>
       </c>
     </row>
     <row r="444" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A444" s="2" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B444" s="2" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C444" s="2" t="s">
         <v>1237</v>
-      </c>
-      <c r="B444" s="2" t="s">
-        <v>1238</v>
-      </c>
-      <c r="C444" s="2" t="s">
-        <v>1239</v>
       </c>
     </row>
     <row r="445" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A445" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B445" s="2" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C445" s="2" t="s">
         <v>1240</v>
-      </c>
-      <c r="B445" s="2" t="s">
-        <v>1241</v>
-      </c>
-      <c r="C445" s="2" t="s">
-        <v>1242</v>
       </c>
     </row>
     <row r="446" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A446" s="2" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B446" s="2" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C446" s="2" t="s">
         <v>1243</v>
-      </c>
-      <c r="B446" s="2" t="s">
-        <v>1244</v>
-      </c>
-      <c r="C446" s="2" t="s">
-        <v>1245</v>
       </c>
     </row>
     <row r="447" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A447" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B447" s="2" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C447" s="2" t="s">
         <v>1246</v>
-      </c>
-      <c r="B447" s="2" t="s">
-        <v>1247</v>
-      </c>
-      <c r="C447" s="2" t="s">
-        <v>1248</v>
       </c>
     </row>
     <row r="448" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A448" s="2" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B448" s="2" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C448" s="2" t="s">
         <v>1249</v>
-      </c>
-      <c r="B448" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C448" s="2" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="449" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9353,21 +9404,21 @@
         <v>1250</v>
       </c>
       <c r="B449" s="2" t="s">
-        <v>1251</v>
+        <v>43</v>
       </c>
       <c r="C449" s="2" t="s">
-        <v>898</v>
+        <v>44</v>
       </c>
     </row>
     <row r="450" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A450" s="2" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B450" s="2" t="s">
         <v>1252</v>
       </c>
-      <c r="B450" s="2" t="s">
-        <v>1193</v>
-      </c>
       <c r="C450" s="2" t="s">
-        <v>1194</v>
+        <v>896</v>
       </c>
     </row>
     <row r="451" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9375,32 +9426,32 @@
         <v>1253</v>
       </c>
       <c r="B451" s="2" t="s">
-        <v>1254</v>
+        <v>1194</v>
       </c>
       <c r="C451" s="2" t="s">
-        <v>1007</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="452" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A452" s="2" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B452" s="2" t="s">
         <v>1255</v>
       </c>
-      <c r="B452" s="2" t="s">
-        <v>1256</v>
-      </c>
       <c r="C452" s="2" t="s">
-        <v>1257</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="453" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A453" s="2" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B453" s="2" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C453" s="2" t="s">
         <v>1258</v>
-      </c>
-      <c r="B453" s="2" t="s">
-        <v>1196</v>
-      </c>
-      <c r="C453" s="2" t="s">
-        <v>1197</v>
       </c>
     </row>
     <row r="454" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9408,10 +9459,10 @@
         <v>1259</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>158</v>
+        <v>1197</v>
       </c>
       <c r="C454" s="2" t="s">
-        <v>158</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="455" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9419,65 +9470,65 @@
         <v>1260</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>1261</v>
+        <v>158</v>
       </c>
       <c r="C455" s="2" t="s">
-        <v>1262</v>
+        <v>158</v>
       </c>
     </row>
     <row r="456" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A456" s="2" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B456" s="2" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C456" s="2" t="s">
         <v>1263</v>
-      </c>
-      <c r="B456" s="2" t="s">
-        <v>1264</v>
-      </c>
-      <c r="C456" s="2" t="s">
-        <v>1265</v>
       </c>
     </row>
     <row r="457" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A457" s="2" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B457" s="2" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C457" s="2" t="s">
         <v>1266</v>
-      </c>
-      <c r="B457" s="2" t="s">
-        <v>1267</v>
-      </c>
-      <c r="C457" s="2" t="s">
-        <v>1268</v>
       </c>
     </row>
     <row r="458" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A458" s="2" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B458" s="2" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C458" s="2" t="s">
         <v>1269</v>
-      </c>
-      <c r="B458" s="2" t="s">
-        <v>1270</v>
-      </c>
-      <c r="C458" s="2" t="s">
-        <v>1271</v>
       </c>
     </row>
     <row r="459" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A459" s="2" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B459" s="2" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C459" s="2" t="s">
         <v>1272</v>
-      </c>
-      <c r="B459" s="2" t="s">
-        <v>1273</v>
-      </c>
-      <c r="C459" s="2" t="s">
-        <v>1274</v>
       </c>
     </row>
     <row r="460" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A460" s="2" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B460" s="2" t="s">
+        <v>1274</v>
+      </c>
+      <c r="C460" s="2" t="s">
         <v>1275</v>
-      </c>
-      <c r="B460" s="2" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C460" s="2" t="s">
-        <v>1046</v>
       </c>
     </row>
     <row r="461" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9485,10 +9536,10 @@
         <v>1276</v>
       </c>
       <c r="B461" s="2" t="s">
-        <v>4</v>
+        <v>1046</v>
       </c>
       <c r="C461" s="2" t="s">
-        <v>5</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="462" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9496,10 +9547,10 @@
         <v>1277</v>
       </c>
       <c r="B462" s="2" t="s">
-        <v>1036</v>
+        <v>4</v>
       </c>
       <c r="C462" s="2" t="s">
-        <v>1037</v>
+        <v>5</v>
       </c>
     </row>
     <row r="463" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9507,10 +9558,10 @@
         <v>1278</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>1048</v>
+        <v>1034</v>
       </c>
       <c r="C463" s="2" t="s">
-        <v>1049</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="464" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9518,32 +9569,32 @@
         <v>1279</v>
       </c>
       <c r="B464" s="2" t="s">
-        <v>1280</v>
+        <v>1049</v>
       </c>
       <c r="C464" s="2" t="s">
-        <v>1281</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="465" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A465" s="2" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B465" s="2" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C465" s="2" t="s">
         <v>1282</v>
-      </c>
-      <c r="B465" s="2" t="s">
-        <v>1283</v>
-      </c>
-      <c r="C465" s="2" t="s">
-        <v>1284</v>
       </c>
     </row>
     <row r="466" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A466" s="2" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B466" s="2" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C466" s="2" t="s">
         <v>1285</v>
-      </c>
-      <c r="B466" s="2" t="s">
-        <v>1051</v>
-      </c>
-      <c r="C466" s="2" t="s">
-        <v>1052</v>
       </c>
     </row>
     <row r="467" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9551,142 +9602,142 @@
         <v>1286</v>
       </c>
       <c r="B467" s="2" t="s">
-        <v>1287</v>
+        <v>1052</v>
       </c>
       <c r="C467" s="2" t="s">
-        <v>1288</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="468" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A468" s="2" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B468" s="2" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C468" s="2" t="s">
         <v>1289</v>
-      </c>
-      <c r="B468" s="2" t="s">
-        <v>1054</v>
-      </c>
-      <c r="C468" s="2" t="s">
-        <v>1290</v>
       </c>
     </row>
     <row r="469" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A469" s="2" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B469" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C469" s="2" t="s">
         <v>1291</v>
-      </c>
-      <c r="B469" s="2" t="s">
-        <v>1006</v>
-      </c>
-      <c r="C469" s="2" t="s">
-        <v>1292</v>
       </c>
     </row>
     <row r="470" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A470" s="2" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B470" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C470" s="2" t="s">
         <v>1293</v>
-      </c>
-      <c r="B470" s="2" t="s">
-        <v>1294</v>
-      </c>
-      <c r="C470" s="2" t="s">
-        <v>1295</v>
       </c>
     </row>
     <row r="471" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A471" s="2" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B471" s="2" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C471" s="2" t="s">
         <v>1296</v>
-      </c>
-      <c r="B471" s="2" t="s">
-        <v>1297</v>
-      </c>
-      <c r="C471" s="2" t="s">
-        <v>1298</v>
       </c>
     </row>
     <row r="472" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A472" s="2" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B472" s="2" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C472" s="2" t="s">
         <v>1299</v>
-      </c>
-      <c r="B472" s="2" t="s">
-        <v>1300</v>
-      </c>
-      <c r="C472" s="2" t="s">
-        <v>1301</v>
       </c>
     </row>
     <row r="473" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A473" s="2" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B473" s="2" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C473" s="2" t="s">
         <v>1302</v>
-      </c>
-      <c r="B473" s="2" t="s">
-        <v>1303</v>
-      </c>
-      <c r="C473" s="2" t="s">
-        <v>1304</v>
       </c>
     </row>
     <row r="474" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A474" s="2" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B474" s="2" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C474" s="2" t="s">
         <v>1305</v>
-      </c>
-      <c r="B474" s="2" t="s">
-        <v>1306</v>
-      </c>
-      <c r="C474" s="2" t="s">
-        <v>1307</v>
       </c>
     </row>
     <row r="475" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A475" s="2" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B475" s="2" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C475" s="2" t="s">
         <v>1308</v>
-      </c>
-      <c r="B475" s="2" t="s">
-        <v>1309</v>
-      </c>
-      <c r="C475" s="2" t="s">
-        <v>1310</v>
       </c>
     </row>
     <row r="476" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A476" s="2" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B476" s="2" t="s">
+        <v>1310</v>
+      </c>
+      <c r="C476" s="2" t="s">
         <v>1311</v>
-      </c>
-      <c r="B476" s="2" t="s">
-        <v>1312</v>
-      </c>
-      <c r="C476" s="2" t="s">
-        <v>1313</v>
       </c>
     </row>
     <row r="477" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A477" s="2" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B477" s="2" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C477" s="2" t="s">
         <v>1314</v>
-      </c>
-      <c r="B477" s="2" t="s">
-        <v>1315</v>
-      </c>
-      <c r="C477" s="2" t="s">
-        <v>1316</v>
       </c>
     </row>
     <row r="478" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A478" s="2" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B478" s="2" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C478" s="2" t="s">
         <v>1317</v>
-      </c>
-      <c r="B478" s="2" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C478" s="2" t="s">
-        <v>1319</v>
       </c>
     </row>
     <row r="479" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A479" s="2" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B479" s="2" t="s">
+        <v>1319</v>
+      </c>
+      <c r="C479" s="2" t="s">
         <v>1320</v>
-      </c>
-      <c r="B479" s="2" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C479" s="2" t="s">
-        <v>1046</v>
       </c>
     </row>
     <row r="480" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9694,10 +9745,10 @@
         <v>1321</v>
       </c>
       <c r="B480" s="2" t="s">
-        <v>4</v>
+        <v>1046</v>
       </c>
       <c r="C480" s="2" t="s">
-        <v>5</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="481" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9705,10 +9756,10 @@
         <v>1322</v>
       </c>
       <c r="B481" s="2" t="s">
-        <v>1051</v>
+        <v>4</v>
       </c>
       <c r="C481" s="2" t="s">
-        <v>1052</v>
+        <v>5</v>
       </c>
     </row>
     <row r="482" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9716,43 +9767,43 @@
         <v>1323</v>
       </c>
       <c r="B482" s="2" t="s">
-        <v>1324</v>
+        <v>1052</v>
       </c>
       <c r="C482" s="2" t="s">
-        <v>1325</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="483" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A483" s="2" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B483" s="2" t="s">
+        <v>1325</v>
+      </c>
+      <c r="C483" s="2" t="s">
         <v>1326</v>
-      </c>
-      <c r="B483" s="2" t="s">
-        <v>1327</v>
-      </c>
-      <c r="C483" s="2" t="s">
-        <v>1328</v>
       </c>
     </row>
     <row r="484" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A484" s="2" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B484" s="2" t="s">
+        <v>1328</v>
+      </c>
+      <c r="C484" s="2" t="s">
         <v>1329</v>
-      </c>
-      <c r="B484" s="2" t="s">
-        <v>1330</v>
-      </c>
-      <c r="C484" s="2" t="s">
-        <v>1331</v>
       </c>
     </row>
     <row r="485" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A485" s="2" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B485" s="2" t="s">
+        <v>1331</v>
+      </c>
+      <c r="C485" s="2" t="s">
         <v>1332</v>
-      </c>
-      <c r="B485" s="2" t="s">
-        <v>1303</v>
-      </c>
-      <c r="C485" s="2" t="s">
-        <v>1304</v>
       </c>
     </row>
     <row r="486" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9760,21 +9811,98 @@
         <v>1333</v>
       </c>
       <c r="B486" s="2" t="s">
-        <v>1334</v>
+        <v>1304</v>
       </c>
       <c r="C486" s="2" t="s">
-        <v>1335</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="487" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A487" s="2" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B487" s="2" t="s">
+        <v>1335</v>
+      </c>
+      <c r="C487" s="2" t="s">
         <v>1336</v>
       </c>
-      <c r="B487" s="2" t="s">
+    </row>
+    <row r="488" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A488" s="2" t="s">
         <v>1337</v>
       </c>
-      <c r="C487" s="2" t="s">
+      <c r="B488" s="2" t="s">
         <v>1338</v>
+      </c>
+      <c r="C488" s="2" t="s">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="489" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A489" s="2" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B489" s="2" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C489" s="2" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="490" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A490" s="2" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B490" s="2" t="s">
+        <v>1342</v>
+      </c>
+      <c r="C490" s="2" t="s">
+        <v>1343</v>
+      </c>
+    </row>
+    <row r="491" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A491" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B491" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="C491" s="2" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="492" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A492" s="2" t="s">
+        <v>1347</v>
+      </c>
+      <c r="B492" s="2" t="s">
+        <v>1348</v>
+      </c>
+      <c r="C492" s="2" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="493" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A493" s="2" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B493" s="2" t="s">
+        <v>1351</v>
+      </c>
+      <c r="C493" s="2" t="s">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="494" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A494" s="2" t="s">
+        <v>1353</v>
+      </c>
+      <c r="B494" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="C494" s="2" t="s">
+        <v>1355</v>
       </c>
     </row>
   </sheetData>

--- a/apps/workspace-web/i18n.xlsx
+++ b/apps/workspace-web/i18n.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1482" uniqueCount="1356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1584" uniqueCount="1448">
   <si>
     <t>key</t>
   </si>
@@ -3466,6 +3466,15 @@
     <t>route.wishlist</t>
   </si>
   <si>
+    <t>route.announcements</t>
+  </si>
+  <si>
+    <t>公告通知</t>
+  </si>
+  <si>
+    <t>Announcements</t>
+  </si>
+  <si>
     <t>header.openMenu</t>
   </si>
   <si>
@@ -4079,6 +4088,273 @@
   </si>
   <si>
     <t>{storeName}: {title}</t>
+  </si>
+  <si>
+    <t>announcements.createTitle</t>
+  </si>
+  <si>
+    <t>發布公告</t>
+  </si>
+  <si>
+    <t>Post an announcement</t>
+  </si>
+  <si>
+    <t>announcements.createDesc</t>
+  </si>
+  <si>
+    <t>通知所有追蹤你商店的粉絲，可立即發送或預定發送時間。</t>
+  </si>
+  <si>
+    <t>Notify everyone following your store. Send now or schedule for later.</t>
+  </si>
+  <si>
+    <t>announcements.fieldTitle</t>
+  </si>
+  <si>
+    <t>公告標題</t>
+  </si>
+  <si>
+    <t>announcements.fieldTitlePlaceholder</t>
+  </si>
+  <si>
+    <t>例如：夏季特賣開跑</t>
+  </si>
+  <si>
+    <t>e.g. Summer sale is on</t>
+  </si>
+  <si>
+    <t>announcements.fieldMessage</t>
+  </si>
+  <si>
+    <t>公告內文</t>
+  </si>
+  <si>
+    <t>Message</t>
+  </si>
+  <si>
+    <t>announcements.fieldMessagePlaceholder</t>
+  </si>
+  <si>
+    <t>想對追蹤者說的話…</t>
+  </si>
+  <si>
+    <t>What do you want to tell your followers…</t>
+  </si>
+  <si>
+    <t>announcements.fieldScheduledAt</t>
+  </si>
+  <si>
+    <t>預定發送時間</t>
+  </si>
+  <si>
+    <t>Scheduled time</t>
+  </si>
+  <si>
+    <t>announcements.fieldScheduledAtPlaceholder</t>
+  </si>
+  <si>
+    <t>留空表示立即發送</t>
+  </si>
+  <si>
+    <t>Leave empty to send now</t>
+  </si>
+  <si>
+    <t>announcements.fieldScheduledAtHint</t>
+  </si>
+  <si>
+    <t>設定未來時間可預約發送；留空則立即通知追蹤者。</t>
+  </si>
+  <si>
+    <t>Pick a future time to schedule; leave empty to notify followers immediately.</t>
+  </si>
+  <si>
+    <t>announcements.submitNow</t>
+  </si>
+  <si>
+    <t>立即發送</t>
+  </si>
+  <si>
+    <t>Send now</t>
+  </si>
+  <si>
+    <t>announcements.submitScheduled</t>
+  </si>
+  <si>
+    <t>預約發送</t>
+  </si>
+  <si>
+    <t>Schedule</t>
+  </si>
+  <si>
+    <t>announcements.colTitle</t>
+  </si>
+  <si>
+    <t>announcements.colScheduledAt</t>
+  </si>
+  <si>
+    <t>預定時間</t>
+  </si>
+  <si>
+    <t>Scheduled at</t>
+  </si>
+  <si>
+    <t>announcements.colDispatchedAt</t>
+  </si>
+  <si>
+    <t>發送時間</t>
+  </si>
+  <si>
+    <t>Dispatched at</t>
+  </si>
+  <si>
+    <t>announcements.colActions</t>
+  </si>
+  <si>
+    <t>announcements.cancelAction</t>
+  </si>
+  <si>
+    <t>取消發送</t>
+  </si>
+  <si>
+    <t>Cancel sending</t>
+  </si>
+  <si>
+    <t>announcements.cancelConfirmTitle</t>
+  </si>
+  <si>
+    <t>取消這則公告？</t>
+  </si>
+  <si>
+    <t>Cancel this announcement?</t>
+  </si>
+  <si>
+    <t>announcements.cancelConfirmDesc</t>
+  </si>
+  <si>
+    <t>「{title}」尚未發送，取消後將不會通知追蹤者。</t>
+  </si>
+  <si>
+    <t>"{title}" has not been sent yet. Cancelling will skip notifying followers.</t>
+  </si>
+  <si>
+    <t>announcements.emptyTitle</t>
+  </si>
+  <si>
+    <t>還沒有公告</t>
+  </si>
+  <si>
+    <t>No announcements yet</t>
+  </si>
+  <si>
+    <t>announcements.emptyDesc</t>
+  </si>
+  <si>
+    <t>發布第一則公告，讓追蹤者知道你的最新動態。</t>
+  </si>
+  <si>
+    <t>Post your first announcement to keep followers in the loop.</t>
+  </si>
+  <si>
+    <t>announcements.msgCreated</t>
+  </si>
+  <si>
+    <t>公告已送出，將立即通知追蹤者</t>
+  </si>
+  <si>
+    <t>Announcement sent — followers will be notified shortly</t>
+  </si>
+  <si>
+    <t>announcements.msgScheduled</t>
+  </si>
+  <si>
+    <t>公告已預約，將於預定時間發送</t>
+  </si>
+  <si>
+    <t>Announcement scheduled</t>
+  </si>
+  <si>
+    <t>announcements.msgScheduledInPast</t>
+  </si>
+  <si>
+    <t>預定時間須晚於現在</t>
+  </si>
+  <si>
+    <t>Scheduled time must be in the future</t>
+  </si>
+  <si>
+    <t>announcements.msgCancelled</t>
+  </si>
+  <si>
+    <t>公告已取消</t>
+  </si>
+  <si>
+    <t>Announcement cancelled</t>
+  </si>
+  <si>
+    <t>announcements.msgLoadFailed</t>
+  </si>
+  <si>
+    <t>公告列表載入失敗</t>
+  </si>
+  <si>
+    <t>Failed to load announcements</t>
+  </si>
+  <si>
+    <t>announcements.msgCreateFailed</t>
+  </si>
+  <si>
+    <t>公告建立失敗</t>
+  </si>
+  <si>
+    <t>Failed to create announcement</t>
+  </si>
+  <si>
+    <t>announcements.msgCancelFailed</t>
+  </si>
+  <si>
+    <t>公告取消失敗</t>
+  </si>
+  <si>
+    <t>Failed to cancel announcement</t>
+  </si>
+  <si>
+    <t>requestStatus.all</t>
+  </si>
+  <si>
+    <t>requestStatus.pending</t>
+  </si>
+  <si>
+    <t>待發送</t>
+  </si>
+  <si>
+    <t>requestStatus.dispatched</t>
+  </si>
+  <si>
+    <t>已發送</t>
+  </si>
+  <si>
+    <t>Dispatched</t>
+  </si>
+  <si>
+    <t>requestStatus.cancelled</t>
+  </si>
+  <si>
+    <t>requestStatus.failed</t>
+  </si>
+  <si>
+    <t>發送失敗</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
+    <t>requestStatus.unknown</t>
+  </si>
+  <si>
+    <t>未知</t>
+  </si>
+  <si>
+    <t>Unknown</t>
   </si>
 </sst>
 </file>
@@ -4464,7 +4740,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C494"/>
+  <dimension ref="A1:C528"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -9074,21 +9350,21 @@
         <v>1169</v>
       </c>
       <c r="B419" s="2" t="s">
-        <v>1049</v>
+        <v>1170</v>
       </c>
       <c r="C419" s="2" t="s">
-        <v>1050</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="420" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A420" s="2" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="B420" s="2" t="s">
-        <v>1171</v>
+        <v>1049</v>
       </c>
       <c r="C420" s="2" t="s">
-        <v>1172</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="421" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9154,51 +9430,51 @@
         <v>1189</v>
       </c>
       <c r="C426" s="2" t="s">
-        <v>181</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="427" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A427" s="2" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>149</v>
+        <v>1192</v>
       </c>
       <c r="C427" s="2" t="s">
-        <v>150</v>
+        <v>181</v>
       </c>
     </row>
     <row r="428" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A428" s="2" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="B428" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C428" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="429" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A429" s="2" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>515</v>
+        <v>152</v>
       </c>
       <c r="C429" s="2" t="s">
-        <v>516</v>
+        <v>153</v>
       </c>
     </row>
     <row r="430" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A430" s="2" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="B430" s="2" t="s">
-        <v>1194</v>
+        <v>515</v>
       </c>
       <c r="C430" s="2" t="s">
-        <v>1195</v>
+        <v>516</v>
       </c>
     </row>
     <row r="431" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9404,54 +9680,54 @@
         <v>1250</v>
       </c>
       <c r="B449" s="2" t="s">
-        <v>43</v>
+        <v>1251</v>
       </c>
       <c r="C449" s="2" t="s">
-        <v>44</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="450" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A450" s="2" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="B450" s="2" t="s">
-        <v>1252</v>
+        <v>43</v>
       </c>
       <c r="C450" s="2" t="s">
-        <v>896</v>
+        <v>44</v>
       </c>
     </row>
     <row r="451" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A451" s="2" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="B451" s="2" t="s">
-        <v>1194</v>
+        <v>1255</v>
       </c>
       <c r="C451" s="2" t="s">
-        <v>1195</v>
+        <v>896</v>
       </c>
     </row>
     <row r="452" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A452" s="2" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="B452" s="2" t="s">
-        <v>1255</v>
+        <v>1197</v>
       </c>
       <c r="C452" s="2" t="s">
-        <v>1005</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="453" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A453" s="2" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="C453" s="2" t="s">
-        <v>1258</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="454" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9459,32 +9735,32 @@
         <v>1259</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>1197</v>
+        <v>1260</v>
       </c>
       <c r="C454" s="2" t="s">
-        <v>1198</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="455" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A455" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>158</v>
+        <v>1200</v>
       </c>
       <c r="C455" s="2" t="s">
-        <v>158</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="456" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A456" s="2" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="B456" s="2" t="s">
-        <v>1262</v>
+        <v>158</v>
       </c>
       <c r="C456" s="2" t="s">
-        <v>1263</v>
+        <v>158</v>
       </c>
     </row>
     <row r="457" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9536,54 +9812,54 @@
         <v>1276</v>
       </c>
       <c r="B461" s="2" t="s">
-        <v>1046</v>
+        <v>1277</v>
       </c>
       <c r="C461" s="2" t="s">
-        <v>1047</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="462" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A462" s="2" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="B462" s="2" t="s">
-        <v>4</v>
+        <v>1046</v>
       </c>
       <c r="C462" s="2" t="s">
-        <v>5</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="463" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A463" s="2" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>1034</v>
+        <v>4</v>
       </c>
       <c r="C463" s="2" t="s">
-        <v>1035</v>
+        <v>5</v>
       </c>
     </row>
     <row r="464" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A464" s="2" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="B464" s="2" t="s">
-        <v>1049</v>
+        <v>1034</v>
       </c>
       <c r="C464" s="2" t="s">
-        <v>1050</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="465" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A465" s="2" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="B465" s="2" t="s">
-        <v>1281</v>
+        <v>1049</v>
       </c>
       <c r="C465" s="2" t="s">
-        <v>1282</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="466" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9602,21 +9878,21 @@
         <v>1286</v>
       </c>
       <c r="B467" s="2" t="s">
-        <v>1052</v>
+        <v>1287</v>
       </c>
       <c r="C467" s="2" t="s">
-        <v>1053</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="468" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A468" s="2" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="B468" s="2" t="s">
-        <v>1288</v>
+        <v>1052</v>
       </c>
       <c r="C468" s="2" t="s">
-        <v>1289</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="469" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9624,29 +9900,29 @@
         <v>1290</v>
       </c>
       <c r="B469" s="2" t="s">
-        <v>1055</v>
+        <v>1291</v>
       </c>
       <c r="C469" s="2" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="470" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A470" s="2" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="B470" s="2" t="s">
-        <v>1004</v>
+        <v>1055</v>
       </c>
       <c r="C470" s="2" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="471" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A471" s="2" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="B471" s="2" t="s">
-        <v>1295</v>
+        <v>1004</v>
       </c>
       <c r="C471" s="2" t="s">
         <v>1296</v>
@@ -9745,43 +10021,43 @@
         <v>1321</v>
       </c>
       <c r="B480" s="2" t="s">
-        <v>1046</v>
+        <v>1322</v>
       </c>
       <c r="C480" s="2" t="s">
-        <v>1047</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="481" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A481" s="2" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="B481" s="2" t="s">
-        <v>4</v>
+        <v>1046</v>
       </c>
       <c r="C481" s="2" t="s">
-        <v>5</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="482" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A482" s="2" t="s">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="B482" s="2" t="s">
-        <v>1052</v>
+        <v>4</v>
       </c>
       <c r="C482" s="2" t="s">
-        <v>1053</v>
+        <v>5</v>
       </c>
     </row>
     <row r="483" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A483" s="2" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
       <c r="B483" s="2" t="s">
-        <v>1325</v>
+        <v>1052</v>
       </c>
       <c r="C483" s="2" t="s">
-        <v>1326</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="484" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9811,21 +10087,21 @@
         <v>1333</v>
       </c>
       <c r="B486" s="2" t="s">
-        <v>1304</v>
+        <v>1334</v>
       </c>
       <c r="C486" s="2" t="s">
-        <v>1305</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="487" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A487" s="2" t="s">
-        <v>1334</v>
+        <v>1336</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>1335</v>
+        <v>1307</v>
       </c>
       <c r="C487" s="2" t="s">
-        <v>1336</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="488" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9844,21 +10120,21 @@
         <v>1340</v>
       </c>
       <c r="B489" s="2" t="s">
-        <v>1158</v>
+        <v>1341</v>
       </c>
       <c r="C489" s="2" t="s">
-        <v>1159</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="490" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A490" s="2" t="s">
-        <v>1341</v>
+        <v>1343</v>
       </c>
       <c r="B490" s="2" t="s">
-        <v>1342</v>
+        <v>1161</v>
       </c>
       <c r="C490" s="2" t="s">
-        <v>1343</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="491" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9903,6 +10179,380 @@
       </c>
       <c r="C494" s="2" t="s">
         <v>1355</v>
+      </c>
+    </row>
+    <row r="495" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A495" s="2" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B495" s="2" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C495" s="2" t="s">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="496" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A496" s="2" t="s">
+        <v>1359</v>
+      </c>
+      <c r="B496" s="2" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C496" s="2" t="s">
+        <v>1361</v>
+      </c>
+    </row>
+    <row r="497" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A497" s="2" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B497" s="2" t="s">
+        <v>1363</v>
+      </c>
+      <c r="C497" s="2" t="s">
+        <v>1364</v>
+      </c>
+    </row>
+    <row r="498" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A498" s="2" t="s">
+        <v>1365</v>
+      </c>
+      <c r="B498" s="2" t="s">
+        <v>1366</v>
+      </c>
+      <c r="C498" s="2" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="499" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A499" s="2" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B499" s="2" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C499" s="2" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="500" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A500" s="2" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B500" s="2" t="s">
+        <v>1371</v>
+      </c>
+      <c r="C500" s="2" t="s">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="501" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A501" s="2" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B501" s="2" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C501" s="2" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="502" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A502" s="2" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B502" s="2" t="s">
+        <v>1377</v>
+      </c>
+      <c r="C502" s="2" t="s">
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="503" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A503" s="2" t="s">
+        <v>1379</v>
+      </c>
+      <c r="B503" s="2" t="s">
+        <v>1380</v>
+      </c>
+      <c r="C503" s="2" t="s">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="504" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A504" s="2" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B504" s="2" t="s">
+        <v>1383</v>
+      </c>
+      <c r="C504" s="2" t="s">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="505" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A505" s="2" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B505" s="2" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C505" s="2" t="s">
+        <v>1387</v>
+      </c>
+    </row>
+    <row r="506" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A506" s="2" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B506" s="2" t="s">
+        <v>1389</v>
+      </c>
+      <c r="C506" s="2" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="507" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A507" s="2" t="s">
+        <v>1391</v>
+      </c>
+      <c r="B507" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="C507" s="2" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="508" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A508" s="2" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B508" s="2" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C508" s="2" t="s">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="509" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A509" s="2" t="s">
+        <v>1395</v>
+      </c>
+      <c r="B509" s="2" t="s">
+        <v>1396</v>
+      </c>
+      <c r="C509" s="2" t="s">
+        <v>1397</v>
+      </c>
+    </row>
+    <row r="510" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A510" s="2" t="s">
+        <v>1398</v>
+      </c>
+      <c r="B510" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C510" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="511" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A511" s="2" t="s">
+        <v>1399</v>
+      </c>
+      <c r="B511" s="2" t="s">
+        <v>1400</v>
+      </c>
+      <c r="C511" s="2" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="512" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A512" s="2" t="s">
+        <v>1402</v>
+      </c>
+      <c r="B512" s="2" t="s">
+        <v>1403</v>
+      </c>
+      <c r="C512" s="2" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="513" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A513" s="2" t="s">
+        <v>1405</v>
+      </c>
+      <c r="B513" s="2" t="s">
+        <v>1406</v>
+      </c>
+      <c r="C513" s="2" t="s">
+        <v>1407</v>
+      </c>
+    </row>
+    <row r="514" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A514" s="2" t="s">
+        <v>1408</v>
+      </c>
+      <c r="B514" s="2" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C514" s="2" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="515" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A515" s="2" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B515" s="2" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C515" s="2" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="516" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A516" s="2" t="s">
+        <v>1414</v>
+      </c>
+      <c r="B516" s="2" t="s">
+        <v>1415</v>
+      </c>
+      <c r="C516" s="2" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="517" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A517" s="2" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B517" s="2" t="s">
+        <v>1418</v>
+      </c>
+      <c r="C517" s="2" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="518" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A518" s="2" t="s">
+        <v>1420</v>
+      </c>
+      <c r="B518" s="2" t="s">
+        <v>1421</v>
+      </c>
+      <c r="C518" s="2" t="s">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="519" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A519" s="2" t="s">
+        <v>1423</v>
+      </c>
+      <c r="B519" s="2" t="s">
+        <v>1424</v>
+      </c>
+      <c r="C519" s="2" t="s">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="520" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A520" s="2" t="s">
+        <v>1426</v>
+      </c>
+      <c r="B520" s="2" t="s">
+        <v>1427</v>
+      </c>
+      <c r="C520" s="2" t="s">
+        <v>1428</v>
+      </c>
+    </row>
+    <row r="521" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A521" s="2" t="s">
+        <v>1429</v>
+      </c>
+      <c r="B521" s="2" t="s">
+        <v>1430</v>
+      </c>
+      <c r="C521" s="2" t="s">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="522" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A522" s="2" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B522" s="2" t="s">
+        <v>1433</v>
+      </c>
+      <c r="C522" s="2" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="523" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A523" s="2" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B523" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C523" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="524" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A524" s="2" t="s">
+        <v>1436</v>
+      </c>
+      <c r="B524" s="2" t="s">
+        <v>1437</v>
+      </c>
+      <c r="C524" s="2" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="525" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A525" s="2" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B525" s="2" t="s">
+        <v>1439</v>
+      </c>
+      <c r="C525" s="2" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="526" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A526" s="2" t="s">
+        <v>1441</v>
+      </c>
+      <c r="B526" s="2" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C526" s="2" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="527" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A527" s="2" t="s">
+        <v>1442</v>
+      </c>
+      <c r="B527" s="2" t="s">
+        <v>1443</v>
+      </c>
+      <c r="C527" s="2" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="528" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A528" s="2" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B528" s="2" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C528" s="2" t="s">
+        <v>1447</v>
       </c>
     </row>
   </sheetData>

--- a/apps/workspace-web/i18n.xlsx
+++ b/apps/workspace-web/i18n.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1584" uniqueCount="1448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1947" uniqueCount="1740">
   <si>
     <t>key</t>
   </si>
@@ -148,6 +148,24 @@
     <t>All</t>
   </si>
   <si>
+    <t>common.perPagePrefix</t>
+  </si>
+  <si>
+    <t>每頁</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>common.perPageSuffix</t>
+  </si>
+  <si>
+    <t>筆</t>
+  </si>
+  <si>
+    <t>/ page</t>
+  </si>
+  <si>
     <t>storeError.actionFailed</t>
   </si>
   <si>
@@ -292,6 +310,24 @@
     <t>Failed to load download links, please try again later.</t>
   </si>
   <si>
+    <t>storeError.loadWishlistFailed</t>
+  </si>
+  <si>
+    <t>載入願望清單失敗，請稍後再試。</t>
+  </si>
+  <si>
+    <t>Failed to load wishlist, please try again later.</t>
+  </si>
+  <si>
+    <t>storeError.removeWishlistFailed</t>
+  </si>
+  <si>
+    <t>移除收藏失敗，請稍後再試。</t>
+  </si>
+  <si>
+    <t>Failed to remove from wishlist, please try again later.</t>
+  </si>
+  <si>
     <t>storeError.loadProductsFailed</t>
   </si>
   <si>
@@ -3085,6 +3121,15 @@
     <t>Add to cart</t>
   </si>
   <si>
+    <t>wishlist.viewProduct</t>
+  </si>
+  <si>
+    <t>前往商品頁</t>
+  </si>
+  <si>
+    <t>View product</t>
+  </si>
+  <si>
     <t>wishlist.emptyTitle</t>
   </si>
   <si>
@@ -3406,6 +3451,24 @@
     <t>Resource usage</t>
   </si>
   <si>
+    <t>route.legalDocs</t>
+  </si>
+  <si>
+    <t>條款管理</t>
+  </si>
+  <si>
+    <t>Legal Documents</t>
+  </si>
+  <si>
+    <t>route.faqCategories</t>
+  </si>
+  <si>
+    <t>常見問題分類</t>
+  </si>
+  <si>
+    <t>FAQ Categories</t>
+  </si>
+  <si>
     <t>route.auditLog</t>
   </si>
   <si>
@@ -3475,6 +3538,15 @@
     <t>Announcements</t>
   </si>
   <si>
+    <t>route.faqs</t>
+  </si>
+  <si>
+    <t>常見問題</t>
+  </si>
+  <si>
+    <t>FAQ</t>
+  </si>
+  <si>
     <t>header.openMenu</t>
   </si>
   <si>
@@ -4355,6 +4427,810 @@
   </si>
   <si>
     <t>Unknown</t>
+  </si>
+  <si>
+    <t>legalDocs.type</t>
+  </si>
+  <si>
+    <t>文件類型</t>
+  </si>
+  <si>
+    <t>Document type</t>
+  </si>
+  <si>
+    <t>legalDocs.typeTerms</t>
+  </si>
+  <si>
+    <t>服務條款</t>
+  </si>
+  <si>
+    <t>Terms of Service</t>
+  </si>
+  <si>
+    <t>legalDocs.typePrivacy</t>
+  </si>
+  <si>
+    <t>隱私權政策</t>
+  </si>
+  <si>
+    <t>Privacy Policy</t>
+  </si>
+  <si>
+    <t>legalDocs.statusDraft</t>
+  </si>
+  <si>
+    <t>legalDocs.statusActive</t>
+  </si>
+  <si>
+    <t>legalDocs.statusInactive</t>
+  </si>
+  <si>
+    <t>Inactive</t>
+  </si>
+  <si>
+    <t>legalDocs.filterAllTypes</t>
+  </si>
+  <si>
+    <t>全部類型</t>
+  </si>
+  <si>
+    <t>All types</t>
+  </si>
+  <si>
+    <t>legalDocs.filterAllStatuses</t>
+  </si>
+  <si>
+    <t>legalDocs.colDocument</t>
+  </si>
+  <si>
+    <t>文件</t>
+  </si>
+  <si>
+    <t>Document</t>
+  </si>
+  <si>
+    <t>legalDocs.colVersion</t>
+  </si>
+  <si>
+    <t>版本</t>
+  </si>
+  <si>
+    <t>Version</t>
+  </si>
+  <si>
+    <t>legalDocs.colActivatedAt</t>
+  </si>
+  <si>
+    <t>啟用時間</t>
+  </si>
+  <si>
+    <t>Activated at</t>
+  </si>
+  <si>
+    <t>legalDocs.colUpdatedAt</t>
+  </si>
+  <si>
+    <t>更新時間</t>
+  </si>
+  <si>
+    <t>Updated at</t>
+  </si>
+  <si>
+    <t>legalDocs.colActions</t>
+  </si>
+  <si>
+    <t>legalDocs.emptyTitle</t>
+  </si>
+  <si>
+    <t>尚無法律文件</t>
+  </si>
+  <si>
+    <t>No legal documents yet</t>
+  </si>
+  <si>
+    <t>legalDocs.emptyDesc</t>
+  </si>
+  <si>
+    <t>點右上角「新增草稿」建立第一個版本</t>
+  </si>
+  <si>
+    <t>Click "New draft" to create the first version</t>
+  </si>
+  <si>
+    <t>legalDocs.newDraft</t>
+  </si>
+  <si>
+    <t>新增草稿</t>
+  </si>
+  <si>
+    <t>New draft</t>
+  </si>
+  <si>
+    <t>legalDocs.createTitle</t>
+  </si>
+  <si>
+    <t>新增條款草稿</t>
+  </si>
+  <si>
+    <t>New legal draft</t>
+  </si>
+  <si>
+    <t>legalDocs.editTitle</t>
+  </si>
+  <si>
+    <t>編輯條款草稿</t>
+  </si>
+  <si>
+    <t>Edit legal draft</t>
+  </si>
+  <si>
+    <t>legalDocs.titleLabel</t>
+  </si>
+  <si>
+    <t>legalDocs.titlePlaceholder</t>
+  </si>
+  <si>
+    <t>例如：服務條款</t>
+  </si>
+  <si>
+    <t>e.g. Terms of Service</t>
+  </si>
+  <si>
+    <t>legalDocs.contentLabel</t>
+  </si>
+  <si>
+    <t>內容</t>
+  </si>
+  <si>
+    <t>Content</t>
+  </si>
+  <si>
+    <t>legalDocs.contentPlaceholder</t>
+  </si>
+  <si>
+    <t>以「## 」開頭的行為章節標題、「- 」開頭為列點，其餘為段落</t>
+  </si>
+  <si>
+    <t>Lines starting with "## " are section headings, "- " are list items, others are paragraphs</t>
+  </si>
+  <si>
+    <t>legalDocs.contentHint</t>
+  </si>
+  <si>
+    <t>「## 」開頭＝章節標題（自動編號）、「- 」開頭＝列點；文件啟用後即不可修改，只能另建新版本</t>
+  </si>
+  <si>
+    <t>"## " = section heading (auto numbered), "- " = list item; once activated a version becomes immutable — create a new draft instead</t>
+  </si>
+  <si>
+    <t>legalDocs.create</t>
+  </si>
+  <si>
+    <t>建立草稿</t>
+  </si>
+  <si>
+    <t>Create draft</t>
+  </si>
+  <si>
+    <t>legalDocs.save</t>
+  </si>
+  <si>
+    <t>legalDocs.view</t>
+  </si>
+  <si>
+    <t>檢視內容</t>
+  </si>
+  <si>
+    <t>View content</t>
+  </si>
+  <si>
+    <t>legalDocs.activate</t>
+  </si>
+  <si>
+    <t>啟用</t>
+  </si>
+  <si>
+    <t>Activate</t>
+  </si>
+  <si>
+    <t>legalDocs.deactivate</t>
+  </si>
+  <si>
+    <t>停用</t>
+  </si>
+  <si>
+    <t>Deactivate</t>
+  </si>
+  <si>
+    <t>legalDocs.activateConfirm</t>
+  </si>
+  <si>
+    <t>啟用後此版本將對外生效，同類型現行版本會自動停用；既有會員登入時需重新同意。確定啟用？</t>
+  </si>
+  <si>
+    <t>Activating publishes this version and deactivates the current one of the same type; existing members must re-consent at sign-in. Continue?</t>
+  </si>
+  <si>
+    <t>legalDocs.deactivateConfirm</t>
+  </si>
+  <si>
+    <t>停用後前台將沒有生效中的版本可呈現。確定停用？</t>
+  </si>
+  <si>
+    <t>After deactivation there will be no active version to display. Continue?</t>
+  </si>
+  <si>
+    <t>legalDocs.valTitleRequired</t>
+  </si>
+  <si>
+    <t>請輸入標題</t>
+  </si>
+  <si>
+    <t>Title is required</t>
+  </si>
+  <si>
+    <t>legalDocs.valContentRequired</t>
+  </si>
+  <si>
+    <t>請輸入內容</t>
+  </si>
+  <si>
+    <t>Content is required</t>
+  </si>
+  <si>
+    <t>legalDocs.msgLoadFailed</t>
+  </si>
+  <si>
+    <t>載入失敗，請稍後再試</t>
+  </si>
+  <si>
+    <t>Failed to load, please try again later</t>
+  </si>
+  <si>
+    <t>legalDocs.msgActionFailed</t>
+  </si>
+  <si>
+    <t>操作失敗，請稍後再試</t>
+  </si>
+  <si>
+    <t>Action failed, please try again later</t>
+  </si>
+  <si>
+    <t>legalDocs.msgCreated</t>
+  </si>
+  <si>
+    <t>草稿已建立</t>
+  </si>
+  <si>
+    <t>Draft created</t>
+  </si>
+  <si>
+    <t>legalDocs.msgUpdated</t>
+  </si>
+  <si>
+    <t>草稿已更新</t>
+  </si>
+  <si>
+    <t>Draft updated</t>
+  </si>
+  <si>
+    <t>legalDocs.msgCreateFailed</t>
+  </si>
+  <si>
+    <t>建立失敗</t>
+  </si>
+  <si>
+    <t>Failed to create</t>
+  </si>
+  <si>
+    <t>legalDocs.msgUpdateFailed</t>
+  </si>
+  <si>
+    <t>Failed to update</t>
+  </si>
+  <si>
+    <t>legalDocs.msgActivated</t>
+  </si>
+  <si>
+    <t>已啟用此版本</t>
+  </si>
+  <si>
+    <t>Version activated</t>
+  </si>
+  <si>
+    <t>legalDocs.msgDeactivated</t>
+  </si>
+  <si>
+    <t>已停用此版本</t>
+  </si>
+  <si>
+    <t>Version deactivated</t>
+  </si>
+  <si>
+    <t>legalDocs.previewLabel</t>
+  </si>
+  <si>
+    <t>預覽</t>
+  </si>
+  <si>
+    <t>Preview</t>
+  </si>
+  <si>
+    <t>legalDocs.previewEmpty</t>
+  </si>
+  <si>
+    <t>輸入內容後即時預覽最終呈現樣式</t>
+  </si>
+  <si>
+    <t>Type content to see a live preview of the final layout</t>
+  </si>
+  <si>
+    <t>faqs.newItem</t>
+  </si>
+  <si>
+    <t>新增問答</t>
+  </si>
+  <si>
+    <t>New Q&amp;A</t>
+  </si>
+  <si>
+    <t>faqs.createTitle</t>
+  </si>
+  <si>
+    <t>新增常見問題</t>
+  </si>
+  <si>
+    <t>New FAQ</t>
+  </si>
+  <si>
+    <t>faqs.editTitle</t>
+  </si>
+  <si>
+    <t>編輯常見問題</t>
+  </si>
+  <si>
+    <t>Edit FAQ</t>
+  </si>
+  <si>
+    <t>faqs.category</t>
+  </si>
+  <si>
+    <t>主題分類</t>
+  </si>
+  <si>
+    <t>faqs.categoryPlaceholder</t>
+  </si>
+  <si>
+    <t>選擇主題分類</t>
+  </si>
+  <si>
+    <t>Select a category</t>
+  </si>
+  <si>
+    <t>faqs.filterAllCategories</t>
+  </si>
+  <si>
+    <t>全部主題</t>
+  </si>
+  <si>
+    <t>All categories</t>
+  </si>
+  <si>
+    <t>faqs.filterAllStatuses</t>
+  </si>
+  <si>
+    <t>faqs.statusPublished</t>
+  </si>
+  <si>
+    <t>已發布</t>
+  </si>
+  <si>
+    <t>faqs.statusHidden</t>
+  </si>
+  <si>
+    <t>未發布</t>
+  </si>
+  <si>
+    <t>Hidden</t>
+  </si>
+  <si>
+    <t>faqs.colCategory</t>
+  </si>
+  <si>
+    <t>主題</t>
+  </si>
+  <si>
+    <t>faqs.colQuestion</t>
+  </si>
+  <si>
+    <t>問題</t>
+  </si>
+  <si>
+    <t>Question</t>
+  </si>
+  <si>
+    <t>faqs.colSort</t>
+  </si>
+  <si>
+    <t>faqs.colStatus</t>
+  </si>
+  <si>
+    <t>faqs.colActions</t>
+  </si>
+  <si>
+    <t>faqs.questionLabel</t>
+  </si>
+  <si>
+    <t>faqs.questionPlaceholder</t>
+  </si>
+  <si>
+    <t>例如：Open Jam 是什麼？</t>
+  </si>
+  <si>
+    <t>e.g. What is Open Jam?</t>
+  </si>
+  <si>
+    <t>faqs.answerLabel</t>
+  </si>
+  <si>
+    <t>解答</t>
+  </si>
+  <si>
+    <t>Answer</t>
+  </si>
+  <si>
+    <t>faqs.answerPlaceholder</t>
+  </si>
+  <si>
+    <t>輸入解答內容（可換行）</t>
+  </si>
+  <si>
+    <t>Enter the answer (line breaks allowed)</t>
+  </si>
+  <si>
+    <t>faqs.sortLabel</t>
+  </si>
+  <si>
+    <t>排序（同主題內由小到大）</t>
+  </si>
+  <si>
+    <t>Order (ascending within a category)</t>
+  </si>
+  <si>
+    <t>faqs.publishedLabel</t>
+  </si>
+  <si>
+    <t>發布（對外公開）</t>
+  </si>
+  <si>
+    <t>Published (publicly visible)</t>
+  </si>
+  <si>
+    <t>faqs.emptyTitle</t>
+  </si>
+  <si>
+    <t>尚無常見問題</t>
+  </si>
+  <si>
+    <t>No FAQ items yet</t>
+  </si>
+  <si>
+    <t>faqs.emptyDesc</t>
+  </si>
+  <si>
+    <t>點右上角「新增問答」建立第一則</t>
+  </si>
+  <si>
+    <t>Click "New Q&amp;A" to create the first one</t>
+  </si>
+  <si>
+    <t>faqs.create</t>
+  </si>
+  <si>
+    <t>建立</t>
+  </si>
+  <si>
+    <t>Create</t>
+  </si>
+  <si>
+    <t>faqs.save</t>
+  </si>
+  <si>
+    <t>faqs.edit</t>
+  </si>
+  <si>
+    <t>faqs.del</t>
+  </si>
+  <si>
+    <t>faqs.deleteConfirm</t>
+  </si>
+  <si>
+    <t>刪除後前台將不再顯示此問答。確定刪除？</t>
+  </si>
+  <si>
+    <t>This Q&amp;A will no longer show on the site. Delete?</t>
+  </si>
+  <si>
+    <t>faqs.valCategoryRequired</t>
+  </si>
+  <si>
+    <t>請選擇主題分類</t>
+  </si>
+  <si>
+    <t>Please select a category</t>
+  </si>
+  <si>
+    <t>faqs.valQuestionRequired</t>
+  </si>
+  <si>
+    <t>請輸入問題</t>
+  </si>
+  <si>
+    <t>Question is required</t>
+  </si>
+  <si>
+    <t>faqs.valAnswerRequired</t>
+  </si>
+  <si>
+    <t>請輸入解答</t>
+  </si>
+  <si>
+    <t>Answer is required</t>
+  </si>
+  <si>
+    <t>faqs.msgLoadFailed</t>
+  </si>
+  <si>
+    <t>faqs.msgActionFailed</t>
+  </si>
+  <si>
+    <t>faqs.msgCreated</t>
+  </si>
+  <si>
+    <t>已新增</t>
+  </si>
+  <si>
+    <t>faqs.msgUpdated</t>
+  </si>
+  <si>
+    <t>已更新</t>
+  </si>
+  <si>
+    <t>Updated</t>
+  </si>
+  <si>
+    <t>faqs.msgDeleted</t>
+  </si>
+  <si>
+    <t>faqs.msgCreateFailed</t>
+  </si>
+  <si>
+    <t>新增失敗</t>
+  </si>
+  <si>
+    <t>faqs.msgUpdateFailed</t>
+  </si>
+  <si>
+    <t>faqs.msgDeleteFailed</t>
+  </si>
+  <si>
+    <t>刪除失敗</t>
+  </si>
+  <si>
+    <t>Failed to delete</t>
+  </si>
+  <si>
+    <t>faqs.colUpdatedAt</t>
+  </si>
+  <si>
+    <t>更新於</t>
+  </si>
+  <si>
+    <t>faqCategories.searchPlaceholder</t>
+  </si>
+  <si>
+    <t>Search by name or slug</t>
+  </si>
+  <si>
+    <t>faqCategories.newCategory</t>
+  </si>
+  <si>
+    <t>New category</t>
+  </si>
+  <si>
+    <t>faqCategories.colCategory</t>
+  </si>
+  <si>
+    <t>faqCategories.colSort</t>
+  </si>
+  <si>
+    <t>faqCategories.colActions</t>
+  </si>
+  <si>
+    <t>faqCategories.emptyTitle</t>
+  </si>
+  <si>
+    <t>尚未建立常見問題分類</t>
+  </si>
+  <si>
+    <t>No FAQ categories yet</t>
+  </si>
+  <si>
+    <t>faqCategories.emptyDesc</t>
+  </si>
+  <si>
+    <t>新增分類後，即可在「常見問題」建立問答並歸類。</t>
+  </si>
+  <si>
+    <t>Create a category, then add and group Q&amp;A under it in FAQ.</t>
+  </si>
+  <si>
+    <t>faqCategories.deleteConfirm</t>
+  </si>
+  <si>
+    <t>刪除後無法復原；若仍有問答引用此分類，後端會拒絕刪除。</t>
+  </si>
+  <si>
+    <t>This cannot be undone; if any Q&amp;A still references this category, the server will reject the deletion.</t>
+  </si>
+  <si>
+    <t>faqCategories.editTitle</t>
+  </si>
+  <si>
+    <t>faqCategories.createTitle</t>
+  </si>
+  <si>
+    <t>faqCategories.nameLabel</t>
+  </si>
+  <si>
+    <t>faqCategories.namePlaceholder</t>
+  </si>
+  <si>
+    <t>例：認識平台</t>
+  </si>
+  <si>
+    <t>e.g. The platform</t>
+  </si>
+  <si>
+    <t>faqCategories.slugLabel</t>
+  </si>
+  <si>
+    <t>Slug</t>
+  </si>
+  <si>
+    <t>faqCategories.slugPlaceholder</t>
+  </si>
+  <si>
+    <t>例：platform</t>
+  </si>
+  <si>
+    <t>e.g. platform</t>
+  </si>
+  <si>
+    <t>faqCategories.slugHint</t>
+  </si>
+  <si>
+    <t>Lowercase letters, digits and hyphens only; unique across the platform.</t>
+  </si>
+  <si>
+    <t>faqCategories.descLabel</t>
+  </si>
+  <si>
+    <t>分類敘述</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>faqCategories.descPlaceholder</t>
+  </si>
+  <si>
+    <t>選填，簡短說明此分類（最多 200 字）</t>
+  </si>
+  <si>
+    <t>Optional short description (max 200 chars)</t>
+  </si>
+  <si>
+    <t>faqCategories.sortLabel</t>
+  </si>
+  <si>
+    <t>顯示排序</t>
+  </si>
+  <si>
+    <t>Display order</t>
+  </si>
+  <si>
+    <t>faqCategories.save</t>
+  </si>
+  <si>
+    <t>faqCategories.create</t>
+  </si>
+  <si>
+    <t>faqCategories.valNameRequired</t>
+  </si>
+  <si>
+    <t>Category name is required.</t>
+  </si>
+  <si>
+    <t>faqCategories.valNameTooLong</t>
+  </si>
+  <si>
+    <t>Category name must be at most 100 characters.</t>
+  </si>
+  <si>
+    <t>faqCategories.valSlugRequired</t>
+  </si>
+  <si>
+    <t>Slug is required.</t>
+  </si>
+  <si>
+    <t>faqCategories.valSlugInvalid</t>
+  </si>
+  <si>
+    <t>代稱須為 3–100 字小寫英數字與連字號，且不可開頭/結尾為連字號。</t>
+  </si>
+  <si>
+    <t>Slug must be 3–100 lowercase letters, digits and hyphens, not starting/ending with a hyphen.</t>
+  </si>
+  <si>
+    <t>faqCategories.msgLoadFailed</t>
+  </si>
+  <si>
+    <t>faqCategories.msgActionFailed</t>
+  </si>
+  <si>
+    <t>faqCategories.msgCreated</t>
+  </si>
+  <si>
+    <t>已新增分類</t>
+  </si>
+  <si>
+    <t>Category created</t>
+  </si>
+  <si>
+    <t>faqCategories.msgUpdated</t>
+  </si>
+  <si>
+    <t>已更新分類</t>
+  </si>
+  <si>
+    <t>Category updated</t>
+  </si>
+  <si>
+    <t>faqCategories.msgDeleted</t>
+  </si>
+  <si>
+    <t>已刪除分類</t>
+  </si>
+  <si>
+    <t>Category deleted</t>
+  </si>
+  <si>
+    <t>faqCategories.msgCreateFailed</t>
+  </si>
+  <si>
+    <t>新增分類失敗</t>
+  </si>
+  <si>
+    <t>Failed to create category</t>
+  </si>
+  <si>
+    <t>faqCategories.msgUpdateFailed</t>
+  </si>
+  <si>
+    <t>更新分類失敗</t>
+  </si>
+  <si>
+    <t>Failed to update category</t>
+  </si>
+  <si>
+    <t>faqCategories.msgDeleteBlocked</t>
+  </si>
+  <si>
+    <t>刪除失敗：此分類可能仍被問答引用</t>
+  </si>
+  <si>
+    <t>Delete failed: the category may still be referenced by Q&amp;A</t>
   </si>
 </sst>
 </file>
@@ -4740,7 +5616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C528"/>
+  <dimension ref="A1:C649"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -5280,54 +6156,54 @@
         <v>144</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>43</v>
+        <v>145</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>44</v>
+        <v>146</v>
       </c>
     </row>
     <row r="50" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="51" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="52" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="53" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>155</v>
+        <v>43</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>156</v>
+        <v>44</v>
       </c>
     </row>
     <row r="54" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5338,48 +6214,48 @@
         <v>158</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="55" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="56" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="57" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="58" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>170</v>
@@ -5415,51 +6291,51 @@
         <v>178</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>147</v>
+        <v>179</v>
       </c>
     </row>
     <row r="62" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="63" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="64" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="65" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>190</v>
+        <v>159</v>
       </c>
     </row>
     <row r="66" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5643,54 +6519,54 @@
         <v>239</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>28</v>
+        <v>240</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>29</v>
+        <v>241</v>
       </c>
     </row>
     <row r="83" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="84" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="85" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="86" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>250</v>
+        <v>28</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>251</v>
+        <v>29</v>
       </c>
     </row>
     <row r="87" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5797,54 +6673,54 @@
         <v>279</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>216</v>
+        <v>280</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>217</v>
+        <v>281</v>
       </c>
     </row>
     <row r="97" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="98" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="99" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="100" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>290</v>
+        <v>228</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>291</v>
+        <v>229</v>
       </c>
     </row>
     <row r="101" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6083,98 +6959,98 @@
         <v>355</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>302</v>
+        <v>356</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>303</v>
+        <v>357</v>
       </c>
     </row>
     <row r="123" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="124" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="125" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="126" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>228</v>
+        <v>314</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>229</v>
+        <v>315</v>
       </c>
     </row>
     <row r="127" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="128" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="129" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="130" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>376</v>
+        <v>240</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>377</v>
+        <v>241</v>
       </c>
     </row>
     <row r="131" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6449,73 +7325,73 @@
         <v>451</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>389</v>
+        <v>452</v>
       </c>
     </row>
     <row r="156" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>400</v>
+        <v>454</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>401</v>
+        <v>455</v>
       </c>
     </row>
     <row r="157" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>409</v>
+        <v>457</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>173</v>
+        <v>458</v>
       </c>
     </row>
     <row r="158" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
     <row r="159" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>459</v>
+        <v>401</v>
       </c>
     </row>
     <row r="160" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>461</v>
+        <v>412</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>462</v>
+        <v>413</v>
       </c>
     </row>
     <row r="161" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>464</v>
+        <v>421</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>465</v>
+        <v>185</v>
       </c>
     </row>
     <row r="162" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6545,54 +7421,54 @@
         <v>472</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>22</v>
+        <v>473</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>23</v>
+        <v>474</v>
       </c>
     </row>
     <row r="165" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="166" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="167" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="168" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>483</v>
+        <v>22</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>484</v>
+        <v>23</v>
       </c>
     </row>
     <row r="169" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6611,51 +7487,51 @@
         <v>488</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>400</v>
+        <v>489</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="171" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="172" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="173" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="174" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>500</v>
+        <v>412</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>501</v>
@@ -6754,76 +7630,76 @@
         <v>526</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>158</v>
+        <v>527</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>158</v>
+        <v>528</v>
       </c>
     </row>
     <row r="184" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="185" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>155</v>
+        <v>533</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>156</v>
+        <v>534</v>
       </c>
     </row>
     <row r="186" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
     </row>
     <row r="187" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>535</v>
+        <v>170</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>536</v>
+        <v>170</v>
       </c>
     </row>
     <row r="188" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="189" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>541</v>
+        <v>167</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>542</v>
+        <v>168</v>
       </c>
     </row>
     <row r="190" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6875,76 +7751,76 @@
         <v>555</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>268</v>
+        <v>556</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>269</v>
+        <v>557</v>
       </c>
     </row>
     <row r="195" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="196" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>271</v>
+        <v>562</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>272</v>
+        <v>563</v>
       </c>
     </row>
     <row r="197" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
     </row>
     <row r="198" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>564</v>
+        <v>280</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>565</v>
+        <v>281</v>
       </c>
     </row>
     <row r="199" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="200" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>570</v>
+        <v>283</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>571</v>
+        <v>284</v>
       </c>
     </row>
     <row r="201" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7062,76 +7938,76 @@
         <v>602</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>268</v>
+        <v>603</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>269</v>
+        <v>604</v>
       </c>
     </row>
     <row r="212" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>557</v>
+        <v>606</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>558</v>
+        <v>607</v>
       </c>
     </row>
     <row r="213" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>271</v>
+        <v>609</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>272</v>
+        <v>610</v>
       </c>
     </row>
     <row r="214" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
     </row>
     <row r="215" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>609</v>
+        <v>280</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>610</v>
+        <v>281</v>
       </c>
     </row>
     <row r="216" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>612</v>
+        <v>569</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>613</v>
+        <v>570</v>
       </c>
     </row>
     <row r="217" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>615</v>
+        <v>283</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>616</v>
+        <v>284</v>
       </c>
     </row>
     <row r="218" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7260,76 +8136,76 @@
         <v>650</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>451</v>
+        <v>651</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>389</v>
+        <v>652</v>
       </c>
     </row>
     <row r="230" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="231" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>216</v>
+        <v>657</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>217</v>
+        <v>658</v>
       </c>
     </row>
     <row r="232" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
     </row>
     <row r="233" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>659</v>
+        <v>463</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>660</v>
+        <v>401</v>
       </c>
     </row>
     <row r="234" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="235" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>665</v>
+        <v>228</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>666</v>
+        <v>229</v>
       </c>
     </row>
     <row r="236" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7392,54 +8268,54 @@
         <v>682</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>648</v>
+        <v>683</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>649</v>
+        <v>684</v>
       </c>
     </row>
     <row r="242" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="243" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="244" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
     </row>
     <row r="245" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>693</v>
+        <v>660</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>694</v>
+        <v>661</v>
       </c>
     </row>
     <row r="246" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7480,54 +8356,54 @@
         <v>704</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>612</v>
+        <v>705</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>613</v>
+        <v>706</v>
       </c>
     </row>
     <row r="250" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
     </row>
     <row r="251" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="252" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
     </row>
     <row r="253" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>715</v>
+        <v>624</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>716</v>
+        <v>625</v>
       </c>
     </row>
     <row r="254" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7546,54 +8422,54 @@
         <v>720</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>46</v>
+        <v>721</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>47</v>
+        <v>722</v>
       </c>
     </row>
     <row r="256" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
     </row>
     <row r="257" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
     </row>
     <row r="258" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
     </row>
     <row r="259" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>731</v>
+        <v>52</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>732</v>
+        <v>53</v>
       </c>
     </row>
     <row r="260" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7736,62 +8612,62 @@
         <v>770</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
     </row>
     <row r="273" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>350</v>
+        <v>773</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>351</v>
+        <v>774</v>
       </c>
     </row>
     <row r="274" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
     </row>
     <row r="275" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
     </row>
     <row r="276" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
     </row>
     <row r="277" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>782</v>
+        <v>362</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>783</v>
+        <v>363</v>
       </c>
     </row>
     <row r="278" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7857,48 +8733,48 @@
         <v>800</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
     </row>
     <row r="284" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
     </row>
     <row r="285" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="286" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
     </row>
     <row r="287" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C287" s="2" t="s">
         <v>812</v>
@@ -8195,98 +9071,98 @@
         <v>891</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>228</v>
+        <v>892</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>229</v>
+        <v>893</v>
       </c>
     </row>
     <row r="315" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>529</v>
+        <v>896</v>
       </c>
     </row>
     <row r="316" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
     </row>
     <row r="317" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
     </row>
     <row r="318" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>155</v>
+        <v>240</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>156</v>
+        <v>241</v>
       </c>
     </row>
     <row r="319" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>903</v>
+        <v>541</v>
       </c>
     </row>
     <row r="320" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
     </row>
     <row r="321" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
     </row>
     <row r="322" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>911</v>
+        <v>167</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>912</v>
+        <v>168</v>
       </c>
     </row>
     <row r="323" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8338,65 +9214,65 @@
         <v>925</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>210</v>
+        <v>926</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>211</v>
+        <v>927</v>
       </c>
     </row>
     <row r="328" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>912</v>
+        <v>930</v>
       </c>
     </row>
     <row r="329" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
     </row>
     <row r="330" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
     </row>
     <row r="331" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>935</v>
+        <v>222</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>936</v>
+        <v>223</v>
       </c>
     </row>
     <row r="332" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>939</v>
+        <v>924</v>
       </c>
     </row>
     <row r="333" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8415,54 +9291,54 @@
         <v>943</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>228</v>
+        <v>944</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>229</v>
+        <v>945</v>
       </c>
     </row>
     <row r="335" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
     </row>
     <row r="336" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
     </row>
     <row r="337" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
     </row>
     <row r="338" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>954</v>
+        <v>240</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>955</v>
+        <v>241</v>
       </c>
     </row>
     <row r="339" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8602,51 +9478,51 @@
         <v>992</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>284</v>
+        <v>993</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="352" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
     </row>
     <row r="353" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="354" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="355" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>1004</v>
+        <v>296</v>
       </c>
       <c r="C355" s="2" t="s">
         <v>1005</v>
@@ -8844,307 +9720,307 @@
         <v>1057</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>773</v>
+        <v>1058</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>774</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="374" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="375" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="376" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A376" s="2" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="C376" s="2" t="s">
-        <v>147</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="377" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A377" s="2" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>149</v>
+        <v>1070</v>
       </c>
       <c r="C377" s="2" t="s">
-        <v>150</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="378" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
-        <v>1067</v>
+        <v>1072</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>1068</v>
+        <v>785</v>
       </c>
       <c r="C378" s="2" t="s">
-        <v>1069</v>
+        <v>786</v>
       </c>
     </row>
     <row r="379" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A379" s="2" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>155</v>
+        <v>1074</v>
       </c>
       <c r="C379" s="2" t="s">
-        <v>156</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="380" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A380" s="2" t="s">
-        <v>1071</v>
+        <v>1076</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>1072</v>
+        <v>1077</v>
       </c>
       <c r="C380" s="2" t="s">
-        <v>1073</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="381" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A381" s="2" t="s">
-        <v>1074</v>
+        <v>1079</v>
       </c>
       <c r="B381" s="2" t="s">
-        <v>216</v>
+        <v>1080</v>
       </c>
       <c r="C381" s="2" t="s">
-        <v>217</v>
+        <v>159</v>
       </c>
     </row>
     <row r="382" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A382" s="2" t="s">
-        <v>1075</v>
+        <v>1081</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>1076</v>
+        <v>161</v>
       </c>
       <c r="C382" s="2" t="s">
-        <v>1077</v>
+        <v>162</v>
       </c>
     </row>
     <row r="383" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A383" s="2" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>886</v>
+        <v>1083</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>1079</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="384" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A384" s="2" t="s">
-        <v>1080</v>
+        <v>1085</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>237</v>
+        <v>167</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>238</v>
+        <v>168</v>
       </c>
     </row>
     <row r="385" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A385" s="2" t="s">
-        <v>1081</v>
+        <v>1086</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>231</v>
+        <v>1087</v>
       </c>
       <c r="C385" s="2" t="s">
-        <v>232</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="386" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A386" s="2" t="s">
-        <v>1082</v>
+        <v>1089</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>1083</v>
+        <v>228</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>1084</v>
+        <v>229</v>
       </c>
     </row>
     <row r="387" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A387" s="2" t="s">
-        <v>1085</v>
+        <v>1090</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>1086</v>
+        <v>1091</v>
       </c>
       <c r="C387" s="2" t="s">
-        <v>1087</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="388" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A388" s="2" t="s">
-        <v>1088</v>
+        <v>1093</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>247</v>
+        <v>898</v>
       </c>
       <c r="C388" s="2" t="s">
-        <v>248</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="389" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A389" s="2" t="s">
-        <v>1089</v>
+        <v>1095</v>
       </c>
       <c r="B389" s="2" t="s">
-        <v>1090</v>
+        <v>249</v>
       </c>
       <c r="C389" s="2" t="s">
-        <v>1091</v>
+        <v>250</v>
       </c>
     </row>
     <row r="390" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A390" s="2" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="B390" s="2" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="C390" s="2" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
     </row>
     <row r="391" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A391" s="2" t="s">
-        <v>1093</v>
+        <v>1097</v>
       </c>
       <c r="B391" s="2" t="s">
-        <v>1094</v>
+        <v>1098</v>
       </c>
       <c r="C391" s="2" t="s">
-        <v>1095</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="392" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A392" s="2" t="s">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="B392" s="2" t="s">
-        <v>1097</v>
+        <v>1101</v>
       </c>
       <c r="C392" s="2" t="s">
-        <v>1097</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="393" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A393" s="2" t="s">
-        <v>1098</v>
+        <v>1103</v>
       </c>
       <c r="B393" s="2" t="s">
-        <v>1099</v>
+        <v>259</v>
       </c>
       <c r="C393" s="2" t="s">
-        <v>1099</v>
+        <v>260</v>
       </c>
     </row>
     <row r="394" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A394" s="2" t="s">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="B394" s="2" t="s">
-        <v>1101</v>
+        <v>1105</v>
       </c>
       <c r="C394" s="2" t="s">
-        <v>1102</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="395" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A395" s="2" t="s">
-        <v>1103</v>
+        <v>1107</v>
       </c>
       <c r="B395" s="2" t="s">
-        <v>1101</v>
+        <v>265</v>
       </c>
       <c r="C395" s="2" t="s">
-        <v>1102</v>
+        <v>266</v>
       </c>
     </row>
     <row r="396" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A396" s="2" t="s">
-        <v>1104</v>
+        <v>1108</v>
       </c>
       <c r="B396" s="2" t="s">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="C396" s="2" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="397" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A397" s="2" t="s">
-        <v>1107</v>
+        <v>1111</v>
       </c>
       <c r="B397" s="2" t="s">
-        <v>1108</v>
+        <v>1112</v>
       </c>
       <c r="C397" s="2" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="398" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A398" s="2" t="s">
-        <v>1110</v>
+        <v>1113</v>
       </c>
       <c r="B398" s="2" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="C398" s="2" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="399" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A399" s="2" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="B399" s="2" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="400" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A400" s="2" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B400" s="2" t="s">
         <v>1116</v>
       </c>
-      <c r="B400" s="2" t="s">
+      <c r="C400" s="2" t="s">
         <v>1117</v>
-      </c>
-      <c r="C400" s="2" t="s">
-        <v>1118</v>
       </c>
     </row>
     <row r="401" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9221,139 +10097,139 @@
         <v>1138</v>
       </c>
       <c r="C407" s="2" t="s">
-        <v>1121</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="408" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A408" s="2" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B408" s="2" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="C408" s="2" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="409" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A409" s="2" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B409" s="2" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="C409" s="2" t="s">
-        <v>1127</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="410" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A410" s="2" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="B410" s="2" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="C410" s="2" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="411" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A411" s="2" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="B411" s="2" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="C411" s="2" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="412" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A412" s="2" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="B412" s="2" t="s">
-        <v>1014</v>
+        <v>1153</v>
       </c>
       <c r="C412" s="2" t="s">
-        <v>1014</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="413" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A413" s="2" t="s">
-        <v>1151</v>
+        <v>1155</v>
       </c>
       <c r="B413" s="2" t="s">
-        <v>1152</v>
+        <v>1156</v>
       </c>
       <c r="C413" s="2" t="s">
-        <v>1153</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="414" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A414" s="2" t="s">
-        <v>1154</v>
+        <v>1158</v>
       </c>
       <c r="B414" s="2" t="s">
-        <v>1155</v>
+        <v>1159</v>
       </c>
       <c r="C414" s="2" t="s">
-        <v>1156</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="415" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A415" s="2" t="s">
-        <v>1157</v>
+        <v>1160</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>1158</v>
+        <v>1161</v>
       </c>
       <c r="C415" s="2" t="s">
-        <v>1159</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="416" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A416" s="2" t="s">
-        <v>1160</v>
+        <v>1163</v>
       </c>
       <c r="B416" s="2" t="s">
-        <v>1161</v>
+        <v>1164</v>
       </c>
       <c r="C416" s="2" t="s">
-        <v>1162</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="417" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A417" s="2" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="B417" s="2" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="C417" s="2" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="418" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A418" s="2" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="B418" s="2" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="C418" s="2" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="419" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A419" s="2" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="B419" s="2" t="s">
-        <v>1170</v>
+        <v>1026</v>
       </c>
       <c r="C419" s="2" t="s">
-        <v>1171</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="420" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9361,208 +10237,208 @@
         <v>1172</v>
       </c>
       <c r="B420" s="2" t="s">
-        <v>1049</v>
+        <v>1173</v>
       </c>
       <c r="C420" s="2" t="s">
-        <v>1050</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="421" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A421" s="2" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="B421" s="2" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="C421" s="2" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="422" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A422" s="2" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="B422" s="2" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="C422" s="2" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="423" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A423" s="2" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="424" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A424" s="2" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="B424" s="2" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="C424" s="2" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="425" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A425" s="2" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="B425" s="2" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="C425" s="2" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="426" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A426" s="2" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="B426" s="2" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="C426" s="2" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="427" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A427" s="2" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="C427" s="2" t="s">
-        <v>181</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="428" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A428" s="2" t="s">
-        <v>1193</v>
+        <v>1196</v>
       </c>
       <c r="B428" s="2" t="s">
-        <v>149</v>
+        <v>1064</v>
       </c>
       <c r="C428" s="2" t="s">
-        <v>150</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="429" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A429" s="2" t="s">
-        <v>1194</v>
+        <v>1197</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>152</v>
+        <v>1198</v>
       </c>
       <c r="C429" s="2" t="s">
-        <v>153</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="430" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A430" s="2" t="s">
-        <v>1195</v>
+        <v>1200</v>
       </c>
       <c r="B430" s="2" t="s">
-        <v>515</v>
+        <v>1201</v>
       </c>
       <c r="C430" s="2" t="s">
-        <v>516</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="431" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A431" s="2" t="s">
-        <v>1196</v>
+        <v>1203</v>
       </c>
       <c r="B431" s="2" t="s">
-        <v>1197</v>
+        <v>1204</v>
       </c>
       <c r="C431" s="2" t="s">
-        <v>1198</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="432" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A432" s="2" t="s">
-        <v>1199</v>
+        <v>1206</v>
       </c>
       <c r="B432" s="2" t="s">
-        <v>1200</v>
+        <v>1207</v>
       </c>
       <c r="C432" s="2" t="s">
-        <v>1201</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="433" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A433" s="2" t="s">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>1203</v>
+        <v>1210</v>
       </c>
       <c r="C433" s="2" t="s">
-        <v>1204</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="434" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A434" s="2" t="s">
-        <v>1205</v>
+        <v>1212</v>
       </c>
       <c r="B434" s="2" t="s">
-        <v>1206</v>
+        <v>1213</v>
       </c>
       <c r="C434" s="2" t="s">
-        <v>1207</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="435" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A435" s="2" t="s">
-        <v>1208</v>
+        <v>1215</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>1209</v>
+        <v>1216</v>
       </c>
       <c r="C435" s="2" t="s">
-        <v>1210</v>
+        <v>193</v>
       </c>
     </row>
     <row r="436" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A436" s="2" t="s">
-        <v>1211</v>
+        <v>1217</v>
       </c>
       <c r="B436" s="2" t="s">
-        <v>1212</v>
+        <v>161</v>
       </c>
       <c r="C436" s="2" t="s">
-        <v>1213</v>
+        <v>162</v>
       </c>
     </row>
     <row r="437" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A437" s="2" t="s">
-        <v>1214</v>
+        <v>1218</v>
       </c>
       <c r="B437" s="2" t="s">
-        <v>1215</v>
+        <v>164</v>
       </c>
       <c r="C437" s="2" t="s">
-        <v>1216</v>
+        <v>165</v>
       </c>
     </row>
     <row r="438" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A438" s="2" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="B438" s="2" t="s">
-        <v>1218</v>
+        <v>527</v>
       </c>
       <c r="C438" s="2" t="s">
-        <v>1219</v>
+        <v>528</v>
       </c>
     </row>
     <row r="439" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9691,326 +10567,326 @@
         <v>1253</v>
       </c>
       <c r="B450" s="2" t="s">
-        <v>43</v>
+        <v>1254</v>
       </c>
       <c r="C450" s="2" t="s">
-        <v>44</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="451" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A451" s="2" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="B451" s="2" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="C451" s="2" t="s">
-        <v>896</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="452" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A452" s="2" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="B452" s="2" t="s">
-        <v>1197</v>
+        <v>1260</v>
       </c>
       <c r="C452" s="2" t="s">
-        <v>1198</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="453" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A453" s="2" t="s">
-        <v>1257</v>
+        <v>1262</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>1258</v>
+        <v>1263</v>
       </c>
       <c r="C453" s="2" t="s">
-        <v>1005</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="454" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A454" s="2" t="s">
-        <v>1259</v>
+        <v>1265</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>1260</v>
+        <v>1266</v>
       </c>
       <c r="C454" s="2" t="s">
-        <v>1261</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="455" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A455" s="2" t="s">
-        <v>1262</v>
+        <v>1268</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>1200</v>
+        <v>1269</v>
       </c>
       <c r="C455" s="2" t="s">
-        <v>1201</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="456" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A456" s="2" t="s">
-        <v>1263</v>
+        <v>1271</v>
       </c>
       <c r="B456" s="2" t="s">
-        <v>158</v>
+        <v>1272</v>
       </c>
       <c r="C456" s="2" t="s">
-        <v>158</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="457" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A457" s="2" t="s">
-        <v>1264</v>
+        <v>1274</v>
       </c>
       <c r="B457" s="2" t="s">
-        <v>1265</v>
+        <v>1275</v>
       </c>
       <c r="C457" s="2" t="s">
-        <v>1266</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="458" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A458" s="2" t="s">
-        <v>1267</v>
+        <v>1277</v>
       </c>
       <c r="B458" s="2" t="s">
-        <v>1268</v>
+        <v>43</v>
       </c>
       <c r="C458" s="2" t="s">
-        <v>1269</v>
+        <v>44</v>
       </c>
     </row>
     <row r="459" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A459" s="2" t="s">
-        <v>1270</v>
+        <v>1278</v>
       </c>
       <c r="B459" s="2" t="s">
-        <v>1271</v>
+        <v>1279</v>
       </c>
       <c r="C459" s="2" t="s">
-        <v>1272</v>
+        <v>908</v>
       </c>
     </row>
     <row r="460" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A460" s="2" t="s">
-        <v>1273</v>
+        <v>1280</v>
       </c>
       <c r="B460" s="2" t="s">
-        <v>1274</v>
+        <v>1221</v>
       </c>
       <c r="C460" s="2" t="s">
-        <v>1275</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="461" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A461" s="2" t="s">
-        <v>1276</v>
+        <v>1281</v>
       </c>
       <c r="B461" s="2" t="s">
-        <v>1277</v>
+        <v>1282</v>
       </c>
       <c r="C461" s="2" t="s">
-        <v>1278</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="462" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A462" s="2" t="s">
-        <v>1279</v>
+        <v>1283</v>
       </c>
       <c r="B462" s="2" t="s">
-        <v>1046</v>
+        <v>1284</v>
       </c>
       <c r="C462" s="2" t="s">
-        <v>1047</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="463" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A463" s="2" t="s">
-        <v>1280</v>
+        <v>1286</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>4</v>
+        <v>1224</v>
       </c>
       <c r="C463" s="2" t="s">
-        <v>5</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="464" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A464" s="2" t="s">
-        <v>1281</v>
+        <v>1287</v>
       </c>
       <c r="B464" s="2" t="s">
-        <v>1034</v>
+        <v>170</v>
       </c>
       <c r="C464" s="2" t="s">
-        <v>1035</v>
+        <v>170</v>
       </c>
     </row>
     <row r="465" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A465" s="2" t="s">
-        <v>1282</v>
+        <v>1288</v>
       </c>
       <c r="B465" s="2" t="s">
-        <v>1049</v>
+        <v>1289</v>
       </c>
       <c r="C465" s="2" t="s">
-        <v>1050</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="466" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A466" s="2" t="s">
-        <v>1283</v>
+        <v>1291</v>
       </c>
       <c r="B466" s="2" t="s">
-        <v>1284</v>
+        <v>1292</v>
       </c>
       <c r="C466" s="2" t="s">
-        <v>1285</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="467" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A467" s="2" t="s">
-        <v>1286</v>
+        <v>1294</v>
       </c>
       <c r="B467" s="2" t="s">
-        <v>1287</v>
+        <v>1295</v>
       </c>
       <c r="C467" s="2" t="s">
-        <v>1288</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="468" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A468" s="2" t="s">
-        <v>1289</v>
+        <v>1297</v>
       </c>
       <c r="B468" s="2" t="s">
-        <v>1052</v>
+        <v>1298</v>
       </c>
       <c r="C468" s="2" t="s">
-        <v>1053</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="469" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A469" s="2" t="s">
-        <v>1290</v>
+        <v>1300</v>
       </c>
       <c r="B469" s="2" t="s">
-        <v>1291</v>
+        <v>1301</v>
       </c>
       <c r="C469" s="2" t="s">
-        <v>1292</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="470" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A470" s="2" t="s">
-        <v>1293</v>
+        <v>1303</v>
       </c>
       <c r="B470" s="2" t="s">
-        <v>1055</v>
+        <v>1061</v>
       </c>
       <c r="C470" s="2" t="s">
-        <v>1294</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="471" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A471" s="2" t="s">
-        <v>1295</v>
+        <v>1304</v>
       </c>
       <c r="B471" s="2" t="s">
-        <v>1004</v>
+        <v>4</v>
       </c>
       <c r="C471" s="2" t="s">
-        <v>1296</v>
+        <v>5</v>
       </c>
     </row>
     <row r="472" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A472" s="2" t="s">
-        <v>1297</v>
+        <v>1305</v>
       </c>
       <c r="B472" s="2" t="s">
-        <v>1298</v>
+        <v>1049</v>
       </c>
       <c r="C472" s="2" t="s">
-        <v>1299</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="473" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A473" s="2" t="s">
-        <v>1300</v>
+        <v>1306</v>
       </c>
       <c r="B473" s="2" t="s">
-        <v>1301</v>
+        <v>1064</v>
       </c>
       <c r="C473" s="2" t="s">
-        <v>1302</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="474" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A474" s="2" t="s">
-        <v>1303</v>
+        <v>1307</v>
       </c>
       <c r="B474" s="2" t="s">
-        <v>1304</v>
+        <v>1308</v>
       </c>
       <c r="C474" s="2" t="s">
-        <v>1305</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="475" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A475" s="2" t="s">
-        <v>1306</v>
+        <v>1310</v>
       </c>
       <c r="B475" s="2" t="s">
-        <v>1307</v>
+        <v>1311</v>
       </c>
       <c r="C475" s="2" t="s">
-        <v>1308</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="476" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A476" s="2" t="s">
-        <v>1309</v>
+        <v>1313</v>
       </c>
       <c r="B476" s="2" t="s">
-        <v>1310</v>
+        <v>1067</v>
       </c>
       <c r="C476" s="2" t="s">
-        <v>1311</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="477" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A477" s="2" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="B477" s="2" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="C477" s="2" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="478" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A478" s="2" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="B478" s="2" t="s">
-        <v>1316</v>
+        <v>1070</v>
       </c>
       <c r="C478" s="2" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="479" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A479" s="2" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B479" s="2" t="s">
-        <v>1319</v>
+        <v>1016</v>
       </c>
       <c r="C479" s="2" t="s">
         <v>1320</v>
@@ -10032,285 +10908,285 @@
         <v>1324</v>
       </c>
       <c r="B481" s="2" t="s">
-        <v>1046</v>
+        <v>1325</v>
       </c>
       <c r="C481" s="2" t="s">
-        <v>1047</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="482" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A482" s="2" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="B482" s="2" t="s">
-        <v>4</v>
+        <v>1328</v>
       </c>
       <c r="C482" s="2" t="s">
-        <v>5</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="483" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A483" s="2" t="s">
-        <v>1326</v>
+        <v>1330</v>
       </c>
       <c r="B483" s="2" t="s">
-        <v>1052</v>
+        <v>1331</v>
       </c>
       <c r="C483" s="2" t="s">
-        <v>1053</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="484" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A484" s="2" t="s">
-        <v>1327</v>
+        <v>1333</v>
       </c>
       <c r="B484" s="2" t="s">
-        <v>1328</v>
+        <v>1334</v>
       </c>
       <c r="C484" s="2" t="s">
-        <v>1329</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="485" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A485" s="2" t="s">
-        <v>1330</v>
+        <v>1336</v>
       </c>
       <c r="B485" s="2" t="s">
-        <v>1331</v>
+        <v>1337</v>
       </c>
       <c r="C485" s="2" t="s">
-        <v>1332</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="486" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A486" s="2" t="s">
-        <v>1333</v>
+        <v>1339</v>
       </c>
       <c r="B486" s="2" t="s">
-        <v>1334</v>
+        <v>1340</v>
       </c>
       <c r="C486" s="2" t="s">
-        <v>1335</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="487" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A487" s="2" t="s">
-        <v>1336</v>
+        <v>1342</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>1307</v>
+        <v>1343</v>
       </c>
       <c r="C487" s="2" t="s">
-        <v>1308</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="488" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A488" s="2" t="s">
-        <v>1337</v>
+        <v>1345</v>
       </c>
       <c r="B488" s="2" t="s">
-        <v>1338</v>
+        <v>1346</v>
       </c>
       <c r="C488" s="2" t="s">
-        <v>1339</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="489" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A489" s="2" t="s">
-        <v>1340</v>
+        <v>1348</v>
       </c>
       <c r="B489" s="2" t="s">
-        <v>1341</v>
+        <v>1061</v>
       </c>
       <c r="C489" s="2" t="s">
-        <v>1342</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="490" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A490" s="2" t="s">
-        <v>1343</v>
+        <v>1349</v>
       </c>
       <c r="B490" s="2" t="s">
-        <v>1161</v>
+        <v>4</v>
       </c>
       <c r="C490" s="2" t="s">
-        <v>1162</v>
+        <v>5</v>
       </c>
     </row>
     <row r="491" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A491" s="2" t="s">
-        <v>1344</v>
+        <v>1350</v>
       </c>
       <c r="B491" s="2" t="s">
-        <v>1345</v>
+        <v>1067</v>
       </c>
       <c r="C491" s="2" t="s">
-        <v>1346</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="492" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A492" s="2" t="s">
-        <v>1347</v>
+        <v>1351</v>
       </c>
       <c r="B492" s="2" t="s">
-        <v>1348</v>
+        <v>1352</v>
       </c>
       <c r="C492" s="2" t="s">
-        <v>1349</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="493" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A493" s="2" t="s">
-        <v>1350</v>
+        <v>1354</v>
       </c>
       <c r="B493" s="2" t="s">
-        <v>1351</v>
+        <v>1355</v>
       </c>
       <c r="C493" s="2" t="s">
-        <v>1352</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="494" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A494" s="2" t="s">
-        <v>1353</v>
+        <v>1357</v>
       </c>
       <c r="B494" s="2" t="s">
-        <v>1354</v>
+        <v>1358</v>
       </c>
       <c r="C494" s="2" t="s">
-        <v>1355</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="495" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A495" s="2" t="s">
-        <v>1356</v>
+        <v>1360</v>
       </c>
       <c r="B495" s="2" t="s">
-        <v>1357</v>
+        <v>1331</v>
       </c>
       <c r="C495" s="2" t="s">
-        <v>1358</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="496" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A496" s="2" t="s">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="B496" s="2" t="s">
-        <v>1360</v>
+        <v>1362</v>
       </c>
       <c r="C496" s="2" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="497" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A497" s="2" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="B497" s="2" t="s">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="C497" s="2" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="498" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A498" s="2" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>1366</v>
+        <v>1185</v>
       </c>
       <c r="C498" s="2" t="s">
-        <v>449</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="499" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A499" s="2" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="C499" s="2" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="500" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A500" s="2" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="B500" s="2" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="C500" s="2" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="501" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A501" s="2" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="B501" s="2" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="C501" s="2" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="502" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A502" s="2" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="B502" s="2" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="C502" s="2" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="503" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A503" s="2" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="B503" s="2" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="C503" s="2" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="504" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A504" s="2" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="B504" s="2" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="C504" s="2" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="505" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A505" s="2" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="B505" s="2" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="C505" s="2" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="506" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A506" s="2" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="B506" s="2" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="C506" s="2" t="s">
-        <v>1390</v>
+        <v>461</v>
       </c>
     </row>
     <row r="507" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10318,131 +11194,131 @@
         <v>1391</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>448</v>
+        <v>1392</v>
       </c>
       <c r="C507" s="2" t="s">
-        <v>449</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="508" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A508" s="2" t="s">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="B508" s="2" t="s">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="C508" s="2" t="s">
-        <v>1394</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="509" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A509" s="2" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="B509" s="2" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
       <c r="C509" s="2" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="510" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A510" s="2" t="s">
-        <v>1398</v>
+        <v>1400</v>
       </c>
       <c r="B510" s="2" t="s">
-        <v>216</v>
+        <v>1401</v>
       </c>
       <c r="C510" s="2" t="s">
-        <v>217</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="511" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A511" s="2" t="s">
-        <v>1399</v>
+        <v>1403</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>1400</v>
+        <v>1404</v>
       </c>
       <c r="C511" s="2" t="s">
-        <v>1401</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="512" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A512" s="2" t="s">
-        <v>1402</v>
+        <v>1406</v>
       </c>
       <c r="B512" s="2" t="s">
-        <v>1403</v>
+        <v>1407</v>
       </c>
       <c r="C512" s="2" t="s">
-        <v>1404</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="513" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A513" s="2" t="s">
-        <v>1405</v>
+        <v>1409</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>1406</v>
+        <v>1410</v>
       </c>
       <c r="C513" s="2" t="s">
-        <v>1407</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="514" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A514" s="2" t="s">
-        <v>1408</v>
+        <v>1412</v>
       </c>
       <c r="B514" s="2" t="s">
-        <v>1409</v>
+        <v>1413</v>
       </c>
       <c r="C514" s="2" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="515" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A515" s="2" t="s">
-        <v>1411</v>
+        <v>1415</v>
       </c>
       <c r="B515" s="2" t="s">
-        <v>1412</v>
+        <v>460</v>
       </c>
       <c r="C515" s="2" t="s">
-        <v>1413</v>
+        <v>461</v>
       </c>
     </row>
     <row r="516" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A516" s="2" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="B516" s="2" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="C516" s="2" t="s">
-        <v>1416</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="517" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A517" s="2" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
       <c r="B517" s="2" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
       <c r="C517" s="2" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="518" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A518" s="2" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="B518" s="2" t="s">
-        <v>1421</v>
+        <v>228</v>
       </c>
       <c r="C518" s="2" t="s">
-        <v>1422</v>
+        <v>229</v>
       </c>
     </row>
     <row r="519" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10494,65 +11370,1396 @@
         <v>1435</v>
       </c>
       <c r="B523" s="2" t="s">
-        <v>210</v>
+        <v>1436</v>
       </c>
       <c r="C523" s="2" t="s">
-        <v>211</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="524" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A524" s="2" t="s">
-        <v>1436</v>
+        <v>1438</v>
       </c>
       <c r="B524" s="2" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="C524" s="2" t="s">
-        <v>896</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="525" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A525" s="2" t="s">
-        <v>1438</v>
+        <v>1441</v>
       </c>
       <c r="B525" s="2" t="s">
-        <v>1439</v>
+        <v>1442</v>
       </c>
       <c r="C525" s="2" t="s">
-        <v>1440</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="526" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A526" s="2" t="s">
-        <v>1441</v>
+        <v>1444</v>
       </c>
       <c r="B526" s="2" t="s">
-        <v>1260</v>
+        <v>1445</v>
       </c>
       <c r="C526" s="2" t="s">
-        <v>1261</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="527" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A527" s="2" t="s">
-        <v>1442</v>
+        <v>1447</v>
       </c>
       <c r="B527" s="2" t="s">
-        <v>1443</v>
+        <v>1448</v>
       </c>
       <c r="C527" s="2" t="s">
-        <v>1444</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="528" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A528" s="2" t="s">
-        <v>1445</v>
+        <v>1450</v>
       </c>
       <c r="B528" s="2" t="s">
-        <v>1446</v>
+        <v>1451</v>
       </c>
       <c r="C528" s="2" t="s">
-        <v>1447</v>
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="529" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A529" s="2" t="s">
+        <v>1453</v>
+      </c>
+      <c r="B529" s="2" t="s">
+        <v>1454</v>
+      </c>
+      <c r="C529" s="2" t="s">
+        <v>1455</v>
+      </c>
+    </row>
+    <row r="530" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A530" s="2" t="s">
+        <v>1456</v>
+      </c>
+      <c r="B530" s="2" t="s">
+        <v>1457</v>
+      </c>
+      <c r="C530" s="2" t="s">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="531" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A531" s="2" t="s">
+        <v>1459</v>
+      </c>
+      <c r="B531" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C531" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="532" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A532" s="2" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B532" s="2" t="s">
+        <v>1461</v>
+      </c>
+      <c r="C532" s="2" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="533" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A533" s="2" t="s">
+        <v>1462</v>
+      </c>
+      <c r="B533" s="2" t="s">
+        <v>1463</v>
+      </c>
+      <c r="C533" s="2" t="s">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="534" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A534" s="2" t="s">
+        <v>1465</v>
+      </c>
+      <c r="B534" s="2" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C534" s="2" t="s">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="535" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A535" s="2" t="s">
+        <v>1466</v>
+      </c>
+      <c r="B535" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="C535" s="2" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="536" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A536" s="2" t="s">
+        <v>1469</v>
+      </c>
+      <c r="B536" s="2" t="s">
+        <v>1470</v>
+      </c>
+      <c r="C536" s="2" t="s">
+        <v>1471</v>
+      </c>
+    </row>
+    <row r="537" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A537" s="2" t="s">
+        <v>1472</v>
+      </c>
+      <c r="B537" s="2" t="s">
+        <v>1473</v>
+      </c>
+      <c r="C537" s="2" t="s">
+        <v>1474</v>
+      </c>
+    </row>
+    <row r="538" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A538" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B538" s="2" t="s">
+        <v>1476</v>
+      </c>
+      <c r="C538" s="2" t="s">
+        <v>1477</v>
+      </c>
+    </row>
+    <row r="539" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A539" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="B539" s="2" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C539" s="2" t="s">
+        <v>1480</v>
+      </c>
+    </row>
+    <row r="540" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A540" s="2" t="s">
+        <v>1481</v>
+      </c>
+      <c r="B540" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C540" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="541" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A541" s="2" t="s">
+        <v>1482</v>
+      </c>
+      <c r="B541" s="2" t="s">
+        <v>905</v>
+      </c>
+      <c r="C541" s="2" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="542" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A542" s="2" t="s">
+        <v>1483</v>
+      </c>
+      <c r="B542" s="2" t="s">
+        <v>914</v>
+      </c>
+      <c r="C542" s="2" t="s">
+        <v>1484</v>
+      </c>
+    </row>
+    <row r="543" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A543" s="2" t="s">
+        <v>1485</v>
+      </c>
+      <c r="B543" s="2" t="s">
+        <v>1486</v>
+      </c>
+      <c r="C543" s="2" t="s">
+        <v>1487</v>
+      </c>
+    </row>
+    <row r="544" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A544" s="2" t="s">
+        <v>1488</v>
+      </c>
+      <c r="B544" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C544" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="545" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A545" s="2" t="s">
+        <v>1489</v>
+      </c>
+      <c r="B545" s="2" t="s">
+        <v>1490</v>
+      </c>
+      <c r="C545" s="2" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="546" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A546" s="2" t="s">
+        <v>1492</v>
+      </c>
+      <c r="B546" s="2" t="s">
+        <v>1493</v>
+      </c>
+      <c r="C546" s="2" t="s">
+        <v>1494</v>
+      </c>
+    </row>
+    <row r="547" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A547" s="2" t="s">
+        <v>1495</v>
+      </c>
+      <c r="B547" s="2" t="s">
+        <v>1496</v>
+      </c>
+      <c r="C547" s="2" t="s">
+        <v>1497</v>
+      </c>
+    </row>
+    <row r="548" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A548" s="2" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B548" s="2" t="s">
+        <v>1499</v>
+      </c>
+      <c r="C548" s="2" t="s">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="549" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A549" s="2" t="s">
+        <v>1501</v>
+      </c>
+      <c r="B549" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C549" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="550" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A550" s="2" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B550" s="2" t="s">
+        <v>1503</v>
+      </c>
+      <c r="C550" s="2" t="s">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="551" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A551" s="2" t="s">
+        <v>1505</v>
+      </c>
+      <c r="B551" s="2" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C551" s="2" t="s">
+        <v>1507</v>
+      </c>
+    </row>
+    <row r="552" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A552" s="2" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B552" s="2" t="s">
+        <v>1509</v>
+      </c>
+      <c r="C552" s="2" t="s">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="553" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A553" s="2" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B553" s="2" t="s">
+        <v>1512</v>
+      </c>
+      <c r="C553" s="2" t="s">
+        <v>1513</v>
+      </c>
+    </row>
+    <row r="554" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A554" s="2" t="s">
+        <v>1514</v>
+      </c>
+      <c r="B554" s="2" t="s">
+        <v>1515</v>
+      </c>
+      <c r="C554" s="2" t="s">
+        <v>1516</v>
+      </c>
+    </row>
+    <row r="555" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A555" s="2" t="s">
+        <v>1517</v>
+      </c>
+      <c r="B555" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="C555" s="2" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="556" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A556" s="2" t="s">
+        <v>1518</v>
+      </c>
+      <c r="B556" s="2" t="s">
+        <v>1519</v>
+      </c>
+      <c r="C556" s="2" t="s">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="557" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A557" s="2" t="s">
+        <v>1521</v>
+      </c>
+      <c r="B557" s="2" t="s">
+        <v>1522</v>
+      </c>
+      <c r="C557" s="2" t="s">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="558" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A558" s="2" t="s">
+        <v>1524</v>
+      </c>
+      <c r="B558" s="2" t="s">
+        <v>1525</v>
+      </c>
+      <c r="C558" s="2" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="559" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A559" s="2" t="s">
+        <v>1527</v>
+      </c>
+      <c r="B559" s="2" t="s">
+        <v>1528</v>
+      </c>
+      <c r="C559" s="2" t="s">
+        <v>1529</v>
+      </c>
+    </row>
+    <row r="560" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A560" s="2" t="s">
+        <v>1530</v>
+      </c>
+      <c r="B560" s="2" t="s">
+        <v>1531</v>
+      </c>
+      <c r="C560" s="2" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="561" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A561" s="2" t="s">
+        <v>1533</v>
+      </c>
+      <c r="B561" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C561" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="562" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A562" s="2" t="s">
+        <v>1534</v>
+      </c>
+      <c r="B562" s="2" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C562" s="2" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="563" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A563" s="2" t="s">
+        <v>1537</v>
+      </c>
+      <c r="B563" s="2" t="s">
+        <v>1538</v>
+      </c>
+      <c r="C563" s="2" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="564" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A564" s="2" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B564" s="2" t="s">
+        <v>1541</v>
+      </c>
+      <c r="C564" s="2" t="s">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="565" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A565" s="2" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B565" s="2" t="s">
+        <v>1544</v>
+      </c>
+      <c r="C565" s="2" t="s">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="566" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A566" s="2" t="s">
+        <v>1546</v>
+      </c>
+      <c r="B566" s="2" t="s">
+        <v>1547</v>
+      </c>
+      <c r="C566" s="2" t="s">
+        <v>1548</v>
+      </c>
+    </row>
+    <row r="567" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A567" s="2" t="s">
+        <v>1549</v>
+      </c>
+      <c r="B567" s="2" t="s">
+        <v>1550</v>
+      </c>
+      <c r="C567" s="2" t="s">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="568" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A568" s="2" t="s">
+        <v>1552</v>
+      </c>
+      <c r="B568" s="2" t="s">
+        <v>1553</v>
+      </c>
+      <c r="C568" s="2" t="s">
+        <v>1554</v>
+      </c>
+    </row>
+    <row r="569" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A569" s="2" t="s">
+        <v>1555</v>
+      </c>
+      <c r="B569" s="2" t="s">
+        <v>1556</v>
+      </c>
+      <c r="C569" s="2" t="s">
+        <v>1557</v>
+      </c>
+    </row>
+    <row r="570" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A570" s="2" t="s">
+        <v>1558</v>
+      </c>
+      <c r="B570" s="2" t="s">
+        <v>1559</v>
+      </c>
+      <c r="C570" s="2" t="s">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="571" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A571" s="2" t="s">
+        <v>1561</v>
+      </c>
+      <c r="B571" s="2" t="s">
+        <v>1562</v>
+      </c>
+      <c r="C571" s="2" t="s">
+        <v>1563</v>
+      </c>
+    </row>
+    <row r="572" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A572" s="2" t="s">
+        <v>1564</v>
+      </c>
+      <c r="B572" s="2" t="s">
+        <v>1565</v>
+      </c>
+      <c r="C572" s="2" t="s">
+        <v>1566</v>
+      </c>
+    </row>
+    <row r="573" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A573" s="2" t="s">
+        <v>1567</v>
+      </c>
+      <c r="B573" s="2" t="s">
+        <v>1568</v>
+      </c>
+      <c r="C573" s="2" t="s">
+        <v>1569</v>
+      </c>
+    </row>
+    <row r="574" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A574" s="2" t="s">
+        <v>1570</v>
+      </c>
+      <c r="B574" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="C574" s="2" t="s">
+        <v>1571</v>
+      </c>
+    </row>
+    <row r="575" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A575" s="2" t="s">
+        <v>1572</v>
+      </c>
+      <c r="B575" s="2" t="s">
+        <v>1573</v>
+      </c>
+      <c r="C575" s="2" t="s">
+        <v>1574</v>
+      </c>
+    </row>
+    <row r="576" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A576" s="2" t="s">
+        <v>1575</v>
+      </c>
+      <c r="B576" s="2" t="s">
+        <v>1576</v>
+      </c>
+      <c r="C576" s="2" t="s">
+        <v>1577</v>
+      </c>
+    </row>
+    <row r="577" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A577" s="2" t="s">
+        <v>1578</v>
+      </c>
+      <c r="B577" s="2" t="s">
+        <v>1579</v>
+      </c>
+      <c r="C577" s="2" t="s">
+        <v>1580</v>
+      </c>
+    </row>
+    <row r="578" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A578" s="2" t="s">
+        <v>1581</v>
+      </c>
+      <c r="B578" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="C578" s="2" t="s">
+        <v>1583</v>
+      </c>
+    </row>
+    <row r="579" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A579" s="2" t="s">
+        <v>1584</v>
+      </c>
+      <c r="B579" s="2" t="s">
+        <v>1585</v>
+      </c>
+      <c r="C579" s="2" t="s">
+        <v>1586</v>
+      </c>
+    </row>
+    <row r="580" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A580" s="2" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B580" s="2" t="s">
+        <v>1588</v>
+      </c>
+      <c r="C580" s="2" t="s">
+        <v>1589</v>
+      </c>
+    </row>
+    <row r="581" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A581" s="2" t="s">
+        <v>1590</v>
+      </c>
+      <c r="B581" s="2" t="s">
+        <v>1591</v>
+      </c>
+      <c r="C581" s="2" t="s">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="582" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A582" s="2" t="s">
+        <v>1593</v>
+      </c>
+      <c r="B582" s="2" t="s">
+        <v>1594</v>
+      </c>
+      <c r="C582" s="2" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="583" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A583" s="2" t="s">
+        <v>1595</v>
+      </c>
+      <c r="B583" s="2" t="s">
+        <v>1596</v>
+      </c>
+      <c r="C583" s="2" t="s">
+        <v>1597</v>
+      </c>
+    </row>
+    <row r="584" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A584" s="2" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B584" s="2" t="s">
+        <v>1599</v>
+      </c>
+      <c r="C584" s="2" t="s">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="585" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A585" s="2" t="s">
+        <v>1601</v>
+      </c>
+      <c r="B585" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C585" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="586" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A586" s="2" t="s">
+        <v>1602</v>
+      </c>
+      <c r="B586" s="2" t="s">
+        <v>1603</v>
+      </c>
+      <c r="C586" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="587" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A587" s="2" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B587" s="2" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C587" s="2" t="s">
+        <v>1606</v>
+      </c>
+    </row>
+    <row r="588" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A588" s="2" t="s">
+        <v>1607</v>
+      </c>
+      <c r="B588" s="2" t="s">
+        <v>1608</v>
+      </c>
+      <c r="C588" s="2" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="589" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A589" s="2" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B589" s="2" t="s">
+        <v>1610</v>
+      </c>
+      <c r="C589" s="2" t="s">
+        <v>1611</v>
+      </c>
+    </row>
+    <row r="590" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A590" s="2" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B590" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="C590" s="2" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="591" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A591" s="2" t="s">
+        <v>1613</v>
+      </c>
+      <c r="B591" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C591" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="592" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A592" s="2" t="s">
+        <v>1614</v>
+      </c>
+      <c r="B592" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C592" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="593" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A593" s="2" t="s">
+        <v>1615</v>
+      </c>
+      <c r="B593" s="2" t="s">
+        <v>1610</v>
+      </c>
+      <c r="C593" s="2" t="s">
+        <v>1611</v>
+      </c>
+    </row>
+    <row r="594" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A594" s="2" t="s">
+        <v>1616</v>
+      </c>
+      <c r="B594" s="2" t="s">
+        <v>1617</v>
+      </c>
+      <c r="C594" s="2" t="s">
+        <v>1618</v>
+      </c>
+    </row>
+    <row r="595" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A595" s="2" t="s">
+        <v>1619</v>
+      </c>
+      <c r="B595" s="2" t="s">
+        <v>1620</v>
+      </c>
+      <c r="C595" s="2" t="s">
+        <v>1621</v>
+      </c>
+    </row>
+    <row r="596" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A596" s="2" t="s">
+        <v>1622</v>
+      </c>
+      <c r="B596" s="2" t="s">
+        <v>1623</v>
+      </c>
+      <c r="C596" s="2" t="s">
+        <v>1624</v>
+      </c>
+    </row>
+    <row r="597" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A597" s="2" t="s">
+        <v>1625</v>
+      </c>
+      <c r="B597" s="2" t="s">
+        <v>1626</v>
+      </c>
+      <c r="C597" s="2" t="s">
+        <v>1627</v>
+      </c>
+    </row>
+    <row r="598" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A598" s="2" t="s">
+        <v>1628</v>
+      </c>
+      <c r="B598" s="2" t="s">
+        <v>1629</v>
+      </c>
+      <c r="C598" s="2" t="s">
+        <v>1630</v>
+      </c>
+    </row>
+    <row r="599" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A599" s="2" t="s">
+        <v>1631</v>
+      </c>
+      <c r="B599" s="2" t="s">
+        <v>1632</v>
+      </c>
+      <c r="C599" s="2" t="s">
+        <v>1633</v>
+      </c>
+    </row>
+    <row r="600" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A600" s="2" t="s">
+        <v>1634</v>
+      </c>
+      <c r="B600" s="2" t="s">
+        <v>1635</v>
+      </c>
+      <c r="C600" s="2" t="s">
+        <v>1636</v>
+      </c>
+    </row>
+    <row r="601" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A601" s="2" t="s">
+        <v>1637</v>
+      </c>
+      <c r="B601" s="2" t="s">
+        <v>1638</v>
+      </c>
+      <c r="C601" s="2" t="s">
+        <v>1639</v>
+      </c>
+    </row>
+    <row r="602" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A602" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B602" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C602" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="603" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A603" s="2" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B603" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C603" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="604" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A604" s="2" t="s">
+        <v>1642</v>
+      </c>
+      <c r="B604" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C604" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="605" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A605" s="2" t="s">
+        <v>1643</v>
+      </c>
+      <c r="B605" s="2" t="s">
+        <v>1644</v>
+      </c>
+      <c r="C605" s="2" t="s">
+        <v>1645</v>
+      </c>
+    </row>
+    <row r="606" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A606" s="2" t="s">
+        <v>1646</v>
+      </c>
+      <c r="B606" s="2" t="s">
+        <v>1647</v>
+      </c>
+      <c r="C606" s="2" t="s">
+        <v>1648</v>
+      </c>
+    </row>
+    <row r="607" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A607" s="2" t="s">
+        <v>1649</v>
+      </c>
+      <c r="B607" s="2" t="s">
+        <v>1650</v>
+      </c>
+      <c r="C607" s="2" t="s">
+        <v>1651</v>
+      </c>
+    </row>
+    <row r="608" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A608" s="2" t="s">
+        <v>1652</v>
+      </c>
+      <c r="B608" s="2" t="s">
+        <v>1653</v>
+      </c>
+      <c r="C608" s="2" t="s">
+        <v>1654</v>
+      </c>
+    </row>
+    <row r="609" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A609" s="2" t="s">
+        <v>1655</v>
+      </c>
+      <c r="B609" s="2" t="s">
+        <v>1556</v>
+      </c>
+      <c r="C609" s="2" t="s">
+        <v>1557</v>
+      </c>
+    </row>
+    <row r="610" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A610" s="2" t="s">
+        <v>1656</v>
+      </c>
+      <c r="B610" s="2" t="s">
+        <v>1559</v>
+      </c>
+      <c r="C610" s="2" t="s">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="611" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A611" s="2" t="s">
+        <v>1657</v>
+      </c>
+      <c r="B611" s="2" t="s">
+        <v>1658</v>
+      </c>
+      <c r="C611" s="2" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="612" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A612" s="2" t="s">
+        <v>1659</v>
+      </c>
+      <c r="B612" s="2" t="s">
+        <v>1660</v>
+      </c>
+      <c r="C612" s="2" t="s">
+        <v>1661</v>
+      </c>
+    </row>
+    <row r="613" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A613" s="2" t="s">
+        <v>1662</v>
+      </c>
+      <c r="B613" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="C613" s="2" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="614" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A614" s="2" t="s">
+        <v>1663</v>
+      </c>
+      <c r="B614" s="2" t="s">
+        <v>1664</v>
+      </c>
+      <c r="C614" s="2" t="s">
+        <v>1569</v>
+      </c>
+    </row>
+    <row r="615" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A615" s="2" t="s">
+        <v>1665</v>
+      </c>
+      <c r="B615" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="C615" s="2" t="s">
+        <v>1571</v>
+      </c>
+    </row>
+    <row r="616" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A616" s="2" t="s">
+        <v>1666</v>
+      </c>
+      <c r="B616" s="2" t="s">
+        <v>1667</v>
+      </c>
+      <c r="C616" s="2" t="s">
+        <v>1668</v>
+      </c>
+    </row>
+    <row r="617" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A617" s="2" t="s">
+        <v>1669</v>
+      </c>
+      <c r="B617" s="2" t="s">
+        <v>1670</v>
+      </c>
+      <c r="C617" s="2" t="s">
+        <v>1661</v>
+      </c>
+    </row>
+    <row r="618" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A618" s="2" t="s">
+        <v>1671</v>
+      </c>
+      <c r="B618" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="C618" s="2" t="s">
+        <v>1672</v>
+      </c>
+    </row>
+    <row r="619" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A619" s="2" t="s">
+        <v>1673</v>
+      </c>
+      <c r="B619" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="C619" s="2" t="s">
+        <v>1674</v>
+      </c>
+    </row>
+    <row r="620" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A620" s="2" t="s">
+        <v>1675</v>
+      </c>
+      <c r="B620" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="C620" s="2" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="621" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A621" s="2" t="s">
+        <v>1676</v>
+      </c>
+      <c r="B621" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="C621" s="2" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="622" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A622" s="2" t="s">
+        <v>1677</v>
+      </c>
+      <c r="B622" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C622" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="623" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A623" s="2" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B623" s="2" t="s">
+        <v>1679</v>
+      </c>
+      <c r="C623" s="2" t="s">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="624" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A624" s="2" t="s">
+        <v>1681</v>
+      </c>
+      <c r="B624" s="2" t="s">
+        <v>1682</v>
+      </c>
+      <c r="C624" s="2" t="s">
+        <v>1683</v>
+      </c>
+    </row>
+    <row r="625" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A625" s="2" t="s">
+        <v>1684</v>
+      </c>
+      <c r="B625" s="2" t="s">
+        <v>1685</v>
+      </c>
+      <c r="C625" s="2" t="s">
+        <v>1686</v>
+      </c>
+    </row>
+    <row r="626" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A626" s="2" t="s">
+        <v>1687</v>
+      </c>
+      <c r="B626" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="C626" s="2" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="627" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A627" s="2" t="s">
+        <v>1688</v>
+      </c>
+      <c r="B627" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="C627" s="2" t="s">
+        <v>1674</v>
+      </c>
+    </row>
+    <row r="628" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A628" s="2" t="s">
+        <v>1689</v>
+      </c>
+      <c r="B628" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="C628" s="2" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="629" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A629" s="2" t="s">
+        <v>1690</v>
+      </c>
+      <c r="B629" s="2" t="s">
+        <v>1691</v>
+      </c>
+      <c r="C629" s="2" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="630" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A630" s="2" t="s">
+        <v>1693</v>
+      </c>
+      <c r="B630" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="C630" s="2" t="s">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="631" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A631" s="2" t="s">
+        <v>1695</v>
+      </c>
+      <c r="B631" s="2" t="s">
+        <v>1696</v>
+      </c>
+      <c r="C631" s="2" t="s">
+        <v>1697</v>
+      </c>
+    </row>
+    <row r="632" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A632" s="2" t="s">
+        <v>1698</v>
+      </c>
+      <c r="B632" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="C632" s="2" t="s">
+        <v>1699</v>
+      </c>
+    </row>
+    <row r="633" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A633" s="2" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B633" s="2" t="s">
+        <v>1701</v>
+      </c>
+      <c r="C633" s="2" t="s">
+        <v>1702</v>
+      </c>
+    </row>
+    <row r="634" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A634" s="2" t="s">
+        <v>1703</v>
+      </c>
+      <c r="B634" s="2" t="s">
+        <v>1704</v>
+      </c>
+      <c r="C634" s="2" t="s">
+        <v>1705</v>
+      </c>
+    </row>
+    <row r="635" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A635" s="2" t="s">
+        <v>1706</v>
+      </c>
+      <c r="B635" s="2" t="s">
+        <v>1707</v>
+      </c>
+      <c r="C635" s="2" t="s">
+        <v>1708</v>
+      </c>
+    </row>
+    <row r="636" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A636" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="B636" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="C636" s="2" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="637" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A637" s="2" t="s">
+        <v>1710</v>
+      </c>
+      <c r="B637" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="C637" s="2" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="638" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A638" s="2" t="s">
+        <v>1711</v>
+      </c>
+      <c r="B638" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="C638" s="2" t="s">
+        <v>1712</v>
+      </c>
+    </row>
+    <row r="639" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A639" s="2" t="s">
+        <v>1713</v>
+      </c>
+      <c r="B639" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="C639" s="2" t="s">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="640" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A640" s="2" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B640" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="C640" s="2" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="641" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A641" s="2" t="s">
+        <v>1717</v>
+      </c>
+      <c r="B641" s="2" t="s">
+        <v>1718</v>
+      </c>
+      <c r="C641" s="2" t="s">
+        <v>1719</v>
+      </c>
+    </row>
+    <row r="642" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A642" s="2" t="s">
+        <v>1720</v>
+      </c>
+      <c r="B642" s="2" t="s">
+        <v>1556</v>
+      </c>
+      <c r="C642" s="2" t="s">
+        <v>1557</v>
+      </c>
+    </row>
+    <row r="643" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A643" s="2" t="s">
+        <v>1721</v>
+      </c>
+      <c r="B643" s="2" t="s">
+        <v>1559</v>
+      </c>
+      <c r="C643" s="2" t="s">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="644" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A644" s="2" t="s">
+        <v>1722</v>
+      </c>
+      <c r="B644" s="2" t="s">
+        <v>1723</v>
+      </c>
+      <c r="C644" s="2" t="s">
+        <v>1724</v>
+      </c>
+    </row>
+    <row r="645" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A645" s="2" t="s">
+        <v>1725</v>
+      </c>
+      <c r="B645" s="2" t="s">
+        <v>1726</v>
+      </c>
+      <c r="C645" s="2" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="646" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A646" s="2" t="s">
+        <v>1728</v>
+      </c>
+      <c r="B646" s="2" t="s">
+        <v>1729</v>
+      </c>
+      <c r="C646" s="2" t="s">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="647" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A647" s="2" t="s">
+        <v>1731</v>
+      </c>
+      <c r="B647" s="2" t="s">
+        <v>1732</v>
+      </c>
+      <c r="C647" s="2" t="s">
+        <v>1733</v>
+      </c>
+    </row>
+    <row r="648" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A648" s="2" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B648" s="2" t="s">
+        <v>1735</v>
+      </c>
+      <c r="C648" s="2" t="s">
+        <v>1736</v>
+      </c>
+    </row>
+    <row r="649" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A649" s="2" t="s">
+        <v>1737</v>
+      </c>
+      <c r="B649" s="2" t="s">
+        <v>1738</v>
+      </c>
+      <c r="C649" s="2" t="s">
+        <v>1739</v>
       </c>
     </row>
   </sheetData>

--- a/apps/workspace-web/i18n.xlsx
+++ b/apps/workspace-web/i18n.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1947" uniqueCount="1740">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2073" uniqueCount="1864">
   <si>
     <t>key</t>
   </si>
@@ -481,6 +481,24 @@
     <t>Failed to create product.</t>
   </si>
   <si>
+    <t>storeError.storeFeatureFailed</t>
+  </si>
+  <si>
+    <t>設定店長精選失敗。</t>
+  </si>
+  <si>
+    <t>Failed to update store feature.</t>
+  </si>
+  <si>
+    <t>storeError.reorderStoreFeaturedFailed</t>
+  </si>
+  <si>
+    <t>更新精選排序失敗。</t>
+  </si>
+  <si>
+    <t>Failed to update featured order.</t>
+  </si>
+  <si>
     <t>catalogStatus.all</t>
   </si>
   <si>
@@ -658,6 +676,96 @@
     <t>Action failed</t>
   </si>
   <si>
+    <t>products.feature</t>
+  </si>
+  <si>
+    <t>設為店長精選</t>
+  </si>
+  <si>
+    <t>Set as store pick</t>
+  </si>
+  <si>
+    <t>products.unfeature</t>
+  </si>
+  <si>
+    <t>取消店長精選</t>
+  </si>
+  <si>
+    <t>Remove store pick</t>
+  </si>
+  <si>
+    <t>products.msgFeatured</t>
+  </si>
+  <si>
+    <t>已設為店長精選。</t>
+  </si>
+  <si>
+    <t>Added to store picks.</t>
+  </si>
+  <si>
+    <t>products.msgUnfeatured</t>
+  </si>
+  <si>
+    <t>已取消店長精選。</t>
+  </si>
+  <si>
+    <t>Removed from store picks.</t>
+  </si>
+  <si>
+    <t>products.manageFeatured</t>
+  </si>
+  <si>
+    <t>精選排序</t>
+  </si>
+  <si>
+    <t>Order picks</t>
+  </si>
+  <si>
+    <t>products.reorderHint</t>
+  </si>
+  <si>
+    <t>拖動排序決定店面首頁精選商品的顯示順序，第一項會作為主打 spotlight。</t>
+  </si>
+  <si>
+    <t>Reorder to control how store picks appear on your storefront — the first item becomes the spotlight.</t>
+  </si>
+  <si>
+    <t>products.noFeatured</t>
+  </si>
+  <si>
+    <t>尚未設定任何店長精選商品。於商品列表點擊星號即可設為精選。</t>
+  </si>
+  <si>
+    <t>No store picks yet. Click the star on a product to feature it.</t>
+  </si>
+  <si>
+    <t>products.moveUp</t>
+  </si>
+  <si>
+    <t>上移</t>
+  </si>
+  <si>
+    <t>Move up</t>
+  </si>
+  <si>
+    <t>products.moveDown</t>
+  </si>
+  <si>
+    <t>下移</t>
+  </si>
+  <si>
+    <t>Move down</t>
+  </si>
+  <si>
+    <t>products.msgOrderSaved</t>
+  </si>
+  <si>
+    <t>已更新精選排序。</t>
+  </si>
+  <si>
+    <t>Featured order updated.</t>
+  </si>
+  <si>
     <t>stores.subStats</t>
   </si>
   <si>
@@ -1330,10 +1438,10 @@
     <t>upload.uploadSub</t>
   </si>
   <si>
-    <t>支援 ZIP、PDF、JPG/PNG、WAV/MP3、PSD 等格式，單檔最大 5 GB。</t>
-  </si>
-  <si>
-    <t>Supports ZIP, PDF, JPG/PNG, WAV/MP3, PSD and more — up to 5 GB per file.</t>
+    <t>支援 ZIP、PDF、JPG/PNG、WAV/MP3、PSD 等格式，單檔最大 2 GB。</t>
+  </si>
+  <si>
+    <t>Supports ZIP, PDF, JPG/PNG, WAV/MP3, PSD and more — up to 2 GB per file.</t>
   </si>
   <si>
     <t>upload.dropzoneTitle</t>
@@ -1591,6 +1699,60 @@
     <t>Failed to create product</t>
   </si>
   <si>
+    <t>upload.msgUploadInProgress</t>
+  </si>
+  <si>
+    <t>檔案上傳中，請稍候再送出。</t>
+  </si>
+  <si>
+    <t>Files are still uploading — please wait before submitting.</t>
+  </si>
+  <si>
+    <t>upload.msgUploadFailed</t>
+  </si>
+  <si>
+    <t>檔案上傳失敗：{name}</t>
+  </si>
+  <si>
+    <t>Upload failed: {name}</t>
+  </si>
+  <si>
+    <t>upload.statusUploading</t>
+  </si>
+  <si>
+    <t>上傳中</t>
+  </si>
+  <si>
+    <t>Uploading</t>
+  </si>
+  <si>
+    <t>upload.statusUploaded</t>
+  </si>
+  <si>
+    <t>已上傳</t>
+  </si>
+  <si>
+    <t>Uploaded</t>
+  </si>
+  <si>
+    <t>upload.statusError</t>
+  </si>
+  <si>
+    <t>上傳失敗</t>
+  </si>
+  <si>
+    <t>Upload failed</t>
+  </si>
+  <si>
+    <t>upload.retryUpload</t>
+  </si>
+  <si>
+    <t>重試上傳</t>
+  </si>
+  <si>
+    <t>Retry upload</t>
+  </si>
+  <si>
     <t>appStatus.pending</t>
   </si>
   <si>
@@ -1930,12 +2092,6 @@
     <t>storeSettings.msgUploadFailed</t>
   </si>
   <si>
-    <t>上傳失敗</t>
-  </si>
-  <si>
-    <t>Upload failed</t>
-  </si>
-  <si>
     <t>storeSettings.msgSaved</t>
   </si>
   <si>
@@ -1954,6 +2110,204 @@
     <t>Update failed</t>
   </si>
   <si>
+    <t>payouts.statusTitle</t>
+  </si>
+  <si>
+    <t>收款狀態</t>
+  </si>
+  <si>
+    <t>Payout status</t>
+  </si>
+  <si>
+    <t>payouts.statusDesc</t>
+  </si>
+  <si>
+    <t>透過 Stripe 收款。完成 Stripe 帳戶設定後，付費商品的款項會在扣除平台服務費後自動撥入你的帳戶。</t>
+  </si>
+  <si>
+    <t>Get paid through Stripe. Once your Stripe account is set up, payments for paid products are automatically transferred to you after the platform fee is deducted.</t>
+  </si>
+  <si>
+    <t>payouts.state.none</t>
+  </si>
+  <si>
+    <t>尚未設定收款</t>
+  </si>
+  <si>
+    <t>Payouts not set up</t>
+  </si>
+  <si>
+    <t>payouts.state.pending</t>
+  </si>
+  <si>
+    <t>設定進行中</t>
+  </si>
+  <si>
+    <t>Setup in progress</t>
+  </si>
+  <si>
+    <t>payouts.state.ready</t>
+  </si>
+  <si>
+    <t>已可收款</t>
+  </si>
+  <si>
+    <t>Ready to receive payments</t>
+  </si>
+  <si>
+    <t>payouts.hint.none</t>
+  </si>
+  <si>
+    <t>你尚未連結 Stripe 帳戶。完成收款設定後才能上架付費商品；免費商品不受影響。</t>
+  </si>
+  <si>
+    <t>You haven't connected a Stripe account yet. Paid products can only be published after payouts are set up; free products are unaffected.</t>
+  </si>
+  <si>
+    <t>payouts.hint.pending</t>
+  </si>
+  <si>
+    <t>Stripe 正在審核你的資料，或仍有資料待補齊。點擊下方按鈕繼續完成設定。</t>
+  </si>
+  <si>
+    <t>Stripe is reviewing your information, or some details are still missing. Click the button below to continue.</t>
+  </si>
+  <si>
+    <t>payouts.hint.ready</t>
+  </si>
+  <si>
+    <t>一切就緒！你的付費商品款項將自動撥入 Stripe 帳戶。</t>
+  </si>
+  <si>
+    <t>All set! Payments for your paid products will be transferred to your Stripe account automatically.</t>
+  </si>
+  <si>
+    <t>payouts.stepAccount</t>
+  </si>
+  <si>
+    <t>建立 Stripe 帳戶</t>
+  </si>
+  <si>
+    <t>Create Stripe account</t>
+  </si>
+  <si>
+    <t>payouts.stepDetails</t>
+  </si>
+  <si>
+    <t>提交帳戶資料</t>
+  </si>
+  <si>
+    <t>Submit account details</t>
+  </si>
+  <si>
+    <t>payouts.stepCharges</t>
+  </si>
+  <si>
+    <t>可承接款項</t>
+  </si>
+  <si>
+    <t>Able to accept payments</t>
+  </si>
+  <si>
+    <t>payouts.stepPayouts</t>
+  </si>
+  <si>
+    <t>可提領出金</t>
+  </si>
+  <si>
+    <t>Able to receive payouts</t>
+  </si>
+  <si>
+    <t>payouts.actionStart</t>
+  </si>
+  <si>
+    <t>前往 Stripe 設定收款</t>
+  </si>
+  <si>
+    <t>Set up payouts with Stripe</t>
+  </si>
+  <si>
+    <t>payouts.actionContinue</t>
+  </si>
+  <si>
+    <t>繼續完成 Stripe 設定</t>
+  </si>
+  <si>
+    <t>Continue Stripe setup</t>
+  </si>
+  <si>
+    <t>payouts.actionUpdate</t>
+  </si>
+  <si>
+    <t>前往 Stripe 更新資料</t>
+  </si>
+  <si>
+    <t>Update details on Stripe</t>
+  </si>
+  <si>
+    <t>payouts.aboutTitle</t>
+  </si>
+  <si>
+    <t>分帳說明</t>
+  </si>
+  <si>
+    <t>How payouts work</t>
+  </si>
+  <si>
+    <t>payouts.aboutDesc</t>
+  </si>
+  <si>
+    <t>款項如何流動、平台如何抽成。</t>
+  </si>
+  <si>
+    <t>How money flows and how the platform fee works.</t>
+  </si>
+  <si>
+    <t>payouts.aboutBody1</t>
+  </si>
+  <si>
+    <t>買家付款後，款項由平台透過 Stripe 自動分帳：扣除平台服務費後，其餘全數轉入你的 Stripe 帳戶，再依 Stripe 的出金排程撥入你的銀行帳戶。</t>
+  </si>
+  <si>
+    <t>When a buyer pays, the platform splits the payment automatically through Stripe: after the platform fee is deducted, the remainder is transferred to your Stripe account and paid out to your bank on Stripe's payout schedule.</t>
+  </si>
+  <si>
+    <t>payouts.aboutBody2</t>
+  </si>
+  <si>
+    <t>免費商品不經過金流，買家送出訂單即可直接下載，無需完成收款設定。</t>
+  </si>
+  <si>
+    <t>Free products skip payment entirely — buyers can download right after placing an order, and no payout setup is required.</t>
+  </si>
+  <si>
+    <t>payouts.msgLoadFailed</t>
+  </si>
+  <si>
+    <t>收款狀態載入失敗</t>
+  </si>
+  <si>
+    <t>Failed to load payout status</t>
+  </si>
+  <si>
+    <t>payouts.msgLinkFailed</t>
+  </si>
+  <si>
+    <t>無法取得 Stripe 設定連結，請稍後再試。</t>
+  </si>
+  <si>
+    <t>Could not get the Stripe setup link. Please try again later.</t>
+  </si>
+  <si>
+    <t>payouts.msgLinkExpired</t>
+  </si>
+  <si>
+    <t>Stripe 設定連結已失效，請重新點擊按鈕前往。</t>
+  </si>
+  <si>
+    <t>The Stripe setup link has expired. Please click the button to try again.</t>
+  </si>
+  <si>
     <t>catalogCategories.searchPlaceholder</t>
   </si>
   <si>
@@ -2275,6 +2629,15 @@
     <t>This category still has subcategories or product references and can’t be deleted.</t>
   </si>
   <si>
+    <t>catalogCategories.systemDeleteBlocked</t>
+  </si>
+  <si>
+    <t>系統預設分類，不允許刪除。</t>
+  </si>
+  <si>
+    <t>System default category — deletion is not allowed.</t>
+  </si>
+  <si>
     <t>auditLog.subStats</t>
   </si>
   <si>
@@ -3515,6 +3878,15 @@
   </si>
   <si>
     <t>Store settings</t>
+  </si>
+  <si>
+    <t>route.payouts</t>
+  </si>
+  <si>
+    <t>收款設定</t>
+  </si>
+  <si>
+    <t>Payouts</t>
   </si>
   <si>
     <t>route.purchases</t>
@@ -5616,7 +5988,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C649"/>
+  <dimension ref="A1:C691"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -6200,32 +6572,32 @@
         <v>156</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>43</v>
+        <v>157</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>44</v>
+        <v>158</v>
       </c>
     </row>
     <row r="54" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="55" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>161</v>
+        <v>43</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>162</v>
+        <v>44</v>
       </c>
     </row>
     <row r="56" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6258,26 +6630,26 @@
         <v>170</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="59" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="60" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>176</v>
@@ -6335,29 +6707,29 @@
         <v>190</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>159</v>
+        <v>191</v>
       </c>
     </row>
     <row r="66" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="67" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>196</v>
+        <v>165</v>
       </c>
     </row>
     <row r="68" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6563,142 +6935,142 @@
         <v>251</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>28</v>
+        <v>252</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>29</v>
+        <v>253</v>
       </c>
     </row>
     <row r="87" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="88" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="89" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="90" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="91" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="92" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="93" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="94" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="95" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="96" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="97" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="98" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>286</v>
+        <v>28</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>287</v>
+        <v>29</v>
       </c>
     </row>
     <row r="99" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6717,142 +7089,142 @@
         <v>291</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>228</v>
+        <v>292</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>229</v>
+        <v>293</v>
       </c>
     </row>
     <row r="101" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="102" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="103" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="104" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="105" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="106" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="107" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="108" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="109" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="110" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="111" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="112" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>326</v>
+        <v>264</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>327</v>
+        <v>265</v>
       </c>
     </row>
     <row r="113" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7003,186 +7375,186 @@
         <v>367</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>314</v>
+        <v>368</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>315</v>
+        <v>369</v>
       </c>
     </row>
     <row r="127" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="128" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="129" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="130" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>240</v>
+        <v>380</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>241</v>
+        <v>381</v>
       </c>
     </row>
     <row r="131" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="132" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="133" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="134" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="135" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="136" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="137" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>401</v>
+        <v>351</v>
       </c>
     </row>
     <row r="139" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="140" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="141" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="142" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>412</v>
+        <v>276</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>413</v>
+        <v>277</v>
       </c>
     </row>
     <row r="143" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7369,301 +7741,301 @@
         <v>463</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>401</v>
+        <v>464</v>
       </c>
     </row>
     <row r="160" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>412</v>
+        <v>466</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>413</v>
+        <v>467</v>
       </c>
     </row>
     <row r="161" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>421</v>
+        <v>469</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>185</v>
+        <v>470</v>
       </c>
     </row>
     <row r="162" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
     </row>
     <row r="163" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
     </row>
     <row r="164" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
     </row>
     <row r="165" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
     </row>
     <row r="166" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
     </row>
     <row r="167" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="168" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>22</v>
+        <v>490</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>23</v>
+        <v>491</v>
       </c>
     </row>
     <row r="169" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
     </row>
     <row r="170" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
     </row>
     <row r="171" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>493</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>495</v>
+        <v>448</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>496</v>
+        <v>449</v>
       </c>
     </row>
     <row r="173" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>498</v>
+        <v>457</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>499</v>
+        <v>191</v>
       </c>
     </row>
     <row r="174" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>412</v>
+        <v>503</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="175" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="176" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="177" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="178" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="179" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="180" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>518</v>
+        <v>22</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>519</v>
+        <v>23</v>
       </c>
     </row>
     <row r="181" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="182" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="183" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="184" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="185" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="186" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>536</v>
+        <v>448</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>537</v>
@@ -7674,5092 +8046,5554 @@
         <v>538</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>170</v>
+        <v>539</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>170</v>
+        <v>540</v>
       </c>
     </row>
     <row r="188" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="189" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>167</v>
+        <v>545</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>168</v>
+        <v>546</v>
       </c>
     </row>
     <row r="190" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
     </row>
     <row r="191" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
     </row>
     <row r="192" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
     </row>
     <row r="193" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
     </row>
     <row r="194" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
     </row>
     <row r="195" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
     </row>
     <row r="196" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
     </row>
     <row r="197" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
     </row>
     <row r="198" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>280</v>
+        <v>572</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>281</v>
+        <v>573</v>
       </c>
     </row>
     <row r="199" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
     </row>
     <row r="200" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>283</v>
+        <v>578</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>284</v>
+        <v>579</v>
       </c>
     </row>
     <row r="201" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
     </row>
     <row r="202" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
     </row>
     <row r="203" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
-        <v>578</v>
+        <v>586</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
     </row>
     <row r="204" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
     </row>
     <row r="205" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>585</v>
+        <v>176</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>586</v>
+        <v>176</v>
       </c>
     </row>
     <row r="206" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
     </row>
     <row r="207" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>591</v>
+        <v>173</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>592</v>
+        <v>174</v>
       </c>
     </row>
     <row r="208" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
     </row>
     <row r="209" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
     </row>
     <row r="210" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
     </row>
     <row r="211" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
     </row>
     <row r="212" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
     </row>
     <row r="213" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
     </row>
     <row r="214" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
     </row>
     <row r="215" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>280</v>
+        <v>619</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>281</v>
+        <v>620</v>
       </c>
     </row>
     <row r="216" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>569</v>
+        <v>316</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>570</v>
+        <v>317</v>
       </c>
     </row>
     <row r="217" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>283</v>
+        <v>623</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>284</v>
+        <v>624</v>
       </c>
     </row>
     <row r="218" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
-        <v>617</v>
+        <v>625</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>618</v>
+        <v>319</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>619</v>
+        <v>320</v>
       </c>
     </row>
     <row r="219" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
     </row>
     <row r="220" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
     </row>
     <row r="221" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
     </row>
     <row r="222" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
     </row>
     <row r="223" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
     </row>
     <row r="224" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
     </row>
     <row r="225" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
     </row>
     <row r="226" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
     </row>
     <row r="227" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
     </row>
     <row r="228" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
     </row>
     <row r="229" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
     </row>
     <row r="230" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
     </row>
     <row r="231" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
     </row>
     <row r="232" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
     </row>
     <row r="233" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>463</v>
+        <v>316</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>401</v>
+        <v>317</v>
       </c>
     </row>
     <row r="234" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>664</v>
+        <v>623</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>665</v>
+        <v>624</v>
       </c>
     </row>
     <row r="235" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>228</v>
+        <v>319</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>229</v>
+        <v>320</v>
       </c>
     </row>
     <row r="236" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
     </row>
     <row r="237" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
     </row>
     <row r="238" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="239" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
     </row>
     <row r="240" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
     </row>
     <row r="241" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
     </row>
     <row r="242" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
     </row>
     <row r="243" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>689</v>
+        <v>575</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>690</v>
+        <v>576</v>
       </c>
     </row>
     <row r="244" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="245" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>660</v>
+        <v>697</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>661</v>
+        <v>698</v>
       </c>
     </row>
     <row r="246" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
     </row>
     <row r="247" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
     </row>
     <row r="248" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
     </row>
     <row r="249" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
     </row>
     <row r="250" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
     </row>
     <row r="251" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
     </row>
     <row r="252" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
     </row>
     <row r="253" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>624</v>
+        <v>721</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>625</v>
+        <v>722</v>
       </c>
     </row>
     <row r="254" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>719</v>
+        <v>725</v>
       </c>
     </row>
     <row r="255" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
-        <v>720</v>
+        <v>726</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
     </row>
     <row r="256" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
     </row>
     <row r="257" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>727</v>
+        <v>733</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>728</v>
+        <v>734</v>
       </c>
     </row>
     <row r="258" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>730</v>
+        <v>736</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>731</v>
+        <v>737</v>
       </c>
     </row>
     <row r="259" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
-        <v>732</v>
+        <v>738</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>52</v>
+        <v>739</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>53</v>
+        <v>740</v>
       </c>
     </row>
     <row r="260" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
-        <v>733</v>
+        <v>741</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>734</v>
+        <v>742</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>735</v>
+        <v>743</v>
       </c>
     </row>
     <row r="261" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
-        <v>736</v>
+        <v>744</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>738</v>
+        <v>746</v>
       </c>
     </row>
     <row r="262" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
-        <v>739</v>
+        <v>747</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>740</v>
+        <v>748</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>741</v>
+        <v>749</v>
       </c>
     </row>
     <row r="263" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
-        <v>742</v>
+        <v>750</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>743</v>
+        <v>751</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>744</v>
+        <v>752</v>
       </c>
     </row>
     <row r="264" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>746</v>
+        <v>754</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>747</v>
+        <v>755</v>
       </c>
     </row>
     <row r="265" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>749</v>
+        <v>757</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>750</v>
+        <v>758</v>
       </c>
     </row>
     <row r="266" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
-        <v>751</v>
+        <v>759</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>752</v>
+        <v>760</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>753</v>
+        <v>761</v>
       </c>
     </row>
     <row r="267" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>755</v>
+        <v>763</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>756</v>
+        <v>764</v>
       </c>
     </row>
     <row r="268" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
-        <v>757</v>
+        <v>765</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>758</v>
+        <v>766</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>759</v>
+        <v>767</v>
       </c>
     </row>
     <row r="269" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>762</v>
+        <v>770</v>
       </c>
     </row>
     <row r="270" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
-        <v>763</v>
+        <v>771</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>764</v>
+        <v>772</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>765</v>
+        <v>773</v>
       </c>
     </row>
     <row r="271" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
-        <v>766</v>
+        <v>774</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>767</v>
+        <v>775</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>768</v>
+        <v>776</v>
       </c>
     </row>
     <row r="272" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
-        <v>769</v>
+        <v>777</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>770</v>
+        <v>778</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>771</v>
+        <v>779</v>
       </c>
     </row>
     <row r="273" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
-        <v>772</v>
+        <v>780</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>773</v>
+        <v>499</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>774</v>
+        <v>437</v>
       </c>
     </row>
     <row r="274" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
-        <v>775</v>
+        <v>781</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>776</v>
+        <v>782</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>777</v>
+        <v>783</v>
       </c>
     </row>
     <row r="275" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
-        <v>778</v>
+        <v>784</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>779</v>
+        <v>264</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>780</v>
+        <v>265</v>
       </c>
     </row>
     <row r="276" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>782</v>
+        <v>787</v>
       </c>
     </row>
     <row r="277" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
-        <v>783</v>
+        <v>788</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>362</v>
+        <v>789</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>363</v>
+        <v>790</v>
       </c>
     </row>
     <row r="278" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
     </row>
     <row r="279" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
     </row>
     <row r="280" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
     </row>
     <row r="281" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>794</v>
+        <v>801</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>795</v>
+        <v>802</v>
       </c>
     </row>
     <row r="282" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
-        <v>796</v>
+        <v>803</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>798</v>
+        <v>805</v>
       </c>
     </row>
     <row r="283" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
-        <v>799</v>
+        <v>806</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>800</v>
+        <v>807</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>801</v>
+        <v>808</v>
       </c>
     </row>
     <row r="284" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
-        <v>802</v>
+        <v>809</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>803</v>
+        <v>810</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>804</v>
+        <v>811</v>
       </c>
     </row>
     <row r="285" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
-        <v>805</v>
+        <v>812</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>806</v>
+        <v>778</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>807</v>
+        <v>779</v>
       </c>
     </row>
     <row r="286" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
-        <v>808</v>
+        <v>813</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>809</v>
+        <v>814</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>810</v>
+        <v>815</v>
       </c>
     </row>
     <row r="287" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
-        <v>811</v>
+        <v>816</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>812</v>
+        <v>817</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>812</v>
+        <v>818</v>
       </c>
     </row>
     <row r="288" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
-        <v>813</v>
+        <v>819</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>814</v>
+        <v>820</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>815</v>
+        <v>821</v>
       </c>
     </row>
     <row r="289" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
-        <v>816</v>
+        <v>822</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>817</v>
+        <v>823</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>818</v>
+        <v>824</v>
       </c>
     </row>
     <row r="290" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>820</v>
+        <v>826</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>821</v>
+        <v>827</v>
       </c>
     </row>
     <row r="291" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
-        <v>822</v>
+        <v>828</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>823</v>
+        <v>829</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>824</v>
+        <v>830</v>
       </c>
     </row>
     <row r="292" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
-        <v>825</v>
+        <v>831</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>826</v>
+        <v>832</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>827</v>
+        <v>833</v>
       </c>
     </row>
     <row r="293" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
-        <v>828</v>
+        <v>834</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>829</v>
+        <v>678</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>830</v>
+        <v>679</v>
       </c>
     </row>
     <row r="294" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
     </row>
     <row r="295" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
     </row>
     <row r="296" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
     </row>
     <row r="297" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
     </row>
     <row r="298" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
     </row>
     <row r="299" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>847</v>
+        <v>52</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>848</v>
+        <v>53</v>
       </c>
     </row>
     <row r="300" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
     </row>
     <row r="301" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
     </row>
     <row r="302" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
     </row>
     <row r="303" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
     </row>
     <row r="304" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
     </row>
     <row r="305" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
     </row>
     <row r="306" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
     </row>
     <row r="307" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
     </row>
     <row r="308" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
     </row>
     <row r="309" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
     </row>
     <row r="310" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
     </row>
     <row r="311" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
     </row>
     <row r="312" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
     </row>
     <row r="313" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
     </row>
     <row r="314" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
     </row>
     <row r="315" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
     </row>
     <row r="316" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
     </row>
     <row r="317" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
     </row>
     <row r="318" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>240</v>
+        <v>398</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>241</v>
+        <v>399</v>
       </c>
     </row>
     <row r="319" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>541</v>
+        <v>907</v>
       </c>
     </row>
     <row r="320" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
     </row>
     <row r="321" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
     </row>
     <row r="322" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>167</v>
+        <v>915</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>168</v>
+        <v>916</v>
       </c>
     </row>
     <row r="323" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
     </row>
     <row r="324" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
     </row>
     <row r="325" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>920</v>
+        <v>924</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
     </row>
     <row r="326" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
-        <v>922</v>
+        <v>926</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>924</v>
+        <v>928</v>
       </c>
     </row>
     <row r="327" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
     </row>
     <row r="328" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
     </row>
     <row r="329" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
     </row>
     <row r="330" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
     </row>
     <row r="331" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>222</v>
+        <v>941</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>223</v>
+        <v>942</v>
       </c>
     </row>
     <row r="332" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
-        <v>938</v>
+        <v>943</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>939</v>
+        <v>944</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>924</v>
+        <v>945</v>
       </c>
     </row>
     <row r="333" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
-        <v>940</v>
+        <v>946</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>941</v>
+        <v>947</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>942</v>
+        <v>948</v>
       </c>
     </row>
     <row r="334" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
-        <v>943</v>
+        <v>949</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>945</v>
+        <v>951</v>
       </c>
     </row>
     <row r="335" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
-        <v>946</v>
+        <v>952</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>947</v>
+        <v>953</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>948</v>
+        <v>954</v>
       </c>
     </row>
     <row r="336" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>950</v>
+        <v>956</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>951</v>
+        <v>957</v>
       </c>
     </row>
     <row r="337" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
-        <v>952</v>
+        <v>958</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>953</v>
+        <v>959</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>954</v>
+        <v>960</v>
       </c>
     </row>
     <row r="338" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
-        <v>955</v>
+        <v>961</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>240</v>
+        <v>962</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>241</v>
+        <v>963</v>
       </c>
     </row>
     <row r="339" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
-        <v>956</v>
+        <v>964</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>957</v>
+        <v>965</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>958</v>
+        <v>966</v>
       </c>
     </row>
     <row r="340" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
-        <v>959</v>
+        <v>967</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>960</v>
+        <v>968</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>961</v>
+        <v>969</v>
       </c>
     </row>
     <row r="341" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
-        <v>962</v>
+        <v>970</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>963</v>
+        <v>971</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>964</v>
+        <v>972</v>
       </c>
     </row>
     <row r="342" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
-        <v>965</v>
+        <v>973</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>966</v>
+        <v>974</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>967</v>
+        <v>975</v>
       </c>
     </row>
     <row r="343" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
-        <v>968</v>
+        <v>976</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>969</v>
+        <v>977</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>970</v>
+        <v>978</v>
       </c>
     </row>
     <row r="344" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
-        <v>971</v>
+        <v>979</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>972</v>
+        <v>980</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>973</v>
+        <v>981</v>
       </c>
     </row>
     <row r="345" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
-        <v>974</v>
+        <v>982</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>975</v>
+        <v>983</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>976</v>
+        <v>984</v>
       </c>
     </row>
     <row r="346" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
-        <v>977</v>
+        <v>985</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>978</v>
+        <v>986</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>979</v>
+        <v>987</v>
       </c>
     </row>
     <row r="347" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
-        <v>980</v>
+        <v>988</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>981</v>
+        <v>989</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>982</v>
+        <v>990</v>
       </c>
     </row>
     <row r="348" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
-        <v>983</v>
+        <v>991</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>984</v>
+        <v>992</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>985</v>
+        <v>993</v>
       </c>
     </row>
     <row r="349" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
-        <v>986</v>
+        <v>994</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>987</v>
+        <v>995</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>988</v>
+        <v>996</v>
       </c>
     </row>
     <row r="350" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
-        <v>989</v>
+        <v>997</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>990</v>
+        <v>998</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>991</v>
+        <v>999</v>
       </c>
     </row>
     <row r="351" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
-        <v>992</v>
+        <v>1000</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>993</v>
+        <v>1001</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>994</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="352" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
-        <v>995</v>
+        <v>1003</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>996</v>
+        <v>1004</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>997</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="353" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
-        <v>998</v>
+        <v>1006</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>999</v>
+        <v>1007</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>1000</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="354" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
-        <v>1001</v>
+        <v>1009</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>1002</v>
+        <v>1010</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>1003</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="355" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>296</v>
+        <v>1013</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>1005</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="356" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
-        <v>1006</v>
+        <v>1015</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>1007</v>
+        <v>1016</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>1008</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="357" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
-        <v>1009</v>
+        <v>1018</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>1010</v>
+        <v>1019</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>1011</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="358" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
-        <v>1012</v>
+        <v>1021</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>1013</v>
+        <v>1022</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>1014</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="359" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
-        <v>1015</v>
+        <v>1024</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>1016</v>
+        <v>276</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>1017</v>
+        <v>277</v>
       </c>
     </row>
     <row r="360" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
-        <v>1018</v>
+        <v>1025</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>1019</v>
+        <v>1026</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>1020</v>
+        <v>595</v>
       </c>
     </row>
     <row r="361" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
-        <v>1021</v>
+        <v>1027</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>1022</v>
+        <v>1028</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>1023</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="362" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
-        <v>1024</v>
+        <v>1030</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>1025</v>
+        <v>1031</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>1026</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="363" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
-        <v>1027</v>
+        <v>1033</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>1028</v>
+        <v>173</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>1029</v>
+        <v>174</v>
       </c>
     </row>
     <row r="364" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
-        <v>1030</v>
+        <v>1034</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="365" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
-        <v>1033</v>
+        <v>1037</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>1034</v>
+        <v>1038</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>1035</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="366" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>1037</v>
+        <v>1041</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="367" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
-        <v>1039</v>
+        <v>1043</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>1040</v>
+        <v>1044</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>1041</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="368" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
-        <v>1042</v>
+        <v>1046</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>1044</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="369" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
-        <v>1045</v>
+        <v>1049</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>1046</v>
+        <v>1050</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>1047</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="370" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="371" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
-        <v>1051</v>
+        <v>1055</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>1052</v>
+        <v>1056</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="372" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
-        <v>1054</v>
+        <v>1058</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>1055</v>
+        <v>258</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>1056</v>
+        <v>259</v>
       </c>
     </row>
     <row r="373" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>1059</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="374" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="375" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="376" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A376" s="2" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="C376" s="2" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="377" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A377" s="2" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="C377" s="2" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="378" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>785</v>
+        <v>1074</v>
       </c>
       <c r="C378" s="2" t="s">
-        <v>786</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="379" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A379" s="2" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>1074</v>
+        <v>276</v>
       </c>
       <c r="C379" s="2" t="s">
-        <v>1075</v>
+        <v>277</v>
       </c>
     </row>
     <row r="380" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A380" s="2" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C380" s="2" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="381" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A381" s="2" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="B381" s="2" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="C381" s="2" t="s">
-        <v>159</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="382" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A382" s="2" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>161</v>
+        <v>1084</v>
       </c>
       <c r="C382" s="2" t="s">
-        <v>162</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="383" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A383" s="2" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>1083</v>
+        <v>1087</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>1084</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="384" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A384" s="2" t="s">
-        <v>1085</v>
+        <v>1089</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>167</v>
+        <v>1090</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>168</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="385" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A385" s="2" t="s">
-        <v>1086</v>
+        <v>1092</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>1087</v>
+        <v>1093</v>
       </c>
       <c r="C385" s="2" t="s">
-        <v>1088</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="386" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A386" s="2" t="s">
-        <v>1089</v>
+        <v>1095</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>228</v>
+        <v>1096</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>229</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="387" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A387" s="2" t="s">
-        <v>1090</v>
+        <v>1098</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>1091</v>
+        <v>1099</v>
       </c>
       <c r="C387" s="2" t="s">
-        <v>1092</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="388" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A388" s="2" t="s">
-        <v>1093</v>
+        <v>1101</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>898</v>
+        <v>1102</v>
       </c>
       <c r="C388" s="2" t="s">
-        <v>1094</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="389" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A389" s="2" t="s">
-        <v>1095</v>
+        <v>1104</v>
       </c>
       <c r="B389" s="2" t="s">
-        <v>249</v>
+        <v>1105</v>
       </c>
       <c r="C389" s="2" t="s">
-        <v>250</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="390" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A390" s="2" t="s">
-        <v>1096</v>
+        <v>1107</v>
       </c>
       <c r="B390" s="2" t="s">
-        <v>243</v>
+        <v>1108</v>
       </c>
       <c r="C390" s="2" t="s">
-        <v>244</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="391" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A391" s="2" t="s">
-        <v>1097</v>
+        <v>1110</v>
       </c>
       <c r="B391" s="2" t="s">
-        <v>1098</v>
+        <v>1111</v>
       </c>
       <c r="C391" s="2" t="s">
-        <v>1099</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="392" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A392" s="2" t="s">
-        <v>1100</v>
+        <v>1113</v>
       </c>
       <c r="B392" s="2" t="s">
-        <v>1101</v>
+        <v>1114</v>
       </c>
       <c r="C392" s="2" t="s">
-        <v>1102</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="393" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A393" s="2" t="s">
-        <v>1103</v>
+        <v>1116</v>
       </c>
       <c r="B393" s="2" t="s">
-        <v>259</v>
+        <v>1117</v>
       </c>
       <c r="C393" s="2" t="s">
-        <v>260</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="394" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A394" s="2" t="s">
-        <v>1104</v>
+        <v>1119</v>
       </c>
       <c r="B394" s="2" t="s">
-        <v>1105</v>
+        <v>1120</v>
       </c>
       <c r="C394" s="2" t="s">
-        <v>1106</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="395" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A395" s="2" t="s">
-        <v>1107</v>
+        <v>1122</v>
       </c>
       <c r="B395" s="2" t="s">
-        <v>265</v>
+        <v>1123</v>
       </c>
       <c r="C395" s="2" t="s">
-        <v>266</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="396" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A396" s="2" t="s">
-        <v>1108</v>
+        <v>1125</v>
       </c>
       <c r="B396" s="2" t="s">
-        <v>1109</v>
+        <v>332</v>
       </c>
       <c r="C396" s="2" t="s">
-        <v>1110</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="397" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A397" s="2" t="s">
-        <v>1111</v>
+        <v>1127</v>
       </c>
       <c r="B397" s="2" t="s">
-        <v>1112</v>
+        <v>1128</v>
       </c>
       <c r="C397" s="2" t="s">
-        <v>1112</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="398" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A398" s="2" t="s">
-        <v>1113</v>
+        <v>1130</v>
       </c>
       <c r="B398" s="2" t="s">
-        <v>1114</v>
+        <v>1131</v>
       </c>
       <c r="C398" s="2" t="s">
-        <v>1114</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="399" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A399" s="2" t="s">
-        <v>1115</v>
+        <v>1133</v>
       </c>
       <c r="B399" s="2" t="s">
-        <v>1116</v>
+        <v>1134</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>1117</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="400" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A400" s="2" t="s">
-        <v>1118</v>
+        <v>1136</v>
       </c>
       <c r="B400" s="2" t="s">
-        <v>1116</v>
+        <v>1137</v>
       </c>
       <c r="C400" s="2" t="s">
-        <v>1117</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="401" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A401" s="2" t="s">
-        <v>1119</v>
+        <v>1139</v>
       </c>
       <c r="B401" s="2" t="s">
-        <v>1120</v>
+        <v>1140</v>
       </c>
       <c r="C401" s="2" t="s">
-        <v>1121</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="402" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A402" s="2" t="s">
-        <v>1122</v>
+        <v>1142</v>
       </c>
       <c r="B402" s="2" t="s">
-        <v>1123</v>
+        <v>1143</v>
       </c>
       <c r="C402" s="2" t="s">
-        <v>1124</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="403" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A403" s="2" t="s">
-        <v>1125</v>
+        <v>1145</v>
       </c>
       <c r="B403" s="2" t="s">
-        <v>1126</v>
+        <v>1146</v>
       </c>
       <c r="C403" s="2" t="s">
-        <v>1127</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="404" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A404" s="2" t="s">
-        <v>1128</v>
+        <v>1148</v>
       </c>
       <c r="B404" s="2" t="s">
-        <v>1129</v>
+        <v>1149</v>
       </c>
       <c r="C404" s="2" t="s">
-        <v>1130</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="405" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A405" s="2" t="s">
-        <v>1131</v>
+        <v>1151</v>
       </c>
       <c r="B405" s="2" t="s">
-        <v>1132</v>
+        <v>1152</v>
       </c>
       <c r="C405" s="2" t="s">
-        <v>1133</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="406" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A406" s="2" t="s">
-        <v>1134</v>
+        <v>1154</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>1135</v>
+        <v>1155</v>
       </c>
       <c r="C406" s="2" t="s">
-        <v>1136</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="407" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A407" s="2" t="s">
-        <v>1137</v>
+        <v>1157</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>1138</v>
+        <v>1158</v>
       </c>
       <c r="C407" s="2" t="s">
-        <v>1139</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="408" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A408" s="2" t="s">
-        <v>1140</v>
+        <v>1160</v>
       </c>
       <c r="B408" s="2" t="s">
-        <v>1141</v>
+        <v>1161</v>
       </c>
       <c r="C408" s="2" t="s">
-        <v>1142</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="409" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A409" s="2" t="s">
-        <v>1143</v>
+        <v>1163</v>
       </c>
       <c r="B409" s="2" t="s">
-        <v>1144</v>
+        <v>1164</v>
       </c>
       <c r="C409" s="2" t="s">
-        <v>1145</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="410" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A410" s="2" t="s">
-        <v>1146</v>
+        <v>1166</v>
       </c>
       <c r="B410" s="2" t="s">
-        <v>1147</v>
+        <v>1167</v>
       </c>
       <c r="C410" s="2" t="s">
-        <v>1148</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="411" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A411" s="2" t="s">
-        <v>1149</v>
+        <v>1169</v>
       </c>
       <c r="B411" s="2" t="s">
-        <v>1150</v>
+        <v>1170</v>
       </c>
       <c r="C411" s="2" t="s">
-        <v>1151</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="412" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A412" s="2" t="s">
-        <v>1152</v>
+        <v>1172</v>
       </c>
       <c r="B412" s="2" t="s">
-        <v>1153</v>
+        <v>1173</v>
       </c>
       <c r="C412" s="2" t="s">
-        <v>1154</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="413" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A413" s="2" t="s">
-        <v>1155</v>
+        <v>1175</v>
       </c>
       <c r="B413" s="2" t="s">
-        <v>1156</v>
+        <v>1176</v>
       </c>
       <c r="C413" s="2" t="s">
-        <v>1157</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="414" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A414" s="2" t="s">
-        <v>1158</v>
+        <v>1178</v>
       </c>
       <c r="B414" s="2" t="s">
-        <v>1159</v>
+        <v>1179</v>
       </c>
       <c r="C414" s="2" t="s">
-        <v>1136</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="415" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A415" s="2" t="s">
-        <v>1160</v>
+        <v>1181</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>1161</v>
+        <v>1182</v>
       </c>
       <c r="C415" s="2" t="s">
-        <v>1162</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="416" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A416" s="2" t="s">
-        <v>1163</v>
+        <v>1184</v>
       </c>
       <c r="B416" s="2" t="s">
-        <v>1164</v>
+        <v>1185</v>
       </c>
       <c r="C416" s="2" t="s">
-        <v>1142</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="417" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A417" s="2" t="s">
-        <v>1165</v>
+        <v>1187</v>
       </c>
       <c r="B417" s="2" t="s">
-        <v>1166</v>
+        <v>1188</v>
       </c>
       <c r="C417" s="2" t="s">
-        <v>1167</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="418" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A418" s="2" t="s">
-        <v>1168</v>
+        <v>1190</v>
       </c>
       <c r="B418" s="2" t="s">
-        <v>1169</v>
+        <v>1191</v>
       </c>
       <c r="C418" s="2" t="s">
-        <v>1170</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="419" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A419" s="2" t="s">
-        <v>1171</v>
+        <v>1193</v>
       </c>
       <c r="B419" s="2" t="s">
-        <v>1026</v>
+        <v>906</v>
       </c>
       <c r="C419" s="2" t="s">
-        <v>1026</v>
+        <v>907</v>
       </c>
     </row>
     <row r="420" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A420" s="2" t="s">
-        <v>1172</v>
+        <v>1194</v>
       </c>
       <c r="B420" s="2" t="s">
-        <v>1173</v>
+        <v>1195</v>
       </c>
       <c r="C420" s="2" t="s">
-        <v>1174</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="421" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A421" s="2" t="s">
-        <v>1175</v>
+        <v>1197</v>
       </c>
       <c r="B421" s="2" t="s">
-        <v>1176</v>
+        <v>1198</v>
       </c>
       <c r="C421" s="2" t="s">
-        <v>1177</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="422" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A422" s="2" t="s">
-        <v>1178</v>
+        <v>1200</v>
       </c>
       <c r="B422" s="2" t="s">
-        <v>1179</v>
+        <v>1201</v>
       </c>
       <c r="C422" s="2" t="s">
-        <v>1180</v>
+        <v>165</v>
       </c>
     </row>
     <row r="423" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A423" s="2" t="s">
-        <v>1181</v>
+        <v>1202</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>1182</v>
+        <v>167</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>1183</v>
+        <v>168</v>
       </c>
     </row>
     <row r="424" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A424" s="2" t="s">
-        <v>1184</v>
+        <v>1203</v>
       </c>
       <c r="B424" s="2" t="s">
-        <v>1185</v>
+        <v>1204</v>
       </c>
       <c r="C424" s="2" t="s">
-        <v>1186</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="425" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A425" s="2" t="s">
-        <v>1187</v>
+        <v>1206</v>
       </c>
       <c r="B425" s="2" t="s">
-        <v>1188</v>
+        <v>173</v>
       </c>
       <c r="C425" s="2" t="s">
-        <v>1189</v>
+        <v>174</v>
       </c>
     </row>
     <row r="426" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A426" s="2" t="s">
-        <v>1190</v>
+        <v>1207</v>
       </c>
       <c r="B426" s="2" t="s">
-        <v>1191</v>
+        <v>1208</v>
       </c>
       <c r="C426" s="2" t="s">
-        <v>1192</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="427" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A427" s="2" t="s">
-        <v>1193</v>
+        <v>1210</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>1194</v>
+        <v>264</v>
       </c>
       <c r="C427" s="2" t="s">
-        <v>1195</v>
+        <v>265</v>
       </c>
     </row>
     <row r="428" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A428" s="2" t="s">
-        <v>1196</v>
+        <v>1211</v>
       </c>
       <c r="B428" s="2" t="s">
-        <v>1064</v>
+        <v>1212</v>
       </c>
       <c r="C428" s="2" t="s">
-        <v>1065</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="429" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A429" s="2" t="s">
-        <v>1197</v>
+        <v>1214</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>1198</v>
+        <v>1019</v>
       </c>
       <c r="C429" s="2" t="s">
-        <v>1199</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="430" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A430" s="2" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="B430" s="2" t="s">
-        <v>1201</v>
+        <v>285</v>
       </c>
       <c r="C430" s="2" t="s">
-        <v>1202</v>
+        <v>286</v>
       </c>
     </row>
     <row r="431" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A431" s="2" t="s">
-        <v>1203</v>
+        <v>1217</v>
       </c>
       <c r="B431" s="2" t="s">
-        <v>1204</v>
+        <v>279</v>
       </c>
       <c r="C431" s="2" t="s">
-        <v>1205</v>
+        <v>280</v>
       </c>
     </row>
     <row r="432" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A432" s="2" t="s">
-        <v>1206</v>
+        <v>1218</v>
       </c>
       <c r="B432" s="2" t="s">
-        <v>1207</v>
+        <v>1219</v>
       </c>
       <c r="C432" s="2" t="s">
-        <v>1208</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="433" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A433" s="2" t="s">
-        <v>1209</v>
+        <v>1221</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>1210</v>
+        <v>1222</v>
       </c>
       <c r="C433" s="2" t="s">
-        <v>1211</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="434" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A434" s="2" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
       <c r="B434" s="2" t="s">
-        <v>1213</v>
+        <v>295</v>
       </c>
       <c r="C434" s="2" t="s">
-        <v>1214</v>
+        <v>296</v>
       </c>
     </row>
     <row r="435" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A435" s="2" t="s">
-        <v>1215</v>
+        <v>1225</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>1216</v>
+        <v>1226</v>
       </c>
       <c r="C435" s="2" t="s">
-        <v>193</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="436" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A436" s="2" t="s">
-        <v>1217</v>
+        <v>1228</v>
       </c>
       <c r="B436" s="2" t="s">
-        <v>161</v>
+        <v>301</v>
       </c>
       <c r="C436" s="2" t="s">
-        <v>162</v>
+        <v>302</v>
       </c>
     </row>
     <row r="437" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A437" s="2" t="s">
-        <v>1218</v>
+        <v>1229</v>
       </c>
       <c r="B437" s="2" t="s">
-        <v>164</v>
+        <v>1230</v>
       </c>
       <c r="C437" s="2" t="s">
-        <v>165</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="438" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A438" s="2" t="s">
-        <v>1219</v>
+        <v>1232</v>
       </c>
       <c r="B438" s="2" t="s">
-        <v>527</v>
+        <v>1233</v>
       </c>
       <c r="C438" s="2" t="s">
-        <v>528</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="439" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A439" s="2" t="s">
-        <v>1220</v>
+        <v>1234</v>
       </c>
       <c r="B439" s="2" t="s">
-        <v>1221</v>
+        <v>1235</v>
       </c>
       <c r="C439" s="2" t="s">
-        <v>1222</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="440" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A440" s="2" t="s">
-        <v>1223</v>
+        <v>1236</v>
       </c>
       <c r="B440" s="2" t="s">
-        <v>1224</v>
+        <v>1237</v>
       </c>
       <c r="C440" s="2" t="s">
-        <v>1225</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="441" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A441" s="2" t="s">
-        <v>1226</v>
+        <v>1239</v>
       </c>
       <c r="B441" s="2" t="s">
-        <v>1227</v>
+        <v>1237</v>
       </c>
       <c r="C441" s="2" t="s">
-        <v>1228</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="442" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A442" s="2" t="s">
-        <v>1229</v>
+        <v>1240</v>
       </c>
       <c r="B442" s="2" t="s">
-        <v>1230</v>
+        <v>1241</v>
       </c>
       <c r="C442" s="2" t="s">
-        <v>1231</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="443" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A443" s="2" t="s">
-        <v>1232</v>
+        <v>1243</v>
       </c>
       <c r="B443" s="2" t="s">
-        <v>1233</v>
+        <v>1244</v>
       </c>
       <c r="C443" s="2" t="s">
-        <v>1234</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="444" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A444" s="2" t="s">
-        <v>1235</v>
+        <v>1246</v>
       </c>
       <c r="B444" s="2" t="s">
-        <v>1236</v>
+        <v>1247</v>
       </c>
       <c r="C444" s="2" t="s">
-        <v>1237</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="445" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A445" s="2" t="s">
-        <v>1238</v>
+        <v>1249</v>
       </c>
       <c r="B445" s="2" t="s">
-        <v>1239</v>
+        <v>1250</v>
       </c>
       <c r="C445" s="2" t="s">
-        <v>1240</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="446" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A446" s="2" t="s">
-        <v>1241</v>
+        <v>1252</v>
       </c>
       <c r="B446" s="2" t="s">
-        <v>1242</v>
+        <v>1253</v>
       </c>
       <c r="C446" s="2" t="s">
-        <v>1243</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="447" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A447" s="2" t="s">
-        <v>1244</v>
+        <v>1255</v>
       </c>
       <c r="B447" s="2" t="s">
-        <v>1245</v>
+        <v>1256</v>
       </c>
       <c r="C447" s="2" t="s">
-        <v>1246</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="448" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A448" s="2" t="s">
-        <v>1247</v>
+        <v>1258</v>
       </c>
       <c r="B448" s="2" t="s">
-        <v>1248</v>
+        <v>1259</v>
       </c>
       <c r="C448" s="2" t="s">
-        <v>1249</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="449" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A449" s="2" t="s">
-        <v>1250</v>
+        <v>1261</v>
       </c>
       <c r="B449" s="2" t="s">
-        <v>1251</v>
+        <v>1262</v>
       </c>
       <c r="C449" s="2" t="s">
-        <v>1252</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="450" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A450" s="2" t="s">
-        <v>1253</v>
+        <v>1264</v>
       </c>
       <c r="B450" s="2" t="s">
-        <v>1254</v>
+        <v>1265</v>
       </c>
       <c r="C450" s="2" t="s">
-        <v>1255</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="451" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A451" s="2" t="s">
-        <v>1256</v>
+        <v>1267</v>
       </c>
       <c r="B451" s="2" t="s">
-        <v>1257</v>
+        <v>1268</v>
       </c>
       <c r="C451" s="2" t="s">
-        <v>1258</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="452" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A452" s="2" t="s">
-        <v>1259</v>
+        <v>1270</v>
       </c>
       <c r="B452" s="2" t="s">
-        <v>1260</v>
+        <v>1271</v>
       </c>
       <c r="C452" s="2" t="s">
-        <v>1261</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="453" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A453" s="2" t="s">
-        <v>1262</v>
+        <v>1273</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>1263</v>
+        <v>1274</v>
       </c>
       <c r="C453" s="2" t="s">
-        <v>1264</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="454" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A454" s="2" t="s">
-        <v>1265</v>
+        <v>1276</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>1266</v>
+        <v>1277</v>
       </c>
       <c r="C454" s="2" t="s">
-        <v>1267</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="455" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A455" s="2" t="s">
-        <v>1268</v>
+        <v>1279</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>1269</v>
+        <v>1280</v>
       </c>
       <c r="C455" s="2" t="s">
-        <v>1270</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="456" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A456" s="2" t="s">
-        <v>1271</v>
+        <v>1281</v>
       </c>
       <c r="B456" s="2" t="s">
-        <v>1272</v>
+        <v>1282</v>
       </c>
       <c r="C456" s="2" t="s">
-        <v>1273</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="457" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A457" s="2" t="s">
-        <v>1274</v>
+        <v>1284</v>
       </c>
       <c r="B457" s="2" t="s">
-        <v>1275</v>
+        <v>1285</v>
       </c>
       <c r="C457" s="2" t="s">
-        <v>1276</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="458" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A458" s="2" t="s">
-        <v>1277</v>
+        <v>1286</v>
       </c>
       <c r="B458" s="2" t="s">
-        <v>43</v>
+        <v>1287</v>
       </c>
       <c r="C458" s="2" t="s">
-        <v>44</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="459" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A459" s="2" t="s">
-        <v>1278</v>
+        <v>1289</v>
       </c>
       <c r="B459" s="2" t="s">
-        <v>1279</v>
+        <v>1290</v>
       </c>
       <c r="C459" s="2" t="s">
-        <v>908</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="460" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A460" s="2" t="s">
-        <v>1280</v>
+        <v>1292</v>
       </c>
       <c r="B460" s="2" t="s">
-        <v>1221</v>
+        <v>1293</v>
       </c>
       <c r="C460" s="2" t="s">
-        <v>1222</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="461" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A461" s="2" t="s">
-        <v>1281</v>
+        <v>1295</v>
       </c>
       <c r="B461" s="2" t="s">
-        <v>1282</v>
+        <v>1147</v>
       </c>
       <c r="C461" s="2" t="s">
-        <v>1017</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="462" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A462" s="2" t="s">
-        <v>1283</v>
+        <v>1296</v>
       </c>
       <c r="B462" s="2" t="s">
-        <v>1284</v>
+        <v>1297</v>
       </c>
       <c r="C462" s="2" t="s">
-        <v>1285</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="463" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A463" s="2" t="s">
-        <v>1286</v>
+        <v>1299</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>1224</v>
+        <v>1300</v>
       </c>
       <c r="C463" s="2" t="s">
-        <v>1225</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="464" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A464" s="2" t="s">
-        <v>1287</v>
+        <v>1302</v>
       </c>
       <c r="B464" s="2" t="s">
-        <v>170</v>
+        <v>1303</v>
       </c>
       <c r="C464" s="2" t="s">
-        <v>170</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="465" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A465" s="2" t="s">
-        <v>1288</v>
+        <v>1305</v>
       </c>
       <c r="B465" s="2" t="s">
-        <v>1289</v>
+        <v>1306</v>
       </c>
       <c r="C465" s="2" t="s">
-        <v>1290</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="466" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A466" s="2" t="s">
-        <v>1291</v>
+        <v>1308</v>
       </c>
       <c r="B466" s="2" t="s">
-        <v>1292</v>
+        <v>1309</v>
       </c>
       <c r="C466" s="2" t="s">
-        <v>1293</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="467" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A467" s="2" t="s">
-        <v>1294</v>
+        <v>1311</v>
       </c>
       <c r="B467" s="2" t="s">
-        <v>1295</v>
+        <v>1312</v>
       </c>
       <c r="C467" s="2" t="s">
-        <v>1296</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="468" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A468" s="2" t="s">
-        <v>1297</v>
+        <v>1314</v>
       </c>
       <c r="B468" s="2" t="s">
-        <v>1298</v>
+        <v>1315</v>
       </c>
       <c r="C468" s="2" t="s">
-        <v>1299</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="469" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A469" s="2" t="s">
-        <v>1300</v>
+        <v>1317</v>
       </c>
       <c r="B469" s="2" t="s">
-        <v>1301</v>
+        <v>1318</v>
       </c>
       <c r="C469" s="2" t="s">
-        <v>1302</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="470" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A470" s="2" t="s">
-        <v>1303</v>
+        <v>1320</v>
       </c>
       <c r="B470" s="2" t="s">
-        <v>1061</v>
+        <v>1185</v>
       </c>
       <c r="C470" s="2" t="s">
-        <v>1062</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="471" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A471" s="2" t="s">
-        <v>1304</v>
+        <v>1321</v>
       </c>
       <c r="B471" s="2" t="s">
-        <v>4</v>
+        <v>1322</v>
       </c>
       <c r="C471" s="2" t="s">
-        <v>5</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="472" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A472" s="2" t="s">
-        <v>1305</v>
+        <v>1324</v>
       </c>
       <c r="B472" s="2" t="s">
-        <v>1049</v>
+        <v>1325</v>
       </c>
       <c r="C472" s="2" t="s">
-        <v>1050</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="473" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A473" s="2" t="s">
-        <v>1306</v>
+        <v>1327</v>
       </c>
       <c r="B473" s="2" t="s">
-        <v>1064</v>
+        <v>1328</v>
       </c>
       <c r="C473" s="2" t="s">
-        <v>1065</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="474" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A474" s="2" t="s">
-        <v>1307</v>
+        <v>1330</v>
       </c>
       <c r="B474" s="2" t="s">
-        <v>1308</v>
+        <v>1331</v>
       </c>
       <c r="C474" s="2" t="s">
-        <v>1309</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="475" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A475" s="2" t="s">
-        <v>1310</v>
+        <v>1333</v>
       </c>
       <c r="B475" s="2" t="s">
-        <v>1311</v>
+        <v>1334</v>
       </c>
       <c r="C475" s="2" t="s">
-        <v>1312</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="476" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A476" s="2" t="s">
-        <v>1313</v>
+        <v>1336</v>
       </c>
       <c r="B476" s="2" t="s">
-        <v>1067</v>
+        <v>1337</v>
       </c>
       <c r="C476" s="2" t="s">
-        <v>1068</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="477" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A477" s="2" t="s">
-        <v>1314</v>
+        <v>1339</v>
       </c>
       <c r="B477" s="2" t="s">
-        <v>1315</v>
+        <v>1340</v>
       </c>
       <c r="C477" s="2" t="s">
-        <v>1316</v>
+        <v>199</v>
       </c>
     </row>
     <row r="478" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A478" s="2" t="s">
-        <v>1317</v>
+        <v>1341</v>
       </c>
       <c r="B478" s="2" t="s">
-        <v>1070</v>
+        <v>167</v>
       </c>
       <c r="C478" s="2" t="s">
-        <v>1318</v>
+        <v>168</v>
       </c>
     </row>
     <row r="479" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A479" s="2" t="s">
-        <v>1319</v>
+        <v>1342</v>
       </c>
       <c r="B479" s="2" t="s">
-        <v>1016</v>
+        <v>170</v>
       </c>
       <c r="C479" s="2" t="s">
-        <v>1320</v>
+        <v>171</v>
       </c>
     </row>
     <row r="480" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A480" s="2" t="s">
-        <v>1321</v>
+        <v>1343</v>
       </c>
       <c r="B480" s="2" t="s">
-        <v>1322</v>
+        <v>581</v>
       </c>
       <c r="C480" s="2" t="s">
-        <v>1323</v>
+        <v>582</v>
       </c>
     </row>
     <row r="481" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A481" s="2" t="s">
-        <v>1324</v>
+        <v>1344</v>
       </c>
       <c r="B481" s="2" t="s">
-        <v>1325</v>
+        <v>1345</v>
       </c>
       <c r="C481" s="2" t="s">
-        <v>1326</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="482" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A482" s="2" t="s">
-        <v>1327</v>
+        <v>1347</v>
       </c>
       <c r="B482" s="2" t="s">
-        <v>1328</v>
+        <v>1348</v>
       </c>
       <c r="C482" s="2" t="s">
-        <v>1329</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="483" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A483" s="2" t="s">
-        <v>1330</v>
+        <v>1350</v>
       </c>
       <c r="B483" s="2" t="s">
-        <v>1331</v>
+        <v>1351</v>
       </c>
       <c r="C483" s="2" t="s">
-        <v>1332</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="484" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A484" s="2" t="s">
-        <v>1333</v>
+        <v>1353</v>
       </c>
       <c r="B484" s="2" t="s">
-        <v>1334</v>
+        <v>1354</v>
       </c>
       <c r="C484" s="2" t="s">
-        <v>1335</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="485" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A485" s="2" t="s">
-        <v>1336</v>
+        <v>1356</v>
       </c>
       <c r="B485" s="2" t="s">
-        <v>1337</v>
+        <v>1357</v>
       </c>
       <c r="C485" s="2" t="s">
-        <v>1338</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="486" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A486" s="2" t="s">
-        <v>1339</v>
+        <v>1359</v>
       </c>
       <c r="B486" s="2" t="s">
-        <v>1340</v>
+        <v>1360</v>
       </c>
       <c r="C486" s="2" t="s">
-        <v>1341</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="487" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A487" s="2" t="s">
-        <v>1342</v>
+        <v>1362</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>1343</v>
+        <v>1363</v>
       </c>
       <c r="C487" s="2" t="s">
-        <v>1344</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="488" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A488" s="2" t="s">
-        <v>1345</v>
+        <v>1365</v>
       </c>
       <c r="B488" s="2" t="s">
-        <v>1346</v>
+        <v>1366</v>
       </c>
       <c r="C488" s="2" t="s">
-        <v>1347</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="489" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A489" s="2" t="s">
-        <v>1348</v>
+        <v>1368</v>
       </c>
       <c r="B489" s="2" t="s">
-        <v>1061</v>
+        <v>1369</v>
       </c>
       <c r="C489" s="2" t="s">
-        <v>1062</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="490" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A490" s="2" t="s">
-        <v>1349</v>
+        <v>1371</v>
       </c>
       <c r="B490" s="2" t="s">
-        <v>4</v>
+        <v>1372</v>
       </c>
       <c r="C490" s="2" t="s">
-        <v>5</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="491" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A491" s="2" t="s">
-        <v>1350</v>
+        <v>1374</v>
       </c>
       <c r="B491" s="2" t="s">
-        <v>1067</v>
+        <v>1375</v>
       </c>
       <c r="C491" s="2" t="s">
-        <v>1068</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="492" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A492" s="2" t="s">
-        <v>1351</v>
+        <v>1377</v>
       </c>
       <c r="B492" s="2" t="s">
-        <v>1352</v>
+        <v>1378</v>
       </c>
       <c r="C492" s="2" t="s">
-        <v>1353</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="493" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A493" s="2" t="s">
-        <v>1354</v>
+        <v>1380</v>
       </c>
       <c r="B493" s="2" t="s">
-        <v>1355</v>
+        <v>1381</v>
       </c>
       <c r="C493" s="2" t="s">
-        <v>1356</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="494" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A494" s="2" t="s">
-        <v>1357</v>
+        <v>1383</v>
       </c>
       <c r="B494" s="2" t="s">
-        <v>1358</v>
+        <v>1384</v>
       </c>
       <c r="C494" s="2" t="s">
-        <v>1359</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="495" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A495" s="2" t="s">
-        <v>1360</v>
+        <v>1386</v>
       </c>
       <c r="B495" s="2" t="s">
-        <v>1331</v>
+        <v>1387</v>
       </c>
       <c r="C495" s="2" t="s">
-        <v>1332</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="496" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A496" s="2" t="s">
-        <v>1361</v>
+        <v>1389</v>
       </c>
       <c r="B496" s="2" t="s">
-        <v>1362</v>
+        <v>1390</v>
       </c>
       <c r="C496" s="2" t="s">
-        <v>1363</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="497" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A497" s="2" t="s">
-        <v>1364</v>
+        <v>1392</v>
       </c>
       <c r="B497" s="2" t="s">
-        <v>1365</v>
+        <v>1393</v>
       </c>
       <c r="C497" s="2" t="s">
-        <v>1366</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="498" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A498" s="2" t="s">
-        <v>1367</v>
+        <v>1395</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>1185</v>
+        <v>1396</v>
       </c>
       <c r="C498" s="2" t="s">
-        <v>1186</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="499" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A499" s="2" t="s">
-        <v>1368</v>
+        <v>1398</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>1369</v>
+        <v>1399</v>
       </c>
       <c r="C499" s="2" t="s">
-        <v>1370</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="500" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A500" s="2" t="s">
-        <v>1371</v>
+        <v>1401</v>
       </c>
       <c r="B500" s="2" t="s">
-        <v>1372</v>
+        <v>43</v>
       </c>
       <c r="C500" s="2" t="s">
-        <v>1373</v>
+        <v>44</v>
       </c>
     </row>
     <row r="501" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A501" s="2" t="s">
-        <v>1374</v>
+        <v>1402</v>
       </c>
       <c r="B501" s="2" t="s">
-        <v>1375</v>
+        <v>1403</v>
       </c>
       <c r="C501" s="2" t="s">
-        <v>1376</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="502" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A502" s="2" t="s">
-        <v>1377</v>
+        <v>1404</v>
       </c>
       <c r="B502" s="2" t="s">
-        <v>1378</v>
+        <v>1345</v>
       </c>
       <c r="C502" s="2" t="s">
-        <v>1379</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="503" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A503" s="2" t="s">
-        <v>1380</v>
+        <v>1405</v>
       </c>
       <c r="B503" s="2" t="s">
-        <v>1381</v>
+        <v>1406</v>
       </c>
       <c r="C503" s="2" t="s">
-        <v>1382</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="504" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A504" s="2" t="s">
-        <v>1383</v>
+        <v>1407</v>
       </c>
       <c r="B504" s="2" t="s">
-        <v>1384</v>
+        <v>1408</v>
       </c>
       <c r="C504" s="2" t="s">
-        <v>1385</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="505" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A505" s="2" t="s">
-        <v>1386</v>
+        <v>1410</v>
       </c>
       <c r="B505" s="2" t="s">
-        <v>1387</v>
+        <v>1348</v>
       </c>
       <c r="C505" s="2" t="s">
-        <v>1388</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="506" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A506" s="2" t="s">
-        <v>1389</v>
+        <v>1411</v>
       </c>
       <c r="B506" s="2" t="s">
-        <v>1390</v>
+        <v>176</v>
       </c>
       <c r="C506" s="2" t="s">
-        <v>461</v>
+        <v>176</v>
       </c>
     </row>
     <row r="507" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A507" s="2" t="s">
-        <v>1391</v>
+        <v>1412</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>1392</v>
+        <v>1413</v>
       </c>
       <c r="C507" s="2" t="s">
-        <v>1393</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="508" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A508" s="2" t="s">
-        <v>1394</v>
+        <v>1415</v>
       </c>
       <c r="B508" s="2" t="s">
-        <v>1395</v>
+        <v>1416</v>
       </c>
       <c r="C508" s="2" t="s">
-        <v>1396</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="509" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A509" s="2" t="s">
-        <v>1397</v>
+        <v>1418</v>
       </c>
       <c r="B509" s="2" t="s">
-        <v>1398</v>
+        <v>1419</v>
       </c>
       <c r="C509" s="2" t="s">
-        <v>1399</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="510" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A510" s="2" t="s">
-        <v>1400</v>
+        <v>1421</v>
       </c>
       <c r="B510" s="2" t="s">
-        <v>1401</v>
+        <v>1422</v>
       </c>
       <c r="C510" s="2" t="s">
-        <v>1402</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="511" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A511" s="2" t="s">
-        <v>1403</v>
+        <v>1424</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>1404</v>
+        <v>1425</v>
       </c>
       <c r="C511" s="2" t="s">
-        <v>1405</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="512" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A512" s="2" t="s">
-        <v>1406</v>
+        <v>1427</v>
       </c>
       <c r="B512" s="2" t="s">
-        <v>1407</v>
+        <v>1182</v>
       </c>
       <c r="C512" s="2" t="s">
-        <v>1408</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="513" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A513" s="2" t="s">
-        <v>1409</v>
+        <v>1428</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>1410</v>
+        <v>4</v>
       </c>
       <c r="C513" s="2" t="s">
-        <v>1411</v>
+        <v>5</v>
       </c>
     </row>
     <row r="514" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A514" s="2" t="s">
-        <v>1412</v>
+        <v>1429</v>
       </c>
       <c r="B514" s="2" t="s">
-        <v>1413</v>
+        <v>1170</v>
       </c>
       <c r="C514" s="2" t="s">
-        <v>1414</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="515" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A515" s="2" t="s">
-        <v>1415</v>
+        <v>1430</v>
       </c>
       <c r="B515" s="2" t="s">
-        <v>460</v>
+        <v>1185</v>
       </c>
       <c r="C515" s="2" t="s">
-        <v>461</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="516" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A516" s="2" t="s">
-        <v>1416</v>
+        <v>1431</v>
       </c>
       <c r="B516" s="2" t="s">
-        <v>1417</v>
+        <v>1432</v>
       </c>
       <c r="C516" s="2" t="s">
-        <v>1418</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="517" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A517" s="2" t="s">
-        <v>1419</v>
+        <v>1434</v>
       </c>
       <c r="B517" s="2" t="s">
-        <v>1420</v>
+        <v>1435</v>
       </c>
       <c r="C517" s="2" t="s">
-        <v>1421</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="518" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A518" s="2" t="s">
-        <v>1422</v>
+        <v>1437</v>
       </c>
       <c r="B518" s="2" t="s">
-        <v>228</v>
+        <v>1188</v>
       </c>
       <c r="C518" s="2" t="s">
-        <v>229</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="519" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A519" s="2" t="s">
-        <v>1423</v>
+        <v>1438</v>
       </c>
       <c r="B519" s="2" t="s">
-        <v>1424</v>
+        <v>1439</v>
       </c>
       <c r="C519" s="2" t="s">
-        <v>1425</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="520" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A520" s="2" t="s">
-        <v>1426</v>
+        <v>1441</v>
       </c>
       <c r="B520" s="2" t="s">
-        <v>1427</v>
+        <v>1191</v>
       </c>
       <c r="C520" s="2" t="s">
-        <v>1428</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="521" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A521" s="2" t="s">
-        <v>1429</v>
+        <v>1443</v>
       </c>
       <c r="B521" s="2" t="s">
-        <v>1430</v>
+        <v>1137</v>
       </c>
       <c r="C521" s="2" t="s">
-        <v>1431</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="522" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A522" s="2" t="s">
-        <v>1432</v>
+        <v>1445</v>
       </c>
       <c r="B522" s="2" t="s">
-        <v>1433</v>
+        <v>1446</v>
       </c>
       <c r="C522" s="2" t="s">
-        <v>1434</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="523" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A523" s="2" t="s">
-        <v>1435</v>
+        <v>1448</v>
       </c>
       <c r="B523" s="2" t="s">
-        <v>1436</v>
+        <v>1449</v>
       </c>
       <c r="C523" s="2" t="s">
-        <v>1437</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="524" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A524" s="2" t="s">
-        <v>1438</v>
+        <v>1451</v>
       </c>
       <c r="B524" s="2" t="s">
-        <v>1439</v>
+        <v>1452</v>
       </c>
       <c r="C524" s="2" t="s">
-        <v>1440</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="525" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A525" s="2" t="s">
-        <v>1441</v>
+        <v>1454</v>
       </c>
       <c r="B525" s="2" t="s">
-        <v>1442</v>
+        <v>1455</v>
       </c>
       <c r="C525" s="2" t="s">
-        <v>1443</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="526" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A526" s="2" t="s">
-        <v>1444</v>
+        <v>1457</v>
       </c>
       <c r="B526" s="2" t="s">
-        <v>1445</v>
+        <v>1458</v>
       </c>
       <c r="C526" s="2" t="s">
-        <v>1446</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="527" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A527" s="2" t="s">
-        <v>1447</v>
+        <v>1460</v>
       </c>
       <c r="B527" s="2" t="s">
-        <v>1448</v>
+        <v>1461</v>
       </c>
       <c r="C527" s="2" t="s">
-        <v>1449</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="528" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A528" s="2" t="s">
-        <v>1450</v>
+        <v>1463</v>
       </c>
       <c r="B528" s="2" t="s">
-        <v>1451</v>
+        <v>1464</v>
       </c>
       <c r="C528" s="2" t="s">
-        <v>1452</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="529" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A529" s="2" t="s">
-        <v>1453</v>
+        <v>1466</v>
       </c>
       <c r="B529" s="2" t="s">
-        <v>1454</v>
+        <v>1467</v>
       </c>
       <c r="C529" s="2" t="s">
-        <v>1455</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="530" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A530" s="2" t="s">
-        <v>1456</v>
+        <v>1469</v>
       </c>
       <c r="B530" s="2" t="s">
-        <v>1457</v>
+        <v>1470</v>
       </c>
       <c r="C530" s="2" t="s">
-        <v>1458</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="531" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A531" s="2" t="s">
-        <v>1459</v>
+        <v>1472</v>
       </c>
       <c r="B531" s="2" t="s">
-        <v>222</v>
+        <v>1182</v>
       </c>
       <c r="C531" s="2" t="s">
-        <v>223</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="532" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A532" s="2" t="s">
-        <v>1460</v>
+        <v>1473</v>
       </c>
       <c r="B532" s="2" t="s">
-        <v>1461</v>
+        <v>4</v>
       </c>
       <c r="C532" s="2" t="s">
-        <v>908</v>
+        <v>5</v>
       </c>
     </row>
     <row r="533" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A533" s="2" t="s">
-        <v>1462</v>
+        <v>1474</v>
       </c>
       <c r="B533" s="2" t="s">
-        <v>1463</v>
+        <v>1188</v>
       </c>
       <c r="C533" s="2" t="s">
-        <v>1464</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="534" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A534" s="2" t="s">
-        <v>1465</v>
+        <v>1475</v>
       </c>
       <c r="B534" s="2" t="s">
-        <v>1284</v>
+        <v>1476</v>
       </c>
       <c r="C534" s="2" t="s">
-        <v>1285</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="535" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A535" s="2" t="s">
-        <v>1466</v>
+        <v>1478</v>
       </c>
       <c r="B535" s="2" t="s">
-        <v>1467</v>
+        <v>1479</v>
       </c>
       <c r="C535" s="2" t="s">
-        <v>1468</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="536" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A536" s="2" t="s">
-        <v>1469</v>
+        <v>1481</v>
       </c>
       <c r="B536" s="2" t="s">
-        <v>1470</v>
+        <v>1482</v>
       </c>
       <c r="C536" s="2" t="s">
-        <v>1471</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="537" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A537" s="2" t="s">
-        <v>1472</v>
+        <v>1484</v>
       </c>
       <c r="B537" s="2" t="s">
-        <v>1473</v>
+        <v>1455</v>
       </c>
       <c r="C537" s="2" t="s">
-        <v>1474</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="538" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A538" s="2" t="s">
-        <v>1475</v>
+        <v>1485</v>
       </c>
       <c r="B538" s="2" t="s">
-        <v>1476</v>
+        <v>1486</v>
       </c>
       <c r="C538" s="2" t="s">
-        <v>1477</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="539" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A539" s="2" t="s">
-        <v>1478</v>
+        <v>1488</v>
       </c>
       <c r="B539" s="2" t="s">
-        <v>1479</v>
+        <v>1489</v>
       </c>
       <c r="C539" s="2" t="s">
-        <v>1480</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="540" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A540" s="2" t="s">
-        <v>1481</v>
+        <v>1491</v>
       </c>
       <c r="B540" s="2" t="s">
-        <v>161</v>
+        <v>1309</v>
       </c>
       <c r="C540" s="2" t="s">
-        <v>162</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="541" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A541" s="2" t="s">
-        <v>1482</v>
+        <v>1492</v>
       </c>
       <c r="B541" s="2" t="s">
-        <v>905</v>
+        <v>1493</v>
       </c>
       <c r="C541" s="2" t="s">
-        <v>541</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="542" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A542" s="2" t="s">
-        <v>1483</v>
+        <v>1495</v>
       </c>
       <c r="B542" s="2" t="s">
-        <v>914</v>
+        <v>1496</v>
       </c>
       <c r="C542" s="2" t="s">
-        <v>1484</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="543" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A543" s="2" t="s">
-        <v>1485</v>
+        <v>1498</v>
       </c>
       <c r="B543" s="2" t="s">
-        <v>1486</v>
+        <v>1499</v>
       </c>
       <c r="C543" s="2" t="s">
-        <v>1487</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="544" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A544" s="2" t="s">
-        <v>1488</v>
+        <v>1501</v>
       </c>
       <c r="B544" s="2" t="s">
-        <v>222</v>
+        <v>1502</v>
       </c>
       <c r="C544" s="2" t="s">
-        <v>223</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="545" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A545" s="2" t="s">
-        <v>1489</v>
+        <v>1504</v>
       </c>
       <c r="B545" s="2" t="s">
-        <v>1490</v>
+        <v>1505</v>
       </c>
       <c r="C545" s="2" t="s">
-        <v>1491</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="546" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A546" s="2" t="s">
-        <v>1492</v>
+        <v>1507</v>
       </c>
       <c r="B546" s="2" t="s">
-        <v>1493</v>
+        <v>1508</v>
       </c>
       <c r="C546" s="2" t="s">
-        <v>1494</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="547" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A547" s="2" t="s">
-        <v>1495</v>
+        <v>1510</v>
       </c>
       <c r="B547" s="2" t="s">
-        <v>1496</v>
+        <v>1511</v>
       </c>
       <c r="C547" s="2" t="s">
-        <v>1497</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="548" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A548" s="2" t="s">
-        <v>1498</v>
+        <v>1513</v>
       </c>
       <c r="B548" s="2" t="s">
-        <v>1499</v>
+        <v>1514</v>
       </c>
       <c r="C548" s="2" t="s">
-        <v>1500</v>
+        <v>497</v>
       </c>
     </row>
     <row r="549" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A549" s="2" t="s">
-        <v>1501</v>
+        <v>1515</v>
       </c>
       <c r="B549" s="2" t="s">
-        <v>228</v>
+        <v>1516</v>
       </c>
       <c r="C549" s="2" t="s">
-        <v>229</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="550" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A550" s="2" t="s">
-        <v>1502</v>
+        <v>1518</v>
       </c>
       <c r="B550" s="2" t="s">
-        <v>1503</v>
+        <v>1519</v>
       </c>
       <c r="C550" s="2" t="s">
-        <v>1504</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="551" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A551" s="2" t="s">
-        <v>1505</v>
+        <v>1521</v>
       </c>
       <c r="B551" s="2" t="s">
-        <v>1506</v>
+        <v>1522</v>
       </c>
       <c r="C551" s="2" t="s">
-        <v>1507</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="552" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A552" s="2" t="s">
-        <v>1508</v>
+        <v>1524</v>
       </c>
       <c r="B552" s="2" t="s">
-        <v>1509</v>
+        <v>1525</v>
       </c>
       <c r="C552" s="2" t="s">
-        <v>1510</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="553" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A553" s="2" t="s">
-        <v>1511</v>
+        <v>1527</v>
       </c>
       <c r="B553" s="2" t="s">
-        <v>1512</v>
+        <v>1528</v>
       </c>
       <c r="C553" s="2" t="s">
-        <v>1513</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="554" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A554" s="2" t="s">
-        <v>1514</v>
+        <v>1530</v>
       </c>
       <c r="B554" s="2" t="s">
-        <v>1515</v>
+        <v>1531</v>
       </c>
       <c r="C554" s="2" t="s">
-        <v>1516</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="555" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A555" s="2" t="s">
-        <v>1517</v>
+        <v>1533</v>
       </c>
       <c r="B555" s="2" t="s">
-        <v>460</v>
+        <v>1534</v>
       </c>
       <c r="C555" s="2" t="s">
-        <v>461</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="556" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A556" s="2" t="s">
-        <v>1518</v>
+        <v>1536</v>
       </c>
       <c r="B556" s="2" t="s">
-        <v>1519</v>
+        <v>1537</v>
       </c>
       <c r="C556" s="2" t="s">
-        <v>1520</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="557" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A557" s="2" t="s">
-        <v>1521</v>
+        <v>1539</v>
       </c>
       <c r="B557" s="2" t="s">
-        <v>1522</v>
+        <v>496</v>
       </c>
       <c r="C557" s="2" t="s">
-        <v>1523</v>
+        <v>497</v>
       </c>
     </row>
     <row r="558" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A558" s="2" t="s">
-        <v>1524</v>
+        <v>1540</v>
       </c>
       <c r="B558" s="2" t="s">
-        <v>1525</v>
+        <v>1541</v>
       </c>
       <c r="C558" s="2" t="s">
-        <v>1526</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="559" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A559" s="2" t="s">
-        <v>1527</v>
+        <v>1543</v>
       </c>
       <c r="B559" s="2" t="s">
-        <v>1528</v>
+        <v>1544</v>
       </c>
       <c r="C559" s="2" t="s">
-        <v>1529</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="560" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A560" s="2" t="s">
-        <v>1530</v>
+        <v>1546</v>
       </c>
       <c r="B560" s="2" t="s">
-        <v>1531</v>
+        <v>264</v>
       </c>
       <c r="C560" s="2" t="s">
-        <v>1532</v>
+        <v>265</v>
       </c>
     </row>
     <row r="561" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A561" s="2" t="s">
-        <v>1533</v>
+        <v>1547</v>
       </c>
       <c r="B561" s="2" t="s">
-        <v>19</v>
+        <v>1548</v>
       </c>
       <c r="C561" s="2" t="s">
-        <v>20</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="562" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A562" s="2" t="s">
-        <v>1534</v>
+        <v>1550</v>
       </c>
       <c r="B562" s="2" t="s">
-        <v>1535</v>
+        <v>1551</v>
       </c>
       <c r="C562" s="2" t="s">
-        <v>1536</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="563" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A563" s="2" t="s">
-        <v>1537</v>
+        <v>1553</v>
       </c>
       <c r="B563" s="2" t="s">
-        <v>1538</v>
+        <v>1554</v>
       </c>
       <c r="C563" s="2" t="s">
-        <v>1539</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="564" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A564" s="2" t="s">
-        <v>1540</v>
+        <v>1556</v>
       </c>
       <c r="B564" s="2" t="s">
-        <v>1541</v>
+        <v>1557</v>
       </c>
       <c r="C564" s="2" t="s">
-        <v>1542</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="565" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A565" s="2" t="s">
-        <v>1543</v>
+        <v>1559</v>
       </c>
       <c r="B565" s="2" t="s">
-        <v>1544</v>
+        <v>1560</v>
       </c>
       <c r="C565" s="2" t="s">
-        <v>1545</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="566" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A566" s="2" t="s">
-        <v>1546</v>
+        <v>1562</v>
       </c>
       <c r="B566" s="2" t="s">
-        <v>1547</v>
+        <v>1563</v>
       </c>
       <c r="C566" s="2" t="s">
-        <v>1548</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="567" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A567" s="2" t="s">
-        <v>1549</v>
+        <v>1565</v>
       </c>
       <c r="B567" s="2" t="s">
-        <v>1550</v>
+        <v>1566</v>
       </c>
       <c r="C567" s="2" t="s">
-        <v>1551</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="568" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A568" s="2" t="s">
-        <v>1552</v>
+        <v>1568</v>
       </c>
       <c r="B568" s="2" t="s">
-        <v>1553</v>
+        <v>1569</v>
       </c>
       <c r="C568" s="2" t="s">
-        <v>1554</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="569" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A569" s="2" t="s">
-        <v>1555</v>
+        <v>1571</v>
       </c>
       <c r="B569" s="2" t="s">
-        <v>1556</v>
+        <v>1572</v>
       </c>
       <c r="C569" s="2" t="s">
-        <v>1557</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="570" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A570" s="2" t="s">
-        <v>1558</v>
+        <v>1574</v>
       </c>
       <c r="B570" s="2" t="s">
-        <v>1559</v>
+        <v>1575</v>
       </c>
       <c r="C570" s="2" t="s">
-        <v>1560</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="571" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A571" s="2" t="s">
-        <v>1561</v>
+        <v>1577</v>
       </c>
       <c r="B571" s="2" t="s">
-        <v>1562</v>
+        <v>1578</v>
       </c>
       <c r="C571" s="2" t="s">
-        <v>1563</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="572" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A572" s="2" t="s">
-        <v>1564</v>
+        <v>1580</v>
       </c>
       <c r="B572" s="2" t="s">
-        <v>1565</v>
+        <v>1581</v>
       </c>
       <c r="C572" s="2" t="s">
-        <v>1566</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="573" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A573" s="2" t="s">
-        <v>1567</v>
+        <v>1583</v>
       </c>
       <c r="B573" s="2" t="s">
-        <v>1568</v>
+        <v>258</v>
       </c>
       <c r="C573" s="2" t="s">
-        <v>1569</v>
+        <v>259</v>
       </c>
     </row>
     <row r="574" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A574" s="2" t="s">
-        <v>1570</v>
+        <v>1584</v>
       </c>
       <c r="B574" s="2" t="s">
-        <v>645</v>
+        <v>1585</v>
       </c>
       <c r="C574" s="2" t="s">
-        <v>1571</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="575" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A575" s="2" t="s">
-        <v>1572</v>
+        <v>1586</v>
       </c>
       <c r="B575" s="2" t="s">
-        <v>1573</v>
+        <v>1587</v>
       </c>
       <c r="C575" s="2" t="s">
-        <v>1574</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="576" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A576" s="2" t="s">
-        <v>1575</v>
+        <v>1589</v>
       </c>
       <c r="B576" s="2" t="s">
-        <v>1576</v>
+        <v>1408</v>
       </c>
       <c r="C576" s="2" t="s">
-        <v>1577</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="577" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A577" s="2" t="s">
-        <v>1578</v>
+        <v>1590</v>
       </c>
       <c r="B577" s="2" t="s">
-        <v>1579</v>
+        <v>1591</v>
       </c>
       <c r="C577" s="2" t="s">
-        <v>1580</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="578" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A578" s="2" t="s">
-        <v>1581</v>
+        <v>1593</v>
       </c>
       <c r="B578" s="2" t="s">
-        <v>1582</v>
+        <v>1594</v>
       </c>
       <c r="C578" s="2" t="s">
-        <v>1583</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="579" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A579" s="2" t="s">
-        <v>1584</v>
+        <v>1596</v>
       </c>
       <c r="B579" s="2" t="s">
-        <v>1585</v>
+        <v>1597</v>
       </c>
       <c r="C579" s="2" t="s">
-        <v>1586</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="580" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A580" s="2" t="s">
-        <v>1587</v>
+        <v>1599</v>
       </c>
       <c r="B580" s="2" t="s">
-        <v>1588</v>
+        <v>1600</v>
       </c>
       <c r="C580" s="2" t="s">
-        <v>1589</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="581" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A581" s="2" t="s">
-        <v>1590</v>
+        <v>1602</v>
       </c>
       <c r="B581" s="2" t="s">
-        <v>1591</v>
+        <v>1603</v>
       </c>
       <c r="C581" s="2" t="s">
-        <v>1592</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="582" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A582" s="2" t="s">
-        <v>1593</v>
+        <v>1605</v>
       </c>
       <c r="B582" s="2" t="s">
-        <v>1594</v>
+        <v>167</v>
       </c>
       <c r="C582" s="2" t="s">
-        <v>401</v>
+        <v>168</v>
       </c>
     </row>
     <row r="583" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A583" s="2" t="s">
-        <v>1595</v>
+        <v>1606</v>
       </c>
       <c r="B583" s="2" t="s">
-        <v>1596</v>
+        <v>1026</v>
       </c>
       <c r="C583" s="2" t="s">
-        <v>1597</v>
+        <v>595</v>
       </c>
     </row>
     <row r="584" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A584" s="2" t="s">
-        <v>1598</v>
+        <v>1607</v>
       </c>
       <c r="B584" s="2" t="s">
-        <v>1599</v>
+        <v>1035</v>
       </c>
       <c r="C584" s="2" t="s">
-        <v>1600</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="585" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A585" s="2" t="s">
-        <v>1601</v>
+        <v>1609</v>
       </c>
       <c r="B585" s="2" t="s">
-        <v>222</v>
+        <v>1610</v>
       </c>
       <c r="C585" s="2" t="s">
-        <v>223</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="586" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A586" s="2" t="s">
-        <v>1602</v>
+        <v>1612</v>
       </c>
       <c r="B586" s="2" t="s">
-        <v>1603</v>
+        <v>258</v>
       </c>
       <c r="C586" s="2" t="s">
-        <v>159</v>
+        <v>259</v>
       </c>
     </row>
     <row r="587" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A587" s="2" t="s">
-        <v>1604</v>
+        <v>1613</v>
       </c>
       <c r="B587" s="2" t="s">
-        <v>1605</v>
+        <v>1614</v>
       </c>
       <c r="C587" s="2" t="s">
-        <v>1606</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="588" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A588" s="2" t="s">
-        <v>1607</v>
+        <v>1616</v>
       </c>
       <c r="B588" s="2" t="s">
-        <v>1608</v>
+        <v>1617</v>
       </c>
       <c r="C588" s="2" t="s">
-        <v>401</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="589" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A589" s="2" t="s">
-        <v>1609</v>
+        <v>1619</v>
       </c>
       <c r="B589" s="2" t="s">
-        <v>1610</v>
+        <v>1620</v>
       </c>
       <c r="C589" s="2" t="s">
-        <v>1611</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="590" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A590" s="2" t="s">
-        <v>1612</v>
+        <v>1622</v>
       </c>
       <c r="B590" s="2" t="s">
-        <v>664</v>
+        <v>1623</v>
       </c>
       <c r="C590" s="2" t="s">
-        <v>665</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="591" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A591" s="2" t="s">
-        <v>1613</v>
+        <v>1625</v>
       </c>
       <c r="B591" s="2" t="s">
-        <v>4</v>
+        <v>264</v>
       </c>
       <c r="C591" s="2" t="s">
-        <v>5</v>
+        <v>265</v>
       </c>
     </row>
     <row r="592" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A592" s="2" t="s">
-        <v>1614</v>
+        <v>1626</v>
       </c>
       <c r="B592" s="2" t="s">
-        <v>228</v>
+        <v>1627</v>
       </c>
       <c r="C592" s="2" t="s">
-        <v>229</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="593" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A593" s="2" t="s">
-        <v>1615</v>
+        <v>1629</v>
       </c>
       <c r="B593" s="2" t="s">
-        <v>1610</v>
+        <v>1630</v>
       </c>
       <c r="C593" s="2" t="s">
-        <v>1611</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="594" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A594" s="2" t="s">
-        <v>1616</v>
+        <v>1632</v>
       </c>
       <c r="B594" s="2" t="s">
-        <v>1617</v>
+        <v>1633</v>
       </c>
       <c r="C594" s="2" t="s">
-        <v>1618</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="595" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A595" s="2" t="s">
-        <v>1619</v>
+        <v>1635</v>
       </c>
       <c r="B595" s="2" t="s">
-        <v>1620</v>
+        <v>1636</v>
       </c>
       <c r="C595" s="2" t="s">
-        <v>1621</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="596" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A596" s="2" t="s">
-        <v>1622</v>
+        <v>1638</v>
       </c>
       <c r="B596" s="2" t="s">
-        <v>1623</v>
+        <v>1639</v>
       </c>
       <c r="C596" s="2" t="s">
-        <v>1624</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="597" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A597" s="2" t="s">
-        <v>1625</v>
+        <v>1641</v>
       </c>
       <c r="B597" s="2" t="s">
-        <v>1626</v>
+        <v>496</v>
       </c>
       <c r="C597" s="2" t="s">
-        <v>1627</v>
+        <v>497</v>
       </c>
     </row>
     <row r="598" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A598" s="2" t="s">
-        <v>1628</v>
+        <v>1642</v>
       </c>
       <c r="B598" s="2" t="s">
-        <v>1629</v>
+        <v>1643</v>
       </c>
       <c r="C598" s="2" t="s">
-        <v>1630</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="599" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A599" s="2" t="s">
-        <v>1631</v>
+        <v>1645</v>
       </c>
       <c r="B599" s="2" t="s">
-        <v>1632</v>
+        <v>1646</v>
       </c>
       <c r="C599" s="2" t="s">
-        <v>1633</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="600" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A600" s="2" t="s">
-        <v>1634</v>
+        <v>1648</v>
       </c>
       <c r="B600" s="2" t="s">
-        <v>1635</v>
+        <v>1649</v>
       </c>
       <c r="C600" s="2" t="s">
-        <v>1636</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="601" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A601" s="2" t="s">
-        <v>1637</v>
+        <v>1651</v>
       </c>
       <c r="B601" s="2" t="s">
-        <v>1638</v>
+        <v>1652</v>
       </c>
       <c r="C601" s="2" t="s">
-        <v>1639</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="602" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A602" s="2" t="s">
-        <v>1640</v>
+        <v>1654</v>
       </c>
       <c r="B602" s="2" t="s">
-        <v>19</v>
+        <v>1655</v>
       </c>
       <c r="C602" s="2" t="s">
-        <v>20</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="603" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A603" s="2" t="s">
-        <v>1641</v>
+        <v>1657</v>
       </c>
       <c r="B603" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C603" s="2" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="604" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A604" s="2" t="s">
-        <v>1642</v>
+        <v>1658</v>
       </c>
       <c r="B604" s="2" t="s">
-        <v>16</v>
+        <v>1659</v>
       </c>
       <c r="C604" s="2" t="s">
-        <v>17</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="605" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A605" s="2" t="s">
-        <v>1643</v>
+        <v>1661</v>
       </c>
       <c r="B605" s="2" t="s">
-        <v>1644</v>
+        <v>1662</v>
       </c>
       <c r="C605" s="2" t="s">
-        <v>1645</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="606" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A606" s="2" t="s">
-        <v>1646</v>
+        <v>1664</v>
       </c>
       <c r="B606" s="2" t="s">
-        <v>1647</v>
+        <v>1665</v>
       </c>
       <c r="C606" s="2" t="s">
-        <v>1648</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="607" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A607" s="2" t="s">
-        <v>1649</v>
+        <v>1667</v>
       </c>
       <c r="B607" s="2" t="s">
-        <v>1650</v>
+        <v>1668</v>
       </c>
       <c r="C607" s="2" t="s">
-        <v>1651</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="608" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A608" s="2" t="s">
-        <v>1652</v>
+        <v>1670</v>
       </c>
       <c r="B608" s="2" t="s">
-        <v>1653</v>
+        <v>1671</v>
       </c>
       <c r="C608" s="2" t="s">
-        <v>1654</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="609" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A609" s="2" t="s">
-        <v>1655</v>
+        <v>1673</v>
       </c>
       <c r="B609" s="2" t="s">
-        <v>1556</v>
+        <v>1674</v>
       </c>
       <c r="C609" s="2" t="s">
-        <v>1557</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="610" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A610" s="2" t="s">
-        <v>1656</v>
+        <v>1676</v>
       </c>
       <c r="B610" s="2" t="s">
-        <v>1559</v>
+        <v>1677</v>
       </c>
       <c r="C610" s="2" t="s">
-        <v>1560</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="611" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A611" s="2" t="s">
-        <v>1657</v>
+        <v>1679</v>
       </c>
       <c r="B611" s="2" t="s">
-        <v>1658</v>
+        <v>1680</v>
       </c>
       <c r="C611" s="2" t="s">
-        <v>1071</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="612" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A612" s="2" t="s">
-        <v>1659</v>
+        <v>1682</v>
       </c>
       <c r="B612" s="2" t="s">
-        <v>1660</v>
+        <v>1683</v>
       </c>
       <c r="C612" s="2" t="s">
-        <v>1661</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="613" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A613" s="2" t="s">
-        <v>1662</v>
+        <v>1685</v>
       </c>
       <c r="B613" s="2" t="s">
-        <v>917</v>
+        <v>1686</v>
       </c>
       <c r="C613" s="2" t="s">
-        <v>918</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="614" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A614" s="2" t="s">
-        <v>1663</v>
+        <v>1688</v>
       </c>
       <c r="B614" s="2" t="s">
-        <v>1664</v>
+        <v>1689</v>
       </c>
       <c r="C614" s="2" t="s">
-        <v>1569</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="615" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A615" s="2" t="s">
-        <v>1665</v>
+        <v>1691</v>
       </c>
       <c r="B615" s="2" t="s">
-        <v>645</v>
+        <v>1692</v>
       </c>
       <c r="C615" s="2" t="s">
-        <v>1571</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="616" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A616" s="2" t="s">
-        <v>1666</v>
+        <v>1694</v>
       </c>
       <c r="B616" s="2" t="s">
-        <v>1667</v>
+        <v>697</v>
       </c>
       <c r="C616" s="2" t="s">
-        <v>1668</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="617" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A617" s="2" t="s">
-        <v>1669</v>
+        <v>1696</v>
       </c>
       <c r="B617" s="2" t="s">
-        <v>1670</v>
+        <v>1697</v>
       </c>
       <c r="C617" s="2" t="s">
-        <v>1661</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="618" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A618" s="2" t="s">
-        <v>1671</v>
+        <v>1699</v>
       </c>
       <c r="B618" s="2" t="s">
-        <v>648</v>
+        <v>1700</v>
       </c>
       <c r="C618" s="2" t="s">
-        <v>1672</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="619" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A619" s="2" t="s">
-        <v>1673</v>
+        <v>1702</v>
       </c>
       <c r="B619" s="2" t="s">
-        <v>660</v>
+        <v>1703</v>
       </c>
       <c r="C619" s="2" t="s">
-        <v>1674</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="620" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A620" s="2" t="s">
-        <v>1675</v>
+        <v>1705</v>
       </c>
       <c r="B620" s="2" t="s">
-        <v>463</v>
+        <v>1706</v>
       </c>
       <c r="C620" s="2" t="s">
-        <v>401</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="621" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A621" s="2" t="s">
-        <v>1676</v>
+        <v>1708</v>
       </c>
       <c r="B621" s="2" t="s">
-        <v>664</v>
+        <v>1709</v>
       </c>
       <c r="C621" s="2" t="s">
-        <v>665</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="622" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A622" s="2" t="s">
-        <v>1677</v>
+        <v>1711</v>
       </c>
       <c r="B622" s="2" t="s">
-        <v>228</v>
+        <v>1712</v>
       </c>
       <c r="C622" s="2" t="s">
-        <v>229</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="623" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A623" s="2" t="s">
-        <v>1678</v>
+        <v>1714</v>
       </c>
       <c r="B623" s="2" t="s">
-        <v>1679</v>
+        <v>1715</v>
       </c>
       <c r="C623" s="2" t="s">
-        <v>1680</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="624" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A624" s="2" t="s">
-        <v>1681</v>
+        <v>1717</v>
       </c>
       <c r="B624" s="2" t="s">
-        <v>1682</v>
+        <v>1718</v>
       </c>
       <c r="C624" s="2" t="s">
-        <v>1683</v>
+        <v>437</v>
       </c>
     </row>
     <row r="625" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A625" s="2" t="s">
-        <v>1684</v>
+        <v>1719</v>
       </c>
       <c r="B625" s="2" t="s">
-        <v>1685</v>
+        <v>1720</v>
       </c>
       <c r="C625" s="2" t="s">
-        <v>1686</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="626" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A626" s="2" t="s">
-        <v>1687</v>
+        <v>1722</v>
       </c>
       <c r="B626" s="2" t="s">
-        <v>692</v>
+        <v>1723</v>
       </c>
       <c r="C626" s="2" t="s">
-        <v>693</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="627" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A627" s="2" t="s">
-        <v>1688</v>
+        <v>1725</v>
       </c>
       <c r="B627" s="2" t="s">
-        <v>660</v>
+        <v>258</v>
       </c>
       <c r="C627" s="2" t="s">
-        <v>1674</v>
+        <v>259</v>
       </c>
     </row>
     <row r="628" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A628" s="2" t="s">
-        <v>1689</v>
+        <v>1726</v>
       </c>
       <c r="B628" s="2" t="s">
-        <v>696</v>
+        <v>1727</v>
       </c>
       <c r="C628" s="2" t="s">
-        <v>697</v>
+        <v>165</v>
       </c>
     </row>
     <row r="629" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A629" s="2" t="s">
-        <v>1690</v>
+        <v>1728</v>
       </c>
       <c r="B629" s="2" t="s">
-        <v>1691</v>
+        <v>1729</v>
       </c>
       <c r="C629" s="2" t="s">
-        <v>1692</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="630" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A630" s="2" t="s">
-        <v>1693</v>
+        <v>1731</v>
       </c>
       <c r="B630" s="2" t="s">
-        <v>702</v>
+        <v>1732</v>
       </c>
       <c r="C630" s="2" t="s">
-        <v>1694</v>
+        <v>437</v>
       </c>
     </row>
     <row r="631" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A631" s="2" t="s">
-        <v>1695</v>
+        <v>1733</v>
       </c>
       <c r="B631" s="2" t="s">
-        <v>1696</v>
+        <v>1734</v>
       </c>
       <c r="C631" s="2" t="s">
-        <v>1697</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="632" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A632" s="2" t="s">
-        <v>1698</v>
+        <v>1736</v>
       </c>
       <c r="B632" s="2" t="s">
-        <v>708</v>
+        <v>782</v>
       </c>
       <c r="C632" s="2" t="s">
-        <v>1699</v>
+        <v>783</v>
       </c>
     </row>
     <row r="633" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A633" s="2" t="s">
-        <v>1700</v>
+        <v>1737</v>
       </c>
       <c r="B633" s="2" t="s">
-        <v>1701</v>
+        <v>4</v>
       </c>
       <c r="C633" s="2" t="s">
-        <v>1702</v>
+        <v>5</v>
       </c>
     </row>
     <row r="634" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A634" s="2" t="s">
-        <v>1703</v>
+        <v>1738</v>
       </c>
       <c r="B634" s="2" t="s">
-        <v>1704</v>
+        <v>264</v>
       </c>
       <c r="C634" s="2" t="s">
-        <v>1705</v>
+        <v>265</v>
       </c>
     </row>
     <row r="635" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A635" s="2" t="s">
-        <v>1706</v>
+        <v>1739</v>
       </c>
       <c r="B635" s="2" t="s">
-        <v>1707</v>
+        <v>1734</v>
       </c>
       <c r="C635" s="2" t="s">
-        <v>1708</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="636" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A636" s="2" t="s">
-        <v>1709</v>
+        <v>1740</v>
       </c>
       <c r="B636" s="2" t="s">
-        <v>624</v>
+        <v>1741</v>
       </c>
       <c r="C636" s="2" t="s">
-        <v>625</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="637" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A637" s="2" t="s">
-        <v>1710</v>
+        <v>1743</v>
       </c>
       <c r="B637" s="2" t="s">
-        <v>718</v>
+        <v>1744</v>
       </c>
       <c r="C637" s="2" t="s">
-        <v>719</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="638" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A638" s="2" t="s">
-        <v>1711</v>
+        <v>1746</v>
       </c>
       <c r="B638" s="2" t="s">
-        <v>721</v>
+        <v>1747</v>
       </c>
       <c r="C638" s="2" t="s">
-        <v>1712</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="639" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A639" s="2" t="s">
-        <v>1713</v>
+        <v>1749</v>
       </c>
       <c r="B639" s="2" t="s">
-        <v>724</v>
+        <v>1750</v>
       </c>
       <c r="C639" s="2" t="s">
-        <v>1714</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="640" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A640" s="2" t="s">
-        <v>1715</v>
+        <v>1752</v>
       </c>
       <c r="B640" s="2" t="s">
-        <v>727</v>
+        <v>1753</v>
       </c>
       <c r="C640" s="2" t="s">
-        <v>1716</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="641" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A641" s="2" t="s">
-        <v>1717</v>
+        <v>1755</v>
       </c>
       <c r="B641" s="2" t="s">
-        <v>1718</v>
+        <v>1756</v>
       </c>
       <c r="C641" s="2" t="s">
-        <v>1719</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="642" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A642" s="2" t="s">
-        <v>1720</v>
+        <v>1758</v>
       </c>
       <c r="B642" s="2" t="s">
-        <v>1556</v>
+        <v>1759</v>
       </c>
       <c r="C642" s="2" t="s">
-        <v>1557</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="643" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A643" s="2" t="s">
-        <v>1721</v>
+        <v>1761</v>
       </c>
       <c r="B643" s="2" t="s">
-        <v>1559</v>
+        <v>1762</v>
       </c>
       <c r="C643" s="2" t="s">
-        <v>1560</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="644" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A644" s="2" t="s">
-        <v>1722</v>
+        <v>1764</v>
       </c>
       <c r="B644" s="2" t="s">
-        <v>1723</v>
+        <v>19</v>
       </c>
       <c r="C644" s="2" t="s">
-        <v>1724</v>
+        <v>20</v>
       </c>
     </row>
     <row r="645" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A645" s="2" t="s">
-        <v>1725</v>
+        <v>1765</v>
       </c>
       <c r="B645" s="2" t="s">
-        <v>1726</v>
+        <v>13</v>
       </c>
       <c r="C645" s="2" t="s">
-        <v>1727</v>
+        <v>14</v>
       </c>
     </row>
     <row r="646" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A646" s="2" t="s">
-        <v>1728</v>
+        <v>1766</v>
       </c>
       <c r="B646" s="2" t="s">
-        <v>1729</v>
+        <v>16</v>
       </c>
       <c r="C646" s="2" t="s">
-        <v>1730</v>
+        <v>17</v>
       </c>
     </row>
     <row r="647" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A647" s="2" t="s">
-        <v>1731</v>
+        <v>1767</v>
       </c>
       <c r="B647" s="2" t="s">
-        <v>1732</v>
+        <v>1768</v>
       </c>
       <c r="C647" s="2" t="s">
-        <v>1733</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="648" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A648" s="2" t="s">
-        <v>1734</v>
+        <v>1770</v>
       </c>
       <c r="B648" s="2" t="s">
-        <v>1735</v>
+        <v>1771</v>
       </c>
       <c r="C648" s="2" t="s">
-        <v>1736</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="649" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A649" s="2" t="s">
-        <v>1737</v>
+        <v>1773</v>
       </c>
       <c r="B649" s="2" t="s">
-        <v>1738</v>
+        <v>1774</v>
       </c>
       <c r="C649" s="2" t="s">
-        <v>1739</v>
+        <v>1775</v>
+      </c>
+    </row>
+    <row r="650" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A650" s="2" t="s">
+        <v>1776</v>
+      </c>
+      <c r="B650" s="2" t="s">
+        <v>1777</v>
+      </c>
+      <c r="C650" s="2" t="s">
+        <v>1778</v>
+      </c>
+    </row>
+    <row r="651" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A651" s="2" t="s">
+        <v>1779</v>
+      </c>
+      <c r="B651" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="C651" s="2" t="s">
+        <v>1681</v>
+      </c>
+    </row>
+    <row r="652" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A652" s="2" t="s">
+        <v>1780</v>
+      </c>
+      <c r="B652" s="2" t="s">
+        <v>1683</v>
+      </c>
+      <c r="C652" s="2" t="s">
+        <v>1684</v>
+      </c>
+    </row>
+    <row r="653" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A653" s="2" t="s">
+        <v>1781</v>
+      </c>
+      <c r="B653" s="2" t="s">
+        <v>1782</v>
+      </c>
+      <c r="C653" s="2" t="s">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="654" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A654" s="2" t="s">
+        <v>1783</v>
+      </c>
+      <c r="B654" s="2" t="s">
+        <v>1784</v>
+      </c>
+      <c r="C654" s="2" t="s">
+        <v>1785</v>
+      </c>
+    </row>
+    <row r="655" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A655" s="2" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B655" s="2" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C655" s="2" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="656" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A656" s="2" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B656" s="2" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C656" s="2" t="s">
+        <v>1693</v>
+      </c>
+    </row>
+    <row r="657" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A657" s="2" t="s">
+        <v>1789</v>
+      </c>
+      <c r="B657" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="C657" s="2" t="s">
+        <v>1695</v>
+      </c>
+    </row>
+    <row r="658" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A658" s="2" t="s">
+        <v>1790</v>
+      </c>
+      <c r="B658" s="2" t="s">
+        <v>1791</v>
+      </c>
+      <c r="C658" s="2" t="s">
+        <v>1792</v>
+      </c>
+    </row>
+    <row r="659" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A659" s="2" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B659" s="2" t="s">
+        <v>1794</v>
+      </c>
+      <c r="C659" s="2" t="s">
+        <v>1785</v>
+      </c>
+    </row>
+    <row r="660" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A660" s="2" t="s">
+        <v>1795</v>
+      </c>
+      <c r="B660" s="2" t="s">
+        <v>766</v>
+      </c>
+      <c r="C660" s="2" t="s">
+        <v>1796</v>
+      </c>
+    </row>
+    <row r="661" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A661" s="2" t="s">
+        <v>1797</v>
+      </c>
+      <c r="B661" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="C661" s="2" t="s">
+        <v>1798</v>
+      </c>
+    </row>
+    <row r="662" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A662" s="2" t="s">
+        <v>1799</v>
+      </c>
+      <c r="B662" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="C662" s="2" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="663" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A663" s="2" t="s">
+        <v>1800</v>
+      </c>
+      <c r="B663" s="2" t="s">
+        <v>782</v>
+      </c>
+      <c r="C663" s="2" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="664" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A664" s="2" t="s">
+        <v>1801</v>
+      </c>
+      <c r="B664" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C664" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="665" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A665" s="2" t="s">
+        <v>1802</v>
+      </c>
+      <c r="B665" s="2" t="s">
+        <v>1803</v>
+      </c>
+      <c r="C665" s="2" t="s">
+        <v>1804</v>
+      </c>
+    </row>
+    <row r="666" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A666" s="2" t="s">
+        <v>1805</v>
+      </c>
+      <c r="B666" s="2" t="s">
+        <v>1806</v>
+      </c>
+      <c r="C666" s="2" t="s">
+        <v>1807</v>
+      </c>
+    </row>
+    <row r="667" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A667" s="2" t="s">
+        <v>1808</v>
+      </c>
+      <c r="B667" s="2" t="s">
+        <v>1809</v>
+      </c>
+      <c r="C667" s="2" t="s">
+        <v>1810</v>
+      </c>
+    </row>
+    <row r="668" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A668" s="2" t="s">
+        <v>1811</v>
+      </c>
+      <c r="B668" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="C668" s="2" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="669" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A669" s="2" t="s">
+        <v>1812</v>
+      </c>
+      <c r="B669" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="C669" s="2" t="s">
+        <v>1798</v>
+      </c>
+    </row>
+    <row r="670" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A670" s="2" t="s">
+        <v>1813</v>
+      </c>
+      <c r="B670" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="C670" s="2" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="671" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A671" s="2" t="s">
+        <v>1814</v>
+      </c>
+      <c r="B671" s="2" t="s">
+        <v>1815</v>
+      </c>
+      <c r="C671" s="2" t="s">
+        <v>1816</v>
+      </c>
+    </row>
+    <row r="672" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A672" s="2" t="s">
+        <v>1817</v>
+      </c>
+      <c r="B672" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="C672" s="2" t="s">
+        <v>1818</v>
+      </c>
+    </row>
+    <row r="673" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A673" s="2" t="s">
+        <v>1819</v>
+      </c>
+      <c r="B673" s="2" t="s">
+        <v>1820</v>
+      </c>
+      <c r="C673" s="2" t="s">
+        <v>1821</v>
+      </c>
+    </row>
+    <row r="674" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A674" s="2" t="s">
+        <v>1822</v>
+      </c>
+      <c r="B674" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="C674" s="2" t="s">
+        <v>1823</v>
+      </c>
+    </row>
+    <row r="675" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A675" s="2" t="s">
+        <v>1824</v>
+      </c>
+      <c r="B675" s="2" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C675" s="2" t="s">
+        <v>1826</v>
+      </c>
+    </row>
+    <row r="676" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A676" s="2" t="s">
+        <v>1827</v>
+      </c>
+      <c r="B676" s="2" t="s">
+        <v>1828</v>
+      </c>
+      <c r="C676" s="2" t="s">
+        <v>1829</v>
+      </c>
+    </row>
+    <row r="677" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A677" s="2" t="s">
+        <v>1830</v>
+      </c>
+      <c r="B677" s="2" t="s">
+        <v>1831</v>
+      </c>
+      <c r="C677" s="2" t="s">
+        <v>1832</v>
+      </c>
+    </row>
+    <row r="678" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A678" s="2" t="s">
+        <v>1833</v>
+      </c>
+      <c r="B678" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="C678" s="2" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="679" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A679" s="2" t="s">
+        <v>1834</v>
+      </c>
+      <c r="B679" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="C679" s="2" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="680" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A680" s="2" t="s">
+        <v>1835</v>
+      </c>
+      <c r="B680" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="C680" s="2" t="s">
+        <v>1836</v>
+      </c>
+    </row>
+    <row r="681" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A681" s="2" t="s">
+        <v>1837</v>
+      </c>
+      <c r="B681" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="C681" s="2" t="s">
+        <v>1838</v>
+      </c>
+    </row>
+    <row r="682" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A682" s="2" t="s">
+        <v>1839</v>
+      </c>
+      <c r="B682" s="2" t="s">
+        <v>845</v>
+      </c>
+      <c r="C682" s="2" t="s">
+        <v>1840</v>
+      </c>
+    </row>
+    <row r="683" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A683" s="2" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B683" s="2" t="s">
+        <v>1842</v>
+      </c>
+      <c r="C683" s="2" t="s">
+        <v>1843</v>
+      </c>
+    </row>
+    <row r="684" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A684" s="2" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B684" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="C684" s="2" t="s">
+        <v>1681</v>
+      </c>
+    </row>
+    <row r="685" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A685" s="2" t="s">
+        <v>1845</v>
+      </c>
+      <c r="B685" s="2" t="s">
+        <v>1683</v>
+      </c>
+      <c r="C685" s="2" t="s">
+        <v>1684</v>
+      </c>
+    </row>
+    <row r="686" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A686" s="2" t="s">
+        <v>1846</v>
+      </c>
+      <c r="B686" s="2" t="s">
+        <v>1847</v>
+      </c>
+      <c r="C686" s="2" t="s">
+        <v>1848</v>
+      </c>
+    </row>
+    <row r="687" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A687" s="2" t="s">
+        <v>1849</v>
+      </c>
+      <c r="B687" s="2" t="s">
+        <v>1850</v>
+      </c>
+      <c r="C687" s="2" t="s">
+        <v>1851</v>
+      </c>
+    </row>
+    <row r="688" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A688" s="2" t="s">
+        <v>1852</v>
+      </c>
+      <c r="B688" s="2" t="s">
+        <v>1853</v>
+      </c>
+      <c r="C688" s="2" t="s">
+        <v>1854</v>
+      </c>
+    </row>
+    <row r="689" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A689" s="2" t="s">
+        <v>1855</v>
+      </c>
+      <c r="B689" s="2" t="s">
+        <v>1856</v>
+      </c>
+      <c r="C689" s="2" t="s">
+        <v>1857</v>
+      </c>
+    </row>
+    <row r="690" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A690" s="2" t="s">
+        <v>1858</v>
+      </c>
+      <c r="B690" s="2" t="s">
+        <v>1859</v>
+      </c>
+      <c r="C690" s="2" t="s">
+        <v>1860</v>
+      </c>
+    </row>
+    <row r="691" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A691" s="2" t="s">
+        <v>1861</v>
+      </c>
+      <c r="B691" s="2" t="s">
+        <v>1862</v>
+      </c>
+      <c r="C691" s="2" t="s">
+        <v>1863</v>
       </c>
     </row>
   </sheetData>

--- a/apps/workspace-web/i18n.xlsx
+++ b/apps/workspace-web/i18n.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2073" uniqueCount="1864">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2271" uniqueCount="2039">
   <si>
     <t>key</t>
   </si>
@@ -499,6 +499,60 @@
     <t>Failed to update featured order.</t>
   </si>
   <si>
+    <t>storeError.saveCatalogFailed</t>
+  </si>
+  <si>
+    <t>儲存商品資料失敗。</t>
+  </si>
+  <si>
+    <t>Failed to save product.</t>
+  </si>
+  <si>
+    <t>storeError.uploadCoverFailed</t>
+  </si>
+  <si>
+    <t>上傳封面圖失敗。</t>
+  </si>
+  <si>
+    <t>Failed to upload cover image.</t>
+  </si>
+  <si>
+    <t>storeError.removeCoverFailed</t>
+  </si>
+  <si>
+    <t>移除封面圖失敗。</t>
+  </si>
+  <si>
+    <t>Failed to remove cover image.</t>
+  </si>
+  <si>
+    <t>storeError.createVersionFailed</t>
+  </si>
+  <si>
+    <t>建立版本失敗。</t>
+  </si>
+  <si>
+    <t>Failed to create version.</t>
+  </si>
+  <si>
+    <t>storeError.uploadFileFailed</t>
+  </si>
+  <si>
+    <t>檔案上傳失敗：{name}</t>
+  </si>
+  <si>
+    <t>Upload failed: {name}</t>
+  </si>
+  <si>
+    <t>storeError.deleteFileFailed</t>
+  </si>
+  <si>
+    <t>刪除檔案失敗。</t>
+  </si>
+  <si>
+    <t>Failed to delete file.</t>
+  </si>
+  <si>
     <t>catalogStatus.all</t>
   </si>
   <si>
@@ -1711,12 +1765,6 @@
     <t>upload.msgUploadFailed</t>
   </si>
   <si>
-    <t>檔案上傳失敗：{name}</t>
-  </si>
-  <si>
-    <t>Upload failed: {name}</t>
-  </si>
-  <si>
     <t>upload.statusUploading</t>
   </si>
   <si>
@@ -3856,6 +3904,15 @@
     <t>商品管理</t>
   </si>
   <si>
+    <t>route.productEdit</t>
+  </si>
+  <si>
+    <t>編輯商品</t>
+  </si>
+  <si>
+    <t>Edit product</t>
+  </si>
+  <si>
     <t>route.upload</t>
   </si>
   <si>
@@ -5603,6 +5660,474 @@
   </si>
   <si>
     <t>Delete failed: the category may still be referenced by Q&amp;A</t>
+  </si>
+  <si>
+    <t>productEdit.backToProducts</t>
+  </si>
+  <si>
+    <t>productEdit.basicsTitle</t>
+  </si>
+  <si>
+    <t>基本資料</t>
+  </si>
+  <si>
+    <t>Basics</t>
+  </si>
+  <si>
+    <t>productEdit.basicsDesc</t>
+  </si>
+  <si>
+    <t>商品在商城與店面呈現的名稱、簡介與定價。</t>
+  </si>
+  <si>
+    <t>The name, blurb and price shown in the marketplace and on your storefront.</t>
+  </si>
+  <si>
+    <t>productEdit.nameLabel</t>
+  </si>
+  <si>
+    <t>productEdit.namePlaceholder</t>
+  </si>
+  <si>
+    <t>e.g. City Mornings — 40 minimal architecture photos</t>
+  </si>
+  <si>
+    <t>productEdit.summaryLabel</t>
+  </si>
+  <si>
+    <t>One-line blurb</t>
+  </si>
+  <si>
+    <t>productEdit.summaryPlaceholder</t>
+  </si>
+  <si>
+    <t>Win the buyer over in one line…</t>
+  </si>
+  <si>
+    <t>productEdit.descriptionLabel</t>
+  </si>
+  <si>
+    <t>詳細介紹</t>
+  </si>
+  <si>
+    <t>Full description</t>
+  </si>
+  <si>
+    <t>productEdit.descriptionPlaceholder</t>
+  </si>
+  <si>
+    <t>介紹作品內容、規格、使用方式…</t>
+  </si>
+  <si>
+    <t>Describe the contents, specs and how to use them…</t>
+  </si>
+  <si>
+    <t>productEdit.descriptionHint</t>
+  </si>
+  <si>
+    <t>顯示於店面商品頁的「關於這件作品」，空行分段。</t>
+  </si>
+  <si>
+    <t>Shown as “About this work” on the product page; blank lines split paragraphs.</t>
+  </si>
+  <si>
+    <t>productEdit.categoryLabel</t>
+  </si>
+  <si>
+    <t>productEdit.noCategory</t>
+  </si>
+  <si>
+    <t>不指定分類</t>
+  </si>
+  <si>
+    <t>No category</t>
+  </si>
+  <si>
+    <t>productEdit.tagsLabel</t>
+  </si>
+  <si>
+    <t>productEdit.tagsPlaceholder</t>
+  </si>
+  <si>
+    <t>productEdit.tagsHint</t>
+  </si>
+  <si>
+    <t>最多 {max} 個，幫助買家在商城找到你。</t>
+  </si>
+  <si>
+    <t>Up to {max}; they help buyers find you in the marketplace.</t>
+  </si>
+  <si>
+    <t>productEdit.priceLabel</t>
+  </si>
+  <si>
+    <t>productEdit.freeToggle</t>
+  </si>
+  <si>
+    <t>Give away free</t>
+  </si>
+  <si>
+    <t>productEdit.coverHueLabel</t>
+  </si>
+  <si>
+    <t>Cover tint</t>
+  </si>
+  <si>
+    <t>productEdit.coverHueHint</t>
+  </si>
+  <si>
+    <t>未設定封面圖時，作品縮圖會以這個色調呈現。</t>
+  </si>
+  <si>
+    <t>Used for the generated thumbnail when no cover image is set.</t>
+  </si>
+  <si>
+    <t>productEdit.coverTitle</t>
+  </si>
+  <si>
+    <t>封面圖</t>
+  </si>
+  <si>
+    <t>Cover image</t>
+  </si>
+  <si>
+    <t>productEdit.coverDesc</t>
+  </si>
+  <si>
+    <t>買家在商城與店面看到的作品縮圖。</t>
+  </si>
+  <si>
+    <t>The thumbnail buyers see in the marketplace and on your storefront.</t>
+  </si>
+  <si>
+    <t>productEdit.coverEmpty</t>
+  </si>
+  <si>
+    <t>尚未設定封面</t>
+  </si>
+  <si>
+    <t>No cover yet</t>
+  </si>
+  <si>
+    <t>productEdit.coverUpload</t>
+  </si>
+  <si>
+    <t>上傳封面</t>
+  </si>
+  <si>
+    <t>Upload cover</t>
+  </si>
+  <si>
+    <t>productEdit.coverReplace</t>
+  </si>
+  <si>
+    <t>更換封面</t>
+  </si>
+  <si>
+    <t>Replace cover</t>
+  </si>
+  <si>
+    <t>productEdit.coverRemove</t>
+  </si>
+  <si>
+    <t>移除封面</t>
+  </si>
+  <si>
+    <t>Remove cover</t>
+  </si>
+  <si>
+    <t>productEdit.coverHint</t>
+  </si>
+  <si>
+    <t>支援 JPG / PNG / GIF / WebP，單檔最大 5 MB。建議 4:3 橫式構圖。</t>
+  </si>
+  <si>
+    <t>JPG / PNG / GIF / WebP, up to 5 MB. A 4:3 landscape crop works best.</t>
+  </si>
+  <si>
+    <t>productEdit.versionsTitle</t>
+  </si>
+  <si>
+    <t>版本與可下載檔</t>
+  </si>
+  <si>
+    <t>Versions &amp; downloads</t>
+  </si>
+  <si>
+    <t>productEdit.versionsDesc</t>
+  </si>
+  <si>
+    <t>買家付款後實際取得的檔案；新版本會成為目前對外版本。</t>
+  </si>
+  <si>
+    <t>What buyers actually get after paying; a new version becomes the live one.</t>
+  </si>
+  <si>
+    <t>productEdit.newVersion</t>
+  </si>
+  <si>
+    <t>建立新版本</t>
+  </si>
+  <si>
+    <t>New version</t>
+  </si>
+  <si>
+    <t>productEdit.newVersionHint</t>
+  </si>
+  <si>
+    <t>建立後將立即成為目前對外版本，記得補上可下載檔，否則買家會拿不到內容。</t>
+  </si>
+  <si>
+    <t>It goes live immediately — add its files, or buyers will get nothing.</t>
+  </si>
+  <si>
+    <t>productEdit.versionLabel</t>
+  </si>
+  <si>
+    <t>版本字串</t>
+  </si>
+  <si>
+    <t>productEdit.versionPlaceholder</t>
+  </si>
+  <si>
+    <t>例如：1.1.0</t>
+  </si>
+  <si>
+    <t>e.g. 1.1.0</t>
+  </si>
+  <si>
+    <t>productEdit.releaseNoteLabel</t>
+  </si>
+  <si>
+    <t>版本說明</t>
+  </si>
+  <si>
+    <t>Release note</t>
+  </si>
+  <si>
+    <t>productEdit.releaseNotePlaceholder</t>
+  </si>
+  <si>
+    <t>這個版本改了什麼…</t>
+  </si>
+  <si>
+    <t>What changed in this version…</t>
+  </si>
+  <si>
+    <t>productEdit.currentVersion</t>
+  </si>
+  <si>
+    <t>目前版本</t>
+  </si>
+  <si>
+    <t>productEdit.versionMeta</t>
+  </si>
+  <si>
+    <t>{count} 個檔案 · {size} · {date}</t>
+  </si>
+  <si>
+    <t>{count} files · {size} · {date}</t>
+  </si>
+  <si>
+    <t>productEdit.addFiles</t>
+  </si>
+  <si>
+    <t>加入檔案</t>
+  </si>
+  <si>
+    <t>Add files</t>
+  </si>
+  <si>
+    <t>productEdit.noFiles</t>
+  </si>
+  <si>
+    <t>這個版本還沒有可下載檔案。</t>
+  </si>
+  <si>
+    <t>No downloadable files in this version yet.</t>
+  </si>
+  <si>
+    <t>productEdit.noVersions</t>
+  </si>
+  <si>
+    <t>尚未建立任何版本</t>
+  </si>
+  <si>
+    <t>No versions yet</t>
+  </si>
+  <si>
+    <t>productEdit.noVersionsHint</t>
+  </si>
+  <si>
+    <t>商品需要有帶檔案的版本才能上架。</t>
+  </si>
+  <si>
+    <t>A product needs a version with files before it can go live.</t>
+  </si>
+  <si>
+    <t>productEdit.downloadFile</t>
+  </si>
+  <si>
+    <t>下載檢查</t>
+  </si>
+  <si>
+    <t>Download to check</t>
+  </si>
+  <si>
+    <t>productEdit.deleteFileConfirm</t>
+  </si>
+  <si>
+    <t>刪除後買家將無法再取得這個檔案，確定要刪除嗎？</t>
+  </si>
+  <si>
+    <t>Buyers will no longer be able to get this file. Delete it?</t>
+  </si>
+  <si>
+    <t>productEdit.notFoundTitle</t>
+  </si>
+  <si>
+    <t>找不到這件作品</t>
+  </si>
+  <si>
+    <t>Product not found</t>
+  </si>
+  <si>
+    <t>productEdit.notFoundDesc</t>
+  </si>
+  <si>
+    <t>作品可能已刪除，或不屬於你的商店。</t>
+  </si>
+  <si>
+    <t>It may have been deleted, or it isn’t one of your store’s products.</t>
+  </si>
+  <si>
+    <t>productEdit.msgSaved</t>
+  </si>
+  <si>
+    <t>已儲存。</t>
+  </si>
+  <si>
+    <t>Saved.</t>
+  </si>
+  <si>
+    <t>productEdit.msgSaveFailed</t>
+  </si>
+  <si>
+    <t>儲存失敗</t>
+  </si>
+  <si>
+    <t>Failed to save</t>
+  </si>
+  <si>
+    <t>productEdit.msgCoverType</t>
+  </si>
+  <si>
+    <t>封面圖僅支援 JPG / PNG / GIF / WebP。</t>
+  </si>
+  <si>
+    <t>Cover images must be JPG / PNG / GIF / WebP.</t>
+  </si>
+  <si>
+    <t>productEdit.msgCoverTooLarge</t>
+  </si>
+  <si>
+    <t>封面圖不得超過 5 MB。</t>
+  </si>
+  <si>
+    <t>Cover images must be 5 MB or smaller.</t>
+  </si>
+  <si>
+    <t>productEdit.msgCoverUpdated</t>
+  </si>
+  <si>
+    <t>已更新封面圖。</t>
+  </si>
+  <si>
+    <t>Cover image updated.</t>
+  </si>
+  <si>
+    <t>productEdit.msgCoverRemoved</t>
+  </si>
+  <si>
+    <t>已移除封面圖。</t>
+  </si>
+  <si>
+    <t>Cover image removed.</t>
+  </si>
+  <si>
+    <t>productEdit.msgCoverFailed</t>
+  </si>
+  <si>
+    <t>封面圖操作失敗</t>
+  </si>
+  <si>
+    <t>Cover image action failed</t>
+  </si>
+  <si>
+    <t>productEdit.msgNeedVersion</t>
+  </si>
+  <si>
+    <t>請填寫版本字串。</t>
+  </si>
+  <si>
+    <t>Please fill in the version.</t>
+  </si>
+  <si>
+    <t>productEdit.msgVersionCreated</t>
+  </si>
+  <si>
+    <t>已建立新版本。</t>
+  </si>
+  <si>
+    <t>New version created.</t>
+  </si>
+  <si>
+    <t>productEdit.msgVersionFailed</t>
+  </si>
+  <si>
+    <t>建立版本失敗</t>
+  </si>
+  <si>
+    <t>Failed to create version</t>
+  </si>
+  <si>
+    <t>productEdit.msgFilesUploaded</t>
+  </si>
+  <si>
+    <t>已上傳 {count} 個檔案。</t>
+  </si>
+  <si>
+    <t>Uploaded {count} files.</t>
+  </si>
+  <si>
+    <t>productEdit.msgFileFailed</t>
+  </si>
+  <si>
+    <t>productEdit.msgFileDeleted</t>
+  </si>
+  <si>
+    <t>已刪除檔案。</t>
+  </si>
+  <si>
+    <t>File deleted.</t>
+  </si>
+  <si>
+    <t>productEdit.msgFileDeleteFailed</t>
+  </si>
+  <si>
+    <t>刪除檔案失敗</t>
+  </si>
+  <si>
+    <t>Failed to delete file</t>
+  </si>
+  <si>
+    <t>productEdit.msgDownloadFailed</t>
+  </si>
+  <si>
+    <t>取得下載連結失敗</t>
+  </si>
+  <si>
+    <t>Failed to get download link</t>
   </si>
 </sst>
 </file>
@@ -5988,7 +6513,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C691"/>
+  <dimension ref="A1:C757"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -6594,128 +7119,128 @@
         <v>162</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>43</v>
+        <v>163</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>44</v>
+        <v>164</v>
       </c>
     </row>
     <row r="56" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="57" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="58" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="59" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="60" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="61" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>178</v>
+        <v>43</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>179</v>
+        <v>44</v>
       </c>
     </row>
     <row r="62" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="63" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="64" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="65" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="66" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>194</v>
@@ -6729,73 +7254,73 @@
         <v>196</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>165</v>
+        <v>197</v>
       </c>
     </row>
     <row r="68" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="69" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="70" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="71" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="72" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="73" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>214</v>
+        <v>183</v>
       </c>
     </row>
     <row r="74" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7067,76 +7592,76 @@
         <v>287</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>28</v>
+        <v>288</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>29</v>
+        <v>289</v>
       </c>
     </row>
     <row r="99" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="100" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="101" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="102" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="103" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="104" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>304</v>
+        <v>28</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>305</v>
+        <v>29</v>
       </c>
     </row>
     <row r="105" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7221,76 +7746,76 @@
         <v>327</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>264</v>
+        <v>328</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>265</v>
+        <v>329</v>
       </c>
     </row>
     <row r="113" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="114" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="115" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="116" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="117" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="118" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>344</v>
+        <v>282</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>345</v>
+        <v>283</v>
       </c>
     </row>
     <row r="119" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7507,120 +8032,120 @@
         <v>403</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>350</v>
+        <v>404</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>351</v>
+        <v>405</v>
       </c>
     </row>
     <row r="139" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="140" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="141" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="142" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>276</v>
+        <v>416</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>277</v>
+        <v>417</v>
       </c>
     </row>
     <row r="143" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="144" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>418</v>
+        <v>368</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>419</v>
+        <v>369</v>
       </c>
     </row>
     <row r="145" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="146" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="147" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="148" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>430</v>
+        <v>294</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>431</v>
+        <v>295</v>
       </c>
     </row>
     <row r="149" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7873,95 +8398,95 @@
         <v>499</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>437</v>
+        <v>500</v>
       </c>
     </row>
     <row r="172" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>448</v>
+        <v>502</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>449</v>
+        <v>503</v>
       </c>
     </row>
     <row r="173" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>457</v>
+        <v>505</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>191</v>
+        <v>506</v>
       </c>
     </row>
     <row r="174" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
     </row>
     <row r="175" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
     </row>
     <row r="176" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
     </row>
     <row r="177" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>513</v>
+        <v>455</v>
       </c>
     </row>
     <row r="178" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>515</v>
+        <v>466</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>516</v>
+        <v>467</v>
       </c>
     </row>
     <row r="179" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>518</v>
+        <v>475</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>519</v>
+        <v>209</v>
       </c>
     </row>
     <row r="180" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7969,139 +8494,139 @@
         <v>520</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>22</v>
+        <v>521</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>23</v>
+        <v>522</v>
       </c>
     </row>
     <row r="181" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="182" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="183" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="184" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="185" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="186" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>448</v>
+        <v>22</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>537</v>
+        <v>23</v>
       </c>
     </row>
     <row r="187" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="188" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="189" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="190" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="191" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="192" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>554</v>
+        <v>466</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>555</v>
@@ -8211,43 +8736,43 @@
         <v>583</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>584</v>
+        <v>175</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>585</v>
+        <v>176</v>
       </c>
     </row>
     <row r="203" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="C203" s="2" t="s">
         <v>586</v>
-      </c>
-      <c r="B203" s="2" t="s">
-        <v>587</v>
-      </c>
-      <c r="C203" s="2" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="204" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="C204" s="2" t="s">
         <v>589</v>
-      </c>
-      <c r="B204" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="C204" s="2" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="205" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="C205" s="2" t="s">
         <v>592</v>
-      </c>
-      <c r="B205" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C205" s="2" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="206" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8266,54 +8791,54 @@
         <v>596</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>173</v>
+        <v>597</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>174</v>
+        <v>598</v>
       </c>
     </row>
     <row r="208" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="209" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="210" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="211" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>607</v>
+        <v>194</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>608</v>
+        <v>194</v>
       </c>
     </row>
     <row r="212" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8332,43 +8857,43 @@
         <v>612</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>613</v>
+        <v>191</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>614</v>
+        <v>192</v>
       </c>
     </row>
     <row r="214" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="C214" s="2" t="s">
         <v>615</v>
-      </c>
-      <c r="B214" s="2" t="s">
-        <v>616</v>
-      </c>
-      <c r="C214" s="2" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="215" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="C215" s="2" t="s">
         <v>618</v>
-      </c>
-      <c r="B215" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="C215" s="2" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="216" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="C216" s="2" t="s">
         <v>621</v>
-      </c>
-      <c r="B216" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="C216" s="2" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="217" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8387,54 +8912,54 @@
         <v>625</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>319</v>
+        <v>626</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>320</v>
+        <v>627</v>
       </c>
     </row>
     <row r="219" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="220" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="221" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="222" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>636</v>
+        <v>334</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>637</v>
+        <v>335</v>
       </c>
     </row>
     <row r="223" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8453,109 +8978,109 @@
         <v>641</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>642</v>
+        <v>337</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>643</v>
+        <v>338</v>
       </c>
     </row>
     <row r="225" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="C225" s="2" t="s">
         <v>644</v>
-      </c>
-      <c r="B225" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="C225" s="2" t="s">
-        <v>646</v>
       </c>
     </row>
     <row r="226" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="C226" s="2" t="s">
         <v>647</v>
-      </c>
-      <c r="B226" s="2" t="s">
-        <v>648</v>
-      </c>
-      <c r="C226" s="2" t="s">
-        <v>649</v>
       </c>
     </row>
     <row r="227" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="C227" s="2" t="s">
         <v>650</v>
-      </c>
-      <c r="B227" s="2" t="s">
-        <v>651</v>
-      </c>
-      <c r="C227" s="2" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="228" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="C228" s="2" t="s">
         <v>653</v>
-      </c>
-      <c r="B228" s="2" t="s">
-        <v>654</v>
-      </c>
-      <c r="C228" s="2" t="s">
-        <v>655</v>
       </c>
     </row>
     <row r="229" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="C229" s="2" t="s">
         <v>656</v>
-      </c>
-      <c r="B229" s="2" t="s">
-        <v>657</v>
-      </c>
-      <c r="C229" s="2" t="s">
-        <v>658</v>
       </c>
     </row>
     <row r="230" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="C230" s="2" t="s">
         <v>659</v>
-      </c>
-      <c r="B230" s="2" t="s">
-        <v>660</v>
-      </c>
-      <c r="C230" s="2" t="s">
-        <v>661</v>
       </c>
     </row>
     <row r="231" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="C231" s="2" t="s">
         <v>662</v>
-      </c>
-      <c r="B231" s="2" t="s">
-        <v>663</v>
-      </c>
-      <c r="C231" s="2" t="s">
-        <v>664</v>
       </c>
     </row>
     <row r="232" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="C232" s="2" t="s">
         <v>665</v>
-      </c>
-      <c r="B232" s="2" t="s">
-        <v>666</v>
-      </c>
-      <c r="C232" s="2" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="233" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="C233" s="2" t="s">
         <v>668</v>
-      </c>
-      <c r="B233" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="C233" s="2" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="234" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8563,76 +9088,76 @@
         <v>669</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>623</v>
+        <v>670</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>624</v>
+        <v>671</v>
       </c>
     </row>
     <row r="235" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>319</v>
+        <v>673</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>320</v>
+        <v>674</v>
       </c>
     </row>
     <row r="236" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
     </row>
     <row r="237" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
     </row>
     <row r="238" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
     </row>
     <row r="239" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>681</v>
+        <v>334</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>682</v>
+        <v>335</v>
       </c>
     </row>
     <row r="240" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>684</v>
+        <v>639</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>685</v>
+        <v>640</v>
       </c>
     </row>
     <row r="241" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8640,32 +9165,32 @@
         <v>686</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>687</v>
+        <v>337</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>688</v>
+        <v>338</v>
       </c>
     </row>
     <row r="242" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="C242" s="2" t="s">
         <v>689</v>
-      </c>
-      <c r="B242" s="2" t="s">
-        <v>690</v>
-      </c>
-      <c r="C242" s="2" t="s">
-        <v>691</v>
       </c>
     </row>
     <row r="243" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="C243" s="2" t="s">
         <v>692</v>
-      </c>
-      <c r="B243" s="2" t="s">
-        <v>575</v>
-      </c>
-      <c r="C243" s="2" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="244" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8728,274 +9253,274 @@
         <v>708</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>709</v>
+        <v>591</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>710</v>
+        <v>592</v>
       </c>
     </row>
     <row r="250" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="B250" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="C250" s="2" t="s">
         <v>711</v>
-      </c>
-      <c r="B250" s="2" t="s">
-        <v>712</v>
-      </c>
-      <c r="C250" s="2" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="251" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="B251" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="C251" s="2" t="s">
         <v>714</v>
-      </c>
-      <c r="B251" s="2" t="s">
-        <v>715</v>
-      </c>
-      <c r="C251" s="2" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="252" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="B252" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="C252" s="2" t="s">
         <v>717</v>
-      </c>
-      <c r="B252" s="2" t="s">
-        <v>718</v>
-      </c>
-      <c r="C252" s="2" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="253" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="B253" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="C253" s="2" t="s">
         <v>720</v>
-      </c>
-      <c r="B253" s="2" t="s">
-        <v>721</v>
-      </c>
-      <c r="C253" s="2" t="s">
-        <v>722</v>
       </c>
     </row>
     <row r="254" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="B254" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="C254" s="2" t="s">
         <v>723</v>
-      </c>
-      <c r="B254" s="2" t="s">
-        <v>724</v>
-      </c>
-      <c r="C254" s="2" t="s">
-        <v>725</v>
       </c>
     </row>
     <row r="255" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="B255" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="C255" s="2" t="s">
         <v>726</v>
-      </c>
-      <c r="B255" s="2" t="s">
-        <v>727</v>
-      </c>
-      <c r="C255" s="2" t="s">
-        <v>728</v>
       </c>
     </row>
     <row r="256" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="B256" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="C256" s="2" t="s">
         <v>729</v>
-      </c>
-      <c r="B256" s="2" t="s">
-        <v>730</v>
-      </c>
-      <c r="C256" s="2" t="s">
-        <v>731</v>
       </c>
     </row>
     <row r="257" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="B257" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="C257" s="2" t="s">
         <v>732</v>
-      </c>
-      <c r="B257" s="2" t="s">
-        <v>733</v>
-      </c>
-      <c r="C257" s="2" t="s">
-        <v>734</v>
       </c>
     </row>
     <row r="258" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="B258" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="C258" s="2" t="s">
         <v>735</v>
-      </c>
-      <c r="B258" s="2" t="s">
-        <v>736</v>
-      </c>
-      <c r="C258" s="2" t="s">
-        <v>737</v>
       </c>
     </row>
     <row r="259" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="B259" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="C259" s="2" t="s">
         <v>738</v>
-      </c>
-      <c r="B259" s="2" t="s">
-        <v>739</v>
-      </c>
-      <c r="C259" s="2" t="s">
-        <v>740</v>
       </c>
     </row>
     <row r="260" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="B260" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="C260" s="2" t="s">
         <v>741</v>
-      </c>
-      <c r="B260" s="2" t="s">
-        <v>742</v>
-      </c>
-      <c r="C260" s="2" t="s">
-        <v>743</v>
       </c>
     </row>
     <row r="261" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="B261" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="C261" s="2" t="s">
         <v>744</v>
-      </c>
-      <c r="B261" s="2" t="s">
-        <v>745</v>
-      </c>
-      <c r="C261" s="2" t="s">
-        <v>746</v>
       </c>
     </row>
     <row r="262" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
+        <v>745</v>
+      </c>
+      <c r="B262" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="C262" s="2" t="s">
         <v>747</v>
-      </c>
-      <c r="B262" s="2" t="s">
-        <v>748</v>
-      </c>
-      <c r="C262" s="2" t="s">
-        <v>749</v>
       </c>
     </row>
     <row r="263" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="B263" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="C263" s="2" t="s">
         <v>750</v>
-      </c>
-      <c r="B263" s="2" t="s">
-        <v>751</v>
-      </c>
-      <c r="C263" s="2" t="s">
-        <v>752</v>
       </c>
     </row>
     <row r="264" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="B264" s="2" t="s">
+        <v>752</v>
+      </c>
+      <c r="C264" s="2" t="s">
         <v>753</v>
-      </c>
-      <c r="B264" s="2" t="s">
-        <v>754</v>
-      </c>
-      <c r="C264" s="2" t="s">
-        <v>755</v>
       </c>
     </row>
     <row r="265" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
+        <v>754</v>
+      </c>
+      <c r="B265" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="C265" s="2" t="s">
         <v>756</v>
-      </c>
-      <c r="B265" s="2" t="s">
-        <v>757</v>
-      </c>
-      <c r="C265" s="2" t="s">
-        <v>758</v>
       </c>
     </row>
     <row r="266" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="B266" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="C266" s="2" t="s">
         <v>759</v>
-      </c>
-      <c r="B266" s="2" t="s">
-        <v>760</v>
-      </c>
-      <c r="C266" s="2" t="s">
-        <v>761</v>
       </c>
     </row>
     <row r="267" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="B267" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="C267" s="2" t="s">
         <v>762</v>
-      </c>
-      <c r="B267" s="2" t="s">
-        <v>763</v>
-      </c>
-      <c r="C267" s="2" t="s">
-        <v>764</v>
       </c>
     </row>
     <row r="268" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="B268" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="C268" s="2" t="s">
         <v>765</v>
-      </c>
-      <c r="B268" s="2" t="s">
-        <v>766</v>
-      </c>
-      <c r="C268" s="2" t="s">
-        <v>767</v>
       </c>
     </row>
     <row r="269" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
+        <v>766</v>
+      </c>
+      <c r="B269" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="C269" s="2" t="s">
         <v>768</v>
-      </c>
-      <c r="B269" s="2" t="s">
-        <v>769</v>
-      </c>
-      <c r="C269" s="2" t="s">
-        <v>770</v>
       </c>
     </row>
     <row r="270" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="B270" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="C270" s="2" t="s">
         <v>771</v>
-      </c>
-      <c r="B270" s="2" t="s">
-        <v>772</v>
-      </c>
-      <c r="C270" s="2" t="s">
-        <v>773</v>
       </c>
     </row>
     <row r="271" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
+        <v>772</v>
+      </c>
+      <c r="B271" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="C271" s="2" t="s">
         <v>774</v>
-      </c>
-      <c r="B271" s="2" t="s">
-        <v>775</v>
-      </c>
-      <c r="C271" s="2" t="s">
-        <v>776</v>
       </c>
     </row>
     <row r="272" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="B272" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="C272" s="2" t="s">
         <v>777</v>
-      </c>
-      <c r="B272" s="2" t="s">
-        <v>778</v>
-      </c>
-      <c r="C272" s="2" t="s">
-        <v>779</v>
       </c>
     </row>
     <row r="273" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="B273" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="C273" s="2" t="s">
         <v>780</v>
-      </c>
-      <c r="B273" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="C273" s="2" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="274" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9014,54 +9539,54 @@
         <v>784</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>264</v>
+        <v>785</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>265</v>
+        <v>786</v>
       </c>
     </row>
     <row r="276" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
     </row>
     <row r="277" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
     </row>
     <row r="278" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
     </row>
     <row r="279" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>795</v>
+        <v>517</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>796</v>
+        <v>455</v>
       </c>
     </row>
     <row r="280" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9080,54 +9605,54 @@
         <v>800</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>801</v>
+        <v>282</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>802</v>
+        <v>283</v>
       </c>
     </row>
     <row r="282" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="B282" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="C282" s="2" t="s">
         <v>803</v>
-      </c>
-      <c r="B282" s="2" t="s">
-        <v>804</v>
-      </c>
-      <c r="C282" s="2" t="s">
-        <v>805</v>
       </c>
     </row>
     <row r="283" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="B283" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="C283" s="2" t="s">
         <v>806</v>
-      </c>
-      <c r="B283" s="2" t="s">
-        <v>807</v>
-      </c>
-      <c r="C283" s="2" t="s">
-        <v>808</v>
       </c>
     </row>
     <row r="284" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="B284" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="C284" s="2" t="s">
         <v>809</v>
-      </c>
-      <c r="B284" s="2" t="s">
-        <v>810</v>
-      </c>
-      <c r="C284" s="2" t="s">
-        <v>811</v>
       </c>
     </row>
     <row r="285" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="B285" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="C285" s="2" t="s">
         <v>812</v>
-      </c>
-      <c r="B285" s="2" t="s">
-        <v>778</v>
-      </c>
-      <c r="C285" s="2" t="s">
-        <v>779</v>
       </c>
     </row>
     <row r="286" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9190,32 +9715,32 @@
         <v>828</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>829</v>
+        <v>794</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>830</v>
+        <v>795</v>
       </c>
     </row>
     <row r="292" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="B292" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="C292" s="2" t="s">
         <v>831</v>
-      </c>
-      <c r="B292" s="2" t="s">
-        <v>832</v>
-      </c>
-      <c r="C292" s="2" t="s">
-        <v>833</v>
       </c>
     </row>
     <row r="293" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="B293" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="C293" s="2" t="s">
         <v>834</v>
-      </c>
-      <c r="B293" s="2" t="s">
-        <v>678</v>
-      </c>
-      <c r="C293" s="2" t="s">
-        <v>679</v>
       </c>
     </row>
     <row r="294" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9278,10 +9803,10 @@
         <v>850</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>52</v>
+        <v>694</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>53</v>
+        <v>695</v>
       </c>
     </row>
     <row r="300" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9344,205 +9869,205 @@
         <v>866</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>867</v>
+        <v>52</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>868</v>
+        <v>53</v>
       </c>
     </row>
     <row r="306" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="B306" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="C306" s="2" t="s">
         <v>869</v>
-      </c>
-      <c r="B306" s="2" t="s">
-        <v>870</v>
-      </c>
-      <c r="C306" s="2" t="s">
-        <v>871</v>
       </c>
     </row>
     <row r="307" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="B307" s="2" t="s">
+        <v>871</v>
+      </c>
+      <c r="C307" s="2" t="s">
         <v>872</v>
-      </c>
-      <c r="B307" s="2" t="s">
-        <v>873</v>
-      </c>
-      <c r="C307" s="2" t="s">
-        <v>874</v>
       </c>
     </row>
     <row r="308" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
+        <v>873</v>
+      </c>
+      <c r="B308" s="2" t="s">
+        <v>874</v>
+      </c>
+      <c r="C308" s="2" t="s">
         <v>875</v>
-      </c>
-      <c r="B308" s="2" t="s">
-        <v>876</v>
-      </c>
-      <c r="C308" s="2" t="s">
-        <v>877</v>
       </c>
     </row>
     <row r="309" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
+        <v>876</v>
+      </c>
+      <c r="B309" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="C309" s="2" t="s">
         <v>878</v>
-      </c>
-      <c r="B309" s="2" t="s">
-        <v>879</v>
-      </c>
-      <c r="C309" s="2" t="s">
-        <v>880</v>
       </c>
     </row>
     <row r="310" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="B310" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="C310" s="2" t="s">
         <v>881</v>
-      </c>
-      <c r="B310" s="2" t="s">
-        <v>882</v>
-      </c>
-      <c r="C310" s="2" t="s">
-        <v>883</v>
       </c>
     </row>
     <row r="311" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="B311" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="C311" s="2" t="s">
         <v>884</v>
-      </c>
-      <c r="B311" s="2" t="s">
-        <v>885</v>
-      </c>
-      <c r="C311" s="2" t="s">
-        <v>886</v>
       </c>
     </row>
     <row r="312" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
+        <v>885</v>
+      </c>
+      <c r="B312" s="2" t="s">
+        <v>886</v>
+      </c>
+      <c r="C312" s="2" t="s">
         <v>887</v>
-      </c>
-      <c r="B312" s="2" t="s">
-        <v>888</v>
-      </c>
-      <c r="C312" s="2" t="s">
-        <v>889</v>
       </c>
     </row>
     <row r="313" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
+        <v>888</v>
+      </c>
+      <c r="B313" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="C313" s="2" t="s">
         <v>890</v>
-      </c>
-      <c r="B313" s="2" t="s">
-        <v>891</v>
-      </c>
-      <c r="C313" s="2" t="s">
-        <v>892</v>
       </c>
     </row>
     <row r="314" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
+        <v>891</v>
+      </c>
+      <c r="B314" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="C314" s="2" t="s">
         <v>893</v>
-      </c>
-      <c r="B314" s="2" t="s">
-        <v>894</v>
-      </c>
-      <c r="C314" s="2" t="s">
-        <v>895</v>
       </c>
     </row>
     <row r="315" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="B315" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="C315" s="2" t="s">
         <v>896</v>
-      </c>
-      <c r="B315" s="2" t="s">
-        <v>897</v>
-      </c>
-      <c r="C315" s="2" t="s">
-        <v>898</v>
       </c>
     </row>
     <row r="316" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="B316" s="2" t="s">
+        <v>898</v>
+      </c>
+      <c r="C316" s="2" t="s">
         <v>899</v>
-      </c>
-      <c r="B316" s="2" t="s">
-        <v>900</v>
-      </c>
-      <c r="C316" s="2" t="s">
-        <v>901</v>
       </c>
     </row>
     <row r="317" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
+        <v>900</v>
+      </c>
+      <c r="B317" s="2" t="s">
+        <v>901</v>
+      </c>
+      <c r="C317" s="2" t="s">
         <v>902</v>
-      </c>
-      <c r="B317" s="2" t="s">
-        <v>903</v>
-      </c>
-      <c r="C317" s="2" t="s">
-        <v>903</v>
       </c>
     </row>
     <row r="318" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
+        <v>903</v>
+      </c>
+      <c r="B318" s="2" t="s">
         <v>904</v>
       </c>
-      <c r="B318" s="2" t="s">
-        <v>398</v>
-      </c>
       <c r="C318" s="2" t="s">
-        <v>399</v>
+        <v>905</v>
       </c>
     </row>
     <row r="319" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
     </row>
     <row r="320" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
     </row>
     <row r="321" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
     </row>
     <row r="322" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="323" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="C323" s="2" t="s">
         <v>919</v>
@@ -9553,395 +10078,395 @@
         <v>920</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>921</v>
+        <v>416</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>922</v>
+        <v>417</v>
       </c>
     </row>
     <row r="325" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
+        <v>921</v>
+      </c>
+      <c r="B325" s="2" t="s">
+        <v>922</v>
+      </c>
+      <c r="C325" s="2" t="s">
         <v>923</v>
-      </c>
-      <c r="B325" s="2" t="s">
-        <v>924</v>
-      </c>
-      <c r="C325" s="2" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="326" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
+        <v>924</v>
+      </c>
+      <c r="B326" s="2" t="s">
+        <v>925</v>
+      </c>
+      <c r="C326" s="2" t="s">
         <v>926</v>
-      </c>
-      <c r="B326" s="2" t="s">
-        <v>927</v>
-      </c>
-      <c r="C326" s="2" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="327" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
+        <v>927</v>
+      </c>
+      <c r="B327" s="2" t="s">
+        <v>928</v>
+      </c>
+      <c r="C327" s="2" t="s">
         <v>929</v>
-      </c>
-      <c r="B327" s="2" t="s">
-        <v>930</v>
-      </c>
-      <c r="C327" s="2" t="s">
-        <v>931</v>
       </c>
     </row>
     <row r="328" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
+        <v>930</v>
+      </c>
+      <c r="B328" s="2" t="s">
+        <v>931</v>
+      </c>
+      <c r="C328" s="2" t="s">
         <v>932</v>
-      </c>
-      <c r="B328" s="2" t="s">
-        <v>933</v>
-      </c>
-      <c r="C328" s="2" t="s">
-        <v>933</v>
       </c>
     </row>
     <row r="329" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
+        <v>933</v>
+      </c>
+      <c r="B329" s="2" t="s">
         <v>934</v>
       </c>
-      <c r="B329" s="2" t="s">
+      <c r="C329" s="2" t="s">
         <v>935</v>
-      </c>
-      <c r="C329" s="2" t="s">
-        <v>936</v>
       </c>
     </row>
     <row r="330" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
+        <v>936</v>
+      </c>
+      <c r="B330" s="2" t="s">
         <v>937</v>
       </c>
-      <c r="B330" s="2" t="s">
+      <c r="C330" s="2" t="s">
         <v>938</v>
-      </c>
-      <c r="C330" s="2" t="s">
-        <v>939</v>
       </c>
     </row>
     <row r="331" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="B331" s="2" t="s">
         <v>940</v>
       </c>
-      <c r="B331" s="2" t="s">
+      <c r="C331" s="2" t="s">
         <v>941</v>
-      </c>
-      <c r="C331" s="2" t="s">
-        <v>942</v>
       </c>
     </row>
     <row r="332" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="B332" s="2" t="s">
         <v>943</v>
       </c>
-      <c r="B332" s="2" t="s">
+      <c r="C332" s="2" t="s">
         <v>944</v>
-      </c>
-      <c r="C332" s="2" t="s">
-        <v>945</v>
       </c>
     </row>
     <row r="333" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
+        <v>945</v>
+      </c>
+      <c r="B333" s="2" t="s">
         <v>946</v>
       </c>
-      <c r="B333" s="2" t="s">
+      <c r="C333" s="2" t="s">
         <v>947</v>
-      </c>
-      <c r="C333" s="2" t="s">
-        <v>948</v>
       </c>
     </row>
     <row r="334" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
+        <v>948</v>
+      </c>
+      <c r="B334" s="2" t="s">
         <v>949</v>
       </c>
-      <c r="B334" s="2" t="s">
-        <v>950</v>
-      </c>
       <c r="C334" s="2" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="335" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
+        <v>950</v>
+      </c>
+      <c r="B335" s="2" t="s">
+        <v>951</v>
+      </c>
+      <c r="C335" s="2" t="s">
         <v>952</v>
-      </c>
-      <c r="B335" s="2" t="s">
-        <v>953</v>
-      </c>
-      <c r="C335" s="2" t="s">
-        <v>954</v>
       </c>
     </row>
     <row r="336" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
+        <v>953</v>
+      </c>
+      <c r="B336" s="2" t="s">
+        <v>954</v>
+      </c>
+      <c r="C336" s="2" t="s">
         <v>955</v>
-      </c>
-      <c r="B336" s="2" t="s">
-        <v>956</v>
-      </c>
-      <c r="C336" s="2" t="s">
-        <v>957</v>
       </c>
     </row>
     <row r="337" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
+        <v>956</v>
+      </c>
+      <c r="B337" s="2" t="s">
+        <v>957</v>
+      </c>
+      <c r="C337" s="2" t="s">
         <v>958</v>
-      </c>
-      <c r="B337" s="2" t="s">
-        <v>959</v>
-      </c>
-      <c r="C337" s="2" t="s">
-        <v>960</v>
       </c>
     </row>
     <row r="338" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
+        <v>959</v>
+      </c>
+      <c r="B338" s="2" t="s">
+        <v>960</v>
+      </c>
+      <c r="C338" s="2" t="s">
         <v>961</v>
-      </c>
-      <c r="B338" s="2" t="s">
-        <v>962</v>
-      </c>
-      <c r="C338" s="2" t="s">
-        <v>963</v>
       </c>
     </row>
     <row r="339" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
+        <v>962</v>
+      </c>
+      <c r="B339" s="2" t="s">
+        <v>963</v>
+      </c>
+      <c r="C339" s="2" t="s">
         <v>964</v>
-      </c>
-      <c r="B339" s="2" t="s">
-        <v>965</v>
-      </c>
-      <c r="C339" s="2" t="s">
-        <v>966</v>
       </c>
     </row>
     <row r="340" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
+        <v>965</v>
+      </c>
+      <c r="B340" s="2" t="s">
+        <v>966</v>
+      </c>
+      <c r="C340" s="2" t="s">
         <v>967</v>
-      </c>
-      <c r="B340" s="2" t="s">
-        <v>968</v>
-      </c>
-      <c r="C340" s="2" t="s">
-        <v>969</v>
       </c>
     </row>
     <row r="341" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="B341" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="C341" s="2" t="s">
         <v>970</v>
-      </c>
-      <c r="B341" s="2" t="s">
-        <v>971</v>
-      </c>
-      <c r="C341" s="2" t="s">
-        <v>972</v>
       </c>
     </row>
     <row r="342" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="B342" s="2" t="s">
+        <v>972</v>
+      </c>
+      <c r="C342" s="2" t="s">
         <v>973</v>
-      </c>
-      <c r="B342" s="2" t="s">
-        <v>974</v>
-      </c>
-      <c r="C342" s="2" t="s">
-        <v>975</v>
       </c>
     </row>
     <row r="343" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
+        <v>974</v>
+      </c>
+      <c r="B343" s="2" t="s">
+        <v>975</v>
+      </c>
+      <c r="C343" s="2" t="s">
         <v>976</v>
-      </c>
-      <c r="B343" s="2" t="s">
-        <v>977</v>
-      </c>
-      <c r="C343" s="2" t="s">
-        <v>978</v>
       </c>
     </row>
     <row r="344" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
+        <v>977</v>
+      </c>
+      <c r="B344" s="2" t="s">
+        <v>978</v>
+      </c>
+      <c r="C344" s="2" t="s">
         <v>979</v>
-      </c>
-      <c r="B344" s="2" t="s">
-        <v>980</v>
-      </c>
-      <c r="C344" s="2" t="s">
-        <v>981</v>
       </c>
     </row>
     <row r="345" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
+        <v>980</v>
+      </c>
+      <c r="B345" s="2" t="s">
+        <v>981</v>
+      </c>
+      <c r="C345" s="2" t="s">
         <v>982</v>
-      </c>
-      <c r="B345" s="2" t="s">
-        <v>983</v>
-      </c>
-      <c r="C345" s="2" t="s">
-        <v>984</v>
       </c>
     </row>
     <row r="346" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
+        <v>983</v>
+      </c>
+      <c r="B346" s="2" t="s">
+        <v>984</v>
+      </c>
+      <c r="C346" s="2" t="s">
         <v>985</v>
-      </c>
-      <c r="B346" s="2" t="s">
-        <v>986</v>
-      </c>
-      <c r="C346" s="2" t="s">
-        <v>987</v>
       </c>
     </row>
     <row r="347" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
+        <v>986</v>
+      </c>
+      <c r="B347" s="2" t="s">
+        <v>987</v>
+      </c>
+      <c r="C347" s="2" t="s">
         <v>988</v>
-      </c>
-      <c r="B347" s="2" t="s">
-        <v>989</v>
-      </c>
-      <c r="C347" s="2" t="s">
-        <v>990</v>
       </c>
     </row>
     <row r="348" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
+        <v>989</v>
+      </c>
+      <c r="B348" s="2" t="s">
+        <v>990</v>
+      </c>
+      <c r="C348" s="2" t="s">
         <v>991</v>
-      </c>
-      <c r="B348" s="2" t="s">
-        <v>992</v>
-      </c>
-      <c r="C348" s="2" t="s">
-        <v>993</v>
       </c>
     </row>
     <row r="349" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
+        <v>992</v>
+      </c>
+      <c r="B349" s="2" t="s">
+        <v>993</v>
+      </c>
+      <c r="C349" s="2" t="s">
         <v>994</v>
-      </c>
-      <c r="B349" s="2" t="s">
-        <v>995</v>
-      </c>
-      <c r="C349" s="2" t="s">
-        <v>996</v>
       </c>
     </row>
     <row r="350" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
+        <v>995</v>
+      </c>
+      <c r="B350" s="2" t="s">
+        <v>996</v>
+      </c>
+      <c r="C350" s="2" t="s">
         <v>997</v>
-      </c>
-      <c r="B350" s="2" t="s">
-        <v>998</v>
-      </c>
-      <c r="C350" s="2" t="s">
-        <v>999</v>
       </c>
     </row>
     <row r="351" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
+        <v>998</v>
+      </c>
+      <c r="B351" s="2" t="s">
+        <v>999</v>
+      </c>
+      <c r="C351" s="2" t="s">
         <v>1000</v>
-      </c>
-      <c r="B351" s="2" t="s">
-        <v>1001</v>
-      </c>
-      <c r="C351" s="2" t="s">
-        <v>1002</v>
       </c>
     </row>
     <row r="352" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B352" s="2" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C352" s="2" t="s">
         <v>1003</v>
-      </c>
-      <c r="B352" s="2" t="s">
-        <v>1004</v>
-      </c>
-      <c r="C352" s="2" t="s">
-        <v>1005</v>
       </c>
     </row>
     <row r="353" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B353" s="2" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C353" s="2" t="s">
         <v>1006</v>
-      </c>
-      <c r="B353" s="2" t="s">
-        <v>1007</v>
-      </c>
-      <c r="C353" s="2" t="s">
-        <v>1008</v>
       </c>
     </row>
     <row r="354" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B354" s="2" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C354" s="2" t="s">
         <v>1009</v>
-      </c>
-      <c r="B354" s="2" t="s">
-        <v>1010</v>
-      </c>
-      <c r="C354" s="2" t="s">
-        <v>1011</v>
       </c>
     </row>
     <row r="355" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B355" s="2" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C355" s="2" t="s">
         <v>1012</v>
-      </c>
-      <c r="B355" s="2" t="s">
-        <v>1013</v>
-      </c>
-      <c r="C355" s="2" t="s">
-        <v>1014</v>
       </c>
     </row>
     <row r="356" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B356" s="2" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C356" s="2" t="s">
         <v>1015</v>
-      </c>
-      <c r="B356" s="2" t="s">
-        <v>1016</v>
-      </c>
-      <c r="C356" s="2" t="s">
-        <v>1017</v>
       </c>
     </row>
     <row r="357" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B357" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C357" s="2" t="s">
         <v>1018</v>
-      </c>
-      <c r="B357" s="2" t="s">
-        <v>1019</v>
-      </c>
-      <c r="C357" s="2" t="s">
-        <v>1020</v>
       </c>
     </row>
     <row r="358" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B358" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C358" s="2" t="s">
         <v>1021</v>
-      </c>
-      <c r="B358" s="2" t="s">
-        <v>1022</v>
-      </c>
-      <c r="C358" s="2" t="s">
-        <v>1023</v>
       </c>
     </row>
     <row r="359" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B359" s="2" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C359" s="2" t="s">
         <v>1024</v>
-      </c>
-      <c r="B359" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="C359" s="2" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="360" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9952,73 +10477,73 @@
         <v>1026</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>595</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="361" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="362" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="363" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>173</v>
+        <v>1035</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>174</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="364" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="365" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>1038</v>
+        <v>294</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>1039</v>
+        <v>295</v>
       </c>
     </row>
     <row r="366" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>1042</v>
+        <v>611</v>
       </c>
     </row>
     <row r="367" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10048,43 +10573,43 @@
         <v>1049</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>1050</v>
+        <v>191</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>1051</v>
+        <v>192</v>
       </c>
     </row>
     <row r="370" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B370" s="2" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C370" s="2" t="s">
         <v>1052</v>
-      </c>
-      <c r="B370" s="2" t="s">
-        <v>1053</v>
-      </c>
-      <c r="C370" s="2" t="s">
-        <v>1054</v>
       </c>
     </row>
     <row r="371" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B371" s="2" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C371" s="2" t="s">
         <v>1055</v>
-      </c>
-      <c r="B371" s="2" t="s">
-        <v>1056</v>
-      </c>
-      <c r="C371" s="2" t="s">
-        <v>1057</v>
       </c>
     </row>
     <row r="372" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B372" s="2" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C372" s="2" t="s">
         <v>1058</v>
-      </c>
-      <c r="B372" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="C372" s="2" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="373" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10095,73 +10620,73 @@
         <v>1060</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>1045</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="374" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="375" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="376" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A376" s="2" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="C376" s="2" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="377" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A377" s="2" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="C377" s="2" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="378" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>1074</v>
+        <v>276</v>
       </c>
       <c r="C378" s="2" t="s">
-        <v>1075</v>
+        <v>277</v>
       </c>
     </row>
     <row r="379" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A379" s="2" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B379" s="2" t="s">
         <v>1076</v>
       </c>
-      <c r="B379" s="2" t="s">
-        <v>276</v>
-      </c>
       <c r="C379" s="2" t="s">
-        <v>277</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="380" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10224,384 +10749,384 @@
         <v>1092</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>1093</v>
+        <v>294</v>
       </c>
       <c r="C385" s="2" t="s">
-        <v>1094</v>
+        <v>295</v>
       </c>
     </row>
     <row r="386" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A386" s="2" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B386" s="2" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C386" s="2" t="s">
         <v>1095</v>
-      </c>
-      <c r="B386" s="2" t="s">
-        <v>1096</v>
-      </c>
-      <c r="C386" s="2" t="s">
-        <v>1097</v>
       </c>
     </row>
     <row r="387" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A387" s="2" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B387" s="2" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C387" s="2" t="s">
         <v>1098</v>
-      </c>
-      <c r="B387" s="2" t="s">
-        <v>1099</v>
-      </c>
-      <c r="C387" s="2" t="s">
-        <v>1100</v>
       </c>
     </row>
     <row r="388" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A388" s="2" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B388" s="2" t="s">
+        <v>1100</v>
+      </c>
+      <c r="C388" s="2" t="s">
         <v>1101</v>
-      </c>
-      <c r="B388" s="2" t="s">
-        <v>1102</v>
-      </c>
-      <c r="C388" s="2" t="s">
-        <v>1103</v>
       </c>
     </row>
     <row r="389" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A389" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B389" s="2" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C389" s="2" t="s">
         <v>1104</v>
-      </c>
-      <c r="B389" s="2" t="s">
-        <v>1105</v>
-      </c>
-      <c r="C389" s="2" t="s">
-        <v>1106</v>
       </c>
     </row>
     <row r="390" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A390" s="2" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B390" s="2" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C390" s="2" t="s">
         <v>1107</v>
-      </c>
-      <c r="B390" s="2" t="s">
-        <v>1108</v>
-      </c>
-      <c r="C390" s="2" t="s">
-        <v>1109</v>
       </c>
     </row>
     <row r="391" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A391" s="2" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B391" s="2" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C391" s="2" t="s">
         <v>1110</v>
-      </c>
-      <c r="B391" s="2" t="s">
-        <v>1111</v>
-      </c>
-      <c r="C391" s="2" t="s">
-        <v>1112</v>
       </c>
     </row>
     <row r="392" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A392" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B392" s="2" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C392" s="2" t="s">
         <v>1113</v>
-      </c>
-      <c r="B392" s="2" t="s">
-        <v>1114</v>
-      </c>
-      <c r="C392" s="2" t="s">
-        <v>1115</v>
       </c>
     </row>
     <row r="393" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A393" s="2" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B393" s="2" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C393" s="2" t="s">
         <v>1116</v>
-      </c>
-      <c r="B393" s="2" t="s">
-        <v>1117</v>
-      </c>
-      <c r="C393" s="2" t="s">
-        <v>1118</v>
       </c>
     </row>
     <row r="394" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A394" s="2" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B394" s="2" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C394" s="2" t="s">
         <v>1119</v>
-      </c>
-      <c r="B394" s="2" t="s">
-        <v>1120</v>
-      </c>
-      <c r="C394" s="2" t="s">
-        <v>1121</v>
       </c>
     </row>
     <row r="395" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A395" s="2" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B395" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C395" s="2" t="s">
         <v>1122</v>
-      </c>
-      <c r="B395" s="2" t="s">
-        <v>1123</v>
-      </c>
-      <c r="C395" s="2" t="s">
-        <v>1124</v>
       </c>
     </row>
     <row r="396" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A396" s="2" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B396" s="2" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C396" s="2" t="s">
         <v>1125</v>
-      </c>
-      <c r="B396" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="C396" s="2" t="s">
-        <v>1126</v>
       </c>
     </row>
     <row r="397" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A397" s="2" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B397" s="2" t="s">
         <v>1127</v>
       </c>
-      <c r="B397" s="2" t="s">
+      <c r="C397" s="2" t="s">
         <v>1128</v>
-      </c>
-      <c r="C397" s="2" t="s">
-        <v>1129</v>
       </c>
     </row>
     <row r="398" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A398" s="2" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B398" s="2" t="s">
         <v>1130</v>
       </c>
-      <c r="B398" s="2" t="s">
+      <c r="C398" s="2" t="s">
         <v>1131</v>
-      </c>
-      <c r="C398" s="2" t="s">
-        <v>1132</v>
       </c>
     </row>
     <row r="399" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A399" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B399" s="2" t="s">
         <v>1133</v>
       </c>
-      <c r="B399" s="2" t="s">
+      <c r="C399" s="2" t="s">
         <v>1134</v>
-      </c>
-      <c r="C399" s="2" t="s">
-        <v>1135</v>
       </c>
     </row>
     <row r="400" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A400" s="2" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B400" s="2" t="s">
         <v>1136</v>
       </c>
-      <c r="B400" s="2" t="s">
+      <c r="C400" s="2" t="s">
         <v>1137</v>
-      </c>
-      <c r="C400" s="2" t="s">
-        <v>1138</v>
       </c>
     </row>
     <row r="401" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A401" s="2" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B401" s="2" t="s">
         <v>1139</v>
       </c>
-      <c r="B401" s="2" t="s">
+      <c r="C401" s="2" t="s">
         <v>1140</v>
-      </c>
-      <c r="C401" s="2" t="s">
-        <v>1141</v>
       </c>
     </row>
     <row r="402" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A402" s="2" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B402" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="C402" s="2" t="s">
         <v>1142</v>
-      </c>
-      <c r="B402" s="2" t="s">
-        <v>1143</v>
-      </c>
-      <c r="C402" s="2" t="s">
-        <v>1144</v>
       </c>
     </row>
     <row r="403" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A403" s="2" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B403" s="2" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C403" s="2" t="s">
         <v>1145</v>
-      </c>
-      <c r="B403" s="2" t="s">
-        <v>1146</v>
-      </c>
-      <c r="C403" s="2" t="s">
-        <v>1147</v>
       </c>
     </row>
     <row r="404" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A404" s="2" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B404" s="2" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C404" s="2" t="s">
         <v>1148</v>
-      </c>
-      <c r="B404" s="2" t="s">
-        <v>1149</v>
-      </c>
-      <c r="C404" s="2" t="s">
-        <v>1150</v>
       </c>
     </row>
     <row r="405" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A405" s="2" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B405" s="2" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C405" s="2" t="s">
         <v>1151</v>
-      </c>
-      <c r="B405" s="2" t="s">
-        <v>1152</v>
-      </c>
-      <c r="C405" s="2" t="s">
-        <v>1153</v>
       </c>
     </row>
     <row r="406" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A406" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B406" s="2" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C406" s="2" t="s">
         <v>1154</v>
-      </c>
-      <c r="B406" s="2" t="s">
-        <v>1155</v>
-      </c>
-      <c r="C406" s="2" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="407" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A407" s="2" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B407" s="2" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C407" s="2" t="s">
         <v>1157</v>
-      </c>
-      <c r="B407" s="2" t="s">
-        <v>1158</v>
-      </c>
-      <c r="C407" s="2" t="s">
-        <v>1159</v>
       </c>
     </row>
     <row r="408" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A408" s="2" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B408" s="2" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C408" s="2" t="s">
         <v>1160</v>
-      </c>
-      <c r="B408" s="2" t="s">
-        <v>1161</v>
-      </c>
-      <c r="C408" s="2" t="s">
-        <v>1162</v>
       </c>
     </row>
     <row r="409" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A409" s="2" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B409" s="2" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C409" s="2" t="s">
         <v>1163</v>
-      </c>
-      <c r="B409" s="2" t="s">
-        <v>1164</v>
-      </c>
-      <c r="C409" s="2" t="s">
-        <v>1165</v>
       </c>
     </row>
     <row r="410" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A410" s="2" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B410" s="2" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C410" s="2" t="s">
         <v>1166</v>
-      </c>
-      <c r="B410" s="2" t="s">
-        <v>1167</v>
-      </c>
-      <c r="C410" s="2" t="s">
-        <v>1168</v>
       </c>
     </row>
     <row r="411" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A411" s="2" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B411" s="2" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C411" s="2" t="s">
         <v>1169</v>
-      </c>
-      <c r="B411" s="2" t="s">
-        <v>1170</v>
-      </c>
-      <c r="C411" s="2" t="s">
-        <v>1171</v>
       </c>
     </row>
     <row r="412" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A412" s="2" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B412" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C412" s="2" t="s">
         <v>1172</v>
-      </c>
-      <c r="B412" s="2" t="s">
-        <v>1173</v>
-      </c>
-      <c r="C412" s="2" t="s">
-        <v>1174</v>
       </c>
     </row>
     <row r="413" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A413" s="2" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B413" s="2" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C413" s="2" t="s">
         <v>1175</v>
-      </c>
-      <c r="B413" s="2" t="s">
-        <v>1176</v>
-      </c>
-      <c r="C413" s="2" t="s">
-        <v>1177</v>
       </c>
     </row>
     <row r="414" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A414" s="2" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B414" s="2" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C414" s="2" t="s">
         <v>1178</v>
-      </c>
-      <c r="B414" s="2" t="s">
-        <v>1179</v>
-      </c>
-      <c r="C414" s="2" t="s">
-        <v>1180</v>
       </c>
     </row>
     <row r="415" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A415" s="2" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B415" s="2" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C415" s="2" t="s">
         <v>1181</v>
-      </c>
-      <c r="B415" s="2" t="s">
-        <v>1182</v>
-      </c>
-      <c r="C415" s="2" t="s">
-        <v>1183</v>
       </c>
     </row>
     <row r="416" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A416" s="2" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B416" s="2" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C416" s="2" t="s">
         <v>1184</v>
-      </c>
-      <c r="B416" s="2" t="s">
-        <v>1185</v>
-      </c>
-      <c r="C416" s="2" t="s">
-        <v>1186</v>
       </c>
     </row>
     <row r="417" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A417" s="2" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B417" s="2" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C417" s="2" t="s">
         <v>1187</v>
-      </c>
-      <c r="B417" s="2" t="s">
-        <v>1188</v>
-      </c>
-      <c r="C417" s="2" t="s">
-        <v>1189</v>
       </c>
     </row>
     <row r="418" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A418" s="2" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B418" s="2" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C418" s="2" t="s">
         <v>1190</v>
-      </c>
-      <c r="B418" s="2" t="s">
-        <v>1191</v>
-      </c>
-      <c r="C418" s="2" t="s">
-        <v>1192</v>
       </c>
     </row>
     <row r="419" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A419" s="2" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B419" s="2" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C419" s="2" t="s">
         <v>1193</v>
-      </c>
-      <c r="B419" s="2" t="s">
-        <v>906</v>
-      </c>
-      <c r="C419" s="2" t="s">
-        <v>907</v>
       </c>
     </row>
     <row r="420" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10634,257 +11159,257 @@
         <v>1201</v>
       </c>
       <c r="C422" s="2" t="s">
-        <v>165</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="423" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A423" s="2" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>167</v>
+        <v>1204</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>168</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="424" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A424" s="2" t="s">
-        <v>1203</v>
+        <v>1206</v>
       </c>
       <c r="B424" s="2" t="s">
-        <v>1204</v>
+        <v>1207</v>
       </c>
       <c r="C424" s="2" t="s">
-        <v>1205</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="425" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A425" s="2" t="s">
-        <v>1206</v>
+        <v>1209</v>
       </c>
       <c r="B425" s="2" t="s">
-        <v>173</v>
+        <v>922</v>
       </c>
       <c r="C425" s="2" t="s">
-        <v>174</v>
+        <v>923</v>
       </c>
     </row>
     <row r="426" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A426" s="2" t="s">
-        <v>1207</v>
+        <v>1210</v>
       </c>
       <c r="B426" s="2" t="s">
-        <v>1208</v>
+        <v>1211</v>
       </c>
       <c r="C426" s="2" t="s">
-        <v>1209</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="427" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A427" s="2" t="s">
-        <v>1210</v>
+        <v>1213</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>264</v>
+        <v>1214</v>
       </c>
       <c r="C427" s="2" t="s">
-        <v>265</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="428" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A428" s="2" t="s">
-        <v>1211</v>
+        <v>1216</v>
       </c>
       <c r="B428" s="2" t="s">
-        <v>1212</v>
+        <v>1217</v>
       </c>
       <c r="C428" s="2" t="s">
-        <v>1213</v>
+        <v>183</v>
       </c>
     </row>
     <row r="429" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A429" s="2" t="s">
-        <v>1214</v>
+        <v>1218</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>1019</v>
+        <v>185</v>
       </c>
       <c r="C429" s="2" t="s">
-        <v>1215</v>
+        <v>186</v>
       </c>
     </row>
     <row r="430" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A430" s="2" t="s">
-        <v>1216</v>
+        <v>1219</v>
       </c>
       <c r="B430" s="2" t="s">
-        <v>285</v>
+        <v>1220</v>
       </c>
       <c r="C430" s="2" t="s">
-        <v>286</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="431" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A431" s="2" t="s">
-        <v>1217</v>
+        <v>1222</v>
       </c>
       <c r="B431" s="2" t="s">
-        <v>279</v>
+        <v>191</v>
       </c>
       <c r="C431" s="2" t="s">
-        <v>280</v>
+        <v>192</v>
       </c>
     </row>
     <row r="432" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A432" s="2" t="s">
-        <v>1218</v>
+        <v>1223</v>
       </c>
       <c r="B432" s="2" t="s">
-        <v>1219</v>
+        <v>1224</v>
       </c>
       <c r="C432" s="2" t="s">
-        <v>1220</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="433" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A433" s="2" t="s">
-        <v>1221</v>
+        <v>1226</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>1222</v>
+        <v>282</v>
       </c>
       <c r="C433" s="2" t="s">
-        <v>1223</v>
+        <v>283</v>
       </c>
     </row>
     <row r="434" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A434" s="2" t="s">
-        <v>1224</v>
+        <v>1227</v>
       </c>
       <c r="B434" s="2" t="s">
-        <v>295</v>
+        <v>1228</v>
       </c>
       <c r="C434" s="2" t="s">
-        <v>296</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="435" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A435" s="2" t="s">
-        <v>1225</v>
+        <v>1230</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>1226</v>
+        <v>1035</v>
       </c>
       <c r="C435" s="2" t="s">
-        <v>1227</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="436" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A436" s="2" t="s">
-        <v>1228</v>
+        <v>1232</v>
       </c>
       <c r="B436" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C436" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="437" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A437" s="2" t="s">
-        <v>1229</v>
+        <v>1233</v>
       </c>
       <c r="B437" s="2" t="s">
-        <v>1230</v>
+        <v>297</v>
       </c>
       <c r="C437" s="2" t="s">
-        <v>1231</v>
+        <v>298</v>
       </c>
     </row>
     <row r="438" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A438" s="2" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="B438" s="2" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="C438" s="2" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="439" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A439" s="2" t="s">
-        <v>1234</v>
+        <v>1237</v>
       </c>
       <c r="B439" s="2" t="s">
-        <v>1235</v>
+        <v>1238</v>
       </c>
       <c r="C439" s="2" t="s">
-        <v>1235</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="440" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A440" s="2" t="s">
-        <v>1236</v>
+        <v>1240</v>
       </c>
       <c r="B440" s="2" t="s">
-        <v>1237</v>
+        <v>313</v>
       </c>
       <c r="C440" s="2" t="s">
-        <v>1238</v>
+        <v>314</v>
       </c>
     </row>
     <row r="441" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A441" s="2" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
       <c r="B441" s="2" t="s">
-        <v>1237</v>
+        <v>1242</v>
       </c>
       <c r="C441" s="2" t="s">
-        <v>1238</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="442" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A442" s="2" t="s">
-        <v>1240</v>
+        <v>1244</v>
       </c>
       <c r="B442" s="2" t="s">
-        <v>1241</v>
+        <v>319</v>
       </c>
       <c r="C442" s="2" t="s">
-        <v>1242</v>
+        <v>320</v>
       </c>
     </row>
     <row r="443" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A443" s="2" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="B443" s="2" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="C443" s="2" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="444" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A444" s="2" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="B444" s="2" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="C444" s="2" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="445" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A445" s="2" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B445" s="2" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="C445" s="2" t="s">
         <v>1251</v>
@@ -10906,120 +11431,120 @@
         <v>1255</v>
       </c>
       <c r="B447" s="2" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="C447" s="2" t="s">
-        <v>1257</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="448" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A448" s="2" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B448" s="2" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C448" s="2" t="s">
         <v>1258</v>
-      </c>
-      <c r="B448" s="2" t="s">
-        <v>1259</v>
-      </c>
-      <c r="C448" s="2" t="s">
-        <v>1260</v>
       </c>
     </row>
     <row r="449" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A449" s="2" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B449" s="2" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C449" s="2" t="s">
         <v>1261</v>
-      </c>
-      <c r="B449" s="2" t="s">
-        <v>1262</v>
-      </c>
-      <c r="C449" s="2" t="s">
-        <v>1263</v>
       </c>
     </row>
     <row r="450" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A450" s="2" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B450" s="2" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C450" s="2" t="s">
         <v>1264</v>
-      </c>
-      <c r="B450" s="2" t="s">
-        <v>1265</v>
-      </c>
-      <c r="C450" s="2" t="s">
-        <v>1266</v>
       </c>
     </row>
     <row r="451" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A451" s="2" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B451" s="2" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C451" s="2" t="s">
         <v>1267</v>
-      </c>
-      <c r="B451" s="2" t="s">
-        <v>1268</v>
-      </c>
-      <c r="C451" s="2" t="s">
-        <v>1269</v>
       </c>
     </row>
     <row r="452" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A452" s="2" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B452" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C452" s="2" t="s">
         <v>1270</v>
-      </c>
-      <c r="B452" s="2" t="s">
-        <v>1271</v>
-      </c>
-      <c r="C452" s="2" t="s">
-        <v>1272</v>
       </c>
     </row>
     <row r="453" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A453" s="2" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B453" s="2" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C453" s="2" t="s">
         <v>1273</v>
-      </c>
-      <c r="B453" s="2" t="s">
-        <v>1274</v>
-      </c>
-      <c r="C453" s="2" t="s">
-        <v>1275</v>
       </c>
     </row>
     <row r="454" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A454" s="2" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B454" s="2" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C454" s="2" t="s">
         <v>1276</v>
-      </c>
-      <c r="B454" s="2" t="s">
-        <v>1277</v>
-      </c>
-      <c r="C454" s="2" t="s">
-        <v>1278</v>
       </c>
     </row>
     <row r="455" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A455" s="2" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B455" s="2" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C455" s="2" t="s">
         <v>1279</v>
-      </c>
-      <c r="B455" s="2" t="s">
-        <v>1280</v>
-      </c>
-      <c r="C455" s="2" t="s">
-        <v>1257</v>
       </c>
     </row>
     <row r="456" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A456" s="2" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B456" s="2" t="s">
         <v>1281</v>
       </c>
-      <c r="B456" s="2" t="s">
+      <c r="C456" s="2" t="s">
         <v>1282</v>
-      </c>
-      <c r="C456" s="2" t="s">
-        <v>1283</v>
       </c>
     </row>
     <row r="457" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A457" s="2" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B457" s="2" t="s">
         <v>1284</v>
       </c>
-      <c r="B457" s="2" t="s">
+      <c r="C457" s="2" t="s">
         <v>1285</v>
-      </c>
-      <c r="C457" s="2" t="s">
-        <v>1263</v>
       </c>
     </row>
     <row r="458" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11060,43 +11585,43 @@
         <v>1295</v>
       </c>
       <c r="B461" s="2" t="s">
-        <v>1147</v>
+        <v>1296</v>
       </c>
       <c r="C461" s="2" t="s">
-        <v>1147</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="462" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A462" s="2" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="B462" s="2" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="C462" s="2" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="463" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A463" s="2" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="C463" s="2" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="464" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A464" s="2" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="B464" s="2" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="C464" s="2" t="s">
-        <v>1304</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="465" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11137,32 +11662,32 @@
         <v>1314</v>
       </c>
       <c r="B468" s="2" t="s">
-        <v>1315</v>
+        <v>1163</v>
       </c>
       <c r="C468" s="2" t="s">
-        <v>1316</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="469" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A469" s="2" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B469" s="2" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C469" s="2" t="s">
         <v>1317</v>
-      </c>
-      <c r="B469" s="2" t="s">
-        <v>1318</v>
-      </c>
-      <c r="C469" s="2" t="s">
-        <v>1319</v>
       </c>
     </row>
     <row r="470" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A470" s="2" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B470" s="2" t="s">
+        <v>1319</v>
+      </c>
+      <c r="C470" s="2" t="s">
         <v>1320</v>
-      </c>
-      <c r="B470" s="2" t="s">
-        <v>1185</v>
-      </c>
-      <c r="C470" s="2" t="s">
-        <v>1186</v>
       </c>
     </row>
     <row r="471" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11236,109 +11761,109 @@
         <v>1339</v>
       </c>
       <c r="B477" s="2" t="s">
-        <v>1340</v>
+        <v>1201</v>
       </c>
       <c r="C477" s="2" t="s">
-        <v>199</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="478" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A478" s="2" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B478" s="2" t="s">
         <v>1341</v>
       </c>
-      <c r="B478" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="C478" s="2" t="s">
-        <v>168</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="479" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A479" s="2" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="B479" s="2" t="s">
-        <v>170</v>
+        <v>1344</v>
       </c>
       <c r="C479" s="2" t="s">
-        <v>171</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="480" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A480" s="2" t="s">
-        <v>1343</v>
+        <v>1346</v>
       </c>
       <c r="B480" s="2" t="s">
-        <v>581</v>
+        <v>1347</v>
       </c>
       <c r="C480" s="2" t="s">
-        <v>582</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="481" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A481" s="2" t="s">
-        <v>1344</v>
+        <v>1349</v>
       </c>
       <c r="B481" s="2" t="s">
-        <v>1345</v>
+        <v>1350</v>
       </c>
       <c r="C481" s="2" t="s">
-        <v>1346</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="482" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A482" s="2" t="s">
-        <v>1347</v>
+        <v>1352</v>
       </c>
       <c r="B482" s="2" t="s">
-        <v>1348</v>
+        <v>1353</v>
       </c>
       <c r="C482" s="2" t="s">
-        <v>1349</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="483" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A483" s="2" t="s">
-        <v>1350</v>
+        <v>1355</v>
       </c>
       <c r="B483" s="2" t="s">
-        <v>1351</v>
+        <v>1356</v>
       </c>
       <c r="C483" s="2" t="s">
-        <v>1352</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="484" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A484" s="2" t="s">
-        <v>1353</v>
+        <v>1358</v>
       </c>
       <c r="B484" s="2" t="s">
-        <v>1354</v>
+        <v>1359</v>
       </c>
       <c r="C484" s="2" t="s">
-        <v>1355</v>
+        <v>217</v>
       </c>
     </row>
     <row r="485" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A485" s="2" t="s">
-        <v>1356</v>
+        <v>1360</v>
       </c>
       <c r="B485" s="2" t="s">
-        <v>1357</v>
+        <v>185</v>
       </c>
       <c r="C485" s="2" t="s">
-        <v>1358</v>
+        <v>186</v>
       </c>
     </row>
     <row r="486" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A486" s="2" t="s">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="B486" s="2" t="s">
-        <v>1360</v>
+        <v>188</v>
       </c>
       <c r="C486" s="2" t="s">
-        <v>1361</v>
+        <v>189</v>
       </c>
     </row>
     <row r="487" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11346,153 +11871,153 @@
         <v>1362</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>1363</v>
+        <v>597</v>
       </c>
       <c r="C487" s="2" t="s">
-        <v>1364</v>
+        <v>598</v>
       </c>
     </row>
     <row r="488" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A488" s="2" t="s">
+        <v>1363</v>
+      </c>
+      <c r="B488" s="2" t="s">
+        <v>1364</v>
+      </c>
+      <c r="C488" s="2" t="s">
         <v>1365</v>
-      </c>
-      <c r="B488" s="2" t="s">
-        <v>1366</v>
-      </c>
-      <c r="C488" s="2" t="s">
-        <v>1367</v>
       </c>
     </row>
     <row r="489" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A489" s="2" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B489" s="2" t="s">
+        <v>1367</v>
+      </c>
+      <c r="C489" s="2" t="s">
         <v>1368</v>
-      </c>
-      <c r="B489" s="2" t="s">
-        <v>1369</v>
-      </c>
-      <c r="C489" s="2" t="s">
-        <v>1370</v>
       </c>
     </row>
     <row r="490" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A490" s="2" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B490" s="2" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C490" s="2" t="s">
         <v>1371</v>
-      </c>
-      <c r="B490" s="2" t="s">
-        <v>1372</v>
-      </c>
-      <c r="C490" s="2" t="s">
-        <v>1373</v>
       </c>
     </row>
     <row r="491" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A491" s="2" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B491" s="2" t="s">
+        <v>1373</v>
+      </c>
+      <c r="C491" s="2" t="s">
         <v>1374</v>
-      </c>
-      <c r="B491" s="2" t="s">
-        <v>1375</v>
-      </c>
-      <c r="C491" s="2" t="s">
-        <v>1376</v>
       </c>
     </row>
     <row r="492" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A492" s="2" t="s">
+        <v>1375</v>
+      </c>
+      <c r="B492" s="2" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C492" s="2" t="s">
         <v>1377</v>
-      </c>
-      <c r="B492" s="2" t="s">
-        <v>1378</v>
-      </c>
-      <c r="C492" s="2" t="s">
-        <v>1379</v>
       </c>
     </row>
     <row r="493" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A493" s="2" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B493" s="2" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C493" s="2" t="s">
         <v>1380</v>
-      </c>
-      <c r="B493" s="2" t="s">
-        <v>1381</v>
-      </c>
-      <c r="C493" s="2" t="s">
-        <v>1382</v>
       </c>
     </row>
     <row r="494" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A494" s="2" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B494" s="2" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C494" s="2" t="s">
         <v>1383</v>
-      </c>
-      <c r="B494" s="2" t="s">
-        <v>1384</v>
-      </c>
-      <c r="C494" s="2" t="s">
-        <v>1385</v>
       </c>
     </row>
     <row r="495" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A495" s="2" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B495" s="2" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C495" s="2" t="s">
         <v>1386</v>
-      </c>
-      <c r="B495" s="2" t="s">
-        <v>1387</v>
-      </c>
-      <c r="C495" s="2" t="s">
-        <v>1388</v>
       </c>
     </row>
     <row r="496" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A496" s="2" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B496" s="2" t="s">
+        <v>1388</v>
+      </c>
+      <c r="C496" s="2" t="s">
         <v>1389</v>
-      </c>
-      <c r="B496" s="2" t="s">
-        <v>1390</v>
-      </c>
-      <c r="C496" s="2" t="s">
-        <v>1391</v>
       </c>
     </row>
     <row r="497" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A497" s="2" t="s">
+        <v>1390</v>
+      </c>
+      <c r="B497" s="2" t="s">
+        <v>1391</v>
+      </c>
+      <c r="C497" s="2" t="s">
         <v>1392</v>
-      </c>
-      <c r="B497" s="2" t="s">
-        <v>1393</v>
-      </c>
-      <c r="C497" s="2" t="s">
-        <v>1394</v>
       </c>
     </row>
     <row r="498" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A498" s="2" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B498" s="2" t="s">
+        <v>1394</v>
+      </c>
+      <c r="C498" s="2" t="s">
         <v>1395</v>
-      </c>
-      <c r="B498" s="2" t="s">
-        <v>1396</v>
-      </c>
-      <c r="C498" s="2" t="s">
-        <v>1397</v>
       </c>
     </row>
     <row r="499" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A499" s="2" t="s">
+        <v>1396</v>
+      </c>
+      <c r="B499" s="2" t="s">
+        <v>1397</v>
+      </c>
+      <c r="C499" s="2" t="s">
         <v>1398</v>
-      </c>
-      <c r="B499" s="2" t="s">
-        <v>1399</v>
-      </c>
-      <c r="C499" s="2" t="s">
-        <v>1400</v>
       </c>
     </row>
     <row r="500" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A500" s="2" t="s">
+        <v>1399</v>
+      </c>
+      <c r="B500" s="2" t="s">
+        <v>1400</v>
+      </c>
+      <c r="C500" s="2" t="s">
         <v>1401</v>
-      </c>
-      <c r="B500" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C500" s="2" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="501" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11503,271 +12028,271 @@
         <v>1403</v>
       </c>
       <c r="C501" s="2" t="s">
-        <v>1029</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="502" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A502" s="2" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="B502" s="2" t="s">
-        <v>1345</v>
+        <v>1406</v>
       </c>
       <c r="C502" s="2" t="s">
-        <v>1346</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="503" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A503" s="2" t="s">
-        <v>1405</v>
+        <v>1408</v>
       </c>
       <c r="B503" s="2" t="s">
-        <v>1406</v>
+        <v>1409</v>
       </c>
       <c r="C503" s="2" t="s">
-        <v>1138</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="504" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A504" s="2" t="s">
-        <v>1407</v>
+        <v>1411</v>
       </c>
       <c r="B504" s="2" t="s">
-        <v>1408</v>
+        <v>1412</v>
       </c>
       <c r="C504" s="2" t="s">
-        <v>1409</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="505" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A505" s="2" t="s">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="B505" s="2" t="s">
-        <v>1348</v>
+        <v>1415</v>
       </c>
       <c r="C505" s="2" t="s">
-        <v>1349</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="506" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A506" s="2" t="s">
-        <v>1411</v>
+        <v>1417</v>
       </c>
       <c r="B506" s="2" t="s">
-        <v>176</v>
+        <v>1418</v>
       </c>
       <c r="C506" s="2" t="s">
-        <v>176</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="507" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A507" s="2" t="s">
-        <v>1412</v>
+        <v>1420</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>1413</v>
+        <v>43</v>
       </c>
       <c r="C507" s="2" t="s">
-        <v>1414</v>
+        <v>44</v>
       </c>
     </row>
     <row r="508" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A508" s="2" t="s">
-        <v>1415</v>
+        <v>1421</v>
       </c>
       <c r="B508" s="2" t="s">
-        <v>1416</v>
+        <v>1422</v>
       </c>
       <c r="C508" s="2" t="s">
-        <v>1417</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="509" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A509" s="2" t="s">
-        <v>1418</v>
+        <v>1423</v>
       </c>
       <c r="B509" s="2" t="s">
-        <v>1419</v>
+        <v>1364</v>
       </c>
       <c r="C509" s="2" t="s">
-        <v>1420</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="510" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A510" s="2" t="s">
-        <v>1421</v>
+        <v>1424</v>
       </c>
       <c r="B510" s="2" t="s">
-        <v>1422</v>
+        <v>1425</v>
       </c>
       <c r="C510" s="2" t="s">
-        <v>1423</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="511" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A511" s="2" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="C511" s="2" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="512" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A512" s="2" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="B512" s="2" t="s">
-        <v>1182</v>
+        <v>1367</v>
       </c>
       <c r="C512" s="2" t="s">
-        <v>1183</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="513" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A513" s="2" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>4</v>
+        <v>194</v>
       </c>
       <c r="C513" s="2" t="s">
-        <v>5</v>
+        <v>194</v>
       </c>
     </row>
     <row r="514" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A514" s="2" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="B514" s="2" t="s">
-        <v>1170</v>
+        <v>1432</v>
       </c>
       <c r="C514" s="2" t="s">
-        <v>1171</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="515" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A515" s="2" t="s">
-        <v>1430</v>
+        <v>1434</v>
       </c>
       <c r="B515" s="2" t="s">
-        <v>1185</v>
+        <v>1435</v>
       </c>
       <c r="C515" s="2" t="s">
-        <v>1186</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="516" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A516" s="2" t="s">
-        <v>1431</v>
+        <v>1437</v>
       </c>
       <c r="B516" s="2" t="s">
-        <v>1432</v>
+        <v>1438</v>
       </c>
       <c r="C516" s="2" t="s">
-        <v>1433</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="517" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A517" s="2" t="s">
-        <v>1434</v>
+        <v>1440</v>
       </c>
       <c r="B517" s="2" t="s">
-        <v>1435</v>
+        <v>1441</v>
       </c>
       <c r="C517" s="2" t="s">
-        <v>1436</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="518" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A518" s="2" t="s">
-        <v>1437</v>
+        <v>1443</v>
       </c>
       <c r="B518" s="2" t="s">
-        <v>1188</v>
+        <v>1444</v>
       </c>
       <c r="C518" s="2" t="s">
-        <v>1189</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="519" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A519" s="2" t="s">
-        <v>1438</v>
+        <v>1446</v>
       </c>
       <c r="B519" s="2" t="s">
-        <v>1439</v>
+        <v>1198</v>
       </c>
       <c r="C519" s="2" t="s">
-        <v>1440</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="520" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A520" s="2" t="s">
-        <v>1441</v>
+        <v>1447</v>
       </c>
       <c r="B520" s="2" t="s">
-        <v>1191</v>
+        <v>4</v>
       </c>
       <c r="C520" s="2" t="s">
-        <v>1442</v>
+        <v>5</v>
       </c>
     </row>
     <row r="521" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A521" s="2" t="s">
-        <v>1443</v>
+        <v>1448</v>
       </c>
       <c r="B521" s="2" t="s">
-        <v>1137</v>
+        <v>1186</v>
       </c>
       <c r="C521" s="2" t="s">
-        <v>1444</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="522" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A522" s="2" t="s">
-        <v>1445</v>
+        <v>1449</v>
       </c>
       <c r="B522" s="2" t="s">
-        <v>1446</v>
+        <v>1201</v>
       </c>
       <c r="C522" s="2" t="s">
-        <v>1447</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="523" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A523" s="2" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="B523" s="2" t="s">
-        <v>1449</v>
+        <v>1451</v>
       </c>
       <c r="C523" s="2" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="524" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A524" s="2" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="B524" s="2" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
       <c r="C524" s="2" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="525" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A525" s="2" t="s">
-        <v>1454</v>
+        <v>1456</v>
       </c>
       <c r="B525" s="2" t="s">
-        <v>1455</v>
+        <v>1204</v>
       </c>
       <c r="C525" s="2" t="s">
-        <v>1456</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="526" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11786,54 +12311,54 @@
         <v>1460</v>
       </c>
       <c r="B527" s="2" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C527" s="2" t="s">
         <v>1461</v>
-      </c>
-      <c r="C527" s="2" t="s">
-        <v>1462</v>
       </c>
     </row>
     <row r="528" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A528" s="2" t="s">
+        <v>1462</v>
+      </c>
+      <c r="B528" s="2" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C528" s="2" t="s">
         <v>1463</v>
-      </c>
-      <c r="B528" s="2" t="s">
-        <v>1464</v>
-      </c>
-      <c r="C528" s="2" t="s">
-        <v>1465</v>
       </c>
     </row>
     <row r="529" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A529" s="2" t="s">
+        <v>1464</v>
+      </c>
+      <c r="B529" s="2" t="s">
+        <v>1465</v>
+      </c>
+      <c r="C529" s="2" t="s">
         <v>1466</v>
-      </c>
-      <c r="B529" s="2" t="s">
-        <v>1467</v>
-      </c>
-      <c r="C529" s="2" t="s">
-        <v>1468</v>
       </c>
     </row>
     <row r="530" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A530" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="B530" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="C530" s="2" t="s">
         <v>1469</v>
-      </c>
-      <c r="B530" s="2" t="s">
-        <v>1470</v>
-      </c>
-      <c r="C530" s="2" t="s">
-        <v>1471</v>
       </c>
     </row>
     <row r="531" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A531" s="2" t="s">
+        <v>1470</v>
+      </c>
+      <c r="B531" s="2" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C531" s="2" t="s">
         <v>1472</v>
-      </c>
-      <c r="B531" s="2" t="s">
-        <v>1182</v>
-      </c>
-      <c r="C531" s="2" t="s">
-        <v>1183</v>
       </c>
     </row>
     <row r="532" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11841,142 +12366,142 @@
         <v>1473</v>
       </c>
       <c r="B532" s="2" t="s">
-        <v>4</v>
+        <v>1474</v>
       </c>
       <c r="C532" s="2" t="s">
-        <v>5</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="533" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A533" s="2" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="B533" s="2" t="s">
-        <v>1188</v>
+        <v>1477</v>
       </c>
       <c r="C533" s="2" t="s">
-        <v>1189</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="534" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A534" s="2" t="s">
-        <v>1475</v>
+        <v>1479</v>
       </c>
       <c r="B534" s="2" t="s">
-        <v>1476</v>
+        <v>1480</v>
       </c>
       <c r="C534" s="2" t="s">
-        <v>1477</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="535" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A535" s="2" t="s">
-        <v>1478</v>
+        <v>1482</v>
       </c>
       <c r="B535" s="2" t="s">
-        <v>1479</v>
+        <v>1483</v>
       </c>
       <c r="C535" s="2" t="s">
-        <v>1480</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="536" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A536" s="2" t="s">
-        <v>1481</v>
+        <v>1485</v>
       </c>
       <c r="B536" s="2" t="s">
-        <v>1482</v>
+        <v>1486</v>
       </c>
       <c r="C536" s="2" t="s">
-        <v>1483</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="537" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A537" s="2" t="s">
-        <v>1484</v>
+        <v>1488</v>
       </c>
       <c r="B537" s="2" t="s">
-        <v>1455</v>
+        <v>1489</v>
       </c>
       <c r="C537" s="2" t="s">
-        <v>1456</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="538" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A538" s="2" t="s">
-        <v>1485</v>
+        <v>1491</v>
       </c>
       <c r="B538" s="2" t="s">
-        <v>1486</v>
+        <v>1198</v>
       </c>
       <c r="C538" s="2" t="s">
-        <v>1487</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="539" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A539" s="2" t="s">
-        <v>1488</v>
+        <v>1492</v>
       </c>
       <c r="B539" s="2" t="s">
-        <v>1489</v>
+        <v>4</v>
       </c>
       <c r="C539" s="2" t="s">
-        <v>1490</v>
+        <v>5</v>
       </c>
     </row>
     <row r="540" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A540" s="2" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="B540" s="2" t="s">
-        <v>1309</v>
+        <v>1204</v>
       </c>
       <c r="C540" s="2" t="s">
-        <v>1310</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="541" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A541" s="2" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="B541" s="2" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="C541" s="2" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="542" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A542" s="2" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="B542" s="2" t="s">
-        <v>1496</v>
+        <v>1498</v>
       </c>
       <c r="C542" s="2" t="s">
-        <v>1497</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="543" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A543" s="2" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="B543" s="2" t="s">
-        <v>1499</v>
+        <v>1501</v>
       </c>
       <c r="C543" s="2" t="s">
-        <v>1500</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="544" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A544" s="2" t="s">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="B544" s="2" t="s">
-        <v>1502</v>
+        <v>1474</v>
       </c>
       <c r="C544" s="2" t="s">
-        <v>1503</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="545" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12006,120 +12531,120 @@
         <v>1510</v>
       </c>
       <c r="B547" s="2" t="s">
-        <v>1511</v>
+        <v>1328</v>
       </c>
       <c r="C547" s="2" t="s">
-        <v>1512</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="548" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A548" s="2" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B548" s="2" t="s">
+        <v>1512</v>
+      </c>
+      <c r="C548" s="2" t="s">
         <v>1513</v>
-      </c>
-      <c r="B548" s="2" t="s">
-        <v>1514</v>
-      </c>
-      <c r="C548" s="2" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="549" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A549" s="2" t="s">
+        <v>1514</v>
+      </c>
+      <c r="B549" s="2" t="s">
         <v>1515</v>
       </c>
-      <c r="B549" s="2" t="s">
+      <c r="C549" s="2" t="s">
         <v>1516</v>
-      </c>
-      <c r="C549" s="2" t="s">
-        <v>1517</v>
       </c>
     </row>
     <row r="550" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A550" s="2" t="s">
+        <v>1517</v>
+      </c>
+      <c r="B550" s="2" t="s">
         <v>1518</v>
       </c>
-      <c r="B550" s="2" t="s">
+      <c r="C550" s="2" t="s">
         <v>1519</v>
-      </c>
-      <c r="C550" s="2" t="s">
-        <v>1520</v>
       </c>
     </row>
     <row r="551" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A551" s="2" t="s">
+        <v>1520</v>
+      </c>
+      <c r="B551" s="2" t="s">
         <v>1521</v>
       </c>
-      <c r="B551" s="2" t="s">
+      <c r="C551" s="2" t="s">
         <v>1522</v>
-      </c>
-      <c r="C551" s="2" t="s">
-        <v>1523</v>
       </c>
     </row>
     <row r="552" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A552" s="2" t="s">
+        <v>1523</v>
+      </c>
+      <c r="B552" s="2" t="s">
         <v>1524</v>
       </c>
-      <c r="B552" s="2" t="s">
+      <c r="C552" s="2" t="s">
         <v>1525</v>
-      </c>
-      <c r="C552" s="2" t="s">
-        <v>1526</v>
       </c>
     </row>
     <row r="553" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A553" s="2" t="s">
+        <v>1526</v>
+      </c>
+      <c r="B553" s="2" t="s">
         <v>1527</v>
       </c>
-      <c r="B553" s="2" t="s">
+      <c r="C553" s="2" t="s">
         <v>1528</v>
-      </c>
-      <c r="C553" s="2" t="s">
-        <v>1529</v>
       </c>
     </row>
     <row r="554" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A554" s="2" t="s">
+        <v>1529</v>
+      </c>
+      <c r="B554" s="2" t="s">
         <v>1530</v>
       </c>
-      <c r="B554" s="2" t="s">
+      <c r="C554" s="2" t="s">
         <v>1531</v>
-      </c>
-      <c r="C554" s="2" t="s">
-        <v>1532</v>
       </c>
     </row>
     <row r="555" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A555" s="2" t="s">
+        <v>1532</v>
+      </c>
+      <c r="B555" s="2" t="s">
         <v>1533</v>
       </c>
-      <c r="B555" s="2" t="s">
-        <v>1534</v>
-      </c>
       <c r="C555" s="2" t="s">
-        <v>1535</v>
+        <v>515</v>
       </c>
     </row>
     <row r="556" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A556" s="2" t="s">
+        <v>1534</v>
+      </c>
+      <c r="B556" s="2" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C556" s="2" t="s">
         <v>1536</v>
-      </c>
-      <c r="B556" s="2" t="s">
-        <v>1537</v>
-      </c>
-      <c r="C556" s="2" t="s">
-        <v>1538</v>
       </c>
     </row>
     <row r="557" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A557" s="2" t="s">
+        <v>1537</v>
+      </c>
+      <c r="B557" s="2" t="s">
+        <v>1538</v>
+      </c>
+      <c r="C557" s="2" t="s">
         <v>1539</v>
-      </c>
-      <c r="B557" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="C557" s="2" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="558" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12149,54 +12674,54 @@
         <v>1546</v>
       </c>
       <c r="B560" s="2" t="s">
-        <v>264</v>
+        <v>1547</v>
       </c>
       <c r="C560" s="2" t="s">
-        <v>265</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="561" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A561" s="2" t="s">
-        <v>1547</v>
+        <v>1549</v>
       </c>
       <c r="B561" s="2" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="C561" s="2" t="s">
-        <v>1549</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="562" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A562" s="2" t="s">
-        <v>1550</v>
+        <v>1552</v>
       </c>
       <c r="B562" s="2" t="s">
-        <v>1551</v>
+        <v>1553</v>
       </c>
       <c r="C562" s="2" t="s">
-        <v>1552</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="563" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A563" s="2" t="s">
-        <v>1553</v>
+        <v>1555</v>
       </c>
       <c r="B563" s="2" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="C563" s="2" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="564" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A564" s="2" t="s">
-        <v>1556</v>
+        <v>1558</v>
       </c>
       <c r="B564" s="2" t="s">
-        <v>1557</v>
+        <v>514</v>
       </c>
       <c r="C564" s="2" t="s">
-        <v>1558</v>
+        <v>515</v>
       </c>
     </row>
     <row r="565" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12226,76 +12751,76 @@
         <v>1565</v>
       </c>
       <c r="B567" s="2" t="s">
-        <v>1566</v>
+        <v>282</v>
       </c>
       <c r="C567" s="2" t="s">
-        <v>1567</v>
+        <v>283</v>
       </c>
     </row>
     <row r="568" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A568" s="2" t="s">
+        <v>1566</v>
+      </c>
+      <c r="B568" s="2" t="s">
+        <v>1567</v>
+      </c>
+      <c r="C568" s="2" t="s">
         <v>1568</v>
-      </c>
-      <c r="B568" s="2" t="s">
-        <v>1569</v>
-      </c>
-      <c r="C568" s="2" t="s">
-        <v>1570</v>
       </c>
     </row>
     <row r="569" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A569" s="2" t="s">
+        <v>1569</v>
+      </c>
+      <c r="B569" s="2" t="s">
+        <v>1570</v>
+      </c>
+      <c r="C569" s="2" t="s">
         <v>1571</v>
-      </c>
-      <c r="B569" s="2" t="s">
-        <v>1572</v>
-      </c>
-      <c r="C569" s="2" t="s">
-        <v>1573</v>
       </c>
     </row>
     <row r="570" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A570" s="2" t="s">
+        <v>1572</v>
+      </c>
+      <c r="B570" s="2" t="s">
+        <v>1573</v>
+      </c>
+      <c r="C570" s="2" t="s">
         <v>1574</v>
-      </c>
-      <c r="B570" s="2" t="s">
-        <v>1575</v>
-      </c>
-      <c r="C570" s="2" t="s">
-        <v>1576</v>
       </c>
     </row>
     <row r="571" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A571" s="2" t="s">
+        <v>1575</v>
+      </c>
+      <c r="B571" s="2" t="s">
+        <v>1576</v>
+      </c>
+      <c r="C571" s="2" t="s">
         <v>1577</v>
-      </c>
-      <c r="B571" s="2" t="s">
-        <v>1578</v>
-      </c>
-      <c r="C571" s="2" t="s">
-        <v>1579</v>
       </c>
     </row>
     <row r="572" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A572" s="2" t="s">
+        <v>1578</v>
+      </c>
+      <c r="B572" s="2" t="s">
+        <v>1579</v>
+      </c>
+      <c r="C572" s="2" t="s">
         <v>1580</v>
-      </c>
-      <c r="B572" s="2" t="s">
-        <v>1581</v>
-      </c>
-      <c r="C572" s="2" t="s">
-        <v>1582</v>
       </c>
     </row>
     <row r="573" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A573" s="2" t="s">
+        <v>1581</v>
+      </c>
+      <c r="B573" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="C573" s="2" t="s">
         <v>1583</v>
-      </c>
-      <c r="B573" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="C573" s="2" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="574" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12306,84 +12831,84 @@
         <v>1585</v>
       </c>
       <c r="C574" s="2" t="s">
-        <v>1029</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="575" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A575" s="2" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="B575" s="2" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="C575" s="2" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="576" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A576" s="2" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="B576" s="2" t="s">
-        <v>1408</v>
+        <v>1591</v>
       </c>
       <c r="C576" s="2" t="s">
-        <v>1409</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="577" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A577" s="2" t="s">
-        <v>1590</v>
+        <v>1593</v>
       </c>
       <c r="B577" s="2" t="s">
-        <v>1591</v>
+        <v>1594</v>
       </c>
       <c r="C577" s="2" t="s">
-        <v>1592</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="578" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A578" s="2" t="s">
-        <v>1593</v>
+        <v>1596</v>
       </c>
       <c r="B578" s="2" t="s">
-        <v>1594</v>
+        <v>1597</v>
       </c>
       <c r="C578" s="2" t="s">
-        <v>1595</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="579" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A579" s="2" t="s">
-        <v>1596</v>
+        <v>1599</v>
       </c>
       <c r="B579" s="2" t="s">
-        <v>1597</v>
+        <v>1600</v>
       </c>
       <c r="C579" s="2" t="s">
-        <v>1598</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="580" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A580" s="2" t="s">
-        <v>1599</v>
+        <v>1602</v>
       </c>
       <c r="B580" s="2" t="s">
-        <v>1600</v>
+        <v>276</v>
       </c>
       <c r="C580" s="2" t="s">
-        <v>1601</v>
+        <v>277</v>
       </c>
     </row>
     <row r="581" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A581" s="2" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="B581" s="2" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="C581" s="2" t="s">
-        <v>1604</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="582" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12391,131 +12916,131 @@
         <v>1605</v>
       </c>
       <c r="B582" s="2" t="s">
-        <v>167</v>
+        <v>1606</v>
       </c>
       <c r="C582" s="2" t="s">
-        <v>168</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="583" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A583" s="2" t="s">
-        <v>1606</v>
+        <v>1608</v>
       </c>
       <c r="B583" s="2" t="s">
-        <v>1026</v>
+        <v>1427</v>
       </c>
       <c r="C583" s="2" t="s">
-        <v>595</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="584" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A584" s="2" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
       <c r="B584" s="2" t="s">
-        <v>1035</v>
+        <v>1610</v>
       </c>
       <c r="C584" s="2" t="s">
-        <v>1608</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="585" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A585" s="2" t="s">
-        <v>1609</v>
+        <v>1612</v>
       </c>
       <c r="B585" s="2" t="s">
-        <v>1610</v>
+        <v>1613</v>
       </c>
       <c r="C585" s="2" t="s">
-        <v>1611</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="586" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A586" s="2" t="s">
-        <v>1612</v>
+        <v>1615</v>
       </c>
       <c r="B586" s="2" t="s">
-        <v>258</v>
+        <v>1616</v>
       </c>
       <c r="C586" s="2" t="s">
-        <v>259</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="587" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A587" s="2" t="s">
-        <v>1613</v>
+        <v>1618</v>
       </c>
       <c r="B587" s="2" t="s">
-        <v>1614</v>
+        <v>1619</v>
       </c>
       <c r="C587" s="2" t="s">
-        <v>1615</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="588" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A588" s="2" t="s">
-        <v>1616</v>
+        <v>1621</v>
       </c>
       <c r="B588" s="2" t="s">
-        <v>1617</v>
+        <v>1622</v>
       </c>
       <c r="C588" s="2" t="s">
-        <v>1618</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="589" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A589" s="2" t="s">
-        <v>1619</v>
+        <v>1624</v>
       </c>
       <c r="B589" s="2" t="s">
-        <v>1620</v>
+        <v>185</v>
       </c>
       <c r="C589" s="2" t="s">
-        <v>1621</v>
+        <v>186</v>
       </c>
     </row>
     <row r="590" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A590" s="2" t="s">
-        <v>1622</v>
+        <v>1625</v>
       </c>
       <c r="B590" s="2" t="s">
-        <v>1623</v>
+        <v>1042</v>
       </c>
       <c r="C590" s="2" t="s">
-        <v>1624</v>
+        <v>611</v>
       </c>
     </row>
     <row r="591" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A591" s="2" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="B591" s="2" t="s">
-        <v>264</v>
+        <v>1051</v>
       </c>
       <c r="C591" s="2" t="s">
-        <v>265</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="592" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A592" s="2" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
       <c r="B592" s="2" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
       <c r="C592" s="2" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="593" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A593" s="2" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
       <c r="B593" s="2" t="s">
-        <v>1630</v>
+        <v>276</v>
       </c>
       <c r="C593" s="2" t="s">
-        <v>1631</v>
+        <v>277</v>
       </c>
     </row>
     <row r="594" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12556,21 +13081,21 @@
         <v>1641</v>
       </c>
       <c r="B597" s="2" t="s">
-        <v>496</v>
+        <v>1642</v>
       </c>
       <c r="C597" s="2" t="s">
-        <v>497</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="598" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A598" s="2" t="s">
-        <v>1642</v>
+        <v>1644</v>
       </c>
       <c r="B598" s="2" t="s">
-        <v>1643</v>
+        <v>282</v>
       </c>
       <c r="C598" s="2" t="s">
-        <v>1644</v>
+        <v>283</v>
       </c>
     </row>
     <row r="599" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12622,21 +13147,21 @@
         <v>1657</v>
       </c>
       <c r="B603" s="2" t="s">
-        <v>19</v>
+        <v>1658</v>
       </c>
       <c r="C603" s="2" t="s">
-        <v>20</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="604" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A604" s="2" t="s">
-        <v>1658</v>
+        <v>1660</v>
       </c>
       <c r="B604" s="2" t="s">
-        <v>1659</v>
+        <v>514</v>
       </c>
       <c r="C604" s="2" t="s">
-        <v>1660</v>
+        <v>515</v>
       </c>
     </row>
     <row r="605" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12699,351 +13224,351 @@
         <v>1676</v>
       </c>
       <c r="B610" s="2" t="s">
-        <v>1677</v>
+        <v>19</v>
       </c>
       <c r="C610" s="2" t="s">
-        <v>1678</v>
+        <v>20</v>
       </c>
     </row>
     <row r="611" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A611" s="2" t="s">
+        <v>1677</v>
+      </c>
+      <c r="B611" s="2" t="s">
+        <v>1678</v>
+      </c>
+      <c r="C611" s="2" t="s">
         <v>1679</v>
-      </c>
-      <c r="B611" s="2" t="s">
-        <v>1680</v>
-      </c>
-      <c r="C611" s="2" t="s">
-        <v>1681</v>
       </c>
     </row>
     <row r="612" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A612" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="B612" s="2" t="s">
+        <v>1681</v>
+      </c>
+      <c r="C612" s="2" t="s">
         <v>1682</v>
-      </c>
-      <c r="B612" s="2" t="s">
-        <v>1683</v>
-      </c>
-      <c r="C612" s="2" t="s">
-        <v>1684</v>
       </c>
     </row>
     <row r="613" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A613" s="2" t="s">
+        <v>1683</v>
+      </c>
+      <c r="B613" s="2" t="s">
+        <v>1684</v>
+      </c>
+      <c r="C613" s="2" t="s">
         <v>1685</v>
-      </c>
-      <c r="B613" s="2" t="s">
-        <v>1686</v>
-      </c>
-      <c r="C613" s="2" t="s">
-        <v>1687</v>
       </c>
     </row>
     <row r="614" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A614" s="2" t="s">
+        <v>1686</v>
+      </c>
+      <c r="B614" s="2" t="s">
+        <v>1687</v>
+      </c>
+      <c r="C614" s="2" t="s">
         <v>1688</v>
-      </c>
-      <c r="B614" s="2" t="s">
-        <v>1689</v>
-      </c>
-      <c r="C614" s="2" t="s">
-        <v>1690</v>
       </c>
     </row>
     <row r="615" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A615" s="2" t="s">
+        <v>1689</v>
+      </c>
+      <c r="B615" s="2" t="s">
+        <v>1690</v>
+      </c>
+      <c r="C615" s="2" t="s">
         <v>1691</v>
-      </c>
-      <c r="B615" s="2" t="s">
-        <v>1692</v>
-      </c>
-      <c r="C615" s="2" t="s">
-        <v>1693</v>
       </c>
     </row>
     <row r="616" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A616" s="2" t="s">
+        <v>1692</v>
+      </c>
+      <c r="B616" s="2" t="s">
+        <v>1693</v>
+      </c>
+      <c r="C616" s="2" t="s">
         <v>1694</v>
-      </c>
-      <c r="B616" s="2" t="s">
-        <v>697</v>
-      </c>
-      <c r="C616" s="2" t="s">
-        <v>1695</v>
       </c>
     </row>
     <row r="617" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A617" s="2" t="s">
+        <v>1695</v>
+      </c>
+      <c r="B617" s="2" t="s">
         <v>1696</v>
       </c>
-      <c r="B617" s="2" t="s">
+      <c r="C617" s="2" t="s">
         <v>1697</v>
-      </c>
-      <c r="C617" s="2" t="s">
-        <v>1698</v>
       </c>
     </row>
     <row r="618" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A618" s="2" t="s">
+        <v>1698</v>
+      </c>
+      <c r="B618" s="2" t="s">
         <v>1699</v>
       </c>
-      <c r="B618" s="2" t="s">
+      <c r="C618" s="2" t="s">
         <v>1700</v>
-      </c>
-      <c r="C618" s="2" t="s">
-        <v>1701</v>
       </c>
     </row>
     <row r="619" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A619" s="2" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B619" s="2" t="s">
         <v>1702</v>
       </c>
-      <c r="B619" s="2" t="s">
+      <c r="C619" s="2" t="s">
         <v>1703</v>
-      </c>
-      <c r="C619" s="2" t="s">
-        <v>1704</v>
       </c>
     </row>
     <row r="620" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A620" s="2" t="s">
+        <v>1704</v>
+      </c>
+      <c r="B620" s="2" t="s">
         <v>1705</v>
       </c>
-      <c r="B620" s="2" t="s">
+      <c r="C620" s="2" t="s">
         <v>1706</v>
-      </c>
-      <c r="C620" s="2" t="s">
-        <v>1707</v>
       </c>
     </row>
     <row r="621" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A621" s="2" t="s">
+        <v>1707</v>
+      </c>
+      <c r="B621" s="2" t="s">
         <v>1708</v>
       </c>
-      <c r="B621" s="2" t="s">
+      <c r="C621" s="2" t="s">
         <v>1709</v>
-      </c>
-      <c r="C621" s="2" t="s">
-        <v>1710</v>
       </c>
     </row>
     <row r="622" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A622" s="2" t="s">
+        <v>1710</v>
+      </c>
+      <c r="B622" s="2" t="s">
         <v>1711</v>
       </c>
-      <c r="B622" s="2" t="s">
+      <c r="C622" s="2" t="s">
         <v>1712</v>
-      </c>
-      <c r="C622" s="2" t="s">
-        <v>1713</v>
       </c>
     </row>
     <row r="623" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A623" s="2" t="s">
+        <v>1713</v>
+      </c>
+      <c r="B623" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="C623" s="2" t="s">
         <v>1714</v>
-      </c>
-      <c r="B623" s="2" t="s">
-        <v>1715</v>
-      </c>
-      <c r="C623" s="2" t="s">
-        <v>1716</v>
       </c>
     </row>
     <row r="624" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A624" s="2" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B624" s="2" t="s">
+        <v>1716</v>
+      </c>
+      <c r="C624" s="2" t="s">
         <v>1717</v>
-      </c>
-      <c r="B624" s="2" t="s">
-        <v>1718</v>
-      </c>
-      <c r="C624" s="2" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="625" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A625" s="2" t="s">
+        <v>1718</v>
+      </c>
+      <c r="B625" s="2" t="s">
         <v>1719</v>
       </c>
-      <c r="B625" s="2" t="s">
+      <c r="C625" s="2" t="s">
         <v>1720</v>
-      </c>
-      <c r="C625" s="2" t="s">
-        <v>1721</v>
       </c>
     </row>
     <row r="626" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A626" s="2" t="s">
+        <v>1721</v>
+      </c>
+      <c r="B626" s="2" t="s">
         <v>1722</v>
       </c>
-      <c r="B626" s="2" t="s">
+      <c r="C626" s="2" t="s">
         <v>1723</v>
-      </c>
-      <c r="C626" s="2" t="s">
-        <v>1724</v>
       </c>
     </row>
     <row r="627" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A627" s="2" t="s">
+        <v>1724</v>
+      </c>
+      <c r="B627" s="2" t="s">
         <v>1725</v>
       </c>
-      <c r="B627" s="2" t="s">
-        <v>258</v>
-      </c>
       <c r="C627" s="2" t="s">
-        <v>259</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="628" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A628" s="2" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="B628" s="2" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="C628" s="2" t="s">
-        <v>165</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="629" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A629" s="2" t="s">
-        <v>1728</v>
+        <v>1730</v>
       </c>
       <c r="B629" s="2" t="s">
-        <v>1729</v>
+        <v>1731</v>
       </c>
       <c r="C629" s="2" t="s">
-        <v>1730</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="630" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A630" s="2" t="s">
-        <v>1731</v>
+        <v>1733</v>
       </c>
       <c r="B630" s="2" t="s">
-        <v>1732</v>
+        <v>1734</v>
       </c>
       <c r="C630" s="2" t="s">
-        <v>437</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="631" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A631" s="2" t="s">
-        <v>1733</v>
+        <v>1736</v>
       </c>
       <c r="B631" s="2" t="s">
-        <v>1734</v>
+        <v>1737</v>
       </c>
       <c r="C631" s="2" t="s">
-        <v>1735</v>
+        <v>455</v>
       </c>
     </row>
     <row r="632" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A632" s="2" t="s">
-        <v>1736</v>
+        <v>1738</v>
       </c>
       <c r="B632" s="2" t="s">
-        <v>782</v>
+        <v>1739</v>
       </c>
       <c r="C632" s="2" t="s">
-        <v>783</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="633" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A633" s="2" t="s">
-        <v>1737</v>
+        <v>1741</v>
       </c>
       <c r="B633" s="2" t="s">
-        <v>4</v>
+        <v>1742</v>
       </c>
       <c r="C633" s="2" t="s">
-        <v>5</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="634" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A634" s="2" t="s">
-        <v>1738</v>
+        <v>1744</v>
       </c>
       <c r="B634" s="2" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="C634" s="2" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
     </row>
     <row r="635" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A635" s="2" t="s">
-        <v>1739</v>
+        <v>1745</v>
       </c>
       <c r="B635" s="2" t="s">
-        <v>1734</v>
+        <v>1746</v>
       </c>
       <c r="C635" s="2" t="s">
-        <v>1735</v>
+        <v>183</v>
       </c>
     </row>
     <row r="636" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A636" s="2" t="s">
-        <v>1740</v>
+        <v>1747</v>
       </c>
       <c r="B636" s="2" t="s">
-        <v>1741</v>
+        <v>1748</v>
       </c>
       <c r="C636" s="2" t="s">
-        <v>1742</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="637" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A637" s="2" t="s">
-        <v>1743</v>
+        <v>1750</v>
       </c>
       <c r="B637" s="2" t="s">
-        <v>1744</v>
+        <v>1751</v>
       </c>
       <c r="C637" s="2" t="s">
-        <v>1745</v>
+        <v>455</v>
       </c>
     </row>
     <row r="638" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A638" s="2" t="s">
-        <v>1746</v>
+        <v>1752</v>
       </c>
       <c r="B638" s="2" t="s">
-        <v>1747</v>
+        <v>1753</v>
       </c>
       <c r="C638" s="2" t="s">
-        <v>1748</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="639" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A639" s="2" t="s">
-        <v>1749</v>
+        <v>1755</v>
       </c>
       <c r="B639" s="2" t="s">
-        <v>1750</v>
+        <v>798</v>
       </c>
       <c r="C639" s="2" t="s">
-        <v>1751</v>
+        <v>799</v>
       </c>
     </row>
     <row r="640" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A640" s="2" t="s">
-        <v>1752</v>
+        <v>1756</v>
       </c>
       <c r="B640" s="2" t="s">
-        <v>1753</v>
+        <v>4</v>
       </c>
       <c r="C640" s="2" t="s">
-        <v>1754</v>
+        <v>5</v>
       </c>
     </row>
     <row r="641" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A641" s="2" t="s">
-        <v>1755</v>
+        <v>1757</v>
       </c>
       <c r="B641" s="2" t="s">
-        <v>1756</v>
+        <v>282</v>
       </c>
       <c r="C641" s="2" t="s">
-        <v>1757</v>
+        <v>283</v>
       </c>
     </row>
     <row r="642" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13051,32 +13576,32 @@
         <v>1758</v>
       </c>
       <c r="B642" s="2" t="s">
-        <v>1759</v>
+        <v>1753</v>
       </c>
       <c r="C642" s="2" t="s">
-        <v>1760</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="643" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A643" s="2" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B643" s="2" t="s">
+        <v>1760</v>
+      </c>
+      <c r="C643" s="2" t="s">
         <v>1761</v>
-      </c>
-      <c r="B643" s="2" t="s">
-        <v>1762</v>
-      </c>
-      <c r="C643" s="2" t="s">
-        <v>1763</v>
       </c>
     </row>
     <row r="644" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A644" s="2" t="s">
+        <v>1762</v>
+      </c>
+      <c r="B644" s="2" t="s">
+        <v>1763</v>
+      </c>
+      <c r="C644" s="2" t="s">
         <v>1764</v>
-      </c>
-      <c r="B644" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C644" s="2" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="645" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13084,362 +13609,362 @@
         <v>1765</v>
       </c>
       <c r="B645" s="2" t="s">
-        <v>13</v>
+        <v>1766</v>
       </c>
       <c r="C645" s="2" t="s">
-        <v>14</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="646" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A646" s="2" t="s">
-        <v>1766</v>
+        <v>1768</v>
       </c>
       <c r="B646" s="2" t="s">
-        <v>16</v>
+        <v>1769</v>
       </c>
       <c r="C646" s="2" t="s">
-        <v>17</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="647" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A647" s="2" t="s">
-        <v>1767</v>
+        <v>1771</v>
       </c>
       <c r="B647" s="2" t="s">
-        <v>1768</v>
+        <v>1772</v>
       </c>
       <c r="C647" s="2" t="s">
-        <v>1769</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="648" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A648" s="2" t="s">
-        <v>1770</v>
+        <v>1774</v>
       </c>
       <c r="B648" s="2" t="s">
-        <v>1771</v>
+        <v>1775</v>
       </c>
       <c r="C648" s="2" t="s">
-        <v>1772</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="649" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A649" s="2" t="s">
-        <v>1773</v>
+        <v>1777</v>
       </c>
       <c r="B649" s="2" t="s">
-        <v>1774</v>
+        <v>1778</v>
       </c>
       <c r="C649" s="2" t="s">
-        <v>1775</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="650" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A650" s="2" t="s">
-        <v>1776</v>
+        <v>1780</v>
       </c>
       <c r="B650" s="2" t="s">
-        <v>1777</v>
+        <v>1781</v>
       </c>
       <c r="C650" s="2" t="s">
-        <v>1778</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="651" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A651" s="2" t="s">
-        <v>1779</v>
+        <v>1783</v>
       </c>
       <c r="B651" s="2" t="s">
-        <v>1680</v>
+        <v>19</v>
       </c>
       <c r="C651" s="2" t="s">
-        <v>1681</v>
+        <v>20</v>
       </c>
     </row>
     <row r="652" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A652" s="2" t="s">
-        <v>1780</v>
+        <v>1784</v>
       </c>
       <c r="B652" s="2" t="s">
-        <v>1683</v>
+        <v>13</v>
       </c>
       <c r="C652" s="2" t="s">
-        <v>1684</v>
+        <v>14</v>
       </c>
     </row>
     <row r="653" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A653" s="2" t="s">
-        <v>1781</v>
+        <v>1785</v>
       </c>
       <c r="B653" s="2" t="s">
-        <v>1782</v>
+        <v>16</v>
       </c>
       <c r="C653" s="2" t="s">
-        <v>1192</v>
+        <v>17</v>
       </c>
     </row>
     <row r="654" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A654" s="2" t="s">
-        <v>1783</v>
+        <v>1786</v>
       </c>
       <c r="B654" s="2" t="s">
-        <v>1784</v>
+        <v>1787</v>
       </c>
       <c r="C654" s="2" t="s">
-        <v>1785</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="655" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A655" s="2" t="s">
-        <v>1786</v>
+        <v>1789</v>
       </c>
       <c r="B655" s="2" t="s">
-        <v>1038</v>
+        <v>1790</v>
       </c>
       <c r="C655" s="2" t="s">
-        <v>1039</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="656" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A656" s="2" t="s">
-        <v>1787</v>
+        <v>1792</v>
       </c>
       <c r="B656" s="2" t="s">
-        <v>1788</v>
+        <v>1793</v>
       </c>
       <c r="C656" s="2" t="s">
-        <v>1693</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="657" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A657" s="2" t="s">
-        <v>1789</v>
+        <v>1795</v>
       </c>
       <c r="B657" s="2" t="s">
-        <v>697</v>
+        <v>1796</v>
       </c>
       <c r="C657" s="2" t="s">
-        <v>1695</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="658" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A658" s="2" t="s">
-        <v>1790</v>
+        <v>1798</v>
       </c>
       <c r="B658" s="2" t="s">
-        <v>1791</v>
+        <v>1699</v>
       </c>
       <c r="C658" s="2" t="s">
-        <v>1792</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="659" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A659" s="2" t="s">
-        <v>1793</v>
+        <v>1799</v>
       </c>
       <c r="B659" s="2" t="s">
-        <v>1794</v>
+        <v>1702</v>
       </c>
       <c r="C659" s="2" t="s">
-        <v>1785</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="660" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A660" s="2" t="s">
-        <v>1795</v>
+        <v>1800</v>
       </c>
       <c r="B660" s="2" t="s">
-        <v>766</v>
+        <v>1801</v>
       </c>
       <c r="C660" s="2" t="s">
-        <v>1796</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="661" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A661" s="2" t="s">
-        <v>1797</v>
+        <v>1802</v>
       </c>
       <c r="B661" s="2" t="s">
-        <v>778</v>
+        <v>1803</v>
       </c>
       <c r="C661" s="2" t="s">
-        <v>1798</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="662" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A662" s="2" t="s">
-        <v>1799</v>
+        <v>1805</v>
       </c>
       <c r="B662" s="2" t="s">
-        <v>499</v>
+        <v>1054</v>
       </c>
       <c r="C662" s="2" t="s">
-        <v>437</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="663" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A663" s="2" t="s">
-        <v>1800</v>
+        <v>1806</v>
       </c>
       <c r="B663" s="2" t="s">
-        <v>782</v>
+        <v>1807</v>
       </c>
       <c r="C663" s="2" t="s">
-        <v>783</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="664" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A664" s="2" t="s">
-        <v>1801</v>
+        <v>1808</v>
       </c>
       <c r="B664" s="2" t="s">
-        <v>264</v>
+        <v>713</v>
       </c>
       <c r="C664" s="2" t="s">
-        <v>265</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="665" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A665" s="2" t="s">
-        <v>1802</v>
+        <v>1809</v>
       </c>
       <c r="B665" s="2" t="s">
-        <v>1803</v>
+        <v>1810</v>
       </c>
       <c r="C665" s="2" t="s">
-        <v>1804</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="666" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A666" s="2" t="s">
-        <v>1805</v>
+        <v>1812</v>
       </c>
       <c r="B666" s="2" t="s">
-        <v>1806</v>
+        <v>1813</v>
       </c>
       <c r="C666" s="2" t="s">
-        <v>1807</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="667" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A667" s="2" t="s">
-        <v>1808</v>
+        <v>1814</v>
       </c>
       <c r="B667" s="2" t="s">
-        <v>1809</v>
+        <v>782</v>
       </c>
       <c r="C667" s="2" t="s">
-        <v>1810</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="668" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A668" s="2" t="s">
-        <v>1811</v>
+        <v>1816</v>
       </c>
       <c r="B668" s="2" t="s">
-        <v>810</v>
+        <v>794</v>
       </c>
       <c r="C668" s="2" t="s">
-        <v>811</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="669" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A669" s="2" t="s">
-        <v>1812</v>
+        <v>1818</v>
       </c>
       <c r="B669" s="2" t="s">
-        <v>778</v>
+        <v>517</v>
       </c>
       <c r="C669" s="2" t="s">
-        <v>1798</v>
+        <v>455</v>
       </c>
     </row>
     <row r="670" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A670" s="2" t="s">
-        <v>1813</v>
+        <v>1819</v>
       </c>
       <c r="B670" s="2" t="s">
-        <v>814</v>
+        <v>798</v>
       </c>
       <c r="C670" s="2" t="s">
-        <v>815</v>
+        <v>799</v>
       </c>
     </row>
     <row r="671" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A671" s="2" t="s">
-        <v>1814</v>
+        <v>1820</v>
       </c>
       <c r="B671" s="2" t="s">
-        <v>1815</v>
+        <v>282</v>
       </c>
       <c r="C671" s="2" t="s">
-        <v>1816</v>
+        <v>283</v>
       </c>
     </row>
     <row r="672" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A672" s="2" t="s">
-        <v>1817</v>
+        <v>1821</v>
       </c>
       <c r="B672" s="2" t="s">
-        <v>820</v>
+        <v>1822</v>
       </c>
       <c r="C672" s="2" t="s">
-        <v>1818</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="673" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A673" s="2" t="s">
-        <v>1819</v>
+        <v>1824</v>
       </c>
       <c r="B673" s="2" t="s">
-        <v>1820</v>
+        <v>1825</v>
       </c>
       <c r="C673" s="2" t="s">
-        <v>1821</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="674" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A674" s="2" t="s">
-        <v>1822</v>
+        <v>1827</v>
       </c>
       <c r="B674" s="2" t="s">
-        <v>826</v>
+        <v>1828</v>
       </c>
       <c r="C674" s="2" t="s">
-        <v>1823</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="675" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A675" s="2" t="s">
-        <v>1824</v>
+        <v>1830</v>
       </c>
       <c r="B675" s="2" t="s">
-        <v>1825</v>
+        <v>826</v>
       </c>
       <c r="C675" s="2" t="s">
-        <v>1826</v>
+        <v>827</v>
       </c>
     </row>
     <row r="676" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A676" s="2" t="s">
-        <v>1827</v>
+        <v>1831</v>
       </c>
       <c r="B676" s="2" t="s">
-        <v>1828</v>
+        <v>794</v>
       </c>
       <c r="C676" s="2" t="s">
-        <v>1829</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="677" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A677" s="2" t="s">
-        <v>1830</v>
+        <v>1832</v>
       </c>
       <c r="B677" s="2" t="s">
-        <v>1831</v>
+        <v>830</v>
       </c>
       <c r="C677" s="2" t="s">
-        <v>1832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="678" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13447,153 +13972,879 @@
         <v>1833</v>
       </c>
       <c r="B678" s="2" t="s">
-        <v>678</v>
+        <v>1834</v>
       </c>
       <c r="C678" s="2" t="s">
-        <v>679</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="679" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A679" s="2" t="s">
-        <v>1834</v>
+        <v>1836</v>
       </c>
       <c r="B679" s="2" t="s">
         <v>836</v>
       </c>
       <c r="C679" s="2" t="s">
-        <v>837</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="680" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A680" s="2" t="s">
-        <v>1835</v>
+        <v>1838</v>
       </c>
       <c r="B680" s="2" t="s">
-        <v>839</v>
+        <v>1839</v>
       </c>
       <c r="C680" s="2" t="s">
-        <v>1836</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="681" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A681" s="2" t="s">
-        <v>1837</v>
+        <v>1841</v>
       </c>
       <c r="B681" s="2" t="s">
         <v>842</v>
       </c>
       <c r="C681" s="2" t="s">
-        <v>1838</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="682" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A682" s="2" t="s">
-        <v>1839</v>
+        <v>1843</v>
       </c>
       <c r="B682" s="2" t="s">
-        <v>845</v>
+        <v>1844</v>
       </c>
       <c r="C682" s="2" t="s">
-        <v>1840</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="683" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A683" s="2" t="s">
-        <v>1841</v>
+        <v>1846</v>
       </c>
       <c r="B683" s="2" t="s">
-        <v>1842</v>
+        <v>1847</v>
       </c>
       <c r="C683" s="2" t="s">
-        <v>1843</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="684" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A684" s="2" t="s">
-        <v>1844</v>
+        <v>1849</v>
       </c>
       <c r="B684" s="2" t="s">
-        <v>1680</v>
+        <v>1850</v>
       </c>
       <c r="C684" s="2" t="s">
-        <v>1681</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="685" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A685" s="2" t="s">
-        <v>1845</v>
+        <v>1852</v>
       </c>
       <c r="B685" s="2" t="s">
-        <v>1683</v>
+        <v>694</v>
       </c>
       <c r="C685" s="2" t="s">
-        <v>1684</v>
+        <v>695</v>
       </c>
     </row>
     <row r="686" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A686" s="2" t="s">
-        <v>1846</v>
+        <v>1853</v>
       </c>
       <c r="B686" s="2" t="s">
-        <v>1847</v>
+        <v>852</v>
       </c>
       <c r="C686" s="2" t="s">
-        <v>1848</v>
+        <v>853</v>
       </c>
     </row>
     <row r="687" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A687" s="2" t="s">
-        <v>1849</v>
+        <v>1854</v>
       </c>
       <c r="B687" s="2" t="s">
-        <v>1850</v>
+        <v>855</v>
       </c>
       <c r="C687" s="2" t="s">
-        <v>1851</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="688" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A688" s="2" t="s">
-        <v>1852</v>
+        <v>1856</v>
       </c>
       <c r="B688" s="2" t="s">
-        <v>1853</v>
+        <v>858</v>
       </c>
       <c r="C688" s="2" t="s">
-        <v>1854</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="689" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A689" s="2" t="s">
-        <v>1855</v>
+        <v>1858</v>
       </c>
       <c r="B689" s="2" t="s">
-        <v>1856</v>
+        <v>861</v>
       </c>
       <c r="C689" s="2" t="s">
-        <v>1857</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="690" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A690" s="2" t="s">
-        <v>1858</v>
+        <v>1860</v>
       </c>
       <c r="B690" s="2" t="s">
-        <v>1859</v>
+        <v>1861</v>
       </c>
       <c r="C690" s="2" t="s">
-        <v>1860</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="691" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A691" s="2" t="s">
-        <v>1861</v>
+        <v>1863</v>
       </c>
       <c r="B691" s="2" t="s">
-        <v>1862</v>
+        <v>1699</v>
       </c>
       <c r="C691" s="2" t="s">
-        <v>1863</v>
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="692" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A692" s="2" t="s">
+        <v>1864</v>
+      </c>
+      <c r="B692" s="2" t="s">
+        <v>1702</v>
+      </c>
+      <c r="C692" s="2" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="693" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A693" s="2" t="s">
+        <v>1865</v>
+      </c>
+      <c r="B693" s="2" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C693" s="2" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="694" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A694" s="2" t="s">
+        <v>1868</v>
+      </c>
+      <c r="B694" s="2" t="s">
+        <v>1869</v>
+      </c>
+      <c r="C694" s="2" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="695" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A695" s="2" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B695" s="2" t="s">
+        <v>1872</v>
+      </c>
+      <c r="C695" s="2" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="696" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A696" s="2" t="s">
+        <v>1874</v>
+      </c>
+      <c r="B696" s="2" t="s">
+        <v>1875</v>
+      </c>
+      <c r="C696" s="2" t="s">
+        <v>1876</v>
+      </c>
+    </row>
+    <row r="697" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A697" s="2" t="s">
+        <v>1877</v>
+      </c>
+      <c r="B697" s="2" t="s">
+        <v>1878</v>
+      </c>
+      <c r="C697" s="2" t="s">
+        <v>1879</v>
+      </c>
+    </row>
+    <row r="698" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A698" s="2" t="s">
+        <v>1880</v>
+      </c>
+      <c r="B698" s="2" t="s">
+        <v>1881</v>
+      </c>
+      <c r="C698" s="2" t="s">
+        <v>1882</v>
+      </c>
+    </row>
+    <row r="699" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A699" s="2" t="s">
+        <v>1883</v>
+      </c>
+      <c r="B699" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="C699" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="700" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A700" s="2" t="s">
+        <v>1884</v>
+      </c>
+      <c r="B700" s="2" t="s">
+        <v>1885</v>
+      </c>
+      <c r="C700" s="2" t="s">
+        <v>1886</v>
+      </c>
+    </row>
+    <row r="701" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A701" s="2" t="s">
+        <v>1887</v>
+      </c>
+      <c r="B701" s="2" t="s">
+        <v>1888</v>
+      </c>
+      <c r="C701" s="2" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="702" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A702" s="2" t="s">
+        <v>1890</v>
+      </c>
+      <c r="B702" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="C702" s="2" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="703" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A703" s="2" t="s">
+        <v>1891</v>
+      </c>
+      <c r="B703" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C703" s="2" t="s">
+        <v>1892</v>
+      </c>
+    </row>
+    <row r="704" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A704" s="2" t="s">
+        <v>1893</v>
+      </c>
+      <c r="B704" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="C704" s="2" t="s">
+        <v>1894</v>
+      </c>
+    </row>
+    <row r="705" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A705" s="2" t="s">
+        <v>1895</v>
+      </c>
+      <c r="B705" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="C705" s="2" t="s">
+        <v>1896</v>
+      </c>
+    </row>
+    <row r="706" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A706" s="2" t="s">
+        <v>1897</v>
+      </c>
+      <c r="B706" s="2" t="s">
+        <v>1898</v>
+      </c>
+      <c r="C706" s="2" t="s">
+        <v>1899</v>
+      </c>
+    </row>
+    <row r="707" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A707" s="2" t="s">
+        <v>1900</v>
+      </c>
+      <c r="B707" s="2" t="s">
+        <v>1901</v>
+      </c>
+      <c r="C707" s="2" t="s">
+        <v>1902</v>
+      </c>
+    </row>
+    <row r="708" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A708" s="2" t="s">
+        <v>1903</v>
+      </c>
+      <c r="B708" s="2" t="s">
+        <v>1904</v>
+      </c>
+      <c r="C708" s="2" t="s">
+        <v>1905</v>
+      </c>
+    </row>
+    <row r="709" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A709" s="2" t="s">
+        <v>1906</v>
+      </c>
+      <c r="B709" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="C709" s="2" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="710" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A710" s="2" t="s">
+        <v>1907</v>
+      </c>
+      <c r="B710" s="2" t="s">
+        <v>1908</v>
+      </c>
+      <c r="C710" s="2" t="s">
+        <v>1909</v>
+      </c>
+    </row>
+    <row r="711" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A711" s="2" t="s">
+        <v>1910</v>
+      </c>
+      <c r="B711" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="C711" s="2" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="712" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A712" s="2" t="s">
+        <v>1911</v>
+      </c>
+      <c r="B712" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="C712" s="2" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="713" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A713" s="2" t="s">
+        <v>1912</v>
+      </c>
+      <c r="B713" s="2" t="s">
+        <v>1913</v>
+      </c>
+      <c r="C713" s="2" t="s">
+        <v>1914</v>
+      </c>
+    </row>
+    <row r="714" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A714" s="2" t="s">
+        <v>1915</v>
+      </c>
+      <c r="B714" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="C714" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="715" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A715" s="2" t="s">
+        <v>1916</v>
+      </c>
+      <c r="B715" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="C715" s="2" t="s">
+        <v>1917</v>
+      </c>
+    </row>
+    <row r="716" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A716" s="2" t="s">
+        <v>1918</v>
+      </c>
+      <c r="B716" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="C716" s="2" t="s">
+        <v>1919</v>
+      </c>
+    </row>
+    <row r="717" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A717" s="2" t="s">
+        <v>1920</v>
+      </c>
+      <c r="B717" s="2" t="s">
+        <v>1921</v>
+      </c>
+      <c r="C717" s="2" t="s">
+        <v>1922</v>
+      </c>
+    </row>
+    <row r="718" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A718" s="2" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B718" s="2" t="s">
+        <v>1924</v>
+      </c>
+      <c r="C718" s="2" t="s">
+        <v>1925</v>
+      </c>
+    </row>
+    <row r="719" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A719" s="2" t="s">
+        <v>1926</v>
+      </c>
+      <c r="B719" s="2" t="s">
+        <v>1927</v>
+      </c>
+      <c r="C719" s="2" t="s">
+        <v>1928</v>
+      </c>
+    </row>
+    <row r="720" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A720" s="2" t="s">
+        <v>1929</v>
+      </c>
+      <c r="B720" s="2" t="s">
+        <v>1930</v>
+      </c>
+      <c r="C720" s="2" t="s">
+        <v>1931</v>
+      </c>
+    </row>
+    <row r="721" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A721" s="2" t="s">
+        <v>1932</v>
+      </c>
+      <c r="B721" s="2" t="s">
+        <v>1933</v>
+      </c>
+      <c r="C721" s="2" t="s">
+        <v>1934</v>
+      </c>
+    </row>
+    <row r="722" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A722" s="2" t="s">
+        <v>1935</v>
+      </c>
+      <c r="B722" s="2" t="s">
+        <v>1936</v>
+      </c>
+      <c r="C722" s="2" t="s">
+        <v>1937</v>
+      </c>
+    </row>
+    <row r="723" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A723" s="2" t="s">
+        <v>1938</v>
+      </c>
+      <c r="B723" s="2" t="s">
+        <v>1939</v>
+      </c>
+      <c r="C723" s="2" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="724" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A724" s="2" t="s">
+        <v>1941</v>
+      </c>
+      <c r="B724" s="2" t="s">
+        <v>1942</v>
+      </c>
+      <c r="C724" s="2" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="725" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A725" s="2" t="s">
+        <v>1944</v>
+      </c>
+      <c r="B725" s="2" t="s">
+        <v>1945</v>
+      </c>
+      <c r="C725" s="2" t="s">
+        <v>1946</v>
+      </c>
+    </row>
+    <row r="726" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A726" s="2" t="s">
+        <v>1947</v>
+      </c>
+      <c r="B726" s="2" t="s">
+        <v>1948</v>
+      </c>
+      <c r="C726" s="2" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="727" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A727" s="2" t="s">
+        <v>1950</v>
+      </c>
+      <c r="B727" s="2" t="s">
+        <v>1951</v>
+      </c>
+      <c r="C727" s="2" t="s">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="728" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A728" s="2" t="s">
+        <v>1953</v>
+      </c>
+      <c r="B728" s="2" t="s">
+        <v>1954</v>
+      </c>
+      <c r="C728" s="2" t="s">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="729" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A729" s="2" t="s">
+        <v>1956</v>
+      </c>
+      <c r="B729" s="2" t="s">
+        <v>1957</v>
+      </c>
+      <c r="C729" s="2" t="s">
+        <v>1637</v>
+      </c>
+    </row>
+    <row r="730" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A730" s="2" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B730" s="2" t="s">
+        <v>1959</v>
+      </c>
+      <c r="C730" s="2" t="s">
+        <v>1960</v>
+      </c>
+    </row>
+    <row r="731" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A731" s="2" t="s">
+        <v>1961</v>
+      </c>
+      <c r="B731" s="2" t="s">
+        <v>1962</v>
+      </c>
+      <c r="C731" s="2" t="s">
+        <v>1963</v>
+      </c>
+    </row>
+    <row r="732" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A732" s="2" t="s">
+        <v>1964</v>
+      </c>
+      <c r="B732" s="2" t="s">
+        <v>1965</v>
+      </c>
+      <c r="C732" s="2" t="s">
+        <v>1966</v>
+      </c>
+    </row>
+    <row r="733" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A733" s="2" t="s">
+        <v>1967</v>
+      </c>
+      <c r="B733" s="2" t="s">
+        <v>1968</v>
+      </c>
+      <c r="C733" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="734" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A734" s="2" t="s">
+        <v>1969</v>
+      </c>
+      <c r="B734" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="C734" s="2" t="s">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="735" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A735" s="2" t="s">
+        <v>1972</v>
+      </c>
+      <c r="B735" s="2" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C735" s="2" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="736" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A736" s="2" t="s">
+        <v>1975</v>
+      </c>
+      <c r="B736" s="2" t="s">
+        <v>1976</v>
+      </c>
+      <c r="C736" s="2" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="737" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A737" s="2" t="s">
+        <v>1978</v>
+      </c>
+      <c r="B737" s="2" t="s">
+        <v>1979</v>
+      </c>
+      <c r="C737" s="2" t="s">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="738" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A738" s="2" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B738" s="2" t="s">
+        <v>1982</v>
+      </c>
+      <c r="C738" s="2" t="s">
+        <v>1983</v>
+      </c>
+    </row>
+    <row r="739" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A739" s="2" t="s">
+        <v>1984</v>
+      </c>
+      <c r="B739" s="2" t="s">
+        <v>1985</v>
+      </c>
+      <c r="C739" s="2" t="s">
+        <v>1986</v>
+      </c>
+    </row>
+    <row r="740" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A740" s="2" t="s">
+        <v>1987</v>
+      </c>
+      <c r="B740" s="2" t="s">
+        <v>1988</v>
+      </c>
+      <c r="C740" s="2" t="s">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="741" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A741" s="2" t="s">
+        <v>1990</v>
+      </c>
+      <c r="B741" s="2" t="s">
+        <v>1991</v>
+      </c>
+      <c r="C741" s="2" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="742" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A742" s="2" t="s">
+        <v>1993</v>
+      </c>
+      <c r="B742" s="2" t="s">
+        <v>1994</v>
+      </c>
+      <c r="C742" s="2" t="s">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="743" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A743" s="2" t="s">
+        <v>1996</v>
+      </c>
+      <c r="B743" s="2" t="s">
+        <v>1997</v>
+      </c>
+      <c r="C743" s="2" t="s">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="744" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A744" s="2" t="s">
+        <v>1999</v>
+      </c>
+      <c r="B744" s="2" t="s">
+        <v>2000</v>
+      </c>
+      <c r="C744" s="2" t="s">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="745" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A745" s="2" t="s">
+        <v>2002</v>
+      </c>
+      <c r="B745" s="2" t="s">
+        <v>2003</v>
+      </c>
+      <c r="C745" s="2" t="s">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="746" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A746" s="2" t="s">
+        <v>2005</v>
+      </c>
+      <c r="B746" s="2" t="s">
+        <v>2006</v>
+      </c>
+      <c r="C746" s="2" t="s">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="747" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A747" s="2" t="s">
+        <v>2008</v>
+      </c>
+      <c r="B747" s="2" t="s">
+        <v>2009</v>
+      </c>
+      <c r="C747" s="2" t="s">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="748" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A748" s="2" t="s">
+        <v>2011</v>
+      </c>
+      <c r="B748" s="2" t="s">
+        <v>2012</v>
+      </c>
+      <c r="C748" s="2" t="s">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="749" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A749" s="2" t="s">
+        <v>2014</v>
+      </c>
+      <c r="B749" s="2" t="s">
+        <v>2015</v>
+      </c>
+      <c r="C749" s="2" t="s">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="750" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A750" s="2" t="s">
+        <v>2017</v>
+      </c>
+      <c r="B750" s="2" t="s">
+        <v>2018</v>
+      </c>
+      <c r="C750" s="2" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="751" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A751" s="2" t="s">
+        <v>2020</v>
+      </c>
+      <c r="B751" s="2" t="s">
+        <v>2021</v>
+      </c>
+      <c r="C751" s="2" t="s">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="752" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A752" s="2" t="s">
+        <v>2023</v>
+      </c>
+      <c r="B752" s="2" t="s">
+        <v>2024</v>
+      </c>
+      <c r="C752" s="2" t="s">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="753" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A753" s="2" t="s">
+        <v>2026</v>
+      </c>
+      <c r="B753" s="2" t="s">
+        <v>2027</v>
+      </c>
+      <c r="C753" s="2" t="s">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="754" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A754" s="2" t="s">
+        <v>2029</v>
+      </c>
+      <c r="B754" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C754" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="755" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A755" s="2" t="s">
+        <v>2030</v>
+      </c>
+      <c r="B755" s="2" t="s">
+        <v>2031</v>
+      </c>
+      <c r="C755" s="2" t="s">
+        <v>2032</v>
+      </c>
+    </row>
+    <row r="756" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A756" s="2" t="s">
+        <v>2033</v>
+      </c>
+      <c r="B756" s="2" t="s">
+        <v>2034</v>
+      </c>
+      <c r="C756" s="2" t="s">
+        <v>2035</v>
+      </c>
+    </row>
+    <row r="757" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A757" s="2" t="s">
+        <v>2036</v>
+      </c>
+      <c r="B757" s="2" t="s">
+        <v>2037</v>
+      </c>
+      <c r="C757" s="2" t="s">
+        <v>2038</v>
       </c>
     </row>
   </sheetData>

--- a/apps/workspace-web/i18n.xlsx
+++ b/apps/workspace-web/i18n.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2271" uniqueCount="2039">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2349" uniqueCount="2105">
   <si>
     <t>key</t>
   </si>
@@ -1516,6 +1516,60 @@
     <t>Buyers can download these files after payment</t>
   </si>
   <si>
+    <t>upload.coverImgLabel</t>
+  </si>
+  <si>
+    <t>封面圖</t>
+  </si>
+  <si>
+    <t>Cover image</t>
+  </si>
+  <si>
+    <t>upload.coverImgSub</t>
+  </si>
+  <si>
+    <t>選填。支援 JPG / PNG / GIF / WebP，最大 5 MB；未上傳時以下方色調封面呈現。</t>
+  </si>
+  <si>
+    <t>Optional. JPG / PNG / GIF / WebP, up to 5 MB; without one, the hue cover below is used.</t>
+  </si>
+  <si>
+    <t>upload.coverEmpty</t>
+  </si>
+  <si>
+    <t>點擊選擇封面圖</t>
+  </si>
+  <si>
+    <t>Click to choose a cover image</t>
+  </si>
+  <si>
+    <t>upload.coverUpload</t>
+  </si>
+  <si>
+    <t>上傳封面圖</t>
+  </si>
+  <si>
+    <t>Upload cover</t>
+  </si>
+  <si>
+    <t>upload.coverReplace</t>
+  </si>
+  <si>
+    <t>更換封面圖</t>
+  </si>
+  <si>
+    <t>Replace cover</t>
+  </si>
+  <si>
+    <t>upload.coverRemove</t>
+  </si>
+  <si>
+    <t>移除</t>
+  </si>
+  <si>
+    <t>Remove</t>
+  </si>
+  <si>
     <t>upload.coverHueLabel</t>
   </si>
   <si>
@@ -1528,10 +1582,10 @@
     <t>upload.coverHueSub</t>
   </si>
   <si>
-    <t>作品縮圖會用這個色調生成漸層封面。</t>
-  </si>
-  <si>
-    <t>Your thumbnail uses this hue to generate a gradient cover.</t>
+    <t>未上傳封面圖時以此色調生成封面；上傳後也會作為圖片載入前的底色。</t>
+  </si>
+  <si>
+    <t>Used to generate the cover when no image is set — and as the backdrop while the image loads.</t>
   </si>
   <si>
     <t>upload.confirmTitle</t>
@@ -1591,6 +1645,18 @@
     <t>{count} files · {size}</t>
   </si>
   <si>
+    <t>upload.revCover</t>
+  </si>
+  <si>
+    <t>upload.revCoverNone</t>
+  </si>
+  <si>
+    <t>使用色調封面</t>
+  </si>
+  <si>
+    <t>Hue cover</t>
+  </si>
+  <si>
     <t>upload.revBlurb</t>
   </si>
   <si>
@@ -1765,6 +1831,33 @@
     <t>upload.msgUploadFailed</t>
   </si>
   <si>
+    <t>upload.msgCoverType</t>
+  </si>
+  <si>
+    <t>封面圖僅支援 JPG / PNG / GIF / WebP。</t>
+  </si>
+  <si>
+    <t>Cover images must be JPG / PNG / GIF / WebP.</t>
+  </si>
+  <si>
+    <t>upload.msgCoverTooLarge</t>
+  </si>
+  <si>
+    <t>封面圖不得超過 5 MB。</t>
+  </si>
+  <si>
+    <t>Cover images must be 5 MB or smaller.</t>
+  </si>
+  <si>
+    <t>upload.msgCoverNotReady</t>
+  </si>
+  <si>
+    <t>封面圖上傳失敗，請重試或移除後再送出。</t>
+  </si>
+  <si>
+    <t>The cover upload failed — retry or remove it before submitting.</t>
+  </si>
+  <si>
     <t>upload.statusUploading</t>
   </si>
   <si>
@@ -2014,10 +2107,10 @@
     <t>storeSettings.appearanceDesc</t>
   </si>
   <si>
-    <t>橫幅與頭像會顯示在你的商店頁。點擊圖片即可更換，支援 JPG / PNG / GIF / WebP，單檔 5 MB 以內。</t>
-  </si>
-  <si>
-    <t>Your banner and avatar appear on your store page. Click an image to replace it — JPG / PNG / GIF / WebP, up to 5 MB each.</t>
+    <t>橫幅與頭像會顯示在你的商店頁。點擊圖片即可更換，支援 JPG / PNG / WebP，單檔 5 MB 以內。</t>
+  </si>
+  <si>
+    <t>Your banner and avatar appear on your store page. Click an image to replace it — JPG / PNG / WebP, up to 5 MB each.</t>
   </si>
   <si>
     <t>storeSettings.changeBanner</t>
@@ -2104,10 +2197,10 @@
     <t>storeSettings.msgInvalidType</t>
   </si>
   <si>
-    <t>僅支援 JPG / PNG / GIF / WebP 圖片。</t>
-  </si>
-  <si>
-    <t>Only JPG / PNG / GIF / WebP images are supported.</t>
+    <t>僅支援 JPG / PNG / WebP 圖片。</t>
+  </si>
+  <si>
+    <t>Only JPG / PNG / WebP images are supported.</t>
   </si>
   <si>
     <t>storeSettings.msgTooLarge</t>
@@ -2158,6 +2251,72 @@
     <t>Update failed</t>
   </si>
   <si>
+    <t>cropDialog.titleAvatar</t>
+  </si>
+  <si>
+    <t>裁切頭像</t>
+  </si>
+  <si>
+    <t>Crop avatar</t>
+  </si>
+  <si>
+    <t>cropDialog.titleBanner</t>
+  </si>
+  <si>
+    <t>裁切橫幅</t>
+  </si>
+  <si>
+    <t>Crop banner</t>
+  </si>
+  <si>
+    <t>cropDialog.hintAvatar</t>
+  </si>
+  <si>
+    <t>拖曳與縮放調整擷取範圍，圓形區域即為店面實際顯示的頭像。</t>
+  </si>
+  <si>
+    <t>Drag and zoom to choose the visible area — the circle is exactly what your store shows.</t>
+  </si>
+  <si>
+    <t>cropDialog.hintBanner</t>
+  </si>
+  <si>
+    <t>拖曳與縮放調整擷取範圍。手機與大螢幕只會顯示中央區域，重點內容請置於虛線框內。</t>
+  </si>
+  <si>
+    <t>Drag and zoom to choose the visible area. Phones and large screens only show the centre — keep key content inside the dashed box.</t>
+  </si>
+  <si>
+    <t>cropDialog.apply</t>
+  </si>
+  <si>
+    <t>套用</t>
+  </si>
+  <si>
+    <t>Apply</t>
+  </si>
+  <si>
+    <t>cropDialog.cancel</t>
+  </si>
+  <si>
+    <t>cropDialog.loadError</t>
+  </si>
+  <si>
+    <t>圖片載入失敗，請改用其他圖片。</t>
+  </si>
+  <si>
+    <t>Couldn’t load this image — please pick another file.</t>
+  </si>
+  <si>
+    <t>cropDialog.cropError</t>
+  </si>
+  <si>
+    <t>裁切失敗，請重試。</t>
+  </si>
+  <si>
+    <t>Cropping failed. Please try again.</t>
+  </si>
+  <si>
     <t>payouts.statusTitle</t>
   </si>
   <si>
@@ -5032,6 +5191,42 @@
     <t>"## " = section heading (auto numbered), "- " = list item; once activated a version becomes immutable — create a new draft instead</t>
   </si>
   <si>
+    <t>legalDocs.highlightsLabel</t>
+  </si>
+  <si>
+    <t>重點速覽</t>
+  </si>
+  <si>
+    <t>Highlights</t>
+  </si>
+  <si>
+    <t>legalDocs.highlightsPlaceholder</t>
+  </si>
+  <si>
+    <t>每行一則，格式「標題|描述」，例如：作品永遠是你的|上架不轉移著作權，你只授權平台展示與銷售你的作品。</t>
+  </si>
+  <si>
+    <t>One per line as "Title|Description", e.g. Your work stays yours|Listing never transfers copyright.</t>
+  </si>
+  <si>
+    <t>legalDocs.highlightsHint</t>
+  </si>
+  <si>
+    <t>選填；每行一則、以第一個「|」分隔標題與描述，最多 6 則。顯示於前台條款頁頂部的 30 秒摘要卡，留空則前台改用預設文案</t>
+  </si>
+  <si>
+    <t>Optional; one per line, split by the first "|", up to 6. Shown as the 30-second summary cards atop the public legal page; leave empty to fall back to the default copy</t>
+  </si>
+  <si>
+    <t>legalDocs.valHighlightsFormat</t>
+  </si>
+  <si>
+    <t>重點速覽每行須為「標題|描述」格式</t>
+  </si>
+  <si>
+    <t>Each highlight line must be in "Title|Description" format</t>
+  </si>
+  <si>
     <t>legalDocs.create</t>
   </si>
   <si>
@@ -5089,6 +5284,24 @@
     <t>After deactivation there will be no active version to display. Continue?</t>
   </si>
   <si>
+    <t>legalDocs.del</t>
+  </si>
+  <si>
+    <t>刪除草稿</t>
+  </si>
+  <si>
+    <t>Delete draft</t>
+  </si>
+  <si>
+    <t>legalDocs.deleteConfirm</t>
+  </si>
+  <si>
+    <t>確定刪除此草稿？啟用過的版本不受影響。</t>
+  </si>
+  <si>
+    <t>Delete this draft? Previously activated versions are not affected.</t>
+  </si>
+  <si>
     <t>legalDocs.valTitleRequired</t>
   </si>
   <si>
@@ -5176,6 +5389,15 @@
     <t>Version deactivated</t>
   </si>
   <si>
+    <t>legalDocs.msgDeleted</t>
+  </si>
+  <si>
+    <t>草稿已刪除</t>
+  </si>
+  <si>
+    <t>Draft deleted</t>
+  </si>
+  <si>
     <t>legalDocs.previewLabel</t>
   </si>
   <si>
@@ -5785,12 +6007,6 @@
     <t>productEdit.coverTitle</t>
   </si>
   <si>
-    <t>封面圖</t>
-  </si>
-  <si>
-    <t>Cover image</t>
-  </si>
-  <si>
     <t>productEdit.coverDesc</t>
   </si>
   <si>
@@ -5815,18 +6031,12 @@
     <t>上傳封面</t>
   </si>
   <si>
-    <t>Upload cover</t>
-  </si>
-  <si>
     <t>productEdit.coverReplace</t>
   </si>
   <si>
     <t>更換封面</t>
   </si>
   <si>
-    <t>Replace cover</t>
-  </si>
-  <si>
     <t>productEdit.coverRemove</t>
   </si>
   <si>
@@ -6022,19 +6232,7 @@
     <t>productEdit.msgCoverType</t>
   </si>
   <si>
-    <t>封面圖僅支援 JPG / PNG / GIF / WebP。</t>
-  </si>
-  <si>
-    <t>Cover images must be JPG / PNG / GIF / WebP.</t>
-  </si>
-  <si>
     <t>productEdit.msgCoverTooLarge</t>
-  </si>
-  <si>
-    <t>封面圖不得超過 5 MB。</t>
-  </si>
-  <si>
-    <t>Cover images must be 5 MB or smaller.</t>
   </si>
   <si>
     <t>productEdit.msgCoverUpdated</t>
@@ -6513,7 +6711,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C757"/>
+  <dimension ref="A1:C783"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -8464,95 +8662,95 @@
         <v>517</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>455</v>
+        <v>518</v>
       </c>
     </row>
     <row r="178" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>466</v>
+        <v>520</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>467</v>
+        <v>521</v>
       </c>
     </row>
     <row r="179" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>475</v>
+        <v>523</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>209</v>
+        <v>524</v>
       </c>
     </row>
     <row r="180" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
     </row>
     <row r="181" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
     </row>
     <row r="182" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
     </row>
     <row r="183" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>531</v>
+        <v>455</v>
       </c>
     </row>
     <row r="184" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>533</v>
+        <v>466</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>534</v>
+        <v>467</v>
       </c>
     </row>
     <row r="185" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>536</v>
+        <v>475</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>537</v>
+        <v>209</v>
       </c>
     </row>
     <row r="186" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8560,32 +8758,32 @@
         <v>538</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>22</v>
+        <v>539</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>23</v>
+        <v>540</v>
       </c>
     </row>
     <row r="187" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="188" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>543</v>
+        <v>502</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>544</v>
+        <v>503</v>
       </c>
     </row>
     <row r="189" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8626,120 +8824,120 @@
         <v>554</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>466</v>
+        <v>555</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="193" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="194" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>560</v>
+        <v>22</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>561</v>
+        <v>23</v>
       </c>
     </row>
     <row r="195" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="B195" s="2" t="s">
         <v>562</v>
       </c>
-      <c r="B195" s="2" t="s">
+      <c r="C195" s="2" t="s">
         <v>563</v>
-      </c>
-      <c r="C195" s="2" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="196" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="B196" s="2" t="s">
         <v>565</v>
       </c>
-      <c r="B196" s="2" t="s">
+      <c r="C196" s="2" t="s">
         <v>566</v>
-      </c>
-      <c r="C196" s="2" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="197" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="B197" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="B197" s="2" t="s">
+      <c r="C197" s="2" t="s">
         <v>569</v>
-      </c>
-      <c r="C197" s="2" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="198" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="B198" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="B198" s="2" t="s">
+      <c r="C198" s="2" t="s">
         <v>572</v>
-      </c>
-      <c r="C198" s="2" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="199" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="B199" s="2" t="s">
         <v>574</v>
       </c>
-      <c r="B199" s="2" t="s">
+      <c r="C199" s="2" t="s">
         <v>575</v>
-      </c>
-      <c r="C199" s="2" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="200" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="C200" s="2" t="s">
         <v>577</v>
-      </c>
-      <c r="B200" s="2" t="s">
-        <v>578</v>
-      </c>
-      <c r="C200" s="2" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="201" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="C201" s="2" t="s">
         <v>580</v>
-      </c>
-      <c r="B201" s="2" t="s">
-        <v>581</v>
-      </c>
-      <c r="C201" s="2" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="202" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="C202" s="2" t="s">
         <v>583</v>
-      </c>
-      <c r="B202" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C202" s="2" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="203" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8824,21 +9022,21 @@
         <v>605</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>606</v>
+        <v>175</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>607</v>
+        <v>176</v>
       </c>
     </row>
     <row r="211" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="C211" s="2" t="s">
         <v>608</v>
-      </c>
-      <c r="B211" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="C211" s="2" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="212" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8857,230 +9055,230 @@
         <v>612</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>191</v>
+        <v>613</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>192</v>
+        <v>614</v>
       </c>
     </row>
     <row r="214" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="215" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="216" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="217" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="218" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="219" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="220" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="221" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="222" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>334</v>
+        <v>194</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>335</v>
+        <v>194</v>
       </c>
     </row>
     <row r="223" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="224" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>337</v>
+        <v>191</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>338</v>
+        <v>192</v>
       </c>
     </row>
     <row r="225" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="226" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
     </row>
     <row r="227" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="228" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="229" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="230" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="231" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="232" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="233" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>667</v>
+        <v>334</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>668</v>
+        <v>335</v>
       </c>
     </row>
     <row r="234" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9099,54 +9297,54 @@
         <v>672</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>673</v>
+        <v>337</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>674</v>
+        <v>338</v>
       </c>
     </row>
     <row r="236" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="C236" s="2" t="s">
         <v>675</v>
-      </c>
-      <c r="B236" s="2" t="s">
-        <v>676</v>
-      </c>
-      <c r="C236" s="2" t="s">
-        <v>677</v>
       </c>
     </row>
     <row r="237" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="C237" s="2" t="s">
         <v>678</v>
-      </c>
-      <c r="B237" s="2" t="s">
-        <v>679</v>
-      </c>
-      <c r="C237" s="2" t="s">
-        <v>680</v>
       </c>
     </row>
     <row r="238" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="B238" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="C238" s="2" t="s">
         <v>681</v>
-      </c>
-      <c r="B238" s="2" t="s">
-        <v>682</v>
-      </c>
-      <c r="C238" s="2" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="239" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="B239" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="C239" s="2" t="s">
         <v>684</v>
-      </c>
-      <c r="B239" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="C239" s="2" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="240" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9154,142 +9352,142 @@
         <v>685</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>639</v>
+        <v>686</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>640</v>
+        <v>687</v>
       </c>
     </row>
     <row r="241" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>337</v>
+        <v>689</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>338</v>
+        <v>690</v>
       </c>
     </row>
     <row r="242" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
     </row>
     <row r="243" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
     </row>
     <row r="244" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
     </row>
     <row r="245" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
     </row>
     <row r="246" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
     </row>
     <row r="247" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
     </row>
     <row r="248" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
     </row>
     <row r="249" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>591</v>
+        <v>713</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>592</v>
+        <v>714</v>
       </c>
     </row>
     <row r="250" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
-        <v>709</v>
+        <v>715</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>710</v>
+        <v>334</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>711</v>
+        <v>335</v>
       </c>
     </row>
     <row r="251" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>713</v>
+        <v>670</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>714</v>
+        <v>671</v>
       </c>
     </row>
     <row r="252" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>716</v>
+        <v>337</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>717</v>
+        <v>338</v>
       </c>
     </row>
     <row r="253" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9374,241 +9572,241 @@
         <v>739</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>740</v>
+        <v>622</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>741</v>
+        <v>623</v>
       </c>
     </row>
     <row r="261" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="B261" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="C261" s="2" t="s">
         <v>742</v>
-      </c>
-      <c r="B261" s="2" t="s">
-        <v>743</v>
-      </c>
-      <c r="C261" s="2" t="s">
-        <v>744</v>
       </c>
     </row>
     <row r="262" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="B262" s="2" t="s">
+        <v>744</v>
+      </c>
+      <c r="C262" s="2" t="s">
         <v>745</v>
-      </c>
-      <c r="B262" s="2" t="s">
-        <v>746</v>
-      </c>
-      <c r="C262" s="2" t="s">
-        <v>747</v>
       </c>
     </row>
     <row r="263" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="B263" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="C263" s="2" t="s">
         <v>748</v>
-      </c>
-      <c r="B263" s="2" t="s">
-        <v>749</v>
-      </c>
-      <c r="C263" s="2" t="s">
-        <v>750</v>
       </c>
     </row>
     <row r="264" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="B264" s="2" t="s">
+        <v>750</v>
+      </c>
+      <c r="C264" s="2" t="s">
         <v>751</v>
-      </c>
-      <c r="B264" s="2" t="s">
-        <v>752</v>
-      </c>
-      <c r="C264" s="2" t="s">
-        <v>753</v>
       </c>
     </row>
     <row r="265" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
+        <v>752</v>
+      </c>
+      <c r="B265" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="C265" s="2" t="s">
         <v>754</v>
-      </c>
-      <c r="B265" s="2" t="s">
-        <v>755</v>
-      </c>
-      <c r="C265" s="2" t="s">
-        <v>756</v>
       </c>
     </row>
     <row r="266" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="B266" s="2" t="s">
+        <v>756</v>
+      </c>
+      <c r="C266" s="2" t="s">
         <v>757</v>
-      </c>
-      <c r="B266" s="2" t="s">
-        <v>758</v>
-      </c>
-      <c r="C266" s="2" t="s">
-        <v>759</v>
       </c>
     </row>
     <row r="267" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="B267" s="2" t="s">
+        <v>759</v>
+      </c>
+      <c r="C267" s="2" t="s">
         <v>760</v>
-      </c>
-      <c r="B267" s="2" t="s">
-        <v>761</v>
-      </c>
-      <c r="C267" s="2" t="s">
-        <v>762</v>
       </c>
     </row>
     <row r="268" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>764</v>
+        <v>22</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>765</v>
+        <v>23</v>
       </c>
     </row>
     <row r="269" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
     </row>
     <row r="270" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
     </row>
     <row r="271" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
     </row>
     <row r="272" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
     </row>
     <row r="273" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
     </row>
     <row r="274" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
     </row>
     <row r="275" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
     </row>
     <row r="276" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
     </row>
     <row r="277" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
     </row>
     <row r="278" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
     </row>
     <row r="279" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>517</v>
+        <v>793</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>455</v>
+        <v>794</v>
       </c>
     </row>
     <row r="280" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="B280" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="C280" s="2" t="s">
         <v>797</v>
-      </c>
-      <c r="B280" s="2" t="s">
-        <v>798</v>
-      </c>
-      <c r="C280" s="2" t="s">
-        <v>799</v>
       </c>
     </row>
     <row r="281" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="B281" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="C281" s="2" t="s">
         <v>800</v>
-      </c>
-      <c r="B281" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="C281" s="2" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="282" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9715,87 +9913,87 @@
         <v>828</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>794</v>
+        <v>829</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>795</v>
+        <v>830</v>
       </c>
     </row>
     <row r="292" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
     </row>
     <row r="293" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
     </row>
     <row r="294" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
     </row>
     <row r="295" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
     </row>
     <row r="296" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
     </row>
     <row r="297" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
     </row>
     <row r="298" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>848</v>
+        <v>535</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>849</v>
+        <v>455</v>
       </c>
     </row>
     <row r="299" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9803,21 +10001,21 @@
         <v>850</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>694</v>
+        <v>851</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>695</v>
+        <v>852</v>
       </c>
     </row>
     <row r="300" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>852</v>
+        <v>282</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>853</v>
+        <v>283</v>
       </c>
     </row>
     <row r="301" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9869,65 +10067,65 @@
         <v>866</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>52</v>
+        <v>867</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>53</v>
+        <v>868</v>
       </c>
     </row>
     <row r="306" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
     </row>
     <row r="307" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
     </row>
     <row r="308" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
     </row>
     <row r="309" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
     </row>
     <row r="310" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>880</v>
+        <v>847</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>881</v>
+        <v>848</v>
       </c>
     </row>
     <row r="311" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10012,183 +10210,183 @@
         <v>903</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>904</v>
+        <v>725</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>905</v>
+        <v>726</v>
       </c>
     </row>
     <row r="319" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
+        <v>904</v>
+      </c>
+      <c r="B319" s="2" t="s">
+        <v>905</v>
+      </c>
+      <c r="C319" s="2" t="s">
         <v>906</v>
-      </c>
-      <c r="B319" s="2" t="s">
-        <v>907</v>
-      </c>
-      <c r="C319" s="2" t="s">
-        <v>908</v>
       </c>
     </row>
     <row r="320" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
+        <v>907</v>
+      </c>
+      <c r="B320" s="2" t="s">
+        <v>908</v>
+      </c>
+      <c r="C320" s="2" t="s">
         <v>909</v>
-      </c>
-      <c r="B320" s="2" t="s">
-        <v>910</v>
-      </c>
-      <c r="C320" s="2" t="s">
-        <v>911</v>
       </c>
     </row>
     <row r="321" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
+        <v>910</v>
+      </c>
+      <c r="B321" s="2" t="s">
+        <v>911</v>
+      </c>
+      <c r="C321" s="2" t="s">
         <v>912</v>
-      </c>
-      <c r="B321" s="2" t="s">
-        <v>913</v>
-      </c>
-      <c r="C321" s="2" t="s">
-        <v>914</v>
       </c>
     </row>
     <row r="322" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
+        <v>913</v>
+      </c>
+      <c r="B322" s="2" t="s">
+        <v>914</v>
+      </c>
+      <c r="C322" s="2" t="s">
         <v>915</v>
-      </c>
-      <c r="B322" s="2" t="s">
-        <v>916</v>
-      </c>
-      <c r="C322" s="2" t="s">
-        <v>917</v>
       </c>
     </row>
     <row r="323" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
+        <v>916</v>
+      </c>
+      <c r="B323" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="C323" s="2" t="s">
         <v>918</v>
-      </c>
-      <c r="B323" s="2" t="s">
-        <v>919</v>
-      </c>
-      <c r="C323" s="2" t="s">
-        <v>919</v>
       </c>
     </row>
     <row r="324" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>416</v>
+        <v>52</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>417</v>
+        <v>53</v>
       </c>
     </row>
     <row r="325" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
+        <v>920</v>
+      </c>
+      <c r="B325" s="2" t="s">
         <v>921</v>
       </c>
-      <c r="B325" s="2" t="s">
+      <c r="C325" s="2" t="s">
         <v>922</v>
-      </c>
-      <c r="C325" s="2" t="s">
-        <v>923</v>
       </c>
     </row>
     <row r="326" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
+        <v>923</v>
+      </c>
+      <c r="B326" s="2" t="s">
         <v>924</v>
       </c>
-      <c r="B326" s="2" t="s">
+      <c r="C326" s="2" t="s">
         <v>925</v>
-      </c>
-      <c r="C326" s="2" t="s">
-        <v>926</v>
       </c>
     </row>
     <row r="327" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
+        <v>926</v>
+      </c>
+      <c r="B327" s="2" t="s">
         <v>927</v>
       </c>
-      <c r="B327" s="2" t="s">
+      <c r="C327" s="2" t="s">
         <v>928</v>
-      </c>
-      <c r="C327" s="2" t="s">
-        <v>929</v>
       </c>
     </row>
     <row r="328" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="B328" s="2" t="s">
         <v>930</v>
       </c>
-      <c r="B328" s="2" t="s">
+      <c r="C328" s="2" t="s">
         <v>931</v>
-      </c>
-      <c r="C328" s="2" t="s">
-        <v>932</v>
       </c>
     </row>
     <row r="329" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="B329" s="2" t="s">
         <v>933</v>
       </c>
-      <c r="B329" s="2" t="s">
+      <c r="C329" s="2" t="s">
         <v>934</v>
-      </c>
-      <c r="C329" s="2" t="s">
-        <v>935</v>
       </c>
     </row>
     <row r="330" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
+        <v>935</v>
+      </c>
+      <c r="B330" s="2" t="s">
         <v>936</v>
       </c>
-      <c r="B330" s="2" t="s">
+      <c r="C330" s="2" t="s">
         <v>937</v>
-      </c>
-      <c r="C330" s="2" t="s">
-        <v>938</v>
       </c>
     </row>
     <row r="331" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="B331" s="2" t="s">
         <v>939</v>
       </c>
-      <c r="B331" s="2" t="s">
+      <c r="C331" s="2" t="s">
         <v>940</v>
-      </c>
-      <c r="C331" s="2" t="s">
-        <v>941</v>
       </c>
     </row>
     <row r="332" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="B332" s="2" t="s">
         <v>942</v>
       </c>
-      <c r="B332" s="2" t="s">
+      <c r="C332" s="2" t="s">
         <v>943</v>
-      </c>
-      <c r="C332" s="2" t="s">
-        <v>944</v>
       </c>
     </row>
     <row r="333" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
+        <v>944</v>
+      </c>
+      <c r="B333" s="2" t="s">
         <v>945</v>
       </c>
-      <c r="B333" s="2" t="s">
+      <c r="C333" s="2" t="s">
         <v>946</v>
-      </c>
-      <c r="C333" s="2" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="334" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
+        <v>947</v>
+      </c>
+      <c r="B334" s="2" t="s">
         <v>948</v>
-      </c>
-      <c r="B334" s="2" t="s">
-        <v>949</v>
       </c>
       <c r="C334" s="2" t="s">
         <v>949</v>
@@ -10279,1335 +10477,1335 @@
         <v>972</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="343" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>975</v>
+        <v>416</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>976</v>
+        <v>417</v>
       </c>
     </row>
     <row r="344" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
     </row>
     <row r="345" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
     </row>
     <row r="346" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
     </row>
     <row r="347" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
     </row>
     <row r="348" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
     </row>
     <row r="349" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
     </row>
     <row r="350" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
     </row>
     <row r="351" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
     </row>
     <row r="352" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="353" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="354" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>1008</v>
+        <v>1004</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>1009</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="355" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
-        <v>1010</v>
+        <v>1006</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>1011</v>
+        <v>1007</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>1012</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="356" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
-        <v>1013</v>
+        <v>1009</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="357" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="358" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
-        <v>1019</v>
+        <v>1015</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>1020</v>
+        <v>1016</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>1021</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="359" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
-        <v>1022</v>
+        <v>1018</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>1023</v>
+        <v>1019</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>1024</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="360" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
-        <v>1025</v>
+        <v>1021</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>1026</v>
+        <v>1022</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="361" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
-        <v>1028</v>
+        <v>1024</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>1029</v>
+        <v>1025</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="362" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
-        <v>1031</v>
+        <v>1027</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>1032</v>
+        <v>1028</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>1033</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="363" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
-        <v>1034</v>
+        <v>1030</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="364" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
-        <v>1037</v>
+        <v>1033</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>1038</v>
+        <v>1034</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>1039</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="365" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
-        <v>1040</v>
+        <v>1036</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>294</v>
+        <v>1037</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>295</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="366" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B366" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C366" s="2" t="s">
         <v>1041</v>
-      </c>
-      <c r="B366" s="2" t="s">
-        <v>1042</v>
-      </c>
-      <c r="C366" s="2" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="367" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B367" s="2" t="s">
         <v>1043</v>
       </c>
-      <c r="B367" s="2" t="s">
+      <c r="C367" s="2" t="s">
         <v>1044</v>
-      </c>
-      <c r="C367" s="2" t="s">
-        <v>1045</v>
       </c>
     </row>
     <row r="368" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B368" s="2" t="s">
         <v>1046</v>
       </c>
-      <c r="B368" s="2" t="s">
+      <c r="C368" s="2" t="s">
         <v>1047</v>
-      </c>
-      <c r="C368" s="2" t="s">
-        <v>1048</v>
       </c>
     </row>
     <row r="369" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B369" s="2" t="s">
         <v>1049</v>
       </c>
-      <c r="B369" s="2" t="s">
-        <v>191</v>
-      </c>
       <c r="C369" s="2" t="s">
-        <v>192</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="370" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="371" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="372" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="373" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="374" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="375" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="376" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A376" s="2" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="C376" s="2" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="377" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A377" s="2" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="C377" s="2" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="378" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>276</v>
+        <v>1076</v>
       </c>
       <c r="C378" s="2" t="s">
-        <v>277</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="379" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A379" s="2" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="C379" s="2" t="s">
-        <v>1061</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="380" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A380" s="2" t="s">
-        <v>1077</v>
+        <v>1081</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="C380" s="2" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="381" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A381" s="2" t="s">
-        <v>1080</v>
+        <v>1084</v>
       </c>
       <c r="B381" s="2" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
       <c r="C381" s="2" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="382" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A382" s="2" t="s">
-        <v>1083</v>
+        <v>1087</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>1084</v>
+        <v>1088</v>
       </c>
       <c r="C382" s="2" t="s">
-        <v>1085</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="383" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A383" s="2" t="s">
-        <v>1086</v>
+        <v>1090</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>1087</v>
+        <v>1091</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="384" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A384" s="2" t="s">
-        <v>1089</v>
+        <v>1093</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>1090</v>
+        <v>294</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>1091</v>
+        <v>295</v>
       </c>
     </row>
     <row r="385" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A385" s="2" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>294</v>
+        <v>1095</v>
       </c>
       <c r="C385" s="2" t="s">
-        <v>295</v>
+        <v>642</v>
       </c>
     </row>
     <row r="386" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A386" s="2" t="s">
-        <v>1093</v>
+        <v>1096</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>1094</v>
+        <v>1097</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>1095</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="387" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A387" s="2" t="s">
-        <v>1096</v>
+        <v>1099</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="C387" s="2" t="s">
-        <v>1098</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="388" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A388" s="2" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>1100</v>
+        <v>191</v>
       </c>
       <c r="C388" s="2" t="s">
-        <v>1101</v>
+        <v>192</v>
       </c>
     </row>
     <row r="389" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A389" s="2" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B389" s="2" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="C389" s="2" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="390" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A390" s="2" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B390" s="2" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="C390" s="2" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="391" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A391" s="2" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="B391" s="2" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C391" s="2" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="392" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A392" s="2" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B392" s="2" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="C392" s="2" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="393" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A393" s="2" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B393" s="2" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="C393" s="2" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="394" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A394" s="2" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="B394" s="2" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="C394" s="2" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="395" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A395" s="2" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="B395" s="2" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="C395" s="2" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="396" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A396" s="2" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="B396" s="2" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="C396" s="2" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="397" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A397" s="2" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="B397" s="2" t="s">
-        <v>1127</v>
+        <v>276</v>
       </c>
       <c r="C397" s="2" t="s">
-        <v>1128</v>
+        <v>277</v>
       </c>
     </row>
     <row r="398" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A398" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B398" s="2" t="s">
         <v>1129</v>
       </c>
-      <c r="B398" s="2" t="s">
-        <v>1130</v>
-      </c>
       <c r="C398" s="2" t="s">
-        <v>1131</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="399" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A399" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B399" s="2" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C399" s="2" t="s">
         <v>1132</v>
-      </c>
-      <c r="B399" s="2" t="s">
-        <v>1133</v>
-      </c>
-      <c r="C399" s="2" t="s">
-        <v>1134</v>
       </c>
     </row>
     <row r="400" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A400" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B400" s="2" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C400" s="2" t="s">
         <v>1135</v>
-      </c>
-      <c r="B400" s="2" t="s">
-        <v>1136</v>
-      </c>
-      <c r="C400" s="2" t="s">
-        <v>1137</v>
       </c>
     </row>
     <row r="401" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A401" s="2" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B401" s="2" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C401" s="2" t="s">
         <v>1138</v>
-      </c>
-      <c r="B401" s="2" t="s">
-        <v>1139</v>
-      </c>
-      <c r="C401" s="2" t="s">
-        <v>1140</v>
       </c>
     </row>
     <row r="402" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A402" s="2" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B402" s="2" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C402" s="2" t="s">
         <v>1141</v>
-      </c>
-      <c r="B402" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="C402" s="2" t="s">
-        <v>1142</v>
       </c>
     </row>
     <row r="403" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A403" s="2" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B403" s="2" t="s">
         <v>1143</v>
       </c>
-      <c r="B403" s="2" t="s">
+      <c r="C403" s="2" t="s">
         <v>1144</v>
-      </c>
-      <c r="C403" s="2" t="s">
-        <v>1145</v>
       </c>
     </row>
     <row r="404" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A404" s="2" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="B404" s="2" t="s">
-        <v>1147</v>
+        <v>294</v>
       </c>
       <c r="C404" s="2" t="s">
-        <v>1148</v>
+        <v>295</v>
       </c>
     </row>
     <row r="405" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A405" s="2" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
       <c r="B405" s="2" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
       <c r="C405" s="2" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="406" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A406" s="2" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>1153</v>
+        <v>1150</v>
       </c>
       <c r="C406" s="2" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="407" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A407" s="2" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>1156</v>
+        <v>1153</v>
       </c>
       <c r="C407" s="2" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="408" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A408" s="2" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="B408" s="2" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
       <c r="C408" s="2" t="s">
-        <v>1160</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="409" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A409" s="2" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="B409" s="2" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="C409" s="2" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="410" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A410" s="2" t="s">
-        <v>1164</v>
+        <v>1161</v>
       </c>
       <c r="B410" s="2" t="s">
-        <v>1165</v>
+        <v>1162</v>
       </c>
       <c r="C410" s="2" t="s">
-        <v>1166</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="411" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A411" s="2" t="s">
-        <v>1167</v>
+        <v>1164</v>
       </c>
       <c r="B411" s="2" t="s">
-        <v>1168</v>
+        <v>1165</v>
       </c>
       <c r="C411" s="2" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="412" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A412" s="2" t="s">
-        <v>1170</v>
+        <v>1167</v>
       </c>
       <c r="B412" s="2" t="s">
-        <v>1171</v>
+        <v>1168</v>
       </c>
       <c r="C412" s="2" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="413" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A413" s="2" t="s">
-        <v>1173</v>
+        <v>1170</v>
       </c>
       <c r="B413" s="2" t="s">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="C413" s="2" t="s">
-        <v>1175</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="414" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A414" s="2" t="s">
-        <v>1176</v>
+        <v>1173</v>
       </c>
       <c r="B414" s="2" t="s">
-        <v>1177</v>
+        <v>1174</v>
       </c>
       <c r="C414" s="2" t="s">
-        <v>1178</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="415" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A415" s="2" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="C415" s="2" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="416" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A416" s="2" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="B416" s="2" t="s">
-        <v>1183</v>
+        <v>1180</v>
       </c>
       <c r="C416" s="2" t="s">
-        <v>1184</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="417" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A417" s="2" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="B417" s="2" t="s">
-        <v>1186</v>
+        <v>1183</v>
       </c>
       <c r="C417" s="2" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="418" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A418" s="2" t="s">
-        <v>1188</v>
+        <v>1185</v>
       </c>
       <c r="B418" s="2" t="s">
-        <v>1189</v>
+        <v>1186</v>
       </c>
       <c r="C418" s="2" t="s">
-        <v>1190</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="419" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A419" s="2" t="s">
-        <v>1191</v>
+        <v>1188</v>
       </c>
       <c r="B419" s="2" t="s">
-        <v>1192</v>
+        <v>1189</v>
       </c>
       <c r="C419" s="2" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="420" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A420" s="2" t="s">
-        <v>1194</v>
+        <v>1191</v>
       </c>
       <c r="B420" s="2" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
       <c r="C420" s="2" t="s">
-        <v>1196</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="421" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A421" s="2" t="s">
-        <v>1197</v>
+        <v>1194</v>
       </c>
       <c r="B421" s="2" t="s">
-        <v>1198</v>
+        <v>350</v>
       </c>
       <c r="C421" s="2" t="s">
-        <v>1199</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="422" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A422" s="2" t="s">
-        <v>1200</v>
+        <v>1196</v>
       </c>
       <c r="B422" s="2" t="s">
-        <v>1201</v>
+        <v>1197</v>
       </c>
       <c r="C422" s="2" t="s">
-        <v>1202</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="423" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A423" s="2" t="s">
-        <v>1203</v>
+        <v>1199</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>1204</v>
+        <v>1200</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="424" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A424" s="2" t="s">
-        <v>1206</v>
+        <v>1202</v>
       </c>
       <c r="B424" s="2" t="s">
-        <v>1207</v>
+        <v>1203</v>
       </c>
       <c r="C424" s="2" t="s">
-        <v>1208</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="425" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A425" s="2" t="s">
-        <v>1209</v>
+        <v>1205</v>
       </c>
       <c r="B425" s="2" t="s">
-        <v>922</v>
+        <v>1206</v>
       </c>
       <c r="C425" s="2" t="s">
-        <v>923</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="426" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A426" s="2" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B426" s="2" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C426" s="2" t="s">
         <v>1210</v>
-      </c>
-      <c r="B426" s="2" t="s">
-        <v>1211</v>
-      </c>
-      <c r="C426" s="2" t="s">
-        <v>1212</v>
       </c>
     </row>
     <row r="427" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A427" s="2" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B427" s="2" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C427" s="2" t="s">
         <v>1213</v>
-      </c>
-      <c r="B427" s="2" t="s">
-        <v>1214</v>
-      </c>
-      <c r="C427" s="2" t="s">
-        <v>1215</v>
       </c>
     </row>
     <row r="428" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A428" s="2" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B428" s="2" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C428" s="2" t="s">
         <v>1216</v>
-      </c>
-      <c r="B428" s="2" t="s">
-        <v>1217</v>
-      </c>
-      <c r="C428" s="2" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="429" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A429" s="2" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B429" s="2" t="s">
         <v>1218</v>
       </c>
-      <c r="B429" s="2" t="s">
-        <v>185</v>
-      </c>
       <c r="C429" s="2" t="s">
-        <v>186</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="430" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A430" s="2" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="B430" s="2" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="C430" s="2" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="431" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A431" s="2" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="B431" s="2" t="s">
-        <v>191</v>
+        <v>1224</v>
       </c>
       <c r="C431" s="2" t="s">
-        <v>192</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="432" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A432" s="2" t="s">
-        <v>1223</v>
+        <v>1226</v>
       </c>
       <c r="B432" s="2" t="s">
-        <v>1224</v>
+        <v>1227</v>
       </c>
       <c r="C432" s="2" t="s">
-        <v>1225</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="433" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A433" s="2" t="s">
-        <v>1226</v>
+        <v>1229</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>282</v>
+        <v>1230</v>
       </c>
       <c r="C433" s="2" t="s">
-        <v>283</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="434" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A434" s="2" t="s">
-        <v>1227</v>
+        <v>1232</v>
       </c>
       <c r="B434" s="2" t="s">
-        <v>1228</v>
+        <v>1233</v>
       </c>
       <c r="C434" s="2" t="s">
-        <v>1229</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="435" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A435" s="2" t="s">
-        <v>1230</v>
+        <v>1235</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>1035</v>
+        <v>1236</v>
       </c>
       <c r="C435" s="2" t="s">
-        <v>1231</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="436" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A436" s="2" t="s">
-        <v>1232</v>
+        <v>1238</v>
       </c>
       <c r="B436" s="2" t="s">
-        <v>303</v>
+        <v>1239</v>
       </c>
       <c r="C436" s="2" t="s">
-        <v>304</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="437" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A437" s="2" t="s">
-        <v>1233</v>
+        <v>1241</v>
       </c>
       <c r="B437" s="2" t="s">
-        <v>297</v>
+        <v>1242</v>
       </c>
       <c r="C437" s="2" t="s">
-        <v>298</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="438" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A438" s="2" t="s">
-        <v>1234</v>
+        <v>1244</v>
       </c>
       <c r="B438" s="2" t="s">
-        <v>1235</v>
+        <v>1245</v>
       </c>
       <c r="C438" s="2" t="s">
-        <v>1236</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="439" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A439" s="2" t="s">
-        <v>1237</v>
+        <v>1247</v>
       </c>
       <c r="B439" s="2" t="s">
-        <v>1238</v>
+        <v>1248</v>
       </c>
       <c r="C439" s="2" t="s">
-        <v>1239</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="440" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A440" s="2" t="s">
-        <v>1240</v>
+        <v>1250</v>
       </c>
       <c r="B440" s="2" t="s">
-        <v>313</v>
+        <v>1251</v>
       </c>
       <c r="C440" s="2" t="s">
-        <v>314</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="441" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A441" s="2" t="s">
-        <v>1241</v>
+        <v>1253</v>
       </c>
       <c r="B441" s="2" t="s">
-        <v>1242</v>
+        <v>1254</v>
       </c>
       <c r="C441" s="2" t="s">
-        <v>1243</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="442" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A442" s="2" t="s">
-        <v>1244</v>
+        <v>1256</v>
       </c>
       <c r="B442" s="2" t="s">
-        <v>319</v>
+        <v>1257</v>
       </c>
       <c r="C442" s="2" t="s">
-        <v>320</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="443" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A443" s="2" t="s">
-        <v>1245</v>
+        <v>1259</v>
       </c>
       <c r="B443" s="2" t="s">
-        <v>1246</v>
+        <v>1260</v>
       </c>
       <c r="C443" s="2" t="s">
-        <v>1247</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="444" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A444" s="2" t="s">
-        <v>1248</v>
+        <v>1262</v>
       </c>
       <c r="B444" s="2" t="s">
-        <v>1249</v>
+        <v>975</v>
       </c>
       <c r="C444" s="2" t="s">
-        <v>1249</v>
+        <v>976</v>
       </c>
     </row>
     <row r="445" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A445" s="2" t="s">
-        <v>1250</v>
+        <v>1263</v>
       </c>
       <c r="B445" s="2" t="s">
-        <v>1251</v>
+        <v>1264</v>
       </c>
       <c r="C445" s="2" t="s">
-        <v>1251</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="446" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A446" s="2" t="s">
-        <v>1252</v>
+        <v>1266</v>
       </c>
       <c r="B446" s="2" t="s">
-        <v>1253</v>
+        <v>1267</v>
       </c>
       <c r="C446" s="2" t="s">
-        <v>1254</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="447" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A447" s="2" t="s">
-        <v>1255</v>
+        <v>1269</v>
       </c>
       <c r="B447" s="2" t="s">
-        <v>1253</v>
+        <v>1270</v>
       </c>
       <c r="C447" s="2" t="s">
-        <v>1254</v>
+        <v>183</v>
       </c>
     </row>
     <row r="448" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A448" s="2" t="s">
-        <v>1256</v>
+        <v>1271</v>
       </c>
       <c r="B448" s="2" t="s">
-        <v>1257</v>
+        <v>185</v>
       </c>
       <c r="C448" s="2" t="s">
-        <v>1258</v>
+        <v>186</v>
       </c>
     </row>
     <row r="449" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A449" s="2" t="s">
-        <v>1259</v>
+        <v>1272</v>
       </c>
       <c r="B449" s="2" t="s">
-        <v>1260</v>
+        <v>1273</v>
       </c>
       <c r="C449" s="2" t="s">
-        <v>1261</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="450" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A450" s="2" t="s">
-        <v>1262</v>
+        <v>1275</v>
       </c>
       <c r="B450" s="2" t="s">
-        <v>1263</v>
+        <v>191</v>
       </c>
       <c r="C450" s="2" t="s">
-        <v>1264</v>
+        <v>192</v>
       </c>
     </row>
     <row r="451" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A451" s="2" t="s">
-        <v>1265</v>
+        <v>1276</v>
       </c>
       <c r="B451" s="2" t="s">
-        <v>1266</v>
+        <v>1277</v>
       </c>
       <c r="C451" s="2" t="s">
-        <v>1267</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="452" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A452" s="2" t="s">
-        <v>1268</v>
+        <v>1279</v>
       </c>
       <c r="B452" s="2" t="s">
-        <v>1269</v>
+        <v>282</v>
       </c>
       <c r="C452" s="2" t="s">
-        <v>1270</v>
+        <v>283</v>
       </c>
     </row>
     <row r="453" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A453" s="2" t="s">
-        <v>1271</v>
+        <v>1280</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>1272</v>
+        <v>1281</v>
       </c>
       <c r="C453" s="2" t="s">
-        <v>1273</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="454" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A454" s="2" t="s">
-        <v>1274</v>
+        <v>1283</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>1275</v>
+        <v>1088</v>
       </c>
       <c r="C454" s="2" t="s">
-        <v>1276</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="455" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A455" s="2" t="s">
-        <v>1277</v>
+        <v>1285</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>1278</v>
+        <v>303</v>
       </c>
       <c r="C455" s="2" t="s">
-        <v>1279</v>
+        <v>304</v>
       </c>
     </row>
     <row r="456" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A456" s="2" t="s">
-        <v>1280</v>
+        <v>1286</v>
       </c>
       <c r="B456" s="2" t="s">
-        <v>1281</v>
+        <v>297</v>
       </c>
       <c r="C456" s="2" t="s">
-        <v>1282</v>
+        <v>298</v>
       </c>
     </row>
     <row r="457" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A457" s="2" t="s">
-        <v>1283</v>
+        <v>1287</v>
       </c>
       <c r="B457" s="2" t="s">
-        <v>1284</v>
+        <v>1288</v>
       </c>
       <c r="C457" s="2" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="458" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A458" s="2" t="s">
-        <v>1286</v>
+        <v>1290</v>
       </c>
       <c r="B458" s="2" t="s">
-        <v>1287</v>
+        <v>1291</v>
       </c>
       <c r="C458" s="2" t="s">
-        <v>1288</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="459" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A459" s="2" t="s">
-        <v>1289</v>
+        <v>1293</v>
       </c>
       <c r="B459" s="2" t="s">
-        <v>1290</v>
+        <v>313</v>
       </c>
       <c r="C459" s="2" t="s">
-        <v>1291</v>
+        <v>314</v>
       </c>
     </row>
     <row r="460" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A460" s="2" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="B460" s="2" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="C460" s="2" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="461" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A461" s="2" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="B461" s="2" t="s">
-        <v>1296</v>
+        <v>319</v>
       </c>
       <c r="C461" s="2" t="s">
-        <v>1273</v>
+        <v>320</v>
       </c>
     </row>
     <row r="462" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A462" s="2" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="B462" s="2" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="C462" s="2" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="463" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A463" s="2" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="C463" s="2" t="s">
         <v>1302</v>
@@ -11621,7 +11819,7 @@
         <v>1304</v>
       </c>
       <c r="C464" s="2" t="s">
-        <v>1279</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="465" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11640,32 +11838,32 @@
         <v>1308</v>
       </c>
       <c r="B466" s="2" t="s">
-        <v>1309</v>
+        <v>1306</v>
       </c>
       <c r="C466" s="2" t="s">
-        <v>1310</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="467" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A467" s="2" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B467" s="2" t="s">
+        <v>1310</v>
+      </c>
+      <c r="C467" s="2" t="s">
         <v>1311</v>
-      </c>
-      <c r="B467" s="2" t="s">
-        <v>1312</v>
-      </c>
-      <c r="C467" s="2" t="s">
-        <v>1313</v>
       </c>
     </row>
     <row r="468" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A468" s="2" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B468" s="2" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C468" s="2" t="s">
         <v>1314</v>
-      </c>
-      <c r="B468" s="2" t="s">
-        <v>1163</v>
-      </c>
-      <c r="C468" s="2" t="s">
-        <v>1163</v>
       </c>
     </row>
     <row r="469" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11761,76 +11959,76 @@
         <v>1339</v>
       </c>
       <c r="B477" s="2" t="s">
-        <v>1201</v>
+        <v>1340</v>
       </c>
       <c r="C477" s="2" t="s">
-        <v>1202</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="478" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A478" s="2" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="B478" s="2" t="s">
-        <v>1341</v>
+        <v>1343</v>
       </c>
       <c r="C478" s="2" t="s">
-        <v>1342</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="479" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A479" s="2" t="s">
-        <v>1343</v>
+        <v>1345</v>
       </c>
       <c r="B479" s="2" t="s">
-        <v>1344</v>
+        <v>1346</v>
       </c>
       <c r="C479" s="2" t="s">
-        <v>1345</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="480" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A480" s="2" t="s">
-        <v>1346</v>
+        <v>1348</v>
       </c>
       <c r="B480" s="2" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
       <c r="C480" s="2" t="s">
-        <v>1348</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="481" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A481" s="2" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="B481" s="2" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="C481" s="2" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="482" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A482" s="2" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="B482" s="2" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="C482" s="2" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="483" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A483" s="2" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="B483" s="2" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="C483" s="2" t="s">
-        <v>1357</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="484" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11841,227 +12039,227 @@
         <v>1359</v>
       </c>
       <c r="C484" s="2" t="s">
-        <v>217</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="485" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A485" s="2" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="B485" s="2" t="s">
-        <v>185</v>
+        <v>1362</v>
       </c>
       <c r="C485" s="2" t="s">
-        <v>186</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="486" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A486" s="2" t="s">
-        <v>1361</v>
+        <v>1364</v>
       </c>
       <c r="B486" s="2" t="s">
-        <v>188</v>
+        <v>1365</v>
       </c>
       <c r="C486" s="2" t="s">
-        <v>189</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="487" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A487" s="2" t="s">
-        <v>1362</v>
+        <v>1367</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>597</v>
+        <v>1216</v>
       </c>
       <c r="C487" s="2" t="s">
-        <v>598</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="488" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A488" s="2" t="s">
-        <v>1363</v>
+        <v>1368</v>
       </c>
       <c r="B488" s="2" t="s">
-        <v>1364</v>
+        <v>1369</v>
       </c>
       <c r="C488" s="2" t="s">
-        <v>1365</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="489" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A489" s="2" t="s">
-        <v>1366</v>
+        <v>1371</v>
       </c>
       <c r="B489" s="2" t="s">
-        <v>1367</v>
+        <v>1372</v>
       </c>
       <c r="C489" s="2" t="s">
-        <v>1368</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="490" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A490" s="2" t="s">
-        <v>1369</v>
+        <v>1374</v>
       </c>
       <c r="B490" s="2" t="s">
-        <v>1370</v>
+        <v>1375</v>
       </c>
       <c r="C490" s="2" t="s">
-        <v>1371</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="491" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A491" s="2" t="s">
-        <v>1372</v>
+        <v>1377</v>
       </c>
       <c r="B491" s="2" t="s">
-        <v>1373</v>
+        <v>1378</v>
       </c>
       <c r="C491" s="2" t="s">
-        <v>1374</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="492" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A492" s="2" t="s">
-        <v>1375</v>
+        <v>1380</v>
       </c>
       <c r="B492" s="2" t="s">
-        <v>1376</v>
+        <v>1381</v>
       </c>
       <c r="C492" s="2" t="s">
-        <v>1377</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="493" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A493" s="2" t="s">
-        <v>1378</v>
+        <v>1383</v>
       </c>
       <c r="B493" s="2" t="s">
-        <v>1379</v>
+        <v>1384</v>
       </c>
       <c r="C493" s="2" t="s">
-        <v>1380</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="494" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A494" s="2" t="s">
-        <v>1381</v>
+        <v>1386</v>
       </c>
       <c r="B494" s="2" t="s">
-        <v>1382</v>
+        <v>1387</v>
       </c>
       <c r="C494" s="2" t="s">
-        <v>1383</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="495" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A495" s="2" t="s">
-        <v>1384</v>
+        <v>1389</v>
       </c>
       <c r="B495" s="2" t="s">
-        <v>1385</v>
+        <v>1390</v>
       </c>
       <c r="C495" s="2" t="s">
-        <v>1386</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="496" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A496" s="2" t="s">
-        <v>1387</v>
+        <v>1392</v>
       </c>
       <c r="B496" s="2" t="s">
-        <v>1388</v>
+        <v>1254</v>
       </c>
       <c r="C496" s="2" t="s">
-        <v>1389</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="497" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A497" s="2" t="s">
-        <v>1390</v>
+        <v>1393</v>
       </c>
       <c r="B497" s="2" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="C497" s="2" t="s">
-        <v>1392</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="498" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A498" s="2" t="s">
-        <v>1393</v>
+        <v>1396</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>1394</v>
+        <v>1397</v>
       </c>
       <c r="C498" s="2" t="s">
-        <v>1395</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="499" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A499" s="2" t="s">
-        <v>1396</v>
+        <v>1399</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>1397</v>
+        <v>1400</v>
       </c>
       <c r="C499" s="2" t="s">
-        <v>1398</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="500" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A500" s="2" t="s">
-        <v>1399</v>
+        <v>1402</v>
       </c>
       <c r="B500" s="2" t="s">
-        <v>1400</v>
+        <v>1403</v>
       </c>
       <c r="C500" s="2" t="s">
-        <v>1401</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="501" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A501" s="2" t="s">
-        <v>1402</v>
+        <v>1405</v>
       </c>
       <c r="B501" s="2" t="s">
-        <v>1403</v>
+        <v>1406</v>
       </c>
       <c r="C501" s="2" t="s">
-        <v>1404</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="502" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A502" s="2" t="s">
-        <v>1405</v>
+        <v>1408</v>
       </c>
       <c r="B502" s="2" t="s">
-        <v>1406</v>
+        <v>1409</v>
       </c>
       <c r="C502" s="2" t="s">
-        <v>1407</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="503" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A503" s="2" t="s">
-        <v>1408</v>
+        <v>1411</v>
       </c>
       <c r="B503" s="2" t="s">
-        <v>1409</v>
+        <v>1412</v>
       </c>
       <c r="C503" s="2" t="s">
-        <v>1410</v>
+        <v>217</v>
       </c>
     </row>
     <row r="504" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A504" s="2" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="B504" s="2" t="s">
-        <v>1412</v>
+        <v>185</v>
       </c>
       <c r="C504" s="2" t="s">
-        <v>1413</v>
+        <v>186</v>
       </c>
     </row>
     <row r="505" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12069,378 +12267,378 @@
         <v>1414</v>
       </c>
       <c r="B505" s="2" t="s">
-        <v>1415</v>
+        <v>188</v>
       </c>
       <c r="C505" s="2" t="s">
-        <v>1416</v>
+        <v>189</v>
       </c>
     </row>
     <row r="506" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A506" s="2" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="B506" s="2" t="s">
-        <v>1418</v>
+        <v>628</v>
       </c>
       <c r="C506" s="2" t="s">
-        <v>1419</v>
+        <v>629</v>
       </c>
     </row>
     <row r="507" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A507" s="2" t="s">
-        <v>1420</v>
+        <v>1416</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>43</v>
+        <v>1417</v>
       </c>
       <c r="C507" s="2" t="s">
-        <v>44</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="508" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A508" s="2" t="s">
+        <v>1419</v>
+      </c>
+      <c r="B508" s="2" t="s">
+        <v>1420</v>
+      </c>
+      <c r="C508" s="2" t="s">
         <v>1421</v>
-      </c>
-      <c r="B508" s="2" t="s">
-        <v>1422</v>
-      </c>
-      <c r="C508" s="2" t="s">
-        <v>1045</v>
       </c>
     </row>
     <row r="509" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A509" s="2" t="s">
+        <v>1422</v>
+      </c>
+      <c r="B509" s="2" t="s">
         <v>1423</v>
       </c>
-      <c r="B509" s="2" t="s">
-        <v>1364</v>
-      </c>
       <c r="C509" s="2" t="s">
-        <v>1365</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="510" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A510" s="2" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="B510" s="2" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="C510" s="2" t="s">
-        <v>1154</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="511" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A511" s="2" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="C511" s="2" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="512" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A512" s="2" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="B512" s="2" t="s">
-        <v>1367</v>
+        <v>1432</v>
       </c>
       <c r="C512" s="2" t="s">
-        <v>1368</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="513" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A513" s="2" t="s">
-        <v>1430</v>
+        <v>1434</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>194</v>
+        <v>1435</v>
       </c>
       <c r="C513" s="2" t="s">
-        <v>194</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="514" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A514" s="2" t="s">
-        <v>1431</v>
+        <v>1437</v>
       </c>
       <c r="B514" s="2" t="s">
-        <v>1432</v>
+        <v>1438</v>
       </c>
       <c r="C514" s="2" t="s">
-        <v>1433</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="515" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A515" s="2" t="s">
-        <v>1434</v>
+        <v>1440</v>
       </c>
       <c r="B515" s="2" t="s">
-        <v>1435</v>
+        <v>1441</v>
       </c>
       <c r="C515" s="2" t="s">
-        <v>1436</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="516" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A516" s="2" t="s">
-        <v>1437</v>
+        <v>1443</v>
       </c>
       <c r="B516" s="2" t="s">
-        <v>1438</v>
+        <v>1444</v>
       </c>
       <c r="C516" s="2" t="s">
-        <v>1439</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="517" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A517" s="2" t="s">
-        <v>1440</v>
+        <v>1446</v>
       </c>
       <c r="B517" s="2" t="s">
-        <v>1441</v>
+        <v>1447</v>
       </c>
       <c r="C517" s="2" t="s">
-        <v>1442</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="518" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A518" s="2" t="s">
-        <v>1443</v>
+        <v>1449</v>
       </c>
       <c r="B518" s="2" t="s">
-        <v>1444</v>
+        <v>1450</v>
       </c>
       <c r="C518" s="2" t="s">
-        <v>1445</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="519" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A519" s="2" t="s">
-        <v>1446</v>
+        <v>1452</v>
       </c>
       <c r="B519" s="2" t="s">
-        <v>1198</v>
+        <v>1453</v>
       </c>
       <c r="C519" s="2" t="s">
-        <v>1199</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="520" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A520" s="2" t="s">
-        <v>1447</v>
+        <v>1455</v>
       </c>
       <c r="B520" s="2" t="s">
-        <v>4</v>
+        <v>1456</v>
       </c>
       <c r="C520" s="2" t="s">
-        <v>5</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="521" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A521" s="2" t="s">
-        <v>1448</v>
+        <v>1458</v>
       </c>
       <c r="B521" s="2" t="s">
-        <v>1186</v>
+        <v>1459</v>
       </c>
       <c r="C521" s="2" t="s">
-        <v>1187</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="522" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A522" s="2" t="s">
-        <v>1449</v>
+        <v>1461</v>
       </c>
       <c r="B522" s="2" t="s">
-        <v>1201</v>
+        <v>1462</v>
       </c>
       <c r="C522" s="2" t="s">
-        <v>1202</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="523" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A523" s="2" t="s">
-        <v>1450</v>
+        <v>1464</v>
       </c>
       <c r="B523" s="2" t="s">
-        <v>1451</v>
+        <v>1465</v>
       </c>
       <c r="C523" s="2" t="s">
-        <v>1452</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="524" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A524" s="2" t="s">
-        <v>1453</v>
+        <v>1467</v>
       </c>
       <c r="B524" s="2" t="s">
-        <v>1454</v>
+        <v>1468</v>
       </c>
       <c r="C524" s="2" t="s">
-        <v>1455</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="525" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A525" s="2" t="s">
-        <v>1456</v>
+        <v>1470</v>
       </c>
       <c r="B525" s="2" t="s">
-        <v>1204</v>
+        <v>1471</v>
       </c>
       <c r="C525" s="2" t="s">
-        <v>1205</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="526" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A526" s="2" t="s">
-        <v>1457</v>
+        <v>1473</v>
       </c>
       <c r="B526" s="2" t="s">
-        <v>1458</v>
+        <v>43</v>
       </c>
       <c r="C526" s="2" t="s">
-        <v>1459</v>
+        <v>44</v>
       </c>
     </row>
     <row r="527" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A527" s="2" t="s">
-        <v>1460</v>
+        <v>1474</v>
       </c>
       <c r="B527" s="2" t="s">
-        <v>1207</v>
+        <v>1475</v>
       </c>
       <c r="C527" s="2" t="s">
-        <v>1461</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="528" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A528" s="2" t="s">
-        <v>1462</v>
+        <v>1476</v>
       </c>
       <c r="B528" s="2" t="s">
-        <v>1153</v>
+        <v>1417</v>
       </c>
       <c r="C528" s="2" t="s">
-        <v>1463</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="529" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A529" s="2" t="s">
-        <v>1464</v>
+        <v>1477</v>
       </c>
       <c r="B529" s="2" t="s">
-        <v>1465</v>
+        <v>1478</v>
       </c>
       <c r="C529" s="2" t="s">
-        <v>1466</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="530" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A530" s="2" t="s">
-        <v>1467</v>
+        <v>1479</v>
       </c>
       <c r="B530" s="2" t="s">
-        <v>1468</v>
+        <v>1480</v>
       </c>
       <c r="C530" s="2" t="s">
-        <v>1469</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="531" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A531" s="2" t="s">
-        <v>1470</v>
+        <v>1482</v>
       </c>
       <c r="B531" s="2" t="s">
-        <v>1471</v>
+        <v>1420</v>
       </c>
       <c r="C531" s="2" t="s">
-        <v>1472</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="532" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A532" s="2" t="s">
-        <v>1473</v>
+        <v>1483</v>
       </c>
       <c r="B532" s="2" t="s">
-        <v>1474</v>
+        <v>194</v>
       </c>
       <c r="C532" s="2" t="s">
-        <v>1475</v>
+        <v>194</v>
       </c>
     </row>
     <row r="533" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A533" s="2" t="s">
-        <v>1476</v>
+        <v>1484</v>
       </c>
       <c r="B533" s="2" t="s">
-        <v>1477</v>
+        <v>1485</v>
       </c>
       <c r="C533" s="2" t="s">
-        <v>1478</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="534" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A534" s="2" t="s">
-        <v>1479</v>
+        <v>1487</v>
       </c>
       <c r="B534" s="2" t="s">
-        <v>1480</v>
+        <v>1488</v>
       </c>
       <c r="C534" s="2" t="s">
-        <v>1481</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="535" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A535" s="2" t="s">
-        <v>1482</v>
+        <v>1490</v>
       </c>
       <c r="B535" s="2" t="s">
-        <v>1483</v>
+        <v>1491</v>
       </c>
       <c r="C535" s="2" t="s">
-        <v>1484</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="536" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A536" s="2" t="s">
-        <v>1485</v>
+        <v>1493</v>
       </c>
       <c r="B536" s="2" t="s">
-        <v>1486</v>
+        <v>1494</v>
       </c>
       <c r="C536" s="2" t="s">
-        <v>1487</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="537" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A537" s="2" t="s">
-        <v>1488</v>
+        <v>1496</v>
       </c>
       <c r="B537" s="2" t="s">
-        <v>1489</v>
+        <v>1497</v>
       </c>
       <c r="C537" s="2" t="s">
-        <v>1490</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="538" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A538" s="2" t="s">
-        <v>1491</v>
+        <v>1499</v>
       </c>
       <c r="B538" s="2" t="s">
-        <v>1198</v>
+        <v>1251</v>
       </c>
       <c r="C538" s="2" t="s">
-        <v>1199</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="539" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A539" s="2" t="s">
-        <v>1492</v>
+        <v>1500</v>
       </c>
       <c r="B539" s="2" t="s">
         <v>4</v>
@@ -12451,387 +12649,387 @@
     </row>
     <row r="540" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A540" s="2" t="s">
-        <v>1493</v>
+        <v>1501</v>
       </c>
       <c r="B540" s="2" t="s">
-        <v>1204</v>
+        <v>1239</v>
       </c>
       <c r="C540" s="2" t="s">
-        <v>1205</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="541" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A541" s="2" t="s">
-        <v>1494</v>
+        <v>1502</v>
       </c>
       <c r="B541" s="2" t="s">
-        <v>1495</v>
+        <v>1254</v>
       </c>
       <c r="C541" s="2" t="s">
-        <v>1496</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="542" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A542" s="2" t="s">
-        <v>1497</v>
+        <v>1503</v>
       </c>
       <c r="B542" s="2" t="s">
-        <v>1498</v>
+        <v>1504</v>
       </c>
       <c r="C542" s="2" t="s">
-        <v>1499</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="543" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A543" s="2" t="s">
-        <v>1500</v>
+        <v>1506</v>
       </c>
       <c r="B543" s="2" t="s">
-        <v>1501</v>
+        <v>1507</v>
       </c>
       <c r="C543" s="2" t="s">
-        <v>1502</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="544" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A544" s="2" t="s">
-        <v>1503</v>
+        <v>1509</v>
       </c>
       <c r="B544" s="2" t="s">
-        <v>1474</v>
+        <v>1257</v>
       </c>
       <c r="C544" s="2" t="s">
-        <v>1475</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="545" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A545" s="2" t="s">
-        <v>1504</v>
+        <v>1510</v>
       </c>
       <c r="B545" s="2" t="s">
-        <v>1505</v>
+        <v>1511</v>
       </c>
       <c r="C545" s="2" t="s">
-        <v>1506</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="546" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A546" s="2" t="s">
-        <v>1507</v>
+        <v>1513</v>
       </c>
       <c r="B546" s="2" t="s">
-        <v>1508</v>
+        <v>1260</v>
       </c>
       <c r="C546" s="2" t="s">
-        <v>1509</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="547" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A547" s="2" t="s">
-        <v>1510</v>
+        <v>1515</v>
       </c>
       <c r="B547" s="2" t="s">
-        <v>1328</v>
+        <v>1206</v>
       </c>
       <c r="C547" s="2" t="s">
-        <v>1329</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="548" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A548" s="2" t="s">
-        <v>1511</v>
+        <v>1517</v>
       </c>
       <c r="B548" s="2" t="s">
-        <v>1512</v>
+        <v>1518</v>
       </c>
       <c r="C548" s="2" t="s">
-        <v>1513</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="549" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A549" s="2" t="s">
-        <v>1514</v>
+        <v>1520</v>
       </c>
       <c r="B549" s="2" t="s">
-        <v>1515</v>
+        <v>1521</v>
       </c>
       <c r="C549" s="2" t="s">
-        <v>1516</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="550" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A550" s="2" t="s">
-        <v>1517</v>
+        <v>1523</v>
       </c>
       <c r="B550" s="2" t="s">
-        <v>1518</v>
+        <v>1524</v>
       </c>
       <c r="C550" s="2" t="s">
-        <v>1519</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="551" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A551" s="2" t="s">
-        <v>1520</v>
+        <v>1526</v>
       </c>
       <c r="B551" s="2" t="s">
-        <v>1521</v>
+        <v>1527</v>
       </c>
       <c r="C551" s="2" t="s">
-        <v>1522</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="552" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A552" s="2" t="s">
-        <v>1523</v>
+        <v>1529</v>
       </c>
       <c r="B552" s="2" t="s">
-        <v>1524</v>
+        <v>1530</v>
       </c>
       <c r="C552" s="2" t="s">
-        <v>1525</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="553" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A553" s="2" t="s">
-        <v>1526</v>
+        <v>1532</v>
       </c>
       <c r="B553" s="2" t="s">
-        <v>1527</v>
+        <v>1533</v>
       </c>
       <c r="C553" s="2" t="s">
-        <v>1528</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="554" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A554" s="2" t="s">
-        <v>1529</v>
+        <v>1535</v>
       </c>
       <c r="B554" s="2" t="s">
-        <v>1530</v>
+        <v>1536</v>
       </c>
       <c r="C554" s="2" t="s">
-        <v>1531</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="555" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A555" s="2" t="s">
-        <v>1532</v>
+        <v>1538</v>
       </c>
       <c r="B555" s="2" t="s">
-        <v>1533</v>
+        <v>1539</v>
       </c>
       <c r="C555" s="2" t="s">
-        <v>515</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="556" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A556" s="2" t="s">
-        <v>1534</v>
+        <v>1541</v>
       </c>
       <c r="B556" s="2" t="s">
-        <v>1535</v>
+        <v>1542</v>
       </c>
       <c r="C556" s="2" t="s">
-        <v>1536</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="557" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A557" s="2" t="s">
-        <v>1537</v>
+        <v>1544</v>
       </c>
       <c r="B557" s="2" t="s">
-        <v>1538</v>
+        <v>1251</v>
       </c>
       <c r="C557" s="2" t="s">
-        <v>1539</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="558" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A558" s="2" t="s">
-        <v>1540</v>
+        <v>1545</v>
       </c>
       <c r="B558" s="2" t="s">
-        <v>1541</v>
+        <v>4</v>
       </c>
       <c r="C558" s="2" t="s">
-        <v>1542</v>
+        <v>5</v>
       </c>
     </row>
     <row r="559" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A559" s="2" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="B559" s="2" t="s">
-        <v>1544</v>
+        <v>1257</v>
       </c>
       <c r="C559" s="2" t="s">
-        <v>1545</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="560" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A560" s="2" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="B560" s="2" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="C560" s="2" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="561" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A561" s="2" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="B561" s="2" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="C561" s="2" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="562" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A562" s="2" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="B562" s="2" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="C562" s="2" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="563" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A563" s="2" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="B563" s="2" t="s">
-        <v>1556</v>
+        <v>1527</v>
       </c>
       <c r="C563" s="2" t="s">
-        <v>1557</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="564" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A564" s="2" t="s">
+        <v>1557</v>
+      </c>
+      <c r="B564" s="2" t="s">
         <v>1558</v>
       </c>
-      <c r="B564" s="2" t="s">
-        <v>514</v>
-      </c>
       <c r="C564" s="2" t="s">
-        <v>515</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="565" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A565" s="2" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="B565" s="2" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="C565" s="2" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="566" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A566" s="2" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="B566" s="2" t="s">
-        <v>1563</v>
+        <v>1381</v>
       </c>
       <c r="C566" s="2" t="s">
-        <v>1564</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="567" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A567" s="2" t="s">
+        <v>1564</v>
+      </c>
+      <c r="B567" s="2" t="s">
         <v>1565</v>
       </c>
-      <c r="B567" s="2" t="s">
-        <v>282</v>
-      </c>
       <c r="C567" s="2" t="s">
-        <v>283</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="568" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A568" s="2" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="B568" s="2" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="C568" s="2" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="569" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A569" s="2" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="B569" s="2" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="C569" s="2" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="570" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A570" s="2" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="B570" s="2" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="C570" s="2" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="571" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A571" s="2" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="B571" s="2" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="C571" s="2" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="572" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A572" s="2" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="B572" s="2" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="C572" s="2" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="573" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A573" s="2" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="B573" s="2" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="C573" s="2" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="574" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A574" s="2" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="B574" s="2" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="C574" s="2" t="s">
-        <v>1586</v>
+        <v>533</v>
       </c>
     </row>
     <row r="575" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12894,417 +13092,417 @@
         <v>1602</v>
       </c>
       <c r="B580" s="2" t="s">
-        <v>276</v>
+        <v>1603</v>
       </c>
       <c r="C580" s="2" t="s">
-        <v>277</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="581" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A581" s="2" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="B581" s="2" t="s">
-        <v>1604</v>
+        <v>1606</v>
       </c>
       <c r="C581" s="2" t="s">
-        <v>1045</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="582" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A582" s="2" t="s">
-        <v>1605</v>
+        <v>1608</v>
       </c>
       <c r="B582" s="2" t="s">
-        <v>1606</v>
+        <v>1609</v>
       </c>
       <c r="C582" s="2" t="s">
-        <v>1607</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="583" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A583" s="2" t="s">
-        <v>1608</v>
+        <v>1611</v>
       </c>
       <c r="B583" s="2" t="s">
-        <v>1427</v>
+        <v>532</v>
       </c>
       <c r="C583" s="2" t="s">
-        <v>1428</v>
+        <v>533</v>
       </c>
     </row>
     <row r="584" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A584" s="2" t="s">
-        <v>1609</v>
+        <v>1612</v>
       </c>
       <c r="B584" s="2" t="s">
-        <v>1610</v>
+        <v>1613</v>
       </c>
       <c r="C584" s="2" t="s">
-        <v>1611</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="585" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A585" s="2" t="s">
-        <v>1612</v>
+        <v>1615</v>
       </c>
       <c r="B585" s="2" t="s">
-        <v>1613</v>
+        <v>1616</v>
       </c>
       <c r="C585" s="2" t="s">
-        <v>1614</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="586" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A586" s="2" t="s">
-        <v>1615</v>
+        <v>1618</v>
       </c>
       <c r="B586" s="2" t="s">
-        <v>1616</v>
+        <v>282</v>
       </c>
       <c r="C586" s="2" t="s">
-        <v>1617</v>
+        <v>283</v>
       </c>
     </row>
     <row r="587" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A587" s="2" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="B587" s="2" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="C587" s="2" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="588" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A588" s="2" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="B588" s="2" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="C588" s="2" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="589" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A589" s="2" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="B589" s="2" t="s">
-        <v>185</v>
+        <v>1626</v>
       </c>
       <c r="C589" s="2" t="s">
-        <v>186</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="590" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A590" s="2" t="s">
-        <v>1625</v>
+        <v>1628</v>
       </c>
       <c r="B590" s="2" t="s">
-        <v>1042</v>
+        <v>1629</v>
       </c>
       <c r="C590" s="2" t="s">
-        <v>611</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="591" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A591" s="2" t="s">
-        <v>1626</v>
+        <v>1631</v>
       </c>
       <c r="B591" s="2" t="s">
-        <v>1051</v>
+        <v>1632</v>
       </c>
       <c r="C591" s="2" t="s">
-        <v>1627</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="592" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A592" s="2" t="s">
-        <v>1628</v>
+        <v>1634</v>
       </c>
       <c r="B592" s="2" t="s">
-        <v>1629</v>
+        <v>1635</v>
       </c>
       <c r="C592" s="2" t="s">
-        <v>1630</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="593" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A593" s="2" t="s">
-        <v>1631</v>
+        <v>1637</v>
       </c>
       <c r="B593" s="2" t="s">
-        <v>276</v>
+        <v>1638</v>
       </c>
       <c r="C593" s="2" t="s">
-        <v>277</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="594" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A594" s="2" t="s">
-        <v>1632</v>
+        <v>1640</v>
       </c>
       <c r="B594" s="2" t="s">
-        <v>1633</v>
+        <v>1641</v>
       </c>
       <c r="C594" s="2" t="s">
-        <v>1634</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="595" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A595" s="2" t="s">
-        <v>1635</v>
+        <v>1643</v>
       </c>
       <c r="B595" s="2" t="s">
-        <v>1636</v>
+        <v>1644</v>
       </c>
       <c r="C595" s="2" t="s">
-        <v>1637</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="596" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A596" s="2" t="s">
-        <v>1638</v>
+        <v>1646</v>
       </c>
       <c r="B596" s="2" t="s">
-        <v>1639</v>
+        <v>1647</v>
       </c>
       <c r="C596" s="2" t="s">
-        <v>1640</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="597" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A597" s="2" t="s">
-        <v>1641</v>
+        <v>1649</v>
       </c>
       <c r="B597" s="2" t="s">
-        <v>1642</v>
+        <v>1650</v>
       </c>
       <c r="C597" s="2" t="s">
-        <v>1643</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="598" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A598" s="2" t="s">
-        <v>1644</v>
+        <v>1652</v>
       </c>
       <c r="B598" s="2" t="s">
-        <v>282</v>
+        <v>1653</v>
       </c>
       <c r="C598" s="2" t="s">
-        <v>283</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="599" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A599" s="2" t="s">
-        <v>1645</v>
+        <v>1655</v>
       </c>
       <c r="B599" s="2" t="s">
-        <v>1646</v>
+        <v>276</v>
       </c>
       <c r="C599" s="2" t="s">
-        <v>1647</v>
+        <v>277</v>
       </c>
     </row>
     <row r="600" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A600" s="2" t="s">
-        <v>1648</v>
+        <v>1656</v>
       </c>
       <c r="B600" s="2" t="s">
-        <v>1649</v>
+        <v>1657</v>
       </c>
       <c r="C600" s="2" t="s">
-        <v>1650</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="601" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A601" s="2" t="s">
-        <v>1651</v>
+        <v>1658</v>
       </c>
       <c r="B601" s="2" t="s">
-        <v>1652</v>
+        <v>1659</v>
       </c>
       <c r="C601" s="2" t="s">
-        <v>1653</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="602" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A602" s="2" t="s">
-        <v>1654</v>
+        <v>1661</v>
       </c>
       <c r="B602" s="2" t="s">
-        <v>1655</v>
+        <v>1480</v>
       </c>
       <c r="C602" s="2" t="s">
-        <v>1656</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="603" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A603" s="2" t="s">
-        <v>1657</v>
+        <v>1662</v>
       </c>
       <c r="B603" s="2" t="s">
-        <v>1658</v>
+        <v>1663</v>
       </c>
       <c r="C603" s="2" t="s">
-        <v>1659</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="604" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A604" s="2" t="s">
-        <v>1660</v>
+        <v>1665</v>
       </c>
       <c r="B604" s="2" t="s">
-        <v>514</v>
+        <v>1666</v>
       </c>
       <c r="C604" s="2" t="s">
-        <v>515</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="605" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A605" s="2" t="s">
-        <v>1661</v>
+        <v>1668</v>
       </c>
       <c r="B605" s="2" t="s">
-        <v>1662</v>
+        <v>1669</v>
       </c>
       <c r="C605" s="2" t="s">
-        <v>1663</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="606" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A606" s="2" t="s">
-        <v>1664</v>
+        <v>1671</v>
       </c>
       <c r="B606" s="2" t="s">
-        <v>1665</v>
+        <v>1672</v>
       </c>
       <c r="C606" s="2" t="s">
-        <v>1666</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="607" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A607" s="2" t="s">
-        <v>1667</v>
+        <v>1674</v>
       </c>
       <c r="B607" s="2" t="s">
-        <v>1668</v>
+        <v>1675</v>
       </c>
       <c r="C607" s="2" t="s">
-        <v>1669</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="608" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A608" s="2" t="s">
-        <v>1670</v>
+        <v>1677</v>
       </c>
       <c r="B608" s="2" t="s">
-        <v>1671</v>
+        <v>185</v>
       </c>
       <c r="C608" s="2" t="s">
-        <v>1672</v>
+        <v>186</v>
       </c>
     </row>
     <row r="609" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A609" s="2" t="s">
-        <v>1673</v>
+        <v>1678</v>
       </c>
       <c r="B609" s="2" t="s">
-        <v>1674</v>
+        <v>1095</v>
       </c>
       <c r="C609" s="2" t="s">
-        <v>1675</v>
+        <v>642</v>
       </c>
     </row>
     <row r="610" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A610" s="2" t="s">
-        <v>1676</v>
+        <v>1679</v>
       </c>
       <c r="B610" s="2" t="s">
-        <v>19</v>
+        <v>1104</v>
       </c>
       <c r="C610" s="2" t="s">
-        <v>20</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="611" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A611" s="2" t="s">
-        <v>1677</v>
+        <v>1681</v>
       </c>
       <c r="B611" s="2" t="s">
-        <v>1678</v>
+        <v>1682</v>
       </c>
       <c r="C611" s="2" t="s">
-        <v>1679</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="612" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A612" s="2" t="s">
-        <v>1680</v>
+        <v>1684</v>
       </c>
       <c r="B612" s="2" t="s">
-        <v>1681</v>
+        <v>276</v>
       </c>
       <c r="C612" s="2" t="s">
-        <v>1682</v>
+        <v>277</v>
       </c>
     </row>
     <row r="613" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A613" s="2" t="s">
-        <v>1683</v>
+        <v>1685</v>
       </c>
       <c r="B613" s="2" t="s">
-        <v>1684</v>
+        <v>1686</v>
       </c>
       <c r="C613" s="2" t="s">
-        <v>1685</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="614" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A614" s="2" t="s">
-        <v>1686</v>
+        <v>1688</v>
       </c>
       <c r="B614" s="2" t="s">
-        <v>1687</v>
+        <v>1689</v>
       </c>
       <c r="C614" s="2" t="s">
-        <v>1688</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="615" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A615" s="2" t="s">
-        <v>1689</v>
+        <v>1691</v>
       </c>
       <c r="B615" s="2" t="s">
-        <v>1690</v>
+        <v>1692</v>
       </c>
       <c r="C615" s="2" t="s">
-        <v>1691</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="616" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A616" s="2" t="s">
-        <v>1692</v>
+        <v>1694</v>
       </c>
       <c r="B616" s="2" t="s">
-        <v>1693</v>
+        <v>1695</v>
       </c>
       <c r="C616" s="2" t="s">
-        <v>1694</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="617" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A617" s="2" t="s">
-        <v>1695</v>
+        <v>1697</v>
       </c>
       <c r="B617" s="2" t="s">
-        <v>1696</v>
+        <v>282</v>
       </c>
       <c r="C617" s="2" t="s">
-        <v>1697</v>
+        <v>283</v>
       </c>
     </row>
     <row r="618" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13367,98 +13565,98 @@
         <v>1713</v>
       </c>
       <c r="B623" s="2" t="s">
-        <v>713</v>
+        <v>532</v>
       </c>
       <c r="C623" s="2" t="s">
-        <v>1714</v>
+        <v>533</v>
       </c>
     </row>
     <row r="624" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A624" s="2" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B624" s="2" t="s">
         <v>1715</v>
       </c>
-      <c r="B624" s="2" t="s">
+      <c r="C624" s="2" t="s">
         <v>1716</v>
-      </c>
-      <c r="C624" s="2" t="s">
-        <v>1717</v>
       </c>
     </row>
     <row r="625" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A625" s="2" t="s">
+        <v>1717</v>
+      </c>
+      <c r="B625" s="2" t="s">
         <v>1718</v>
       </c>
-      <c r="B625" s="2" t="s">
+      <c r="C625" s="2" t="s">
         <v>1719</v>
-      </c>
-      <c r="C625" s="2" t="s">
-        <v>1720</v>
       </c>
     </row>
     <row r="626" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A626" s="2" t="s">
+        <v>1720</v>
+      </c>
+      <c r="B626" s="2" t="s">
         <v>1721</v>
       </c>
-      <c r="B626" s="2" t="s">
+      <c r="C626" s="2" t="s">
         <v>1722</v>
-      </c>
-      <c r="C626" s="2" t="s">
-        <v>1723</v>
       </c>
     </row>
     <row r="627" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A627" s="2" t="s">
+        <v>1723</v>
+      </c>
+      <c r="B627" s="2" t="s">
         <v>1724</v>
       </c>
-      <c r="B627" s="2" t="s">
+      <c r="C627" s="2" t="s">
         <v>1725</v>
-      </c>
-      <c r="C627" s="2" t="s">
-        <v>1726</v>
       </c>
     </row>
     <row r="628" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A628" s="2" t="s">
+        <v>1726</v>
+      </c>
+      <c r="B628" s="2" t="s">
         <v>1727</v>
       </c>
-      <c r="B628" s="2" t="s">
+      <c r="C628" s="2" t="s">
         <v>1728</v>
-      </c>
-      <c r="C628" s="2" t="s">
-        <v>1729</v>
       </c>
     </row>
     <row r="629" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A629" s="2" t="s">
+        <v>1729</v>
+      </c>
+      <c r="B629" s="2" t="s">
         <v>1730</v>
       </c>
-      <c r="B629" s="2" t="s">
+      <c r="C629" s="2" t="s">
         <v>1731</v>
-      </c>
-      <c r="C629" s="2" t="s">
-        <v>1732</v>
       </c>
     </row>
     <row r="630" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A630" s="2" t="s">
+        <v>1732</v>
+      </c>
+      <c r="B630" s="2" t="s">
         <v>1733</v>
       </c>
-      <c r="B630" s="2" t="s">
+      <c r="C630" s="2" t="s">
         <v>1734</v>
-      </c>
-      <c r="C630" s="2" t="s">
-        <v>1735</v>
       </c>
     </row>
     <row r="631" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A631" s="2" t="s">
+        <v>1735</v>
+      </c>
+      <c r="B631" s="2" t="s">
         <v>1736</v>
       </c>
-      <c r="B631" s="2" t="s">
+      <c r="C631" s="2" t="s">
         <v>1737</v>
-      </c>
-      <c r="C631" s="2" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="632" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13477,21 +13675,21 @@
         <v>1741</v>
       </c>
       <c r="B633" s="2" t="s">
-        <v>1742</v>
+        <v>19</v>
       </c>
       <c r="C633" s="2" t="s">
-        <v>1743</v>
+        <v>20</v>
       </c>
     </row>
     <row r="634" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A634" s="2" t="s">
+        <v>1742</v>
+      </c>
+      <c r="B634" s="2" t="s">
+        <v>1743</v>
+      </c>
+      <c r="C634" s="2" t="s">
         <v>1744</v>
-      </c>
-      <c r="B634" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="C634" s="2" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="635" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13502,1162 +13700,1162 @@
         <v>1746</v>
       </c>
       <c r="C635" s="2" t="s">
-        <v>183</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="636" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A636" s="2" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="B636" s="2" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="C636" s="2" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="637" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A637" s="2" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="B637" s="2" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="C637" s="2" t="s">
-        <v>455</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="638" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A638" s="2" t="s">
-        <v>1752</v>
+        <v>1754</v>
       </c>
       <c r="B638" s="2" t="s">
-        <v>1753</v>
+        <v>1755</v>
       </c>
       <c r="C638" s="2" t="s">
-        <v>1754</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="639" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A639" s="2" t="s">
-        <v>1755</v>
+        <v>1757</v>
       </c>
       <c r="B639" s="2" t="s">
-        <v>798</v>
+        <v>1758</v>
       </c>
       <c r="C639" s="2" t="s">
-        <v>799</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="640" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A640" s="2" t="s">
-        <v>1756</v>
+        <v>1760</v>
       </c>
       <c r="B640" s="2" t="s">
-        <v>4</v>
+        <v>1761</v>
       </c>
       <c r="C640" s="2" t="s">
-        <v>5</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="641" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A641" s="2" t="s">
-        <v>1757</v>
+        <v>1763</v>
       </c>
       <c r="B641" s="2" t="s">
-        <v>282</v>
+        <v>1764</v>
       </c>
       <c r="C641" s="2" t="s">
-        <v>283</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="642" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A642" s="2" t="s">
-        <v>1758</v>
+        <v>1766</v>
       </c>
       <c r="B642" s="2" t="s">
-        <v>1753</v>
+        <v>1767</v>
       </c>
       <c r="C642" s="2" t="s">
-        <v>1754</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="643" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A643" s="2" t="s">
-        <v>1759</v>
+        <v>1769</v>
       </c>
       <c r="B643" s="2" t="s">
-        <v>1760</v>
+        <v>1770</v>
       </c>
       <c r="C643" s="2" t="s">
-        <v>1761</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="644" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A644" s="2" t="s">
-        <v>1762</v>
+        <v>1772</v>
       </c>
       <c r="B644" s="2" t="s">
-        <v>1763</v>
+        <v>1773</v>
       </c>
       <c r="C644" s="2" t="s">
-        <v>1764</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="645" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A645" s="2" t="s">
-        <v>1765</v>
+        <v>1775</v>
       </c>
       <c r="B645" s="2" t="s">
-        <v>1766</v>
+        <v>1776</v>
       </c>
       <c r="C645" s="2" t="s">
-        <v>1767</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="646" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A646" s="2" t="s">
-        <v>1768</v>
+        <v>1778</v>
       </c>
       <c r="B646" s="2" t="s">
-        <v>1769</v>
+        <v>1779</v>
       </c>
       <c r="C646" s="2" t="s">
-        <v>1770</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="647" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A647" s="2" t="s">
-        <v>1771</v>
+        <v>1781</v>
       </c>
       <c r="B647" s="2" t="s">
-        <v>1772</v>
+        <v>1782</v>
       </c>
       <c r="C647" s="2" t="s">
-        <v>1773</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="648" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A648" s="2" t="s">
-        <v>1774</v>
+        <v>1784</v>
       </c>
       <c r="B648" s="2" t="s">
-        <v>1775</v>
+        <v>744</v>
       </c>
       <c r="C648" s="2" t="s">
-        <v>1776</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="649" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A649" s="2" t="s">
-        <v>1777</v>
+        <v>1786</v>
       </c>
       <c r="B649" s="2" t="s">
-        <v>1778</v>
+        <v>1787</v>
       </c>
       <c r="C649" s="2" t="s">
-        <v>1779</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="650" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A650" s="2" t="s">
-        <v>1780</v>
+        <v>1789</v>
       </c>
       <c r="B650" s="2" t="s">
-        <v>1781</v>
+        <v>1790</v>
       </c>
       <c r="C650" s="2" t="s">
-        <v>1782</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="651" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A651" s="2" t="s">
-        <v>1783</v>
+        <v>1792</v>
       </c>
       <c r="B651" s="2" t="s">
-        <v>19</v>
+        <v>1793</v>
       </c>
       <c r="C651" s="2" t="s">
-        <v>20</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="652" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A652" s="2" t="s">
-        <v>1784</v>
+        <v>1795</v>
       </c>
       <c r="B652" s="2" t="s">
-        <v>13</v>
+        <v>1796</v>
       </c>
       <c r="C652" s="2" t="s">
-        <v>14</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="653" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A653" s="2" t="s">
-        <v>1785</v>
+        <v>1798</v>
       </c>
       <c r="B653" s="2" t="s">
-        <v>16</v>
+        <v>1799</v>
       </c>
       <c r="C653" s="2" t="s">
-        <v>17</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="654" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A654" s="2" t="s">
-        <v>1786</v>
+        <v>1801</v>
       </c>
       <c r="B654" s="2" t="s">
-        <v>1787</v>
+        <v>1802</v>
       </c>
       <c r="C654" s="2" t="s">
-        <v>1788</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="655" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A655" s="2" t="s">
-        <v>1789</v>
+        <v>1804</v>
       </c>
       <c r="B655" s="2" t="s">
-        <v>1790</v>
+        <v>1805</v>
       </c>
       <c r="C655" s="2" t="s">
-        <v>1791</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="656" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A656" s="2" t="s">
-        <v>1792</v>
+        <v>1807</v>
       </c>
       <c r="B656" s="2" t="s">
-        <v>1793</v>
+        <v>1808</v>
       </c>
       <c r="C656" s="2" t="s">
-        <v>1794</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="657" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A657" s="2" t="s">
-        <v>1795</v>
+        <v>1810</v>
       </c>
       <c r="B657" s="2" t="s">
-        <v>1796</v>
+        <v>1811</v>
       </c>
       <c r="C657" s="2" t="s">
-        <v>1797</v>
+        <v>455</v>
       </c>
     </row>
     <row r="658" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A658" s="2" t="s">
-        <v>1798</v>
+        <v>1812</v>
       </c>
       <c r="B658" s="2" t="s">
-        <v>1699</v>
+        <v>1813</v>
       </c>
       <c r="C658" s="2" t="s">
-        <v>1700</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="659" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A659" s="2" t="s">
-        <v>1799</v>
+        <v>1815</v>
       </c>
       <c r="B659" s="2" t="s">
-        <v>1702</v>
+        <v>1816</v>
       </c>
       <c r="C659" s="2" t="s">
-        <v>1703</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="660" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A660" s="2" t="s">
-        <v>1800</v>
+        <v>1818</v>
       </c>
       <c r="B660" s="2" t="s">
-        <v>1801</v>
+        <v>276</v>
       </c>
       <c r="C660" s="2" t="s">
-        <v>1208</v>
+        <v>277</v>
       </c>
     </row>
     <row r="661" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A661" s="2" t="s">
-        <v>1802</v>
+        <v>1819</v>
       </c>
       <c r="B661" s="2" t="s">
-        <v>1803</v>
+        <v>1820</v>
       </c>
       <c r="C661" s="2" t="s">
-        <v>1804</v>
+        <v>183</v>
       </c>
     </row>
     <row r="662" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A662" s="2" t="s">
-        <v>1805</v>
+        <v>1821</v>
       </c>
       <c r="B662" s="2" t="s">
-        <v>1054</v>
+        <v>1822</v>
       </c>
       <c r="C662" s="2" t="s">
-        <v>1055</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="663" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A663" s="2" t="s">
-        <v>1806</v>
+        <v>1824</v>
       </c>
       <c r="B663" s="2" t="s">
-        <v>1807</v>
+        <v>1825</v>
       </c>
       <c r="C663" s="2" t="s">
-        <v>1712</v>
+        <v>455</v>
       </c>
     </row>
     <row r="664" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A664" s="2" t="s">
-        <v>1808</v>
+        <v>1826</v>
       </c>
       <c r="B664" s="2" t="s">
-        <v>713</v>
+        <v>1827</v>
       </c>
       <c r="C664" s="2" t="s">
-        <v>1714</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="665" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A665" s="2" t="s">
-        <v>1809</v>
+        <v>1829</v>
       </c>
       <c r="B665" s="2" t="s">
-        <v>1810</v>
+        <v>851</v>
       </c>
       <c r="C665" s="2" t="s">
-        <v>1811</v>
+        <v>852</v>
       </c>
     </row>
     <row r="666" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A666" s="2" t="s">
-        <v>1812</v>
+        <v>1830</v>
       </c>
       <c r="B666" s="2" t="s">
-        <v>1813</v>
+        <v>4</v>
       </c>
       <c r="C666" s="2" t="s">
-        <v>1804</v>
+        <v>5</v>
       </c>
     </row>
     <row r="667" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A667" s="2" t="s">
-        <v>1814</v>
+        <v>1831</v>
       </c>
       <c r="B667" s="2" t="s">
-        <v>782</v>
+        <v>282</v>
       </c>
       <c r="C667" s="2" t="s">
-        <v>1815</v>
+        <v>283</v>
       </c>
     </row>
     <row r="668" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A668" s="2" t="s">
-        <v>1816</v>
+        <v>1832</v>
       </c>
       <c r="B668" s="2" t="s">
-        <v>794</v>
+        <v>1827</v>
       </c>
       <c r="C668" s="2" t="s">
-        <v>1817</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="669" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A669" s="2" t="s">
-        <v>1818</v>
+        <v>1833</v>
       </c>
       <c r="B669" s="2" t="s">
-        <v>517</v>
+        <v>1834</v>
       </c>
       <c r="C669" s="2" t="s">
-        <v>455</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="670" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A670" s="2" t="s">
-        <v>1819</v>
+        <v>1836</v>
       </c>
       <c r="B670" s="2" t="s">
-        <v>798</v>
+        <v>1837</v>
       </c>
       <c r="C670" s="2" t="s">
-        <v>799</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="671" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A671" s="2" t="s">
-        <v>1820</v>
+        <v>1839</v>
       </c>
       <c r="B671" s="2" t="s">
-        <v>282</v>
+        <v>1840</v>
       </c>
       <c r="C671" s="2" t="s">
-        <v>283</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="672" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A672" s="2" t="s">
-        <v>1821</v>
+        <v>1842</v>
       </c>
       <c r="B672" s="2" t="s">
-        <v>1822</v>
+        <v>1843</v>
       </c>
       <c r="C672" s="2" t="s">
-        <v>1823</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="673" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A673" s="2" t="s">
-        <v>1824</v>
+        <v>1845</v>
       </c>
       <c r="B673" s="2" t="s">
-        <v>1825</v>
+        <v>1846</v>
       </c>
       <c r="C673" s="2" t="s">
-        <v>1826</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="674" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A674" s="2" t="s">
-        <v>1827</v>
+        <v>1848</v>
       </c>
       <c r="B674" s="2" t="s">
-        <v>1828</v>
+        <v>1849</v>
       </c>
       <c r="C674" s="2" t="s">
-        <v>1829</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="675" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A675" s="2" t="s">
-        <v>1830</v>
+        <v>1851</v>
       </c>
       <c r="B675" s="2" t="s">
-        <v>826</v>
+        <v>1852</v>
       </c>
       <c r="C675" s="2" t="s">
-        <v>827</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="676" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A676" s="2" t="s">
-        <v>1831</v>
+        <v>1854</v>
       </c>
       <c r="B676" s="2" t="s">
-        <v>794</v>
+        <v>1855</v>
       </c>
       <c r="C676" s="2" t="s">
-        <v>1817</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="677" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A677" s="2" t="s">
-        <v>1832</v>
+        <v>1857</v>
       </c>
       <c r="B677" s="2" t="s">
-        <v>830</v>
+        <v>19</v>
       </c>
       <c r="C677" s="2" t="s">
-        <v>831</v>
+        <v>20</v>
       </c>
     </row>
     <row r="678" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A678" s="2" t="s">
-        <v>1833</v>
+        <v>1858</v>
       </c>
       <c r="B678" s="2" t="s">
-        <v>1834</v>
+        <v>13</v>
       </c>
       <c r="C678" s="2" t="s">
-        <v>1835</v>
+        <v>14</v>
       </c>
     </row>
     <row r="679" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A679" s="2" t="s">
-        <v>1836</v>
+        <v>1859</v>
       </c>
       <c r="B679" s="2" t="s">
-        <v>836</v>
+        <v>16</v>
       </c>
       <c r="C679" s="2" t="s">
-        <v>1837</v>
+        <v>17</v>
       </c>
     </row>
     <row r="680" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A680" s="2" t="s">
-        <v>1838</v>
+        <v>1860</v>
       </c>
       <c r="B680" s="2" t="s">
-        <v>1839</v>
+        <v>1861</v>
       </c>
       <c r="C680" s="2" t="s">
-        <v>1840</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="681" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A681" s="2" t="s">
-        <v>1841</v>
+        <v>1863</v>
       </c>
       <c r="B681" s="2" t="s">
-        <v>842</v>
+        <v>1864</v>
       </c>
       <c r="C681" s="2" t="s">
-        <v>1842</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="682" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A682" s="2" t="s">
-        <v>1843</v>
+        <v>1866</v>
       </c>
       <c r="B682" s="2" t="s">
-        <v>1844</v>
+        <v>1867</v>
       </c>
       <c r="C682" s="2" t="s">
-        <v>1845</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="683" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A683" s="2" t="s">
-        <v>1846</v>
+        <v>1869</v>
       </c>
       <c r="B683" s="2" t="s">
-        <v>1847</v>
+        <v>1870</v>
       </c>
       <c r="C683" s="2" t="s">
-        <v>1848</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="684" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A684" s="2" t="s">
-        <v>1849</v>
+        <v>1872</v>
       </c>
       <c r="B684" s="2" t="s">
-        <v>1850</v>
+        <v>1770</v>
       </c>
       <c r="C684" s="2" t="s">
-        <v>1851</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="685" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A685" s="2" t="s">
-        <v>1852</v>
+        <v>1873</v>
       </c>
       <c r="B685" s="2" t="s">
-        <v>694</v>
+        <v>1773</v>
       </c>
       <c r="C685" s="2" t="s">
-        <v>695</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="686" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A686" s="2" t="s">
-        <v>1853</v>
+        <v>1874</v>
       </c>
       <c r="B686" s="2" t="s">
-        <v>852</v>
+        <v>1875</v>
       </c>
       <c r="C686" s="2" t="s">
-        <v>853</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="687" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A687" s="2" t="s">
-        <v>1854</v>
+        <v>1876</v>
       </c>
       <c r="B687" s="2" t="s">
-        <v>855</v>
+        <v>1877</v>
       </c>
       <c r="C687" s="2" t="s">
-        <v>1855</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="688" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A688" s="2" t="s">
-        <v>1856</v>
+        <v>1879</v>
       </c>
       <c r="B688" s="2" t="s">
-        <v>858</v>
+        <v>1107</v>
       </c>
       <c r="C688" s="2" t="s">
-        <v>1857</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="689" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A689" s="2" t="s">
-        <v>1858</v>
+        <v>1880</v>
       </c>
       <c r="B689" s="2" t="s">
-        <v>861</v>
+        <v>1881</v>
       </c>
       <c r="C689" s="2" t="s">
-        <v>1859</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="690" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A690" s="2" t="s">
-        <v>1860</v>
+        <v>1882</v>
       </c>
       <c r="B690" s="2" t="s">
-        <v>1861</v>
+        <v>744</v>
       </c>
       <c r="C690" s="2" t="s">
-        <v>1862</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="691" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A691" s="2" t="s">
-        <v>1863</v>
+        <v>1883</v>
       </c>
       <c r="B691" s="2" t="s">
-        <v>1699</v>
+        <v>1884</v>
       </c>
       <c r="C691" s="2" t="s">
-        <v>1700</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="692" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A692" s="2" t="s">
-        <v>1864</v>
+        <v>1886</v>
       </c>
       <c r="B692" s="2" t="s">
-        <v>1702</v>
+        <v>1887</v>
       </c>
       <c r="C692" s="2" t="s">
-        <v>1703</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="693" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A693" s="2" t="s">
-        <v>1865</v>
+        <v>1888</v>
       </c>
       <c r="B693" s="2" t="s">
-        <v>1866</v>
+        <v>835</v>
       </c>
       <c r="C693" s="2" t="s">
-        <v>1867</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="694" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A694" s="2" t="s">
-        <v>1868</v>
+        <v>1890</v>
       </c>
       <c r="B694" s="2" t="s">
-        <v>1869</v>
+        <v>847</v>
       </c>
       <c r="C694" s="2" t="s">
-        <v>1870</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="695" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A695" s="2" t="s">
-        <v>1871</v>
+        <v>1892</v>
       </c>
       <c r="B695" s="2" t="s">
-        <v>1872</v>
+        <v>535</v>
       </c>
       <c r="C695" s="2" t="s">
-        <v>1873</v>
+        <v>455</v>
       </c>
     </row>
     <row r="696" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A696" s="2" t="s">
-        <v>1874</v>
+        <v>1893</v>
       </c>
       <c r="B696" s="2" t="s">
-        <v>1875</v>
+        <v>851</v>
       </c>
       <c r="C696" s="2" t="s">
-        <v>1876</v>
+        <v>852</v>
       </c>
     </row>
     <row r="697" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A697" s="2" t="s">
-        <v>1877</v>
+        <v>1894</v>
       </c>
       <c r="B697" s="2" t="s">
-        <v>1878</v>
+        <v>282</v>
       </c>
       <c r="C697" s="2" t="s">
-        <v>1879</v>
+        <v>283</v>
       </c>
     </row>
     <row r="698" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A698" s="2" t="s">
-        <v>1880</v>
+        <v>1895</v>
       </c>
       <c r="B698" s="2" t="s">
-        <v>1881</v>
+        <v>1896</v>
       </c>
       <c r="C698" s="2" t="s">
-        <v>1882</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="699" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A699" s="2" t="s">
-        <v>1883</v>
+        <v>1898</v>
       </c>
       <c r="B699" s="2" t="s">
-        <v>433</v>
+        <v>1899</v>
       </c>
       <c r="C699" s="2" t="s">
-        <v>434</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="700" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A700" s="2" t="s">
-        <v>1884</v>
+        <v>1901</v>
       </c>
       <c r="B700" s="2" t="s">
-        <v>1885</v>
+        <v>1902</v>
       </c>
       <c r="C700" s="2" t="s">
-        <v>1886</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="701" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A701" s="2" t="s">
-        <v>1887</v>
+        <v>1904</v>
       </c>
       <c r="B701" s="2" t="s">
-        <v>1888</v>
+        <v>879</v>
       </c>
       <c r="C701" s="2" t="s">
-        <v>1889</v>
+        <v>880</v>
       </c>
     </row>
     <row r="702" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A702" s="2" t="s">
-        <v>1890</v>
+        <v>1905</v>
       </c>
       <c r="B702" s="2" t="s">
-        <v>445</v>
+        <v>847</v>
       </c>
       <c r="C702" s="2" t="s">
-        <v>515</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="703" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A703" s="2" t="s">
-        <v>1891</v>
+        <v>1906</v>
       </c>
       <c r="B703" s="2" t="s">
-        <v>451</v>
+        <v>883</v>
       </c>
       <c r="C703" s="2" t="s">
-        <v>1892</v>
+        <v>884</v>
       </c>
     </row>
     <row r="704" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A704" s="2" t="s">
-        <v>1893</v>
+        <v>1907</v>
       </c>
       <c r="B704" s="2" t="s">
-        <v>484</v>
+        <v>1908</v>
       </c>
       <c r="C704" s="2" t="s">
-        <v>1894</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="705" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A705" s="2" t="s">
-        <v>1895</v>
+        <v>1910</v>
       </c>
       <c r="B705" s="2" t="s">
-        <v>487</v>
+        <v>889</v>
       </c>
       <c r="C705" s="2" t="s">
-        <v>1896</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="706" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A706" s="2" t="s">
-        <v>1897</v>
+        <v>1912</v>
       </c>
       <c r="B706" s="2" t="s">
-        <v>1898</v>
+        <v>1913</v>
       </c>
       <c r="C706" s="2" t="s">
-        <v>1899</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="707" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A707" s="2" t="s">
-        <v>1900</v>
+        <v>1915</v>
       </c>
       <c r="B707" s="2" t="s">
-        <v>1901</v>
+        <v>895</v>
       </c>
       <c r="C707" s="2" t="s">
-        <v>1902</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="708" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A708" s="2" t="s">
-        <v>1903</v>
+        <v>1917</v>
       </c>
       <c r="B708" s="2" t="s">
-        <v>1904</v>
+        <v>1918</v>
       </c>
       <c r="C708" s="2" t="s">
-        <v>1905</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="709" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A709" s="2" t="s">
-        <v>1906</v>
+        <v>1920</v>
       </c>
       <c r="B709" s="2" t="s">
-        <v>454</v>
+        <v>1921</v>
       </c>
       <c r="C709" s="2" t="s">
-        <v>455</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="710" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A710" s="2" t="s">
-        <v>1907</v>
+        <v>1923</v>
       </c>
       <c r="B710" s="2" t="s">
-        <v>1908</v>
+        <v>1924</v>
       </c>
       <c r="C710" s="2" t="s">
-        <v>1909</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="711" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A711" s="2" t="s">
-        <v>1910</v>
+        <v>1926</v>
       </c>
       <c r="B711" s="2" t="s">
-        <v>466</v>
+        <v>725</v>
       </c>
       <c r="C711" s="2" t="s">
-        <v>467</v>
+        <v>726</v>
       </c>
     </row>
     <row r="712" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A712" s="2" t="s">
-        <v>1911</v>
+        <v>1927</v>
       </c>
       <c r="B712" s="2" t="s">
-        <v>472</v>
+        <v>905</v>
       </c>
       <c r="C712" s="2" t="s">
-        <v>473</v>
+        <v>906</v>
       </c>
     </row>
     <row r="713" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A713" s="2" t="s">
-        <v>1912</v>
+        <v>1928</v>
       </c>
       <c r="B713" s="2" t="s">
-        <v>1913</v>
+        <v>908</v>
       </c>
       <c r="C713" s="2" t="s">
-        <v>1914</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="714" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A714" s="2" t="s">
-        <v>1915</v>
+        <v>1930</v>
       </c>
       <c r="B714" s="2" t="s">
-        <v>475</v>
+        <v>911</v>
       </c>
       <c r="C714" s="2" t="s">
-        <v>209</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="715" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A715" s="2" t="s">
-        <v>1916</v>
+        <v>1932</v>
       </c>
       <c r="B715" s="2" t="s">
-        <v>478</v>
+        <v>914</v>
       </c>
       <c r="C715" s="2" t="s">
-        <v>1917</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="716" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A716" s="2" t="s">
-        <v>1918</v>
+        <v>1934</v>
       </c>
       <c r="B716" s="2" t="s">
-        <v>502</v>
+        <v>1935</v>
       </c>
       <c r="C716" s="2" t="s">
-        <v>1919</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="717" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A717" s="2" t="s">
-        <v>1920</v>
+        <v>1937</v>
       </c>
       <c r="B717" s="2" t="s">
-        <v>1921</v>
+        <v>1770</v>
       </c>
       <c r="C717" s="2" t="s">
-        <v>1922</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="718" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A718" s="2" t="s">
-        <v>1923</v>
+        <v>1938</v>
       </c>
       <c r="B718" s="2" t="s">
-        <v>1924</v>
+        <v>1773</v>
       </c>
       <c r="C718" s="2" t="s">
-        <v>1925</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="719" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A719" s="2" t="s">
-        <v>1926</v>
+        <v>1939</v>
       </c>
       <c r="B719" s="2" t="s">
-        <v>1927</v>
+        <v>1940</v>
       </c>
       <c r="C719" s="2" t="s">
-        <v>1928</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="720" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A720" s="2" t="s">
-        <v>1929</v>
+        <v>1942</v>
       </c>
       <c r="B720" s="2" t="s">
-        <v>1930</v>
+        <v>1943</v>
       </c>
       <c r="C720" s="2" t="s">
-        <v>1931</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="721" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A721" s="2" t="s">
-        <v>1932</v>
+        <v>1945</v>
       </c>
       <c r="B721" s="2" t="s">
-        <v>1933</v>
+        <v>1946</v>
       </c>
       <c r="C721" s="2" t="s">
-        <v>1934</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="722" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A722" s="2" t="s">
-        <v>1935</v>
+        <v>1948</v>
       </c>
       <c r="B722" s="2" t="s">
-        <v>1936</v>
+        <v>1949</v>
       </c>
       <c r="C722" s="2" t="s">
-        <v>1937</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="723" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A723" s="2" t="s">
-        <v>1938</v>
+        <v>1951</v>
       </c>
       <c r="B723" s="2" t="s">
-        <v>1939</v>
+        <v>1952</v>
       </c>
       <c r="C723" s="2" t="s">
-        <v>1940</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="724" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A724" s="2" t="s">
-        <v>1941</v>
+        <v>1954</v>
       </c>
       <c r="B724" s="2" t="s">
-        <v>1942</v>
+        <v>1955</v>
       </c>
       <c r="C724" s="2" t="s">
-        <v>1943</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="725" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A725" s="2" t="s">
-        <v>1944</v>
+        <v>1957</v>
       </c>
       <c r="B725" s="2" t="s">
-        <v>1945</v>
+        <v>433</v>
       </c>
       <c r="C725" s="2" t="s">
-        <v>1946</v>
+        <v>434</v>
       </c>
     </row>
     <row r="726" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A726" s="2" t="s">
-        <v>1947</v>
+        <v>1958</v>
       </c>
       <c r="B726" s="2" t="s">
-        <v>1948</v>
+        <v>1959</v>
       </c>
       <c r="C726" s="2" t="s">
-        <v>1949</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="727" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A727" s="2" t="s">
-        <v>1950</v>
+        <v>1961</v>
       </c>
       <c r="B727" s="2" t="s">
-        <v>1951</v>
+        <v>1962</v>
       </c>
       <c r="C727" s="2" t="s">
-        <v>1952</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="728" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A728" s="2" t="s">
-        <v>1953</v>
+        <v>1964</v>
       </c>
       <c r="B728" s="2" t="s">
-        <v>1954</v>
+        <v>445</v>
       </c>
       <c r="C728" s="2" t="s">
-        <v>1955</v>
+        <v>533</v>
       </c>
     </row>
     <row r="729" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A729" s="2" t="s">
-        <v>1956</v>
+        <v>1965</v>
       </c>
       <c r="B729" s="2" t="s">
-        <v>1957</v>
+        <v>451</v>
       </c>
       <c r="C729" s="2" t="s">
-        <v>1637</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="730" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A730" s="2" t="s">
-        <v>1958</v>
+        <v>1967</v>
       </c>
       <c r="B730" s="2" t="s">
-        <v>1959</v>
+        <v>484</v>
       </c>
       <c r="C730" s="2" t="s">
-        <v>1960</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="731" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A731" s="2" t="s">
-        <v>1961</v>
+        <v>1969</v>
       </c>
       <c r="B731" s="2" t="s">
-        <v>1962</v>
+        <v>487</v>
       </c>
       <c r="C731" s="2" t="s">
-        <v>1963</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="732" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A732" s="2" t="s">
-        <v>1964</v>
+        <v>1971</v>
       </c>
       <c r="B732" s="2" t="s">
-        <v>1965</v>
+        <v>1972</v>
       </c>
       <c r="C732" s="2" t="s">
-        <v>1966</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="733" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A733" s="2" t="s">
-        <v>1967</v>
+        <v>1974</v>
       </c>
       <c r="B733" s="2" t="s">
-        <v>1968</v>
+        <v>1975</v>
       </c>
       <c r="C733" s="2" t="s">
-        <v>217</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="734" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A734" s="2" t="s">
-        <v>1969</v>
+        <v>1977</v>
       </c>
       <c r="B734" s="2" t="s">
-        <v>1970</v>
+        <v>1978</v>
       </c>
       <c r="C734" s="2" t="s">
-        <v>1971</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="735" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A735" s="2" t="s">
-        <v>1972</v>
+        <v>1980</v>
       </c>
       <c r="B735" s="2" t="s">
-        <v>1973</v>
+        <v>454</v>
       </c>
       <c r="C735" s="2" t="s">
-        <v>1974</v>
+        <v>455</v>
       </c>
     </row>
     <row r="736" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A736" s="2" t="s">
-        <v>1975</v>
+        <v>1981</v>
       </c>
       <c r="B736" s="2" t="s">
-        <v>1976</v>
+        <v>1982</v>
       </c>
       <c r="C736" s="2" t="s">
-        <v>1977</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="737" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A737" s="2" t="s">
-        <v>1978</v>
+        <v>1984</v>
       </c>
       <c r="B737" s="2" t="s">
-        <v>1979</v>
+        <v>466</v>
       </c>
       <c r="C737" s="2" t="s">
-        <v>1980</v>
+        <v>467</v>
       </c>
     </row>
     <row r="738" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A738" s="2" t="s">
-        <v>1981</v>
+        <v>1985</v>
       </c>
       <c r="B738" s="2" t="s">
-        <v>1982</v>
+        <v>472</v>
       </c>
       <c r="C738" s="2" t="s">
-        <v>1983</v>
+        <v>473</v>
       </c>
     </row>
     <row r="739" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A739" s="2" t="s">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="B739" s="2" t="s">
-        <v>1985</v>
+        <v>1987</v>
       </c>
       <c r="C739" s="2" t="s">
-        <v>1986</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="740" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A740" s="2" t="s">
-        <v>1987</v>
+        <v>1989</v>
       </c>
       <c r="B740" s="2" t="s">
-        <v>1988</v>
+        <v>475</v>
       </c>
       <c r="C740" s="2" t="s">
-        <v>1989</v>
+        <v>209</v>
       </c>
     </row>
     <row r="741" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14665,186 +14863,472 @@
         <v>1990</v>
       </c>
       <c r="B741" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="C741" s="2" t="s">
         <v>1991</v>
-      </c>
-      <c r="C741" s="2" t="s">
-        <v>1992</v>
       </c>
     </row>
     <row r="742" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A742" s="2" t="s">
+        <v>1992</v>
+      </c>
+      <c r="B742" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="C742" s="2" t="s">
         <v>1993</v>
-      </c>
-      <c r="B742" s="2" t="s">
-        <v>1994</v>
-      </c>
-      <c r="C742" s="2" t="s">
-        <v>1995</v>
       </c>
     </row>
     <row r="743" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A743" s="2" t="s">
+        <v>1994</v>
+      </c>
+      <c r="B743" s="2" t="s">
+        <v>1995</v>
+      </c>
+      <c r="C743" s="2" t="s">
         <v>1996</v>
-      </c>
-      <c r="B743" s="2" t="s">
-        <v>1997</v>
-      </c>
-      <c r="C743" s="2" t="s">
-        <v>1998</v>
       </c>
     </row>
     <row r="744" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A744" s="2" t="s">
-        <v>1999</v>
+        <v>1997</v>
       </c>
       <c r="B744" s="2" t="s">
-        <v>2000</v>
+        <v>502</v>
       </c>
       <c r="C744" s="2" t="s">
-        <v>2001</v>
+        <v>503</v>
       </c>
     </row>
     <row r="745" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A745" s="2" t="s">
-        <v>2002</v>
+        <v>1998</v>
       </c>
       <c r="B745" s="2" t="s">
-        <v>2003</v>
+        <v>1999</v>
       </c>
       <c r="C745" s="2" t="s">
-        <v>2004</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="746" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A746" s="2" t="s">
-        <v>2005</v>
+        <v>2001</v>
       </c>
       <c r="B746" s="2" t="s">
-        <v>2006</v>
+        <v>2002</v>
       </c>
       <c r="C746" s="2" t="s">
-        <v>2007</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="747" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A747" s="2" t="s">
-        <v>2008</v>
+        <v>2004</v>
       </c>
       <c r="B747" s="2" t="s">
-        <v>2009</v>
+        <v>2005</v>
       </c>
       <c r="C747" s="2" t="s">
-        <v>2010</v>
+        <v>512</v>
       </c>
     </row>
     <row r="748" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A748" s="2" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="B748" s="2" t="s">
-        <v>2012</v>
+        <v>2007</v>
       </c>
       <c r="C748" s="2" t="s">
-        <v>2013</v>
+        <v>515</v>
       </c>
     </row>
     <row r="749" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A749" s="2" t="s">
-        <v>2014</v>
+        <v>2008</v>
       </c>
       <c r="B749" s="2" t="s">
-        <v>2015</v>
+        <v>2009</v>
       </c>
       <c r="C749" s="2" t="s">
-        <v>2016</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="750" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A750" s="2" t="s">
-        <v>2017</v>
+        <v>2011</v>
       </c>
       <c r="B750" s="2" t="s">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="C750" s="2" t="s">
-        <v>2019</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="751" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A751" s="2" t="s">
-        <v>2020</v>
+        <v>2014</v>
       </c>
       <c r="B751" s="2" t="s">
-        <v>2021</v>
+        <v>2015</v>
       </c>
       <c r="C751" s="2" t="s">
-        <v>2022</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="752" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A752" s="2" t="s">
-        <v>2023</v>
+        <v>2017</v>
       </c>
       <c r="B752" s="2" t="s">
-        <v>2024</v>
+        <v>2018</v>
       </c>
       <c r="C752" s="2" t="s">
-        <v>2025</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="753" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A753" s="2" t="s">
-        <v>2026</v>
+        <v>2020</v>
       </c>
       <c r="B753" s="2" t="s">
-        <v>2027</v>
+        <v>2021</v>
       </c>
       <c r="C753" s="2" t="s">
-        <v>2028</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="754" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A754" s="2" t="s">
-        <v>2029</v>
+        <v>2023</v>
       </c>
       <c r="B754" s="2" t="s">
-        <v>175</v>
+        <v>2024</v>
       </c>
       <c r="C754" s="2" t="s">
-        <v>176</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="755" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A755" s="2" t="s">
-        <v>2030</v>
+        <v>2026</v>
       </c>
       <c r="B755" s="2" t="s">
-        <v>2031</v>
+        <v>2027</v>
       </c>
       <c r="C755" s="2" t="s">
-        <v>2032</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="756" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A756" s="2" t="s">
-        <v>2033</v>
+        <v>2028</v>
       </c>
       <c r="B756" s="2" t="s">
-        <v>2034</v>
+        <v>2029</v>
       </c>
       <c r="C756" s="2" t="s">
-        <v>2035</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="757" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A757" s="2" t="s">
+        <v>2031</v>
+      </c>
+      <c r="B757" s="2" t="s">
+        <v>2032</v>
+      </c>
+      <c r="C757" s="2" t="s">
+        <v>2033</v>
+      </c>
+    </row>
+    <row r="758" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A758" s="2" t="s">
+        <v>2034</v>
+      </c>
+      <c r="B758" s="2" t="s">
+        <v>2035</v>
+      </c>
+      <c r="C758" s="2" t="s">
         <v>2036</v>
       </c>
-      <c r="B757" s="2" t="s">
+    </row>
+    <row r="759" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A759" s="2" t="s">
         <v>2037</v>
       </c>
-      <c r="C757" s="2" t="s">
+      <c r="B759" s="2" t="s">
         <v>2038</v>
+      </c>
+      <c r="C759" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="760" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A760" s="2" t="s">
+        <v>2039</v>
+      </c>
+      <c r="B760" s="2" t="s">
+        <v>2040</v>
+      </c>
+      <c r="C760" s="2" t="s">
+        <v>2041</v>
+      </c>
+    </row>
+    <row r="761" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A761" s="2" t="s">
+        <v>2042</v>
+      </c>
+      <c r="B761" s="2" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C761" s="2" t="s">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="762" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A762" s="2" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B762" s="2" t="s">
+        <v>2046</v>
+      </c>
+      <c r="C762" s="2" t="s">
+        <v>2047</v>
+      </c>
+    </row>
+    <row r="763" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A763" s="2" t="s">
+        <v>2048</v>
+      </c>
+      <c r="B763" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="C763" s="2" t="s">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="764" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A764" s="2" t="s">
+        <v>2051</v>
+      </c>
+      <c r="B764" s="2" t="s">
+        <v>2052</v>
+      </c>
+      <c r="C764" s="2" t="s">
+        <v>2053</v>
+      </c>
+    </row>
+    <row r="765" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A765" s="2" t="s">
+        <v>2054</v>
+      </c>
+      <c r="B765" s="2" t="s">
+        <v>2055</v>
+      </c>
+      <c r="C765" s="2" t="s">
+        <v>2056</v>
+      </c>
+    </row>
+    <row r="766" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A766" s="2" t="s">
+        <v>2057</v>
+      </c>
+      <c r="B766" s="2" t="s">
+        <v>2058</v>
+      </c>
+      <c r="C766" s="2" t="s">
+        <v>2059</v>
+      </c>
+    </row>
+    <row r="767" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A767" s="2" t="s">
+        <v>2060</v>
+      </c>
+      <c r="B767" s="2" t="s">
+        <v>2061</v>
+      </c>
+      <c r="C767" s="2" t="s">
+        <v>2062</v>
+      </c>
+    </row>
+    <row r="768" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A768" s="2" t="s">
+        <v>2063</v>
+      </c>
+      <c r="B768" s="2" t="s">
+        <v>2064</v>
+      </c>
+      <c r="C768" s="2" t="s">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="769" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A769" s="2" t="s">
+        <v>2066</v>
+      </c>
+      <c r="B769" s="2" t="s">
+        <v>2067</v>
+      </c>
+      <c r="C769" s="2" t="s">
+        <v>2068</v>
+      </c>
+    </row>
+    <row r="770" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A770" s="2" t="s">
+        <v>2069</v>
+      </c>
+      <c r="B770" s="2" t="s">
+        <v>2070</v>
+      </c>
+      <c r="C770" s="2" t="s">
+        <v>2071</v>
+      </c>
+    </row>
+    <row r="771" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A771" s="2" t="s">
+        <v>2072</v>
+      </c>
+      <c r="B771" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="C771" s="2" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="772" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A772" s="2" t="s">
+        <v>2073</v>
+      </c>
+      <c r="B772" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="C772" s="2" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="773" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A773" s="2" t="s">
+        <v>2074</v>
+      </c>
+      <c r="B773" s="2" t="s">
+        <v>2075</v>
+      </c>
+      <c r="C773" s="2" t="s">
+        <v>2076</v>
+      </c>
+    </row>
+    <row r="774" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A774" s="2" t="s">
+        <v>2077</v>
+      </c>
+      <c r="B774" s="2" t="s">
+        <v>2078</v>
+      </c>
+      <c r="C774" s="2" t="s">
+        <v>2079</v>
+      </c>
+    </row>
+    <row r="775" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A775" s="2" t="s">
+        <v>2080</v>
+      </c>
+      <c r="B775" s="2" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C775" s="2" t="s">
+        <v>2082</v>
+      </c>
+    </row>
+    <row r="776" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A776" s="2" t="s">
+        <v>2083</v>
+      </c>
+      <c r="B776" s="2" t="s">
+        <v>2084</v>
+      </c>
+      <c r="C776" s="2" t="s">
+        <v>2085</v>
+      </c>
+    </row>
+    <row r="777" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A777" s="2" t="s">
+        <v>2086</v>
+      </c>
+      <c r="B777" s="2" t="s">
+        <v>2087</v>
+      </c>
+      <c r="C777" s="2" t="s">
+        <v>2088</v>
+      </c>
+    </row>
+    <row r="778" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A778" s="2" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B778" s="2" t="s">
+        <v>2090</v>
+      </c>
+      <c r="C778" s="2" t="s">
+        <v>2091</v>
+      </c>
+    </row>
+    <row r="779" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A779" s="2" t="s">
+        <v>2092</v>
+      </c>
+      <c r="B779" s="2" t="s">
+        <v>2093</v>
+      </c>
+      <c r="C779" s="2" t="s">
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="780" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A780" s="2" t="s">
+        <v>2095</v>
+      </c>
+      <c r="B780" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C780" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="781" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A781" s="2" t="s">
+        <v>2096</v>
+      </c>
+      <c r="B781" s="2" t="s">
+        <v>2097</v>
+      </c>
+      <c r="C781" s="2" t="s">
+        <v>2098</v>
+      </c>
+    </row>
+    <row r="782" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A782" s="2" t="s">
+        <v>2099</v>
+      </c>
+      <c r="B782" s="2" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C782" s="2" t="s">
+        <v>2101</v>
+      </c>
+    </row>
+    <row r="783" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A783" s="2" t="s">
+        <v>2102</v>
+      </c>
+      <c r="B783" s="2" t="s">
+        <v>2103</v>
+      </c>
+      <c r="C783" s="2" t="s">
+        <v>2104</v>
       </c>
     </row>
   </sheetData>

--- a/apps/workspace-web/i18n.xlsx
+++ b/apps/workspace-web/i18n.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2349" uniqueCount="2105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2355" uniqueCount="2111">
   <si>
     <t>key</t>
   </si>
@@ -2251,7 +2251,7 @@
     <t>Update failed</t>
   </si>
   <si>
-    <t>cropDialog.titleAvatar</t>
+    <t>cropDialog.title.avatar</t>
   </si>
   <si>
     <t>裁切頭像</t>
@@ -2260,7 +2260,7 @@
     <t>Crop avatar</t>
   </si>
   <si>
-    <t>cropDialog.titleBanner</t>
+    <t>cropDialog.title.banner</t>
   </si>
   <si>
     <t>裁切橫幅</t>
@@ -2269,7 +2269,16 @@
     <t>Crop banner</t>
   </si>
   <si>
-    <t>cropDialog.hintAvatar</t>
+    <t>cropDialog.title.cover</t>
+  </si>
+  <si>
+    <t>裁切封面圖</t>
+  </si>
+  <si>
+    <t>Crop cover image</t>
+  </si>
+  <si>
+    <t>cropDialog.hint.avatar</t>
   </si>
   <si>
     <t>拖曳與縮放調整擷取範圍，圓形區域即為店面實際顯示的頭像。</t>
@@ -2278,13 +2287,22 @@
     <t>Drag and zoom to choose the visible area — the circle is exactly what your store shows.</t>
   </si>
   <si>
-    <t>cropDialog.hintBanner</t>
+    <t>cropDialog.hint.banner</t>
   </si>
   <si>
     <t>拖曳與縮放調整擷取範圍。手機與大螢幕只會顯示中央區域，重點內容請置於虛線框內。</t>
   </si>
   <si>
     <t>Drag and zoom to choose the visible area. Phones and large screens only show the centre — keep key content inside the dashed box.</t>
+  </si>
+  <si>
+    <t>cropDialog.hint.cover</t>
+  </si>
+  <si>
+    <t>拖曳與縮放調整擷取範圍。列表小圖只會顯示中央正方形區域，重點內容請置於虛線框內。</t>
+  </si>
+  <si>
+    <t>Drag and zoom to choose the visible area. Small list thumbnails only show the centre square — keep key content inside the dashed box.</t>
   </si>
   <si>
     <t>cropDialog.apply</t>
@@ -6711,7 +6729,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C783"/>
+  <dimension ref="A1:C785"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -9660,32 +9678,32 @@
         <v>761</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>22</v>
+        <v>762</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>23</v>
+        <v>763</v>
       </c>
     </row>
     <row r="269" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
     </row>
     <row r="270" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>766</v>
+        <v>22</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>767</v>
+        <v>23</v>
       </c>
     </row>
     <row r="271" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9990,54 +10008,54 @@
         <v>849</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>535</v>
+        <v>850</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>455</v>
+        <v>851</v>
       </c>
     </row>
     <row r="299" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
     </row>
     <row r="300" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>282</v>
+        <v>535</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>283</v>
+        <v>455</v>
       </c>
     </row>
     <row r="301" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
     </row>
     <row r="302" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>858</v>
+        <v>282</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>859</v>
+        <v>283</v>
       </c>
     </row>
     <row r="303" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10122,32 +10140,32 @@
         <v>881</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>847</v>
+        <v>882</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>848</v>
+        <v>883</v>
       </c>
     </row>
     <row r="311" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
     </row>
     <row r="312" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>886</v>
+        <v>853</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>887</v>
+        <v>854</v>
       </c>
     </row>
     <row r="313" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10210,32 +10228,32 @@
         <v>903</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>725</v>
+        <v>904</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>726</v>
+        <v>905</v>
       </c>
     </row>
     <row r="319" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
     </row>
     <row r="320" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>908</v>
+        <v>725</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>909</v>
+        <v>726</v>
       </c>
     </row>
     <row r="321" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10276,32 +10294,32 @@
         <v>919</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>52</v>
+        <v>920</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>53</v>
+        <v>921</v>
       </c>
     </row>
     <row r="325" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
     </row>
     <row r="326" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>924</v>
+        <v>52</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>925</v>
+        <v>53</v>
       </c>
     </row>
     <row r="327" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10477,40 +10495,40 @@
         <v>972</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="343" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>416</v>
+        <v>975</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>417</v>
+        <v>976</v>
       </c>
     </row>
     <row r="344" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
     </row>
     <row r="345" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>978</v>
+        <v>416</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>979</v>
+        <v>417</v>
       </c>
     </row>
     <row r="346" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10598,26 +10616,26 @@
         <v>1002</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="354" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="355" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="C355" s="2" t="s">
         <v>1008</v>
@@ -10936,43 +10954,43 @@
         <v>1093</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>294</v>
+        <v>1094</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>295</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="385" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A385" s="2" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="C385" s="2" t="s">
-        <v>642</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="386" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A386" s="2" t="s">
-        <v>1096</v>
+        <v>1099</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>1097</v>
+        <v>294</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>1098</v>
+        <v>295</v>
       </c>
     </row>
     <row r="387" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A387" s="2" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="C387" s="2" t="s">
-        <v>1101</v>
+        <v>642</v>
       </c>
     </row>
     <row r="388" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10980,32 +10998,32 @@
         <v>1102</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>191</v>
+        <v>1103</v>
       </c>
       <c r="C388" s="2" t="s">
-        <v>192</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="389" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A389" s="2" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="B389" s="2" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="C389" s="2" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="390" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A390" s="2" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="B390" s="2" t="s">
-        <v>1107</v>
+        <v>191</v>
       </c>
       <c r="C390" s="2" t="s">
-        <v>1108</v>
+        <v>192</v>
       </c>
     </row>
     <row r="391" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11079,43 +11097,43 @@
         <v>1127</v>
       </c>
       <c r="B397" s="2" t="s">
-        <v>276</v>
+        <v>1128</v>
       </c>
       <c r="C397" s="2" t="s">
-        <v>277</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="398" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A398" s="2" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="B398" s="2" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="C398" s="2" t="s">
-        <v>1114</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="399" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A399" s="2" t="s">
-        <v>1130</v>
+        <v>1133</v>
       </c>
       <c r="B399" s="2" t="s">
-        <v>1131</v>
+        <v>276</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>1132</v>
+        <v>277</v>
       </c>
     </row>
     <row r="400" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A400" s="2" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B400" s="2" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="C400" s="2" t="s">
-        <v>1135</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="401" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11156,32 +11174,32 @@
         <v>1145</v>
       </c>
       <c r="B404" s="2" t="s">
-        <v>294</v>
+        <v>1146</v>
       </c>
       <c r="C404" s="2" t="s">
-        <v>295</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="405" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A405" s="2" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="B405" s="2" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="C405" s="2" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="406" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A406" s="2" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>1150</v>
+        <v>294</v>
       </c>
       <c r="C406" s="2" t="s">
-        <v>1151</v>
+        <v>295</v>
       </c>
     </row>
     <row r="407" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11343,29 +11361,29 @@
         <v>1194</v>
       </c>
       <c r="B421" s="2" t="s">
-        <v>350</v>
+        <v>1195</v>
       </c>
       <c r="C421" s="2" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="422" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A422" s="2" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B422" s="2" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="C422" s="2" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="423" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A423" s="2" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>1200</v>
+        <v>350</v>
       </c>
       <c r="C423" s="2" t="s">
         <v>1201</v>
@@ -11596,32 +11614,32 @@
         <v>1262</v>
       </c>
       <c r="B444" s="2" t="s">
-        <v>975</v>
+        <v>1263</v>
       </c>
       <c r="C444" s="2" t="s">
-        <v>976</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="445" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A445" s="2" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="B445" s="2" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="C445" s="2" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="446" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A446" s="2" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="B446" s="2" t="s">
-        <v>1267</v>
+        <v>981</v>
       </c>
       <c r="C446" s="2" t="s">
-        <v>1268</v>
+        <v>982</v>
       </c>
     </row>
     <row r="447" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11632,128 +11650,128 @@
         <v>1270</v>
       </c>
       <c r="C447" s="2" t="s">
-        <v>183</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="448" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A448" s="2" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="B448" s="2" t="s">
-        <v>185</v>
+        <v>1273</v>
       </c>
       <c r="C448" s="2" t="s">
-        <v>186</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="449" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A449" s="2" t="s">
-        <v>1272</v>
+        <v>1275</v>
       </c>
       <c r="B449" s="2" t="s">
-        <v>1273</v>
+        <v>1276</v>
       </c>
       <c r="C449" s="2" t="s">
-        <v>1274</v>
+        <v>183</v>
       </c>
     </row>
     <row r="450" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A450" s="2" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="B450" s="2" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="C450" s="2" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="451" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A451" s="2" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="B451" s="2" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="C451" s="2" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="452" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A452" s="2" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="B452" s="2" t="s">
-        <v>282</v>
+        <v>191</v>
       </c>
       <c r="C452" s="2" t="s">
-        <v>283</v>
+        <v>192</v>
       </c>
     </row>
     <row r="453" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A453" s="2" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="C453" s="2" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="454" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A454" s="2" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>1088</v>
+        <v>282</v>
       </c>
       <c r="C454" s="2" t="s">
-        <v>1284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="455" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A455" s="2" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>303</v>
+        <v>1287</v>
       </c>
       <c r="C455" s="2" t="s">
-        <v>304</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="456" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A456" s="2" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
       <c r="B456" s="2" t="s">
-        <v>297</v>
+        <v>1094</v>
       </c>
       <c r="C456" s="2" t="s">
-        <v>298</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="457" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A457" s="2" t="s">
-        <v>1287</v>
+        <v>1291</v>
       </c>
       <c r="B457" s="2" t="s">
-        <v>1288</v>
+        <v>303</v>
       </c>
       <c r="C457" s="2" t="s">
-        <v>1289</v>
+        <v>304</v>
       </c>
     </row>
     <row r="458" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A458" s="2" t="s">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="B458" s="2" t="s">
-        <v>1291</v>
+        <v>297</v>
       </c>
       <c r="C458" s="2" t="s">
-        <v>1292</v>
+        <v>298</v>
       </c>
     </row>
     <row r="459" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11761,109 +11779,109 @@
         <v>1293</v>
       </c>
       <c r="B459" s="2" t="s">
-        <v>313</v>
+        <v>1294</v>
       </c>
       <c r="C459" s="2" t="s">
-        <v>314</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="460" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A460" s="2" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="B460" s="2" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="C460" s="2" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="461" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A461" s="2" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="B461" s="2" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C461" s="2" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
     </row>
     <row r="462" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A462" s="2" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="B462" s="2" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="C462" s="2" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="463" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A463" s="2" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>1302</v>
+        <v>319</v>
       </c>
       <c r="C463" s="2" t="s">
-        <v>1302</v>
+        <v>320</v>
       </c>
     </row>
     <row r="464" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A464" s="2" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="B464" s="2" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="C464" s="2" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="465" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A465" s="2" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="B465" s="2" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="C465" s="2" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="466" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A466" s="2" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="B466" s="2" t="s">
-        <v>1306</v>
+        <v>1310</v>
       </c>
       <c r="C466" s="2" t="s">
-        <v>1307</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="467" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A467" s="2" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="B467" s="2" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="C467" s="2" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="468" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A468" s="2" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B468" s="2" t="s">
         <v>1312</v>
       </c>
-      <c r="B468" s="2" t="s">
+      <c r="C468" s="2" t="s">
         <v>1313</v>
-      </c>
-      <c r="C468" s="2" t="s">
-        <v>1314</v>
       </c>
     </row>
     <row r="469" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11995,29 +12013,29 @@
         <v>1349</v>
       </c>
       <c r="C480" s="2" t="s">
-        <v>1326</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="481" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A481" s="2" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="B481" s="2" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="C481" s="2" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="482" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A482" s="2" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B482" s="2" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="C482" s="2" t="s">
-        <v>1355</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="483" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12028,29 +12046,29 @@
         <v>1357</v>
       </c>
       <c r="C483" s="2" t="s">
-        <v>1332</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="484" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A484" s="2" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="B484" s="2" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="C484" s="2" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="485" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A485" s="2" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="B485" s="2" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="C485" s="2" t="s">
-        <v>1363</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="486" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12069,32 +12087,32 @@
         <v>1367</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>1216</v>
+        <v>1368</v>
       </c>
       <c r="C487" s="2" t="s">
-        <v>1216</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="488" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A488" s="2" t="s">
-        <v>1368</v>
+        <v>1370</v>
       </c>
       <c r="B488" s="2" t="s">
-        <v>1369</v>
+        <v>1371</v>
       </c>
       <c r="C488" s="2" t="s">
-        <v>1370</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="489" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A489" s="2" t="s">
-        <v>1371</v>
+        <v>1373</v>
       </c>
       <c r="B489" s="2" t="s">
-        <v>1372</v>
+        <v>1222</v>
       </c>
       <c r="C489" s="2" t="s">
-        <v>1373</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="490" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12168,32 +12186,32 @@
         <v>1392</v>
       </c>
       <c r="B496" s="2" t="s">
-        <v>1254</v>
+        <v>1393</v>
       </c>
       <c r="C496" s="2" t="s">
-        <v>1255</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="497" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A497" s="2" t="s">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="B497" s="2" t="s">
-        <v>1394</v>
+        <v>1396</v>
       </c>
       <c r="C497" s="2" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="498" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A498" s="2" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>1397</v>
+        <v>1260</v>
       </c>
       <c r="C498" s="2" t="s">
-        <v>1398</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="499" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12248,62 +12266,62 @@
         <v>1412</v>
       </c>
       <c r="C503" s="2" t="s">
-        <v>217</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="504" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A504" s="2" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="B504" s="2" t="s">
-        <v>185</v>
+        <v>1415</v>
       </c>
       <c r="C504" s="2" t="s">
-        <v>186</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="505" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A505" s="2" t="s">
-        <v>1414</v>
+        <v>1417</v>
       </c>
       <c r="B505" s="2" t="s">
-        <v>188</v>
+        <v>1418</v>
       </c>
       <c r="C505" s="2" t="s">
-        <v>189</v>
+        <v>217</v>
       </c>
     </row>
     <row r="506" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A506" s="2" t="s">
-        <v>1415</v>
+        <v>1419</v>
       </c>
       <c r="B506" s="2" t="s">
-        <v>628</v>
+        <v>185</v>
       </c>
       <c r="C506" s="2" t="s">
-        <v>629</v>
+        <v>186</v>
       </c>
     </row>
     <row r="507" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A507" s="2" t="s">
-        <v>1416</v>
+        <v>1420</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>1417</v>
+        <v>188</v>
       </c>
       <c r="C507" s="2" t="s">
-        <v>1418</v>
+        <v>189</v>
       </c>
     </row>
     <row r="508" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A508" s="2" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="B508" s="2" t="s">
-        <v>1420</v>
+        <v>628</v>
       </c>
       <c r="C508" s="2" t="s">
-        <v>1421</v>
+        <v>629</v>
       </c>
     </row>
     <row r="509" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12498,98 +12516,98 @@
         <v>1473</v>
       </c>
       <c r="B526" s="2" t="s">
-        <v>43</v>
+        <v>1474</v>
       </c>
       <c r="C526" s="2" t="s">
-        <v>44</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="527" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A527" s="2" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="B527" s="2" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
       <c r="C527" s="2" t="s">
-        <v>1098</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="528" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A528" s="2" t="s">
-        <v>1476</v>
+        <v>1479</v>
       </c>
       <c r="B528" s="2" t="s">
-        <v>1417</v>
+        <v>43</v>
       </c>
       <c r="C528" s="2" t="s">
-        <v>1418</v>
+        <v>44</v>
       </c>
     </row>
     <row r="529" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A529" s="2" t="s">
-        <v>1477</v>
+        <v>1480</v>
       </c>
       <c r="B529" s="2" t="s">
-        <v>1478</v>
+        <v>1481</v>
       </c>
       <c r="C529" s="2" t="s">
-        <v>1207</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="530" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A530" s="2" t="s">
-        <v>1479</v>
+        <v>1482</v>
       </c>
       <c r="B530" s="2" t="s">
-        <v>1480</v>
+        <v>1423</v>
       </c>
       <c r="C530" s="2" t="s">
-        <v>1481</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="531" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A531" s="2" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="B531" s="2" t="s">
-        <v>1420</v>
+        <v>1484</v>
       </c>
       <c r="C531" s="2" t="s">
-        <v>1421</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="532" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A532" s="2" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="B532" s="2" t="s">
-        <v>194</v>
+        <v>1486</v>
       </c>
       <c r="C532" s="2" t="s">
-        <v>194</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="533" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A533" s="2" t="s">
-        <v>1484</v>
+        <v>1488</v>
       </c>
       <c r="B533" s="2" t="s">
-        <v>1485</v>
+        <v>1426</v>
       </c>
       <c r="C533" s="2" t="s">
-        <v>1486</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="534" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A534" s="2" t="s">
-        <v>1487</v>
+        <v>1489</v>
       </c>
       <c r="B534" s="2" t="s">
-        <v>1488</v>
+        <v>194</v>
       </c>
       <c r="C534" s="2" t="s">
-        <v>1489</v>
+        <v>194</v>
       </c>
     </row>
     <row r="535" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12630,65 +12648,65 @@
         <v>1499</v>
       </c>
       <c r="B538" s="2" t="s">
-        <v>1251</v>
+        <v>1500</v>
       </c>
       <c r="C538" s="2" t="s">
-        <v>1252</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="539" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A539" s="2" t="s">
-        <v>1500</v>
+        <v>1502</v>
       </c>
       <c r="B539" s="2" t="s">
-        <v>4</v>
+        <v>1503</v>
       </c>
       <c r="C539" s="2" t="s">
-        <v>5</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="540" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A540" s="2" t="s">
-        <v>1501</v>
+        <v>1505</v>
       </c>
       <c r="B540" s="2" t="s">
-        <v>1239</v>
+        <v>1257</v>
       </c>
       <c r="C540" s="2" t="s">
-        <v>1240</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="541" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A541" s="2" t="s">
-        <v>1502</v>
+        <v>1506</v>
       </c>
       <c r="B541" s="2" t="s">
-        <v>1254</v>
+        <v>4</v>
       </c>
       <c r="C541" s="2" t="s">
-        <v>1255</v>
+        <v>5</v>
       </c>
     </row>
     <row r="542" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A542" s="2" t="s">
-        <v>1503</v>
+        <v>1507</v>
       </c>
       <c r="B542" s="2" t="s">
-        <v>1504</v>
+        <v>1245</v>
       </c>
       <c r="C542" s="2" t="s">
-        <v>1505</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="543" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A543" s="2" t="s">
-        <v>1506</v>
+        <v>1508</v>
       </c>
       <c r="B543" s="2" t="s">
-        <v>1507</v>
+        <v>1260</v>
       </c>
       <c r="C543" s="2" t="s">
-        <v>1508</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="544" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12696,62 +12714,62 @@
         <v>1509</v>
       </c>
       <c r="B544" s="2" t="s">
-        <v>1257</v>
+        <v>1510</v>
       </c>
       <c r="C544" s="2" t="s">
-        <v>1258</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="545" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A545" s="2" t="s">
-        <v>1510</v>
+        <v>1512</v>
       </c>
       <c r="B545" s="2" t="s">
-        <v>1511</v>
+        <v>1513</v>
       </c>
       <c r="C545" s="2" t="s">
-        <v>1512</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="546" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A546" s="2" t="s">
-        <v>1513</v>
+        <v>1515</v>
       </c>
       <c r="B546" s="2" t="s">
-        <v>1260</v>
+        <v>1263</v>
       </c>
       <c r="C546" s="2" t="s">
-        <v>1514</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="547" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A547" s="2" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="B547" s="2" t="s">
-        <v>1206</v>
+        <v>1517</v>
       </c>
       <c r="C547" s="2" t="s">
-        <v>1516</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="548" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A548" s="2" t="s">
-        <v>1517</v>
+        <v>1519</v>
       </c>
       <c r="B548" s="2" t="s">
-        <v>1518</v>
+        <v>1266</v>
       </c>
       <c r="C548" s="2" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="549" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A549" s="2" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="B549" s="2" t="s">
-        <v>1521</v>
+        <v>1212</v>
       </c>
       <c r="C549" s="2" t="s">
         <v>1522</v>
@@ -12839,26 +12857,26 @@
         <v>1544</v>
       </c>
       <c r="B557" s="2" t="s">
-        <v>1251</v>
+        <v>1545</v>
       </c>
       <c r="C557" s="2" t="s">
-        <v>1252</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="558" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A558" s="2" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
       <c r="B558" s="2" t="s">
-        <v>4</v>
+        <v>1548</v>
       </c>
       <c r="C558" s="2" t="s">
-        <v>5</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="559" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A559" s="2" t="s">
-        <v>1546</v>
+        <v>1550</v>
       </c>
       <c r="B559" s="2" t="s">
         <v>1257</v>
@@ -12869,24 +12887,24 @@
     </row>
     <row r="560" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A560" s="2" t="s">
-        <v>1547</v>
+        <v>1551</v>
       </c>
       <c r="B560" s="2" t="s">
-        <v>1548</v>
+        <v>4</v>
       </c>
       <c r="C560" s="2" t="s">
-        <v>1549</v>
+        <v>5</v>
       </c>
     </row>
     <row r="561" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A561" s="2" t="s">
-        <v>1550</v>
+        <v>1552</v>
       </c>
       <c r="B561" s="2" t="s">
-        <v>1551</v>
+        <v>1263</v>
       </c>
       <c r="C561" s="2" t="s">
-        <v>1552</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="562" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12905,32 +12923,32 @@
         <v>1556</v>
       </c>
       <c r="B563" s="2" t="s">
-        <v>1527</v>
+        <v>1557</v>
       </c>
       <c r="C563" s="2" t="s">
-        <v>1528</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="564" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A564" s="2" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="B564" s="2" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="C564" s="2" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="565" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A565" s="2" t="s">
-        <v>1560</v>
+        <v>1562</v>
       </c>
       <c r="B565" s="2" t="s">
-        <v>1561</v>
+        <v>1533</v>
       </c>
       <c r="C565" s="2" t="s">
-        <v>1562</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="566" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12938,32 +12956,32 @@
         <v>1563</v>
       </c>
       <c r="B566" s="2" t="s">
-        <v>1381</v>
+        <v>1564</v>
       </c>
       <c r="C566" s="2" t="s">
-        <v>1382</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="567" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A567" s="2" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="B567" s="2" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="C567" s="2" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="568" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A568" s="2" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="B568" s="2" t="s">
-        <v>1568</v>
+        <v>1387</v>
       </c>
       <c r="C568" s="2" t="s">
-        <v>1569</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="569" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13029,29 +13047,29 @@
         <v>1586</v>
       </c>
       <c r="C574" s="2" t="s">
-        <v>533</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="575" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A575" s="2" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="B575" s="2" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="C575" s="2" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="576" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A576" s="2" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="B576" s="2" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="C576" s="2" t="s">
-        <v>1592</v>
+        <v>533</v>
       </c>
     </row>
     <row r="577" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13125,32 +13143,32 @@
         <v>1611</v>
       </c>
       <c r="B583" s="2" t="s">
-        <v>532</v>
+        <v>1612</v>
       </c>
       <c r="C583" s="2" t="s">
-        <v>533</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="584" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A584" s="2" t="s">
-        <v>1612</v>
+        <v>1614</v>
       </c>
       <c r="B584" s="2" t="s">
-        <v>1613</v>
+        <v>1615</v>
       </c>
       <c r="C584" s="2" t="s">
-        <v>1614</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="585" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A585" s="2" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="B585" s="2" t="s">
-        <v>1616</v>
+        <v>532</v>
       </c>
       <c r="C585" s="2" t="s">
-        <v>1617</v>
+        <v>533</v>
       </c>
     </row>
     <row r="586" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13158,32 +13176,32 @@
         <v>1618</v>
       </c>
       <c r="B586" s="2" t="s">
-        <v>282</v>
+        <v>1619</v>
       </c>
       <c r="C586" s="2" t="s">
-        <v>283</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="587" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A587" s="2" t="s">
-        <v>1619</v>
+        <v>1621</v>
       </c>
       <c r="B587" s="2" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="C587" s="2" t="s">
-        <v>1621</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="588" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A588" s="2" t="s">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="B588" s="2" t="s">
-        <v>1623</v>
+        <v>282</v>
       </c>
       <c r="C588" s="2" t="s">
-        <v>1624</v>
+        <v>283</v>
       </c>
     </row>
     <row r="589" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13301,65 +13319,65 @@
         <v>1655</v>
       </c>
       <c r="B599" s="2" t="s">
-        <v>276</v>
+        <v>1656</v>
       </c>
       <c r="C599" s="2" t="s">
-        <v>277</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="600" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A600" s="2" t="s">
-        <v>1656</v>
+        <v>1658</v>
       </c>
       <c r="B600" s="2" t="s">
-        <v>1657</v>
+        <v>1659</v>
       </c>
       <c r="C600" s="2" t="s">
-        <v>1098</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="601" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A601" s="2" t="s">
-        <v>1658</v>
+        <v>1661</v>
       </c>
       <c r="B601" s="2" t="s">
-        <v>1659</v>
+        <v>276</v>
       </c>
       <c r="C601" s="2" t="s">
-        <v>1660</v>
+        <v>277</v>
       </c>
     </row>
     <row r="602" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A602" s="2" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="B602" s="2" t="s">
-        <v>1480</v>
+        <v>1663</v>
       </c>
       <c r="C602" s="2" t="s">
-        <v>1481</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="603" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A603" s="2" t="s">
-        <v>1662</v>
+        <v>1664</v>
       </c>
       <c r="B603" s="2" t="s">
-        <v>1663</v>
+        <v>1665</v>
       </c>
       <c r="C603" s="2" t="s">
-        <v>1664</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="604" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A604" s="2" t="s">
-        <v>1665</v>
+        <v>1667</v>
       </c>
       <c r="B604" s="2" t="s">
-        <v>1666</v>
+        <v>1486</v>
       </c>
       <c r="C604" s="2" t="s">
-        <v>1667</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="605" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13400,76 +13418,76 @@
         <v>1677</v>
       </c>
       <c r="B608" s="2" t="s">
-        <v>185</v>
+        <v>1678</v>
       </c>
       <c r="C608" s="2" t="s">
-        <v>186</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="609" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A609" s="2" t="s">
-        <v>1678</v>
+        <v>1680</v>
       </c>
       <c r="B609" s="2" t="s">
-        <v>1095</v>
+        <v>1681</v>
       </c>
       <c r="C609" s="2" t="s">
-        <v>642</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="610" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A610" s="2" t="s">
-        <v>1679</v>
+        <v>1683</v>
       </c>
       <c r="B610" s="2" t="s">
-        <v>1104</v>
+        <v>185</v>
       </c>
       <c r="C610" s="2" t="s">
-        <v>1680</v>
+        <v>186</v>
       </c>
     </row>
     <row r="611" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A611" s="2" t="s">
-        <v>1681</v>
+        <v>1684</v>
       </c>
       <c r="B611" s="2" t="s">
-        <v>1682</v>
+        <v>1101</v>
       </c>
       <c r="C611" s="2" t="s">
-        <v>1683</v>
+        <v>642</v>
       </c>
     </row>
     <row r="612" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A612" s="2" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="B612" s="2" t="s">
-        <v>276</v>
+        <v>1110</v>
       </c>
       <c r="C612" s="2" t="s">
-        <v>277</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="613" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A613" s="2" t="s">
-        <v>1685</v>
+        <v>1687</v>
       </c>
       <c r="B613" s="2" t="s">
-        <v>1686</v>
+        <v>1688</v>
       </c>
       <c r="C613" s="2" t="s">
-        <v>1687</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="614" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A614" s="2" t="s">
-        <v>1688</v>
+        <v>1690</v>
       </c>
       <c r="B614" s="2" t="s">
-        <v>1689</v>
+        <v>276</v>
       </c>
       <c r="C614" s="2" t="s">
-        <v>1690</v>
+        <v>277</v>
       </c>
     </row>
     <row r="615" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13499,32 +13517,32 @@
         <v>1697</v>
       </c>
       <c r="B617" s="2" t="s">
-        <v>282</v>
+        <v>1698</v>
       </c>
       <c r="C617" s="2" t="s">
-        <v>283</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="618" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A618" s="2" t="s">
-        <v>1698</v>
+        <v>1700</v>
       </c>
       <c r="B618" s="2" t="s">
-        <v>1699</v>
+        <v>1701</v>
       </c>
       <c r="C618" s="2" t="s">
-        <v>1700</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="619" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A619" s="2" t="s">
-        <v>1701</v>
+        <v>1703</v>
       </c>
       <c r="B619" s="2" t="s">
-        <v>1702</v>
+        <v>282</v>
       </c>
       <c r="C619" s="2" t="s">
-        <v>1703</v>
+        <v>283</v>
       </c>
     </row>
     <row r="620" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13565,32 +13583,32 @@
         <v>1713</v>
       </c>
       <c r="B623" s="2" t="s">
-        <v>532</v>
+        <v>1714</v>
       </c>
       <c r="C623" s="2" t="s">
-        <v>533</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="624" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A624" s="2" t="s">
-        <v>1714</v>
+        <v>1716</v>
       </c>
       <c r="B624" s="2" t="s">
-        <v>1715</v>
+        <v>1717</v>
       </c>
       <c r="C624" s="2" t="s">
-        <v>1716</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="625" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A625" s="2" t="s">
-        <v>1717</v>
+        <v>1719</v>
       </c>
       <c r="B625" s="2" t="s">
-        <v>1718</v>
+        <v>532</v>
       </c>
       <c r="C625" s="2" t="s">
-        <v>1719</v>
+        <v>533</v>
       </c>
     </row>
     <row r="626" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13675,32 +13693,32 @@
         <v>1741</v>
       </c>
       <c r="B633" s="2" t="s">
-        <v>19</v>
+        <v>1742</v>
       </c>
       <c r="C633" s="2" t="s">
-        <v>20</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="634" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A634" s="2" t="s">
-        <v>1742</v>
+        <v>1744</v>
       </c>
       <c r="B634" s="2" t="s">
-        <v>1743</v>
+        <v>1745</v>
       </c>
       <c r="C634" s="2" t="s">
-        <v>1744</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="635" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A635" s="2" t="s">
-        <v>1745</v>
+        <v>1747</v>
       </c>
       <c r="B635" s="2" t="s">
-        <v>1746</v>
+        <v>19</v>
       </c>
       <c r="C635" s="2" t="s">
-        <v>1747</v>
+        <v>20</v>
       </c>
     </row>
     <row r="636" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13840,29 +13858,29 @@
         <v>1784</v>
       </c>
       <c r="B648" s="2" t="s">
-        <v>744</v>
+        <v>1785</v>
       </c>
       <c r="C648" s="2" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="649" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A649" s="2" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="B649" s="2" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="C649" s="2" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="650" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A650" s="2" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="B650" s="2" t="s">
-        <v>1790</v>
+        <v>744</v>
       </c>
       <c r="C650" s="2" t="s">
         <v>1791</v>
@@ -13942,29 +13960,29 @@
         <v>1811</v>
       </c>
       <c r="C657" s="2" t="s">
-        <v>455</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="658" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A658" s="2" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="B658" s="2" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="C658" s="2" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="659" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A659" s="2" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="B659" s="2" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="C659" s="2" t="s">
-        <v>1817</v>
+        <v>455</v>
       </c>
     </row>
     <row r="660" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13972,120 +13990,120 @@
         <v>1818</v>
       </c>
       <c r="B660" s="2" t="s">
-        <v>276</v>
+        <v>1819</v>
       </c>
       <c r="C660" s="2" t="s">
-        <v>277</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="661" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A661" s="2" t="s">
-        <v>1819</v>
+        <v>1821</v>
       </c>
       <c r="B661" s="2" t="s">
-        <v>1820</v>
+        <v>1822</v>
       </c>
       <c r="C661" s="2" t="s">
-        <v>183</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="662" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A662" s="2" t="s">
-        <v>1821</v>
+        <v>1824</v>
       </c>
       <c r="B662" s="2" t="s">
-        <v>1822</v>
+        <v>276</v>
       </c>
       <c r="C662" s="2" t="s">
-        <v>1823</v>
+        <v>277</v>
       </c>
     </row>
     <row r="663" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A663" s="2" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B663" s="2" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="C663" s="2" t="s">
-        <v>455</v>
+        <v>183</v>
       </c>
     </row>
     <row r="664" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A664" s="2" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="B664" s="2" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="C664" s="2" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="665" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A665" s="2" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="B665" s="2" t="s">
-        <v>851</v>
+        <v>1831</v>
       </c>
       <c r="C665" s="2" t="s">
-        <v>852</v>
+        <v>455</v>
       </c>
     </row>
     <row r="666" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A666" s="2" t="s">
-        <v>1830</v>
+        <v>1832</v>
       </c>
       <c r="B666" s="2" t="s">
-        <v>4</v>
+        <v>1833</v>
       </c>
       <c r="C666" s="2" t="s">
-        <v>5</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="667" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A667" s="2" t="s">
-        <v>1831</v>
+        <v>1835</v>
       </c>
       <c r="B667" s="2" t="s">
-        <v>282</v>
+        <v>857</v>
       </c>
       <c r="C667" s="2" t="s">
-        <v>283</v>
+        <v>858</v>
       </c>
     </row>
     <row r="668" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A668" s="2" t="s">
-        <v>1832</v>
+        <v>1836</v>
       </c>
       <c r="B668" s="2" t="s">
-        <v>1827</v>
+        <v>4</v>
       </c>
       <c r="C668" s="2" t="s">
-        <v>1828</v>
+        <v>5</v>
       </c>
     </row>
     <row r="669" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A669" s="2" t="s">
-        <v>1833</v>
+        <v>1837</v>
       </c>
       <c r="B669" s="2" t="s">
-        <v>1834</v>
+        <v>282</v>
       </c>
       <c r="C669" s="2" t="s">
-        <v>1835</v>
+        <v>283</v>
       </c>
     </row>
     <row r="670" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A670" s="2" t="s">
-        <v>1836</v>
+        <v>1838</v>
       </c>
       <c r="B670" s="2" t="s">
-        <v>1837</v>
+        <v>1833</v>
       </c>
       <c r="C670" s="2" t="s">
-        <v>1838</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="671" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14159,54 +14177,54 @@
         <v>1857</v>
       </c>
       <c r="B677" s="2" t="s">
-        <v>19</v>
+        <v>1858</v>
       </c>
       <c r="C677" s="2" t="s">
-        <v>20</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="678" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A678" s="2" t="s">
-        <v>1858</v>
+        <v>1860</v>
       </c>
       <c r="B678" s="2" t="s">
-        <v>13</v>
+        <v>1861</v>
       </c>
       <c r="C678" s="2" t="s">
-        <v>14</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="679" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A679" s="2" t="s">
-        <v>1859</v>
+        <v>1863</v>
       </c>
       <c r="B679" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C679" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="680" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A680" s="2" t="s">
-        <v>1860</v>
+        <v>1864</v>
       </c>
       <c r="B680" s="2" t="s">
-        <v>1861</v>
+        <v>13</v>
       </c>
       <c r="C680" s="2" t="s">
-        <v>1862</v>
+        <v>14</v>
       </c>
     </row>
     <row r="681" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A681" s="2" t="s">
-        <v>1863</v>
+        <v>1865</v>
       </c>
       <c r="B681" s="2" t="s">
-        <v>1864</v>
+        <v>16</v>
       </c>
       <c r="C681" s="2" t="s">
-        <v>1865</v>
+        <v>17</v>
       </c>
     </row>
     <row r="682" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14236,175 +14254,175 @@
         <v>1872</v>
       </c>
       <c r="B684" s="2" t="s">
-        <v>1770</v>
+        <v>1873</v>
       </c>
       <c r="C684" s="2" t="s">
-        <v>1771</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="685" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A685" s="2" t="s">
-        <v>1873</v>
+        <v>1875</v>
       </c>
       <c r="B685" s="2" t="s">
-        <v>1773</v>
+        <v>1876</v>
       </c>
       <c r="C685" s="2" t="s">
-        <v>1774</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="686" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A686" s="2" t="s">
-        <v>1874</v>
+        <v>1878</v>
       </c>
       <c r="B686" s="2" t="s">
-        <v>1875</v>
+        <v>1776</v>
       </c>
       <c r="C686" s="2" t="s">
-        <v>1261</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="687" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A687" s="2" t="s">
-        <v>1876</v>
+        <v>1879</v>
       </c>
       <c r="B687" s="2" t="s">
-        <v>1877</v>
+        <v>1779</v>
       </c>
       <c r="C687" s="2" t="s">
-        <v>1878</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="688" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A688" s="2" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
       <c r="B688" s="2" t="s">
-        <v>1107</v>
+        <v>1881</v>
       </c>
       <c r="C688" s="2" t="s">
-        <v>1108</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="689" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A689" s="2" t="s">
-        <v>1880</v>
+        <v>1882</v>
       </c>
       <c r="B689" s="2" t="s">
-        <v>1881</v>
+        <v>1883</v>
       </c>
       <c r="C689" s="2" t="s">
-        <v>1783</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="690" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A690" s="2" t="s">
-        <v>1882</v>
+        <v>1885</v>
       </c>
       <c r="B690" s="2" t="s">
-        <v>744</v>
+        <v>1113</v>
       </c>
       <c r="C690" s="2" t="s">
-        <v>1785</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="691" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A691" s="2" t="s">
-        <v>1883</v>
+        <v>1886</v>
       </c>
       <c r="B691" s="2" t="s">
-        <v>1884</v>
+        <v>1887</v>
       </c>
       <c r="C691" s="2" t="s">
-        <v>1885</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="692" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A692" s="2" t="s">
-        <v>1886</v>
+        <v>1888</v>
       </c>
       <c r="B692" s="2" t="s">
-        <v>1887</v>
+        <v>744</v>
       </c>
       <c r="C692" s="2" t="s">
-        <v>1878</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="693" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A693" s="2" t="s">
-        <v>1888</v>
+        <v>1889</v>
       </c>
       <c r="B693" s="2" t="s">
-        <v>835</v>
+        <v>1890</v>
       </c>
       <c r="C693" s="2" t="s">
-        <v>1889</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="694" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A694" s="2" t="s">
-        <v>1890</v>
+        <v>1892</v>
       </c>
       <c r="B694" s="2" t="s">
-        <v>847</v>
+        <v>1893</v>
       </c>
       <c r="C694" s="2" t="s">
-        <v>1891</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="695" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A695" s="2" t="s">
-        <v>1892</v>
+        <v>1894</v>
       </c>
       <c r="B695" s="2" t="s">
-        <v>535</v>
+        <v>841</v>
       </c>
       <c r="C695" s="2" t="s">
-        <v>455</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="696" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A696" s="2" t="s">
-        <v>1893</v>
+        <v>1896</v>
       </c>
       <c r="B696" s="2" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="C696" s="2" t="s">
-        <v>852</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="697" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A697" s="2" t="s">
-        <v>1894</v>
+        <v>1898</v>
       </c>
       <c r="B697" s="2" t="s">
-        <v>282</v>
+        <v>535</v>
       </c>
       <c r="C697" s="2" t="s">
-        <v>283</v>
+        <v>455</v>
       </c>
     </row>
     <row r="698" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A698" s="2" t="s">
-        <v>1895</v>
+        <v>1899</v>
       </c>
       <c r="B698" s="2" t="s">
-        <v>1896</v>
+        <v>857</v>
       </c>
       <c r="C698" s="2" t="s">
-        <v>1897</v>
+        <v>858</v>
       </c>
     </row>
     <row r="699" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A699" s="2" t="s">
-        <v>1898</v>
+        <v>1900</v>
       </c>
       <c r="B699" s="2" t="s">
-        <v>1899</v>
+        <v>282</v>
       </c>
       <c r="C699" s="2" t="s">
-        <v>1900</v>
+        <v>283</v>
       </c>
     </row>
     <row r="700" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14423,95 +14441,95 @@
         <v>1904</v>
       </c>
       <c r="B701" s="2" t="s">
-        <v>879</v>
+        <v>1905</v>
       </c>
       <c r="C701" s="2" t="s">
-        <v>880</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="702" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A702" s="2" t="s">
-        <v>1905</v>
+        <v>1907</v>
       </c>
       <c r="B702" s="2" t="s">
-        <v>847</v>
+        <v>1908</v>
       </c>
       <c r="C702" s="2" t="s">
-        <v>1891</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="703" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A703" s="2" t="s">
-        <v>1906</v>
+        <v>1910</v>
       </c>
       <c r="B703" s="2" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="C703" s="2" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
     </row>
     <row r="704" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A704" s="2" t="s">
-        <v>1907</v>
+        <v>1911</v>
       </c>
       <c r="B704" s="2" t="s">
-        <v>1908</v>
+        <v>853</v>
       </c>
       <c r="C704" s="2" t="s">
-        <v>1909</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="705" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A705" s="2" t="s">
-        <v>1910</v>
+        <v>1912</v>
       </c>
       <c r="B705" s="2" t="s">
         <v>889</v>
       </c>
       <c r="C705" s="2" t="s">
-        <v>1911</v>
+        <v>890</v>
       </c>
     </row>
     <row r="706" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A706" s="2" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="B706" s="2" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="C706" s="2" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="707" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A707" s="2" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="B707" s="2" t="s">
         <v>895</v>
       </c>
       <c r="C707" s="2" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="708" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A708" s="2" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="B708" s="2" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="C708" s="2" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="709" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A709" s="2" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
       <c r="B709" s="2" t="s">
-        <v>1921</v>
+        <v>901</v>
       </c>
       <c r="C709" s="2" t="s">
         <v>1922</v>
@@ -14533,109 +14551,109 @@
         <v>1926</v>
       </c>
       <c r="B711" s="2" t="s">
-        <v>725</v>
+        <v>1927</v>
       </c>
       <c r="C711" s="2" t="s">
-        <v>726</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="712" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A712" s="2" t="s">
-        <v>1927</v>
+        <v>1929</v>
       </c>
       <c r="B712" s="2" t="s">
-        <v>905</v>
+        <v>1930</v>
       </c>
       <c r="C712" s="2" t="s">
-        <v>906</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="713" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A713" s="2" t="s">
-        <v>1928</v>
+        <v>1932</v>
       </c>
       <c r="B713" s="2" t="s">
-        <v>908</v>
+        <v>725</v>
       </c>
       <c r="C713" s="2" t="s">
-        <v>1929</v>
+        <v>726</v>
       </c>
     </row>
     <row r="714" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A714" s="2" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B714" s="2" t="s">
         <v>911</v>
       </c>
       <c r="C714" s="2" t="s">
-        <v>1931</v>
+        <v>912</v>
       </c>
     </row>
     <row r="715" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A715" s="2" t="s">
-        <v>1932</v>
+        <v>1934</v>
       </c>
       <c r="B715" s="2" t="s">
         <v>914</v>
       </c>
       <c r="C715" s="2" t="s">
-        <v>1933</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="716" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A716" s="2" t="s">
-        <v>1934</v>
+        <v>1936</v>
       </c>
       <c r="B716" s="2" t="s">
-        <v>1935</v>
+        <v>917</v>
       </c>
       <c r="C716" s="2" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="717" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A717" s="2" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="B717" s="2" t="s">
-        <v>1770</v>
+        <v>920</v>
       </c>
       <c r="C717" s="2" t="s">
-        <v>1771</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="718" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A718" s="2" t="s">
-        <v>1938</v>
+        <v>1940</v>
       </c>
       <c r="B718" s="2" t="s">
-        <v>1773</v>
+        <v>1941</v>
       </c>
       <c r="C718" s="2" t="s">
-        <v>1774</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="719" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A719" s="2" t="s">
-        <v>1939</v>
+        <v>1943</v>
       </c>
       <c r="B719" s="2" t="s">
-        <v>1940</v>
+        <v>1776</v>
       </c>
       <c r="C719" s="2" t="s">
-        <v>1941</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="720" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A720" s="2" t="s">
-        <v>1942</v>
+        <v>1944</v>
       </c>
       <c r="B720" s="2" t="s">
-        <v>1943</v>
+        <v>1779</v>
       </c>
       <c r="C720" s="2" t="s">
-        <v>1944</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="721" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14687,32 +14705,32 @@
         <v>1957</v>
       </c>
       <c r="B725" s="2" t="s">
-        <v>433</v>
+        <v>1958</v>
       </c>
       <c r="C725" s="2" t="s">
-        <v>434</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="726" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A726" s="2" t="s">
-        <v>1958</v>
+        <v>1960</v>
       </c>
       <c r="B726" s="2" t="s">
-        <v>1959</v>
+        <v>1961</v>
       </c>
       <c r="C726" s="2" t="s">
-        <v>1960</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="727" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A727" s="2" t="s">
-        <v>1961</v>
+        <v>1963</v>
       </c>
       <c r="B727" s="2" t="s">
-        <v>1962</v>
+        <v>433</v>
       </c>
       <c r="C727" s="2" t="s">
-        <v>1963</v>
+        <v>434</v>
       </c>
     </row>
     <row r="728" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14720,62 +14738,62 @@
         <v>1964</v>
       </c>
       <c r="B728" s="2" t="s">
-        <v>445</v>
+        <v>1965</v>
       </c>
       <c r="C728" s="2" t="s">
-        <v>533</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="729" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A729" s="2" t="s">
-        <v>1965</v>
+        <v>1967</v>
       </c>
       <c r="B729" s="2" t="s">
-        <v>451</v>
+        <v>1968</v>
       </c>
       <c r="C729" s="2" t="s">
-        <v>1966</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="730" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A730" s="2" t="s">
-        <v>1967</v>
+        <v>1970</v>
       </c>
       <c r="B730" s="2" t="s">
-        <v>484</v>
+        <v>445</v>
       </c>
       <c r="C730" s="2" t="s">
-        <v>1968</v>
+        <v>533</v>
       </c>
     </row>
     <row r="731" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A731" s="2" t="s">
-        <v>1969</v>
+        <v>1971</v>
       </c>
       <c r="B731" s="2" t="s">
-        <v>487</v>
+        <v>451</v>
       </c>
       <c r="C731" s="2" t="s">
-        <v>1970</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="732" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A732" s="2" t="s">
-        <v>1971</v>
+        <v>1973</v>
       </c>
       <c r="B732" s="2" t="s">
-        <v>1972</v>
+        <v>484</v>
       </c>
       <c r="C732" s="2" t="s">
-        <v>1973</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="733" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A733" s="2" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="B733" s="2" t="s">
-        <v>1975</v>
+        <v>487</v>
       </c>
       <c r="C733" s="2" t="s">
         <v>1976</v>
@@ -14797,131 +14815,131 @@
         <v>1980</v>
       </c>
       <c r="B735" s="2" t="s">
-        <v>454</v>
+        <v>1981</v>
       </c>
       <c r="C735" s="2" t="s">
-        <v>455</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="736" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A736" s="2" t="s">
-        <v>1981</v>
+        <v>1983</v>
       </c>
       <c r="B736" s="2" t="s">
-        <v>1982</v>
+        <v>1984</v>
       </c>
       <c r="C736" s="2" t="s">
-        <v>1983</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="737" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A737" s="2" t="s">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="B737" s="2" t="s">
-        <v>466</v>
+        <v>454</v>
       </c>
       <c r="C737" s="2" t="s">
-        <v>467</v>
+        <v>455</v>
       </c>
     </row>
     <row r="738" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A738" s="2" t="s">
-        <v>1985</v>
+        <v>1987</v>
       </c>
       <c r="B738" s="2" t="s">
-        <v>472</v>
+        <v>1988</v>
       </c>
       <c r="C738" s="2" t="s">
-        <v>473</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="739" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A739" s="2" t="s">
-        <v>1986</v>
+        <v>1990</v>
       </c>
       <c r="B739" s="2" t="s">
-        <v>1987</v>
+        <v>466</v>
       </c>
       <c r="C739" s="2" t="s">
-        <v>1988</v>
+        <v>467</v>
       </c>
     </row>
     <row r="740" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A740" s="2" t="s">
-        <v>1989</v>
+        <v>1991</v>
       </c>
       <c r="B740" s="2" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="C740" s="2" t="s">
-        <v>209</v>
+        <v>473</v>
       </c>
     </row>
     <row r="741" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A741" s="2" t="s">
-        <v>1990</v>
+        <v>1992</v>
       </c>
       <c r="B741" s="2" t="s">
-        <v>478</v>
+        <v>1993</v>
       </c>
       <c r="C741" s="2" t="s">
-        <v>1991</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="742" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A742" s="2" t="s">
-        <v>1992</v>
+        <v>1995</v>
       </c>
       <c r="B742" s="2" t="s">
-        <v>520</v>
+        <v>475</v>
       </c>
       <c r="C742" s="2" t="s">
-        <v>1993</v>
+        <v>209</v>
       </c>
     </row>
     <row r="743" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A743" s="2" t="s">
-        <v>1994</v>
+        <v>1996</v>
       </c>
       <c r="B743" s="2" t="s">
-        <v>1995</v>
+        <v>478</v>
       </c>
       <c r="C743" s="2" t="s">
-        <v>1996</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="744" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A744" s="2" t="s">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="B744" s="2" t="s">
-        <v>502</v>
+        <v>520</v>
       </c>
       <c r="C744" s="2" t="s">
-        <v>503</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="745" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A745" s="2" t="s">
-        <v>1998</v>
+        <v>2000</v>
       </c>
       <c r="B745" s="2" t="s">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="C745" s="2" t="s">
-        <v>2000</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="746" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A746" s="2" t="s">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="B746" s="2" t="s">
-        <v>2002</v>
+        <v>502</v>
       </c>
       <c r="C746" s="2" t="s">
-        <v>2003</v>
+        <v>503</v>
       </c>
     </row>
     <row r="747" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14932,40 +14950,40 @@
         <v>2005</v>
       </c>
       <c r="C747" s="2" t="s">
-        <v>512</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="748" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A748" s="2" t="s">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="B748" s="2" t="s">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="C748" s="2" t="s">
-        <v>515</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="749" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A749" s="2" t="s">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="B749" s="2" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="C749" s="2" t="s">
-        <v>2010</v>
+        <v>512</v>
       </c>
     </row>
     <row r="750" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A750" s="2" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="B750" s="2" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="C750" s="2" t="s">
-        <v>2013</v>
+        <v>515</v>
       </c>
     </row>
     <row r="751" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15020,29 +15038,29 @@
         <v>2027</v>
       </c>
       <c r="C755" s="2" t="s">
-        <v>1690</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="756" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A756" s="2" t="s">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="B756" s="2" t="s">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="C756" s="2" t="s">
-        <v>2030</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="757" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A757" s="2" t="s">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="B757" s="2" t="s">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="C757" s="2" t="s">
-        <v>2033</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="758" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15064,29 +15082,29 @@
         <v>2038</v>
       </c>
       <c r="C759" s="2" t="s">
-        <v>217</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="760" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A760" s="2" t="s">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="B760" s="2" t="s">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="C760" s="2" t="s">
-        <v>2041</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="761" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A761" s="2" t="s">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="B761" s="2" t="s">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="C761" s="2" t="s">
-        <v>2044</v>
+        <v>217</v>
       </c>
     </row>
     <row r="762" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15193,43 +15211,43 @@
         <v>2072</v>
       </c>
       <c r="B771" s="2" t="s">
-        <v>607</v>
+        <v>2073</v>
       </c>
       <c r="C771" s="2" t="s">
-        <v>608</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="772" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A772" s="2" t="s">
-        <v>2073</v>
+        <v>2075</v>
       </c>
       <c r="B772" s="2" t="s">
-        <v>610</v>
+        <v>2076</v>
       </c>
       <c r="C772" s="2" t="s">
-        <v>611</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="773" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A773" s="2" t="s">
-        <v>2074</v>
+        <v>2078</v>
       </c>
       <c r="B773" s="2" t="s">
-        <v>2075</v>
+        <v>607</v>
       </c>
       <c r="C773" s="2" t="s">
-        <v>2076</v>
+        <v>608</v>
       </c>
     </row>
     <row r="774" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A774" s="2" t="s">
-        <v>2077</v>
+        <v>2079</v>
       </c>
       <c r="B774" s="2" t="s">
-        <v>2078</v>
+        <v>610</v>
       </c>
       <c r="C774" s="2" t="s">
-        <v>2079</v>
+        <v>611</v>
       </c>
     </row>
     <row r="775" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15292,32 +15310,32 @@
         <v>2095</v>
       </c>
       <c r="B780" s="2" t="s">
-        <v>175</v>
+        <v>2096</v>
       </c>
       <c r="C780" s="2" t="s">
-        <v>176</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="781" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A781" s="2" t="s">
-        <v>2096</v>
+        <v>2098</v>
       </c>
       <c r="B781" s="2" t="s">
-        <v>2097</v>
+        <v>2099</v>
       </c>
       <c r="C781" s="2" t="s">
-        <v>2098</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="782" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A782" s="2" t="s">
-        <v>2099</v>
+        <v>2101</v>
       </c>
       <c r="B782" s="2" t="s">
-        <v>2100</v>
+        <v>175</v>
       </c>
       <c r="C782" s="2" t="s">
-        <v>2101</v>
+        <v>176</v>
       </c>
     </row>
     <row r="783" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15329,6 +15347,28 @@
       </c>
       <c r="C783" s="2" t="s">
         <v>2104</v>
+      </c>
+    </row>
+    <row r="784" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A784" s="2" t="s">
+        <v>2105</v>
+      </c>
+      <c r="B784" s="2" t="s">
+        <v>2106</v>
+      </c>
+      <c r="C784" s="2" t="s">
+        <v>2107</v>
+      </c>
+    </row>
+    <row r="785" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A785" s="2" t="s">
+        <v>2108</v>
+      </c>
+      <c r="B785" s="2" t="s">
+        <v>2109</v>
+      </c>
+      <c r="C785" s="2" t="s">
+        <v>2110</v>
       </c>
     </row>
   </sheetData>

--- a/apps/workspace-web/i18n.xlsx
+++ b/apps/workspace-web/i18n.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2355" uniqueCount="2111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2367" uniqueCount="2121">
   <si>
     <t>key</t>
   </si>
@@ -553,6 +553,15 @@
     <t>Failed to delete file.</t>
   </si>
   <si>
+    <t>storeError.deleteProductFailed</t>
+  </si>
+  <si>
+    <t>刪除商品失敗。</t>
+  </si>
+  <si>
+    <t>Failed to delete product.</t>
+  </si>
+  <si>
     <t>catalogStatus.all</t>
   </si>
   <si>
@@ -820,6 +829,33 @@
     <t>Featured order updated.</t>
   </si>
   <si>
+    <t>products.deleteConfirmTitle</t>
+  </si>
+  <si>
+    <t>刪除草稿</t>
+  </si>
+  <si>
+    <t>Delete draft</t>
+  </si>
+  <si>
+    <t>products.deleteConfirmDesc</t>
+  </si>
+  <si>
+    <t>刪除後「{name}」將自列表移除，已上傳的檔案也會一併刪除。確定刪除？</t>
+  </si>
+  <si>
+    <t>"{name}" will be removed from the list, along with any uploaded files. Delete it?</t>
+  </si>
+  <si>
+    <t>products.msgDeleted</t>
+  </si>
+  <si>
+    <t>已刪除草稿。</t>
+  </si>
+  <si>
+    <t>Draft deleted.</t>
+  </si>
+  <si>
     <t>stores.subStats</t>
   </si>
   <si>
@@ -5303,12 +5339,6 @@
   </si>
   <si>
     <t>legalDocs.del</t>
-  </si>
-  <si>
-    <t>刪除草稿</t>
-  </si>
-  <si>
-    <t>Delete draft</t>
   </si>
   <si>
     <t>legalDocs.deleteConfirm</t>
@@ -6729,7 +6759,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C785"/>
+  <dimension ref="A1:C789"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -7401,21 +7431,21 @@
         <v>180</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>43</v>
+        <v>181</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>44</v>
+        <v>182</v>
       </c>
     </row>
     <row r="62" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>182</v>
+        <v>43</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>183</v>
+        <v>44</v>
       </c>
     </row>
     <row r="63" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7459,15 +7489,15 @@
         <v>194</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="67" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>197</v>
@@ -7536,18 +7566,18 @@
         <v>214</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>183</v>
+        <v>215</v>
       </c>
     </row>
     <row r="74" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>217</v>
+        <v>186</v>
       </c>
     </row>
     <row r="75" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7874,54 +7904,54 @@
         <v>305</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>28</v>
+        <v>306</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>29</v>
+        <v>307</v>
       </c>
     </row>
     <row r="105" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="106" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="107" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="108" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>316</v>
+        <v>28</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>317</v>
+        <v>29</v>
       </c>
     </row>
     <row r="109" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8028,54 +8058,54 @@
         <v>345</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>282</v>
+        <v>346</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>283</v>
+        <v>347</v>
       </c>
     </row>
     <row r="119" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="120" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="121" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="122" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>356</v>
+        <v>294</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>357</v>
+        <v>295</v>
       </c>
     </row>
     <row r="123" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8314,98 +8344,98 @@
         <v>421</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>368</v>
+        <v>422</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>369</v>
+        <v>423</v>
       </c>
     </row>
     <row r="145" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="146" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="147" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="148" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>294</v>
+        <v>380</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>295</v>
+        <v>381</v>
       </c>
     </row>
     <row r="149" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="150" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="151" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="152" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>442</v>
+        <v>306</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>443</v>
+        <v>307</v>
       </c>
     </row>
     <row r="153" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8746,106 +8776,106 @@
         <v>535</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>455</v>
+        <v>536</v>
       </c>
     </row>
     <row r="184" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>466</v>
+        <v>538</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>467</v>
+        <v>539</v>
       </c>
     </row>
     <row r="185" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>475</v>
+        <v>541</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>209</v>
+        <v>542</v>
       </c>
     </row>
     <row r="186" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
     </row>
     <row r="187" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>543</v>
+        <v>467</v>
       </c>
     </row>
     <row r="188" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>502</v>
+        <v>478</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>503</v>
+        <v>479</v>
       </c>
     </row>
     <row r="189" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>546</v>
+        <v>487</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>547</v>
+        <v>212</v>
       </c>
     </row>
     <row r="190" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="191" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="192" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>555</v>
+        <v>514</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>556</v>
+        <v>515</v>
       </c>
     </row>
     <row r="193" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8864,54 +8894,54 @@
         <v>560</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>22</v>
+        <v>561</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>23</v>
+        <v>562</v>
       </c>
     </row>
     <row r="195" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="196" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="197" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="198" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>571</v>
+        <v>22</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>572</v>
+        <v>23</v>
       </c>
     </row>
     <row r="199" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8930,51 +8960,51 @@
         <v>576</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>466</v>
+        <v>577</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="201" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="202" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="203" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="204" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>588</v>
+        <v>478</v>
       </c>
       <c r="C204" s="2" t="s">
         <v>589</v>
@@ -9040,54 +9070,54 @@
         <v>605</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>175</v>
+        <v>606</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>176</v>
+        <v>607</v>
       </c>
     </row>
     <row r="211" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="212" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="213" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="214" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>616</v>
+        <v>175</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>617</v>
+        <v>176</v>
       </c>
     </row>
     <row r="215" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9172,76 +9202,76 @@
         <v>639</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>194</v>
+        <v>640</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>194</v>
+        <v>641</v>
       </c>
     </row>
     <row r="223" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="224" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>191</v>
+        <v>646</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>192</v>
+        <v>647</v>
       </c>
     </row>
     <row r="225" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
     </row>
     <row r="226" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>648</v>
+        <v>197</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>649</v>
+        <v>197</v>
       </c>
     </row>
     <row r="227" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="228" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>654</v>
+        <v>194</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>655</v>
+        <v>195</v>
       </c>
     </row>
     <row r="229" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9293,76 +9323,76 @@
         <v>668</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>334</v>
+        <v>669</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>335</v>
+        <v>670</v>
       </c>
     </row>
     <row r="234" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="235" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>337</v>
+        <v>675</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>338</v>
+        <v>676</v>
       </c>
     </row>
     <row r="236" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="237" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>677</v>
+        <v>346</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>678</v>
+        <v>347</v>
       </c>
     </row>
     <row r="238" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="239" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>683</v>
+        <v>349</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>684</v>
+        <v>350</v>
       </c>
     </row>
     <row r="240" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9480,76 +9510,76 @@
         <v>715</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>334</v>
+        <v>716</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>335</v>
+        <v>717</v>
       </c>
     </row>
     <row r="251" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>670</v>
+        <v>719</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>671</v>
+        <v>720</v>
       </c>
     </row>
     <row r="252" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>337</v>
+        <v>722</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>338</v>
+        <v>723</v>
       </c>
     </row>
     <row r="253" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>720</v>
+        <v>726</v>
       </c>
     </row>
     <row r="254" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>722</v>
+        <v>346</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>723</v>
+        <v>347</v>
       </c>
     </row>
     <row r="255" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>725</v>
+        <v>682</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>726</v>
+        <v>683</v>
       </c>
     </row>
     <row r="256" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>728</v>
+        <v>349</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>729</v>
+        <v>350</v>
       </c>
     </row>
     <row r="257" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9590,54 +9620,54 @@
         <v>739</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>622</v>
+        <v>740</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>623</v>
+        <v>741</v>
       </c>
     </row>
     <row r="261" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
     </row>
     <row r="262" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
     </row>
     <row r="263" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
     </row>
     <row r="264" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>750</v>
+        <v>634</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>751</v>
+        <v>635</v>
       </c>
     </row>
     <row r="265" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9700,54 +9730,54 @@
         <v>767</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>22</v>
+        <v>768</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>23</v>
+        <v>769</v>
       </c>
     </row>
     <row r="271" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
     </row>
     <row r="272" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
     </row>
     <row r="273" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
     </row>
     <row r="274" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>778</v>
+        <v>22</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>779</v>
+        <v>23</v>
       </c>
     </row>
     <row r="275" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10030,76 +10060,76 @@
         <v>855</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>535</v>
+        <v>856</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>455</v>
+        <v>857</v>
       </c>
     </row>
     <row r="301" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
     </row>
     <row r="302" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>282</v>
+        <v>862</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>283</v>
+        <v>863</v>
       </c>
     </row>
     <row r="303" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
     </row>
     <row r="304" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>864</v>
+        <v>547</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>865</v>
+        <v>467</v>
       </c>
     </row>
     <row r="305" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
     </row>
     <row r="306" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>870</v>
+        <v>294</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>871</v>
+        <v>295</v>
       </c>
     </row>
     <row r="307" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10162,54 +10192,54 @@
         <v>887</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>853</v>
+        <v>888</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>854</v>
+        <v>889</v>
       </c>
     </row>
     <row r="313" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
     </row>
     <row r="314" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
     </row>
     <row r="315" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
     </row>
     <row r="316" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>898</v>
+        <v>865</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>899</v>
+        <v>866</v>
       </c>
     </row>
     <row r="317" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10250,54 +10280,54 @@
         <v>909</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>725</v>
+        <v>910</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>726</v>
+        <v>911</v>
       </c>
     </row>
     <row r="321" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
     </row>
     <row r="322" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
     </row>
     <row r="323" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
     </row>
     <row r="324" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>920</v>
+        <v>737</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>921</v>
+        <v>738</v>
       </c>
     </row>
     <row r="325" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10316,54 +10346,54 @@
         <v>925</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>52</v>
+        <v>926</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>53</v>
+        <v>927</v>
       </c>
     </row>
     <row r="327" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
     </row>
     <row r="328" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
     </row>
     <row r="329" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
     </row>
     <row r="330" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>936</v>
+        <v>52</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>937</v>
+        <v>53</v>
       </c>
     </row>
     <row r="331" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10517,62 +10547,62 @@
         <v>978</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="345" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>416</v>
+        <v>981</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>417</v>
+        <v>982</v>
       </c>
     </row>
     <row r="346" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
     </row>
     <row r="347" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
     </row>
     <row r="348" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
     </row>
     <row r="349" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>990</v>
+        <v>428</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>991</v>
+        <v>429</v>
       </c>
     </row>
     <row r="350" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10638,48 +10668,48 @@
         <v>1008</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="356" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="357" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="358" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="359" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="C359" s="2" t="s">
         <v>1020</v>
@@ -10976,98 +11006,98 @@
         <v>1099</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>294</v>
+        <v>1100</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>295</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="387" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A387" s="2" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="C387" s="2" t="s">
-        <v>642</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="388" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A388" s="2" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
       <c r="C388" s="2" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="389" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A389" s="2" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="B389" s="2" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="C389" s="2" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="390" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A390" s="2" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="B390" s="2" t="s">
-        <v>191</v>
+        <v>306</v>
       </c>
       <c r="C390" s="2" t="s">
-        <v>192</v>
+        <v>307</v>
       </c>
     </row>
     <row r="391" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A391" s="2" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="B391" s="2" t="s">
-        <v>1110</v>
+        <v>1113</v>
       </c>
       <c r="C391" s="2" t="s">
-        <v>1111</v>
+        <v>654</v>
       </c>
     </row>
     <row r="392" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A392" s="2" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="B392" s="2" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="C392" s="2" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="393" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A393" s="2" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="B393" s="2" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="C393" s="2" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="394" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A394" s="2" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="B394" s="2" t="s">
-        <v>1119</v>
+        <v>194</v>
       </c>
       <c r="C394" s="2" t="s">
-        <v>1120</v>
+        <v>195</v>
       </c>
     </row>
     <row r="395" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11119,65 +11149,65 @@
         <v>1133</v>
       </c>
       <c r="B399" s="2" t="s">
-        <v>276</v>
+        <v>1134</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>277</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="400" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A400" s="2" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="B400" s="2" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="C400" s="2" t="s">
-        <v>1120</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="401" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A401" s="2" t="s">
-        <v>1136</v>
+        <v>1139</v>
       </c>
       <c r="B401" s="2" t="s">
-        <v>1137</v>
+        <v>1140</v>
       </c>
       <c r="C401" s="2" t="s">
-        <v>1138</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="402" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A402" s="2" t="s">
-        <v>1139</v>
+        <v>1142</v>
       </c>
       <c r="B402" s="2" t="s">
-        <v>1140</v>
+        <v>1143</v>
       </c>
       <c r="C402" s="2" t="s">
-        <v>1141</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="403" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A403" s="2" t="s">
-        <v>1142</v>
+        <v>1145</v>
       </c>
       <c r="B403" s="2" t="s">
-        <v>1143</v>
+        <v>288</v>
       </c>
       <c r="C403" s="2" t="s">
-        <v>1144</v>
+        <v>289</v>
       </c>
     </row>
     <row r="404" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A404" s="2" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="B404" s="2" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="C404" s="2" t="s">
-        <v>1147</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="405" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11196,54 +11226,54 @@
         <v>1151</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>294</v>
+        <v>1152</v>
       </c>
       <c r="C406" s="2" t="s">
-        <v>295</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="407" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A407" s="2" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="C407" s="2" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="408" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A408" s="2" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="B408" s="2" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="C408" s="2" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="409" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A409" s="2" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="B409" s="2" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="C409" s="2" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="410" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A410" s="2" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="B410" s="2" t="s">
-        <v>1162</v>
+        <v>306</v>
       </c>
       <c r="C410" s="2" t="s">
-        <v>1163</v>
+        <v>307</v>
       </c>
     </row>
     <row r="411" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11383,51 +11413,51 @@
         <v>1200</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>350</v>
+        <v>1201</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="424" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A424" s="2" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="B424" s="2" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="C424" s="2" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="425" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A425" s="2" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="B425" s="2" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="C425" s="2" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="426" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A426" s="2" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="B426" s="2" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="C426" s="2" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="427" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A427" s="2" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>1212</v>
+        <v>362</v>
       </c>
       <c r="C427" s="2" t="s">
         <v>1213</v>
@@ -11636,296 +11666,296 @@
         <v>1268</v>
       </c>
       <c r="B446" s="2" t="s">
-        <v>981</v>
+        <v>1269</v>
       </c>
       <c r="C446" s="2" t="s">
-        <v>982</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="447" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A447" s="2" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="B447" s="2" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="C447" s="2" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="448" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A448" s="2" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="B448" s="2" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="C448" s="2" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="449" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A449" s="2" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="B449" s="2" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="C449" s="2" t="s">
-        <v>183</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="450" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A450" s="2" t="s">
-        <v>1277</v>
+        <v>1280</v>
       </c>
       <c r="B450" s="2" t="s">
-        <v>185</v>
+        <v>993</v>
       </c>
       <c r="C450" s="2" t="s">
-        <v>186</v>
+        <v>994</v>
       </c>
     </row>
     <row r="451" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A451" s="2" t="s">
-        <v>1278</v>
+        <v>1281</v>
       </c>
       <c r="B451" s="2" t="s">
-        <v>1279</v>
+        <v>1282</v>
       </c>
       <c r="C451" s="2" t="s">
-        <v>1280</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="452" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A452" s="2" t="s">
-        <v>1281</v>
+        <v>1284</v>
       </c>
       <c r="B452" s="2" t="s">
-        <v>191</v>
+        <v>1285</v>
       </c>
       <c r="C452" s="2" t="s">
-        <v>192</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="453" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A453" s="2" t="s">
-        <v>1282</v>
+        <v>1287</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>1283</v>
+        <v>1288</v>
       </c>
       <c r="C453" s="2" t="s">
-        <v>1284</v>
+        <v>186</v>
       </c>
     </row>
     <row r="454" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A454" s="2" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>282</v>
+        <v>188</v>
       </c>
       <c r="C454" s="2" t="s">
-        <v>283</v>
+        <v>189</v>
       </c>
     </row>
     <row r="455" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A455" s="2" t="s">
-        <v>1286</v>
+        <v>1290</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>1287</v>
+        <v>1291</v>
       </c>
       <c r="C455" s="2" t="s">
-        <v>1288</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="456" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A456" s="2" t="s">
-        <v>1289</v>
+        <v>1293</v>
       </c>
       <c r="B456" s="2" t="s">
-        <v>1094</v>
+        <v>194</v>
       </c>
       <c r="C456" s="2" t="s">
-        <v>1290</v>
+        <v>195</v>
       </c>
     </row>
     <row r="457" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A457" s="2" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="B457" s="2" t="s">
-        <v>303</v>
+        <v>1295</v>
       </c>
       <c r="C457" s="2" t="s">
-        <v>304</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="458" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A458" s="2" t="s">
-        <v>1292</v>
+        <v>1297</v>
       </c>
       <c r="B458" s="2" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C458" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="459" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A459" s="2" t="s">
-        <v>1293</v>
+        <v>1298</v>
       </c>
       <c r="B459" s="2" t="s">
-        <v>1294</v>
+        <v>1299</v>
       </c>
       <c r="C459" s="2" t="s">
-        <v>1295</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="460" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A460" s="2" t="s">
-        <v>1296</v>
+        <v>1301</v>
       </c>
       <c r="B460" s="2" t="s">
-        <v>1297</v>
+        <v>1106</v>
       </c>
       <c r="C460" s="2" t="s">
-        <v>1298</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="461" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A461" s="2" t="s">
-        <v>1299</v>
+        <v>1303</v>
       </c>
       <c r="B461" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C461" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="462" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A462" s="2" t="s">
-        <v>1300</v>
+        <v>1304</v>
       </c>
       <c r="B462" s="2" t="s">
-        <v>1301</v>
+        <v>309</v>
       </c>
       <c r="C462" s="2" t="s">
-        <v>1302</v>
+        <v>310</v>
       </c>
     </row>
     <row r="463" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A463" s="2" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>319</v>
+        <v>1306</v>
       </c>
       <c r="C463" s="2" t="s">
-        <v>320</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="464" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A464" s="2" t="s">
-        <v>1304</v>
+        <v>1308</v>
       </c>
       <c r="B464" s="2" t="s">
-        <v>1305</v>
+        <v>1309</v>
       </c>
       <c r="C464" s="2" t="s">
-        <v>1306</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="465" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A465" s="2" t="s">
-        <v>1307</v>
+        <v>1311</v>
       </c>
       <c r="B465" s="2" t="s">
-        <v>1308</v>
+        <v>325</v>
       </c>
       <c r="C465" s="2" t="s">
-        <v>1308</v>
+        <v>326</v>
       </c>
     </row>
     <row r="466" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A466" s="2" t="s">
-        <v>1309</v>
+        <v>1312</v>
       </c>
       <c r="B466" s="2" t="s">
-        <v>1310</v>
+        <v>1313</v>
       </c>
       <c r="C466" s="2" t="s">
-        <v>1310</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="467" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A467" s="2" t="s">
-        <v>1311</v>
+        <v>1315</v>
       </c>
       <c r="B467" s="2" t="s">
-        <v>1312</v>
+        <v>331</v>
       </c>
       <c r="C467" s="2" t="s">
-        <v>1313</v>
+        <v>332</v>
       </c>
     </row>
     <row r="468" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A468" s="2" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="B468" s="2" t="s">
-        <v>1312</v>
+        <v>1317</v>
       </c>
       <c r="C468" s="2" t="s">
-        <v>1313</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="469" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A469" s="2" t="s">
-        <v>1315</v>
+        <v>1319</v>
       </c>
       <c r="B469" s="2" t="s">
-        <v>1316</v>
+        <v>1320</v>
       </c>
       <c r="C469" s="2" t="s">
-        <v>1317</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="470" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A470" s="2" t="s">
-        <v>1318</v>
+        <v>1321</v>
       </c>
       <c r="B470" s="2" t="s">
-        <v>1319</v>
+        <v>1322</v>
       </c>
       <c r="C470" s="2" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="471" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A471" s="2" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="B471" s="2" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="C471" s="2" t="s">
-        <v>1323</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="472" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A472" s="2" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B472" s="2" t="s">
         <v>1324</v>
       </c>
-      <c r="B472" s="2" t="s">
+      <c r="C472" s="2" t="s">
         <v>1325</v>
-      </c>
-      <c r="C472" s="2" t="s">
-        <v>1326</v>
       </c>
     </row>
     <row r="473" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12035,128 +12065,128 @@
         <v>1355</v>
       </c>
       <c r="C482" s="2" t="s">
-        <v>1332</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="483" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A483" s="2" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="B483" s="2" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="C483" s="2" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="484" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A484" s="2" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="B484" s="2" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="C484" s="2" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="485" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A485" s="2" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="B485" s="2" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="C485" s="2" t="s">
-        <v>1338</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="486" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A486" s="2" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="B486" s="2" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="C486" s="2" t="s">
-        <v>1366</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="487" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A487" s="2" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="C487" s="2" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="488" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A488" s="2" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="B488" s="2" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="C488" s="2" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="489" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A489" s="2" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="B489" s="2" t="s">
-        <v>1222</v>
+        <v>1375</v>
       </c>
       <c r="C489" s="2" t="s">
-        <v>1222</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="490" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A490" s="2" t="s">
-        <v>1374</v>
+        <v>1376</v>
       </c>
       <c r="B490" s="2" t="s">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="C490" s="2" t="s">
-        <v>1376</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="491" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A491" s="2" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="B491" s="2" t="s">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="C491" s="2" t="s">
-        <v>1379</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="492" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A492" s="2" t="s">
-        <v>1380</v>
+        <v>1382</v>
       </c>
       <c r="B492" s="2" t="s">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="C492" s="2" t="s">
-        <v>1382</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="493" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A493" s="2" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="B493" s="2" t="s">
-        <v>1384</v>
+        <v>1234</v>
       </c>
       <c r="C493" s="2" t="s">
-        <v>1385</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="494" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12208,54 +12238,54 @@
         <v>1398</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>1260</v>
+        <v>1399</v>
       </c>
       <c r="C498" s="2" t="s">
-        <v>1261</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="499" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A499" s="2" t="s">
-        <v>1399</v>
+        <v>1401</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>1400</v>
+        <v>1402</v>
       </c>
       <c r="C499" s="2" t="s">
-        <v>1401</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="500" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A500" s="2" t="s">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="B500" s="2" t="s">
-        <v>1403</v>
+        <v>1405</v>
       </c>
       <c r="C500" s="2" t="s">
-        <v>1404</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="501" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A501" s="2" t="s">
-        <v>1405</v>
+        <v>1407</v>
       </c>
       <c r="B501" s="2" t="s">
-        <v>1406</v>
+        <v>1408</v>
       </c>
       <c r="C501" s="2" t="s">
-        <v>1407</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="502" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A502" s="2" t="s">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="B502" s="2" t="s">
-        <v>1409</v>
+        <v>1272</v>
       </c>
       <c r="C502" s="2" t="s">
-        <v>1410</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="503" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12288,84 +12318,84 @@
         <v>1418</v>
       </c>
       <c r="C505" s="2" t="s">
-        <v>217</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="506" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A506" s="2" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="B506" s="2" t="s">
-        <v>185</v>
+        <v>1421</v>
       </c>
       <c r="C506" s="2" t="s">
-        <v>186</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="507" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A507" s="2" t="s">
-        <v>1420</v>
+        <v>1423</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>188</v>
+        <v>1424</v>
       </c>
       <c r="C507" s="2" t="s">
-        <v>189</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="508" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A508" s="2" t="s">
-        <v>1421</v>
+        <v>1426</v>
       </c>
       <c r="B508" s="2" t="s">
-        <v>628</v>
+        <v>1427</v>
       </c>
       <c r="C508" s="2" t="s">
-        <v>629</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="509" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A509" s="2" t="s">
-        <v>1422</v>
+        <v>1429</v>
       </c>
       <c r="B509" s="2" t="s">
-        <v>1423</v>
+        <v>1430</v>
       </c>
       <c r="C509" s="2" t="s">
-        <v>1424</v>
+        <v>220</v>
       </c>
     </row>
     <row r="510" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A510" s="2" t="s">
-        <v>1425</v>
+        <v>1431</v>
       </c>
       <c r="B510" s="2" t="s">
-        <v>1426</v>
+        <v>188</v>
       </c>
       <c r="C510" s="2" t="s">
-        <v>1427</v>
+        <v>189</v>
       </c>
     </row>
     <row r="511" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A511" s="2" t="s">
-        <v>1428</v>
+        <v>1432</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>1429</v>
+        <v>191</v>
       </c>
       <c r="C511" s="2" t="s">
-        <v>1430</v>
+        <v>192</v>
       </c>
     </row>
     <row r="512" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A512" s="2" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="B512" s="2" t="s">
-        <v>1432</v>
+        <v>640</v>
       </c>
       <c r="C512" s="2" t="s">
-        <v>1433</v>
+        <v>641</v>
       </c>
     </row>
     <row r="513" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12538,120 +12568,120 @@
         <v>1479</v>
       </c>
       <c r="B528" s="2" t="s">
-        <v>43</v>
+        <v>1480</v>
       </c>
       <c r="C528" s="2" t="s">
-        <v>44</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="529" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A529" s="2" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="B529" s="2" t="s">
-        <v>1481</v>
+        <v>1483</v>
       </c>
       <c r="C529" s="2" t="s">
-        <v>1104</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="530" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A530" s="2" t="s">
-        <v>1482</v>
+        <v>1485</v>
       </c>
       <c r="B530" s="2" t="s">
-        <v>1423</v>
+        <v>1486</v>
       </c>
       <c r="C530" s="2" t="s">
-        <v>1424</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="531" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A531" s="2" t="s">
-        <v>1483</v>
+        <v>1488</v>
       </c>
       <c r="B531" s="2" t="s">
-        <v>1484</v>
+        <v>1489</v>
       </c>
       <c r="C531" s="2" t="s">
-        <v>1213</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="532" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A532" s="2" t="s">
-        <v>1485</v>
+        <v>1491</v>
       </c>
       <c r="B532" s="2" t="s">
-        <v>1486</v>
+        <v>43</v>
       </c>
       <c r="C532" s="2" t="s">
-        <v>1487</v>
+        <v>44</v>
       </c>
     </row>
     <row r="533" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A533" s="2" t="s">
-        <v>1488</v>
+        <v>1492</v>
       </c>
       <c r="B533" s="2" t="s">
-        <v>1426</v>
+        <v>1493</v>
       </c>
       <c r="C533" s="2" t="s">
-        <v>1427</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="534" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A534" s="2" t="s">
-        <v>1489</v>
+        <v>1494</v>
       </c>
       <c r="B534" s="2" t="s">
-        <v>194</v>
+        <v>1435</v>
       </c>
       <c r="C534" s="2" t="s">
-        <v>194</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="535" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A535" s="2" t="s">
-        <v>1490</v>
+        <v>1495</v>
       </c>
       <c r="B535" s="2" t="s">
-        <v>1491</v>
+        <v>1496</v>
       </c>
       <c r="C535" s="2" t="s">
-        <v>1492</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="536" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A536" s="2" t="s">
-        <v>1493</v>
+        <v>1497</v>
       </c>
       <c r="B536" s="2" t="s">
-        <v>1494</v>
+        <v>1498</v>
       </c>
       <c r="C536" s="2" t="s">
-        <v>1495</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="537" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A537" s="2" t="s">
-        <v>1496</v>
+        <v>1500</v>
       </c>
       <c r="B537" s="2" t="s">
-        <v>1497</v>
+        <v>1438</v>
       </c>
       <c r="C537" s="2" t="s">
-        <v>1498</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="538" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A538" s="2" t="s">
-        <v>1499</v>
+        <v>1501</v>
       </c>
       <c r="B538" s="2" t="s">
-        <v>1500</v>
+        <v>197</v>
       </c>
       <c r="C538" s="2" t="s">
-        <v>1501</v>
+        <v>197</v>
       </c>
     </row>
     <row r="539" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12670,150 +12700,150 @@
         <v>1505</v>
       </c>
       <c r="B540" s="2" t="s">
-        <v>1257</v>
+        <v>1506</v>
       </c>
       <c r="C540" s="2" t="s">
-        <v>1258</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="541" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A541" s="2" t="s">
-        <v>1506</v>
+        <v>1508</v>
       </c>
       <c r="B541" s="2" t="s">
-        <v>4</v>
+        <v>1509</v>
       </c>
       <c r="C541" s="2" t="s">
-        <v>5</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="542" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A542" s="2" t="s">
-        <v>1507</v>
+        <v>1511</v>
       </c>
       <c r="B542" s="2" t="s">
-        <v>1245</v>
+        <v>1512</v>
       </c>
       <c r="C542" s="2" t="s">
-        <v>1246</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="543" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A543" s="2" t="s">
-        <v>1508</v>
+        <v>1514</v>
       </c>
       <c r="B543" s="2" t="s">
-        <v>1260</v>
+        <v>1515</v>
       </c>
       <c r="C543" s="2" t="s">
-        <v>1261</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="544" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A544" s="2" t="s">
-        <v>1509</v>
+        <v>1517</v>
       </c>
       <c r="B544" s="2" t="s">
-        <v>1510</v>
+        <v>1269</v>
       </c>
       <c r="C544" s="2" t="s">
-        <v>1511</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="545" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A545" s="2" t="s">
-        <v>1512</v>
+        <v>1518</v>
       </c>
       <c r="B545" s="2" t="s">
-        <v>1513</v>
+        <v>4</v>
       </c>
       <c r="C545" s="2" t="s">
-        <v>1514</v>
+        <v>5</v>
       </c>
     </row>
     <row r="546" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A546" s="2" t="s">
-        <v>1515</v>
+        <v>1519</v>
       </c>
       <c r="B546" s="2" t="s">
-        <v>1263</v>
+        <v>1257</v>
       </c>
       <c r="C546" s="2" t="s">
-        <v>1264</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="547" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A547" s="2" t="s">
-        <v>1516</v>
+        <v>1520</v>
       </c>
       <c r="B547" s="2" t="s">
-        <v>1517</v>
+        <v>1272</v>
       </c>
       <c r="C547" s="2" t="s">
-        <v>1518</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="548" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A548" s="2" t="s">
-        <v>1519</v>
+        <v>1521</v>
       </c>
       <c r="B548" s="2" t="s">
-        <v>1266</v>
+        <v>1522</v>
       </c>
       <c r="C548" s="2" t="s">
-        <v>1520</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="549" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A549" s="2" t="s">
-        <v>1521</v>
+        <v>1524</v>
       </c>
       <c r="B549" s="2" t="s">
-        <v>1212</v>
+        <v>1525</v>
       </c>
       <c r="C549" s="2" t="s">
-        <v>1522</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="550" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A550" s="2" t="s">
-        <v>1523</v>
+        <v>1527</v>
       </c>
       <c r="B550" s="2" t="s">
-        <v>1524</v>
+        <v>1275</v>
       </c>
       <c r="C550" s="2" t="s">
-        <v>1525</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="551" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A551" s="2" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
       <c r="B551" s="2" t="s">
-        <v>1527</v>
+        <v>1529</v>
       </c>
       <c r="C551" s="2" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="552" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A552" s="2" t="s">
-        <v>1529</v>
+        <v>1531</v>
       </c>
       <c r="B552" s="2" t="s">
-        <v>1530</v>
+        <v>1278</v>
       </c>
       <c r="C552" s="2" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="553" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A553" s="2" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="B553" s="2" t="s">
-        <v>1533</v>
+        <v>1224</v>
       </c>
       <c r="C553" s="2" t="s">
         <v>1534</v>
@@ -12879,153 +12909,153 @@
         <v>1550</v>
       </c>
       <c r="B559" s="2" t="s">
-        <v>1257</v>
+        <v>1551</v>
       </c>
       <c r="C559" s="2" t="s">
-        <v>1258</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="560" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A560" s="2" t="s">
-        <v>1551</v>
+        <v>1553</v>
       </c>
       <c r="B560" s="2" t="s">
-        <v>4</v>
+        <v>1554</v>
       </c>
       <c r="C560" s="2" t="s">
-        <v>5</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="561" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A561" s="2" t="s">
-        <v>1552</v>
+        <v>1556</v>
       </c>
       <c r="B561" s="2" t="s">
-        <v>1263</v>
+        <v>1557</v>
       </c>
       <c r="C561" s="2" t="s">
-        <v>1264</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="562" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A562" s="2" t="s">
-        <v>1553</v>
+        <v>1559</v>
       </c>
       <c r="B562" s="2" t="s">
-        <v>1554</v>
+        <v>1560</v>
       </c>
       <c r="C562" s="2" t="s">
-        <v>1555</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="563" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A563" s="2" t="s">
-        <v>1556</v>
+        <v>1562</v>
       </c>
       <c r="B563" s="2" t="s">
-        <v>1557</v>
+        <v>1269</v>
       </c>
       <c r="C563" s="2" t="s">
-        <v>1558</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="564" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A564" s="2" t="s">
-        <v>1559</v>
+        <v>1563</v>
       </c>
       <c r="B564" s="2" t="s">
-        <v>1560</v>
+        <v>4</v>
       </c>
       <c r="C564" s="2" t="s">
-        <v>1561</v>
+        <v>5</v>
       </c>
     </row>
     <row r="565" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A565" s="2" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="B565" s="2" t="s">
-        <v>1533</v>
+        <v>1275</v>
       </c>
       <c r="C565" s="2" t="s">
-        <v>1534</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="566" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A566" s="2" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="B566" s="2" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="C566" s="2" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="567" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A567" s="2" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
       <c r="B567" s="2" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="C567" s="2" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="568" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A568" s="2" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
       <c r="B568" s="2" t="s">
-        <v>1387</v>
+        <v>1572</v>
       </c>
       <c r="C568" s="2" t="s">
-        <v>1388</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="569" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A569" s="2" t="s">
-        <v>1570</v>
+        <v>1574</v>
       </c>
       <c r="B569" s="2" t="s">
-        <v>1571</v>
+        <v>1545</v>
       </c>
       <c r="C569" s="2" t="s">
-        <v>1572</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="570" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A570" s="2" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
       <c r="B570" s="2" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="C570" s="2" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="571" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A571" s="2" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="B571" s="2" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="C571" s="2" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="572" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A572" s="2" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="B572" s="2" t="s">
-        <v>1580</v>
+        <v>1399</v>
       </c>
       <c r="C572" s="2" t="s">
-        <v>1581</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="573" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13069,51 +13099,51 @@
         <v>1592</v>
       </c>
       <c r="C576" s="2" t="s">
-        <v>533</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="577" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A577" s="2" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="B577" s="2" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="C577" s="2" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="578" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A578" s="2" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="B578" s="2" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="C578" s="2" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="579" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A579" s="2" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="B579" s="2" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="C579" s="2" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="580" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A580" s="2" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="B580" s="2" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="C580" s="2" t="s">
-        <v>1604</v>
+        <v>545</v>
       </c>
     </row>
     <row r="581" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13165,87 +13195,87 @@
         <v>1617</v>
       </c>
       <c r="B585" s="2" t="s">
-        <v>532</v>
+        <v>1618</v>
       </c>
       <c r="C585" s="2" t="s">
-        <v>533</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="586" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A586" s="2" t="s">
-        <v>1618</v>
+        <v>1620</v>
       </c>
       <c r="B586" s="2" t="s">
-        <v>1619</v>
+        <v>1621</v>
       </c>
       <c r="C586" s="2" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="587" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A587" s="2" t="s">
-        <v>1621</v>
+        <v>1623</v>
       </c>
       <c r="B587" s="2" t="s">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="C587" s="2" t="s">
-        <v>1623</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="588" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A588" s="2" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
       <c r="B588" s="2" t="s">
-        <v>282</v>
+        <v>1627</v>
       </c>
       <c r="C588" s="2" t="s">
-        <v>283</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="589" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A589" s="2" t="s">
-        <v>1625</v>
+        <v>1629</v>
       </c>
       <c r="B589" s="2" t="s">
-        <v>1626</v>
+        <v>544</v>
       </c>
       <c r="C589" s="2" t="s">
-        <v>1627</v>
+        <v>545</v>
       </c>
     </row>
     <row r="590" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A590" s="2" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="B590" s="2" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
       <c r="C590" s="2" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="591" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A591" s="2" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
       <c r="B591" s="2" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="C591" s="2" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="592" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A592" s="2" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="B592" s="2" t="s">
-        <v>1635</v>
+        <v>294</v>
       </c>
       <c r="C592" s="2" t="s">
-        <v>1636</v>
+        <v>295</v>
       </c>
     </row>
     <row r="593" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13341,87 +13371,87 @@
         <v>1661</v>
       </c>
       <c r="B601" s="2" t="s">
-        <v>276</v>
+        <v>1662</v>
       </c>
       <c r="C601" s="2" t="s">
-        <v>277</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="602" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A602" s="2" t="s">
-        <v>1662</v>
+        <v>1664</v>
       </c>
       <c r="B602" s="2" t="s">
-        <v>1663</v>
+        <v>1665</v>
       </c>
       <c r="C602" s="2" t="s">
-        <v>1104</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="603" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A603" s="2" t="s">
-        <v>1664</v>
+        <v>1667</v>
       </c>
       <c r="B603" s="2" t="s">
-        <v>1665</v>
+        <v>1668</v>
       </c>
       <c r="C603" s="2" t="s">
-        <v>1666</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="604" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A604" s="2" t="s">
-        <v>1667</v>
+        <v>1670</v>
       </c>
       <c r="B604" s="2" t="s">
-        <v>1486</v>
+        <v>1671</v>
       </c>
       <c r="C604" s="2" t="s">
-        <v>1487</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="605" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A605" s="2" t="s">
-        <v>1668</v>
+        <v>1673</v>
       </c>
       <c r="B605" s="2" t="s">
-        <v>1669</v>
+        <v>288</v>
       </c>
       <c r="C605" s="2" t="s">
-        <v>1670</v>
+        <v>289</v>
       </c>
     </row>
     <row r="606" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A606" s="2" t="s">
-        <v>1671</v>
+        <v>1674</v>
       </c>
       <c r="B606" s="2" t="s">
-        <v>1672</v>
+        <v>1675</v>
       </c>
       <c r="C606" s="2" t="s">
-        <v>1673</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="607" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A607" s="2" t="s">
-        <v>1674</v>
+        <v>1676</v>
       </c>
       <c r="B607" s="2" t="s">
-        <v>1675</v>
+        <v>1677</v>
       </c>
       <c r="C607" s="2" t="s">
-        <v>1676</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="608" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A608" s="2" t="s">
-        <v>1677</v>
+        <v>1679</v>
       </c>
       <c r="B608" s="2" t="s">
-        <v>1678</v>
+        <v>1498</v>
       </c>
       <c r="C608" s="2" t="s">
-        <v>1679</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="609" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13440,98 +13470,98 @@
         <v>1683</v>
       </c>
       <c r="B610" s="2" t="s">
-        <v>185</v>
+        <v>1684</v>
       </c>
       <c r="C610" s="2" t="s">
-        <v>186</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="611" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A611" s="2" t="s">
-        <v>1684</v>
+        <v>1686</v>
       </c>
       <c r="B611" s="2" t="s">
-        <v>1101</v>
+        <v>1687</v>
       </c>
       <c r="C611" s="2" t="s">
-        <v>642</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="612" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A612" s="2" t="s">
-        <v>1685</v>
+        <v>1689</v>
       </c>
       <c r="B612" s="2" t="s">
-        <v>1110</v>
+        <v>1690</v>
       </c>
       <c r="C612" s="2" t="s">
-        <v>1686</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="613" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A613" s="2" t="s">
-        <v>1687</v>
+        <v>1692</v>
       </c>
       <c r="B613" s="2" t="s">
-        <v>1688</v>
+        <v>1693</v>
       </c>
       <c r="C613" s="2" t="s">
-        <v>1689</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="614" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A614" s="2" t="s">
-        <v>1690</v>
+        <v>1695</v>
       </c>
       <c r="B614" s="2" t="s">
-        <v>276</v>
+        <v>188</v>
       </c>
       <c r="C614" s="2" t="s">
-        <v>277</v>
+        <v>189</v>
       </c>
     </row>
     <row r="615" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A615" s="2" t="s">
-        <v>1691</v>
+        <v>1696</v>
       </c>
       <c r="B615" s="2" t="s">
-        <v>1692</v>
+        <v>1113</v>
       </c>
       <c r="C615" s="2" t="s">
-        <v>1693</v>
+        <v>654</v>
       </c>
     </row>
     <row r="616" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A616" s="2" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="B616" s="2" t="s">
-        <v>1695</v>
+        <v>1122</v>
       </c>
       <c r="C616" s="2" t="s">
-        <v>1696</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="617" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A617" s="2" t="s">
-        <v>1697</v>
+        <v>1699</v>
       </c>
       <c r="B617" s="2" t="s">
-        <v>1698</v>
+        <v>1700</v>
       </c>
       <c r="C617" s="2" t="s">
-        <v>1699</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="618" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A618" s="2" t="s">
-        <v>1700</v>
+        <v>1702</v>
       </c>
       <c r="B618" s="2" t="s">
-        <v>1701</v>
+        <v>288</v>
       </c>
       <c r="C618" s="2" t="s">
-        <v>1702</v>
+        <v>289</v>
       </c>
     </row>
     <row r="619" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13539,54 +13569,54 @@
         <v>1703</v>
       </c>
       <c r="B619" s="2" t="s">
-        <v>282</v>
+        <v>1704</v>
       </c>
       <c r="C619" s="2" t="s">
-        <v>283</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="620" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A620" s="2" t="s">
-        <v>1704</v>
+        <v>1706</v>
       </c>
       <c r="B620" s="2" t="s">
-        <v>1705</v>
+        <v>1707</v>
       </c>
       <c r="C620" s="2" t="s">
-        <v>1706</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="621" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A621" s="2" t="s">
-        <v>1707</v>
+        <v>1709</v>
       </c>
       <c r="B621" s="2" t="s">
-        <v>1708</v>
+        <v>1710</v>
       </c>
       <c r="C621" s="2" t="s">
-        <v>1709</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="622" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A622" s="2" t="s">
-        <v>1710</v>
+        <v>1712</v>
       </c>
       <c r="B622" s="2" t="s">
-        <v>1711</v>
+        <v>1713</v>
       </c>
       <c r="C622" s="2" t="s">
-        <v>1712</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="623" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A623" s="2" t="s">
-        <v>1713</v>
+        <v>1715</v>
       </c>
       <c r="B623" s="2" t="s">
-        <v>1714</v>
+        <v>294</v>
       </c>
       <c r="C623" s="2" t="s">
-        <v>1715</v>
+        <v>295</v>
       </c>
     </row>
     <row r="624" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13605,54 +13635,54 @@
         <v>1719</v>
       </c>
       <c r="B625" s="2" t="s">
-        <v>532</v>
+        <v>1720</v>
       </c>
       <c r="C625" s="2" t="s">
-        <v>533</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="626" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A626" s="2" t="s">
-        <v>1720</v>
+        <v>1722</v>
       </c>
       <c r="B626" s="2" t="s">
-        <v>1721</v>
+        <v>1723</v>
       </c>
       <c r="C626" s="2" t="s">
-        <v>1722</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="627" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A627" s="2" t="s">
-        <v>1723</v>
+        <v>1725</v>
       </c>
       <c r="B627" s="2" t="s">
-        <v>1724</v>
+        <v>1726</v>
       </c>
       <c r="C627" s="2" t="s">
-        <v>1725</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="628" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A628" s="2" t="s">
-        <v>1726</v>
+        <v>1728</v>
       </c>
       <c r="B628" s="2" t="s">
-        <v>1727</v>
+        <v>1729</v>
       </c>
       <c r="C628" s="2" t="s">
-        <v>1728</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="629" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A629" s="2" t="s">
-        <v>1729</v>
+        <v>1731</v>
       </c>
       <c r="B629" s="2" t="s">
-        <v>1730</v>
+        <v>544</v>
       </c>
       <c r="C629" s="2" t="s">
-        <v>1731</v>
+        <v>545</v>
       </c>
     </row>
     <row r="630" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13715,54 +13745,54 @@
         <v>1747</v>
       </c>
       <c r="B635" s="2" t="s">
-        <v>19</v>
+        <v>1748</v>
       </c>
       <c r="C635" s="2" t="s">
-        <v>20</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="636" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A636" s="2" t="s">
-        <v>1748</v>
+        <v>1750</v>
       </c>
       <c r="B636" s="2" t="s">
-        <v>1749</v>
+        <v>1751</v>
       </c>
       <c r="C636" s="2" t="s">
-        <v>1750</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="637" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A637" s="2" t="s">
-        <v>1751</v>
+        <v>1753</v>
       </c>
       <c r="B637" s="2" t="s">
-        <v>1752</v>
+        <v>1754</v>
       </c>
       <c r="C637" s="2" t="s">
-        <v>1753</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="638" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A638" s="2" t="s">
-        <v>1754</v>
+        <v>1756</v>
       </c>
       <c r="B638" s="2" t="s">
-        <v>1755</v>
+        <v>1757</v>
       </c>
       <c r="C638" s="2" t="s">
-        <v>1756</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="639" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A639" s="2" t="s">
-        <v>1757</v>
+        <v>1759</v>
       </c>
       <c r="B639" s="2" t="s">
-        <v>1758</v>
+        <v>19</v>
       </c>
       <c r="C639" s="2" t="s">
-        <v>1759</v>
+        <v>20</v>
       </c>
     </row>
     <row r="640" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13825,241 +13855,241 @@
         <v>1775</v>
       </c>
       <c r="B645" s="2" t="s">
-        <v>1776</v>
+        <v>273</v>
       </c>
       <c r="C645" s="2" t="s">
-        <v>1777</v>
+        <v>274</v>
       </c>
     </row>
     <row r="646" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A646" s="2" t="s">
+        <v>1776</v>
+      </c>
+      <c r="B646" s="2" t="s">
+        <v>1777</v>
+      </c>
+      <c r="C646" s="2" t="s">
         <v>1778</v>
-      </c>
-      <c r="B646" s="2" t="s">
-        <v>1779</v>
-      </c>
-      <c r="C646" s="2" t="s">
-        <v>1780</v>
       </c>
     </row>
     <row r="647" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A647" s="2" t="s">
+        <v>1779</v>
+      </c>
+      <c r="B647" s="2" t="s">
+        <v>1780</v>
+      </c>
+      <c r="C647" s="2" t="s">
         <v>1781</v>
-      </c>
-      <c r="B647" s="2" t="s">
-        <v>1782</v>
-      </c>
-      <c r="C647" s="2" t="s">
-        <v>1783</v>
       </c>
     </row>
     <row r="648" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A648" s="2" t="s">
+        <v>1782</v>
+      </c>
+      <c r="B648" s="2" t="s">
+        <v>1783</v>
+      </c>
+      <c r="C648" s="2" t="s">
         <v>1784</v>
-      </c>
-      <c r="B648" s="2" t="s">
-        <v>1785</v>
-      </c>
-      <c r="C648" s="2" t="s">
-        <v>1786</v>
       </c>
     </row>
     <row r="649" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A649" s="2" t="s">
+        <v>1785</v>
+      </c>
+      <c r="B649" s="2" t="s">
+        <v>1786</v>
+      </c>
+      <c r="C649" s="2" t="s">
         <v>1787</v>
-      </c>
-      <c r="B649" s="2" t="s">
-        <v>1788</v>
-      </c>
-      <c r="C649" s="2" t="s">
-        <v>1789</v>
       </c>
     </row>
     <row r="650" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A650" s="2" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B650" s="2" t="s">
+        <v>1789</v>
+      </c>
+      <c r="C650" s="2" t="s">
         <v>1790</v>
-      </c>
-      <c r="B650" s="2" t="s">
-        <v>744</v>
-      </c>
-      <c r="C650" s="2" t="s">
-        <v>1791</v>
       </c>
     </row>
     <row r="651" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A651" s="2" t="s">
+        <v>1791</v>
+      </c>
+      <c r="B651" s="2" t="s">
         <v>1792</v>
       </c>
-      <c r="B651" s="2" t="s">
+      <c r="C651" s="2" t="s">
         <v>1793</v>
-      </c>
-      <c r="C651" s="2" t="s">
-        <v>1794</v>
       </c>
     </row>
     <row r="652" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A652" s="2" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B652" s="2" t="s">
         <v>1795</v>
       </c>
-      <c r="B652" s="2" t="s">
+      <c r="C652" s="2" t="s">
         <v>1796</v>
-      </c>
-      <c r="C652" s="2" t="s">
-        <v>1797</v>
       </c>
     </row>
     <row r="653" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A653" s="2" t="s">
+        <v>1797</v>
+      </c>
+      <c r="B653" s="2" t="s">
         <v>1798</v>
       </c>
-      <c r="B653" s="2" t="s">
+      <c r="C653" s="2" t="s">
         <v>1799</v>
-      </c>
-      <c r="C653" s="2" t="s">
-        <v>1800</v>
       </c>
     </row>
     <row r="654" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A654" s="2" t="s">
+        <v>1800</v>
+      </c>
+      <c r="B654" s="2" t="s">
+        <v>756</v>
+      </c>
+      <c r="C654" s="2" t="s">
         <v>1801</v>
-      </c>
-      <c r="B654" s="2" t="s">
-        <v>1802</v>
-      </c>
-      <c r="C654" s="2" t="s">
-        <v>1803</v>
       </c>
     </row>
     <row r="655" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A655" s="2" t="s">
+        <v>1802</v>
+      </c>
+      <c r="B655" s="2" t="s">
+        <v>1803</v>
+      </c>
+      <c r="C655" s="2" t="s">
         <v>1804</v>
-      </c>
-      <c r="B655" s="2" t="s">
-        <v>1805</v>
-      </c>
-      <c r="C655" s="2" t="s">
-        <v>1806</v>
       </c>
     </row>
     <row r="656" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A656" s="2" t="s">
+        <v>1805</v>
+      </c>
+      <c r="B656" s="2" t="s">
+        <v>1806</v>
+      </c>
+      <c r="C656" s="2" t="s">
         <v>1807</v>
-      </c>
-      <c r="B656" s="2" t="s">
-        <v>1808</v>
-      </c>
-      <c r="C656" s="2" t="s">
-        <v>1809</v>
       </c>
     </row>
     <row r="657" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A657" s="2" t="s">
+        <v>1808</v>
+      </c>
+      <c r="B657" s="2" t="s">
+        <v>1809</v>
+      </c>
+      <c r="C657" s="2" t="s">
         <v>1810</v>
-      </c>
-      <c r="B657" s="2" t="s">
-        <v>1811</v>
-      </c>
-      <c r="C657" s="2" t="s">
-        <v>1812</v>
       </c>
     </row>
     <row r="658" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A658" s="2" t="s">
+        <v>1811</v>
+      </c>
+      <c r="B658" s="2" t="s">
+        <v>1812</v>
+      </c>
+      <c r="C658" s="2" t="s">
         <v>1813</v>
-      </c>
-      <c r="B658" s="2" t="s">
-        <v>1814</v>
-      </c>
-      <c r="C658" s="2" t="s">
-        <v>1815</v>
       </c>
     </row>
     <row r="659" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A659" s="2" t="s">
+        <v>1814</v>
+      </c>
+      <c r="B659" s="2" t="s">
+        <v>1815</v>
+      </c>
+      <c r="C659" s="2" t="s">
         <v>1816</v>
-      </c>
-      <c r="B659" s="2" t="s">
-        <v>1817</v>
-      </c>
-      <c r="C659" s="2" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="660" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A660" s="2" t="s">
+        <v>1817</v>
+      </c>
+      <c r="B660" s="2" t="s">
         <v>1818</v>
       </c>
-      <c r="B660" s="2" t="s">
+      <c r="C660" s="2" t="s">
         <v>1819</v>
-      </c>
-      <c r="C660" s="2" t="s">
-        <v>1820</v>
       </c>
     </row>
     <row r="661" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A661" s="2" t="s">
+        <v>1820</v>
+      </c>
+      <c r="B661" s="2" t="s">
         <v>1821</v>
       </c>
-      <c r="B661" s="2" t="s">
+      <c r="C661" s="2" t="s">
         <v>1822</v>
-      </c>
-      <c r="C661" s="2" t="s">
-        <v>1823</v>
       </c>
     </row>
     <row r="662" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A662" s="2" t="s">
+        <v>1823</v>
+      </c>
+      <c r="B662" s="2" t="s">
         <v>1824</v>
       </c>
-      <c r="B662" s="2" t="s">
-        <v>276</v>
-      </c>
       <c r="C662" s="2" t="s">
-        <v>277</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="663" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A663" s="2" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="B663" s="2" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="C663" s="2" t="s">
-        <v>183</v>
+        <v>467</v>
       </c>
     </row>
     <row r="664" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A664" s="2" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="B664" s="2" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="C664" s="2" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="665" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A665" s="2" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="B665" s="2" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="C665" s="2" t="s">
-        <v>455</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="666" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A666" s="2" t="s">
-        <v>1832</v>
+        <v>1834</v>
       </c>
       <c r="B666" s="2" t="s">
-        <v>1833</v>
+        <v>288</v>
       </c>
       <c r="C666" s="2" t="s">
-        <v>1834</v>
+        <v>289</v>
       </c>
     </row>
     <row r="667" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14067,76 +14097,76 @@
         <v>1835</v>
       </c>
       <c r="B667" s="2" t="s">
-        <v>857</v>
+        <v>1836</v>
       </c>
       <c r="C667" s="2" t="s">
-        <v>858</v>
+        <v>186</v>
       </c>
     </row>
     <row r="668" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A668" s="2" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="B668" s="2" t="s">
-        <v>4</v>
+        <v>1838</v>
       </c>
       <c r="C668" s="2" t="s">
-        <v>5</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="669" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A669" s="2" t="s">
-        <v>1837</v>
+        <v>1840</v>
       </c>
       <c r="B669" s="2" t="s">
-        <v>282</v>
+        <v>1841</v>
       </c>
       <c r="C669" s="2" t="s">
-        <v>283</v>
+        <v>467</v>
       </c>
     </row>
     <row r="670" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A670" s="2" t="s">
-        <v>1838</v>
+        <v>1842</v>
       </c>
       <c r="B670" s="2" t="s">
-        <v>1833</v>
+        <v>1843</v>
       </c>
       <c r="C670" s="2" t="s">
-        <v>1834</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="671" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A671" s="2" t="s">
-        <v>1839</v>
+        <v>1845</v>
       </c>
       <c r="B671" s="2" t="s">
-        <v>1840</v>
+        <v>869</v>
       </c>
       <c r="C671" s="2" t="s">
-        <v>1841</v>
+        <v>870</v>
       </c>
     </row>
     <row r="672" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A672" s="2" t="s">
-        <v>1842</v>
+        <v>1846</v>
       </c>
       <c r="B672" s="2" t="s">
-        <v>1843</v>
+        <v>4</v>
       </c>
       <c r="C672" s="2" t="s">
-        <v>1844</v>
+        <v>5</v>
       </c>
     </row>
     <row r="673" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A673" s="2" t="s">
-        <v>1845</v>
+        <v>1847</v>
       </c>
       <c r="B673" s="2" t="s">
-        <v>1846</v>
+        <v>294</v>
       </c>
       <c r="C673" s="2" t="s">
-        <v>1847</v>
+        <v>295</v>
       </c>
     </row>
     <row r="674" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14144,65 +14174,65 @@
         <v>1848</v>
       </c>
       <c r="B674" s="2" t="s">
-        <v>1849</v>
+        <v>1843</v>
       </c>
       <c r="C674" s="2" t="s">
-        <v>1850</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="675" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A675" s="2" t="s">
+        <v>1849</v>
+      </c>
+      <c r="B675" s="2" t="s">
+        <v>1850</v>
+      </c>
+      <c r="C675" s="2" t="s">
         <v>1851</v>
-      </c>
-      <c r="B675" s="2" t="s">
-        <v>1852</v>
-      </c>
-      <c r="C675" s="2" t="s">
-        <v>1853</v>
       </c>
     </row>
     <row r="676" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A676" s="2" t="s">
+        <v>1852</v>
+      </c>
+      <c r="B676" s="2" t="s">
+        <v>1853</v>
+      </c>
+      <c r="C676" s="2" t="s">
         <v>1854</v>
-      </c>
-      <c r="B676" s="2" t="s">
-        <v>1855</v>
-      </c>
-      <c r="C676" s="2" t="s">
-        <v>1856</v>
       </c>
     </row>
     <row r="677" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A677" s="2" t="s">
+        <v>1855</v>
+      </c>
+      <c r="B677" s="2" t="s">
+        <v>1856</v>
+      </c>
+      <c r="C677" s="2" t="s">
         <v>1857</v>
-      </c>
-      <c r="B677" s="2" t="s">
-        <v>1858</v>
-      </c>
-      <c r="C677" s="2" t="s">
-        <v>1859</v>
       </c>
     </row>
     <row r="678" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A678" s="2" t="s">
+        <v>1858</v>
+      </c>
+      <c r="B678" s="2" t="s">
+        <v>1859</v>
+      </c>
+      <c r="C678" s="2" t="s">
         <v>1860</v>
-      </c>
-      <c r="B678" s="2" t="s">
-        <v>1861</v>
-      </c>
-      <c r="C678" s="2" t="s">
-        <v>1862</v>
       </c>
     </row>
     <row r="679" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A679" s="2" t="s">
+        <v>1861</v>
+      </c>
+      <c r="B679" s="2" t="s">
+        <v>1862</v>
+      </c>
+      <c r="C679" s="2" t="s">
         <v>1863</v>
-      </c>
-      <c r="B679" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C679" s="2" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="680" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14210,54 +14240,54 @@
         <v>1864</v>
       </c>
       <c r="B680" s="2" t="s">
-        <v>13</v>
+        <v>1865</v>
       </c>
       <c r="C680" s="2" t="s">
-        <v>14</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="681" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A681" s="2" t="s">
-        <v>1865</v>
+        <v>1867</v>
       </c>
       <c r="B681" s="2" t="s">
-        <v>16</v>
+        <v>1868</v>
       </c>
       <c r="C681" s="2" t="s">
-        <v>17</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="682" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A682" s="2" t="s">
-        <v>1866</v>
+        <v>1870</v>
       </c>
       <c r="B682" s="2" t="s">
-        <v>1867</v>
+        <v>1871</v>
       </c>
       <c r="C682" s="2" t="s">
-        <v>1868</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="683" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A683" s="2" t="s">
-        <v>1869</v>
+        <v>1873</v>
       </c>
       <c r="B683" s="2" t="s">
-        <v>1870</v>
+        <v>19</v>
       </c>
       <c r="C683" s="2" t="s">
-        <v>1871</v>
+        <v>20</v>
       </c>
     </row>
     <row r="684" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A684" s="2" t="s">
-        <v>1872</v>
+        <v>1874</v>
       </c>
       <c r="B684" s="2" t="s">
-        <v>1873</v>
+        <v>13</v>
       </c>
       <c r="C684" s="2" t="s">
-        <v>1874</v>
+        <v>14</v>
       </c>
     </row>
     <row r="685" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14265,21 +14295,21 @@
         <v>1875</v>
       </c>
       <c r="B685" s="2" t="s">
-        <v>1876</v>
+        <v>16</v>
       </c>
       <c r="C685" s="2" t="s">
-        <v>1877</v>
+        <v>17</v>
       </c>
     </row>
     <row r="686" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A686" s="2" t="s">
+        <v>1876</v>
+      </c>
+      <c r="B686" s="2" t="s">
+        <v>1877</v>
+      </c>
+      <c r="C686" s="2" t="s">
         <v>1878</v>
-      </c>
-      <c r="B686" s="2" t="s">
-        <v>1776</v>
-      </c>
-      <c r="C686" s="2" t="s">
-        <v>1777</v>
       </c>
     </row>
     <row r="687" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14287,175 +14317,175 @@
         <v>1879</v>
       </c>
       <c r="B687" s="2" t="s">
-        <v>1779</v>
+        <v>1880</v>
       </c>
       <c r="C687" s="2" t="s">
-        <v>1780</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="688" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A688" s="2" t="s">
-        <v>1880</v>
+        <v>1882</v>
       </c>
       <c r="B688" s="2" t="s">
-        <v>1881</v>
+        <v>1883</v>
       </c>
       <c r="C688" s="2" t="s">
-        <v>1267</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="689" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A689" s="2" t="s">
-        <v>1882</v>
+        <v>1885</v>
       </c>
       <c r="B689" s="2" t="s">
-        <v>1883</v>
+        <v>1886</v>
       </c>
       <c r="C689" s="2" t="s">
-        <v>1884</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="690" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A690" s="2" t="s">
-        <v>1885</v>
+        <v>1888</v>
       </c>
       <c r="B690" s="2" t="s">
-        <v>1113</v>
+        <v>1786</v>
       </c>
       <c r="C690" s="2" t="s">
-        <v>1114</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="691" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A691" s="2" t="s">
-        <v>1886</v>
+        <v>1889</v>
       </c>
       <c r="B691" s="2" t="s">
-        <v>1887</v>
+        <v>1789</v>
       </c>
       <c r="C691" s="2" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="692" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A692" s="2" t="s">
-        <v>1888</v>
+        <v>1890</v>
       </c>
       <c r="B692" s="2" t="s">
-        <v>744</v>
+        <v>1891</v>
       </c>
       <c r="C692" s="2" t="s">
-        <v>1791</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="693" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A693" s="2" t="s">
-        <v>1889</v>
+        <v>1892</v>
       </c>
       <c r="B693" s="2" t="s">
-        <v>1890</v>
+        <v>1893</v>
       </c>
       <c r="C693" s="2" t="s">
-        <v>1891</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="694" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A694" s="2" t="s">
-        <v>1892</v>
+        <v>1895</v>
       </c>
       <c r="B694" s="2" t="s">
-        <v>1893</v>
+        <v>1125</v>
       </c>
       <c r="C694" s="2" t="s">
-        <v>1884</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="695" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A695" s="2" t="s">
-        <v>1894</v>
+        <v>1896</v>
       </c>
       <c r="B695" s="2" t="s">
-        <v>841</v>
+        <v>1897</v>
       </c>
       <c r="C695" s="2" t="s">
-        <v>1895</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="696" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A696" s="2" t="s">
-        <v>1896</v>
+        <v>1898</v>
       </c>
       <c r="B696" s="2" t="s">
-        <v>853</v>
+        <v>756</v>
       </c>
       <c r="C696" s="2" t="s">
-        <v>1897</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="697" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A697" s="2" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="B697" s="2" t="s">
-        <v>535</v>
+        <v>1900</v>
       </c>
       <c r="C697" s="2" t="s">
-        <v>455</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="698" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A698" s="2" t="s">
-        <v>1899</v>
+        <v>1902</v>
       </c>
       <c r="B698" s="2" t="s">
-        <v>857</v>
+        <v>1903</v>
       </c>
       <c r="C698" s="2" t="s">
-        <v>858</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="699" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A699" s="2" t="s">
-        <v>1900</v>
+        <v>1904</v>
       </c>
       <c r="B699" s="2" t="s">
-        <v>282</v>
+        <v>853</v>
       </c>
       <c r="C699" s="2" t="s">
-        <v>283</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="700" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A700" s="2" t="s">
-        <v>1901</v>
+        <v>1906</v>
       </c>
       <c r="B700" s="2" t="s">
-        <v>1902</v>
+        <v>865</v>
       </c>
       <c r="C700" s="2" t="s">
-        <v>1903</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="701" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A701" s="2" t="s">
-        <v>1904</v>
+        <v>1908</v>
       </c>
       <c r="B701" s="2" t="s">
-        <v>1905</v>
+        <v>547</v>
       </c>
       <c r="C701" s="2" t="s">
-        <v>1906</v>
+        <v>467</v>
       </c>
     </row>
     <row r="702" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A702" s="2" t="s">
-        <v>1907</v>
+        <v>1909</v>
       </c>
       <c r="B702" s="2" t="s">
-        <v>1908</v>
+        <v>869</v>
       </c>
       <c r="C702" s="2" t="s">
-        <v>1909</v>
+        <v>870</v>
       </c>
     </row>
     <row r="703" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14463,10 +14493,10 @@
         <v>1910</v>
       </c>
       <c r="B703" s="2" t="s">
-        <v>885</v>
+        <v>294</v>
       </c>
       <c r="C703" s="2" t="s">
-        <v>886</v>
+        <v>295</v>
       </c>
     </row>
     <row r="704" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14474,65 +14504,65 @@
         <v>1911</v>
       </c>
       <c r="B704" s="2" t="s">
-        <v>853</v>
+        <v>1912</v>
       </c>
       <c r="C704" s="2" t="s">
-        <v>1897</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="705" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A705" s="2" t="s">
-        <v>1912</v>
+        <v>1914</v>
       </c>
       <c r="B705" s="2" t="s">
-        <v>889</v>
+        <v>1915</v>
       </c>
       <c r="C705" s="2" t="s">
-        <v>890</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="706" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A706" s="2" t="s">
-        <v>1913</v>
+        <v>1917</v>
       </c>
       <c r="B706" s="2" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C706" s="2" t="s">
-        <v>1915</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="707" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A707" s="2" t="s">
-        <v>1916</v>
+        <v>1920</v>
       </c>
       <c r="B707" s="2" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="C707" s="2" t="s">
-        <v>1917</v>
+        <v>898</v>
       </c>
     </row>
     <row r="708" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A708" s="2" t="s">
-        <v>1918</v>
+        <v>1921</v>
       </c>
       <c r="B708" s="2" t="s">
-        <v>1919</v>
+        <v>865</v>
       </c>
       <c r="C708" s="2" t="s">
-        <v>1920</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="709" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A709" s="2" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="B709" s="2" t="s">
         <v>901</v>
       </c>
       <c r="C709" s="2" t="s">
-        <v>1922</v>
+        <v>902</v>
       </c>
     </row>
     <row r="710" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14551,32 +14581,32 @@
         <v>1926</v>
       </c>
       <c r="B711" s="2" t="s">
+        <v>907</v>
+      </c>
+      <c r="C711" s="2" t="s">
         <v>1927</v>
-      </c>
-      <c r="C711" s="2" t="s">
-        <v>1928</v>
       </c>
     </row>
     <row r="712" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A712" s="2" t="s">
+        <v>1928</v>
+      </c>
+      <c r="B712" s="2" t="s">
         <v>1929</v>
       </c>
-      <c r="B712" s="2" t="s">
+      <c r="C712" s="2" t="s">
         <v>1930</v>
-      </c>
-      <c r="C712" s="2" t="s">
-        <v>1931</v>
       </c>
     </row>
     <row r="713" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A713" s="2" t="s">
+        <v>1931</v>
+      </c>
+      <c r="B713" s="2" t="s">
+        <v>913</v>
+      </c>
+      <c r="C713" s="2" t="s">
         <v>1932</v>
-      </c>
-      <c r="B713" s="2" t="s">
-        <v>725</v>
-      </c>
-      <c r="C713" s="2" t="s">
-        <v>726</v>
       </c>
     </row>
     <row r="714" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14584,109 +14614,109 @@
         <v>1933</v>
       </c>
       <c r="B714" s="2" t="s">
-        <v>911</v>
+        <v>1934</v>
       </c>
       <c r="C714" s="2" t="s">
-        <v>912</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="715" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A715" s="2" t="s">
-        <v>1934</v>
+        <v>1936</v>
       </c>
       <c r="B715" s="2" t="s">
-        <v>914</v>
+        <v>1937</v>
       </c>
       <c r="C715" s="2" t="s">
-        <v>1935</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="716" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A716" s="2" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B716" s="2" t="s">
-        <v>917</v>
+        <v>1940</v>
       </c>
       <c r="C716" s="2" t="s">
-        <v>1937</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="717" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A717" s="2" t="s">
-        <v>1938</v>
+        <v>1942</v>
       </c>
       <c r="B717" s="2" t="s">
-        <v>920</v>
+        <v>737</v>
       </c>
       <c r="C717" s="2" t="s">
-        <v>1939</v>
+        <v>738</v>
       </c>
     </row>
     <row r="718" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A718" s="2" t="s">
-        <v>1940</v>
+        <v>1943</v>
       </c>
       <c r="B718" s="2" t="s">
-        <v>1941</v>
+        <v>923</v>
       </c>
       <c r="C718" s="2" t="s">
-        <v>1942</v>
+        <v>924</v>
       </c>
     </row>
     <row r="719" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A719" s="2" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="B719" s="2" t="s">
-        <v>1776</v>
+        <v>926</v>
       </c>
       <c r="C719" s="2" t="s">
-        <v>1777</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="720" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A720" s="2" t="s">
-        <v>1944</v>
+        <v>1946</v>
       </c>
       <c r="B720" s="2" t="s">
-        <v>1779</v>
+        <v>929</v>
       </c>
       <c r="C720" s="2" t="s">
-        <v>1780</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="721" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A721" s="2" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="B721" s="2" t="s">
-        <v>1946</v>
+        <v>932</v>
       </c>
       <c r="C721" s="2" t="s">
-        <v>1947</v>
+        <v>1949</v>
       </c>
     </row>
     <row r="722" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A722" s="2" t="s">
-        <v>1948</v>
+        <v>1950</v>
       </c>
       <c r="B722" s="2" t="s">
-        <v>1949</v>
+        <v>1951</v>
       </c>
       <c r="C722" s="2" t="s">
-        <v>1950</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="723" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A723" s="2" t="s">
-        <v>1951</v>
+        <v>1953</v>
       </c>
       <c r="B723" s="2" t="s">
-        <v>1952</v>
+        <v>1786</v>
       </c>
       <c r="C723" s="2" t="s">
-        <v>1953</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="724" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14694,43 +14724,43 @@
         <v>1954</v>
       </c>
       <c r="B724" s="2" t="s">
-        <v>1955</v>
+        <v>1789</v>
       </c>
       <c r="C724" s="2" t="s">
-        <v>1956</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="725" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A725" s="2" t="s">
+        <v>1955</v>
+      </c>
+      <c r="B725" s="2" t="s">
+        <v>1956</v>
+      </c>
+      <c r="C725" s="2" t="s">
         <v>1957</v>
-      </c>
-      <c r="B725" s="2" t="s">
-        <v>1958</v>
-      </c>
-      <c r="C725" s="2" t="s">
-        <v>1959</v>
       </c>
     </row>
     <row r="726" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A726" s="2" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B726" s="2" t="s">
+        <v>1959</v>
+      </c>
+      <c r="C726" s="2" t="s">
         <v>1960</v>
-      </c>
-      <c r="B726" s="2" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C726" s="2" t="s">
-        <v>1962</v>
       </c>
     </row>
     <row r="727" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A727" s="2" t="s">
+        <v>1961</v>
+      </c>
+      <c r="B727" s="2" t="s">
+        <v>1962</v>
+      </c>
+      <c r="C727" s="2" t="s">
         <v>1963</v>
-      </c>
-      <c r="B727" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="C727" s="2" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="728" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14760,62 +14790,62 @@
         <v>1970</v>
       </c>
       <c r="B730" s="2" t="s">
-        <v>445</v>
+        <v>1971</v>
       </c>
       <c r="C730" s="2" t="s">
-        <v>533</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="731" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A731" s="2" t="s">
-        <v>1971</v>
+        <v>1973</v>
       </c>
       <c r="B731" s="2" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="C731" s="2" t="s">
-        <v>1972</v>
+        <v>446</v>
       </c>
     </row>
     <row r="732" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A732" s="2" t="s">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="B732" s="2" t="s">
-        <v>484</v>
+        <v>1975</v>
       </c>
       <c r="C732" s="2" t="s">
-        <v>1974</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="733" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A733" s="2" t="s">
-        <v>1975</v>
+        <v>1977</v>
       </c>
       <c r="B733" s="2" t="s">
-        <v>487</v>
+        <v>1978</v>
       </c>
       <c r="C733" s="2" t="s">
-        <v>1976</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="734" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A734" s="2" t="s">
-        <v>1977</v>
+        <v>1980</v>
       </c>
       <c r="B734" s="2" t="s">
-        <v>1978</v>
+        <v>457</v>
       </c>
       <c r="C734" s="2" t="s">
-        <v>1979</v>
+        <v>545</v>
       </c>
     </row>
     <row r="735" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A735" s="2" t="s">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="B735" s="2" t="s">
-        <v>1981</v>
+        <v>463</v>
       </c>
       <c r="C735" s="2" t="s">
         <v>1982</v>
@@ -14826,21 +14856,21 @@
         <v>1983</v>
       </c>
       <c r="B736" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="C736" s="2" t="s">
         <v>1984</v>
-      </c>
-      <c r="C736" s="2" t="s">
-        <v>1985</v>
       </c>
     </row>
     <row r="737" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A737" s="2" t="s">
+        <v>1985</v>
+      </c>
+      <c r="B737" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="C737" s="2" t="s">
         <v>1986</v>
-      </c>
-      <c r="B737" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="C737" s="2" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="738" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14859,106 +14889,106 @@
         <v>1990</v>
       </c>
       <c r="B739" s="2" t="s">
-        <v>466</v>
+        <v>1991</v>
       </c>
       <c r="C739" s="2" t="s">
-        <v>467</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="740" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A740" s="2" t="s">
-        <v>1991</v>
+        <v>1993</v>
       </c>
       <c r="B740" s="2" t="s">
-        <v>472</v>
+        <v>1994</v>
       </c>
       <c r="C740" s="2" t="s">
-        <v>473</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="741" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A741" s="2" t="s">
-        <v>1992</v>
+        <v>1996</v>
       </c>
       <c r="B741" s="2" t="s">
-        <v>1993</v>
+        <v>466</v>
       </c>
       <c r="C741" s="2" t="s">
-        <v>1994</v>
+        <v>467</v>
       </c>
     </row>
     <row r="742" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A742" s="2" t="s">
-        <v>1995</v>
+        <v>1997</v>
       </c>
       <c r="B742" s="2" t="s">
-        <v>475</v>
+        <v>1998</v>
       </c>
       <c r="C742" s="2" t="s">
-        <v>209</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="743" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A743" s="2" t="s">
-        <v>1996</v>
+        <v>2000</v>
       </c>
       <c r="B743" s="2" t="s">
         <v>478</v>
       </c>
       <c r="C743" s="2" t="s">
-        <v>1997</v>
+        <v>479</v>
       </c>
     </row>
     <row r="744" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A744" s="2" t="s">
-        <v>1998</v>
+        <v>2001</v>
       </c>
       <c r="B744" s="2" t="s">
-        <v>520</v>
+        <v>484</v>
       </c>
       <c r="C744" s="2" t="s">
-        <v>1999</v>
+        <v>485</v>
       </c>
     </row>
     <row r="745" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A745" s="2" t="s">
-        <v>2000</v>
+        <v>2002</v>
       </c>
       <c r="B745" s="2" t="s">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="C745" s="2" t="s">
-        <v>2002</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="746" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A746" s="2" t="s">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="B746" s="2" t="s">
-        <v>502</v>
+        <v>487</v>
       </c>
       <c r="C746" s="2" t="s">
-        <v>503</v>
+        <v>212</v>
       </c>
     </row>
     <row r="747" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A747" s="2" t="s">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="B747" s="2" t="s">
-        <v>2005</v>
+        <v>490</v>
       </c>
       <c r="C747" s="2" t="s">
-        <v>2006</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="748" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A748" s="2" t="s">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="B748" s="2" t="s">
-        <v>2008</v>
+        <v>532</v>
       </c>
       <c r="C748" s="2" t="s">
         <v>2009</v>
@@ -14972,15 +15002,15 @@
         <v>2011</v>
       </c>
       <c r="C749" s="2" t="s">
-        <v>512</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="750" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A750" s="2" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="B750" s="2" t="s">
-        <v>2013</v>
+        <v>514</v>
       </c>
       <c r="C750" s="2" t="s">
         <v>515</v>
@@ -15016,227 +15046,227 @@
         <v>2021</v>
       </c>
       <c r="C753" s="2" t="s">
-        <v>2022</v>
+        <v>524</v>
       </c>
     </row>
     <row r="754" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A754" s="2" t="s">
+        <v>2022</v>
+      </c>
+      <c r="B754" s="2" t="s">
         <v>2023</v>
       </c>
-      <c r="B754" s="2" t="s">
-        <v>2024</v>
-      </c>
       <c r="C754" s="2" t="s">
-        <v>2025</v>
+        <v>527</v>
       </c>
     </row>
     <row r="755" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A755" s="2" t="s">
+        <v>2024</v>
+      </c>
+      <c r="B755" s="2" t="s">
+        <v>2025</v>
+      </c>
+      <c r="C755" s="2" t="s">
         <v>2026</v>
-      </c>
-      <c r="B755" s="2" t="s">
-        <v>2027</v>
-      </c>
-      <c r="C755" s="2" t="s">
-        <v>2028</v>
       </c>
     </row>
     <row r="756" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A756" s="2" t="s">
+        <v>2027</v>
+      </c>
+      <c r="B756" s="2" t="s">
+        <v>2028</v>
+      </c>
+      <c r="C756" s="2" t="s">
         <v>2029</v>
-      </c>
-      <c r="B756" s="2" t="s">
-        <v>2030</v>
-      </c>
-      <c r="C756" s="2" t="s">
-        <v>2031</v>
       </c>
     </row>
     <row r="757" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A757" s="2" t="s">
+        <v>2030</v>
+      </c>
+      <c r="B757" s="2" t="s">
+        <v>2031</v>
+      </c>
+      <c r="C757" s="2" t="s">
         <v>2032</v>
-      </c>
-      <c r="B757" s="2" t="s">
-        <v>2033</v>
-      </c>
-      <c r="C757" s="2" t="s">
-        <v>1696</v>
       </c>
     </row>
     <row r="758" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A758" s="2" t="s">
+        <v>2033</v>
+      </c>
+      <c r="B758" s="2" t="s">
         <v>2034</v>
       </c>
-      <c r="B758" s="2" t="s">
+      <c r="C758" s="2" t="s">
         <v>2035</v>
-      </c>
-      <c r="C758" s="2" t="s">
-        <v>2036</v>
       </c>
     </row>
     <row r="759" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A759" s="2" t="s">
+        <v>2036</v>
+      </c>
+      <c r="B759" s="2" t="s">
         <v>2037</v>
       </c>
-      <c r="B759" s="2" t="s">
+      <c r="C759" s="2" t="s">
         <v>2038</v>
-      </c>
-      <c r="C759" s="2" t="s">
-        <v>2039</v>
       </c>
     </row>
     <row r="760" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A760" s="2" t="s">
+        <v>2039</v>
+      </c>
+      <c r="B760" s="2" t="s">
         <v>2040</v>
       </c>
-      <c r="B760" s="2" t="s">
+      <c r="C760" s="2" t="s">
         <v>2041</v>
-      </c>
-      <c r="C760" s="2" t="s">
-        <v>2042</v>
       </c>
     </row>
     <row r="761" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A761" s="2" t="s">
+        <v>2042</v>
+      </c>
+      <c r="B761" s="2" t="s">
         <v>2043</v>
       </c>
-      <c r="B761" s="2" t="s">
-        <v>2044</v>
-      </c>
       <c r="C761" s="2" t="s">
-        <v>217</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="762" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A762" s="2" t="s">
+        <v>2044</v>
+      </c>
+      <c r="B762" s="2" t="s">
         <v>2045</v>
       </c>
-      <c r="B762" s="2" t="s">
+      <c r="C762" s="2" t="s">
         <v>2046</v>
-      </c>
-      <c r="C762" s="2" t="s">
-        <v>2047</v>
       </c>
     </row>
     <row r="763" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A763" s="2" t="s">
+        <v>2047</v>
+      </c>
+      <c r="B763" s="2" t="s">
         <v>2048</v>
       </c>
-      <c r="B763" s="2" t="s">
+      <c r="C763" s="2" t="s">
         <v>2049</v>
-      </c>
-      <c r="C763" s="2" t="s">
-        <v>2050</v>
       </c>
     </row>
     <row r="764" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A764" s="2" t="s">
+        <v>2050</v>
+      </c>
+      <c r="B764" s="2" t="s">
         <v>2051</v>
       </c>
-      <c r="B764" s="2" t="s">
+      <c r="C764" s="2" t="s">
         <v>2052</v>
-      </c>
-      <c r="C764" s="2" t="s">
-        <v>2053</v>
       </c>
     </row>
     <row r="765" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A765" s="2" t="s">
+        <v>2053</v>
+      </c>
+      <c r="B765" s="2" t="s">
         <v>2054</v>
       </c>
-      <c r="B765" s="2" t="s">
-        <v>2055</v>
-      </c>
       <c r="C765" s="2" t="s">
-        <v>2056</v>
+        <v>220</v>
       </c>
     </row>
     <row r="766" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A766" s="2" t="s">
+        <v>2055</v>
+      </c>
+      <c r="B766" s="2" t="s">
+        <v>2056</v>
+      </c>
+      <c r="C766" s="2" t="s">
         <v>2057</v>
-      </c>
-      <c r="B766" s="2" t="s">
-        <v>2058</v>
-      </c>
-      <c r="C766" s="2" t="s">
-        <v>2059</v>
       </c>
     </row>
     <row r="767" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A767" s="2" t="s">
+        <v>2058</v>
+      </c>
+      <c r="B767" s="2" t="s">
+        <v>2059</v>
+      </c>
+      <c r="C767" s="2" t="s">
         <v>2060</v>
-      </c>
-      <c r="B767" s="2" t="s">
-        <v>2061</v>
-      </c>
-      <c r="C767" s="2" t="s">
-        <v>2062</v>
       </c>
     </row>
     <row r="768" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A768" s="2" t="s">
+        <v>2061</v>
+      </c>
+      <c r="B768" s="2" t="s">
+        <v>2062</v>
+      </c>
+      <c r="C768" s="2" t="s">
         <v>2063</v>
-      </c>
-      <c r="B768" s="2" t="s">
-        <v>2064</v>
-      </c>
-      <c r="C768" s="2" t="s">
-        <v>2065</v>
       </c>
     </row>
     <row r="769" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A769" s="2" t="s">
+        <v>2064</v>
+      </c>
+      <c r="B769" s="2" t="s">
+        <v>2065</v>
+      </c>
+      <c r="C769" s="2" t="s">
         <v>2066</v>
-      </c>
-      <c r="B769" s="2" t="s">
-        <v>2067</v>
-      </c>
-      <c r="C769" s="2" t="s">
-        <v>2068</v>
       </c>
     </row>
     <row r="770" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A770" s="2" t="s">
+        <v>2067</v>
+      </c>
+      <c r="B770" s="2" t="s">
+        <v>2068</v>
+      </c>
+      <c r="C770" s="2" t="s">
         <v>2069</v>
-      </c>
-      <c r="B770" s="2" t="s">
-        <v>2070</v>
-      </c>
-      <c r="C770" s="2" t="s">
-        <v>2071</v>
       </c>
     </row>
     <row r="771" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A771" s="2" t="s">
+        <v>2070</v>
+      </c>
+      <c r="B771" s="2" t="s">
+        <v>2071</v>
+      </c>
+      <c r="C771" s="2" t="s">
         <v>2072</v>
-      </c>
-      <c r="B771" s="2" t="s">
-        <v>2073</v>
-      </c>
-      <c r="C771" s="2" t="s">
-        <v>2074</v>
       </c>
     </row>
     <row r="772" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A772" s="2" t="s">
+        <v>2073</v>
+      </c>
+      <c r="B772" s="2" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C772" s="2" t="s">
         <v>2075</v>
-      </c>
-      <c r="B772" s="2" t="s">
-        <v>2076</v>
-      </c>
-      <c r="C772" s="2" t="s">
-        <v>2077</v>
       </c>
     </row>
     <row r="773" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A773" s="2" t="s">
+        <v>2076</v>
+      </c>
+      <c r="B773" s="2" t="s">
+        <v>2077</v>
+      </c>
+      <c r="C773" s="2" t="s">
         <v>2078</v>
-      </c>
-      <c r="B773" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="C773" s="2" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="774" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15244,43 +15274,43 @@
         <v>2079</v>
       </c>
       <c r="B774" s="2" t="s">
-        <v>610</v>
+        <v>2080</v>
       </c>
       <c r="C774" s="2" t="s">
-        <v>611</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="775" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A775" s="2" t="s">
-        <v>2080</v>
+        <v>2082</v>
       </c>
       <c r="B775" s="2" t="s">
-        <v>2081</v>
+        <v>2083</v>
       </c>
       <c r="C775" s="2" t="s">
-        <v>2082</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="776" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A776" s="2" t="s">
-        <v>2083</v>
+        <v>2085</v>
       </c>
       <c r="B776" s="2" t="s">
-        <v>2084</v>
+        <v>2086</v>
       </c>
       <c r="C776" s="2" t="s">
-        <v>2085</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="777" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A777" s="2" t="s">
-        <v>2086</v>
+        <v>2088</v>
       </c>
       <c r="B777" s="2" t="s">
-        <v>2087</v>
+        <v>619</v>
       </c>
       <c r="C777" s="2" t="s">
-        <v>2088</v>
+        <v>620</v>
       </c>
     </row>
     <row r="778" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15288,54 +15318,54 @@
         <v>2089</v>
       </c>
       <c r="B778" s="2" t="s">
-        <v>2090</v>
+        <v>622</v>
       </c>
       <c r="C778" s="2" t="s">
-        <v>2091</v>
+        <v>623</v>
       </c>
     </row>
     <row r="779" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A779" s="2" t="s">
+        <v>2090</v>
+      </c>
+      <c r="B779" s="2" t="s">
+        <v>2091</v>
+      </c>
+      <c r="C779" s="2" t="s">
         <v>2092</v>
-      </c>
-      <c r="B779" s="2" t="s">
-        <v>2093</v>
-      </c>
-      <c r="C779" s="2" t="s">
-        <v>2094</v>
       </c>
     </row>
     <row r="780" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A780" s="2" t="s">
+        <v>2093</v>
+      </c>
+      <c r="B780" s="2" t="s">
+        <v>2094</v>
+      </c>
+      <c r="C780" s="2" t="s">
         <v>2095</v>
-      </c>
-      <c r="B780" s="2" t="s">
-        <v>2096</v>
-      </c>
-      <c r="C780" s="2" t="s">
-        <v>2097</v>
       </c>
     </row>
     <row r="781" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A781" s="2" t="s">
+        <v>2096</v>
+      </c>
+      <c r="B781" s="2" t="s">
+        <v>2097</v>
+      </c>
+      <c r="C781" s="2" t="s">
         <v>2098</v>
-      </c>
-      <c r="B781" s="2" t="s">
-        <v>2099</v>
-      </c>
-      <c r="C781" s="2" t="s">
-        <v>2100</v>
       </c>
     </row>
     <row r="782" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A782" s="2" t="s">
+        <v>2099</v>
+      </c>
+      <c r="B782" s="2" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C782" s="2" t="s">
         <v>2101</v>
-      </c>
-      <c r="B782" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C782" s="2" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="783" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15369,6 +15399,50 @@
       </c>
       <c r="C785" s="2" t="s">
         <v>2110</v>
+      </c>
+    </row>
+    <row r="786" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A786" s="2" t="s">
+        <v>2111</v>
+      </c>
+      <c r="B786" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C786" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="787" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A787" s="2" t="s">
+        <v>2112</v>
+      </c>
+      <c r="B787" s="2" t="s">
+        <v>2113</v>
+      </c>
+      <c r="C787" s="2" t="s">
+        <v>2114</v>
+      </c>
+    </row>
+    <row r="788" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A788" s="2" t="s">
+        <v>2115</v>
+      </c>
+      <c r="B788" s="2" t="s">
+        <v>2116</v>
+      </c>
+      <c r="C788" s="2" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="789" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A789" s="2" t="s">
+        <v>2118</v>
+      </c>
+      <c r="B789" s="2" t="s">
+        <v>2119</v>
+      </c>
+      <c r="C789" s="2" t="s">
+        <v>2120</v>
       </c>
     </row>
   </sheetData>

--- a/apps/workspace-web/i18n.xlsx
+++ b/apps/workspace-web/i18n.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2367" uniqueCount="2121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2364" uniqueCount="2118">
   <si>
     <t>key</t>
   </si>
@@ -3808,15 +3808,6 @@
     <t>Order status</t>
   </si>
   <si>
-    <t>orders.orderStatusPlaceholder</t>
-  </si>
-  <si>
-    <t>請選擇狀態</t>
-  </si>
-  <si>
-    <t>Select a status</t>
-  </si>
-  <si>
     <t>orders.colOrderNumber</t>
   </si>
   <si>
@@ -5257,19 +5248,21 @@
     <t>legalDocs.highlightsPlaceholder</t>
   </si>
   <si>
-    <t>每行一則，格式「標題|描述」，例如：作品永遠是你的|上架不轉移著作權，你只授權平台展示與銷售你的作品。</t>
-  </si>
-  <si>
-    <t>One per line as "Title|Description", e.g. Your work stays yours|Listing never transfers copyright.</t>
+    <t xml:space="preserve">每行一則，以第一個「|」分隔標題與描述，例如：
+作品永遠是你的|上架不會轉移著作權，創作者僅授權平台展示與銷售作品。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One per line, title and description split by the first "|", e.g.:
+Your work stays yours|Listing never transfers copyright — creators only license us to display and sell their work.</t>
   </si>
   <si>
     <t>legalDocs.highlightsHint</t>
   </si>
   <si>
-    <t>選填；每行一則、以第一個「|」分隔標題與描述，最多 6 則。顯示於前台條款頁頂部的 30 秒摘要卡，留空則前台改用預設文案</t>
-  </si>
-  <si>
-    <t>Optional; one per line, split by the first "|", up to 6. Shown as the 30-second summary cards atop the public legal page; leave empty to fall back to the default copy</t>
+    <t>選填，最多 6 則；顯示於前台條款頁頂部的 30 秒摘要卡，留空則前台改用預設文案。</t>
+  </si>
+  <si>
+    <t>Optional, up to 6 items; shown as the 30-second summary cards atop the public legal page. Leave empty to fall back to the default copy.</t>
   </si>
   <si>
     <t>legalDocs.valHighlightsFormat</t>
@@ -6759,7 +6752,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C789"/>
+  <dimension ref="A1:C788"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -11699,21 +11692,21 @@
         <v>1277</v>
       </c>
       <c r="B449" s="2" t="s">
-        <v>1278</v>
+        <v>993</v>
       </c>
       <c r="C449" s="2" t="s">
-        <v>1279</v>
+        <v>994</v>
       </c>
     </row>
     <row r="450" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A450" s="2" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B450" s="2" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C450" s="2" t="s">
         <v>1280</v>
-      </c>
-      <c r="B450" s="2" t="s">
-        <v>993</v>
-      </c>
-      <c r="C450" s="2" t="s">
-        <v>994</v>
       </c>
     </row>
     <row r="451" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11735,29 +11728,29 @@
         <v>1285</v>
       </c>
       <c r="C452" s="2" t="s">
-        <v>1286</v>
+        <v>186</v>
       </c>
     </row>
     <row r="453" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A453" s="2" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>1288</v>
+        <v>188</v>
       </c>
       <c r="C453" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="454" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A454" s="2" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B454" s="2" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C454" s="2" t="s">
         <v>1289</v>
-      </c>
-      <c r="B454" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="C454" s="2" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="455" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11765,21 +11758,21 @@
         <v>1290</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>1291</v>
+        <v>194</v>
       </c>
       <c r="C455" s="2" t="s">
-        <v>1292</v>
+        <v>195</v>
       </c>
     </row>
     <row r="456" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A456" s="2" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B456" s="2" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C456" s="2" t="s">
         <v>1293</v>
-      </c>
-      <c r="B456" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="C456" s="2" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="457" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11787,21 +11780,21 @@
         <v>1294</v>
       </c>
       <c r="B457" s="2" t="s">
-        <v>1295</v>
+        <v>294</v>
       </c>
       <c r="C457" s="2" t="s">
-        <v>1296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="458" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A458" s="2" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B458" s="2" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C458" s="2" t="s">
         <v>1297</v>
-      </c>
-      <c r="B458" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="C458" s="2" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="459" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11809,43 +11802,43 @@
         <v>1298</v>
       </c>
       <c r="B459" s="2" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C459" s="2" t="s">
         <v>1299</v>
-      </c>
-      <c r="C459" s="2" t="s">
-        <v>1300</v>
       </c>
     </row>
     <row r="460" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A460" s="2" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="B460" s="2" t="s">
-        <v>1106</v>
+        <v>315</v>
       </c>
       <c r="C460" s="2" t="s">
-        <v>1302</v>
+        <v>316</v>
       </c>
     </row>
     <row r="461" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A461" s="2" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="B461" s="2" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="C461" s="2" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
     </row>
     <row r="462" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A462" s="2" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B462" s="2" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C462" s="2" t="s">
         <v>1304</v>
-      </c>
-      <c r="B462" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="C462" s="2" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="463" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11864,21 +11857,21 @@
         <v>1308</v>
       </c>
       <c r="B464" s="2" t="s">
-        <v>1309</v>
+        <v>325</v>
       </c>
       <c r="C464" s="2" t="s">
-        <v>1310</v>
+        <v>326</v>
       </c>
     </row>
     <row r="465" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A465" s="2" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B465" s="2" t="s">
+        <v>1310</v>
+      </c>
+      <c r="C465" s="2" t="s">
         <v>1311</v>
-      </c>
-      <c r="B465" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="C465" s="2" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="466" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11886,21 +11879,21 @@
         <v>1312</v>
       </c>
       <c r="B466" s="2" t="s">
-        <v>1313</v>
+        <v>331</v>
       </c>
       <c r="C466" s="2" t="s">
-        <v>1314</v>
+        <v>332</v>
       </c>
     </row>
     <row r="467" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A467" s="2" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B467" s="2" t="s">
+        <v>1314</v>
+      </c>
+      <c r="C467" s="2" t="s">
         <v>1315</v>
-      </c>
-      <c r="B467" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="C467" s="2" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="468" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11911,26 +11904,26 @@
         <v>1317</v>
       </c>
       <c r="C468" s="2" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="469" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A469" s="2" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B469" s="2" t="s">
         <v>1319</v>
       </c>
-      <c r="B469" s="2" t="s">
-        <v>1320</v>
-      </c>
       <c r="C469" s="2" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="470" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A470" s="2" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B470" s="2" t="s">
         <v>1321</v>
-      </c>
-      <c r="B470" s="2" t="s">
-        <v>1322</v>
       </c>
       <c r="C470" s="2" t="s">
         <v>1322</v>
@@ -11941,21 +11934,21 @@
         <v>1323</v>
       </c>
       <c r="B471" s="2" t="s">
-        <v>1324</v>
+        <v>1321</v>
       </c>
       <c r="C471" s="2" t="s">
-        <v>1325</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="472" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A472" s="2" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B472" s="2" t="s">
+        <v>1325</v>
+      </c>
+      <c r="C472" s="2" t="s">
         <v>1326</v>
-      </c>
-      <c r="B472" s="2" t="s">
-        <v>1324</v>
-      </c>
-      <c r="C472" s="2" t="s">
-        <v>1325</v>
       </c>
     </row>
     <row r="473" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12098,18 +12091,18 @@
         <v>1364</v>
       </c>
       <c r="C485" s="2" t="s">
-        <v>1365</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="486" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A486" s="2" t="s">
+        <v>1365</v>
+      </c>
+      <c r="B486" s="2" t="s">
         <v>1366</v>
       </c>
-      <c r="B486" s="2" t="s">
+      <c r="C486" s="2" t="s">
         <v>1367</v>
-      </c>
-      <c r="C486" s="2" t="s">
-        <v>1344</v>
       </c>
     </row>
     <row r="487" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12131,18 +12124,18 @@
         <v>1372</v>
       </c>
       <c r="C488" s="2" t="s">
-        <v>1373</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="489" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A489" s="2" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B489" s="2" t="s">
         <v>1374</v>
       </c>
-      <c r="B489" s="2" t="s">
+      <c r="C489" s="2" t="s">
         <v>1375</v>
-      </c>
-      <c r="C489" s="2" t="s">
-        <v>1350</v>
       </c>
     </row>
     <row r="490" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12172,21 +12165,21 @@
         <v>1382</v>
       </c>
       <c r="B492" s="2" t="s">
-        <v>1383</v>
+        <v>1234</v>
       </c>
       <c r="C492" s="2" t="s">
-        <v>1384</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="493" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A493" s="2" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B493" s="2" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C493" s="2" t="s">
         <v>1385</v>
-      </c>
-      <c r="B493" s="2" t="s">
-        <v>1234</v>
-      </c>
-      <c r="C493" s="2" t="s">
-        <v>1234</v>
       </c>
     </row>
     <row r="494" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12271,21 +12264,21 @@
         <v>1407</v>
       </c>
       <c r="B501" s="2" t="s">
-        <v>1408</v>
+        <v>1269</v>
       </c>
       <c r="C501" s="2" t="s">
-        <v>1409</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="502" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A502" s="2" t="s">
+        <v>1408</v>
+      </c>
+      <c r="B502" s="2" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C502" s="2" t="s">
         <v>1410</v>
-      </c>
-      <c r="B502" s="2" t="s">
-        <v>1272</v>
-      </c>
-      <c r="C502" s="2" t="s">
-        <v>1273</v>
       </c>
     </row>
     <row r="503" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12351,51 +12344,51 @@
         <v>1427</v>
       </c>
       <c r="C508" s="2" t="s">
-        <v>1428</v>
+        <v>220</v>
       </c>
     </row>
     <row r="509" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A509" s="2" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="B509" s="2" t="s">
-        <v>1430</v>
+        <v>188</v>
       </c>
       <c r="C509" s="2" t="s">
-        <v>220</v>
+        <v>189</v>
       </c>
     </row>
     <row r="510" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A510" s="2" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="B510" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C510" s="2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="511" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A511" s="2" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>191</v>
+        <v>640</v>
       </c>
       <c r="C511" s="2" t="s">
-        <v>192</v>
+        <v>641</v>
       </c>
     </row>
     <row r="512" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A512" s="2" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B512" s="2" t="s">
+        <v>1432</v>
+      </c>
+      <c r="C512" s="2" t="s">
         <v>1433</v>
-      </c>
-      <c r="B512" s="2" t="s">
-        <v>640</v>
-      </c>
-      <c r="C512" s="2" t="s">
-        <v>641</v>
       </c>
     </row>
     <row r="513" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12601,54 +12594,54 @@
         <v>1488</v>
       </c>
       <c r="B531" s="2" t="s">
-        <v>1489</v>
+        <v>43</v>
       </c>
       <c r="C531" s="2" t="s">
-        <v>1490</v>
+        <v>44</v>
       </c>
     </row>
     <row r="532" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A532" s="2" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="B532" s="2" t="s">
-        <v>43</v>
+        <v>1490</v>
       </c>
       <c r="C532" s="2" t="s">
-        <v>44</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="533" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A533" s="2" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="B533" s="2" t="s">
-        <v>1493</v>
+        <v>1432</v>
       </c>
       <c r="C533" s="2" t="s">
-        <v>1116</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="534" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A534" s="2" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
       <c r="B534" s="2" t="s">
-        <v>1435</v>
+        <v>1493</v>
       </c>
       <c r="C534" s="2" t="s">
-        <v>1436</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="535" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A535" s="2" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B535" s="2" t="s">
         <v>1495</v>
       </c>
-      <c r="B535" s="2" t="s">
+      <c r="C535" s="2" t="s">
         <v>1496</v>
-      </c>
-      <c r="C535" s="2" t="s">
-        <v>1225</v>
       </c>
     </row>
     <row r="536" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12656,32 +12649,32 @@
         <v>1497</v>
       </c>
       <c r="B536" s="2" t="s">
-        <v>1498</v>
+        <v>1435</v>
       </c>
       <c r="C536" s="2" t="s">
-        <v>1499</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="537" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A537" s="2" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
       <c r="B537" s="2" t="s">
-        <v>1438</v>
+        <v>197</v>
       </c>
       <c r="C537" s="2" t="s">
-        <v>1439</v>
+        <v>197</v>
       </c>
     </row>
     <row r="538" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A538" s="2" t="s">
+        <v>1499</v>
+      </c>
+      <c r="B538" s="2" t="s">
+        <v>1500</v>
+      </c>
+      <c r="C538" s="2" t="s">
         <v>1501</v>
-      </c>
-      <c r="B538" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="C538" s="2" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="539" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12733,54 +12726,54 @@
         <v>1514</v>
       </c>
       <c r="B543" s="2" t="s">
-        <v>1515</v>
+        <v>1266</v>
       </c>
       <c r="C543" s="2" t="s">
-        <v>1516</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="544" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A544" s="2" t="s">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="B544" s="2" t="s">
-        <v>1269</v>
+        <v>4</v>
       </c>
       <c r="C544" s="2" t="s">
-        <v>1270</v>
+        <v>5</v>
       </c>
     </row>
     <row r="545" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A545" s="2" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="B545" s="2" t="s">
-        <v>4</v>
+        <v>1257</v>
       </c>
       <c r="C545" s="2" t="s">
-        <v>5</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="546" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A546" s="2" t="s">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="B546" s="2" t="s">
-        <v>1257</v>
+        <v>1269</v>
       </c>
       <c r="C546" s="2" t="s">
-        <v>1258</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="547" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A547" s="2" t="s">
+        <v>1518</v>
+      </c>
+      <c r="B547" s="2" t="s">
+        <v>1519</v>
+      </c>
+      <c r="C547" s="2" t="s">
         <v>1520</v>
-      </c>
-      <c r="B547" s="2" t="s">
-        <v>1272</v>
-      </c>
-      <c r="C547" s="2" t="s">
-        <v>1273</v>
       </c>
     </row>
     <row r="548" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12799,21 +12792,21 @@
         <v>1524</v>
       </c>
       <c r="B549" s="2" t="s">
-        <v>1525</v>
+        <v>1272</v>
       </c>
       <c r="C549" s="2" t="s">
-        <v>1526</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="550" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A550" s="2" t="s">
+        <v>1525</v>
+      </c>
+      <c r="B550" s="2" t="s">
+        <v>1526</v>
+      </c>
+      <c r="C550" s="2" t="s">
         <v>1527</v>
-      </c>
-      <c r="B550" s="2" t="s">
-        <v>1275</v>
-      </c>
-      <c r="C550" s="2" t="s">
-        <v>1276</v>
       </c>
     </row>
     <row r="551" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12821,29 +12814,29 @@
         <v>1528</v>
       </c>
       <c r="B551" s="2" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C551" s="2" t="s">
         <v>1529</v>
-      </c>
-      <c r="C551" s="2" t="s">
-        <v>1530</v>
       </c>
     </row>
     <row r="552" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A552" s="2" t="s">
+        <v>1530</v>
+      </c>
+      <c r="B552" s="2" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C552" s="2" t="s">
         <v>1531</v>
-      </c>
-      <c r="B552" s="2" t="s">
-        <v>1278</v>
-      </c>
-      <c r="C552" s="2" t="s">
-        <v>1532</v>
       </c>
     </row>
     <row r="553" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A553" s="2" t="s">
+        <v>1532</v>
+      </c>
+      <c r="B553" s="2" t="s">
         <v>1533</v>
-      </c>
-      <c r="B553" s="2" t="s">
-        <v>1224</v>
       </c>
       <c r="C553" s="2" t="s">
         <v>1534</v>
@@ -12942,43 +12935,43 @@
         <v>1559</v>
       </c>
       <c r="B562" s="2" t="s">
-        <v>1560</v>
+        <v>1266</v>
       </c>
       <c r="C562" s="2" t="s">
-        <v>1561</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="563" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A563" s="2" t="s">
-        <v>1562</v>
+        <v>1560</v>
       </c>
       <c r="B563" s="2" t="s">
-        <v>1269</v>
+        <v>4</v>
       </c>
       <c r="C563" s="2" t="s">
-        <v>1270</v>
+        <v>5</v>
       </c>
     </row>
     <row r="564" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A564" s="2" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="B564" s="2" t="s">
-        <v>4</v>
+        <v>1272</v>
       </c>
       <c r="C564" s="2" t="s">
-        <v>5</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="565" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A565" s="2" t="s">
+        <v>1562</v>
+      </c>
+      <c r="B565" s="2" t="s">
+        <v>1563</v>
+      </c>
+      <c r="C565" s="2" t="s">
         <v>1564</v>
-      </c>
-      <c r="B565" s="2" t="s">
-        <v>1275</v>
-      </c>
-      <c r="C565" s="2" t="s">
-        <v>1276</v>
       </c>
     </row>
     <row r="566" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13008,21 +13001,21 @@
         <v>1571</v>
       </c>
       <c r="B568" s="2" t="s">
-        <v>1572</v>
+        <v>1542</v>
       </c>
       <c r="C568" s="2" t="s">
-        <v>1573</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="569" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A569" s="2" t="s">
+        <v>1572</v>
+      </c>
+      <c r="B569" s="2" t="s">
+        <v>1573</v>
+      </c>
+      <c r="C569" s="2" t="s">
         <v>1574</v>
-      </c>
-      <c r="B569" s="2" t="s">
-        <v>1545</v>
-      </c>
-      <c r="C569" s="2" t="s">
-        <v>1546</v>
       </c>
     </row>
     <row r="570" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13041,21 +13034,21 @@
         <v>1578</v>
       </c>
       <c r="B571" s="2" t="s">
-        <v>1579</v>
+        <v>1396</v>
       </c>
       <c r="C571" s="2" t="s">
-        <v>1580</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="572" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A572" s="2" t="s">
+        <v>1579</v>
+      </c>
+      <c r="B572" s="2" t="s">
+        <v>1580</v>
+      </c>
+      <c r="C572" s="2" t="s">
         <v>1581</v>
-      </c>
-      <c r="B572" s="2" t="s">
-        <v>1399</v>
-      </c>
-      <c r="C572" s="2" t="s">
-        <v>1400</v>
       </c>
     </row>
     <row r="573" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13132,18 +13125,18 @@
         <v>1601</v>
       </c>
       <c r="C579" s="2" t="s">
-        <v>1602</v>
+        <v>545</v>
       </c>
     </row>
     <row r="580" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A580" s="2" t="s">
+        <v>1602</v>
+      </c>
+      <c r="B580" s="2" t="s">
         <v>1603</v>
       </c>
-      <c r="B580" s="2" t="s">
+      <c r="C580" s="2" t="s">
         <v>1604</v>
-      </c>
-      <c r="C580" s="2" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="581" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13228,21 +13221,21 @@
         <v>1626</v>
       </c>
       <c r="B588" s="2" t="s">
-        <v>1627</v>
+        <v>544</v>
       </c>
       <c r="C588" s="2" t="s">
-        <v>1628</v>
+        <v>545</v>
       </c>
     </row>
     <row r="589" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A589" s="2" t="s">
+        <v>1627</v>
+      </c>
+      <c r="B589" s="2" t="s">
+        <v>1628</v>
+      </c>
+      <c r="C589" s="2" t="s">
         <v>1629</v>
-      </c>
-      <c r="B589" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="C589" s="2" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="590" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13261,21 +13254,21 @@
         <v>1633</v>
       </c>
       <c r="B591" s="2" t="s">
-        <v>1634</v>
+        <v>294</v>
       </c>
       <c r="C591" s="2" t="s">
-        <v>1635</v>
+        <v>295</v>
       </c>
     </row>
     <row r="592" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A592" s="2" t="s">
+        <v>1634</v>
+      </c>
+      <c r="B592" s="2" t="s">
+        <v>1635</v>
+      </c>
+      <c r="C592" s="2" t="s">
         <v>1636</v>
-      </c>
-      <c r="B592" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="C592" s="2" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="593" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13404,32 +13397,32 @@
         <v>1670</v>
       </c>
       <c r="B604" s="2" t="s">
-        <v>1671</v>
+        <v>288</v>
       </c>
       <c r="C604" s="2" t="s">
-        <v>1672</v>
+        <v>289</v>
       </c>
     </row>
     <row r="605" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A605" s="2" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="B605" s="2" t="s">
-        <v>288</v>
+        <v>1672</v>
       </c>
       <c r="C605" s="2" t="s">
-        <v>289</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="606" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A606" s="2" t="s">
+        <v>1673</v>
+      </c>
+      <c r="B606" s="2" t="s">
         <v>1674</v>
       </c>
-      <c r="B606" s="2" t="s">
+      <c r="C606" s="2" t="s">
         <v>1675</v>
-      </c>
-      <c r="C606" s="2" t="s">
-        <v>1116</v>
       </c>
     </row>
     <row r="607" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13437,21 +13430,21 @@
         <v>1676</v>
       </c>
       <c r="B607" s="2" t="s">
-        <v>1677</v>
+        <v>1495</v>
       </c>
       <c r="C607" s="2" t="s">
-        <v>1678</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="608" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A608" s="2" t="s">
+        <v>1677</v>
+      </c>
+      <c r="B608" s="2" t="s">
+        <v>1678</v>
+      </c>
+      <c r="C608" s="2" t="s">
         <v>1679</v>
-      </c>
-      <c r="B608" s="2" t="s">
-        <v>1498</v>
-      </c>
-      <c r="C608" s="2" t="s">
-        <v>1499</v>
       </c>
     </row>
     <row r="609" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13503,40 +13496,40 @@
         <v>1692</v>
       </c>
       <c r="B613" s="2" t="s">
-        <v>1693</v>
+        <v>188</v>
       </c>
       <c r="C613" s="2" t="s">
-        <v>1694</v>
+        <v>189</v>
       </c>
     </row>
     <row r="614" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A614" s="2" t="s">
-        <v>1695</v>
+        <v>1693</v>
       </c>
       <c r="B614" s="2" t="s">
-        <v>188</v>
+        <v>1113</v>
       </c>
       <c r="C614" s="2" t="s">
-        <v>189</v>
+        <v>654</v>
       </c>
     </row>
     <row r="615" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A615" s="2" t="s">
-        <v>1696</v>
+        <v>1694</v>
       </c>
       <c r="B615" s="2" t="s">
-        <v>1113</v>
+        <v>1122</v>
       </c>
       <c r="C615" s="2" t="s">
-        <v>654</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="616" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A616" s="2" t="s">
+        <v>1696</v>
+      </c>
+      <c r="B616" s="2" t="s">
         <v>1697</v>
-      </c>
-      <c r="B616" s="2" t="s">
-        <v>1122</v>
       </c>
       <c r="C616" s="2" t="s">
         <v>1698</v>
@@ -13547,21 +13540,21 @@
         <v>1699</v>
       </c>
       <c r="B617" s="2" t="s">
-        <v>1700</v>
+        <v>288</v>
       </c>
       <c r="C617" s="2" t="s">
-        <v>1701</v>
+        <v>289</v>
       </c>
     </row>
     <row r="618" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A618" s="2" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B618" s="2" t="s">
+        <v>1701</v>
+      </c>
+      <c r="C618" s="2" t="s">
         <v>1702</v>
-      </c>
-      <c r="B618" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="C618" s="2" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="619" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13602,21 +13595,21 @@
         <v>1712</v>
       </c>
       <c r="B622" s="2" t="s">
-        <v>1713</v>
+        <v>294</v>
       </c>
       <c r="C622" s="2" t="s">
-        <v>1714</v>
+        <v>295</v>
       </c>
     </row>
     <row r="623" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A623" s="2" t="s">
+        <v>1713</v>
+      </c>
+      <c r="B623" s="2" t="s">
+        <v>1714</v>
+      </c>
+      <c r="C623" s="2" t="s">
         <v>1715</v>
-      </c>
-      <c r="B623" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="C623" s="2" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="624" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13668,21 +13661,21 @@
         <v>1728</v>
       </c>
       <c r="B628" s="2" t="s">
-        <v>1729</v>
+        <v>544</v>
       </c>
       <c r="C628" s="2" t="s">
-        <v>1730</v>
+        <v>545</v>
       </c>
     </row>
     <row r="629" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A629" s="2" t="s">
+        <v>1729</v>
+      </c>
+      <c r="B629" s="2" t="s">
+        <v>1730</v>
+      </c>
+      <c r="C629" s="2" t="s">
         <v>1731</v>
-      </c>
-      <c r="B629" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="C629" s="2" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="630" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13778,21 +13771,21 @@
         <v>1756</v>
       </c>
       <c r="B638" s="2" t="s">
-        <v>1757</v>
+        <v>19</v>
       </c>
       <c r="C638" s="2" t="s">
-        <v>1758</v>
+        <v>20</v>
       </c>
     </row>
     <row r="639" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A639" s="2" t="s">
+        <v>1757</v>
+      </c>
+      <c r="B639" s="2" t="s">
+        <v>1758</v>
+      </c>
+      <c r="C639" s="2" t="s">
         <v>1759</v>
-      </c>
-      <c r="B639" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C639" s="2" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="640" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13844,21 +13837,21 @@
         <v>1772</v>
       </c>
       <c r="B644" s="2" t="s">
-        <v>1773</v>
+        <v>273</v>
       </c>
       <c r="C644" s="2" t="s">
-        <v>1774</v>
+        <v>274</v>
       </c>
     </row>
     <row r="645" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A645" s="2" t="s">
+        <v>1773</v>
+      </c>
+      <c r="B645" s="2" t="s">
+        <v>1774</v>
+      </c>
+      <c r="C645" s="2" t="s">
         <v>1775</v>
-      </c>
-      <c r="B645" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="C645" s="2" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="646" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13943,18 +13936,18 @@
         <v>1797</v>
       </c>
       <c r="B653" s="2" t="s">
+        <v>756</v>
+      </c>
+      <c r="C653" s="2" t="s">
         <v>1798</v>
-      </c>
-      <c r="C653" s="2" t="s">
-        <v>1799</v>
       </c>
     </row>
     <row r="654" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A654" s="2" t="s">
+        <v>1799</v>
+      </c>
+      <c r="B654" s="2" t="s">
         <v>1800</v>
-      </c>
-      <c r="B654" s="2" t="s">
-        <v>756</v>
       </c>
       <c r="C654" s="2" t="s">
         <v>1801</v>
@@ -14045,18 +14038,18 @@
         <v>1824</v>
       </c>
       <c r="C662" s="2" t="s">
-        <v>1825</v>
+        <v>467</v>
       </c>
     </row>
     <row r="663" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A663" s="2" t="s">
+        <v>1825</v>
+      </c>
+      <c r="B663" s="2" t="s">
         <v>1826</v>
       </c>
-      <c r="B663" s="2" t="s">
+      <c r="C663" s="2" t="s">
         <v>1827</v>
-      </c>
-      <c r="C663" s="2" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="664" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14075,32 +14068,32 @@
         <v>1831</v>
       </c>
       <c r="B665" s="2" t="s">
-        <v>1832</v>
+        <v>288</v>
       </c>
       <c r="C665" s="2" t="s">
-        <v>1833</v>
+        <v>289</v>
       </c>
     </row>
     <row r="666" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A666" s="2" t="s">
-        <v>1834</v>
+        <v>1832</v>
       </c>
       <c r="B666" s="2" t="s">
-        <v>288</v>
+        <v>1833</v>
       </c>
       <c r="C666" s="2" t="s">
-        <v>289</v>
+        <v>186</v>
       </c>
     </row>
     <row r="667" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A667" s="2" t="s">
+        <v>1834</v>
+      </c>
+      <c r="B667" s="2" t="s">
         <v>1835</v>
       </c>
-      <c r="B667" s="2" t="s">
+      <c r="C667" s="2" t="s">
         <v>1836</v>
-      </c>
-      <c r="C667" s="2" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="668" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14111,18 +14104,18 @@
         <v>1838</v>
       </c>
       <c r="C668" s="2" t="s">
-        <v>1839</v>
+        <v>467</v>
       </c>
     </row>
     <row r="669" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A669" s="2" t="s">
+        <v>1839</v>
+      </c>
+      <c r="B669" s="2" t="s">
         <v>1840</v>
       </c>
-      <c r="B669" s="2" t="s">
+      <c r="C669" s="2" t="s">
         <v>1841</v>
-      </c>
-      <c r="C669" s="2" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="670" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14130,54 +14123,54 @@
         <v>1842</v>
       </c>
       <c r="B670" s="2" t="s">
-        <v>1843</v>
+        <v>869</v>
       </c>
       <c r="C670" s="2" t="s">
-        <v>1844</v>
+        <v>870</v>
       </c>
     </row>
     <row r="671" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A671" s="2" t="s">
-        <v>1845</v>
+        <v>1843</v>
       </c>
       <c r="B671" s="2" t="s">
-        <v>869</v>
+        <v>4</v>
       </c>
       <c r="C671" s="2" t="s">
-        <v>870</v>
+        <v>5</v>
       </c>
     </row>
     <row r="672" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A672" s="2" t="s">
-        <v>1846</v>
+        <v>1844</v>
       </c>
       <c r="B672" s="2" t="s">
-        <v>4</v>
+        <v>294</v>
       </c>
       <c r="C672" s="2" t="s">
-        <v>5</v>
+        <v>295</v>
       </c>
     </row>
     <row r="673" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A673" s="2" t="s">
-        <v>1847</v>
+        <v>1845</v>
       </c>
       <c r="B673" s="2" t="s">
-        <v>294</v>
+        <v>1840</v>
       </c>
       <c r="C673" s="2" t="s">
-        <v>295</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="674" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A674" s="2" t="s">
+        <v>1846</v>
+      </c>
+      <c r="B674" s="2" t="s">
+        <v>1847</v>
+      </c>
+      <c r="C674" s="2" t="s">
         <v>1848</v>
-      </c>
-      <c r="B674" s="2" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C674" s="2" t="s">
-        <v>1844</v>
       </c>
     </row>
     <row r="675" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14262,43 +14255,43 @@
         <v>1870</v>
       </c>
       <c r="B682" s="2" t="s">
-        <v>1871</v>
+        <v>19</v>
       </c>
       <c r="C682" s="2" t="s">
-        <v>1872</v>
+        <v>20</v>
       </c>
     </row>
     <row r="683" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A683" s="2" t="s">
-        <v>1873</v>
+        <v>1871</v>
       </c>
       <c r="B683" s="2" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C683" s="2" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="684" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A684" s="2" t="s">
-        <v>1874</v>
+        <v>1872</v>
       </c>
       <c r="B684" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C684" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="685" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A685" s="2" t="s">
+        <v>1873</v>
+      </c>
+      <c r="B685" s="2" t="s">
+        <v>1874</v>
+      </c>
+      <c r="C685" s="2" t="s">
         <v>1875</v>
-      </c>
-      <c r="B685" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C685" s="2" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="686" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14339,15 +14332,15 @@
         <v>1885</v>
       </c>
       <c r="B689" s="2" t="s">
-        <v>1886</v>
+        <v>1783</v>
       </c>
       <c r="C689" s="2" t="s">
-        <v>1887</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="690" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A690" s="2" t="s">
-        <v>1888</v>
+        <v>1886</v>
       </c>
       <c r="B690" s="2" t="s">
         <v>1786</v>
@@ -14358,24 +14351,24 @@
     </row>
     <row r="691" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A691" s="2" t="s">
-        <v>1889</v>
+        <v>1887</v>
       </c>
       <c r="B691" s="2" t="s">
-        <v>1789</v>
+        <v>1888</v>
       </c>
       <c r="C691" s="2" t="s">
-        <v>1790</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="692" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A692" s="2" t="s">
+        <v>1889</v>
+      </c>
+      <c r="B692" s="2" t="s">
         <v>1890</v>
       </c>
-      <c r="B692" s="2" t="s">
+      <c r="C692" s="2" t="s">
         <v>1891</v>
-      </c>
-      <c r="C692" s="2" t="s">
-        <v>1279</v>
       </c>
     </row>
     <row r="693" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14383,43 +14376,43 @@
         <v>1892</v>
       </c>
       <c r="B693" s="2" t="s">
-        <v>1893</v>
+        <v>1125</v>
       </c>
       <c r="C693" s="2" t="s">
-        <v>1894</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="694" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A694" s="2" t="s">
-        <v>1895</v>
+        <v>1893</v>
       </c>
       <c r="B694" s="2" t="s">
-        <v>1125</v>
+        <v>1894</v>
       </c>
       <c r="C694" s="2" t="s">
-        <v>1126</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="695" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A695" s="2" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="B695" s="2" t="s">
-        <v>1897</v>
+        <v>756</v>
       </c>
       <c r="C695" s="2" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="696" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A696" s="2" t="s">
+        <v>1896</v>
+      </c>
+      <c r="B696" s="2" t="s">
+        <v>1897</v>
+      </c>
+      <c r="C696" s="2" t="s">
         <v>1898</v>
-      </c>
-      <c r="B696" s="2" t="s">
-        <v>756</v>
-      </c>
-      <c r="C696" s="2" t="s">
-        <v>1801</v>
       </c>
     </row>
     <row r="697" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14430,73 +14423,73 @@
         <v>1900</v>
       </c>
       <c r="C697" s="2" t="s">
-        <v>1901</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="698" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A698" s="2" t="s">
+        <v>1901</v>
+      </c>
+      <c r="B698" s="2" t="s">
+        <v>853</v>
+      </c>
+      <c r="C698" s="2" t="s">
         <v>1902</v>
-      </c>
-      <c r="B698" s="2" t="s">
-        <v>1903</v>
-      </c>
-      <c r="C698" s="2" t="s">
-        <v>1894</v>
       </c>
     </row>
     <row r="699" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A699" s="2" t="s">
+        <v>1903</v>
+      </c>
+      <c r="B699" s="2" t="s">
+        <v>865</v>
+      </c>
+      <c r="C699" s="2" t="s">
         <v>1904</v>
-      </c>
-      <c r="B699" s="2" t="s">
-        <v>853</v>
-      </c>
-      <c r="C699" s="2" t="s">
-        <v>1905</v>
       </c>
     </row>
     <row r="700" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A700" s="2" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
       <c r="B700" s="2" t="s">
-        <v>865</v>
+        <v>547</v>
       </c>
       <c r="C700" s="2" t="s">
-        <v>1907</v>
+        <v>467</v>
       </c>
     </row>
     <row r="701" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A701" s="2" t="s">
-        <v>1908</v>
+        <v>1906</v>
       </c>
       <c r="B701" s="2" t="s">
-        <v>547</v>
+        <v>869</v>
       </c>
       <c r="C701" s="2" t="s">
-        <v>467</v>
+        <v>870</v>
       </c>
     </row>
     <row r="702" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A702" s="2" t="s">
-        <v>1909</v>
+        <v>1907</v>
       </c>
       <c r="B702" s="2" t="s">
-        <v>869</v>
+        <v>294</v>
       </c>
       <c r="C702" s="2" t="s">
-        <v>870</v>
+        <v>295</v>
       </c>
     </row>
     <row r="703" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A703" s="2" t="s">
+        <v>1908</v>
+      </c>
+      <c r="B703" s="2" t="s">
+        <v>1909</v>
+      </c>
+      <c r="C703" s="2" t="s">
         <v>1910</v>
-      </c>
-      <c r="B703" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="C703" s="2" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="704" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14526,43 +14519,43 @@
         <v>1917</v>
       </c>
       <c r="B706" s="2" t="s">
-        <v>1918</v>
+        <v>897</v>
       </c>
       <c r="C706" s="2" t="s">
-        <v>1919</v>
+        <v>898</v>
       </c>
     </row>
     <row r="707" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A707" s="2" t="s">
-        <v>1920</v>
+        <v>1918</v>
       </c>
       <c r="B707" s="2" t="s">
-        <v>897</v>
+        <v>865</v>
       </c>
       <c r="C707" s="2" t="s">
-        <v>898</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="708" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A708" s="2" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="B708" s="2" t="s">
-        <v>865</v>
+        <v>901</v>
       </c>
       <c r="C708" s="2" t="s">
-        <v>1907</v>
+        <v>902</v>
       </c>
     </row>
     <row r="709" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A709" s="2" t="s">
+        <v>1920</v>
+      </c>
+      <c r="B709" s="2" t="s">
+        <v>1921</v>
+      </c>
+      <c r="C709" s="2" t="s">
         <v>1922</v>
-      </c>
-      <c r="B709" s="2" t="s">
-        <v>901</v>
-      </c>
-      <c r="C709" s="2" t="s">
-        <v>902</v>
       </c>
     </row>
     <row r="710" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14570,18 +14563,18 @@
         <v>1923</v>
       </c>
       <c r="B710" s="2" t="s">
+        <v>907</v>
+      </c>
+      <c r="C710" s="2" t="s">
         <v>1924</v>
-      </c>
-      <c r="C710" s="2" t="s">
-        <v>1925</v>
       </c>
     </row>
     <row r="711" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A711" s="2" t="s">
+        <v>1925</v>
+      </c>
+      <c r="B711" s="2" t="s">
         <v>1926</v>
-      </c>
-      <c r="B711" s="2" t="s">
-        <v>907</v>
       </c>
       <c r="C711" s="2" t="s">
         <v>1927</v>
@@ -14592,18 +14585,18 @@
         <v>1928</v>
       </c>
       <c r="B712" s="2" t="s">
+        <v>913</v>
+      </c>
+      <c r="C712" s="2" t="s">
         <v>1929</v>
-      </c>
-      <c r="C712" s="2" t="s">
-        <v>1930</v>
       </c>
     </row>
     <row r="713" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A713" s="2" t="s">
+        <v>1930</v>
+      </c>
+      <c r="B713" s="2" t="s">
         <v>1931</v>
-      </c>
-      <c r="B713" s="2" t="s">
-        <v>913</v>
       </c>
       <c r="C713" s="2" t="s">
         <v>1932</v>
@@ -14636,62 +14629,62 @@
         <v>1939</v>
       </c>
       <c r="B716" s="2" t="s">
-        <v>1940</v>
+        <v>737</v>
       </c>
       <c r="C716" s="2" t="s">
-        <v>1941</v>
+        <v>738</v>
       </c>
     </row>
     <row r="717" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A717" s="2" t="s">
-        <v>1942</v>
+        <v>1940</v>
       </c>
       <c r="B717" s="2" t="s">
-        <v>737</v>
+        <v>923</v>
       </c>
       <c r="C717" s="2" t="s">
-        <v>738</v>
+        <v>924</v>
       </c>
     </row>
     <row r="718" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A718" s="2" t="s">
-        <v>1943</v>
+        <v>1941</v>
       </c>
       <c r="B718" s="2" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="C718" s="2" t="s">
-        <v>924</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="719" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A719" s="2" t="s">
+        <v>1943</v>
+      </c>
+      <c r="B719" s="2" t="s">
+        <v>929</v>
+      </c>
+      <c r="C719" s="2" t="s">
         <v>1944</v>
-      </c>
-      <c r="B719" s="2" t="s">
-        <v>926</v>
-      </c>
-      <c r="C719" s="2" t="s">
-        <v>1945</v>
       </c>
     </row>
     <row r="720" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A720" s="2" t="s">
+        <v>1945</v>
+      </c>
+      <c r="B720" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="C720" s="2" t="s">
         <v>1946</v>
-      </c>
-      <c r="B720" s="2" t="s">
-        <v>929</v>
-      </c>
-      <c r="C720" s="2" t="s">
-        <v>1947</v>
       </c>
     </row>
     <row r="721" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A721" s="2" t="s">
+        <v>1947</v>
+      </c>
+      <c r="B721" s="2" t="s">
         <v>1948</v>
-      </c>
-      <c r="B721" s="2" t="s">
-        <v>932</v>
       </c>
       <c r="C721" s="2" t="s">
         <v>1949</v>
@@ -14702,15 +14695,15 @@
         <v>1950</v>
       </c>
       <c r="B722" s="2" t="s">
-        <v>1951</v>
+        <v>1783</v>
       </c>
       <c r="C722" s="2" t="s">
-        <v>1952</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="723" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A723" s="2" t="s">
-        <v>1953</v>
+        <v>1951</v>
       </c>
       <c r="B723" s="2" t="s">
         <v>1786</v>
@@ -14721,13 +14714,13 @@
     </row>
     <row r="724" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A724" s="2" t="s">
+        <v>1952</v>
+      </c>
+      <c r="B724" s="2" t="s">
+        <v>1953</v>
+      </c>
+      <c r="C724" s="2" t="s">
         <v>1954</v>
-      </c>
-      <c r="B724" s="2" t="s">
-        <v>1789</v>
-      </c>
-      <c r="C724" s="2" t="s">
-        <v>1790</v>
       </c>
     </row>
     <row r="725" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14790,21 +14783,21 @@
         <v>1970</v>
       </c>
       <c r="B730" s="2" t="s">
-        <v>1971</v>
+        <v>445</v>
       </c>
       <c r="C730" s="2" t="s">
-        <v>1972</v>
+        <v>446</v>
       </c>
     </row>
     <row r="731" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A731" s="2" t="s">
+        <v>1971</v>
+      </c>
+      <c r="B731" s="2" t="s">
+        <v>1972</v>
+      </c>
+      <c r="C731" s="2" t="s">
         <v>1973</v>
-      </c>
-      <c r="B731" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="C731" s="2" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="732" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14823,51 +14816,51 @@
         <v>1977</v>
       </c>
       <c r="B733" s="2" t="s">
-        <v>1978</v>
+        <v>457</v>
       </c>
       <c r="C733" s="2" t="s">
-        <v>1979</v>
+        <v>545</v>
       </c>
     </row>
     <row r="734" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A734" s="2" t="s">
-        <v>1980</v>
+        <v>1978</v>
       </c>
       <c r="B734" s="2" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="C734" s="2" t="s">
-        <v>545</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="735" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A735" s="2" t="s">
+        <v>1980</v>
+      </c>
+      <c r="B735" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="C735" s="2" t="s">
         <v>1981</v>
-      </c>
-      <c r="B735" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="C735" s="2" t="s">
-        <v>1982</v>
       </c>
     </row>
     <row r="736" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A736" s="2" t="s">
+        <v>1982</v>
+      </c>
+      <c r="B736" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="C736" s="2" t="s">
         <v>1983</v>
-      </c>
-      <c r="B736" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="C736" s="2" t="s">
-        <v>1984</v>
       </c>
     </row>
     <row r="737" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A737" s="2" t="s">
+        <v>1984</v>
+      </c>
+      <c r="B737" s="2" t="s">
         <v>1985</v>
-      </c>
-      <c r="B737" s="2" t="s">
-        <v>499</v>
       </c>
       <c r="C737" s="2" t="s">
         <v>1986</v>
@@ -14900,21 +14893,21 @@
         <v>1993</v>
       </c>
       <c r="B740" s="2" t="s">
-        <v>1994</v>
+        <v>466</v>
       </c>
       <c r="C740" s="2" t="s">
-        <v>1995</v>
+        <v>467</v>
       </c>
     </row>
     <row r="741" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A741" s="2" t="s">
+        <v>1994</v>
+      </c>
+      <c r="B741" s="2" t="s">
+        <v>1995</v>
+      </c>
+      <c r="C741" s="2" t="s">
         <v>1996</v>
-      </c>
-      <c r="B741" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="C741" s="2" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="742" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14922,32 +14915,32 @@
         <v>1997</v>
       </c>
       <c r="B742" s="2" t="s">
-        <v>1998</v>
+        <v>478</v>
       </c>
       <c r="C742" s="2" t="s">
-        <v>1999</v>
+        <v>479</v>
       </c>
     </row>
     <row r="743" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A743" s="2" t="s">
-        <v>2000</v>
+        <v>1998</v>
       </c>
       <c r="B743" s="2" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="C743" s="2" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="744" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A744" s="2" t="s">
+        <v>1999</v>
+      </c>
+      <c r="B744" s="2" t="s">
+        <v>2000</v>
+      </c>
+      <c r="C744" s="2" t="s">
         <v>2001</v>
-      </c>
-      <c r="B744" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="C744" s="2" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="745" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14955,40 +14948,40 @@
         <v>2002</v>
       </c>
       <c r="B745" s="2" t="s">
-        <v>2003</v>
+        <v>487</v>
       </c>
       <c r="C745" s="2" t="s">
-        <v>2004</v>
+        <v>212</v>
       </c>
     </row>
     <row r="746" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A746" s="2" t="s">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="B746" s="2" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="C746" s="2" t="s">
-        <v>212</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="747" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A747" s="2" t="s">
+        <v>2005</v>
+      </c>
+      <c r="B747" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="C747" s="2" t="s">
         <v>2006</v>
-      </c>
-      <c r="B747" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="C747" s="2" t="s">
-        <v>2007</v>
       </c>
     </row>
     <row r="748" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A748" s="2" t="s">
+        <v>2007</v>
+      </c>
+      <c r="B748" s="2" t="s">
         <v>2008</v>
-      </c>
-      <c r="B748" s="2" t="s">
-        <v>532</v>
       </c>
       <c r="C748" s="2" t="s">
         <v>2009</v>
@@ -14999,21 +14992,21 @@
         <v>2010</v>
       </c>
       <c r="B749" s="2" t="s">
-        <v>2011</v>
+        <v>514</v>
       </c>
       <c r="C749" s="2" t="s">
-        <v>2012</v>
+        <v>515</v>
       </c>
     </row>
     <row r="750" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A750" s="2" t="s">
+        <v>2011</v>
+      </c>
+      <c r="B750" s="2" t="s">
+        <v>2012</v>
+      </c>
+      <c r="C750" s="2" t="s">
         <v>2013</v>
-      </c>
-      <c r="B750" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="C750" s="2" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="751" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15035,29 +15028,29 @@
         <v>2018</v>
       </c>
       <c r="C752" s="2" t="s">
-        <v>2019</v>
+        <v>524</v>
       </c>
     </row>
     <row r="753" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A753" s="2" t="s">
+        <v>2019</v>
+      </c>
+      <c r="B753" s="2" t="s">
         <v>2020</v>
       </c>
-      <c r="B753" s="2" t="s">
-        <v>2021</v>
-      </c>
       <c r="C753" s="2" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
     </row>
     <row r="754" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A754" s="2" t="s">
+        <v>2021</v>
+      </c>
+      <c r="B754" s="2" t="s">
         <v>2022</v>
       </c>
-      <c r="B754" s="2" t="s">
+      <c r="C754" s="2" t="s">
         <v>2023</v>
-      </c>
-      <c r="C754" s="2" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="755" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15123,18 +15116,18 @@
         <v>2040</v>
       </c>
       <c r="C760" s="2" t="s">
-        <v>2041</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="761" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A761" s="2" t="s">
+        <v>2041</v>
+      </c>
+      <c r="B761" s="2" t="s">
         <v>2042</v>
       </c>
-      <c r="B761" s="2" t="s">
+      <c r="C761" s="2" t="s">
         <v>2043</v>
-      </c>
-      <c r="C761" s="2" t="s">
-        <v>1708</v>
       </c>
     </row>
     <row r="762" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15167,18 +15160,18 @@
         <v>2051</v>
       </c>
       <c r="C764" s="2" t="s">
-        <v>2052</v>
+        <v>220</v>
       </c>
     </row>
     <row r="765" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A765" s="2" t="s">
+        <v>2052</v>
+      </c>
+      <c r="B765" s="2" t="s">
         <v>2053</v>
       </c>
-      <c r="B765" s="2" t="s">
+      <c r="C765" s="2" t="s">
         <v>2054</v>
-      </c>
-      <c r="C765" s="2" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="766" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15296,32 +15289,32 @@
         <v>2085</v>
       </c>
       <c r="B776" s="2" t="s">
-        <v>2086</v>
+        <v>619</v>
       </c>
       <c r="C776" s="2" t="s">
-        <v>2087</v>
+        <v>620</v>
       </c>
     </row>
     <row r="777" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A777" s="2" t="s">
-        <v>2088</v>
+        <v>2086</v>
       </c>
       <c r="B777" s="2" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="C777" s="2" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
     </row>
     <row r="778" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A778" s="2" t="s">
+        <v>2087</v>
+      </c>
+      <c r="B778" s="2" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C778" s="2" t="s">
         <v>2089</v>
-      </c>
-      <c r="B778" s="2" t="s">
-        <v>622</v>
-      </c>
-      <c r="C778" s="2" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="779" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15395,21 +15388,21 @@
         <v>2108</v>
       </c>
       <c r="B785" s="2" t="s">
-        <v>2109</v>
+        <v>175</v>
       </c>
       <c r="C785" s="2" t="s">
-        <v>2110</v>
+        <v>176</v>
       </c>
     </row>
     <row r="786" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A786" s="2" t="s">
+        <v>2109</v>
+      </c>
+      <c r="B786" s="2" t="s">
+        <v>2110</v>
+      </c>
+      <c r="C786" s="2" t="s">
         <v>2111</v>
-      </c>
-      <c r="B786" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C786" s="2" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="787" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15432,17 +15425,6 @@
       </c>
       <c r="C788" s="2" t="s">
         <v>2117</v>
-      </c>
-    </row>
-    <row r="789" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A789" s="2" t="s">
-        <v>2118</v>
-      </c>
-      <c r="B789" s="2" t="s">
-        <v>2119</v>
-      </c>
-      <c r="C789" s="2" t="s">
-        <v>2120</v>
       </c>
     </row>
   </sheetData>

--- a/apps/workspace-web/i18n.xlsx
+++ b/apps/workspace-web/i18n.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2364" uniqueCount="2118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2397" uniqueCount="2151">
   <si>
     <t>key</t>
   </si>
@@ -524,6 +524,24 @@
   </si>
   <si>
     <t>Failed to remove cover image.</t>
+  </si>
+  <si>
+    <t>storeError.uploadScreenshotFailed</t>
+  </si>
+  <si>
+    <t>上傳預覽圖失敗。</t>
+  </si>
+  <si>
+    <t>Failed to upload preview image.</t>
+  </si>
+  <si>
+    <t>storeError.deleteScreenshotFailed</t>
+  </si>
+  <si>
+    <t>刪除預覽圖失敗。</t>
+  </si>
+  <si>
+    <t>Failed to delete preview image.</t>
   </si>
   <si>
     <t>storeError.createVersionFailed</t>
@@ -6094,6 +6112,87 @@
   </si>
   <si>
     <t>JPG / PNG / GIF / WebP, up to 5 MB. A 4:3 landscape crop works best.</t>
+  </si>
+  <si>
+    <t>productEdit.screenshotsTitle</t>
+  </si>
+  <si>
+    <t>預覽圖</t>
+  </si>
+  <si>
+    <t>Preview images</t>
+  </si>
+  <si>
+    <t>productEdit.screenshotsDesc</t>
+  </si>
+  <si>
+    <t>商品頁圖庫展示的截圖 / 預覽畫面，買家可於封面之外瀏覽更多細節。</t>
+  </si>
+  <si>
+    <t>Gallery screenshots shown on the product page, letting buyers browse more detail beyond the cover.</t>
+  </si>
+  <si>
+    <t>productEdit.screenshotAdd</t>
+  </si>
+  <si>
+    <t>新增預覽圖</t>
+  </si>
+  <si>
+    <t>Add image</t>
+  </si>
+  <si>
+    <t>productEdit.screenshotDeleteConfirm</t>
+  </si>
+  <si>
+    <t>確定刪除這張預覽圖？</t>
+  </si>
+  <si>
+    <t>Delete this preview image?</t>
+  </si>
+  <si>
+    <t>productEdit.screenshotsHint</t>
+  </si>
+  <si>
+    <t>支援 JPG / PNG / GIF / WebP，單檔最大 5 MB，最多 {max} 張。依上傳順序顯示於商品頁圖庫。</t>
+  </si>
+  <si>
+    <t>JPG / PNG / GIF / WebP, up to 5 MB each, max {max} images. Shown in the product gallery in upload order.</t>
+  </si>
+  <si>
+    <t>productEdit.msgScreenshotsUploaded</t>
+  </si>
+  <si>
+    <t>已新增 {count} 張預覽圖。</t>
+  </si>
+  <si>
+    <t>Added {count} preview image(s).</t>
+  </si>
+  <si>
+    <t>productEdit.msgScreenshotDeleted</t>
+  </si>
+  <si>
+    <t>已刪除預覽圖。</t>
+  </si>
+  <si>
+    <t>Preview image deleted.</t>
+  </si>
+  <si>
+    <t>productEdit.msgScreenshotFailed</t>
+  </si>
+  <si>
+    <t>預覽圖操作失敗。</t>
+  </si>
+  <si>
+    <t>Preview image action failed.</t>
+  </si>
+  <si>
+    <t>productEdit.msgScreenshotLimit</t>
+  </si>
+  <si>
+    <t>預覽圖最多 {max} 張，請先刪除再新增。</t>
+  </si>
+  <si>
+    <t>Up to {max} preview images — delete one first.</t>
   </si>
   <si>
     <t>productEdit.versionsTitle</t>
@@ -6752,7 +6851,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C788"/>
+  <dimension ref="A1:C799"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -7435,32 +7534,32 @@
         <v>183</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>43</v>
+        <v>184</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>44</v>
+        <v>185</v>
       </c>
     </row>
     <row r="63" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="64" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>188</v>
+        <v>43</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>189</v>
+        <v>44</v>
       </c>
     </row>
     <row r="65" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7493,26 +7592,26 @@
         <v>197</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="68" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="69" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>203</v>
@@ -7570,29 +7669,29 @@
         <v>217</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>186</v>
+        <v>218</v>
       </c>
     </row>
     <row r="75" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="76" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>223</v>
+        <v>192</v>
       </c>
     </row>
     <row r="77" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7941,32 +8040,32 @@
         <v>317</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>28</v>
+        <v>318</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>29</v>
+        <v>319</v>
       </c>
     </row>
     <row r="109" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="110" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>322</v>
+        <v>28</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>323</v>
+        <v>29</v>
       </c>
     </row>
     <row r="111" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8095,32 +8194,32 @@
         <v>357</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>294</v>
+        <v>358</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>295</v>
+        <v>359</v>
       </c>
     </row>
     <row r="123" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="124" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>362</v>
+        <v>300</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>363</v>
+        <v>301</v>
       </c>
     </row>
     <row r="125" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8381,32 +8480,32 @@
         <v>433</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>380</v>
+        <v>434</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>381</v>
+        <v>435</v>
       </c>
     </row>
     <row r="149" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="150" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>438</v>
+        <v>386</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>439</v>
+        <v>387</v>
       </c>
     </row>
     <row r="151" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8425,32 +8524,32 @@
         <v>443</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>306</v>
+        <v>444</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>307</v>
+        <v>445</v>
       </c>
     </row>
     <row r="153" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="154" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>448</v>
+        <v>312</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>449</v>
+        <v>313</v>
       </c>
     </row>
     <row r="155" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8813,51 +8912,51 @@
         <v>547</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>467</v>
+        <v>548</v>
       </c>
     </row>
     <row r="188" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>478</v>
+        <v>550</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>479</v>
+        <v>551</v>
       </c>
     </row>
     <row r="189" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>487</v>
+        <v>553</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>212</v>
+        <v>473</v>
       </c>
     </row>
     <row r="190" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>551</v>
+        <v>484</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>552</v>
+        <v>485</v>
       </c>
     </row>
     <row r="191" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>554</v>
+        <v>493</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>555</v>
+        <v>218</v>
       </c>
     </row>
     <row r="192" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8865,32 +8964,32 @@
         <v>556</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>514</v>
+        <v>557</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>515</v>
+        <v>558</v>
       </c>
     </row>
     <row r="193" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="194" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>561</v>
+        <v>520</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>562</v>
+        <v>521</v>
       </c>
     </row>
     <row r="195" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8931,32 +9030,32 @@
         <v>572</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>22</v>
+        <v>573</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>23</v>
+        <v>574</v>
       </c>
     </row>
     <row r="199" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="200" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>577</v>
+        <v>22</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>578</v>
+        <v>23</v>
       </c>
     </row>
     <row r="201" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8997,29 +9096,29 @@
         <v>588</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>478</v>
+        <v>589</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="205" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="206" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>594</v>
+        <v>484</v>
       </c>
       <c r="C206" s="2" t="s">
         <v>595</v>
@@ -9107,32 +9206,32 @@
         <v>617</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>175</v>
+        <v>618</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>176</v>
+        <v>619</v>
       </c>
     </row>
     <row r="215" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="216" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>622</v>
+        <v>181</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>623</v>
+        <v>182</v>
       </c>
     </row>
     <row r="217" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9239,54 +9338,54 @@
         <v>651</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>197</v>
+        <v>652</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>197</v>
+        <v>653</v>
       </c>
     </row>
     <row r="227" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="228" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
     </row>
     <row r="229" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="230" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>660</v>
+        <v>200</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>661</v>
+        <v>201</v>
       </c>
     </row>
     <row r="231" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9360,54 +9459,54 @@
         <v>680</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>346</v>
+        <v>681</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>347</v>
+        <v>682</v>
       </c>
     </row>
     <row r="238" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
     </row>
     <row r="239" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="240" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="241" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>689</v>
+        <v>355</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>690</v>
+        <v>356</v>
       </c>
     </row>
     <row r="242" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9547,54 +9646,54 @@
         <v>727</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>346</v>
+        <v>728</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>347</v>
+        <v>729</v>
       </c>
     </row>
     <row r="255" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>682</v>
+        <v>731</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>683</v>
+        <v>732</v>
       </c>
     </row>
     <row r="256" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="257" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>731</v>
+        <v>688</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>732</v>
+        <v>689</v>
       </c>
     </row>
     <row r="258" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>734</v>
+        <v>355</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>735</v>
+        <v>356</v>
       </c>
     </row>
     <row r="259" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9657,32 +9756,32 @@
         <v>751</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>634</v>
+        <v>752</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>635</v>
+        <v>753</v>
       </c>
     </row>
     <row r="265" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
     </row>
     <row r="266" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>756</v>
+        <v>640</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>757</v>
+        <v>641</v>
       </c>
     </row>
     <row r="267" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9767,32 +9866,32 @@
         <v>779</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>22</v>
+        <v>780</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>23</v>
+        <v>781</v>
       </c>
     </row>
     <row r="275" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
     </row>
     <row r="276" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>784</v>
+        <v>22</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>785</v>
+        <v>23</v>
       </c>
     </row>
     <row r="277" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10097,54 +10196,54 @@
         <v>867</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>547</v>
+        <v>868</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>467</v>
+        <v>869</v>
       </c>
     </row>
     <row r="305" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
     </row>
     <row r="306" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>294</v>
+        <v>553</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>295</v>
+        <v>473</v>
       </c>
     </row>
     <row r="307" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
     </row>
     <row r="308" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>876</v>
+        <v>300</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>877</v>
+        <v>301</v>
       </c>
     </row>
     <row r="309" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10229,32 +10328,32 @@
         <v>899</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>865</v>
+        <v>900</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>866</v>
+        <v>901</v>
       </c>
     </row>
     <row r="317" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
     </row>
     <row r="318" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>904</v>
+        <v>871</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>905</v>
+        <v>872</v>
       </c>
     </row>
     <row r="319" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10317,32 +10416,32 @@
         <v>921</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>737</v>
+        <v>922</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>738</v>
+        <v>923</v>
       </c>
     </row>
     <row r="325" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
     </row>
     <row r="326" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>926</v>
+        <v>743</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>927</v>
+        <v>744</v>
       </c>
     </row>
     <row r="327" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10383,32 +10482,32 @@
         <v>937</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>52</v>
+        <v>938</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>53</v>
+        <v>939</v>
       </c>
     </row>
     <row r="331" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
     </row>
     <row r="332" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>942</v>
+        <v>52</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>943</v>
+        <v>53</v>
       </c>
     </row>
     <row r="333" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10584,40 +10683,40 @@
         <v>990</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
     </row>
     <row r="349" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>428</v>
+        <v>993</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>429</v>
+        <v>994</v>
       </c>
     </row>
     <row r="350" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
     </row>
     <row r="351" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>996</v>
+        <v>434</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>997</v>
+        <v>435</v>
       </c>
     </row>
     <row r="352" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10705,26 +10804,26 @@
         <v>1020</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="360" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="361" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="C361" s="2" t="s">
         <v>1026</v>
@@ -11043,43 +11142,43 @@
         <v>1111</v>
       </c>
       <c r="B390" s="2" t="s">
-        <v>306</v>
+        <v>1112</v>
       </c>
       <c r="C390" s="2" t="s">
-        <v>307</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="391" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A391" s="2" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="B391" s="2" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="C391" s="2" t="s">
-        <v>654</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="392" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A392" s="2" t="s">
-        <v>1114</v>
+        <v>1117</v>
       </c>
       <c r="B392" s="2" t="s">
-        <v>1115</v>
+        <v>312</v>
       </c>
       <c r="C392" s="2" t="s">
-        <v>1116</v>
+        <v>313</v>
       </c>
     </row>
     <row r="393" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A393" s="2" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="B393" s="2" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="C393" s="2" t="s">
-        <v>1119</v>
+        <v>660</v>
       </c>
     </row>
     <row r="394" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11087,32 +11186,32 @@
         <v>1120</v>
       </c>
       <c r="B394" s="2" t="s">
-        <v>194</v>
+        <v>1121</v>
       </c>
       <c r="C394" s="2" t="s">
-        <v>195</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="395" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A395" s="2" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="B395" s="2" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="C395" s="2" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="396" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A396" s="2" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="B396" s="2" t="s">
-        <v>1125</v>
+        <v>200</v>
       </c>
       <c r="C396" s="2" t="s">
-        <v>1126</v>
+        <v>201</v>
       </c>
     </row>
     <row r="397" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11186,43 +11285,43 @@
         <v>1145</v>
       </c>
       <c r="B403" s="2" t="s">
-        <v>288</v>
+        <v>1146</v>
       </c>
       <c r="C403" s="2" t="s">
-        <v>289</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="404" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A404" s="2" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="B404" s="2" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="C404" s="2" t="s">
-        <v>1132</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="405" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A405" s="2" t="s">
-        <v>1148</v>
+        <v>1151</v>
       </c>
       <c r="B405" s="2" t="s">
-        <v>1149</v>
+        <v>294</v>
       </c>
       <c r="C405" s="2" t="s">
-        <v>1150</v>
+        <v>295</v>
       </c>
     </row>
     <row r="406" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A406" s="2" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="C406" s="2" t="s">
-        <v>1153</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="407" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11263,32 +11362,32 @@
         <v>1163</v>
       </c>
       <c r="B410" s="2" t="s">
-        <v>306</v>
+        <v>1164</v>
       </c>
       <c r="C410" s="2" t="s">
-        <v>307</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="411" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A411" s="2" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="B411" s="2" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="C411" s="2" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="412" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A412" s="2" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="B412" s="2" t="s">
-        <v>1168</v>
+        <v>312</v>
       </c>
       <c r="C412" s="2" t="s">
-        <v>1169</v>
+        <v>313</v>
       </c>
     </row>
     <row r="413" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11450,29 +11549,29 @@
         <v>1212</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>362</v>
+        <v>1213</v>
       </c>
       <c r="C427" s="2" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="428" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A428" s="2" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="B428" s="2" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="C428" s="2" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="429" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A429" s="2" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>1218</v>
+        <v>368</v>
       </c>
       <c r="C429" s="2" t="s">
         <v>1219</v>
@@ -11692,32 +11791,32 @@
         <v>1277</v>
       </c>
       <c r="B449" s="2" t="s">
-        <v>993</v>
+        <v>1278</v>
       </c>
       <c r="C449" s="2" t="s">
-        <v>994</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="450" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A450" s="2" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="B450" s="2" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="C450" s="2" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="451" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A451" s="2" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="B451" s="2" t="s">
-        <v>1282</v>
+        <v>999</v>
       </c>
       <c r="C451" s="2" t="s">
-        <v>1283</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="452" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11728,34 +11827,34 @@
         <v>1285</v>
       </c>
       <c r="C452" s="2" t="s">
-        <v>186</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="453" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A453" s="2" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>188</v>
+        <v>1288</v>
       </c>
       <c r="C453" s="2" t="s">
-        <v>189</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="454" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A454" s="2" t="s">
-        <v>1287</v>
+        <v>1290</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>1288</v>
+        <v>1291</v>
       </c>
       <c r="C454" s="2" t="s">
-        <v>1289</v>
+        <v>192</v>
       </c>
     </row>
     <row r="455" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A455" s="2" t="s">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="B455" s="2" t="s">
         <v>194</v>
@@ -11766,90 +11865,90 @@
     </row>
     <row r="456" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A456" s="2" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="B456" s="2" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="C456" s="2" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="457" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A457" s="2" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="B457" s="2" t="s">
-        <v>294</v>
+        <v>200</v>
       </c>
       <c r="C457" s="2" t="s">
-        <v>295</v>
+        <v>201</v>
       </c>
     </row>
     <row r="458" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A458" s="2" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="B458" s="2" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="C458" s="2" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="459" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A459" s="2" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="B459" s="2" t="s">
-        <v>1106</v>
+        <v>300</v>
       </c>
       <c r="C459" s="2" t="s">
-        <v>1299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="460" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A460" s="2" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="B460" s="2" t="s">
-        <v>315</v>
+        <v>1302</v>
       </c>
       <c r="C460" s="2" t="s">
-        <v>316</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="461" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A461" s="2" t="s">
-        <v>1301</v>
+        <v>1304</v>
       </c>
       <c r="B461" s="2" t="s">
-        <v>309</v>
+        <v>1112</v>
       </c>
       <c r="C461" s="2" t="s">
-        <v>310</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="462" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A462" s="2" t="s">
-        <v>1302</v>
+        <v>1306</v>
       </c>
       <c r="B462" s="2" t="s">
-        <v>1303</v>
+        <v>321</v>
       </c>
       <c r="C462" s="2" t="s">
-        <v>1304</v>
+        <v>322</v>
       </c>
     </row>
     <row r="463" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A463" s="2" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>1306</v>
+        <v>315</v>
       </c>
       <c r="C463" s="2" t="s">
-        <v>1307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="464" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11857,26 +11956,26 @@
         <v>1308</v>
       </c>
       <c r="B464" s="2" t="s">
-        <v>325</v>
+        <v>1309</v>
       </c>
       <c r="C464" s="2" t="s">
-        <v>326</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="465" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A465" s="2" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="B465" s="2" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="C465" s="2" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="466" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A466" s="2" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="B466" s="2" t="s">
         <v>331</v>
@@ -11887,79 +11986,79 @@
     </row>
     <row r="467" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A467" s="2" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="B467" s="2" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="C467" s="2" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="468" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A468" s="2" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
       <c r="B468" s="2" t="s">
-        <v>1317</v>
+        <v>337</v>
       </c>
       <c r="C468" s="2" t="s">
-        <v>1317</v>
+        <v>338</v>
       </c>
     </row>
     <row r="469" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A469" s="2" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B469" s="2" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="C469" s="2" t="s">
-        <v>1319</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="470" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A470" s="2" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="B470" s="2" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="C470" s="2" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="471" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A471" s="2" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="B471" s="2" t="s">
-        <v>1321</v>
+        <v>1325</v>
       </c>
       <c r="C471" s="2" t="s">
-        <v>1322</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="472" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A472" s="2" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
       <c r="B472" s="2" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="C472" s="2" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="473" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A473" s="2" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B473" s="2" t="s">
         <v>1327</v>
       </c>
-      <c r="B473" s="2" t="s">
+      <c r="C473" s="2" t="s">
         <v>1328</v>
-      </c>
-      <c r="C473" s="2" t="s">
-        <v>1329</v>
       </c>
     </row>
     <row r="474" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12091,29 +12190,29 @@
         <v>1364</v>
       </c>
       <c r="C485" s="2" t="s">
-        <v>1341</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="486" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A486" s="2" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="B486" s="2" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="C486" s="2" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="487" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A487" s="2" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="C487" s="2" t="s">
-        <v>1370</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="488" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12124,29 +12223,29 @@
         <v>1372</v>
       </c>
       <c r="C488" s="2" t="s">
-        <v>1347</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="489" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A489" s="2" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="B489" s="2" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="C489" s="2" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="490" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A490" s="2" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="B490" s="2" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="C490" s="2" t="s">
-        <v>1378</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="491" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12165,32 +12264,32 @@
         <v>1382</v>
       </c>
       <c r="B492" s="2" t="s">
-        <v>1234</v>
+        <v>1383</v>
       </c>
       <c r="C492" s="2" t="s">
-        <v>1234</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="493" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A493" s="2" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="B493" s="2" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="C493" s="2" t="s">
-        <v>1385</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="494" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A494" s="2" t="s">
-        <v>1386</v>
+        <v>1388</v>
       </c>
       <c r="B494" s="2" t="s">
-        <v>1387</v>
+        <v>1240</v>
       </c>
       <c r="C494" s="2" t="s">
-        <v>1388</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="495" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12264,32 +12363,32 @@
         <v>1407</v>
       </c>
       <c r="B501" s="2" t="s">
-        <v>1269</v>
+        <v>1408</v>
       </c>
       <c r="C501" s="2" t="s">
-        <v>1270</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="502" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A502" s="2" t="s">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="B502" s="2" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="C502" s="2" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="503" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A503" s="2" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="B503" s="2" t="s">
-        <v>1412</v>
+        <v>1275</v>
       </c>
       <c r="C503" s="2" t="s">
-        <v>1413</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="504" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12344,62 +12443,62 @@
         <v>1427</v>
       </c>
       <c r="C508" s="2" t="s">
-        <v>220</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="509" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A509" s="2" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="B509" s="2" t="s">
-        <v>188</v>
+        <v>1430</v>
       </c>
       <c r="C509" s="2" t="s">
-        <v>189</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="510" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A510" s="2" t="s">
-        <v>1429</v>
+        <v>1432</v>
       </c>
       <c r="B510" s="2" t="s">
-        <v>191</v>
+        <v>1433</v>
       </c>
       <c r="C510" s="2" t="s">
-        <v>192</v>
+        <v>226</v>
       </c>
     </row>
     <row r="511" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A511" s="2" t="s">
-        <v>1430</v>
+        <v>1434</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>640</v>
+        <v>194</v>
       </c>
       <c r="C511" s="2" t="s">
-        <v>641</v>
+        <v>195</v>
       </c>
     </row>
     <row r="512" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A512" s="2" t="s">
-        <v>1431</v>
+        <v>1435</v>
       </c>
       <c r="B512" s="2" t="s">
-        <v>1432</v>
+        <v>197</v>
       </c>
       <c r="C512" s="2" t="s">
-        <v>1433</v>
+        <v>198</v>
       </c>
     </row>
     <row r="513" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A513" s="2" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>1435</v>
+        <v>646</v>
       </c>
       <c r="C513" s="2" t="s">
-        <v>1436</v>
+        <v>647</v>
       </c>
     </row>
     <row r="514" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12594,98 +12693,98 @@
         <v>1488</v>
       </c>
       <c r="B531" s="2" t="s">
-        <v>43</v>
+        <v>1489</v>
       </c>
       <c r="C531" s="2" t="s">
-        <v>44</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="532" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A532" s="2" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="B532" s="2" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
       <c r="C532" s="2" t="s">
-        <v>1116</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="533" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A533" s="2" t="s">
-        <v>1491</v>
+        <v>1494</v>
       </c>
       <c r="B533" s="2" t="s">
-        <v>1432</v>
+        <v>43</v>
       </c>
       <c r="C533" s="2" t="s">
-        <v>1433</v>
+        <v>44</v>
       </c>
     </row>
     <row r="534" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A534" s="2" t="s">
-        <v>1492</v>
+        <v>1495</v>
       </c>
       <c r="B534" s="2" t="s">
-        <v>1493</v>
+        <v>1496</v>
       </c>
       <c r="C534" s="2" t="s">
-        <v>1225</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="535" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A535" s="2" t="s">
-        <v>1494</v>
+        <v>1497</v>
       </c>
       <c r="B535" s="2" t="s">
-        <v>1495</v>
+        <v>1438</v>
       </c>
       <c r="C535" s="2" t="s">
-        <v>1496</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="536" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A536" s="2" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="B536" s="2" t="s">
-        <v>1435</v>
+        <v>1499</v>
       </c>
       <c r="C536" s="2" t="s">
-        <v>1436</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="537" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A537" s="2" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="B537" s="2" t="s">
-        <v>197</v>
+        <v>1501</v>
       </c>
       <c r="C537" s="2" t="s">
-        <v>197</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="538" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A538" s="2" t="s">
-        <v>1499</v>
+        <v>1503</v>
       </c>
       <c r="B538" s="2" t="s">
-        <v>1500</v>
+        <v>1441</v>
       </c>
       <c r="C538" s="2" t="s">
-        <v>1501</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="539" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A539" s="2" t="s">
-        <v>1502</v>
+        <v>1504</v>
       </c>
       <c r="B539" s="2" t="s">
-        <v>1503</v>
+        <v>203</v>
       </c>
       <c r="C539" s="2" t="s">
-        <v>1504</v>
+        <v>203</v>
       </c>
     </row>
     <row r="540" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12726,65 +12825,65 @@
         <v>1514</v>
       </c>
       <c r="B543" s="2" t="s">
-        <v>1266</v>
+        <v>1515</v>
       </c>
       <c r="C543" s="2" t="s">
-        <v>1267</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="544" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A544" s="2" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="B544" s="2" t="s">
-        <v>4</v>
+        <v>1518</v>
       </c>
       <c r="C544" s="2" t="s">
-        <v>5</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="545" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A545" s="2" t="s">
-        <v>1516</v>
+        <v>1520</v>
       </c>
       <c r="B545" s="2" t="s">
-        <v>1257</v>
+        <v>1272</v>
       </c>
       <c r="C545" s="2" t="s">
-        <v>1258</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="546" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A546" s="2" t="s">
-        <v>1517</v>
+        <v>1521</v>
       </c>
       <c r="B546" s="2" t="s">
-        <v>1269</v>
+        <v>4</v>
       </c>
       <c r="C546" s="2" t="s">
-        <v>1270</v>
+        <v>5</v>
       </c>
     </row>
     <row r="547" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A547" s="2" t="s">
-        <v>1518</v>
+        <v>1522</v>
       </c>
       <c r="B547" s="2" t="s">
-        <v>1519</v>
+        <v>1263</v>
       </c>
       <c r="C547" s="2" t="s">
-        <v>1520</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="548" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A548" s="2" t="s">
-        <v>1521</v>
+        <v>1523</v>
       </c>
       <c r="B548" s="2" t="s">
-        <v>1522</v>
+        <v>1275</v>
       </c>
       <c r="C548" s="2" t="s">
-        <v>1523</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="549" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12792,62 +12891,62 @@
         <v>1524</v>
       </c>
       <c r="B549" s="2" t="s">
-        <v>1272</v>
+        <v>1525</v>
       </c>
       <c r="C549" s="2" t="s">
-        <v>1273</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="550" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A550" s="2" t="s">
-        <v>1525</v>
+        <v>1527</v>
       </c>
       <c r="B550" s="2" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
       <c r="C550" s="2" t="s">
-        <v>1527</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="551" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A551" s="2" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="B551" s="2" t="s">
-        <v>1275</v>
+        <v>1278</v>
       </c>
       <c r="C551" s="2" t="s">
-        <v>1529</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="552" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A552" s="2" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="B552" s="2" t="s">
-        <v>1224</v>
+        <v>1532</v>
       </c>
       <c r="C552" s="2" t="s">
-        <v>1531</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="553" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A553" s="2" t="s">
-        <v>1532</v>
+        <v>1534</v>
       </c>
       <c r="B553" s="2" t="s">
-        <v>1533</v>
+        <v>1281</v>
       </c>
       <c r="C553" s="2" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="554" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A554" s="2" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="B554" s="2" t="s">
-        <v>1536</v>
+        <v>1230</v>
       </c>
       <c r="C554" s="2" t="s">
         <v>1537</v>
@@ -12935,26 +13034,26 @@
         <v>1559</v>
       </c>
       <c r="B562" s="2" t="s">
-        <v>1266</v>
+        <v>1560</v>
       </c>
       <c r="C562" s="2" t="s">
-        <v>1267</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="563" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A563" s="2" t="s">
-        <v>1560</v>
+        <v>1562</v>
       </c>
       <c r="B563" s="2" t="s">
-        <v>4</v>
+        <v>1563</v>
       </c>
       <c r="C563" s="2" t="s">
-        <v>5</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="564" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A564" s="2" t="s">
-        <v>1561</v>
+        <v>1565</v>
       </c>
       <c r="B564" s="2" t="s">
         <v>1272</v>
@@ -12965,24 +13064,24 @@
     </row>
     <row r="565" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A565" s="2" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="B565" s="2" t="s">
-        <v>1563</v>
+        <v>4</v>
       </c>
       <c r="C565" s="2" t="s">
-        <v>1564</v>
+        <v>5</v>
       </c>
     </row>
     <row r="566" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A566" s="2" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="B566" s="2" t="s">
-        <v>1566</v>
+        <v>1278</v>
       </c>
       <c r="C566" s="2" t="s">
-        <v>1567</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="567" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13001,32 +13100,32 @@
         <v>1571</v>
       </c>
       <c r="B568" s="2" t="s">
-        <v>1542</v>
+        <v>1572</v>
       </c>
       <c r="C568" s="2" t="s">
-        <v>1543</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="569" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A569" s="2" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="B569" s="2" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
       <c r="C569" s="2" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="570" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A570" s="2" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="B570" s="2" t="s">
-        <v>1576</v>
+        <v>1548</v>
       </c>
       <c r="C570" s="2" t="s">
-        <v>1577</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="571" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13034,32 +13133,32 @@
         <v>1578</v>
       </c>
       <c r="B571" s="2" t="s">
-        <v>1396</v>
+        <v>1579</v>
       </c>
       <c r="C571" s="2" t="s">
-        <v>1397</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="572" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A572" s="2" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="B572" s="2" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="C572" s="2" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="573" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A573" s="2" t="s">
-        <v>1582</v>
+        <v>1584</v>
       </c>
       <c r="B573" s="2" t="s">
-        <v>1583</v>
+        <v>1402</v>
       </c>
       <c r="C573" s="2" t="s">
-        <v>1584</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="574" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13125,29 +13224,29 @@
         <v>1601</v>
       </c>
       <c r="C579" s="2" t="s">
-        <v>545</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="580" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A580" s="2" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="B580" s="2" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="C580" s="2" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="581" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A581" s="2" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="B581" s="2" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="C581" s="2" t="s">
-        <v>1607</v>
+        <v>551</v>
       </c>
     </row>
     <row r="582" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13221,32 +13320,32 @@
         <v>1626</v>
       </c>
       <c r="B588" s="2" t="s">
-        <v>544</v>
+        <v>1627</v>
       </c>
       <c r="C588" s="2" t="s">
-        <v>545</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="589" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A589" s="2" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
       <c r="B589" s="2" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="C589" s="2" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="590" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A590" s="2" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="B590" s="2" t="s">
-        <v>1631</v>
+        <v>550</v>
       </c>
       <c r="C590" s="2" t="s">
-        <v>1632</v>
+        <v>551</v>
       </c>
     </row>
     <row r="591" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13254,32 +13353,32 @@
         <v>1633</v>
       </c>
       <c r="B591" s="2" t="s">
-        <v>294</v>
+        <v>1634</v>
       </c>
       <c r="C591" s="2" t="s">
-        <v>295</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="592" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A592" s="2" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="B592" s="2" t="s">
-        <v>1635</v>
+        <v>1637</v>
       </c>
       <c r="C592" s="2" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="593" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A593" s="2" t="s">
-        <v>1637</v>
+        <v>1639</v>
       </c>
       <c r="B593" s="2" t="s">
-        <v>1638</v>
+        <v>300</v>
       </c>
       <c r="C593" s="2" t="s">
-        <v>1639</v>
+        <v>301</v>
       </c>
     </row>
     <row r="594" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13397,65 +13496,65 @@
         <v>1670</v>
       </c>
       <c r="B604" s="2" t="s">
-        <v>288</v>
+        <v>1671</v>
       </c>
       <c r="C604" s="2" t="s">
-        <v>289</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="605" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A605" s="2" t="s">
-        <v>1671</v>
+        <v>1673</v>
       </c>
       <c r="B605" s="2" t="s">
-        <v>1672</v>
+        <v>1674</v>
       </c>
       <c r="C605" s="2" t="s">
-        <v>1116</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="606" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A606" s="2" t="s">
-        <v>1673</v>
+        <v>1676</v>
       </c>
       <c r="B606" s="2" t="s">
-        <v>1674</v>
+        <v>294</v>
       </c>
       <c r="C606" s="2" t="s">
-        <v>1675</v>
+        <v>295</v>
       </c>
     </row>
     <row r="607" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A607" s="2" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="B607" s="2" t="s">
-        <v>1495</v>
+        <v>1678</v>
       </c>
       <c r="C607" s="2" t="s">
-        <v>1496</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="608" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A608" s="2" t="s">
-        <v>1677</v>
+        <v>1679</v>
       </c>
       <c r="B608" s="2" t="s">
-        <v>1678</v>
+        <v>1680</v>
       </c>
       <c r="C608" s="2" t="s">
-        <v>1679</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="609" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A609" s="2" t="s">
-        <v>1680</v>
+        <v>1682</v>
       </c>
       <c r="B609" s="2" t="s">
-        <v>1681</v>
+        <v>1501</v>
       </c>
       <c r="C609" s="2" t="s">
-        <v>1682</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="610" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13496,76 +13595,76 @@
         <v>1692</v>
       </c>
       <c r="B613" s="2" t="s">
-        <v>188</v>
+        <v>1693</v>
       </c>
       <c r="C613" s="2" t="s">
-        <v>189</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="614" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A614" s="2" t="s">
-        <v>1693</v>
+        <v>1695</v>
       </c>
       <c r="B614" s="2" t="s">
-        <v>1113</v>
+        <v>1696</v>
       </c>
       <c r="C614" s="2" t="s">
-        <v>654</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="615" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A615" s="2" t="s">
-        <v>1694</v>
+        <v>1698</v>
       </c>
       <c r="B615" s="2" t="s">
-        <v>1122</v>
+        <v>194</v>
       </c>
       <c r="C615" s="2" t="s">
-        <v>1695</v>
+        <v>195</v>
       </c>
     </row>
     <row r="616" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A616" s="2" t="s">
-        <v>1696</v>
+        <v>1699</v>
       </c>
       <c r="B616" s="2" t="s">
-        <v>1697</v>
+        <v>1119</v>
       </c>
       <c r="C616" s="2" t="s">
-        <v>1698</v>
+        <v>660</v>
       </c>
     </row>
     <row r="617" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A617" s="2" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="B617" s="2" t="s">
-        <v>288</v>
+        <v>1128</v>
       </c>
       <c r="C617" s="2" t="s">
-        <v>289</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="618" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A618" s="2" t="s">
-        <v>1700</v>
+        <v>1702</v>
       </c>
       <c r="B618" s="2" t="s">
-        <v>1701</v>
+        <v>1703</v>
       </c>
       <c r="C618" s="2" t="s">
-        <v>1702</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="619" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A619" s="2" t="s">
-        <v>1703</v>
+        <v>1705</v>
       </c>
       <c r="B619" s="2" t="s">
-        <v>1704</v>
+        <v>294</v>
       </c>
       <c r="C619" s="2" t="s">
-        <v>1705</v>
+        <v>295</v>
       </c>
     </row>
     <row r="620" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13595,32 +13694,32 @@
         <v>1712</v>
       </c>
       <c r="B622" s="2" t="s">
-        <v>294</v>
+        <v>1713</v>
       </c>
       <c r="C622" s="2" t="s">
-        <v>295</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="623" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A623" s="2" t="s">
-        <v>1713</v>
+        <v>1715</v>
       </c>
       <c r="B623" s="2" t="s">
-        <v>1714</v>
+        <v>1716</v>
       </c>
       <c r="C623" s="2" t="s">
-        <v>1715</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="624" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A624" s="2" t="s">
-        <v>1716</v>
+        <v>1718</v>
       </c>
       <c r="B624" s="2" t="s">
-        <v>1717</v>
+        <v>300</v>
       </c>
       <c r="C624" s="2" t="s">
-        <v>1718</v>
+        <v>301</v>
       </c>
     </row>
     <row r="625" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13661,32 +13760,32 @@
         <v>1728</v>
       </c>
       <c r="B628" s="2" t="s">
-        <v>544</v>
+        <v>1729</v>
       </c>
       <c r="C628" s="2" t="s">
-        <v>545</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="629" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A629" s="2" t="s">
-        <v>1729</v>
+        <v>1731</v>
       </c>
       <c r="B629" s="2" t="s">
-        <v>1730</v>
+        <v>1732</v>
       </c>
       <c r="C629" s="2" t="s">
-        <v>1731</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="630" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A630" s="2" t="s">
-        <v>1732</v>
+        <v>1734</v>
       </c>
       <c r="B630" s="2" t="s">
-        <v>1733</v>
+        <v>550</v>
       </c>
       <c r="C630" s="2" t="s">
-        <v>1734</v>
+        <v>551</v>
       </c>
     </row>
     <row r="631" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13771,32 +13870,32 @@
         <v>1756</v>
       </c>
       <c r="B638" s="2" t="s">
-        <v>19</v>
+        <v>1757</v>
       </c>
       <c r="C638" s="2" t="s">
-        <v>20</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="639" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A639" s="2" t="s">
-        <v>1757</v>
+        <v>1759</v>
       </c>
       <c r="B639" s="2" t="s">
-        <v>1758</v>
+        <v>1760</v>
       </c>
       <c r="C639" s="2" t="s">
-        <v>1759</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="640" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A640" s="2" t="s">
-        <v>1760</v>
+        <v>1762</v>
       </c>
       <c r="B640" s="2" t="s">
-        <v>1761</v>
+        <v>19</v>
       </c>
       <c r="C640" s="2" t="s">
-        <v>1762</v>
+        <v>20</v>
       </c>
     </row>
     <row r="641" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13837,32 +13936,32 @@
         <v>1772</v>
       </c>
       <c r="B644" s="2" t="s">
-        <v>273</v>
+        <v>1773</v>
       </c>
       <c r="C644" s="2" t="s">
-        <v>274</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="645" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A645" s="2" t="s">
-        <v>1773</v>
+        <v>1775</v>
       </c>
       <c r="B645" s="2" t="s">
-        <v>1774</v>
+        <v>1776</v>
       </c>
       <c r="C645" s="2" t="s">
-        <v>1775</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="646" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A646" s="2" t="s">
-        <v>1776</v>
+        <v>1778</v>
       </c>
       <c r="B646" s="2" t="s">
-        <v>1777</v>
+        <v>279</v>
       </c>
       <c r="C646" s="2" t="s">
-        <v>1778</v>
+        <v>280</v>
       </c>
     </row>
     <row r="647" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13936,29 +14035,29 @@
         <v>1797</v>
       </c>
       <c r="B653" s="2" t="s">
-        <v>756</v>
+        <v>1798</v>
       </c>
       <c r="C653" s="2" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="654" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A654" s="2" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="B654" s="2" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="C654" s="2" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="655" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A655" s="2" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="B655" s="2" t="s">
-        <v>1803</v>
+        <v>762</v>
       </c>
       <c r="C655" s="2" t="s">
         <v>1804</v>
@@ -14038,29 +14137,29 @@
         <v>1824</v>
       </c>
       <c r="C662" s="2" t="s">
-        <v>467</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="663" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A663" s="2" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="B663" s="2" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="C663" s="2" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="664" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A664" s="2" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="B664" s="2" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="C664" s="2" t="s">
-        <v>1830</v>
+        <v>473</v>
       </c>
     </row>
     <row r="665" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14068,120 +14167,120 @@
         <v>1831</v>
       </c>
       <c r="B665" s="2" t="s">
-        <v>288</v>
+        <v>1832</v>
       </c>
       <c r="C665" s="2" t="s">
-        <v>289</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="666" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A666" s="2" t="s">
-        <v>1832</v>
+        <v>1834</v>
       </c>
       <c r="B666" s="2" t="s">
-        <v>1833</v>
+        <v>1835</v>
       </c>
       <c r="C666" s="2" t="s">
-        <v>186</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="667" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A667" s="2" t="s">
-        <v>1834</v>
+        <v>1837</v>
       </c>
       <c r="B667" s="2" t="s">
-        <v>1835</v>
+        <v>294</v>
       </c>
       <c r="C667" s="2" t="s">
-        <v>1836</v>
+        <v>295</v>
       </c>
     </row>
     <row r="668" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A668" s="2" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="B668" s="2" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="C668" s="2" t="s">
-        <v>467</v>
+        <v>192</v>
       </c>
     </row>
     <row r="669" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A669" s="2" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="B669" s="2" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="C669" s="2" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="670" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A670" s="2" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="B670" s="2" t="s">
-        <v>869</v>
+        <v>1844</v>
       </c>
       <c r="C670" s="2" t="s">
-        <v>870</v>
+        <v>473</v>
       </c>
     </row>
     <row r="671" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A671" s="2" t="s">
-        <v>1843</v>
+        <v>1845</v>
       </c>
       <c r="B671" s="2" t="s">
-        <v>4</v>
+        <v>1846</v>
       </c>
       <c r="C671" s="2" t="s">
-        <v>5</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="672" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A672" s="2" t="s">
-        <v>1844</v>
+        <v>1848</v>
       </c>
       <c r="B672" s="2" t="s">
-        <v>294</v>
+        <v>875</v>
       </c>
       <c r="C672" s="2" t="s">
-        <v>295</v>
+        <v>876</v>
       </c>
     </row>
     <row r="673" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A673" s="2" t="s">
-        <v>1845</v>
+        <v>1849</v>
       </c>
       <c r="B673" s="2" t="s">
-        <v>1840</v>
+        <v>4</v>
       </c>
       <c r="C673" s="2" t="s">
-        <v>1841</v>
+        <v>5</v>
       </c>
     </row>
     <row r="674" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A674" s="2" t="s">
-        <v>1846</v>
+        <v>1850</v>
       </c>
       <c r="B674" s="2" t="s">
-        <v>1847</v>
+        <v>300</v>
       </c>
       <c r="C674" s="2" t="s">
-        <v>1848</v>
+        <v>301</v>
       </c>
     </row>
     <row r="675" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A675" s="2" t="s">
-        <v>1849</v>
+        <v>1851</v>
       </c>
       <c r="B675" s="2" t="s">
-        <v>1850</v>
+        <v>1846</v>
       </c>
       <c r="C675" s="2" t="s">
-        <v>1851</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="676" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14255,54 +14354,54 @@
         <v>1870</v>
       </c>
       <c r="B682" s="2" t="s">
-        <v>19</v>
+        <v>1871</v>
       </c>
       <c r="C682" s="2" t="s">
-        <v>20</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="683" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A683" s="2" t="s">
-        <v>1871</v>
+        <v>1873</v>
       </c>
       <c r="B683" s="2" t="s">
-        <v>13</v>
+        <v>1874</v>
       </c>
       <c r="C683" s="2" t="s">
-        <v>14</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="684" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A684" s="2" t="s">
-        <v>1872</v>
+        <v>1876</v>
       </c>
       <c r="B684" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C684" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="685" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A685" s="2" t="s">
-        <v>1873</v>
+        <v>1877</v>
       </c>
       <c r="B685" s="2" t="s">
-        <v>1874</v>
+        <v>13</v>
       </c>
       <c r="C685" s="2" t="s">
-        <v>1875</v>
+        <v>14</v>
       </c>
     </row>
     <row r="686" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A686" s="2" t="s">
-        <v>1876</v>
+        <v>1878</v>
       </c>
       <c r="B686" s="2" t="s">
-        <v>1877</v>
+        <v>16</v>
       </c>
       <c r="C686" s="2" t="s">
-        <v>1878</v>
+        <v>17</v>
       </c>
     </row>
     <row r="687" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14332,175 +14431,175 @@
         <v>1885</v>
       </c>
       <c r="B689" s="2" t="s">
-        <v>1783</v>
+        <v>1886</v>
       </c>
       <c r="C689" s="2" t="s">
-        <v>1784</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="690" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A690" s="2" t="s">
-        <v>1886</v>
+        <v>1888</v>
       </c>
       <c r="B690" s="2" t="s">
-        <v>1786</v>
+        <v>1889</v>
       </c>
       <c r="C690" s="2" t="s">
-        <v>1787</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="691" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A691" s="2" t="s">
-        <v>1887</v>
+        <v>1891</v>
       </c>
       <c r="B691" s="2" t="s">
-        <v>1888</v>
+        <v>1789</v>
       </c>
       <c r="C691" s="2" t="s">
-        <v>1276</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="692" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A692" s="2" t="s">
-        <v>1889</v>
+        <v>1892</v>
       </c>
       <c r="B692" s="2" t="s">
-        <v>1890</v>
+        <v>1792</v>
       </c>
       <c r="C692" s="2" t="s">
-        <v>1891</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="693" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A693" s="2" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="B693" s="2" t="s">
-        <v>1125</v>
+        <v>1894</v>
       </c>
       <c r="C693" s="2" t="s">
-        <v>1126</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="694" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A694" s="2" t="s">
-        <v>1893</v>
+        <v>1895</v>
       </c>
       <c r="B694" s="2" t="s">
-        <v>1894</v>
+        <v>1896</v>
       </c>
       <c r="C694" s="2" t="s">
-        <v>1796</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="695" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A695" s="2" t="s">
-        <v>1895</v>
+        <v>1898</v>
       </c>
       <c r="B695" s="2" t="s">
-        <v>756</v>
+        <v>1131</v>
       </c>
       <c r="C695" s="2" t="s">
-        <v>1798</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="696" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A696" s="2" t="s">
-        <v>1896</v>
+        <v>1899</v>
       </c>
       <c r="B696" s="2" t="s">
-        <v>1897</v>
+        <v>1900</v>
       </c>
       <c r="C696" s="2" t="s">
-        <v>1898</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="697" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A697" s="2" t="s">
-        <v>1899</v>
+        <v>1901</v>
       </c>
       <c r="B697" s="2" t="s">
-        <v>1900</v>
+        <v>762</v>
       </c>
       <c r="C697" s="2" t="s">
-        <v>1891</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="698" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A698" s="2" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
       <c r="B698" s="2" t="s">
-        <v>853</v>
+        <v>1903</v>
       </c>
       <c r="C698" s="2" t="s">
-        <v>1902</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="699" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A699" s="2" t="s">
-        <v>1903</v>
+        <v>1905</v>
       </c>
       <c r="B699" s="2" t="s">
-        <v>865</v>
+        <v>1906</v>
       </c>
       <c r="C699" s="2" t="s">
-        <v>1904</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="700" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A700" s="2" t="s">
-        <v>1905</v>
+        <v>1907</v>
       </c>
       <c r="B700" s="2" t="s">
-        <v>547</v>
+        <v>859</v>
       </c>
       <c r="C700" s="2" t="s">
-        <v>467</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="701" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A701" s="2" t="s">
-        <v>1906</v>
+        <v>1909</v>
       </c>
       <c r="B701" s="2" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="C701" s="2" t="s">
-        <v>870</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="702" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A702" s="2" t="s">
-        <v>1907</v>
+        <v>1911</v>
       </c>
       <c r="B702" s="2" t="s">
-        <v>294</v>
+        <v>553</v>
       </c>
       <c r="C702" s="2" t="s">
-        <v>295</v>
+        <v>473</v>
       </c>
     </row>
     <row r="703" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A703" s="2" t="s">
-        <v>1908</v>
+        <v>1912</v>
       </c>
       <c r="B703" s="2" t="s">
-        <v>1909</v>
+        <v>875</v>
       </c>
       <c r="C703" s="2" t="s">
-        <v>1910</v>
+        <v>876</v>
       </c>
     </row>
     <row r="704" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A704" s="2" t="s">
-        <v>1911</v>
+        <v>1913</v>
       </c>
       <c r="B704" s="2" t="s">
-        <v>1912</v>
+        <v>300</v>
       </c>
       <c r="C704" s="2" t="s">
-        <v>1913</v>
+        <v>301</v>
       </c>
     </row>
     <row r="705" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14519,95 +14618,95 @@
         <v>1917</v>
       </c>
       <c r="B706" s="2" t="s">
-        <v>897</v>
+        <v>1918</v>
       </c>
       <c r="C706" s="2" t="s">
-        <v>898</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="707" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A707" s="2" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="B707" s="2" t="s">
-        <v>865</v>
+        <v>1921</v>
       </c>
       <c r="C707" s="2" t="s">
-        <v>1904</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="708" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A708" s="2" t="s">
-        <v>1919</v>
+        <v>1923</v>
       </c>
       <c r="B708" s="2" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="C708" s="2" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
     </row>
     <row r="709" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A709" s="2" t="s">
-        <v>1920</v>
+        <v>1924</v>
       </c>
       <c r="B709" s="2" t="s">
-        <v>1921</v>
+        <v>871</v>
       </c>
       <c r="C709" s="2" t="s">
-        <v>1922</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="710" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A710" s="2" t="s">
-        <v>1923</v>
+        <v>1925</v>
       </c>
       <c r="B710" s="2" t="s">
         <v>907</v>
       </c>
       <c r="C710" s="2" t="s">
-        <v>1924</v>
+        <v>908</v>
       </c>
     </row>
     <row r="711" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A711" s="2" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="B711" s="2" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="C711" s="2" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="712" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A712" s="2" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="B712" s="2" t="s">
         <v>913</v>
       </c>
       <c r="C712" s="2" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="713" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A713" s="2" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="B713" s="2" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="C713" s="2" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="714" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A714" s="2" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="B714" s="2" t="s">
-        <v>1934</v>
+        <v>919</v>
       </c>
       <c r="C714" s="2" t="s">
         <v>1935</v>
@@ -14629,109 +14728,109 @@
         <v>1939</v>
       </c>
       <c r="B716" s="2" t="s">
-        <v>737</v>
+        <v>1940</v>
       </c>
       <c r="C716" s="2" t="s">
-        <v>738</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="717" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A717" s="2" t="s">
-        <v>1940</v>
+        <v>1942</v>
       </c>
       <c r="B717" s="2" t="s">
-        <v>923</v>
+        <v>1943</v>
       </c>
       <c r="C717" s="2" t="s">
-        <v>924</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="718" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A718" s="2" t="s">
-        <v>1941</v>
+        <v>1945</v>
       </c>
       <c r="B718" s="2" t="s">
-        <v>926</v>
+        <v>743</v>
       </c>
       <c r="C718" s="2" t="s">
-        <v>1942</v>
+        <v>744</v>
       </c>
     </row>
     <row r="719" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A719" s="2" t="s">
-        <v>1943</v>
+        <v>1946</v>
       </c>
       <c r="B719" s="2" t="s">
         <v>929</v>
       </c>
       <c r="C719" s="2" t="s">
-        <v>1944</v>
+        <v>930</v>
       </c>
     </row>
     <row r="720" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A720" s="2" t="s">
-        <v>1945</v>
+        <v>1947</v>
       </c>
       <c r="B720" s="2" t="s">
         <v>932</v>
       </c>
       <c r="C720" s="2" t="s">
-        <v>1946</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="721" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A721" s="2" t="s">
-        <v>1947</v>
+        <v>1949</v>
       </c>
       <c r="B721" s="2" t="s">
-        <v>1948</v>
+        <v>935</v>
       </c>
       <c r="C721" s="2" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="722" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A722" s="2" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="B722" s="2" t="s">
-        <v>1783</v>
+        <v>938</v>
       </c>
       <c r="C722" s="2" t="s">
-        <v>1784</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="723" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A723" s="2" t="s">
-        <v>1951</v>
+        <v>1953</v>
       </c>
       <c r="B723" s="2" t="s">
-        <v>1786</v>
+        <v>1954</v>
       </c>
       <c r="C723" s="2" t="s">
-        <v>1787</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="724" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A724" s="2" t="s">
-        <v>1952</v>
+        <v>1956</v>
       </c>
       <c r="B724" s="2" t="s">
-        <v>1953</v>
+        <v>1789</v>
       </c>
       <c r="C724" s="2" t="s">
-        <v>1954</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="725" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A725" s="2" t="s">
-        <v>1955</v>
+        <v>1957</v>
       </c>
       <c r="B725" s="2" t="s">
-        <v>1956</v>
+        <v>1792</v>
       </c>
       <c r="C725" s="2" t="s">
-        <v>1957</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="726" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14783,32 +14882,32 @@
         <v>1970</v>
       </c>
       <c r="B730" s="2" t="s">
-        <v>445</v>
+        <v>1971</v>
       </c>
       <c r="C730" s="2" t="s">
-        <v>446</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="731" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A731" s="2" t="s">
-        <v>1971</v>
+        <v>1973</v>
       </c>
       <c r="B731" s="2" t="s">
-        <v>1972</v>
+        <v>1974</v>
       </c>
       <c r="C731" s="2" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="732" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A732" s="2" t="s">
-        <v>1974</v>
+        <v>1976</v>
       </c>
       <c r="B732" s="2" t="s">
-        <v>1975</v>
+        <v>451</v>
       </c>
       <c r="C732" s="2" t="s">
-        <v>1976</v>
+        <v>452</v>
       </c>
     </row>
     <row r="733" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14816,62 +14915,62 @@
         <v>1977</v>
       </c>
       <c r="B733" s="2" t="s">
-        <v>457</v>
+        <v>1978</v>
       </c>
       <c r="C733" s="2" t="s">
-        <v>545</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="734" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A734" s="2" t="s">
-        <v>1978</v>
+        <v>1980</v>
       </c>
       <c r="B734" s="2" t="s">
-        <v>463</v>
+        <v>1981</v>
       </c>
       <c r="C734" s="2" t="s">
-        <v>1979</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="735" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A735" s="2" t="s">
-        <v>1980</v>
+        <v>1983</v>
       </c>
       <c r="B735" s="2" t="s">
-        <v>496</v>
+        <v>463</v>
       </c>
       <c r="C735" s="2" t="s">
-        <v>1981</v>
+        <v>551</v>
       </c>
     </row>
     <row r="736" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A736" s="2" t="s">
-        <v>1982</v>
+        <v>1984</v>
       </c>
       <c r="B736" s="2" t="s">
-        <v>499</v>
+        <v>469</v>
       </c>
       <c r="C736" s="2" t="s">
-        <v>1983</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="737" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A737" s="2" t="s">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="B737" s="2" t="s">
-        <v>1985</v>
+        <v>502</v>
       </c>
       <c r="C737" s="2" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="738" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A738" s="2" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="B738" s="2" t="s">
-        <v>1988</v>
+        <v>505</v>
       </c>
       <c r="C738" s="2" t="s">
         <v>1989</v>
@@ -14893,131 +14992,131 @@
         <v>1993</v>
       </c>
       <c r="B740" s="2" t="s">
-        <v>466</v>
+        <v>1994</v>
       </c>
       <c r="C740" s="2" t="s">
-        <v>467</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="741" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A741" s="2" t="s">
-        <v>1994</v>
+        <v>1996</v>
       </c>
       <c r="B741" s="2" t="s">
-        <v>1995</v>
+        <v>1997</v>
       </c>
       <c r="C741" s="2" t="s">
-        <v>1996</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="742" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A742" s="2" t="s">
-        <v>1997</v>
+        <v>1999</v>
       </c>
       <c r="B742" s="2" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="C742" s="2" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
     </row>
     <row r="743" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A743" s="2" t="s">
-        <v>1998</v>
+        <v>2000</v>
       </c>
       <c r="B743" s="2" t="s">
-        <v>484</v>
+        <v>2001</v>
       </c>
       <c r="C743" s="2" t="s">
-        <v>485</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="744" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A744" s="2" t="s">
-        <v>1999</v>
+        <v>2003</v>
       </c>
       <c r="B744" s="2" t="s">
-        <v>2000</v>
+        <v>484</v>
       </c>
       <c r="C744" s="2" t="s">
-        <v>2001</v>
+        <v>485</v>
       </c>
     </row>
     <row r="745" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A745" s="2" t="s">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="B745" s="2" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="C745" s="2" t="s">
-        <v>212</v>
+        <v>491</v>
       </c>
     </row>
     <row r="746" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A746" s="2" t="s">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="B746" s="2" t="s">
-        <v>490</v>
+        <v>2006</v>
       </c>
       <c r="C746" s="2" t="s">
-        <v>2004</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="747" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A747" s="2" t="s">
-        <v>2005</v>
+        <v>2008</v>
       </c>
       <c r="B747" s="2" t="s">
-        <v>532</v>
+        <v>493</v>
       </c>
       <c r="C747" s="2" t="s">
-        <v>2006</v>
+        <v>218</v>
       </c>
     </row>
     <row r="748" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A748" s="2" t="s">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="B748" s="2" t="s">
-        <v>2008</v>
+        <v>496</v>
       </c>
       <c r="C748" s="2" t="s">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="749" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A749" s="2" t="s">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="B749" s="2" t="s">
-        <v>514</v>
+        <v>538</v>
       </c>
       <c r="C749" s="2" t="s">
-        <v>515</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="750" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A750" s="2" t="s">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="B750" s="2" t="s">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="C750" s="2" t="s">
-        <v>2013</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="751" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A751" s="2" t="s">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="B751" s="2" t="s">
-        <v>2015</v>
+        <v>520</v>
       </c>
       <c r="C751" s="2" t="s">
-        <v>2016</v>
+        <v>521</v>
       </c>
     </row>
     <row r="752" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15028,40 +15127,40 @@
         <v>2018</v>
       </c>
       <c r="C752" s="2" t="s">
-        <v>524</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="753" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A753" s="2" t="s">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B753" s="2" t="s">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C753" s="2" t="s">
-        <v>527</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="754" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A754" s="2" t="s">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="B754" s="2" t="s">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="C754" s="2" t="s">
-        <v>2023</v>
+        <v>530</v>
       </c>
     </row>
     <row r="755" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A755" s="2" t="s">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B755" s="2" t="s">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C755" s="2" t="s">
-        <v>2026</v>
+        <v>533</v>
       </c>
     </row>
     <row r="756" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15116,172 +15215,172 @@
         <v>2040</v>
       </c>
       <c r="C760" s="2" t="s">
-        <v>1705</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="761" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A761" s="2" t="s">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="B761" s="2" t="s">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="C761" s="2" t="s">
-        <v>2043</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="762" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A762" s="2" t="s">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="B762" s="2" t="s">
-        <v>2045</v>
+        <v>2046</v>
       </c>
       <c r="C762" s="2" t="s">
-        <v>2046</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="763" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A763" s="2" t="s">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="B763" s="2" t="s">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="C763" s="2" t="s">
-        <v>2049</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="764" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A764" s="2" t="s">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="B764" s="2" t="s">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="C764" s="2" t="s">
-        <v>220</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="765" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A765" s="2" t="s">
-        <v>2052</v>
+        <v>2054</v>
       </c>
       <c r="B765" s="2" t="s">
-        <v>2053</v>
+        <v>2055</v>
       </c>
       <c r="C765" s="2" t="s">
-        <v>2054</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="766" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A766" s="2" t="s">
-        <v>2055</v>
+        <v>2057</v>
       </c>
       <c r="B766" s="2" t="s">
-        <v>2056</v>
+        <v>2058</v>
       </c>
       <c r="C766" s="2" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="767" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A767" s="2" t="s">
-        <v>2058</v>
+        <v>2060</v>
       </c>
       <c r="B767" s="2" t="s">
-        <v>2059</v>
+        <v>2061</v>
       </c>
       <c r="C767" s="2" t="s">
-        <v>2060</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="768" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A768" s="2" t="s">
-        <v>2061</v>
+        <v>2063</v>
       </c>
       <c r="B768" s="2" t="s">
-        <v>2062</v>
+        <v>2064</v>
       </c>
       <c r="C768" s="2" t="s">
-        <v>2063</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="769" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A769" s="2" t="s">
-        <v>2064</v>
+        <v>2066</v>
       </c>
       <c r="B769" s="2" t="s">
-        <v>2065</v>
+        <v>2067</v>
       </c>
       <c r="C769" s="2" t="s">
-        <v>2066</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="770" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A770" s="2" t="s">
-        <v>2067</v>
+        <v>2069</v>
       </c>
       <c r="B770" s="2" t="s">
-        <v>2068</v>
+        <v>2070</v>
       </c>
       <c r="C770" s="2" t="s">
-        <v>2069</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="771" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A771" s="2" t="s">
-        <v>2070</v>
+        <v>2072</v>
       </c>
       <c r="B771" s="2" t="s">
-        <v>2071</v>
+        <v>2073</v>
       </c>
       <c r="C771" s="2" t="s">
-        <v>2072</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="772" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A772" s="2" t="s">
-        <v>2073</v>
+        <v>2074</v>
       </c>
       <c r="B772" s="2" t="s">
-        <v>2074</v>
+        <v>2075</v>
       </c>
       <c r="C772" s="2" t="s">
-        <v>2075</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="773" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A773" s="2" t="s">
-        <v>2076</v>
+        <v>2077</v>
       </c>
       <c r="B773" s="2" t="s">
-        <v>2077</v>
+        <v>2078</v>
       </c>
       <c r="C773" s="2" t="s">
-        <v>2078</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="774" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A774" s="2" t="s">
-        <v>2079</v>
+        <v>2080</v>
       </c>
       <c r="B774" s="2" t="s">
-        <v>2080</v>
+        <v>2081</v>
       </c>
       <c r="C774" s="2" t="s">
-        <v>2081</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="775" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A775" s="2" t="s">
-        <v>2082</v>
+        <v>2083</v>
       </c>
       <c r="B775" s="2" t="s">
-        <v>2083</v>
+        <v>2084</v>
       </c>
       <c r="C775" s="2" t="s">
-        <v>2084</v>
+        <v>226</v>
       </c>
     </row>
     <row r="776" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15289,142 +15388,263 @@
         <v>2085</v>
       </c>
       <c r="B776" s="2" t="s">
-        <v>619</v>
+        <v>2086</v>
       </c>
       <c r="C776" s="2" t="s">
-        <v>620</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="777" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A777" s="2" t="s">
-        <v>2086</v>
+        <v>2088</v>
       </c>
       <c r="B777" s="2" t="s">
-        <v>622</v>
+        <v>2089</v>
       </c>
       <c r="C777" s="2" t="s">
-        <v>623</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="778" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A778" s="2" t="s">
-        <v>2087</v>
+        <v>2091</v>
       </c>
       <c r="B778" s="2" t="s">
-        <v>2088</v>
+        <v>2092</v>
       </c>
       <c r="C778" s="2" t="s">
-        <v>2089</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="779" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A779" s="2" t="s">
-        <v>2090</v>
+        <v>2094</v>
       </c>
       <c r="B779" s="2" t="s">
-        <v>2091</v>
+        <v>2095</v>
       </c>
       <c r="C779" s="2" t="s">
-        <v>2092</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="780" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A780" s="2" t="s">
-        <v>2093</v>
+        <v>2097</v>
       </c>
       <c r="B780" s="2" t="s">
-        <v>2094</v>
+        <v>2098</v>
       </c>
       <c r="C780" s="2" t="s">
-        <v>2095</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="781" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A781" s="2" t="s">
-        <v>2096</v>
+        <v>2100</v>
       </c>
       <c r="B781" s="2" t="s">
-        <v>2097</v>
+        <v>2101</v>
       </c>
       <c r="C781" s="2" t="s">
-        <v>2098</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="782" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A782" s="2" t="s">
-        <v>2099</v>
+        <v>2103</v>
       </c>
       <c r="B782" s="2" t="s">
-        <v>2100</v>
+        <v>2104</v>
       </c>
       <c r="C782" s="2" t="s">
-        <v>2101</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="783" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A783" s="2" t="s">
-        <v>2102</v>
+        <v>2106</v>
       </c>
       <c r="B783" s="2" t="s">
-        <v>2103</v>
+        <v>2107</v>
       </c>
       <c r="C783" s="2" t="s">
-        <v>2104</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="784" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A784" s="2" t="s">
-        <v>2105</v>
+        <v>2109</v>
       </c>
       <c r="B784" s="2" t="s">
-        <v>2106</v>
+        <v>2110</v>
       </c>
       <c r="C784" s="2" t="s">
-        <v>2107</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="785" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A785" s="2" t="s">
-        <v>2108</v>
+        <v>2112</v>
       </c>
       <c r="B785" s="2" t="s">
-        <v>175</v>
+        <v>2113</v>
       </c>
       <c r="C785" s="2" t="s">
-        <v>176</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="786" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A786" s="2" t="s">
-        <v>2109</v>
+        <v>2115</v>
       </c>
       <c r="B786" s="2" t="s">
-        <v>2110</v>
+        <v>2116</v>
       </c>
       <c r="C786" s="2" t="s">
-        <v>2111</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="787" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A787" s="2" t="s">
-        <v>2112</v>
+        <v>2118</v>
       </c>
       <c r="B787" s="2" t="s">
-        <v>2113</v>
+        <v>625</v>
       </c>
       <c r="C787" s="2" t="s">
-        <v>2114</v>
+        <v>626</v>
       </c>
     </row>
     <row r="788" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A788" s="2" t="s">
-        <v>2115</v>
+        <v>2119</v>
       </c>
       <c r="B788" s="2" t="s">
-        <v>2116</v>
+        <v>628</v>
       </c>
       <c r="C788" s="2" t="s">
-        <v>2117</v>
+        <v>629</v>
+      </c>
+    </row>
+    <row r="789" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A789" s="2" t="s">
+        <v>2120</v>
+      </c>
+      <c r="B789" s="2" t="s">
+        <v>2121</v>
+      </c>
+      <c r="C789" s="2" t="s">
+        <v>2122</v>
+      </c>
+    </row>
+    <row r="790" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A790" s="2" t="s">
+        <v>2123</v>
+      </c>
+      <c r="B790" s="2" t="s">
+        <v>2124</v>
+      </c>
+      <c r="C790" s="2" t="s">
+        <v>2125</v>
+      </c>
+    </row>
+    <row r="791" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A791" s="2" t="s">
+        <v>2126</v>
+      </c>
+      <c r="B791" s="2" t="s">
+        <v>2127</v>
+      </c>
+      <c r="C791" s="2" t="s">
+        <v>2128</v>
+      </c>
+    </row>
+    <row r="792" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A792" s="2" t="s">
+        <v>2129</v>
+      </c>
+      <c r="B792" s="2" t="s">
+        <v>2130</v>
+      </c>
+      <c r="C792" s="2" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="793" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A793" s="2" t="s">
+        <v>2132</v>
+      </c>
+      <c r="B793" s="2" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C793" s="2" t="s">
+        <v>2134</v>
+      </c>
+    </row>
+    <row r="794" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A794" s="2" t="s">
+        <v>2135</v>
+      </c>
+      <c r="B794" s="2" t="s">
+        <v>2136</v>
+      </c>
+      <c r="C794" s="2" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="795" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A795" s="2" t="s">
+        <v>2138</v>
+      </c>
+      <c r="B795" s="2" t="s">
+        <v>2139</v>
+      </c>
+      <c r="C795" s="2" t="s">
+        <v>2140</v>
+      </c>
+    </row>
+    <row r="796" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A796" s="2" t="s">
+        <v>2141</v>
+      </c>
+      <c r="B796" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C796" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="797" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A797" s="2" t="s">
+        <v>2142</v>
+      </c>
+      <c r="B797" s="2" t="s">
+        <v>2143</v>
+      </c>
+      <c r="C797" s="2" t="s">
+        <v>2144</v>
+      </c>
+    </row>
+    <row r="798" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A798" s="2" t="s">
+        <v>2145</v>
+      </c>
+      <c r="B798" s="2" t="s">
+        <v>2146</v>
+      </c>
+      <c r="C798" s="2" t="s">
+        <v>2147</v>
+      </c>
+    </row>
+    <row r="799" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A799" s="2" t="s">
+        <v>2148</v>
+      </c>
+      <c r="B799" s="2" t="s">
+        <v>2149</v>
+      </c>
+      <c r="C799" s="2" t="s">
+        <v>2150</v>
       </c>
     </row>
   </sheetData>

--- a/apps/workspace-web/i18n.xlsx
+++ b/apps/workspace-web/i18n.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2397" uniqueCount="2151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2481" uniqueCount="2208">
   <si>
     <t>key</t>
   </si>
@@ -529,19 +529,28 @@
     <t>storeError.uploadScreenshotFailed</t>
   </si>
   <si>
-    <t>上傳預覽圖失敗。</t>
-  </si>
-  <si>
-    <t>Failed to upload preview image.</t>
+    <t>上傳預覽媒體失敗。</t>
+  </si>
+  <si>
+    <t>Failed to upload preview media.</t>
   </si>
   <si>
     <t>storeError.deleteScreenshotFailed</t>
   </si>
   <si>
-    <t>刪除預覽圖失敗。</t>
-  </si>
-  <si>
-    <t>Failed to delete preview image.</t>
+    <t>刪除預覽媒體失敗。</t>
+  </si>
+  <si>
+    <t>Failed to delete preview media.</t>
+  </si>
+  <si>
+    <t>storeError.addExternalVideoFailed</t>
+  </si>
+  <si>
+    <t>加入 YouTube 影片失敗。</t>
+  </si>
+  <si>
+    <t>Failed to add YouTube video.</t>
   </si>
   <si>
     <t>storeError.createVersionFailed</t>
@@ -1640,6 +1649,153 @@
   </si>
   <si>
     <t>Used to generate the cover when no image is set — and as the backdrop while the image loads.</t>
+  </si>
+  <si>
+    <t>upload.mediaLabel</t>
+  </si>
+  <si>
+    <t>預覽媒體</t>
+  </si>
+  <si>
+    <t>Preview media</t>
+  </si>
+  <si>
+    <t>upload.mediaSub</t>
+  </si>
+  <si>
+    <t>選填。商品內頁圖庫展示的圖片、影片或 YouTube 影片，買家可於封面之外切換瀏覽。</t>
+  </si>
+  <si>
+    <t>Optional. Images, videos or YouTube videos shown in the product page gallery, letting buyers browse beyond the cover.</t>
+  </si>
+  <si>
+    <t>upload.mediaAdd</t>
+  </si>
+  <si>
+    <t>上傳圖片 / 影片</t>
+  </si>
+  <si>
+    <t>Upload image / video</t>
+  </si>
+  <si>
+    <t>upload.mediaAddYoutube</t>
+  </si>
+  <si>
+    <t>YouTube 連結</t>
+  </si>
+  <si>
+    <t>YouTube link</t>
+  </si>
+  <si>
+    <t>upload.mediaHint</t>
+  </si>
+  <si>
+    <t>圖片支援 JPG / PNG / GIF / WebP（單檔 5 MB）；影片支援 MP4 / MOV / AVI / WebM（單檔 100 MB）。最多 {max} 項，依加入順序顯示。</t>
+  </si>
+  <si>
+    <t>Images: JPG / PNG / GIF / WebP (5 MB each). Videos: MP4 / MOV / AVI / WebM (100 MB each). Max {max} items, shown in the order added.</t>
+  </si>
+  <si>
+    <t>upload.msgMediaLimit</t>
+  </si>
+  <si>
+    <t>預覽媒體最多 {max} 項，請先移除再新增。</t>
+  </si>
+  <si>
+    <t>Up to {max} preview media items — remove one first.</t>
+  </si>
+  <si>
+    <t>upload.msgMediaType</t>
+  </si>
+  <si>
+    <t>僅支援圖片（JPG / PNG / GIF / WebP）或影片（MP4 / MOV / AVI / WebM）。</t>
+  </si>
+  <si>
+    <t>Only images (JPG / PNG / GIF / WebP) or videos (MP4 / MOV / AVI / WebM) are supported.</t>
+  </si>
+  <si>
+    <t>upload.msgVideoTooLarge</t>
+  </si>
+  <si>
+    <t>影片大小不得超過 100 MB。</t>
+  </si>
+  <si>
+    <t>Videos must be 100 MB or smaller.</t>
+  </si>
+  <si>
+    <t>upload.msgMediaNotReady</t>
+  </si>
+  <si>
+    <t>有預覽媒體上傳失敗，請重試或移除後再送出。</t>
+  </si>
+  <si>
+    <t>Some preview media failed to upload — retry or remove before submitting.</t>
+  </si>
+  <si>
+    <t>upload.msgMediaFailed</t>
+  </si>
+  <si>
+    <t>預覽媒體操作失敗。</t>
+  </si>
+  <si>
+    <t>Preview media action failed.</t>
+  </si>
+  <si>
+    <t>upload.msgYoutubeFailed</t>
+  </si>
+  <si>
+    <t>upload.msgNeedYoutubeUrl</t>
+  </si>
+  <si>
+    <t>請輸入 YouTube 影片網址。</t>
+  </si>
+  <si>
+    <t>Please enter a YouTube video URL.</t>
+  </si>
+  <si>
+    <t>upload.youtubeModalTitle</t>
+  </si>
+  <si>
+    <t>加入 YouTube 連結</t>
+  </si>
+  <si>
+    <t>Add YouTube link</t>
+  </si>
+  <si>
+    <t>upload.youtubeUrlLabel</t>
+  </si>
+  <si>
+    <t>影片網址</t>
+  </si>
+  <si>
+    <t>Video URL</t>
+  </si>
+  <si>
+    <t>upload.youtubeUrlPlaceholder</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=...</t>
+  </si>
+  <si>
+    <t>upload.youtubeHint</t>
+  </si>
+  <si>
+    <t>支援 watch / youtu.be / shorts 連結；影片將以嵌入播放器顯示於商品頁圖庫。</t>
+  </si>
+  <si>
+    <t>Supports watch / youtu.be / shorts links; the video is shown in the product gallery as an embedded player.</t>
+  </si>
+  <si>
+    <t>upload.revMedia</t>
+  </si>
+  <si>
+    <t>upload.revMediaValue</t>
+  </si>
+  <si>
+    <t>{count} 項</t>
+  </si>
+  <si>
+    <t>{count} item(s)</t>
   </si>
   <si>
     <t>upload.confirmTitle</t>
@@ -6114,85 +6270,100 @@
     <t>JPG / PNG / GIF / WebP, up to 5 MB. A 4:3 landscape crop works best.</t>
   </si>
   <si>
-    <t>productEdit.screenshotsTitle</t>
-  </si>
-  <si>
-    <t>預覽圖</t>
-  </si>
-  <si>
-    <t>Preview images</t>
-  </si>
-  <si>
-    <t>productEdit.screenshotsDesc</t>
-  </si>
-  <si>
-    <t>商品頁圖庫展示的截圖 / 預覽畫面，買家可於封面之外瀏覽更多細節。</t>
-  </si>
-  <si>
-    <t>Gallery screenshots shown on the product page, letting buyers browse more detail beyond the cover.</t>
-  </si>
-  <si>
-    <t>productEdit.screenshotAdd</t>
-  </si>
-  <si>
-    <t>新增預覽圖</t>
-  </si>
-  <si>
-    <t>Add image</t>
-  </si>
-  <si>
-    <t>productEdit.screenshotDeleteConfirm</t>
-  </si>
-  <si>
-    <t>確定刪除這張預覽圖？</t>
-  </si>
-  <si>
-    <t>Delete this preview image?</t>
-  </si>
-  <si>
-    <t>productEdit.screenshotsHint</t>
-  </si>
-  <si>
-    <t>支援 JPG / PNG / GIF / WebP，單檔最大 5 MB，最多 {max} 張。依上傳順序顯示於商品頁圖庫。</t>
-  </si>
-  <si>
-    <t>JPG / PNG / GIF / WebP, up to 5 MB each, max {max} images. Shown in the product gallery in upload order.</t>
-  </si>
-  <si>
-    <t>productEdit.msgScreenshotsUploaded</t>
-  </si>
-  <si>
-    <t>已新增 {count} 張預覽圖。</t>
-  </si>
-  <si>
-    <t>Added {count} preview image(s).</t>
-  </si>
-  <si>
-    <t>productEdit.msgScreenshotDeleted</t>
-  </si>
-  <si>
-    <t>已刪除預覽圖。</t>
-  </si>
-  <si>
-    <t>Preview image deleted.</t>
-  </si>
-  <si>
-    <t>productEdit.msgScreenshotFailed</t>
-  </si>
-  <si>
-    <t>預覽圖操作失敗。</t>
-  </si>
-  <si>
-    <t>Preview image action failed.</t>
-  </si>
-  <si>
-    <t>productEdit.msgScreenshotLimit</t>
-  </si>
-  <si>
-    <t>預覽圖最多 {max} 張，請先刪除再新增。</t>
-  </si>
-  <si>
-    <t>Up to {max} preview images — delete one first.</t>
+    <t>productEdit.mediaTitle</t>
+  </si>
+  <si>
+    <t>productEdit.mediaDesc</t>
+  </si>
+  <si>
+    <t>商品頁圖庫展示的圖片、影片與 YouTube 嵌入，買家可於封面之外切換瀏覽更多細節。</t>
+  </si>
+  <si>
+    <t>Images, videos and YouTube embeds shown in the product page gallery, letting buyers browse more detail beyond the cover.</t>
+  </si>
+  <si>
+    <t>productEdit.mediaAdd</t>
+  </si>
+  <si>
+    <t>productEdit.mediaAddYoutube</t>
+  </si>
+  <si>
+    <t>productEdit.mediaDeleteConfirm</t>
+  </si>
+  <si>
+    <t>確定刪除這個預覽媒體？</t>
+  </si>
+  <si>
+    <t>Delete this preview media?</t>
+  </si>
+  <si>
+    <t>productEdit.mediaHint</t>
+  </si>
+  <si>
+    <t>圖片支援 JPG / PNG / GIF / WebP（單檔 5 MB）；影片支援 MP4 / MOV / AVI / WebM（單檔 100 MB）；另可貼 YouTube 連結。最多 {max} 項，依加入順序顯示於商品頁圖庫。</t>
+  </si>
+  <si>
+    <t>Images: JPG / PNG / GIF / WebP (5 MB each). Videos: MP4 / MOV / AVI / WebM (100 MB each). You can also paste a YouTube link. Max {max} items, shown in the gallery in the order added.</t>
+  </si>
+  <si>
+    <t>productEdit.msgMediaUploaded</t>
+  </si>
+  <si>
+    <t>已新增 {count} 項預覽媒體。</t>
+  </si>
+  <si>
+    <t>Added {count} preview media item(s).</t>
+  </si>
+  <si>
+    <t>productEdit.msgMediaDeleted</t>
+  </si>
+  <si>
+    <t>已刪除預覽媒體。</t>
+  </si>
+  <si>
+    <t>Preview media deleted.</t>
+  </si>
+  <si>
+    <t>productEdit.msgMediaFailed</t>
+  </si>
+  <si>
+    <t>productEdit.msgMediaLimit</t>
+  </si>
+  <si>
+    <t>預覽媒體最多 {max} 項，請先刪除再新增。</t>
+  </si>
+  <si>
+    <t>Up to {max} preview media items — delete one first.</t>
+  </si>
+  <si>
+    <t>productEdit.msgMediaType</t>
+  </si>
+  <si>
+    <t>productEdit.msgVideoTooLarge</t>
+  </si>
+  <si>
+    <t>productEdit.youtubeModalTitle</t>
+  </si>
+  <si>
+    <t>productEdit.youtubeUrlLabel</t>
+  </si>
+  <si>
+    <t>productEdit.youtubeUrlPlaceholder</t>
+  </si>
+  <si>
+    <t>productEdit.youtubeHint</t>
+  </si>
+  <si>
+    <t>productEdit.msgNeedYoutubeUrl</t>
+  </si>
+  <si>
+    <t>productEdit.msgYoutubeAdded</t>
+  </si>
+  <si>
+    <t>已加入 YouTube 影片。</t>
+  </si>
+  <si>
+    <t>YouTube video added.</t>
   </si>
   <si>
     <t>productEdit.versionsTitle</t>
@@ -6851,7 +7022,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C799"/>
+  <dimension ref="A1:C827"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -7556,21 +7727,21 @@
         <v>189</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>43</v>
+        <v>190</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>44</v>
+        <v>191</v>
       </c>
     </row>
     <row r="65" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>191</v>
+        <v>43</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>192</v>
+        <v>44</v>
       </c>
     </row>
     <row r="66" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7614,15 +7785,15 @@
         <v>203</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="70" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>206</v>
@@ -7691,18 +7862,18 @@
         <v>223</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
     </row>
     <row r="77" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>226</v>
+        <v>195</v>
       </c>
     </row>
     <row r="78" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8062,21 +8233,21 @@
         <v>323</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>28</v>
+        <v>324</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>29</v>
+        <v>325</v>
       </c>
     </row>
     <row r="111" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>325</v>
+        <v>28</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>326</v>
+        <v>29</v>
       </c>
     </row>
     <row r="112" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8216,21 +8387,21 @@
         <v>363</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>300</v>
+        <v>364</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>301</v>
+        <v>365</v>
       </c>
     </row>
     <row r="125" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>365</v>
+        <v>303</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>366</v>
+        <v>304</v>
       </c>
     </row>
     <row r="126" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8502,21 +8673,21 @@
         <v>439</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>386</v>
+        <v>440</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>387</v>
+        <v>441</v>
       </c>
     </row>
     <row r="151" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>441</v>
+        <v>389</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>442</v>
+        <v>390</v>
       </c>
     </row>
     <row r="152" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8546,21 +8717,21 @@
         <v>449</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>312</v>
+        <v>450</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>313</v>
+        <v>451</v>
       </c>
     </row>
     <row r="155" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>451</v>
+        <v>315</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>452</v>
+        <v>316</v>
       </c>
     </row>
     <row r="156" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8934,238 +9105,238 @@
         <v>553</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>473</v>
+        <v>554</v>
       </c>
     </row>
     <row r="190" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>484</v>
+        <v>556</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>485</v>
+        <v>557</v>
       </c>
     </row>
     <row r="191" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>493</v>
+        <v>559</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>218</v>
+        <v>560</v>
       </c>
     </row>
     <row r="192" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
     </row>
     <row r="193" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
     </row>
     <row r="194" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>520</v>
+        <v>568</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>521</v>
+        <v>569</v>
       </c>
     </row>
     <row r="195" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
     </row>
     <row r="196" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>568</v>
+        <v>575</v>
       </c>
     </row>
     <row r="197" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>570</v>
+        <v>178</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>571</v>
+        <v>179</v>
       </c>
     </row>
     <row r="198" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
     </row>
     <row r="199" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
     </row>
     <row r="200" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>22</v>
+        <v>584</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>23</v>
+        <v>585</v>
       </c>
     </row>
     <row r="201" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>580</v>
+        <v>587</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
     </row>
     <row r="202" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
     </row>
     <row r="203" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>586</v>
+        <v>547</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>587</v>
+        <v>548</v>
       </c>
     </row>
     <row r="204" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
     </row>
     <row r="205" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
     </row>
     <row r="206" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>484</v>
+        <v>599</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
     </row>
     <row r="207" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
     </row>
     <row r="208" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>601</v>
+        <v>476</v>
       </c>
     </row>
     <row r="209" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>603</v>
+        <v>487</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>604</v>
+        <v>488</v>
       </c>
     </row>
     <row r="210" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>606</v>
+        <v>496</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>607</v>
+        <v>221</v>
       </c>
     </row>
     <row r="211" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9195,43 +9366,43 @@
         <v>614</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>615</v>
+        <v>523</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>616</v>
+        <v>524</v>
       </c>
     </row>
     <row r="214" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="C214" s="2" t="s">
         <v>617</v>
-      </c>
-      <c r="B214" s="2" t="s">
-        <v>618</v>
-      </c>
-      <c r="C214" s="2" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="215" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="C215" s="2" t="s">
         <v>620</v>
-      </c>
-      <c r="B215" s="2" t="s">
-        <v>621</v>
-      </c>
-      <c r="C215" s="2" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="216" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="C216" s="2" t="s">
         <v>623</v>
-      </c>
-      <c r="B216" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C216" s="2" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="217" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9261,433 +9432,433 @@
         <v>630</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>631</v>
+        <v>22</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>632</v>
+        <v>23</v>
       </c>
     </row>
     <row r="220" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="C220" s="2" t="s">
         <v>633</v>
-      </c>
-      <c r="B220" s="2" t="s">
-        <v>634</v>
-      </c>
-      <c r="C220" s="2" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="221" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C221" s="2" t="s">
         <v>636</v>
-      </c>
-      <c r="B221" s="2" t="s">
-        <v>637</v>
-      </c>
-      <c r="C221" s="2" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="222" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="C222" s="2" t="s">
         <v>639</v>
-      </c>
-      <c r="B222" s="2" t="s">
-        <v>640</v>
-      </c>
-      <c r="C222" s="2" t="s">
-        <v>641</v>
       </c>
     </row>
     <row r="223" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="C223" s="2" t="s">
         <v>642</v>
-      </c>
-      <c r="B223" s="2" t="s">
-        <v>643</v>
-      </c>
-      <c r="C223" s="2" t="s">
-        <v>644</v>
       </c>
     </row>
     <row r="224" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="C224" s="2" t="s">
         <v>645</v>
-      </c>
-      <c r="B224" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="C224" s="2" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="225" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>649</v>
+        <v>487</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
     </row>
     <row r="226" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
     </row>
     <row r="227" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
     </row>
     <row r="228" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>203</v>
+        <v>655</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>203</v>
+        <v>656</v>
       </c>
     </row>
     <row r="229" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="B229" s="2" t="s">
         <v>658</v>
       </c>
-      <c r="B229" s="2" t="s">
+      <c r="C229" s="2" t="s">
         <v>659</v>
-      </c>
-      <c r="C229" s="2" t="s">
-        <v>660</v>
       </c>
     </row>
     <row r="230" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="B230" s="2" t="s">
         <v>661</v>
       </c>
-      <c r="B230" s="2" t="s">
-        <v>200</v>
-      </c>
       <c r="C230" s="2" t="s">
-        <v>201</v>
+        <v>662</v>
       </c>
     </row>
     <row r="231" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="232" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="233" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="234" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="235" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>675</v>
+        <v>184</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>676</v>
+        <v>185</v>
       </c>
     </row>
     <row r="236" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="B236" s="2" t="s">
         <v>677</v>
       </c>
-      <c r="B236" s="2" t="s">
+      <c r="C236" s="2" t="s">
         <v>678</v>
-      </c>
-      <c r="C236" s="2" t="s">
-        <v>679</v>
       </c>
     </row>
     <row r="237" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="B237" s="2" t="s">
         <v>680</v>
       </c>
-      <c r="B237" s="2" t="s">
+      <c r="C237" s="2" t="s">
         <v>681</v>
-      </c>
-      <c r="C237" s="2" t="s">
-        <v>682</v>
       </c>
     </row>
     <row r="238" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="B238" s="2" t="s">
         <v>683</v>
       </c>
-      <c r="B238" s="2" t="s">
+      <c r="C238" s="2" t="s">
         <v>684</v>
-      </c>
-      <c r="C238" s="2" t="s">
-        <v>685</v>
       </c>
     </row>
     <row r="239" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="B239" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="B239" s="2" t="s">
-        <v>352</v>
-      </c>
       <c r="C239" s="2" t="s">
-        <v>353</v>
+        <v>687</v>
       </c>
     </row>
     <row r="240" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="241" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>355</v>
+        <v>692</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>356</v>
+        <v>693</v>
       </c>
     </row>
     <row r="242" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
     </row>
     <row r="243" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
     </row>
     <row r="244" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
     </row>
     <row r="245" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
     </row>
     <row r="246" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
     </row>
     <row r="247" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>707</v>
+        <v>206</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>708</v>
+        <v>206</v>
       </c>
     </row>
     <row r="248" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="249" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>713</v>
+        <v>203</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>714</v>
+        <v>204</v>
       </c>
     </row>
     <row r="250" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="B250" s="2" t="s">
         <v>715</v>
       </c>
-      <c r="B250" s="2" t="s">
+      <c r="C250" s="2" t="s">
         <v>716</v>
-      </c>
-      <c r="C250" s="2" t="s">
-        <v>717</v>
       </c>
     </row>
     <row r="251" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="B251" s="2" t="s">
         <v>718</v>
       </c>
-      <c r="B251" s="2" t="s">
+      <c r="C251" s="2" t="s">
         <v>719</v>
-      </c>
-      <c r="C251" s="2" t="s">
-        <v>720</v>
       </c>
     </row>
     <row r="252" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="B252" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="B252" s="2" t="s">
+      <c r="C252" s="2" t="s">
         <v>722</v>
-      </c>
-      <c r="C252" s="2" t="s">
-        <v>723</v>
       </c>
     </row>
     <row r="253" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="B253" s="2" t="s">
         <v>724</v>
       </c>
-      <c r="B253" s="2" t="s">
+      <c r="C253" s="2" t="s">
         <v>725</v>
-      </c>
-      <c r="C253" s="2" t="s">
-        <v>726</v>
       </c>
     </row>
     <row r="254" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="B254" s="2" t="s">
         <v>727</v>
       </c>
-      <c r="B254" s="2" t="s">
+      <c r="C254" s="2" t="s">
         <v>728</v>
-      </c>
-      <c r="C254" s="2" t="s">
-        <v>729</v>
       </c>
     </row>
     <row r="255" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="B255" s="2" t="s">
         <v>730</v>
       </c>
-      <c r="B255" s="2" t="s">
+      <c r="C255" s="2" t="s">
         <v>731</v>
-      </c>
-      <c r="C255" s="2" t="s">
-        <v>732</v>
       </c>
     </row>
     <row r="256" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="B256" s="2" t="s">
         <v>733</v>
       </c>
-      <c r="B256" s="2" t="s">
-        <v>352</v>
-      </c>
       <c r="C256" s="2" t="s">
-        <v>353</v>
+        <v>734</v>
       </c>
     </row>
     <row r="257" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>688</v>
+        <v>736</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>689</v>
+        <v>737</v>
       </c>
     </row>
     <row r="258" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="B258" s="2" t="s">
         <v>355</v>
@@ -9698,1520 +9869,1520 @@
     </row>
     <row r="259" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
     </row>
     <row r="260" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>740</v>
+        <v>358</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>741</v>
+        <v>359</v>
       </c>
     </row>
     <row r="261" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="262" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="263" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="264" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
     </row>
     <row r="265" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="266" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>640</v>
+        <v>759</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>641</v>
+        <v>760</v>
       </c>
     </row>
     <row r="267" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
     </row>
     <row r="268" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
     </row>
     <row r="269" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
     </row>
     <row r="270" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
     </row>
     <row r="271" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
     </row>
     <row r="272" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
     </row>
     <row r="273" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
     </row>
     <row r="274" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
     </row>
     <row r="275" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>783</v>
+        <v>355</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>784</v>
+        <v>356</v>
       </c>
     </row>
     <row r="276" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>22</v>
+        <v>740</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>23</v>
+        <v>741</v>
       </c>
     </row>
     <row r="277" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>787</v>
+        <v>358</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>788</v>
+        <v>359</v>
       </c>
     </row>
     <row r="278" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="B278" s="2" t="s">
         <v>789</v>
       </c>
-      <c r="B278" s="2" t="s">
+      <c r="C278" s="2" t="s">
         <v>790</v>
-      </c>
-      <c r="C278" s="2" t="s">
-        <v>791</v>
       </c>
     </row>
     <row r="279" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="B279" s="2" t="s">
         <v>792</v>
       </c>
-      <c r="B279" s="2" t="s">
+      <c r="C279" s="2" t="s">
         <v>793</v>
-      </c>
-      <c r="C279" s="2" t="s">
-        <v>794</v>
       </c>
     </row>
     <row r="280" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="B280" s="2" t="s">
         <v>795</v>
       </c>
-      <c r="B280" s="2" t="s">
+      <c r="C280" s="2" t="s">
         <v>796</v>
-      </c>
-      <c r="C280" s="2" t="s">
-        <v>797</v>
       </c>
     </row>
     <row r="281" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="B281" s="2" t="s">
         <v>798</v>
       </c>
-      <c r="B281" s="2" t="s">
+      <c r="C281" s="2" t="s">
         <v>799</v>
-      </c>
-      <c r="C281" s="2" t="s">
-        <v>800</v>
       </c>
     </row>
     <row r="282" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
+        <v>800</v>
+      </c>
+      <c r="B282" s="2" t="s">
         <v>801</v>
       </c>
-      <c r="B282" s="2" t="s">
+      <c r="C282" s="2" t="s">
         <v>802</v>
-      </c>
-      <c r="C282" s="2" t="s">
-        <v>803</v>
       </c>
     </row>
     <row r="283" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="B283" s="2" t="s">
         <v>804</v>
       </c>
-      <c r="B283" s="2" t="s">
+      <c r="C283" s="2" t="s">
         <v>805</v>
-      </c>
-      <c r="C283" s="2" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="284" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="B284" s="2" t="s">
         <v>807</v>
       </c>
-      <c r="B284" s="2" t="s">
+      <c r="C284" s="2" t="s">
         <v>808</v>
-      </c>
-      <c r="C284" s="2" t="s">
-        <v>809</v>
       </c>
     </row>
     <row r="285" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>811</v>
+        <v>692</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>812</v>
+        <v>693</v>
       </c>
     </row>
     <row r="286" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
     </row>
     <row r="287" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
     </row>
     <row r="288" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
     </row>
     <row r="289" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
     </row>
     <row r="290" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
     </row>
     <row r="291" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
     </row>
     <row r="292" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
     </row>
     <row r="293" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
     </row>
     <row r="294" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
     </row>
     <row r="295" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>841</v>
+        <v>22</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>842</v>
+        <v>23</v>
       </c>
     </row>
     <row r="296" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
-        <v>843</v>
+        <v>838</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>844</v>
+        <v>839</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
     </row>
     <row r="297" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>847</v>
+        <v>842</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>848</v>
+        <v>843</v>
       </c>
     </row>
     <row r="298" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
-        <v>849</v>
+        <v>844</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>851</v>
+        <v>846</v>
       </c>
     </row>
     <row r="299" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>853</v>
+        <v>848</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
     </row>
     <row r="300" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
     </row>
     <row r="301" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
     </row>
     <row r="302" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
-        <v>861</v>
+        <v>856</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
     </row>
     <row r="303" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
-        <v>864</v>
+        <v>859</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
     </row>
     <row r="304" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
     </row>
     <row r="305" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>872</v>
+        <v>867</v>
       </c>
     </row>
     <row r="306" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>553</v>
+        <v>869</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>473</v>
+        <v>870</v>
       </c>
     </row>
     <row r="307" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
     </row>
     <row r="308" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>300</v>
+        <v>875</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>301</v>
+        <v>876</v>
       </c>
     </row>
     <row r="309" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="B309" s="2" t="s">
         <v>878</v>
       </c>
-      <c r="B309" s="2" t="s">
+      <c r="C309" s="2" t="s">
         <v>879</v>
-      </c>
-      <c r="C309" s="2" t="s">
-        <v>880</v>
       </c>
     </row>
     <row r="310" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="B310" s="2" t="s">
         <v>881</v>
       </c>
-      <c r="B310" s="2" t="s">
+      <c r="C310" s="2" t="s">
         <v>882</v>
-      </c>
-      <c r="C310" s="2" t="s">
-        <v>883</v>
       </c>
     </row>
     <row r="311" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="B311" s="2" t="s">
         <v>884</v>
       </c>
-      <c r="B311" s="2" t="s">
+      <c r="C311" s="2" t="s">
         <v>885</v>
-      </c>
-      <c r="C311" s="2" t="s">
-        <v>886</v>
       </c>
     </row>
     <row r="312" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
+        <v>886</v>
+      </c>
+      <c r="B312" s="2" t="s">
         <v>887</v>
       </c>
-      <c r="B312" s="2" t="s">
+      <c r="C312" s="2" t="s">
         <v>888</v>
-      </c>
-      <c r="C312" s="2" t="s">
-        <v>889</v>
       </c>
     </row>
     <row r="313" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="B313" s="2" t="s">
         <v>890</v>
       </c>
-      <c r="B313" s="2" t="s">
+      <c r="C313" s="2" t="s">
         <v>891</v>
-      </c>
-      <c r="C313" s="2" t="s">
-        <v>892</v>
       </c>
     </row>
     <row r="314" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B314" s="2" t="s">
         <v>893</v>
       </c>
-      <c r="B314" s="2" t="s">
+      <c r="C314" s="2" t="s">
         <v>894</v>
-      </c>
-      <c r="C314" s="2" t="s">
-        <v>895</v>
       </c>
     </row>
     <row r="315" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="B315" s="2" t="s">
         <v>896</v>
       </c>
-      <c r="B315" s="2" t="s">
+      <c r="C315" s="2" t="s">
         <v>897</v>
-      </c>
-      <c r="C315" s="2" t="s">
-        <v>898</v>
       </c>
     </row>
     <row r="316" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
+        <v>898</v>
+      </c>
+      <c r="B316" s="2" t="s">
         <v>899</v>
       </c>
-      <c r="B316" s="2" t="s">
+      <c r="C316" s="2" t="s">
         <v>900</v>
-      </c>
-      <c r="C316" s="2" t="s">
-        <v>901</v>
       </c>
     </row>
     <row r="317" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
+        <v>901</v>
+      </c>
+      <c r="B317" s="2" t="s">
         <v>902</v>
       </c>
-      <c r="B317" s="2" t="s">
+      <c r="C317" s="2" t="s">
         <v>903</v>
-      </c>
-      <c r="C317" s="2" t="s">
-        <v>904</v>
       </c>
     </row>
     <row r="318" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
+        <v>904</v>
+      </c>
+      <c r="B318" s="2" t="s">
         <v>905</v>
       </c>
-      <c r="B318" s="2" t="s">
-        <v>871</v>
-      </c>
       <c r="C318" s="2" t="s">
-        <v>872</v>
+        <v>906</v>
       </c>
     </row>
     <row r="319" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
     </row>
     <row r="320" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
     </row>
     <row r="321" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
     </row>
     <row r="322" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
     </row>
     <row r="323" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="324" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
     </row>
     <row r="325" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>925</v>
+        <v>605</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>926</v>
+        <v>476</v>
       </c>
     </row>
     <row r="326" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
+        <v>926</v>
+      </c>
+      <c r="B326" s="2" t="s">
         <v>927</v>
       </c>
-      <c r="B326" s="2" t="s">
-        <v>743</v>
-      </c>
       <c r="C326" s="2" t="s">
-        <v>744</v>
+        <v>928</v>
       </c>
     </row>
     <row r="327" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>929</v>
+        <v>303</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>930</v>
+        <v>304</v>
       </c>
     </row>
     <row r="328" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
+        <v>930</v>
+      </c>
+      <c r="B328" s="2" t="s">
         <v>931</v>
       </c>
-      <c r="B328" s="2" t="s">
+      <c r="C328" s="2" t="s">
         <v>932</v>
-      </c>
-      <c r="C328" s="2" t="s">
-        <v>933</v>
       </c>
     </row>
     <row r="329" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
+        <v>933</v>
+      </c>
+      <c r="B329" s="2" t="s">
         <v>934</v>
       </c>
-      <c r="B329" s="2" t="s">
+      <c r="C329" s="2" t="s">
         <v>935</v>
-      </c>
-      <c r="C329" s="2" t="s">
-        <v>936</v>
       </c>
     </row>
     <row r="330" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
+        <v>936</v>
+      </c>
+      <c r="B330" s="2" t="s">
         <v>937</v>
       </c>
-      <c r="B330" s="2" t="s">
+      <c r="C330" s="2" t="s">
         <v>938</v>
-      </c>
-      <c r="C330" s="2" t="s">
-        <v>939</v>
       </c>
     </row>
     <row r="331" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="B331" s="2" t="s">
         <v>940</v>
       </c>
-      <c r="B331" s="2" t="s">
+      <c r="C331" s="2" t="s">
         <v>941</v>
-      </c>
-      <c r="C331" s="2" t="s">
-        <v>942</v>
       </c>
     </row>
     <row r="332" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="B332" s="2" t="s">
         <v>943</v>
       </c>
-      <c r="B332" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="C332" s="2" t="s">
-        <v>53</v>
+        <v>944</v>
       </c>
     </row>
     <row r="333" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
     </row>
     <row r="334" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
     </row>
     <row r="335" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
     </row>
     <row r="336" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
     </row>
     <row r="337" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>957</v>
+        <v>923</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>958</v>
+        <v>924</v>
       </c>
     </row>
     <row r="338" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
+        <v>958</v>
+      </c>
+      <c r="B338" s="2" t="s">
         <v>959</v>
       </c>
-      <c r="B338" s="2" t="s">
+      <c r="C338" s="2" t="s">
         <v>960</v>
-      </c>
-      <c r="C338" s="2" t="s">
-        <v>961</v>
       </c>
     </row>
     <row r="339" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
+        <v>961</v>
+      </c>
+      <c r="B339" s="2" t="s">
         <v>962</v>
       </c>
-      <c r="B339" s="2" t="s">
+      <c r="C339" s="2" t="s">
         <v>963</v>
-      </c>
-      <c r="C339" s="2" t="s">
-        <v>964</v>
       </c>
     </row>
     <row r="340" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
+        <v>964</v>
+      </c>
+      <c r="B340" s="2" t="s">
         <v>965</v>
       </c>
-      <c r="B340" s="2" t="s">
+      <c r="C340" s="2" t="s">
         <v>966</v>
-      </c>
-      <c r="C340" s="2" t="s">
-        <v>967</v>
       </c>
     </row>
     <row r="341" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
+        <v>967</v>
+      </c>
+      <c r="B341" s="2" t="s">
         <v>968</v>
       </c>
-      <c r="B341" s="2" t="s">
+      <c r="C341" s="2" t="s">
         <v>969</v>
-      </c>
-      <c r="C341" s="2" t="s">
-        <v>970</v>
       </c>
     </row>
     <row r="342" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
+        <v>970</v>
+      </c>
+      <c r="B342" s="2" t="s">
         <v>971</v>
       </c>
-      <c r="B342" s="2" t="s">
+      <c r="C342" s="2" t="s">
         <v>972</v>
-      </c>
-      <c r="C342" s="2" t="s">
-        <v>973</v>
       </c>
     </row>
     <row r="343" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
+        <v>973</v>
+      </c>
+      <c r="B343" s="2" t="s">
         <v>974</v>
       </c>
-      <c r="B343" s="2" t="s">
+      <c r="C343" s="2" t="s">
         <v>975</v>
-      </c>
-      <c r="C343" s="2" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="344" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
+        <v>976</v>
+      </c>
+      <c r="B344" s="2" t="s">
         <v>977</v>
       </c>
-      <c r="B344" s="2" t="s">
+      <c r="C344" s="2" t="s">
         <v>978</v>
-      </c>
-      <c r="C344" s="2" t="s">
-        <v>979</v>
       </c>
     </row>
     <row r="345" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>981</v>
+        <v>795</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>982</v>
+        <v>796</v>
       </c>
     </row>
     <row r="346" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
     </row>
     <row r="347" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
     </row>
     <row r="348" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
     </row>
     <row r="349" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
     </row>
     <row r="350" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
     </row>
     <row r="351" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>434</v>
+        <v>52</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>435</v>
+        <v>53</v>
       </c>
     </row>
     <row r="352" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
+        <v>996</v>
+      </c>
+      <c r="B352" s="2" t="s">
+        <v>997</v>
+      </c>
+      <c r="C352" s="2" t="s">
         <v>998</v>
-      </c>
-      <c r="B352" s="2" t="s">
-        <v>999</v>
-      </c>
-      <c r="C352" s="2" t="s">
-        <v>1000</v>
       </c>
     </row>
     <row r="353" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
+        <v>999</v>
+      </c>
+      <c r="B353" s="2" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C353" s="2" t="s">
         <v>1001</v>
-      </c>
-      <c r="B353" s="2" t="s">
-        <v>1002</v>
-      </c>
-      <c r="C353" s="2" t="s">
-        <v>1003</v>
       </c>
     </row>
     <row r="354" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B354" s="2" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C354" s="2" t="s">
         <v>1004</v>
-      </c>
-      <c r="B354" s="2" t="s">
-        <v>1005</v>
-      </c>
-      <c r="C354" s="2" t="s">
-        <v>1006</v>
       </c>
     </row>
     <row r="355" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B355" s="2" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C355" s="2" t="s">
         <v>1007</v>
-      </c>
-      <c r="B355" s="2" t="s">
-        <v>1008</v>
-      </c>
-      <c r="C355" s="2" t="s">
-        <v>1009</v>
       </c>
     </row>
     <row r="356" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B356" s="2" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C356" s="2" t="s">
         <v>1010</v>
-      </c>
-      <c r="B356" s="2" t="s">
-        <v>1011</v>
-      </c>
-      <c r="C356" s="2" t="s">
-        <v>1012</v>
       </c>
     </row>
     <row r="357" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B357" s="2" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C357" s="2" t="s">
         <v>1013</v>
-      </c>
-      <c r="B357" s="2" t="s">
-        <v>1014</v>
-      </c>
-      <c r="C357" s="2" t="s">
-        <v>1015</v>
       </c>
     </row>
     <row r="358" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B358" s="2" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C358" s="2" t="s">
         <v>1016</v>
-      </c>
-      <c r="B358" s="2" t="s">
-        <v>1017</v>
-      </c>
-      <c r="C358" s="2" t="s">
-        <v>1018</v>
       </c>
     </row>
     <row r="359" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B359" s="2" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C359" s="2" t="s">
         <v>1019</v>
-      </c>
-      <c r="B359" s="2" t="s">
-        <v>1020</v>
-      </c>
-      <c r="C359" s="2" t="s">
-        <v>1021</v>
       </c>
     </row>
     <row r="360" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B360" s="2" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C360" s="2" t="s">
         <v>1022</v>
-      </c>
-      <c r="B360" s="2" t="s">
-        <v>1023</v>
-      </c>
-      <c r="C360" s="2" t="s">
-        <v>1024</v>
       </c>
     </row>
     <row r="361" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B361" s="2" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C361" s="2" t="s">
         <v>1025</v>
-      </c>
-      <c r="B361" s="2" t="s">
-        <v>1026</v>
-      </c>
-      <c r="C361" s="2" t="s">
-        <v>1026</v>
       </c>
     </row>
     <row r="362" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B362" s="2" t="s">
         <v>1027</v>
       </c>
-      <c r="B362" s="2" t="s">
+      <c r="C362" s="2" t="s">
         <v>1028</v>
-      </c>
-      <c r="C362" s="2" t="s">
-        <v>1029</v>
       </c>
     </row>
     <row r="363" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B363" s="2" t="s">
         <v>1030</v>
       </c>
-      <c r="B363" s="2" t="s">
+      <c r="C363" s="2" t="s">
         <v>1031</v>
-      </c>
-      <c r="C363" s="2" t="s">
-        <v>1032</v>
       </c>
     </row>
     <row r="364" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B364" s="2" t="s">
         <v>1033</v>
       </c>
-      <c r="B364" s="2" t="s">
+      <c r="C364" s="2" t="s">
         <v>1034</v>
-      </c>
-      <c r="C364" s="2" t="s">
-        <v>1035</v>
       </c>
     </row>
     <row r="365" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B365" s="2" t="s">
         <v>1036</v>
       </c>
-      <c r="B365" s="2" t="s">
+      <c r="C365" s="2" t="s">
         <v>1037</v>
-      </c>
-      <c r="C365" s="2" t="s">
-        <v>1038</v>
       </c>
     </row>
     <row r="366" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B366" s="2" t="s">
         <v>1039</v>
       </c>
-      <c r="B366" s="2" t="s">
+      <c r="C366" s="2" t="s">
         <v>1040</v>
-      </c>
-      <c r="C366" s="2" t="s">
-        <v>1041</v>
       </c>
     </row>
     <row r="367" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B367" s="2" t="s">
         <v>1042</v>
       </c>
-      <c r="B367" s="2" t="s">
+      <c r="C367" s="2" t="s">
         <v>1043</v>
-      </c>
-      <c r="C367" s="2" t="s">
-        <v>1044</v>
       </c>
     </row>
     <row r="368" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B368" s="2" t="s">
         <v>1045</v>
       </c>
-      <c r="B368" s="2" t="s">
+      <c r="C368" s="2" t="s">
         <v>1046</v>
-      </c>
-      <c r="C368" s="2" t="s">
-        <v>1047</v>
       </c>
     </row>
     <row r="369" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B369" s="2" t="s">
         <v>1048</v>
       </c>
-      <c r="B369" s="2" t="s">
-        <v>1049</v>
-      </c>
       <c r="C369" s="2" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="370" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>1052</v>
+        <v>437</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>1053</v>
+        <v>438</v>
       </c>
     </row>
     <row r="371" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>1056</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="372" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
-        <v>1057</v>
+        <v>1053</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>1058</v>
+        <v>1054</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>1059</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="373" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="374" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
-        <v>1063</v>
+        <v>1059</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>1064</v>
+        <v>1060</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>1065</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="375" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
-        <v>1066</v>
+        <v>1062</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="376" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A376" s="2" t="s">
-        <v>1069</v>
+        <v>1065</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>1070</v>
+        <v>1066</v>
       </c>
       <c r="C376" s="2" t="s">
-        <v>1071</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="377" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A377" s="2" t="s">
-        <v>1072</v>
+        <v>1068</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>1073</v>
+        <v>1069</v>
       </c>
       <c r="C377" s="2" t="s">
-        <v>1074</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="378" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
-        <v>1075</v>
+        <v>1071</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>1076</v>
+        <v>1072</v>
       </c>
       <c r="C378" s="2" t="s">
-        <v>1077</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="379" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A379" s="2" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>1079</v>
+        <v>1075</v>
       </c>
       <c r="C379" s="2" t="s">
-        <v>1080</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="380" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A380" s="2" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>1082</v>
+        <v>1078</v>
       </c>
       <c r="C380" s="2" t="s">
-        <v>1083</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="381" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A381" s="2" t="s">
-        <v>1084</v>
+        <v>1079</v>
       </c>
       <c r="B381" s="2" t="s">
-        <v>1085</v>
+        <v>1080</v>
       </c>
       <c r="C381" s="2" t="s">
-        <v>1086</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="382" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A382" s="2" t="s">
-        <v>1087</v>
+        <v>1082</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>1088</v>
+        <v>1083</v>
       </c>
       <c r="C382" s="2" t="s">
-        <v>1089</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="383" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A383" s="2" t="s">
-        <v>1090</v>
+        <v>1085</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>1091</v>
+        <v>1086</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>1092</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="384" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A384" s="2" t="s">
-        <v>1093</v>
+        <v>1088</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>1094</v>
+        <v>1089</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>1095</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="385" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A385" s="2" t="s">
-        <v>1096</v>
+        <v>1091</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>1097</v>
+        <v>1092</v>
       </c>
       <c r="C385" s="2" t="s">
-        <v>1098</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="386" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A386" s="2" t="s">
-        <v>1099</v>
+        <v>1094</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>1100</v>
+        <v>1095</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>1101</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="387" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A387" s="2" t="s">
-        <v>1102</v>
+        <v>1097</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
       <c r="C387" s="2" t="s">
-        <v>1104</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="388" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A388" s="2" t="s">
-        <v>1105</v>
+        <v>1100</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>1106</v>
+        <v>1101</v>
       </c>
       <c r="C388" s="2" t="s">
-        <v>1107</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="389" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A389" s="2" t="s">
-        <v>1108</v>
+        <v>1103</v>
       </c>
       <c r="B389" s="2" t="s">
-        <v>1109</v>
+        <v>1104</v>
       </c>
       <c r="C389" s="2" t="s">
-        <v>1110</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="390" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A390" s="2" t="s">
-        <v>1111</v>
+        <v>1106</v>
       </c>
       <c r="B390" s="2" t="s">
-        <v>1112</v>
+        <v>1107</v>
       </c>
       <c r="C390" s="2" t="s">
-        <v>1113</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="391" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A391" s="2" t="s">
-        <v>1114</v>
+        <v>1109</v>
       </c>
       <c r="B391" s="2" t="s">
-        <v>1115</v>
+        <v>1110</v>
       </c>
       <c r="C391" s="2" t="s">
-        <v>1116</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="392" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A392" s="2" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
       <c r="B392" s="2" t="s">
-        <v>312</v>
+        <v>1113</v>
       </c>
       <c r="C392" s="2" t="s">
-        <v>313</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="393" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A393" s="2" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="B393" s="2" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
       <c r="C393" s="2" t="s">
-        <v>660</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="394" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A394" s="2" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B394" s="2" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C394" s="2" t="s">
         <v>1120</v>
-      </c>
-      <c r="B394" s="2" t="s">
-        <v>1121</v>
-      </c>
-      <c r="C394" s="2" t="s">
-        <v>1122</v>
       </c>
     </row>
     <row r="395" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A395" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B395" s="2" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C395" s="2" t="s">
         <v>1123</v>
-      </c>
-      <c r="B395" s="2" t="s">
-        <v>1124</v>
-      </c>
-      <c r="C395" s="2" t="s">
-        <v>1125</v>
       </c>
     </row>
     <row r="396" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A396" s="2" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B396" s="2" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C396" s="2" t="s">
         <v>1126</v>
-      </c>
-      <c r="B396" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="C396" s="2" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="397" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11307,120 +11478,120 @@
         <v>1151</v>
       </c>
       <c r="B405" s="2" t="s">
-        <v>294</v>
+        <v>1152</v>
       </c>
       <c r="C405" s="2" t="s">
-        <v>295</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="406" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A406" s="2" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="C406" s="2" t="s">
-        <v>1138</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="407" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A407" s="2" t="s">
-        <v>1154</v>
+        <v>1157</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>1155</v>
+        <v>1158</v>
       </c>
       <c r="C407" s="2" t="s">
-        <v>1156</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="408" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A408" s="2" t="s">
-        <v>1157</v>
+        <v>1160</v>
       </c>
       <c r="B408" s="2" t="s">
-        <v>1158</v>
+        <v>1161</v>
       </c>
       <c r="C408" s="2" t="s">
-        <v>1159</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="409" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A409" s="2" t="s">
-        <v>1160</v>
+        <v>1163</v>
       </c>
       <c r="B409" s="2" t="s">
-        <v>1161</v>
+        <v>1164</v>
       </c>
       <c r="C409" s="2" t="s">
-        <v>1162</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="410" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A410" s="2" t="s">
-        <v>1163</v>
+        <v>1166</v>
       </c>
       <c r="B410" s="2" t="s">
-        <v>1164</v>
+        <v>1167</v>
       </c>
       <c r="C410" s="2" t="s">
-        <v>1165</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="411" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A411" s="2" t="s">
-        <v>1166</v>
+        <v>1169</v>
       </c>
       <c r="B411" s="2" t="s">
-        <v>1167</v>
+        <v>315</v>
       </c>
       <c r="C411" s="2" t="s">
-        <v>1168</v>
+        <v>316</v>
       </c>
     </row>
     <row r="412" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A412" s="2" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="B412" s="2" t="s">
-        <v>312</v>
+        <v>1171</v>
       </c>
       <c r="C412" s="2" t="s">
-        <v>313</v>
+        <v>712</v>
       </c>
     </row>
     <row r="413" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A413" s="2" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="B413" s="2" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="C413" s="2" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="414" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A414" s="2" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="B414" s="2" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="C414" s="2" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="415" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A415" s="2" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>1177</v>
+        <v>203</v>
       </c>
       <c r="C415" s="2" t="s">
-        <v>1178</v>
+        <v>204</v>
       </c>
     </row>
     <row r="416" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11516,351 +11687,351 @@
         <v>1203</v>
       </c>
       <c r="B424" s="2" t="s">
-        <v>1204</v>
+        <v>297</v>
       </c>
       <c r="C424" s="2" t="s">
-        <v>1205</v>
+        <v>298</v>
       </c>
     </row>
     <row r="425" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A425" s="2" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="B425" s="2" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="C425" s="2" t="s">
-        <v>1208</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="426" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A426" s="2" t="s">
-        <v>1209</v>
+        <v>1206</v>
       </c>
       <c r="B426" s="2" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="C426" s="2" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="427" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A427" s="2" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>1213</v>
+        <v>1210</v>
       </c>
       <c r="C427" s="2" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="428" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A428" s="2" t="s">
-        <v>1215</v>
+        <v>1212</v>
       </c>
       <c r="B428" s="2" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="C428" s="2" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="429" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A429" s="2" t="s">
-        <v>1218</v>
+        <v>1215</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>368</v>
+        <v>1216</v>
       </c>
       <c r="C429" s="2" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="430" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A430" s="2" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B430" s="2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C430" s="2" t="s">
         <v>1220</v>
-      </c>
-      <c r="B430" s="2" t="s">
-        <v>1221</v>
-      </c>
-      <c r="C430" s="2" t="s">
-        <v>1222</v>
       </c>
     </row>
     <row r="431" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A431" s="2" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="B431" s="2" t="s">
-        <v>1224</v>
+        <v>315</v>
       </c>
       <c r="C431" s="2" t="s">
-        <v>1225</v>
+        <v>316</v>
       </c>
     </row>
     <row r="432" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A432" s="2" t="s">
-        <v>1226</v>
+        <v>1222</v>
       </c>
       <c r="B432" s="2" t="s">
-        <v>1227</v>
+        <v>1223</v>
       </c>
       <c r="C432" s="2" t="s">
-        <v>1228</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="433" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A433" s="2" t="s">
-        <v>1229</v>
+        <v>1225</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>1230</v>
+        <v>1226</v>
       </c>
       <c r="C433" s="2" t="s">
-        <v>1231</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="434" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A434" s="2" t="s">
-        <v>1232</v>
+        <v>1228</v>
       </c>
       <c r="B434" s="2" t="s">
-        <v>1233</v>
+        <v>1229</v>
       </c>
       <c r="C434" s="2" t="s">
-        <v>1234</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="435" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A435" s="2" t="s">
-        <v>1235</v>
+        <v>1231</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>1236</v>
+        <v>1232</v>
       </c>
       <c r="C435" s="2" t="s">
-        <v>1237</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="436" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A436" s="2" t="s">
-        <v>1238</v>
+        <v>1234</v>
       </c>
       <c r="B436" s="2" t="s">
-        <v>1239</v>
+        <v>1235</v>
       </c>
       <c r="C436" s="2" t="s">
-        <v>1240</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="437" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A437" s="2" t="s">
-        <v>1241</v>
+        <v>1237</v>
       </c>
       <c r="B437" s="2" t="s">
-        <v>1242</v>
+        <v>1238</v>
       </c>
       <c r="C437" s="2" t="s">
-        <v>1243</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="438" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A438" s="2" t="s">
-        <v>1244</v>
+        <v>1240</v>
       </c>
       <c r="B438" s="2" t="s">
-        <v>1245</v>
+        <v>1241</v>
       </c>
       <c r="C438" s="2" t="s">
-        <v>1246</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="439" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A439" s="2" t="s">
-        <v>1247</v>
+        <v>1243</v>
       </c>
       <c r="B439" s="2" t="s">
-        <v>1248</v>
+        <v>1244</v>
       </c>
       <c r="C439" s="2" t="s">
-        <v>1249</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="440" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A440" s="2" t="s">
-        <v>1250</v>
+        <v>1246</v>
       </c>
       <c r="B440" s="2" t="s">
-        <v>1251</v>
+        <v>1247</v>
       </c>
       <c r="C440" s="2" t="s">
-        <v>1252</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="441" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A441" s="2" t="s">
-        <v>1253</v>
+        <v>1249</v>
       </c>
       <c r="B441" s="2" t="s">
-        <v>1254</v>
+        <v>1250</v>
       </c>
       <c r="C441" s="2" t="s">
-        <v>1255</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="442" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A442" s="2" t="s">
-        <v>1256</v>
+        <v>1252</v>
       </c>
       <c r="B442" s="2" t="s">
-        <v>1257</v>
+        <v>1253</v>
       </c>
       <c r="C442" s="2" t="s">
-        <v>1258</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="443" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A443" s="2" t="s">
-        <v>1259</v>
+        <v>1255</v>
       </c>
       <c r="B443" s="2" t="s">
-        <v>1260</v>
+        <v>1256</v>
       </c>
       <c r="C443" s="2" t="s">
-        <v>1261</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="444" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A444" s="2" t="s">
-        <v>1262</v>
+        <v>1258</v>
       </c>
       <c r="B444" s="2" t="s">
-        <v>1263</v>
+        <v>1259</v>
       </c>
       <c r="C444" s="2" t="s">
-        <v>1264</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="445" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A445" s="2" t="s">
-        <v>1265</v>
+        <v>1261</v>
       </c>
       <c r="B445" s="2" t="s">
-        <v>1266</v>
+        <v>1262</v>
       </c>
       <c r="C445" s="2" t="s">
-        <v>1267</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="446" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A446" s="2" t="s">
-        <v>1268</v>
+        <v>1264</v>
       </c>
       <c r="B446" s="2" t="s">
-        <v>1269</v>
+        <v>1265</v>
       </c>
       <c r="C446" s="2" t="s">
-        <v>1270</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="447" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A447" s="2" t="s">
-        <v>1271</v>
+        <v>1267</v>
       </c>
       <c r="B447" s="2" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="C447" s="2" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="448" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A448" s="2" t="s">
-        <v>1274</v>
+        <v>1270</v>
       </c>
       <c r="B448" s="2" t="s">
-        <v>1275</v>
+        <v>371</v>
       </c>
       <c r="C448" s="2" t="s">
-        <v>1276</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="449" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A449" s="2" t="s">
-        <v>1277</v>
+        <v>1272</v>
       </c>
       <c r="B449" s="2" t="s">
-        <v>1278</v>
+        <v>1273</v>
       </c>
       <c r="C449" s="2" t="s">
-        <v>1279</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="450" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A450" s="2" t="s">
-        <v>1280</v>
+        <v>1275</v>
       </c>
       <c r="B450" s="2" t="s">
-        <v>1281</v>
+        <v>1276</v>
       </c>
       <c r="C450" s="2" t="s">
-        <v>1282</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="451" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A451" s="2" t="s">
-        <v>1283</v>
+        <v>1278</v>
       </c>
       <c r="B451" s="2" t="s">
-        <v>999</v>
+        <v>1279</v>
       </c>
       <c r="C451" s="2" t="s">
-        <v>1000</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="452" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A452" s="2" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="B452" s="2" t="s">
-        <v>1285</v>
+        <v>1282</v>
       </c>
       <c r="C452" s="2" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="453" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A453" s="2" t="s">
-        <v>1287</v>
+        <v>1284</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>1288</v>
+        <v>1285</v>
       </c>
       <c r="C453" s="2" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="454" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A454" s="2" t="s">
-        <v>1290</v>
+        <v>1287</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>1291</v>
+        <v>1288</v>
       </c>
       <c r="C454" s="2" t="s">
-        <v>192</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="455" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A455" s="2" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B455" s="2" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C455" s="2" t="s">
         <v>1292</v>
-      </c>
-      <c r="B455" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="C455" s="2" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="456" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11879,340 +12050,340 @@
         <v>1296</v>
       </c>
       <c r="B457" s="2" t="s">
-        <v>200</v>
+        <v>1297</v>
       </c>
       <c r="C457" s="2" t="s">
-        <v>201</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="458" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A458" s="2" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="B458" s="2" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="C458" s="2" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="459" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A459" s="2" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="B459" s="2" t="s">
-        <v>300</v>
+        <v>1303</v>
       </c>
       <c r="C459" s="2" t="s">
-        <v>301</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="460" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A460" s="2" t="s">
-        <v>1301</v>
+        <v>1305</v>
       </c>
       <c r="B460" s="2" t="s">
-        <v>1302</v>
+        <v>1306</v>
       </c>
       <c r="C460" s="2" t="s">
-        <v>1303</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="461" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A461" s="2" t="s">
-        <v>1304</v>
+        <v>1308</v>
       </c>
       <c r="B461" s="2" t="s">
-        <v>1112</v>
+        <v>1309</v>
       </c>
       <c r="C461" s="2" t="s">
-        <v>1305</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="462" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A462" s="2" t="s">
-        <v>1306</v>
+        <v>1311</v>
       </c>
       <c r="B462" s="2" t="s">
-        <v>321</v>
+        <v>1312</v>
       </c>
       <c r="C462" s="2" t="s">
-        <v>322</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="463" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A463" s="2" t="s">
-        <v>1307</v>
+        <v>1314</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>315</v>
+        <v>1315</v>
       </c>
       <c r="C463" s="2" t="s">
-        <v>316</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="464" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A464" s="2" t="s">
-        <v>1308</v>
+        <v>1317</v>
       </c>
       <c r="B464" s="2" t="s">
-        <v>1309</v>
+        <v>1318</v>
       </c>
       <c r="C464" s="2" t="s">
-        <v>1310</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="465" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A465" s="2" t="s">
-        <v>1311</v>
+        <v>1320</v>
       </c>
       <c r="B465" s="2" t="s">
-        <v>1312</v>
+        <v>1321</v>
       </c>
       <c r="C465" s="2" t="s">
-        <v>1313</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="466" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A466" s="2" t="s">
-        <v>1314</v>
+        <v>1323</v>
       </c>
       <c r="B466" s="2" t="s">
-        <v>331</v>
+        <v>1324</v>
       </c>
       <c r="C466" s="2" t="s">
-        <v>332</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="467" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A467" s="2" t="s">
-        <v>1315</v>
+        <v>1326</v>
       </c>
       <c r="B467" s="2" t="s">
-        <v>1316</v>
+        <v>1327</v>
       </c>
       <c r="C467" s="2" t="s">
-        <v>1317</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="468" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A468" s="2" t="s">
-        <v>1318</v>
+        <v>1329</v>
       </c>
       <c r="B468" s="2" t="s">
-        <v>337</v>
+        <v>1330</v>
       </c>
       <c r="C468" s="2" t="s">
-        <v>338</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="469" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A469" s="2" t="s">
-        <v>1319</v>
+        <v>1332</v>
       </c>
       <c r="B469" s="2" t="s">
-        <v>1320</v>
+        <v>1333</v>
       </c>
       <c r="C469" s="2" t="s">
-        <v>1321</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="470" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A470" s="2" t="s">
-        <v>1322</v>
+        <v>1335</v>
       </c>
       <c r="B470" s="2" t="s">
-        <v>1323</v>
+        <v>1051</v>
       </c>
       <c r="C470" s="2" t="s">
-        <v>1323</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="471" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A471" s="2" t="s">
-        <v>1324</v>
+        <v>1336</v>
       </c>
       <c r="B471" s="2" t="s">
-        <v>1325</v>
+        <v>1337</v>
       </c>
       <c r="C471" s="2" t="s">
-        <v>1325</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="472" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A472" s="2" t="s">
-        <v>1326</v>
+        <v>1339</v>
       </c>
       <c r="B472" s="2" t="s">
-        <v>1327</v>
+        <v>1340</v>
       </c>
       <c r="C472" s="2" t="s">
-        <v>1328</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="473" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A473" s="2" t="s">
-        <v>1329</v>
+        <v>1342</v>
       </c>
       <c r="B473" s="2" t="s">
-        <v>1327</v>
+        <v>1343</v>
       </c>
       <c r="C473" s="2" t="s">
-        <v>1328</v>
+        <v>195</v>
       </c>
     </row>
     <row r="474" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A474" s="2" t="s">
-        <v>1330</v>
+        <v>1344</v>
       </c>
       <c r="B474" s="2" t="s">
-        <v>1331</v>
+        <v>197</v>
       </c>
       <c r="C474" s="2" t="s">
-        <v>1332</v>
+        <v>198</v>
       </c>
     </row>
     <row r="475" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A475" s="2" t="s">
-        <v>1333</v>
+        <v>1345</v>
       </c>
       <c r="B475" s="2" t="s">
-        <v>1334</v>
+        <v>1346</v>
       </c>
       <c r="C475" s="2" t="s">
-        <v>1335</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="476" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A476" s="2" t="s">
-        <v>1336</v>
+        <v>1348</v>
       </c>
       <c r="B476" s="2" t="s">
-        <v>1337</v>
+        <v>203</v>
       </c>
       <c r="C476" s="2" t="s">
-        <v>1338</v>
+        <v>204</v>
       </c>
     </row>
     <row r="477" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A477" s="2" t="s">
-        <v>1339</v>
+        <v>1349</v>
       </c>
       <c r="B477" s="2" t="s">
-        <v>1340</v>
+        <v>1350</v>
       </c>
       <c r="C477" s="2" t="s">
-        <v>1341</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="478" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A478" s="2" t="s">
-        <v>1342</v>
+        <v>1352</v>
       </c>
       <c r="B478" s="2" t="s">
-        <v>1343</v>
+        <v>303</v>
       </c>
       <c r="C478" s="2" t="s">
-        <v>1344</v>
+        <v>304</v>
       </c>
     </row>
     <row r="479" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A479" s="2" t="s">
-        <v>1345</v>
+        <v>1353</v>
       </c>
       <c r="B479" s="2" t="s">
-        <v>1346</v>
+        <v>1354</v>
       </c>
       <c r="C479" s="2" t="s">
-        <v>1347</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="480" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A480" s="2" t="s">
-        <v>1348</v>
+        <v>1356</v>
       </c>
       <c r="B480" s="2" t="s">
-        <v>1349</v>
+        <v>1164</v>
       </c>
       <c r="C480" s="2" t="s">
-        <v>1350</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="481" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A481" s="2" t="s">
-        <v>1351</v>
+        <v>1358</v>
       </c>
       <c r="B481" s="2" t="s">
-        <v>1352</v>
+        <v>324</v>
       </c>
       <c r="C481" s="2" t="s">
-        <v>1353</v>
+        <v>325</v>
       </c>
     </row>
     <row r="482" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A482" s="2" t="s">
-        <v>1354</v>
+        <v>1359</v>
       </c>
       <c r="B482" s="2" t="s">
-        <v>1355</v>
+        <v>318</v>
       </c>
       <c r="C482" s="2" t="s">
-        <v>1356</v>
+        <v>319</v>
       </c>
     </row>
     <row r="483" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A483" s="2" t="s">
-        <v>1357</v>
+        <v>1360</v>
       </c>
       <c r="B483" s="2" t="s">
-        <v>1358</v>
+        <v>1361</v>
       </c>
       <c r="C483" s="2" t="s">
-        <v>1359</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="484" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A484" s="2" t="s">
-        <v>1360</v>
+        <v>1363</v>
       </c>
       <c r="B484" s="2" t="s">
-        <v>1361</v>
+        <v>1364</v>
       </c>
       <c r="C484" s="2" t="s">
-        <v>1362</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="485" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A485" s="2" t="s">
-        <v>1363</v>
+        <v>1366</v>
       </c>
       <c r="B485" s="2" t="s">
-        <v>1364</v>
+        <v>334</v>
       </c>
       <c r="C485" s="2" t="s">
-        <v>1365</v>
+        <v>335</v>
       </c>
     </row>
     <row r="486" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A486" s="2" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="B486" s="2" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="C486" s="2" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="487" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A487" s="2" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>1370</v>
+        <v>340</v>
       </c>
       <c r="C487" s="2" t="s">
-        <v>1347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="488" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12234,194 +12405,194 @@
         <v>1375</v>
       </c>
       <c r="C489" s="2" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="490" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A490" s="2" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B490" s="2" t="s">
         <v>1377</v>
       </c>
-      <c r="B490" s="2" t="s">
-        <v>1378</v>
-      </c>
       <c r="C490" s="2" t="s">
-        <v>1353</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="491" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A491" s="2" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B491" s="2" t="s">
         <v>1379</v>
       </c>
-      <c r="B491" s="2" t="s">
+      <c r="C491" s="2" t="s">
         <v>1380</v>
-      </c>
-      <c r="C491" s="2" t="s">
-        <v>1381</v>
       </c>
     </row>
     <row r="492" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A492" s="2" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="B492" s="2" t="s">
-        <v>1383</v>
+        <v>1379</v>
       </c>
       <c r="C492" s="2" t="s">
-        <v>1384</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="493" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A493" s="2" t="s">
-        <v>1385</v>
+        <v>1382</v>
       </c>
       <c r="B493" s="2" t="s">
-        <v>1386</v>
+        <v>1383</v>
       </c>
       <c r="C493" s="2" t="s">
-        <v>1387</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="494" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A494" s="2" t="s">
-        <v>1388</v>
+        <v>1385</v>
       </c>
       <c r="B494" s="2" t="s">
-        <v>1240</v>
+        <v>1386</v>
       </c>
       <c r="C494" s="2" t="s">
-        <v>1240</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="495" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A495" s="2" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B495" s="2" t="s">
         <v>1389</v>
       </c>
-      <c r="B495" s="2" t="s">
+      <c r="C495" s="2" t="s">
         <v>1390</v>
-      </c>
-      <c r="C495" s="2" t="s">
-        <v>1391</v>
       </c>
     </row>
     <row r="496" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A496" s="2" t="s">
+        <v>1391</v>
+      </c>
+      <c r="B496" s="2" t="s">
         <v>1392</v>
       </c>
-      <c r="B496" s="2" t="s">
+      <c r="C496" s="2" t="s">
         <v>1393</v>
-      </c>
-      <c r="C496" s="2" t="s">
-        <v>1394</v>
       </c>
     </row>
     <row r="497" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A497" s="2" t="s">
+        <v>1394</v>
+      </c>
+      <c r="B497" s="2" t="s">
         <v>1395</v>
       </c>
-      <c r="B497" s="2" t="s">
+      <c r="C497" s="2" t="s">
         <v>1396</v>
-      </c>
-      <c r="C497" s="2" t="s">
-        <v>1397</v>
       </c>
     </row>
     <row r="498" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A498" s="2" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B498" s="2" t="s">
         <v>1398</v>
       </c>
-      <c r="B498" s="2" t="s">
+      <c r="C498" s="2" t="s">
         <v>1399</v>
-      </c>
-      <c r="C498" s="2" t="s">
-        <v>1400</v>
       </c>
     </row>
     <row r="499" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A499" s="2" t="s">
+        <v>1400</v>
+      </c>
+      <c r="B499" s="2" t="s">
         <v>1401</v>
       </c>
-      <c r="B499" s="2" t="s">
+      <c r="C499" s="2" t="s">
         <v>1402</v>
-      </c>
-      <c r="C499" s="2" t="s">
-        <v>1403</v>
       </c>
     </row>
     <row r="500" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A500" s="2" t="s">
+        <v>1403</v>
+      </c>
+      <c r="B500" s="2" t="s">
         <v>1404</v>
       </c>
-      <c r="B500" s="2" t="s">
+      <c r="C500" s="2" t="s">
         <v>1405</v>
-      </c>
-      <c r="C500" s="2" t="s">
-        <v>1406</v>
       </c>
     </row>
     <row r="501" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A501" s="2" t="s">
+        <v>1406</v>
+      </c>
+      <c r="B501" s="2" t="s">
         <v>1407</v>
       </c>
-      <c r="B501" s="2" t="s">
+      <c r="C501" s="2" t="s">
         <v>1408</v>
-      </c>
-      <c r="C501" s="2" t="s">
-        <v>1409</v>
       </c>
     </row>
     <row r="502" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A502" s="2" t="s">
+        <v>1409</v>
+      </c>
+      <c r="B502" s="2" t="s">
         <v>1410</v>
       </c>
-      <c r="B502" s="2" t="s">
+      <c r="C502" s="2" t="s">
         <v>1411</v>
-      </c>
-      <c r="C502" s="2" t="s">
-        <v>1412</v>
       </c>
     </row>
     <row r="503" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A503" s="2" t="s">
+        <v>1412</v>
+      </c>
+      <c r="B503" s="2" t="s">
         <v>1413</v>
       </c>
-      <c r="B503" s="2" t="s">
-        <v>1275</v>
-      </c>
       <c r="C503" s="2" t="s">
-        <v>1276</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="504" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A504" s="2" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="B504" s="2" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="C504" s="2" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="505" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A505" s="2" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="B505" s="2" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="C505" s="2" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="506" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A506" s="2" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="B506" s="2" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="C506" s="2" t="s">
-        <v>1422</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="507" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12454,18 +12625,18 @@
         <v>1430</v>
       </c>
       <c r="C509" s="2" t="s">
-        <v>1431</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="510" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A510" s="2" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B510" s="2" t="s">
         <v>1432</v>
       </c>
-      <c r="B510" s="2" t="s">
+      <c r="C510" s="2" t="s">
         <v>1433</v>
-      </c>
-      <c r="C510" s="2" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="511" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12473,274 +12644,274 @@
         <v>1434</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>194</v>
+        <v>1435</v>
       </c>
       <c r="C511" s="2" t="s">
-        <v>195</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="512" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A512" s="2" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="B512" s="2" t="s">
-        <v>197</v>
+        <v>1438</v>
       </c>
       <c r="C512" s="2" t="s">
-        <v>198</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="513" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A513" s="2" t="s">
-        <v>1436</v>
+        <v>1440</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>646</v>
+        <v>1292</v>
       </c>
       <c r="C513" s="2" t="s">
-        <v>647</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="514" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A514" s="2" t="s">
-        <v>1437</v>
+        <v>1441</v>
       </c>
       <c r="B514" s="2" t="s">
-        <v>1438</v>
+        <v>1442</v>
       </c>
       <c r="C514" s="2" t="s">
-        <v>1439</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="515" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A515" s="2" t="s">
-        <v>1440</v>
+        <v>1444</v>
       </c>
       <c r="B515" s="2" t="s">
-        <v>1441</v>
+        <v>1445</v>
       </c>
       <c r="C515" s="2" t="s">
-        <v>1442</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="516" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A516" s="2" t="s">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="B516" s="2" t="s">
-        <v>1444</v>
+        <v>1448</v>
       </c>
       <c r="C516" s="2" t="s">
-        <v>1445</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="517" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A517" s="2" t="s">
-        <v>1446</v>
+        <v>1450</v>
       </c>
       <c r="B517" s="2" t="s">
-        <v>1447</v>
+        <v>1451</v>
       </c>
       <c r="C517" s="2" t="s">
-        <v>1448</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="518" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A518" s="2" t="s">
-        <v>1449</v>
+        <v>1453</v>
       </c>
       <c r="B518" s="2" t="s">
-        <v>1450</v>
+        <v>1454</v>
       </c>
       <c r="C518" s="2" t="s">
-        <v>1451</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="519" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A519" s="2" t="s">
-        <v>1452</v>
+        <v>1456</v>
       </c>
       <c r="B519" s="2" t="s">
-        <v>1453</v>
+        <v>1457</v>
       </c>
       <c r="C519" s="2" t="s">
-        <v>1454</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="520" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A520" s="2" t="s">
-        <v>1455</v>
+        <v>1459</v>
       </c>
       <c r="B520" s="2" t="s">
-        <v>1456</v>
+        <v>1460</v>
       </c>
       <c r="C520" s="2" t="s">
-        <v>1457</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="521" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A521" s="2" t="s">
-        <v>1458</v>
+        <v>1462</v>
       </c>
       <c r="B521" s="2" t="s">
-        <v>1459</v>
+        <v>1463</v>
       </c>
       <c r="C521" s="2" t="s">
-        <v>1460</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="522" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A522" s="2" t="s">
-        <v>1461</v>
+        <v>1465</v>
       </c>
       <c r="B522" s="2" t="s">
-        <v>1462</v>
+        <v>1327</v>
       </c>
       <c r="C522" s="2" t="s">
-        <v>1463</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="523" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A523" s="2" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="B523" s="2" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="C523" s="2" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="524" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A524" s="2" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="B524" s="2" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="C524" s="2" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="525" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A525" s="2" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="B525" s="2" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="C525" s="2" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="526" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A526" s="2" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="B526" s="2" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="C526" s="2" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="527" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A527" s="2" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="B527" s="2" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="C527" s="2" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="528" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A528" s="2" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="B528" s="2" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="C528" s="2" t="s">
-        <v>1481</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="529" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A529" s="2" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="B529" s="2" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="C529" s="2" t="s">
-        <v>1484</v>
+        <v>229</v>
       </c>
     </row>
     <row r="530" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A530" s="2" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="B530" s="2" t="s">
-        <v>1486</v>
+        <v>197</v>
       </c>
       <c r="C530" s="2" t="s">
-        <v>1487</v>
+        <v>198</v>
       </c>
     </row>
     <row r="531" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A531" s="2" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="B531" s="2" t="s">
-        <v>1489</v>
+        <v>200</v>
       </c>
       <c r="C531" s="2" t="s">
-        <v>1490</v>
+        <v>201</v>
       </c>
     </row>
     <row r="532" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A532" s="2" t="s">
-        <v>1491</v>
+        <v>1488</v>
       </c>
       <c r="B532" s="2" t="s">
-        <v>1492</v>
+        <v>698</v>
       </c>
       <c r="C532" s="2" t="s">
-        <v>1493</v>
+        <v>699</v>
       </c>
     </row>
     <row r="533" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A533" s="2" t="s">
-        <v>1494</v>
+        <v>1489</v>
       </c>
       <c r="B533" s="2" t="s">
-        <v>43</v>
+        <v>1490</v>
       </c>
       <c r="C533" s="2" t="s">
-        <v>44</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="534" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A534" s="2" t="s">
-        <v>1495</v>
+        <v>1492</v>
       </c>
       <c r="B534" s="2" t="s">
-        <v>1496</v>
+        <v>1493</v>
       </c>
       <c r="C534" s="2" t="s">
-        <v>1122</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="535" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A535" s="2" t="s">
+        <v>1495</v>
+      </c>
+      <c r="B535" s="2" t="s">
+        <v>1496</v>
+      </c>
+      <c r="C535" s="2" t="s">
         <v>1497</v>
-      </c>
-      <c r="B535" s="2" t="s">
-        <v>1438</v>
-      </c>
-      <c r="C535" s="2" t="s">
-        <v>1439</v>
       </c>
     </row>
     <row r="536" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12751,320 +12922,320 @@
         <v>1499</v>
       </c>
       <c r="C536" s="2" t="s">
-        <v>1231</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="537" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A537" s="2" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="B537" s="2" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="C537" s="2" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="538" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A538" s="2" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="B538" s="2" t="s">
-        <v>1441</v>
+        <v>1505</v>
       </c>
       <c r="C538" s="2" t="s">
-        <v>1442</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="539" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A539" s="2" t="s">
-        <v>1504</v>
+        <v>1507</v>
       </c>
       <c r="B539" s="2" t="s">
-        <v>203</v>
+        <v>1508</v>
       </c>
       <c r="C539" s="2" t="s">
-        <v>203</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="540" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A540" s="2" t="s">
-        <v>1505</v>
+        <v>1510</v>
       </c>
       <c r="B540" s="2" t="s">
-        <v>1506</v>
+        <v>1511</v>
       </c>
       <c r="C540" s="2" t="s">
-        <v>1507</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="541" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A541" s="2" t="s">
-        <v>1508</v>
+        <v>1513</v>
       </c>
       <c r="B541" s="2" t="s">
-        <v>1509</v>
+        <v>1514</v>
       </c>
       <c r="C541" s="2" t="s">
-        <v>1510</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="542" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A542" s="2" t="s">
-        <v>1511</v>
+        <v>1516</v>
       </c>
       <c r="B542" s="2" t="s">
-        <v>1512</v>
+        <v>1517</v>
       </c>
       <c r="C542" s="2" t="s">
-        <v>1513</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="543" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A543" s="2" t="s">
-        <v>1514</v>
+        <v>1519</v>
       </c>
       <c r="B543" s="2" t="s">
-        <v>1515</v>
+        <v>1520</v>
       </c>
       <c r="C543" s="2" t="s">
-        <v>1516</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="544" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A544" s="2" t="s">
-        <v>1517</v>
+        <v>1522</v>
       </c>
       <c r="B544" s="2" t="s">
-        <v>1518</v>
+        <v>1523</v>
       </c>
       <c r="C544" s="2" t="s">
-        <v>1519</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="545" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A545" s="2" t="s">
-        <v>1520</v>
+        <v>1525</v>
       </c>
       <c r="B545" s="2" t="s">
-        <v>1272</v>
+        <v>1526</v>
       </c>
       <c r="C545" s="2" t="s">
-        <v>1273</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="546" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A546" s="2" t="s">
-        <v>1521</v>
+        <v>1528</v>
       </c>
       <c r="B546" s="2" t="s">
-        <v>4</v>
+        <v>1529</v>
       </c>
       <c r="C546" s="2" t="s">
-        <v>5</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="547" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A547" s="2" t="s">
-        <v>1522</v>
+        <v>1531</v>
       </c>
       <c r="B547" s="2" t="s">
-        <v>1263</v>
+        <v>1532</v>
       </c>
       <c r="C547" s="2" t="s">
-        <v>1264</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="548" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A548" s="2" t="s">
-        <v>1523</v>
+        <v>1534</v>
       </c>
       <c r="B548" s="2" t="s">
-        <v>1275</v>
+        <v>1535</v>
       </c>
       <c r="C548" s="2" t="s">
-        <v>1276</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="549" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A549" s="2" t="s">
-        <v>1524</v>
+        <v>1537</v>
       </c>
       <c r="B549" s="2" t="s">
-        <v>1525</v>
+        <v>1538</v>
       </c>
       <c r="C549" s="2" t="s">
-        <v>1526</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="550" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A550" s="2" t="s">
-        <v>1527</v>
+        <v>1540</v>
       </c>
       <c r="B550" s="2" t="s">
-        <v>1528</v>
+        <v>1541</v>
       </c>
       <c r="C550" s="2" t="s">
-        <v>1529</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="551" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A551" s="2" t="s">
-        <v>1530</v>
+        <v>1543</v>
       </c>
       <c r="B551" s="2" t="s">
-        <v>1278</v>
+        <v>1544</v>
       </c>
       <c r="C551" s="2" t="s">
-        <v>1279</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="552" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A552" s="2" t="s">
-        <v>1531</v>
+        <v>1546</v>
       </c>
       <c r="B552" s="2" t="s">
-        <v>1532</v>
+        <v>43</v>
       </c>
       <c r="C552" s="2" t="s">
-        <v>1533</v>
+        <v>44</v>
       </c>
     </row>
     <row r="553" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A553" s="2" t="s">
-        <v>1534</v>
+        <v>1547</v>
       </c>
       <c r="B553" s="2" t="s">
-        <v>1281</v>
+        <v>1548</v>
       </c>
       <c r="C553" s="2" t="s">
-        <v>1535</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="554" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A554" s="2" t="s">
-        <v>1536</v>
+        <v>1549</v>
       </c>
       <c r="B554" s="2" t="s">
-        <v>1230</v>
+        <v>1490</v>
       </c>
       <c r="C554" s="2" t="s">
-        <v>1537</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="555" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A555" s="2" t="s">
-        <v>1538</v>
+        <v>1550</v>
       </c>
       <c r="B555" s="2" t="s">
-        <v>1539</v>
+        <v>1551</v>
       </c>
       <c r="C555" s="2" t="s">
-        <v>1540</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="556" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A556" s="2" t="s">
-        <v>1541</v>
+        <v>1552</v>
       </c>
       <c r="B556" s="2" t="s">
-        <v>1542</v>
+        <v>1553</v>
       </c>
       <c r="C556" s="2" t="s">
-        <v>1543</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="557" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A557" s="2" t="s">
-        <v>1544</v>
+        <v>1555</v>
       </c>
       <c r="B557" s="2" t="s">
-        <v>1545</v>
+        <v>1493</v>
       </c>
       <c r="C557" s="2" t="s">
-        <v>1546</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="558" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A558" s="2" t="s">
-        <v>1547</v>
+        <v>1556</v>
       </c>
       <c r="B558" s="2" t="s">
-        <v>1548</v>
+        <v>206</v>
       </c>
       <c r="C558" s="2" t="s">
-        <v>1549</v>
+        <v>206</v>
       </c>
     </row>
     <row r="559" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A559" s="2" t="s">
-        <v>1550</v>
+        <v>1557</v>
       </c>
       <c r="B559" s="2" t="s">
-        <v>1551</v>
+        <v>1558</v>
       </c>
       <c r="C559" s="2" t="s">
-        <v>1552</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="560" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A560" s="2" t="s">
-        <v>1553</v>
+        <v>1560</v>
       </c>
       <c r="B560" s="2" t="s">
-        <v>1554</v>
+        <v>1561</v>
       </c>
       <c r="C560" s="2" t="s">
-        <v>1555</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="561" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A561" s="2" t="s">
-        <v>1556</v>
+        <v>1563</v>
       </c>
       <c r="B561" s="2" t="s">
-        <v>1557</v>
+        <v>1564</v>
       </c>
       <c r="C561" s="2" t="s">
-        <v>1558</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="562" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A562" s="2" t="s">
-        <v>1559</v>
+        <v>1566</v>
       </c>
       <c r="B562" s="2" t="s">
-        <v>1560</v>
+        <v>1567</v>
       </c>
       <c r="C562" s="2" t="s">
-        <v>1561</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="563" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A563" s="2" t="s">
-        <v>1562</v>
+        <v>1569</v>
       </c>
       <c r="B563" s="2" t="s">
-        <v>1563</v>
+        <v>1570</v>
       </c>
       <c r="C563" s="2" t="s">
-        <v>1564</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="564" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A564" s="2" t="s">
-        <v>1565</v>
+        <v>1572</v>
       </c>
       <c r="B564" s="2" t="s">
-        <v>1272</v>
+        <v>1324</v>
       </c>
       <c r="C564" s="2" t="s">
-        <v>1273</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="565" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A565" s="2" t="s">
-        <v>1566</v>
+        <v>1573</v>
       </c>
       <c r="B565" s="2" t="s">
         <v>4</v>
@@ -13075,222 +13246,222 @@
     </row>
     <row r="566" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A566" s="2" t="s">
-        <v>1567</v>
+        <v>1574</v>
       </c>
       <c r="B566" s="2" t="s">
-        <v>1278</v>
+        <v>1315</v>
       </c>
       <c r="C566" s="2" t="s">
-        <v>1279</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="567" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A567" s="2" t="s">
-        <v>1568</v>
+        <v>1575</v>
       </c>
       <c r="B567" s="2" t="s">
-        <v>1569</v>
+        <v>1327</v>
       </c>
       <c r="C567" s="2" t="s">
-        <v>1570</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="568" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A568" s="2" t="s">
-        <v>1571</v>
+        <v>1576</v>
       </c>
       <c r="B568" s="2" t="s">
-        <v>1572</v>
+        <v>1577</v>
       </c>
       <c r="C568" s="2" t="s">
-        <v>1573</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="569" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A569" s="2" t="s">
-        <v>1574</v>
+        <v>1579</v>
       </c>
       <c r="B569" s="2" t="s">
-        <v>1575</v>
+        <v>1580</v>
       </c>
       <c r="C569" s="2" t="s">
-        <v>1576</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="570" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A570" s="2" t="s">
-        <v>1577</v>
+        <v>1582</v>
       </c>
       <c r="B570" s="2" t="s">
-        <v>1548</v>
+        <v>1330</v>
       </c>
       <c r="C570" s="2" t="s">
-        <v>1549</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="571" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A571" s="2" t="s">
-        <v>1578</v>
+        <v>1583</v>
       </c>
       <c r="B571" s="2" t="s">
-        <v>1579</v>
+        <v>1584</v>
       </c>
       <c r="C571" s="2" t="s">
-        <v>1580</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="572" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A572" s="2" t="s">
-        <v>1581</v>
+        <v>1586</v>
       </c>
       <c r="B572" s="2" t="s">
-        <v>1582</v>
+        <v>1333</v>
       </c>
       <c r="C572" s="2" t="s">
-        <v>1583</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="573" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A573" s="2" t="s">
-        <v>1584</v>
+        <v>1588</v>
       </c>
       <c r="B573" s="2" t="s">
-        <v>1402</v>
+        <v>1282</v>
       </c>
       <c r="C573" s="2" t="s">
-        <v>1403</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="574" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A574" s="2" t="s">
-        <v>1585</v>
+        <v>1590</v>
       </c>
       <c r="B574" s="2" t="s">
-        <v>1586</v>
+        <v>1591</v>
       </c>
       <c r="C574" s="2" t="s">
-        <v>1587</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="575" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A575" s="2" t="s">
-        <v>1588</v>
+        <v>1593</v>
       </c>
       <c r="B575" s="2" t="s">
-        <v>1589</v>
+        <v>1594</v>
       </c>
       <c r="C575" s="2" t="s">
-        <v>1590</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="576" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A576" s="2" t="s">
-        <v>1591</v>
+        <v>1596</v>
       </c>
       <c r="B576" s="2" t="s">
-        <v>1592</v>
+        <v>1597</v>
       </c>
       <c r="C576" s="2" t="s">
-        <v>1593</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="577" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A577" s="2" t="s">
-        <v>1594</v>
+        <v>1599</v>
       </c>
       <c r="B577" s="2" t="s">
-        <v>1595</v>
+        <v>1600</v>
       </c>
       <c r="C577" s="2" t="s">
-        <v>1596</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="578" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A578" s="2" t="s">
-        <v>1597</v>
+        <v>1602</v>
       </c>
       <c r="B578" s="2" t="s">
-        <v>1598</v>
+        <v>1603</v>
       </c>
       <c r="C578" s="2" t="s">
-        <v>1599</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="579" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A579" s="2" t="s">
-        <v>1600</v>
+        <v>1605</v>
       </c>
       <c r="B579" s="2" t="s">
-        <v>1601</v>
+        <v>1606</v>
       </c>
       <c r="C579" s="2" t="s">
-        <v>1602</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="580" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A580" s="2" t="s">
-        <v>1603</v>
+        <v>1608</v>
       </c>
       <c r="B580" s="2" t="s">
-        <v>1604</v>
+        <v>1609</v>
       </c>
       <c r="C580" s="2" t="s">
-        <v>1605</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="581" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A581" s="2" t="s">
-        <v>1606</v>
+        <v>1611</v>
       </c>
       <c r="B581" s="2" t="s">
-        <v>1607</v>
+        <v>1612</v>
       </c>
       <c r="C581" s="2" t="s">
-        <v>551</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="582" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A582" s="2" t="s">
-        <v>1608</v>
+        <v>1614</v>
       </c>
       <c r="B582" s="2" t="s">
-        <v>1609</v>
+        <v>1615</v>
       </c>
       <c r="C582" s="2" t="s">
-        <v>1610</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="583" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A583" s="2" t="s">
-        <v>1611</v>
+        <v>1617</v>
       </c>
       <c r="B583" s="2" t="s">
-        <v>1612</v>
+        <v>1324</v>
       </c>
       <c r="C583" s="2" t="s">
-        <v>1613</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="584" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A584" s="2" t="s">
-        <v>1614</v>
+        <v>1618</v>
       </c>
       <c r="B584" s="2" t="s">
-        <v>1615</v>
+        <v>4</v>
       </c>
       <c r="C584" s="2" t="s">
-        <v>1616</v>
+        <v>5</v>
       </c>
     </row>
     <row r="585" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A585" s="2" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="B585" s="2" t="s">
-        <v>1618</v>
+        <v>1330</v>
       </c>
       <c r="C585" s="2" t="s">
-        <v>1619</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="586" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13331,21 +13502,21 @@
         <v>1629</v>
       </c>
       <c r="B589" s="2" t="s">
-        <v>1630</v>
+        <v>1600</v>
       </c>
       <c r="C589" s="2" t="s">
-        <v>1631</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="590" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A590" s="2" t="s">
+        <v>1630</v>
+      </c>
+      <c r="B590" s="2" t="s">
+        <v>1631</v>
+      </c>
+      <c r="C590" s="2" t="s">
         <v>1632</v>
-      </c>
-      <c r="B590" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="C590" s="2" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="591" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13364,21 +13535,21 @@
         <v>1636</v>
       </c>
       <c r="B592" s="2" t="s">
-        <v>1637</v>
+        <v>1454</v>
       </c>
       <c r="C592" s="2" t="s">
-        <v>1638</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="593" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A593" s="2" t="s">
+        <v>1637</v>
+      </c>
+      <c r="B593" s="2" t="s">
+        <v>1638</v>
+      </c>
+      <c r="C593" s="2" t="s">
         <v>1639</v>
-      </c>
-      <c r="B593" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="C593" s="2" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="594" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13455,139 +13626,139 @@
         <v>1659</v>
       </c>
       <c r="C600" s="2" t="s">
-        <v>1660</v>
+        <v>603</v>
       </c>
     </row>
     <row r="601" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A601" s="2" t="s">
+        <v>1660</v>
+      </c>
+      <c r="B601" s="2" t="s">
         <v>1661</v>
       </c>
-      <c r="B601" s="2" t="s">
+      <c r="C601" s="2" t="s">
         <v>1662</v>
-      </c>
-      <c r="C601" s="2" t="s">
-        <v>1663</v>
       </c>
     </row>
     <row r="602" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A602" s="2" t="s">
+        <v>1663</v>
+      </c>
+      <c r="B602" s="2" t="s">
         <v>1664</v>
       </c>
-      <c r="B602" s="2" t="s">
+      <c r="C602" s="2" t="s">
         <v>1665</v>
-      </c>
-      <c r="C602" s="2" t="s">
-        <v>1666</v>
       </c>
     </row>
     <row r="603" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A603" s="2" t="s">
+        <v>1666</v>
+      </c>
+      <c r="B603" s="2" t="s">
         <v>1667</v>
       </c>
-      <c r="B603" s="2" t="s">
+      <c r="C603" s="2" t="s">
         <v>1668</v>
-      </c>
-      <c r="C603" s="2" t="s">
-        <v>1669</v>
       </c>
     </row>
     <row r="604" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A604" s="2" t="s">
+        <v>1669</v>
+      </c>
+      <c r="B604" s="2" t="s">
         <v>1670</v>
       </c>
-      <c r="B604" s="2" t="s">
+      <c r="C604" s="2" t="s">
         <v>1671</v>
-      </c>
-      <c r="C604" s="2" t="s">
-        <v>1672</v>
       </c>
     </row>
     <row r="605" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A605" s="2" t="s">
+        <v>1672</v>
+      </c>
+      <c r="B605" s="2" t="s">
         <v>1673</v>
       </c>
-      <c r="B605" s="2" t="s">
+      <c r="C605" s="2" t="s">
         <v>1674</v>
-      </c>
-      <c r="C605" s="2" t="s">
-        <v>1675</v>
       </c>
     </row>
     <row r="606" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A606" s="2" t="s">
+        <v>1675</v>
+      </c>
+      <c r="B606" s="2" t="s">
         <v>1676</v>
       </c>
-      <c r="B606" s="2" t="s">
-        <v>294</v>
-      </c>
       <c r="C606" s="2" t="s">
-        <v>295</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="607" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A607" s="2" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="B607" s="2" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="C607" s="2" t="s">
-        <v>1122</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="608" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A608" s="2" t="s">
-        <v>1679</v>
+        <v>1681</v>
       </c>
       <c r="B608" s="2" t="s">
-        <v>1680</v>
+        <v>1682</v>
       </c>
       <c r="C608" s="2" t="s">
-        <v>1681</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="609" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A609" s="2" t="s">
-        <v>1682</v>
+        <v>1684</v>
       </c>
       <c r="B609" s="2" t="s">
-        <v>1501</v>
+        <v>602</v>
       </c>
       <c r="C609" s="2" t="s">
-        <v>1502</v>
+        <v>603</v>
       </c>
     </row>
     <row r="610" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A610" s="2" t="s">
-        <v>1683</v>
+        <v>1685</v>
       </c>
       <c r="B610" s="2" t="s">
-        <v>1684</v>
+        <v>1686</v>
       </c>
       <c r="C610" s="2" t="s">
-        <v>1685</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="611" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A611" s="2" t="s">
-        <v>1686</v>
+        <v>1688</v>
       </c>
       <c r="B611" s="2" t="s">
-        <v>1687</v>
+        <v>1689</v>
       </c>
       <c r="C611" s="2" t="s">
-        <v>1688</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="612" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A612" s="2" t="s">
-        <v>1689</v>
+        <v>1691</v>
       </c>
       <c r="B612" s="2" t="s">
-        <v>1690</v>
+        <v>303</v>
       </c>
       <c r="C612" s="2" t="s">
-        <v>1691</v>
+        <v>304</v>
       </c>
     </row>
     <row r="613" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13617,447 +13788,447 @@
         <v>1698</v>
       </c>
       <c r="B615" s="2" t="s">
-        <v>194</v>
+        <v>1699</v>
       </c>
       <c r="C615" s="2" t="s">
-        <v>195</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="616" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A616" s="2" t="s">
-        <v>1699</v>
+        <v>1701</v>
       </c>
       <c r="B616" s="2" t="s">
-        <v>1119</v>
+        <v>1702</v>
       </c>
       <c r="C616" s="2" t="s">
-        <v>660</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="617" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A617" s="2" t="s">
-        <v>1700</v>
+        <v>1704</v>
       </c>
       <c r="B617" s="2" t="s">
-        <v>1128</v>
+        <v>1705</v>
       </c>
       <c r="C617" s="2" t="s">
-        <v>1701</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="618" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A618" s="2" t="s">
-        <v>1702</v>
+        <v>1707</v>
       </c>
       <c r="B618" s="2" t="s">
-        <v>1703</v>
+        <v>1708</v>
       </c>
       <c r="C618" s="2" t="s">
-        <v>1704</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="619" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A619" s="2" t="s">
-        <v>1705</v>
+        <v>1710</v>
       </c>
       <c r="B619" s="2" t="s">
-        <v>294</v>
+        <v>1711</v>
       </c>
       <c r="C619" s="2" t="s">
-        <v>295</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="620" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A620" s="2" t="s">
-        <v>1706</v>
+        <v>1713</v>
       </c>
       <c r="B620" s="2" t="s">
-        <v>1707</v>
+        <v>1714</v>
       </c>
       <c r="C620" s="2" t="s">
-        <v>1708</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="621" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A621" s="2" t="s">
-        <v>1709</v>
+        <v>1716</v>
       </c>
       <c r="B621" s="2" t="s">
-        <v>1710</v>
+        <v>1717</v>
       </c>
       <c r="C621" s="2" t="s">
-        <v>1711</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="622" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A622" s="2" t="s">
-        <v>1712</v>
+        <v>1719</v>
       </c>
       <c r="B622" s="2" t="s">
-        <v>1713</v>
+        <v>1720</v>
       </c>
       <c r="C622" s="2" t="s">
-        <v>1714</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="623" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A623" s="2" t="s">
-        <v>1715</v>
+        <v>1722</v>
       </c>
       <c r="B623" s="2" t="s">
-        <v>1716</v>
+        <v>1723</v>
       </c>
       <c r="C623" s="2" t="s">
-        <v>1717</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="624" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A624" s="2" t="s">
-        <v>1718</v>
+        <v>1725</v>
       </c>
       <c r="B624" s="2" t="s">
-        <v>300</v>
+        <v>1726</v>
       </c>
       <c r="C624" s="2" t="s">
-        <v>301</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="625" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A625" s="2" t="s">
-        <v>1719</v>
+        <v>1728</v>
       </c>
       <c r="B625" s="2" t="s">
-        <v>1720</v>
+        <v>297</v>
       </c>
       <c r="C625" s="2" t="s">
-        <v>1721</v>
+        <v>298</v>
       </c>
     </row>
     <row r="626" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A626" s="2" t="s">
-        <v>1722</v>
+        <v>1729</v>
       </c>
       <c r="B626" s="2" t="s">
-        <v>1723</v>
+        <v>1730</v>
       </c>
       <c r="C626" s="2" t="s">
-        <v>1724</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="627" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A627" s="2" t="s">
-        <v>1725</v>
+        <v>1731</v>
       </c>
       <c r="B627" s="2" t="s">
-        <v>1726</v>
+        <v>1732</v>
       </c>
       <c r="C627" s="2" t="s">
-        <v>1727</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="628" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A628" s="2" t="s">
-        <v>1728</v>
+        <v>1734</v>
       </c>
       <c r="B628" s="2" t="s">
-        <v>1729</v>
+        <v>1553</v>
       </c>
       <c r="C628" s="2" t="s">
-        <v>1730</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="629" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A629" s="2" t="s">
-        <v>1731</v>
+        <v>1735</v>
       </c>
       <c r="B629" s="2" t="s">
-        <v>1732</v>
+        <v>1736</v>
       </c>
       <c r="C629" s="2" t="s">
-        <v>1733</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="630" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A630" s="2" t="s">
-        <v>1734</v>
+        <v>1738</v>
       </c>
       <c r="B630" s="2" t="s">
-        <v>550</v>
+        <v>1739</v>
       </c>
       <c r="C630" s="2" t="s">
-        <v>551</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="631" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A631" s="2" t="s">
-        <v>1735</v>
+        <v>1741</v>
       </c>
       <c r="B631" s="2" t="s">
-        <v>1736</v>
+        <v>1742</v>
       </c>
       <c r="C631" s="2" t="s">
-        <v>1737</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="632" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A632" s="2" t="s">
-        <v>1738</v>
+        <v>1744</v>
       </c>
       <c r="B632" s="2" t="s">
-        <v>1739</v>
+        <v>1745</v>
       </c>
       <c r="C632" s="2" t="s">
-        <v>1740</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="633" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A633" s="2" t="s">
-        <v>1741</v>
+        <v>1747</v>
       </c>
       <c r="B633" s="2" t="s">
-        <v>1742</v>
+        <v>1748</v>
       </c>
       <c r="C633" s="2" t="s">
-        <v>1743</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="634" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A634" s="2" t="s">
-        <v>1744</v>
+        <v>1750</v>
       </c>
       <c r="B634" s="2" t="s">
-        <v>1745</v>
+        <v>197</v>
       </c>
       <c r="C634" s="2" t="s">
-        <v>1746</v>
+        <v>198</v>
       </c>
     </row>
     <row r="635" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A635" s="2" t="s">
-        <v>1747</v>
+        <v>1751</v>
       </c>
       <c r="B635" s="2" t="s">
-        <v>1748</v>
+        <v>1171</v>
       </c>
       <c r="C635" s="2" t="s">
-        <v>1749</v>
+        <v>712</v>
       </c>
     </row>
     <row r="636" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A636" s="2" t="s">
-        <v>1750</v>
+        <v>1752</v>
       </c>
       <c r="B636" s="2" t="s">
-        <v>1751</v>
+        <v>1180</v>
       </c>
       <c r="C636" s="2" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="637" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A637" s="2" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="B637" s="2" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="C637" s="2" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="638" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A638" s="2" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="B638" s="2" t="s">
-        <v>1757</v>
+        <v>297</v>
       </c>
       <c r="C638" s="2" t="s">
-        <v>1758</v>
+        <v>298</v>
       </c>
     </row>
     <row r="639" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A639" s="2" t="s">
+        <v>1758</v>
+      </c>
+      <c r="B639" s="2" t="s">
         <v>1759</v>
       </c>
-      <c r="B639" s="2" t="s">
+      <c r="C639" s="2" t="s">
         <v>1760</v>
-      </c>
-      <c r="C639" s="2" t="s">
-        <v>1761</v>
       </c>
     </row>
     <row r="640" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A640" s="2" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B640" s="2" t="s">
         <v>1762</v>
       </c>
-      <c r="B640" s="2" t="s">
-        <v>19</v>
-      </c>
       <c r="C640" s="2" t="s">
-        <v>20</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="641" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A641" s="2" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B641" s="2" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="C641" s="2" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="642" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A642" s="2" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="B642" s="2" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="C642" s="2" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="643" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A643" s="2" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="B643" s="2" t="s">
-        <v>1770</v>
+        <v>303</v>
       </c>
       <c r="C643" s="2" t="s">
-        <v>1771</v>
+        <v>304</v>
       </c>
     </row>
     <row r="644" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A644" s="2" t="s">
+        <v>1771</v>
+      </c>
+      <c r="B644" s="2" t="s">
         <v>1772</v>
       </c>
-      <c r="B644" s="2" t="s">
+      <c r="C644" s="2" t="s">
         <v>1773</v>
-      </c>
-      <c r="C644" s="2" t="s">
-        <v>1774</v>
       </c>
     </row>
     <row r="645" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A645" s="2" t="s">
+        <v>1774</v>
+      </c>
+      <c r="B645" s="2" t="s">
         <v>1775</v>
       </c>
-      <c r="B645" s="2" t="s">
+      <c r="C645" s="2" t="s">
         <v>1776</v>
-      </c>
-      <c r="C645" s="2" t="s">
-        <v>1777</v>
       </c>
     </row>
     <row r="646" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A646" s="2" t="s">
+        <v>1777</v>
+      </c>
+      <c r="B646" s="2" t="s">
         <v>1778</v>
       </c>
-      <c r="B646" s="2" t="s">
-        <v>279</v>
-      </c>
       <c r="C646" s="2" t="s">
-        <v>280</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="647" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A647" s="2" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="B647" s="2" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="C647" s="2" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="648" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A648" s="2" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="B648" s="2" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="C648" s="2" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="649" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A649" s="2" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="B649" s="2" t="s">
-        <v>1786</v>
+        <v>602</v>
       </c>
       <c r="C649" s="2" t="s">
-        <v>1787</v>
+        <v>603</v>
       </c>
     </row>
     <row r="650" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A650" s="2" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B650" s="2" t="s">
         <v>1788</v>
       </c>
-      <c r="B650" s="2" t="s">
+      <c r="C650" s="2" t="s">
         <v>1789</v>
-      </c>
-      <c r="C650" s="2" t="s">
-        <v>1790</v>
       </c>
     </row>
     <row r="651" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A651" s="2" t="s">
+        <v>1790</v>
+      </c>
+      <c r="B651" s="2" t="s">
         <v>1791</v>
       </c>
-      <c r="B651" s="2" t="s">
+      <c r="C651" s="2" t="s">
         <v>1792</v>
-      </c>
-      <c r="C651" s="2" t="s">
-        <v>1793</v>
       </c>
     </row>
     <row r="652" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A652" s="2" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B652" s="2" t="s">
         <v>1794</v>
       </c>
-      <c r="B652" s="2" t="s">
+      <c r="C652" s="2" t="s">
         <v>1795</v>
-      </c>
-      <c r="C652" s="2" t="s">
-        <v>1796</v>
       </c>
     </row>
     <row r="653" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A653" s="2" t="s">
+        <v>1796</v>
+      </c>
+      <c r="B653" s="2" t="s">
         <v>1797</v>
       </c>
-      <c r="B653" s="2" t="s">
+      <c r="C653" s="2" t="s">
         <v>1798</v>
-      </c>
-      <c r="C653" s="2" t="s">
-        <v>1799</v>
       </c>
     </row>
     <row r="654" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A654" s="2" t="s">
+        <v>1799</v>
+      </c>
+      <c r="B654" s="2" t="s">
         <v>1800</v>
       </c>
-      <c r="B654" s="2" t="s">
+      <c r="C654" s="2" t="s">
         <v>1801</v>
-      </c>
-      <c r="C654" s="2" t="s">
-        <v>1802</v>
       </c>
     </row>
     <row r="655" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A655" s="2" t="s">
+        <v>1802</v>
+      </c>
+      <c r="B655" s="2" t="s">
         <v>1803</v>
-      </c>
-      <c r="B655" s="2" t="s">
-        <v>762</v>
       </c>
       <c r="C655" s="2" t="s">
         <v>1804</v>
@@ -14101,109 +14272,109 @@
         <v>1814</v>
       </c>
       <c r="B659" s="2" t="s">
-        <v>1815</v>
+        <v>19</v>
       </c>
       <c r="C659" s="2" t="s">
-        <v>1816</v>
+        <v>20</v>
       </c>
     </row>
     <row r="660" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A660" s="2" t="s">
+        <v>1815</v>
+      </c>
+      <c r="B660" s="2" t="s">
+        <v>1816</v>
+      </c>
+      <c r="C660" s="2" t="s">
         <v>1817</v>
-      </c>
-      <c r="B660" s="2" t="s">
-        <v>1818</v>
-      </c>
-      <c r="C660" s="2" t="s">
-        <v>1819</v>
       </c>
     </row>
     <row r="661" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A661" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B661" s="2" t="s">
+        <v>1819</v>
+      </c>
+      <c r="C661" s="2" t="s">
         <v>1820</v>
-      </c>
-      <c r="B661" s="2" t="s">
-        <v>1821</v>
-      </c>
-      <c r="C661" s="2" t="s">
-        <v>1822</v>
       </c>
     </row>
     <row r="662" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A662" s="2" t="s">
+        <v>1821</v>
+      </c>
+      <c r="B662" s="2" t="s">
+        <v>1822</v>
+      </c>
+      <c r="C662" s="2" t="s">
         <v>1823</v>
-      </c>
-      <c r="B662" s="2" t="s">
-        <v>1824</v>
-      </c>
-      <c r="C662" s="2" t="s">
-        <v>1825</v>
       </c>
     </row>
     <row r="663" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A663" s="2" t="s">
+        <v>1824</v>
+      </c>
+      <c r="B663" s="2" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C663" s="2" t="s">
         <v>1826</v>
-      </c>
-      <c r="B663" s="2" t="s">
-        <v>1827</v>
-      </c>
-      <c r="C663" s="2" t="s">
-        <v>1828</v>
       </c>
     </row>
     <row r="664" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A664" s="2" t="s">
+        <v>1827</v>
+      </c>
+      <c r="B664" s="2" t="s">
+        <v>1828</v>
+      </c>
+      <c r="C664" s="2" t="s">
         <v>1829</v>
-      </c>
-      <c r="B664" s="2" t="s">
-        <v>1830</v>
-      </c>
-      <c r="C664" s="2" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="665" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A665" s="2" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="B665" s="2" t="s">
-        <v>1832</v>
+        <v>282</v>
       </c>
       <c r="C665" s="2" t="s">
-        <v>1833</v>
+        <v>283</v>
       </c>
     </row>
     <row r="666" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A666" s="2" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="B666" s="2" t="s">
-        <v>1835</v>
+        <v>1832</v>
       </c>
       <c r="C666" s="2" t="s">
-        <v>1836</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="667" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A667" s="2" t="s">
-        <v>1837</v>
+        <v>1834</v>
       </c>
       <c r="B667" s="2" t="s">
-        <v>294</v>
+        <v>1835</v>
       </c>
       <c r="C667" s="2" t="s">
-        <v>295</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="668" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A668" s="2" t="s">
+        <v>1837</v>
+      </c>
+      <c r="B668" s="2" t="s">
         <v>1838</v>
       </c>
-      <c r="B668" s="2" t="s">
+      <c r="C668" s="2" t="s">
         <v>1839</v>
-      </c>
-      <c r="C668" s="2" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="669" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14225,1071 +14396,1071 @@
         <v>1844</v>
       </c>
       <c r="C670" s="2" t="s">
-        <v>473</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="671" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A671" s="2" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="B671" s="2" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="C671" s="2" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="672" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A672" s="2" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="B672" s="2" t="s">
-        <v>875</v>
+        <v>1850</v>
       </c>
       <c r="C672" s="2" t="s">
-        <v>876</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="673" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A673" s="2" t="s">
-        <v>1849</v>
+        <v>1852</v>
       </c>
       <c r="B673" s="2" t="s">
-        <v>4</v>
+        <v>1853</v>
       </c>
       <c r="C673" s="2" t="s">
-        <v>5</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="674" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A674" s="2" t="s">
-        <v>1850</v>
+        <v>1855</v>
       </c>
       <c r="B674" s="2" t="s">
-        <v>300</v>
+        <v>814</v>
       </c>
       <c r="C674" s="2" t="s">
-        <v>301</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="675" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A675" s="2" t="s">
-        <v>1851</v>
+        <v>1857</v>
       </c>
       <c r="B675" s="2" t="s">
-        <v>1846</v>
+        <v>1858</v>
       </c>
       <c r="C675" s="2" t="s">
-        <v>1847</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="676" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A676" s="2" t="s">
-        <v>1852</v>
+        <v>1860</v>
       </c>
       <c r="B676" s="2" t="s">
-        <v>1853</v>
+        <v>1861</v>
       </c>
       <c r="C676" s="2" t="s">
-        <v>1854</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="677" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A677" s="2" t="s">
-        <v>1855</v>
+        <v>1863</v>
       </c>
       <c r="B677" s="2" t="s">
-        <v>1856</v>
+        <v>1864</v>
       </c>
       <c r="C677" s="2" t="s">
-        <v>1857</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="678" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A678" s="2" t="s">
-        <v>1858</v>
+        <v>1866</v>
       </c>
       <c r="B678" s="2" t="s">
-        <v>1859</v>
+        <v>1867</v>
       </c>
       <c r="C678" s="2" t="s">
-        <v>1860</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="679" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A679" s="2" t="s">
-        <v>1861</v>
+        <v>1869</v>
       </c>
       <c r="B679" s="2" t="s">
-        <v>1862</v>
+        <v>1870</v>
       </c>
       <c r="C679" s="2" t="s">
-        <v>1863</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="680" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A680" s="2" t="s">
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="B680" s="2" t="s">
-        <v>1865</v>
+        <v>1873</v>
       </c>
       <c r="C680" s="2" t="s">
-        <v>1866</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="681" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A681" s="2" t="s">
-        <v>1867</v>
+        <v>1875</v>
       </c>
       <c r="B681" s="2" t="s">
-        <v>1868</v>
+        <v>1876</v>
       </c>
       <c r="C681" s="2" t="s">
-        <v>1869</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="682" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A682" s="2" t="s">
-        <v>1870</v>
+        <v>1878</v>
       </c>
       <c r="B682" s="2" t="s">
-        <v>1871</v>
+        <v>1879</v>
       </c>
       <c r="C682" s="2" t="s">
-        <v>1872</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="683" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A683" s="2" t="s">
-        <v>1873</v>
+        <v>1881</v>
       </c>
       <c r="B683" s="2" t="s">
-        <v>1874</v>
+        <v>1882</v>
       </c>
       <c r="C683" s="2" t="s">
-        <v>1875</v>
+        <v>476</v>
       </c>
     </row>
     <row r="684" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A684" s="2" t="s">
-        <v>1876</v>
+        <v>1883</v>
       </c>
       <c r="B684" s="2" t="s">
-        <v>19</v>
+        <v>1884</v>
       </c>
       <c r="C684" s="2" t="s">
-        <v>20</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="685" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A685" s="2" t="s">
-        <v>1877</v>
+        <v>1886</v>
       </c>
       <c r="B685" s="2" t="s">
-        <v>13</v>
+        <v>1887</v>
       </c>
       <c r="C685" s="2" t="s">
-        <v>14</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="686" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A686" s="2" t="s">
-        <v>1878</v>
+        <v>1889</v>
       </c>
       <c r="B686" s="2" t="s">
-        <v>16</v>
+        <v>297</v>
       </c>
       <c r="C686" s="2" t="s">
-        <v>17</v>
+        <v>298</v>
       </c>
     </row>
     <row r="687" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A687" s="2" t="s">
-        <v>1879</v>
+        <v>1890</v>
       </c>
       <c r="B687" s="2" t="s">
-        <v>1880</v>
+        <v>1891</v>
       </c>
       <c r="C687" s="2" t="s">
-        <v>1881</v>
+        <v>195</v>
       </c>
     </row>
     <row r="688" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A688" s="2" t="s">
-        <v>1882</v>
+        <v>1892</v>
       </c>
       <c r="B688" s="2" t="s">
-        <v>1883</v>
+        <v>1893</v>
       </c>
       <c r="C688" s="2" t="s">
-        <v>1884</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="689" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A689" s="2" t="s">
-        <v>1885</v>
+        <v>1895</v>
       </c>
       <c r="B689" s="2" t="s">
-        <v>1886</v>
+        <v>1896</v>
       </c>
       <c r="C689" s="2" t="s">
-        <v>1887</v>
+        <v>476</v>
       </c>
     </row>
     <row r="690" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A690" s="2" t="s">
-        <v>1888</v>
+        <v>1897</v>
       </c>
       <c r="B690" s="2" t="s">
-        <v>1889</v>
+        <v>1898</v>
       </c>
       <c r="C690" s="2" t="s">
-        <v>1890</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="691" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A691" s="2" t="s">
-        <v>1891</v>
+        <v>1900</v>
       </c>
       <c r="B691" s="2" t="s">
-        <v>1789</v>
+        <v>927</v>
       </c>
       <c r="C691" s="2" t="s">
-        <v>1790</v>
+        <v>928</v>
       </c>
     </row>
     <row r="692" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A692" s="2" t="s">
-        <v>1892</v>
+        <v>1901</v>
       </c>
       <c r="B692" s="2" t="s">
-        <v>1792</v>
+        <v>4</v>
       </c>
       <c r="C692" s="2" t="s">
-        <v>1793</v>
+        <v>5</v>
       </c>
     </row>
     <row r="693" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A693" s="2" t="s">
-        <v>1893</v>
+        <v>1902</v>
       </c>
       <c r="B693" s="2" t="s">
-        <v>1894</v>
+        <v>303</v>
       </c>
       <c r="C693" s="2" t="s">
-        <v>1282</v>
+        <v>304</v>
       </c>
     </row>
     <row r="694" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A694" s="2" t="s">
-        <v>1895</v>
+        <v>1903</v>
       </c>
       <c r="B694" s="2" t="s">
-        <v>1896</v>
+        <v>1898</v>
       </c>
       <c r="C694" s="2" t="s">
-        <v>1897</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="695" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A695" s="2" t="s">
-        <v>1898</v>
+        <v>1904</v>
       </c>
       <c r="B695" s="2" t="s">
-        <v>1131</v>
+        <v>1905</v>
       </c>
       <c r="C695" s="2" t="s">
-        <v>1132</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="696" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A696" s="2" t="s">
-        <v>1899</v>
+        <v>1907</v>
       </c>
       <c r="B696" s="2" t="s">
-        <v>1900</v>
+        <v>1908</v>
       </c>
       <c r="C696" s="2" t="s">
-        <v>1802</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="697" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A697" s="2" t="s">
-        <v>1901</v>
+        <v>1910</v>
       </c>
       <c r="B697" s="2" t="s">
-        <v>762</v>
+        <v>1911</v>
       </c>
       <c r="C697" s="2" t="s">
-        <v>1804</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="698" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A698" s="2" t="s">
-        <v>1902</v>
+        <v>1913</v>
       </c>
       <c r="B698" s="2" t="s">
-        <v>1903</v>
+        <v>1914</v>
       </c>
       <c r="C698" s="2" t="s">
-        <v>1904</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="699" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A699" s="2" t="s">
-        <v>1905</v>
+        <v>1916</v>
       </c>
       <c r="B699" s="2" t="s">
-        <v>1906</v>
+        <v>1917</v>
       </c>
       <c r="C699" s="2" t="s">
-        <v>1897</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="700" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A700" s="2" t="s">
-        <v>1907</v>
+        <v>1919</v>
       </c>
       <c r="B700" s="2" t="s">
-        <v>859</v>
+        <v>1920</v>
       </c>
       <c r="C700" s="2" t="s">
-        <v>1908</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="701" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A701" s="2" t="s">
-        <v>1909</v>
+        <v>1922</v>
       </c>
       <c r="B701" s="2" t="s">
-        <v>871</v>
+        <v>1923</v>
       </c>
       <c r="C701" s="2" t="s">
-        <v>1910</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="702" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A702" s="2" t="s">
-        <v>1911</v>
+        <v>1925</v>
       </c>
       <c r="B702" s="2" t="s">
-        <v>553</v>
+        <v>1926</v>
       </c>
       <c r="C702" s="2" t="s">
-        <v>473</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="703" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A703" s="2" t="s">
-        <v>1912</v>
+        <v>1928</v>
       </c>
       <c r="B703" s="2" t="s">
-        <v>875</v>
+        <v>19</v>
       </c>
       <c r="C703" s="2" t="s">
-        <v>876</v>
+        <v>20</v>
       </c>
     </row>
     <row r="704" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A704" s="2" t="s">
-        <v>1913</v>
+        <v>1929</v>
       </c>
       <c r="B704" s="2" t="s">
-        <v>300</v>
+        <v>13</v>
       </c>
       <c r="C704" s="2" t="s">
-        <v>301</v>
+        <v>14</v>
       </c>
     </row>
     <row r="705" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A705" s="2" t="s">
-        <v>1914</v>
+        <v>1930</v>
       </c>
       <c r="B705" s="2" t="s">
-        <v>1915</v>
+        <v>16</v>
       </c>
       <c r="C705" s="2" t="s">
-        <v>1916</v>
+        <v>17</v>
       </c>
     </row>
     <row r="706" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A706" s="2" t="s">
-        <v>1917</v>
+        <v>1931</v>
       </c>
       <c r="B706" s="2" t="s">
-        <v>1918</v>
+        <v>1932</v>
       </c>
       <c r="C706" s="2" t="s">
-        <v>1919</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="707" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A707" s="2" t="s">
-        <v>1920</v>
+        <v>1934</v>
       </c>
       <c r="B707" s="2" t="s">
-        <v>1921</v>
+        <v>1935</v>
       </c>
       <c r="C707" s="2" t="s">
-        <v>1922</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="708" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A708" s="2" t="s">
-        <v>1923</v>
+        <v>1937</v>
       </c>
       <c r="B708" s="2" t="s">
-        <v>903</v>
+        <v>1938</v>
       </c>
       <c r="C708" s="2" t="s">
-        <v>904</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="709" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A709" s="2" t="s">
-        <v>1924</v>
+        <v>1940</v>
       </c>
       <c r="B709" s="2" t="s">
-        <v>871</v>
+        <v>1941</v>
       </c>
       <c r="C709" s="2" t="s">
-        <v>1910</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="710" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A710" s="2" t="s">
-        <v>1925</v>
+        <v>1943</v>
       </c>
       <c r="B710" s="2" t="s">
-        <v>907</v>
+        <v>1841</v>
       </c>
       <c r="C710" s="2" t="s">
-        <v>908</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="711" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A711" s="2" t="s">
-        <v>1926</v>
+        <v>1944</v>
       </c>
       <c r="B711" s="2" t="s">
-        <v>1927</v>
+        <v>1844</v>
       </c>
       <c r="C711" s="2" t="s">
-        <v>1928</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="712" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A712" s="2" t="s">
-        <v>1929</v>
+        <v>1945</v>
       </c>
       <c r="B712" s="2" t="s">
-        <v>913</v>
+        <v>1946</v>
       </c>
       <c r="C712" s="2" t="s">
-        <v>1930</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="713" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A713" s="2" t="s">
-        <v>1931</v>
+        <v>1947</v>
       </c>
       <c r="B713" s="2" t="s">
-        <v>1932</v>
+        <v>1948</v>
       </c>
       <c r="C713" s="2" t="s">
-        <v>1933</v>
+        <v>1949</v>
       </c>
     </row>
     <row r="714" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A714" s="2" t="s">
-        <v>1934</v>
+        <v>1950</v>
       </c>
       <c r="B714" s="2" t="s">
-        <v>919</v>
+        <v>1183</v>
       </c>
       <c r="C714" s="2" t="s">
-        <v>1935</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="715" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A715" s="2" t="s">
-        <v>1936</v>
+        <v>1951</v>
       </c>
       <c r="B715" s="2" t="s">
-        <v>1937</v>
+        <v>1952</v>
       </c>
       <c r="C715" s="2" t="s">
-        <v>1938</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="716" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A716" s="2" t="s">
-        <v>1939</v>
+        <v>1953</v>
       </c>
       <c r="B716" s="2" t="s">
-        <v>1940</v>
+        <v>814</v>
       </c>
       <c r="C716" s="2" t="s">
-        <v>1941</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="717" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A717" s="2" t="s">
-        <v>1942</v>
+        <v>1954</v>
       </c>
       <c r="B717" s="2" t="s">
-        <v>1943</v>
+        <v>1955</v>
       </c>
       <c r="C717" s="2" t="s">
-        <v>1944</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="718" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A718" s="2" t="s">
-        <v>1945</v>
+        <v>1957</v>
       </c>
       <c r="B718" s="2" t="s">
-        <v>743</v>
+        <v>1958</v>
       </c>
       <c r="C718" s="2" t="s">
-        <v>744</v>
+        <v>1949</v>
       </c>
     </row>
     <row r="719" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A719" s="2" t="s">
-        <v>1946</v>
+        <v>1959</v>
       </c>
       <c r="B719" s="2" t="s">
-        <v>929</v>
+        <v>911</v>
       </c>
       <c r="C719" s="2" t="s">
-        <v>930</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="720" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A720" s="2" t="s">
-        <v>1947</v>
+        <v>1961</v>
       </c>
       <c r="B720" s="2" t="s">
-        <v>932</v>
+        <v>923</v>
       </c>
       <c r="C720" s="2" t="s">
-        <v>1948</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="721" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A721" s="2" t="s">
-        <v>1949</v>
+        <v>1963</v>
       </c>
       <c r="B721" s="2" t="s">
-        <v>935</v>
+        <v>605</v>
       </c>
       <c r="C721" s="2" t="s">
-        <v>1950</v>
+        <v>476</v>
       </c>
     </row>
     <row r="722" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A722" s="2" t="s">
-        <v>1951</v>
+        <v>1964</v>
       </c>
       <c r="B722" s="2" t="s">
-        <v>938</v>
+        <v>927</v>
       </c>
       <c r="C722" s="2" t="s">
-        <v>1952</v>
+        <v>928</v>
       </c>
     </row>
     <row r="723" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A723" s="2" t="s">
-        <v>1953</v>
+        <v>1965</v>
       </c>
       <c r="B723" s="2" t="s">
-        <v>1954</v>
+        <v>303</v>
       </c>
       <c r="C723" s="2" t="s">
-        <v>1955</v>
+        <v>304</v>
       </c>
     </row>
     <row r="724" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A724" s="2" t="s">
-        <v>1956</v>
+        <v>1966</v>
       </c>
       <c r="B724" s="2" t="s">
-        <v>1789</v>
+        <v>1967</v>
       </c>
       <c r="C724" s="2" t="s">
-        <v>1790</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="725" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A725" s="2" t="s">
-        <v>1957</v>
+        <v>1969</v>
       </c>
       <c r="B725" s="2" t="s">
-        <v>1792</v>
+        <v>1970</v>
       </c>
       <c r="C725" s="2" t="s">
-        <v>1793</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="726" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A726" s="2" t="s">
-        <v>1958</v>
+        <v>1972</v>
       </c>
       <c r="B726" s="2" t="s">
-        <v>1959</v>
+        <v>1973</v>
       </c>
       <c r="C726" s="2" t="s">
-        <v>1960</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="727" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A727" s="2" t="s">
-        <v>1961</v>
+        <v>1975</v>
       </c>
       <c r="B727" s="2" t="s">
-        <v>1962</v>
+        <v>955</v>
       </c>
       <c r="C727" s="2" t="s">
-        <v>1963</v>
+        <v>956</v>
       </c>
     </row>
     <row r="728" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A728" s="2" t="s">
-        <v>1964</v>
+        <v>1976</v>
       </c>
       <c r="B728" s="2" t="s">
-        <v>1965</v>
+        <v>923</v>
       </c>
       <c r="C728" s="2" t="s">
-        <v>1966</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="729" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A729" s="2" t="s">
-        <v>1967</v>
+        <v>1977</v>
       </c>
       <c r="B729" s="2" t="s">
-        <v>1968</v>
+        <v>959</v>
       </c>
       <c r="C729" s="2" t="s">
-        <v>1969</v>
+        <v>960</v>
       </c>
     </row>
     <row r="730" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A730" s="2" t="s">
-        <v>1970</v>
+        <v>1978</v>
       </c>
       <c r="B730" s="2" t="s">
-        <v>1971</v>
+        <v>1979</v>
       </c>
       <c r="C730" s="2" t="s">
-        <v>1972</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="731" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A731" s="2" t="s">
-        <v>1973</v>
+        <v>1981</v>
       </c>
       <c r="B731" s="2" t="s">
-        <v>1974</v>
+        <v>965</v>
       </c>
       <c r="C731" s="2" t="s">
-        <v>1975</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="732" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A732" s="2" t="s">
-        <v>1976</v>
+        <v>1983</v>
       </c>
       <c r="B732" s="2" t="s">
-        <v>451</v>
+        <v>1984</v>
       </c>
       <c r="C732" s="2" t="s">
-        <v>452</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="733" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A733" s="2" t="s">
-        <v>1977</v>
+        <v>1986</v>
       </c>
       <c r="B733" s="2" t="s">
-        <v>1978</v>
+        <v>971</v>
       </c>
       <c r="C733" s="2" t="s">
-        <v>1979</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="734" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A734" s="2" t="s">
-        <v>1980</v>
+        <v>1988</v>
       </c>
       <c r="B734" s="2" t="s">
-        <v>1981</v>
+        <v>1989</v>
       </c>
       <c r="C734" s="2" t="s">
-        <v>1982</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="735" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A735" s="2" t="s">
-        <v>1983</v>
+        <v>1991</v>
       </c>
       <c r="B735" s="2" t="s">
-        <v>463</v>
+        <v>1992</v>
       </c>
       <c r="C735" s="2" t="s">
-        <v>551</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="736" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A736" s="2" t="s">
-        <v>1984</v>
+        <v>1994</v>
       </c>
       <c r="B736" s="2" t="s">
-        <v>469</v>
+        <v>1995</v>
       </c>
       <c r="C736" s="2" t="s">
-        <v>1985</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="737" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A737" s="2" t="s">
-        <v>1986</v>
+        <v>1997</v>
       </c>
       <c r="B737" s="2" t="s">
-        <v>502</v>
+        <v>795</v>
       </c>
       <c r="C737" s="2" t="s">
-        <v>1987</v>
+        <v>796</v>
       </c>
     </row>
     <row r="738" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A738" s="2" t="s">
-        <v>1988</v>
+        <v>1998</v>
       </c>
       <c r="B738" s="2" t="s">
-        <v>505</v>
+        <v>981</v>
       </c>
       <c r="C738" s="2" t="s">
-        <v>1989</v>
+        <v>982</v>
       </c>
     </row>
     <row r="739" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A739" s="2" t="s">
-        <v>1990</v>
+        <v>1999</v>
       </c>
       <c r="B739" s="2" t="s">
-        <v>1991</v>
+        <v>984</v>
       </c>
       <c r="C739" s="2" t="s">
-        <v>1992</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="740" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A740" s="2" t="s">
-        <v>1993</v>
+        <v>2001</v>
       </c>
       <c r="B740" s="2" t="s">
-        <v>1994</v>
+        <v>987</v>
       </c>
       <c r="C740" s="2" t="s">
-        <v>1995</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="741" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A741" s="2" t="s">
-        <v>1996</v>
+        <v>2003</v>
       </c>
       <c r="B741" s="2" t="s">
-        <v>1997</v>
+        <v>990</v>
       </c>
       <c r="C741" s="2" t="s">
-        <v>1998</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="742" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A742" s="2" t="s">
-        <v>1999</v>
+        <v>2005</v>
       </c>
       <c r="B742" s="2" t="s">
-        <v>472</v>
+        <v>2006</v>
       </c>
       <c r="C742" s="2" t="s">
-        <v>473</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="743" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A743" s="2" t="s">
-        <v>2000</v>
+        <v>2008</v>
       </c>
       <c r="B743" s="2" t="s">
-        <v>2001</v>
+        <v>1841</v>
       </c>
       <c r="C743" s="2" t="s">
-        <v>2002</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="744" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A744" s="2" t="s">
-        <v>2003</v>
+        <v>2009</v>
       </c>
       <c r="B744" s="2" t="s">
-        <v>484</v>
+        <v>1844</v>
       </c>
       <c r="C744" s="2" t="s">
-        <v>485</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="745" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A745" s="2" t="s">
-        <v>2004</v>
+        <v>2010</v>
       </c>
       <c r="B745" s="2" t="s">
-        <v>490</v>
+        <v>2011</v>
       </c>
       <c r="C745" s="2" t="s">
-        <v>491</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="746" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A746" s="2" t="s">
-        <v>2005</v>
+        <v>2013</v>
       </c>
       <c r="B746" s="2" t="s">
-        <v>2006</v>
+        <v>2014</v>
       </c>
       <c r="C746" s="2" t="s">
-        <v>2007</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="747" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A747" s="2" t="s">
-        <v>2008</v>
+        <v>2016</v>
       </c>
       <c r="B747" s="2" t="s">
-        <v>493</v>
+        <v>2017</v>
       </c>
       <c r="C747" s="2" t="s">
-        <v>218</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="748" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A748" s="2" t="s">
-        <v>2009</v>
+        <v>2019</v>
       </c>
       <c r="B748" s="2" t="s">
-        <v>496</v>
+        <v>2020</v>
       </c>
       <c r="C748" s="2" t="s">
-        <v>2010</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="749" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A749" s="2" t="s">
-        <v>2011</v>
+        <v>2022</v>
       </c>
       <c r="B749" s="2" t="s">
-        <v>538</v>
+        <v>2023</v>
       </c>
       <c r="C749" s="2" t="s">
-        <v>2012</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="750" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A750" s="2" t="s">
-        <v>2013</v>
+        <v>2025</v>
       </c>
       <c r="B750" s="2" t="s">
-        <v>2014</v>
+        <v>2026</v>
       </c>
       <c r="C750" s="2" t="s">
-        <v>2015</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="751" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A751" s="2" t="s">
-        <v>2016</v>
+        <v>2028</v>
       </c>
       <c r="B751" s="2" t="s">
-        <v>520</v>
+        <v>454</v>
       </c>
       <c r="C751" s="2" t="s">
-        <v>521</v>
+        <v>455</v>
       </c>
     </row>
     <row r="752" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A752" s="2" t="s">
-        <v>2017</v>
+        <v>2029</v>
       </c>
       <c r="B752" s="2" t="s">
-        <v>2018</v>
+        <v>2030</v>
       </c>
       <c r="C752" s="2" t="s">
-        <v>2019</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="753" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A753" s="2" t="s">
-        <v>2020</v>
+        <v>2032</v>
       </c>
       <c r="B753" s="2" t="s">
-        <v>2021</v>
+        <v>2033</v>
       </c>
       <c r="C753" s="2" t="s">
-        <v>2022</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="754" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A754" s="2" t="s">
-        <v>2023</v>
+        <v>2035</v>
       </c>
       <c r="B754" s="2" t="s">
-        <v>2024</v>
+        <v>466</v>
       </c>
       <c r="C754" s="2" t="s">
-        <v>530</v>
+        <v>603</v>
       </c>
     </row>
     <row r="755" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A755" s="2" t="s">
-        <v>2025</v>
+        <v>2036</v>
       </c>
       <c r="B755" s="2" t="s">
-        <v>2026</v>
+        <v>472</v>
       </c>
       <c r="C755" s="2" t="s">
-        <v>533</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="756" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A756" s="2" t="s">
-        <v>2027</v>
+        <v>2038</v>
       </c>
       <c r="B756" s="2" t="s">
-        <v>2028</v>
+        <v>505</v>
       </c>
       <c r="C756" s="2" t="s">
-        <v>2029</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="757" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A757" s="2" t="s">
-        <v>2030</v>
+        <v>2040</v>
       </c>
       <c r="B757" s="2" t="s">
-        <v>2031</v>
+        <v>508</v>
       </c>
       <c r="C757" s="2" t="s">
-        <v>2032</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="758" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A758" s="2" t="s">
-        <v>2033</v>
+        <v>2042</v>
       </c>
       <c r="B758" s="2" t="s">
-        <v>2034</v>
+        <v>2043</v>
       </c>
       <c r="C758" s="2" t="s">
-        <v>2035</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="759" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A759" s="2" t="s">
-        <v>2036</v>
+        <v>2045</v>
       </c>
       <c r="B759" s="2" t="s">
-        <v>2037</v>
+        <v>2046</v>
       </c>
       <c r="C759" s="2" t="s">
-        <v>2038</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="760" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A760" s="2" t="s">
-        <v>2039</v>
+        <v>2048</v>
       </c>
       <c r="B760" s="2" t="s">
-        <v>2040</v>
+        <v>2049</v>
       </c>
       <c r="C760" s="2" t="s">
-        <v>2041</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="761" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A761" s="2" t="s">
-        <v>2042</v>
+        <v>2051</v>
       </c>
       <c r="B761" s="2" t="s">
-        <v>2043</v>
+        <v>475</v>
       </c>
       <c r="C761" s="2" t="s">
-        <v>2044</v>
+        <v>476</v>
       </c>
     </row>
     <row r="762" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A762" s="2" t="s">
-        <v>2045</v>
+        <v>2052</v>
       </c>
       <c r="B762" s="2" t="s">
-        <v>2046</v>
+        <v>2053</v>
       </c>
       <c r="C762" s="2" t="s">
-        <v>2047</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="763" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A763" s="2" t="s">
-        <v>2048</v>
+        <v>2055</v>
       </c>
       <c r="B763" s="2" t="s">
-        <v>2049</v>
+        <v>487</v>
       </c>
       <c r="C763" s="2" t="s">
-        <v>2050</v>
+        <v>488</v>
       </c>
     </row>
     <row r="764" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A764" s="2" t="s">
-        <v>2051</v>
+        <v>2056</v>
       </c>
       <c r="B764" s="2" t="s">
-        <v>2052</v>
+        <v>493</v>
       </c>
       <c r="C764" s="2" t="s">
-        <v>2053</v>
+        <v>494</v>
       </c>
     </row>
     <row r="765" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A765" s="2" t="s">
-        <v>2054</v>
+        <v>2057</v>
       </c>
       <c r="B765" s="2" t="s">
-        <v>2055</v>
+        <v>2058</v>
       </c>
       <c r="C765" s="2" t="s">
-        <v>2056</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="766" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A766" s="2" t="s">
-        <v>2057</v>
+        <v>2060</v>
       </c>
       <c r="B766" s="2" t="s">
-        <v>2058</v>
+        <v>496</v>
       </c>
       <c r="C766" s="2" t="s">
-        <v>2059</v>
+        <v>221</v>
       </c>
     </row>
     <row r="767" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A767" s="2" t="s">
-        <v>2060</v>
+        <v>2061</v>
       </c>
       <c r="B767" s="2" t="s">
-        <v>2061</v>
+        <v>499</v>
       </c>
       <c r="C767" s="2" t="s">
         <v>2062</v>
@@ -15300,351 +15471,659 @@
         <v>2063</v>
       </c>
       <c r="B768" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="C768" s="2" t="s">
         <v>2064</v>
-      </c>
-      <c r="C768" s="2" t="s">
-        <v>2065</v>
       </c>
     </row>
     <row r="769" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A769" s="2" t="s">
+        <v>2065</v>
+      </c>
+      <c r="B769" s="2" t="s">
         <v>2066</v>
       </c>
-      <c r="B769" s="2" t="s">
+      <c r="C769" s="2" t="s">
         <v>2067</v>
-      </c>
-      <c r="C769" s="2" t="s">
-        <v>2068</v>
       </c>
     </row>
     <row r="770" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A770" s="2" t="s">
-        <v>2069</v>
+        <v>2068</v>
       </c>
       <c r="B770" s="2" t="s">
-        <v>2070</v>
+        <v>523</v>
       </c>
       <c r="C770" s="2" t="s">
-        <v>2071</v>
+        <v>524</v>
       </c>
     </row>
     <row r="771" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A771" s="2" t="s">
-        <v>2072</v>
+        <v>2069</v>
       </c>
       <c r="B771" s="2" t="s">
-        <v>2073</v>
+        <v>2070</v>
       </c>
       <c r="C771" s="2" t="s">
-        <v>1711</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="772" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A772" s="2" t="s">
+        <v>2072</v>
+      </c>
+      <c r="B772" s="2" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C772" s="2" t="s">
         <v>2074</v>
-      </c>
-      <c r="B772" s="2" t="s">
-        <v>2075</v>
-      </c>
-      <c r="C772" s="2" t="s">
-        <v>2076</v>
       </c>
     </row>
     <row r="773" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A773" s="2" t="s">
-        <v>2077</v>
+        <v>2075</v>
       </c>
       <c r="B773" s="2" t="s">
-        <v>2078</v>
+        <v>2076</v>
       </c>
       <c r="C773" s="2" t="s">
-        <v>2079</v>
+        <v>533</v>
       </c>
     </row>
     <row r="774" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A774" s="2" t="s">
-        <v>2080</v>
+        <v>2077</v>
       </c>
       <c r="B774" s="2" t="s">
-        <v>2081</v>
+        <v>2078</v>
       </c>
       <c r="C774" s="2" t="s">
-        <v>2082</v>
+        <v>536</v>
       </c>
     </row>
     <row r="775" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A775" s="2" t="s">
-        <v>2083</v>
+        <v>2079</v>
       </c>
       <c r="B775" s="2" t="s">
-        <v>2084</v>
+        <v>2080</v>
       </c>
       <c r="C775" s="2" t="s">
-        <v>226</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="776" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A776" s="2" t="s">
-        <v>2085</v>
+        <v>2082</v>
       </c>
       <c r="B776" s="2" t="s">
-        <v>2086</v>
+        <v>2083</v>
       </c>
       <c r="C776" s="2" t="s">
-        <v>2087</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="777" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A777" s="2" t="s">
-        <v>2088</v>
+        <v>2085</v>
       </c>
       <c r="B777" s="2" t="s">
-        <v>2089</v>
+        <v>547</v>
       </c>
       <c r="C777" s="2" t="s">
-        <v>2090</v>
+        <v>548</v>
       </c>
     </row>
     <row r="778" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A778" s="2" t="s">
-        <v>2091</v>
+        <v>2086</v>
       </c>
       <c r="B778" s="2" t="s">
-        <v>2092</v>
+        <v>2087</v>
       </c>
       <c r="C778" s="2" t="s">
-        <v>2093</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="779" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A779" s="2" t="s">
-        <v>2094</v>
+        <v>2089</v>
       </c>
       <c r="B779" s="2" t="s">
-        <v>2095</v>
+        <v>553</v>
       </c>
       <c r="C779" s="2" t="s">
-        <v>2096</v>
+        <v>554</v>
       </c>
     </row>
     <row r="780" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A780" s="2" t="s">
-        <v>2097</v>
+        <v>2090</v>
       </c>
       <c r="B780" s="2" t="s">
-        <v>2098</v>
+        <v>556</v>
       </c>
       <c r="C780" s="2" t="s">
-        <v>2099</v>
+        <v>557</v>
       </c>
     </row>
     <row r="781" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A781" s="2" t="s">
-        <v>2100</v>
+        <v>2091</v>
       </c>
       <c r="B781" s="2" t="s">
-        <v>2101</v>
+        <v>2092</v>
       </c>
       <c r="C781" s="2" t="s">
-        <v>2102</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="782" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A782" s="2" t="s">
-        <v>2103</v>
+        <v>2094</v>
       </c>
       <c r="B782" s="2" t="s">
-        <v>2104</v>
+        <v>2095</v>
       </c>
       <c r="C782" s="2" t="s">
-        <v>2105</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="783" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A783" s="2" t="s">
-        <v>2106</v>
+        <v>2097</v>
       </c>
       <c r="B783" s="2" t="s">
-        <v>2107</v>
+        <v>2098</v>
       </c>
       <c r="C783" s="2" t="s">
-        <v>2108</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="784" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A784" s="2" t="s">
-        <v>2109</v>
+        <v>2100</v>
       </c>
       <c r="B784" s="2" t="s">
-        <v>2110</v>
+        <v>2101</v>
       </c>
       <c r="C784" s="2" t="s">
-        <v>2111</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="785" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A785" s="2" t="s">
-        <v>2112</v>
+        <v>2103</v>
       </c>
       <c r="B785" s="2" t="s">
-        <v>2113</v>
+        <v>574</v>
       </c>
       <c r="C785" s="2" t="s">
-        <v>2114</v>
+        <v>575</v>
       </c>
     </row>
     <row r="786" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A786" s="2" t="s">
-        <v>2115</v>
+        <v>2104</v>
       </c>
       <c r="B786" s="2" t="s">
-        <v>2116</v>
+        <v>2105</v>
       </c>
       <c r="C786" s="2" t="s">
-        <v>2117</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="787" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A787" s="2" t="s">
-        <v>2118</v>
+        <v>2107</v>
       </c>
       <c r="B787" s="2" t="s">
-        <v>625</v>
+        <v>565</v>
       </c>
       <c r="C787" s="2" t="s">
-        <v>626</v>
+        <v>566</v>
       </c>
     </row>
     <row r="788" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A788" s="2" t="s">
-        <v>2119</v>
+        <v>2108</v>
       </c>
       <c r="B788" s="2" t="s">
-        <v>628</v>
+        <v>568</v>
       </c>
       <c r="C788" s="2" t="s">
-        <v>629</v>
+        <v>569</v>
       </c>
     </row>
     <row r="789" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A789" s="2" t="s">
-        <v>2120</v>
+        <v>2109</v>
       </c>
       <c r="B789" s="2" t="s">
-        <v>2121</v>
+        <v>581</v>
       </c>
       <c r="C789" s="2" t="s">
-        <v>2122</v>
+        <v>582</v>
       </c>
     </row>
     <row r="790" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A790" s="2" t="s">
-        <v>2123</v>
+        <v>2110</v>
       </c>
       <c r="B790" s="2" t="s">
-        <v>2124</v>
+        <v>584</v>
       </c>
       <c r="C790" s="2" t="s">
-        <v>2125</v>
+        <v>585</v>
       </c>
     </row>
     <row r="791" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A791" s="2" t="s">
-        <v>2126</v>
+        <v>2111</v>
       </c>
       <c r="B791" s="2" t="s">
-        <v>2127</v>
+        <v>587</v>
       </c>
       <c r="C791" s="2" t="s">
-        <v>2128</v>
+        <v>587</v>
       </c>
     </row>
     <row r="792" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A792" s="2" t="s">
-        <v>2129</v>
+        <v>2112</v>
       </c>
       <c r="B792" s="2" t="s">
-        <v>2130</v>
+        <v>589</v>
       </c>
       <c r="C792" s="2" t="s">
-        <v>2131</v>
+        <v>590</v>
       </c>
     </row>
     <row r="793" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A793" s="2" t="s">
-        <v>2132</v>
+        <v>2113</v>
       </c>
       <c r="B793" s="2" t="s">
-        <v>2133</v>
+        <v>578</v>
       </c>
       <c r="C793" s="2" t="s">
-        <v>2134</v>
+        <v>579</v>
       </c>
     </row>
     <row r="794" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A794" s="2" t="s">
-        <v>2135</v>
+        <v>2114</v>
       </c>
       <c r="B794" s="2" t="s">
-        <v>2136</v>
+        <v>2115</v>
       </c>
       <c r="C794" s="2" t="s">
-        <v>2137</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="795" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A795" s="2" t="s">
-        <v>2138</v>
+        <v>2117</v>
       </c>
       <c r="B795" s="2" t="s">
-        <v>2139</v>
+        <v>2118</v>
       </c>
       <c r="C795" s="2" t="s">
-        <v>2140</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="796" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A796" s="2" t="s">
-        <v>2141</v>
+        <v>2120</v>
       </c>
       <c r="B796" s="2" t="s">
-        <v>181</v>
+        <v>2121</v>
       </c>
       <c r="C796" s="2" t="s">
-        <v>182</v>
+        <v>2122</v>
       </c>
     </row>
     <row r="797" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A797" s="2" t="s">
-        <v>2142</v>
+        <v>2123</v>
       </c>
       <c r="B797" s="2" t="s">
-        <v>2143</v>
+        <v>2124</v>
       </c>
       <c r="C797" s="2" t="s">
-        <v>2144</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="798" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A798" s="2" t="s">
-        <v>2145</v>
+        <v>2126</v>
       </c>
       <c r="B798" s="2" t="s">
-        <v>2146</v>
+        <v>2127</v>
       </c>
       <c r="C798" s="2" t="s">
-        <v>2147</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="799" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A799" s="2" t="s">
+        <v>2129</v>
+      </c>
+      <c r="B799" s="2" t="s">
+        <v>2130</v>
+      </c>
+      <c r="C799" s="2" t="s">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="800" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A800" s="2" t="s">
+        <v>2131</v>
+      </c>
+      <c r="B800" s="2" t="s">
+        <v>2132</v>
+      </c>
+      <c r="C800" s="2" t="s">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="801" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A801" s="2" t="s">
+        <v>2134</v>
+      </c>
+      <c r="B801" s="2" t="s">
+        <v>2135</v>
+      </c>
+      <c r="C801" s="2" t="s">
+        <v>2136</v>
+      </c>
+    </row>
+    <row r="802" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A802" s="2" t="s">
+        <v>2137</v>
+      </c>
+      <c r="B802" s="2" t="s">
+        <v>2138</v>
+      </c>
+      <c r="C802" s="2" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="803" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A803" s="2" t="s">
+        <v>2140</v>
+      </c>
+      <c r="B803" s="2" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C803" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="804" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A804" s="2" t="s">
+        <v>2142</v>
+      </c>
+      <c r="B804" s="2" t="s">
+        <v>2143</v>
+      </c>
+      <c r="C804" s="2" t="s">
+        <v>2144</v>
+      </c>
+    </row>
+    <row r="805" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A805" s="2" t="s">
+        <v>2145</v>
+      </c>
+      <c r="B805" s="2" t="s">
+        <v>2146</v>
+      </c>
+      <c r="C805" s="2" t="s">
+        <v>2147</v>
+      </c>
+    </row>
+    <row r="806" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A806" s="2" t="s">
         <v>2148</v>
       </c>
-      <c r="B799" s="2" t="s">
+      <c r="B806" s="2" t="s">
         <v>2149</v>
       </c>
-      <c r="C799" s="2" t="s">
+      <c r="C806" s="2" t="s">
         <v>2150</v>
+      </c>
+    </row>
+    <row r="807" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A807" s="2" t="s">
+        <v>2151</v>
+      </c>
+      <c r="B807" s="2" t="s">
+        <v>2152</v>
+      </c>
+      <c r="C807" s="2" t="s">
+        <v>2153</v>
+      </c>
+    </row>
+    <row r="808" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A808" s="2" t="s">
+        <v>2154</v>
+      </c>
+      <c r="B808" s="2" t="s">
+        <v>2155</v>
+      </c>
+      <c r="C808" s="2" t="s">
+        <v>2156</v>
+      </c>
+    </row>
+    <row r="809" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A809" s="2" t="s">
+        <v>2157</v>
+      </c>
+      <c r="B809" s="2" t="s">
+        <v>2158</v>
+      </c>
+      <c r="C809" s="2" t="s">
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="810" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A810" s="2" t="s">
+        <v>2160</v>
+      </c>
+      <c r="B810" s="2" t="s">
+        <v>2161</v>
+      </c>
+      <c r="C810" s="2" t="s">
+        <v>2162</v>
+      </c>
+    </row>
+    <row r="811" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A811" s="2" t="s">
+        <v>2163</v>
+      </c>
+      <c r="B811" s="2" t="s">
+        <v>2164</v>
+      </c>
+      <c r="C811" s="2" t="s">
+        <v>2165</v>
+      </c>
+    </row>
+    <row r="812" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A812" s="2" t="s">
+        <v>2166</v>
+      </c>
+      <c r="B812" s="2" t="s">
+        <v>2167</v>
+      </c>
+      <c r="C812" s="2" t="s">
+        <v>2168</v>
+      </c>
+    </row>
+    <row r="813" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A813" s="2" t="s">
+        <v>2169</v>
+      </c>
+      <c r="B813" s="2" t="s">
+        <v>2170</v>
+      </c>
+      <c r="C813" s="2" t="s">
+        <v>2171</v>
+      </c>
+    </row>
+    <row r="814" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A814" s="2" t="s">
+        <v>2172</v>
+      </c>
+      <c r="B814" s="2" t="s">
+        <v>2173</v>
+      </c>
+      <c r="C814" s="2" t="s">
+        <v>2174</v>
+      </c>
+    </row>
+    <row r="815" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A815" s="2" t="s">
+        <v>2175</v>
+      </c>
+      <c r="B815" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="C815" s="2" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="816" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A816" s="2" t="s">
+        <v>2176</v>
+      </c>
+      <c r="B816" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="C816" s="2" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="817" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A817" s="2" t="s">
+        <v>2177</v>
+      </c>
+      <c r="B817" s="2" t="s">
+        <v>2178</v>
+      </c>
+      <c r="C817" s="2" t="s">
+        <v>2179</v>
+      </c>
+    </row>
+    <row r="818" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A818" s="2" t="s">
+        <v>2180</v>
+      </c>
+      <c r="B818" s="2" t="s">
+        <v>2181</v>
+      </c>
+      <c r="C818" s="2" t="s">
+        <v>2182</v>
+      </c>
+    </row>
+    <row r="819" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A819" s="2" t="s">
+        <v>2183</v>
+      </c>
+      <c r="B819" s="2" t="s">
+        <v>2184</v>
+      </c>
+      <c r="C819" s="2" t="s">
+        <v>2185</v>
+      </c>
+    </row>
+    <row r="820" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A820" s="2" t="s">
+        <v>2186</v>
+      </c>
+      <c r="B820" s="2" t="s">
+        <v>2187</v>
+      </c>
+      <c r="C820" s="2" t="s">
+        <v>2188</v>
+      </c>
+    </row>
+    <row r="821" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A821" s="2" t="s">
+        <v>2189</v>
+      </c>
+      <c r="B821" s="2" t="s">
+        <v>2190</v>
+      </c>
+      <c r="C821" s="2" t="s">
+        <v>2191</v>
+      </c>
+    </row>
+    <row r="822" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A822" s="2" t="s">
+        <v>2192</v>
+      </c>
+      <c r="B822" s="2" t="s">
+        <v>2193</v>
+      </c>
+      <c r="C822" s="2" t="s">
+        <v>2194</v>
+      </c>
+    </row>
+    <row r="823" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A823" s="2" t="s">
+        <v>2195</v>
+      </c>
+      <c r="B823" s="2" t="s">
+        <v>2196</v>
+      </c>
+      <c r="C823" s="2" t="s">
+        <v>2197</v>
+      </c>
+    </row>
+    <row r="824" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A824" s="2" t="s">
+        <v>2198</v>
+      </c>
+      <c r="B824" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C824" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="825" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A825" s="2" t="s">
+        <v>2199</v>
+      </c>
+      <c r="B825" s="2" t="s">
+        <v>2200</v>
+      </c>
+      <c r="C825" s="2" t="s">
+        <v>2201</v>
+      </c>
+    </row>
+    <row r="826" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A826" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="B826" s="2" t="s">
+        <v>2203</v>
+      </c>
+      <c r="C826" s="2" t="s">
+        <v>2204</v>
+      </c>
+    </row>
+    <row r="827" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A827" s="2" t="s">
+        <v>2205</v>
+      </c>
+      <c r="B827" s="2" t="s">
+        <v>2206</v>
+      </c>
+      <c r="C827" s="2" t="s">
+        <v>2207</v>
       </c>
     </row>
   </sheetData>

--- a/apps/workspace-web/i18n.xlsx
+++ b/apps/workspace-web/i18n.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2481" uniqueCount="2208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2496" uniqueCount="2219">
   <si>
     <t>key</t>
   </si>
@@ -553,6 +553,15 @@
     <t>Failed to add YouTube video.</t>
   </si>
   <si>
+    <t>storeError.reorderMediaFailed</t>
+  </si>
+  <si>
+    <t>更新預覽媒體排序失敗。</t>
+  </si>
+  <si>
+    <t>Failed to update preview media order.</t>
+  </si>
+  <si>
     <t>storeError.createVersionFailed</t>
   </si>
   <si>
@@ -1690,10 +1699,28 @@
     <t>upload.mediaHint</t>
   </si>
   <si>
-    <t>圖片支援 JPG / PNG / GIF / WebP（單檔 5 MB）；影片支援 MP4 / MOV / AVI / WebM（單檔 100 MB）。最多 {max} 項，依加入順序顯示。</t>
-  </si>
-  <si>
-    <t>Images: JPG / PNG / GIF / WebP (5 MB each). Videos: MP4 / MOV / AVI / WebM (100 MB each). Max {max} items, shown in the order added.</t>
+    <t>圖片支援 JPG / PNG / GIF / WebP（單檔 5 MB）；影片支援 MP4 / MOV / AVI / WebM（單檔 100 MB）。最多 {max} 項，可用磚上箭頭調整顯示順序。</t>
+  </si>
+  <si>
+    <t>Images: JPG / PNG / GIF / WebP (5 MB each). Videos: MP4 / MOV / AVI / WebM (100 MB each). Max {max} items; use the arrows on each tile to reorder.</t>
+  </si>
+  <si>
+    <t>upload.mediaMoveForward</t>
+  </si>
+  <si>
+    <t>前移</t>
+  </si>
+  <si>
+    <t>Move forward</t>
+  </si>
+  <si>
+    <t>upload.mediaMoveBackward</t>
+  </si>
+  <si>
+    <t>後移</t>
+  </si>
+  <si>
+    <t>Move backward</t>
   </si>
   <si>
     <t>upload.msgMediaLimit</t>
@@ -6295,6 +6322,12 @@
   </si>
   <si>
     <t>Delete this preview media?</t>
+  </si>
+  <si>
+    <t>productEdit.mediaMoveForward</t>
+  </si>
+  <si>
+    <t>productEdit.mediaMoveBackward</t>
   </si>
   <si>
     <t>productEdit.mediaHint</t>
@@ -7022,7 +7055,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C827"/>
+  <dimension ref="A1:C832"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -7738,21 +7771,21 @@
         <v>192</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>43</v>
+        <v>193</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>44</v>
+        <v>194</v>
       </c>
     </row>
     <row r="66" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>194</v>
+        <v>43</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>195</v>
+        <v>44</v>
       </c>
     </row>
     <row r="67" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7796,15 +7829,15 @@
         <v>206</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="71" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>209</v>
@@ -7873,18 +7906,18 @@
         <v>226</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
     </row>
     <row r="78" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>229</v>
+        <v>198</v>
       </c>
     </row>
     <row r="79" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8244,21 +8277,21 @@
         <v>326</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>28</v>
+        <v>327</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>29</v>
+        <v>328</v>
       </c>
     </row>
     <row r="112" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>328</v>
+        <v>28</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>329</v>
+        <v>29</v>
       </c>
     </row>
     <row r="113" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8398,21 +8431,21 @@
         <v>366</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>303</v>
+        <v>367</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>304</v>
+        <v>368</v>
       </c>
     </row>
     <row r="126" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>368</v>
+        <v>306</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>369</v>
+        <v>307</v>
       </c>
     </row>
     <row r="127" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8684,21 +8717,21 @@
         <v>442</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>389</v>
+        <v>443</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>390</v>
+        <v>444</v>
       </c>
     </row>
     <row r="152" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>444</v>
+        <v>392</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>445</v>
+        <v>393</v>
       </c>
     </row>
     <row r="153" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8728,21 +8761,21 @@
         <v>452</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>315</v>
+        <v>453</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>316</v>
+        <v>454</v>
       </c>
     </row>
     <row r="156" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>454</v>
+        <v>318</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>455</v>
+        <v>319</v>
       </c>
     </row>
     <row r="157" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9190,43 +9223,43 @@
         <v>576</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>178</v>
+        <v>577</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>179</v>
+        <v>578</v>
       </c>
     </row>
     <row r="198" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="199" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="200" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>584</v>
+        <v>178</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>585</v>
+        <v>179</v>
       </c>
     </row>
     <row r="201" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9237,62 +9270,62 @@
         <v>587</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="202" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="203" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>547</v>
+        <v>593</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>548</v>
+        <v>594</v>
       </c>
     </row>
     <row r="204" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="205" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="206" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>599</v>
+        <v>550</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>600</v>
+        <v>551</v>
       </c>
     </row>
     <row r="207" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9314,95 +9347,95 @@
         <v>605</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>476</v>
+        <v>606</v>
       </c>
     </row>
     <row r="209" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>487</v>
+        <v>608</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>488</v>
+        <v>609</v>
       </c>
     </row>
     <row r="210" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>496</v>
+        <v>611</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>221</v>
+        <v>612</v>
       </c>
     </row>
     <row r="211" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>610</v>
+        <v>479</v>
       </c>
     </row>
     <row r="212" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>612</v>
+        <v>490</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>613</v>
+        <v>491</v>
       </c>
     </row>
     <row r="213" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>523</v>
+        <v>499</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>524</v>
+        <v>224</v>
       </c>
     </row>
     <row r="214" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="215" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="216" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>622</v>
+        <v>526</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>623</v>
+        <v>527</v>
       </c>
     </row>
     <row r="217" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9432,43 +9465,43 @@
         <v>630</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>22</v>
+        <v>631</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>23</v>
+        <v>632</v>
       </c>
     </row>
     <row r="220" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="221" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="222" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>638</v>
+        <v>22</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>639</v>
+        <v>23</v>
       </c>
     </row>
     <row r="223" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9498,40 +9531,40 @@
         <v>646</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>487</v>
+        <v>647</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="226" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="227" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="228" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>655</v>
+        <v>490</v>
       </c>
       <c r="C228" s="2" t="s">
         <v>656</v>
@@ -9608,43 +9641,43 @@
         <v>675</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>184</v>
+        <v>676</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>185</v>
+        <v>677</v>
       </c>
     </row>
     <row r="236" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="237" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="238" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>683</v>
+        <v>187</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>684</v>
+        <v>188</v>
       </c>
     </row>
     <row r="239" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9740,65 +9773,65 @@
         <v>709</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>206</v>
+        <v>710</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>206</v>
+        <v>711</v>
       </c>
     </row>
     <row r="248" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
     </row>
     <row r="249" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>203</v>
+        <v>716</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>204</v>
+        <v>717</v>
       </c>
     </row>
     <row r="250" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>715</v>
+        <v>209</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>716</v>
+        <v>209</v>
       </c>
     </row>
     <row r="251" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
     </row>
     <row r="252" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>721</v>
+        <v>206</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>722</v>
+        <v>207</v>
       </c>
     </row>
     <row r="253" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9861,65 +9894,65 @@
         <v>738</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>355</v>
+        <v>739</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>356</v>
+        <v>740</v>
       </c>
     </row>
     <row r="259" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
     </row>
     <row r="260" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>358</v>
+        <v>745</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>359</v>
+        <v>746</v>
       </c>
     </row>
     <row r="261" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>744</v>
+        <v>358</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>745</v>
+        <v>359</v>
       </c>
     </row>
     <row r="262" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
     </row>
     <row r="263" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>750</v>
+        <v>361</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>751</v>
+        <v>362</v>
       </c>
     </row>
     <row r="264" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10048,65 +10081,65 @@
         <v>785</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>355</v>
+        <v>786</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>356</v>
+        <v>787</v>
       </c>
     </row>
     <row r="276" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>740</v>
+        <v>789</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>741</v>
+        <v>790</v>
       </c>
     </row>
     <row r="277" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>358</v>
+        <v>792</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>359</v>
+        <v>793</v>
       </c>
     </row>
     <row r="278" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
-        <v>788</v>
+        <v>794</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>789</v>
+        <v>358</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>790</v>
+        <v>359</v>
       </c>
     </row>
     <row r="279" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>792</v>
+        <v>749</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>793</v>
+        <v>750</v>
       </c>
     </row>
     <row r="280" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>795</v>
+        <v>361</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>796</v>
+        <v>362</v>
       </c>
     </row>
     <row r="281" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10158,43 +10191,43 @@
         <v>809</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>692</v>
+        <v>810</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>693</v>
+        <v>811</v>
       </c>
     </row>
     <row r="286" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
     </row>
     <row r="287" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
     </row>
     <row r="288" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>817</v>
+        <v>701</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>818</v>
+        <v>702</v>
       </c>
     </row>
     <row r="289" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10268,43 +10301,43 @@
         <v>837</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>22</v>
+        <v>838</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>23</v>
+        <v>839</v>
       </c>
     </row>
     <row r="296" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
     </row>
     <row r="297" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
     </row>
     <row r="298" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>845</v>
+        <v>22</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>846</v>
+        <v>23</v>
       </c>
     </row>
     <row r="299" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10598,65 +10631,65 @@
         <v>925</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>605</v>
+        <v>926</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>476</v>
+        <v>927</v>
       </c>
     </row>
     <row r="326" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
     </row>
     <row r="327" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>303</v>
+        <v>932</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>304</v>
+        <v>933</v>
       </c>
     </row>
     <row r="328" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
-        <v>930</v>
+        <v>934</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>931</v>
+        <v>614</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>932</v>
+        <v>479</v>
       </c>
     </row>
     <row r="329" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
     </row>
     <row r="330" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>937</v>
+        <v>306</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>938</v>
+        <v>307</v>
       </c>
     </row>
     <row r="331" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10730,43 +10763,43 @@
         <v>957</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>923</v>
+        <v>958</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>924</v>
+        <v>959</v>
       </c>
     </row>
     <row r="338" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
     </row>
     <row r="339" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
     </row>
     <row r="340" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>965</v>
+        <v>932</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>966</v>
+        <v>933</v>
       </c>
     </row>
     <row r="341" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10818,43 +10851,43 @@
         <v>979</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>795</v>
+        <v>980</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>796</v>
+        <v>981</v>
       </c>
     </row>
     <row r="346" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
     </row>
     <row r="347" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
     </row>
     <row r="348" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>987</v>
+        <v>804</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>988</v>
+        <v>805</v>
       </c>
     </row>
     <row r="349" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10884,43 +10917,43 @@
         <v>995</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>52</v>
+        <v>996</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>53</v>
+        <v>997</v>
       </c>
     </row>
     <row r="352" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="353" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="354" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>1003</v>
+        <v>52</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>1004</v>
+        <v>53</v>
       </c>
     </row>
     <row r="355" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11085,51 +11118,51 @@
         <v>1048</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="370" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>437</v>
+        <v>1051</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>438</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="371" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="372" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="373" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>1057</v>
+        <v>440</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>1058</v>
+        <v>441</v>
       </c>
     </row>
     <row r="374" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11206,37 +11239,37 @@
         <v>1078</v>
       </c>
       <c r="C380" s="2" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="381" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A381" s="2" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="B381" s="2" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="C381" s="2" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="382" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A382" s="2" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="C382" s="2" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="383" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A383" s="2" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="C383" s="2" t="s">
         <v>1087</v>
@@ -11544,87 +11577,87 @@
         <v>1169</v>
       </c>
       <c r="B411" s="2" t="s">
-        <v>315</v>
+        <v>1170</v>
       </c>
       <c r="C411" s="2" t="s">
-        <v>316</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="412" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A412" s="2" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="B412" s="2" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="C412" s="2" t="s">
-        <v>712</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="413" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A413" s="2" t="s">
-        <v>1172</v>
+        <v>1175</v>
       </c>
       <c r="B413" s="2" t="s">
-        <v>1173</v>
+        <v>1176</v>
       </c>
       <c r="C413" s="2" t="s">
-        <v>1174</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="414" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A414" s="2" t="s">
-        <v>1175</v>
+        <v>1178</v>
       </c>
       <c r="B414" s="2" t="s">
-        <v>1176</v>
+        <v>318</v>
       </c>
       <c r="C414" s="2" t="s">
-        <v>1177</v>
+        <v>319</v>
       </c>
     </row>
     <row r="415" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A415" s="2" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>203</v>
+        <v>1180</v>
       </c>
       <c r="C415" s="2" t="s">
-        <v>204</v>
+        <v>721</v>
       </c>
     </row>
     <row r="416" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A416" s="2" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="B416" s="2" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="C416" s="2" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="417" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A417" s="2" t="s">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="B417" s="2" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="C417" s="2" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="418" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A418" s="2" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="B418" s="2" t="s">
-        <v>1186</v>
+        <v>206</v>
       </c>
       <c r="C418" s="2" t="s">
-        <v>1187</v>
+        <v>207</v>
       </c>
     </row>
     <row r="419" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11687,54 +11720,54 @@
         <v>1203</v>
       </c>
       <c r="B424" s="2" t="s">
-        <v>297</v>
+        <v>1204</v>
       </c>
       <c r="C424" s="2" t="s">
-        <v>298</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="425" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A425" s="2" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="B425" s="2" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="C425" s="2" t="s">
-        <v>1190</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="426" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A426" s="2" t="s">
-        <v>1206</v>
+        <v>1209</v>
       </c>
       <c r="B426" s="2" t="s">
-        <v>1207</v>
+        <v>1210</v>
       </c>
       <c r="C426" s="2" t="s">
-        <v>1208</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="427" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A427" s="2" t="s">
-        <v>1209</v>
+        <v>1212</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>1210</v>
+        <v>300</v>
       </c>
       <c r="C427" s="2" t="s">
-        <v>1211</v>
+        <v>301</v>
       </c>
     </row>
     <row r="428" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A428" s="2" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="B428" s="2" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="C428" s="2" t="s">
-        <v>1214</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="429" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11764,43 +11797,43 @@
         <v>1221</v>
       </c>
       <c r="B431" s="2" t="s">
-        <v>315</v>
+        <v>1222</v>
       </c>
       <c r="C431" s="2" t="s">
-        <v>316</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="432" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A432" s="2" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="B432" s="2" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="C432" s="2" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="433" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A433" s="2" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="C433" s="2" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="434" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A434" s="2" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="B434" s="2" t="s">
-        <v>1229</v>
+        <v>318</v>
       </c>
       <c r="C434" s="2" t="s">
-        <v>1230</v>
+        <v>319</v>
       </c>
     </row>
     <row r="435" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11951,40 +11984,40 @@
         <v>1270</v>
       </c>
       <c r="B448" s="2" t="s">
-        <v>371</v>
+        <v>1271</v>
       </c>
       <c r="C448" s="2" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="449" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A449" s="2" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="B449" s="2" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="C449" s="2" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="450" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A450" s="2" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B450" s="2" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="C450" s="2" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="451" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A451" s="2" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="B451" s="2" t="s">
-        <v>1279</v>
+        <v>374</v>
       </c>
       <c r="C451" s="2" t="s">
         <v>1280</v>
@@ -12193,285 +12226,285 @@
         <v>1335</v>
       </c>
       <c r="B470" s="2" t="s">
-        <v>1051</v>
+        <v>1336</v>
       </c>
       <c r="C470" s="2" t="s">
-        <v>1052</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="471" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A471" s="2" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
       <c r="B471" s="2" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
       <c r="C471" s="2" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="472" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A472" s="2" t="s">
-        <v>1339</v>
+        <v>1341</v>
       </c>
       <c r="B472" s="2" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="C472" s="2" t="s">
-        <v>1341</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="473" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A473" s="2" t="s">
-        <v>1342</v>
+        <v>1344</v>
       </c>
       <c r="B473" s="2" t="s">
-        <v>1343</v>
+        <v>1060</v>
       </c>
       <c r="C473" s="2" t="s">
-        <v>195</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="474" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A474" s="2" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="B474" s="2" t="s">
-        <v>197</v>
+        <v>1346</v>
       </c>
       <c r="C474" s="2" t="s">
-        <v>198</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="475" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A475" s="2" t="s">
-        <v>1345</v>
+        <v>1348</v>
       </c>
       <c r="B475" s="2" t="s">
-        <v>1346</v>
+        <v>1349</v>
       </c>
       <c r="C475" s="2" t="s">
-        <v>1347</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="476" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A476" s="2" t="s">
-        <v>1348</v>
+        <v>1351</v>
       </c>
       <c r="B476" s="2" t="s">
-        <v>203</v>
+        <v>1352</v>
       </c>
       <c r="C476" s="2" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
     </row>
     <row r="477" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A477" s="2" t="s">
-        <v>1349</v>
+        <v>1353</v>
       </c>
       <c r="B477" s="2" t="s">
-        <v>1350</v>
+        <v>200</v>
       </c>
       <c r="C477" s="2" t="s">
-        <v>1351</v>
+        <v>201</v>
       </c>
     </row>
     <row r="478" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A478" s="2" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
       <c r="B478" s="2" t="s">
-        <v>303</v>
+        <v>1355</v>
       </c>
       <c r="C478" s="2" t="s">
-        <v>304</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="479" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A479" s="2" t="s">
-        <v>1353</v>
+        <v>1357</v>
       </c>
       <c r="B479" s="2" t="s">
-        <v>1354</v>
+        <v>206</v>
       </c>
       <c r="C479" s="2" t="s">
-        <v>1355</v>
+        <v>207</v>
       </c>
     </row>
     <row r="480" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A480" s="2" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
       <c r="B480" s="2" t="s">
-        <v>1164</v>
+        <v>1359</v>
       </c>
       <c r="C480" s="2" t="s">
-        <v>1357</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="481" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A481" s="2" t="s">
-        <v>1358</v>
+        <v>1361</v>
       </c>
       <c r="B481" s="2" t="s">
-        <v>324</v>
+        <v>306</v>
       </c>
       <c r="C481" s="2" t="s">
-        <v>325</v>
+        <v>307</v>
       </c>
     </row>
     <row r="482" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A482" s="2" t="s">
-        <v>1359</v>
+        <v>1362</v>
       </c>
       <c r="B482" s="2" t="s">
-        <v>318</v>
+        <v>1363</v>
       </c>
       <c r="C482" s="2" t="s">
-        <v>319</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="483" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A483" s="2" t="s">
-        <v>1360</v>
+        <v>1365</v>
       </c>
       <c r="B483" s="2" t="s">
-        <v>1361</v>
+        <v>1173</v>
       </c>
       <c r="C483" s="2" t="s">
-        <v>1362</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="484" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A484" s="2" t="s">
-        <v>1363</v>
+        <v>1367</v>
       </c>
       <c r="B484" s="2" t="s">
-        <v>1364</v>
+        <v>327</v>
       </c>
       <c r="C484" s="2" t="s">
-        <v>1365</v>
+        <v>328</v>
       </c>
     </row>
     <row r="485" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A485" s="2" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
       <c r="B485" s="2" t="s">
-        <v>334</v>
+        <v>321</v>
       </c>
       <c r="C485" s="2" t="s">
-        <v>335</v>
+        <v>322</v>
       </c>
     </row>
     <row r="486" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A486" s="2" t="s">
-        <v>1367</v>
+        <v>1369</v>
       </c>
       <c r="B486" s="2" t="s">
-        <v>1368</v>
+        <v>1370</v>
       </c>
       <c r="C486" s="2" t="s">
-        <v>1369</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="487" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A487" s="2" t="s">
-        <v>1370</v>
+        <v>1372</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>340</v>
+        <v>1373</v>
       </c>
       <c r="C487" s="2" t="s">
-        <v>341</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="488" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A488" s="2" t="s">
-        <v>1371</v>
+        <v>1375</v>
       </c>
       <c r="B488" s="2" t="s">
-        <v>1372</v>
+        <v>337</v>
       </c>
       <c r="C488" s="2" t="s">
-        <v>1373</v>
+        <v>338</v>
       </c>
     </row>
     <row r="489" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A489" s="2" t="s">
-        <v>1374</v>
+        <v>1376</v>
       </c>
       <c r="B489" s="2" t="s">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="C489" s="2" t="s">
-        <v>1375</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="490" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A490" s="2" t="s">
-        <v>1376</v>
+        <v>1379</v>
       </c>
       <c r="B490" s="2" t="s">
-        <v>1377</v>
+        <v>343</v>
       </c>
       <c r="C490" s="2" t="s">
-        <v>1377</v>
+        <v>344</v>
       </c>
     </row>
     <row r="491" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A491" s="2" t="s">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="B491" s="2" t="s">
-        <v>1379</v>
+        <v>1381</v>
       </c>
       <c r="C491" s="2" t="s">
-        <v>1380</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="492" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A492" s="2" t="s">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="B492" s="2" t="s">
-        <v>1379</v>
+        <v>1384</v>
       </c>
       <c r="C492" s="2" t="s">
-        <v>1380</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="493" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A493" s="2" t="s">
-        <v>1382</v>
+        <v>1385</v>
       </c>
       <c r="B493" s="2" t="s">
-        <v>1383</v>
+        <v>1386</v>
       </c>
       <c r="C493" s="2" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="494" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A494" s="2" t="s">
-        <v>1385</v>
+        <v>1387</v>
       </c>
       <c r="B494" s="2" t="s">
-        <v>1386</v>
+        <v>1388</v>
       </c>
       <c r="C494" s="2" t="s">
-        <v>1387</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="495" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A495" s="2" t="s">
+        <v>1390</v>
+      </c>
+      <c r="B495" s="2" t="s">
         <v>1388</v>
       </c>
-      <c r="B495" s="2" t="s">
+      <c r="C495" s="2" t="s">
         <v>1389</v>
-      </c>
-      <c r="C495" s="2" t="s">
-        <v>1390</v>
       </c>
     </row>
     <row r="496" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12592,73 +12625,73 @@
         <v>1422</v>
       </c>
       <c r="C506" s="2" t="s">
-        <v>1399</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="507" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A507" s="2" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="C507" s="2" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="508" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A508" s="2" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="B508" s="2" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="C508" s="2" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="509" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A509" s="2" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="B509" s="2" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="C509" s="2" t="s">
-        <v>1405</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="510" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A510" s="2" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="B510" s="2" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="C510" s="2" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="511" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A511" s="2" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="C511" s="2" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="512" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A512" s="2" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="B512" s="2" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="C512" s="2" t="s">
-        <v>1439</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="513" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12666,43 +12699,43 @@
         <v>1440</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>1292</v>
+        <v>1441</v>
       </c>
       <c r="C513" s="2" t="s">
-        <v>1292</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="514" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A514" s="2" t="s">
-        <v>1441</v>
+        <v>1443</v>
       </c>
       <c r="B514" s="2" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="C514" s="2" t="s">
-        <v>1443</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="515" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A515" s="2" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="B515" s="2" t="s">
-        <v>1445</v>
+        <v>1447</v>
       </c>
       <c r="C515" s="2" t="s">
-        <v>1446</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="516" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A516" s="2" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="B516" s="2" t="s">
-        <v>1448</v>
+        <v>1301</v>
       </c>
       <c r="C516" s="2" t="s">
-        <v>1449</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="517" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12765,43 +12798,43 @@
         <v>1465</v>
       </c>
       <c r="B522" s="2" t="s">
-        <v>1327</v>
+        <v>1466</v>
       </c>
       <c r="C522" s="2" t="s">
-        <v>1328</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="523" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A523" s="2" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="B523" s="2" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="C523" s="2" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="524" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A524" s="2" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="B524" s="2" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="C524" s="2" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="525" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A525" s="2" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="B525" s="2" t="s">
-        <v>1473</v>
+        <v>1336</v>
       </c>
       <c r="C525" s="2" t="s">
-        <v>1474</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="526" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12845,73 +12878,73 @@
         <v>1485</v>
       </c>
       <c r="C529" s="2" t="s">
-        <v>229</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="530" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A530" s="2" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="B530" s="2" t="s">
-        <v>197</v>
+        <v>1488</v>
       </c>
       <c r="C530" s="2" t="s">
-        <v>198</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="531" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A531" s="2" t="s">
-        <v>1487</v>
+        <v>1490</v>
       </c>
       <c r="B531" s="2" t="s">
-        <v>200</v>
+        <v>1491</v>
       </c>
       <c r="C531" s="2" t="s">
-        <v>201</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="532" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A532" s="2" t="s">
-        <v>1488</v>
+        <v>1493</v>
       </c>
       <c r="B532" s="2" t="s">
-        <v>698</v>
+        <v>1494</v>
       </c>
       <c r="C532" s="2" t="s">
-        <v>699</v>
+        <v>232</v>
       </c>
     </row>
     <row r="533" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A533" s="2" t="s">
-        <v>1489</v>
+        <v>1495</v>
       </c>
       <c r="B533" s="2" t="s">
-        <v>1490</v>
+        <v>200</v>
       </c>
       <c r="C533" s="2" t="s">
-        <v>1491</v>
+        <v>201</v>
       </c>
     </row>
     <row r="534" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A534" s="2" t="s">
-        <v>1492</v>
+        <v>1496</v>
       </c>
       <c r="B534" s="2" t="s">
-        <v>1493</v>
+        <v>203</v>
       </c>
       <c r="C534" s="2" t="s">
-        <v>1494</v>
+        <v>204</v>
       </c>
     </row>
     <row r="535" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A535" s="2" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="B535" s="2" t="s">
-        <v>1496</v>
+        <v>707</v>
       </c>
       <c r="C535" s="2" t="s">
-        <v>1497</v>
+        <v>708</v>
       </c>
     </row>
     <row r="536" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13095,109 +13128,109 @@
         <v>1546</v>
       </c>
       <c r="B552" s="2" t="s">
-        <v>43</v>
+        <v>1547</v>
       </c>
       <c r="C552" s="2" t="s">
-        <v>44</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="553" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A553" s="2" t="s">
-        <v>1547</v>
+        <v>1549</v>
       </c>
       <c r="B553" s="2" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="C553" s="2" t="s">
-        <v>1174</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="554" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A554" s="2" t="s">
-        <v>1549</v>
+        <v>1552</v>
       </c>
       <c r="B554" s="2" t="s">
-        <v>1490</v>
+        <v>1553</v>
       </c>
       <c r="C554" s="2" t="s">
-        <v>1491</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="555" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A555" s="2" t="s">
-        <v>1550</v>
+        <v>1555</v>
       </c>
       <c r="B555" s="2" t="s">
-        <v>1551</v>
+        <v>43</v>
       </c>
       <c r="C555" s="2" t="s">
-        <v>1283</v>
+        <v>44</v>
       </c>
     </row>
     <row r="556" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A556" s="2" t="s">
-        <v>1552</v>
+        <v>1556</v>
       </c>
       <c r="B556" s="2" t="s">
-        <v>1553</v>
+        <v>1557</v>
       </c>
       <c r="C556" s="2" t="s">
-        <v>1554</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="557" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A557" s="2" t="s">
-        <v>1555</v>
+        <v>1558</v>
       </c>
       <c r="B557" s="2" t="s">
-        <v>1493</v>
+        <v>1499</v>
       </c>
       <c r="C557" s="2" t="s">
-        <v>1494</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="558" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A558" s="2" t="s">
-        <v>1556</v>
+        <v>1559</v>
       </c>
       <c r="B558" s="2" t="s">
-        <v>206</v>
+        <v>1560</v>
       </c>
       <c r="C558" s="2" t="s">
-        <v>206</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="559" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A559" s="2" t="s">
-        <v>1557</v>
+        <v>1561</v>
       </c>
       <c r="B559" s="2" t="s">
-        <v>1558</v>
+        <v>1562</v>
       </c>
       <c r="C559" s="2" t="s">
-        <v>1559</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="560" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A560" s="2" t="s">
-        <v>1560</v>
+        <v>1564</v>
       </c>
       <c r="B560" s="2" t="s">
-        <v>1561</v>
+        <v>1502</v>
       </c>
       <c r="C560" s="2" t="s">
-        <v>1562</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="561" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A561" s="2" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="B561" s="2" t="s">
-        <v>1564</v>
+        <v>209</v>
       </c>
       <c r="C561" s="2" t="s">
-        <v>1565</v>
+        <v>209</v>
       </c>
     </row>
     <row r="562" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13227,139 +13260,139 @@
         <v>1572</v>
       </c>
       <c r="B564" s="2" t="s">
-        <v>1324</v>
+        <v>1573</v>
       </c>
       <c r="C564" s="2" t="s">
-        <v>1325</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="565" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A565" s="2" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
       <c r="B565" s="2" t="s">
-        <v>4</v>
+        <v>1576</v>
       </c>
       <c r="C565" s="2" t="s">
-        <v>5</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="566" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A566" s="2" t="s">
-        <v>1574</v>
+        <v>1578</v>
       </c>
       <c r="B566" s="2" t="s">
-        <v>1315</v>
+        <v>1579</v>
       </c>
       <c r="C566" s="2" t="s">
-        <v>1316</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="567" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A567" s="2" t="s">
-        <v>1575</v>
+        <v>1581</v>
       </c>
       <c r="B567" s="2" t="s">
-        <v>1327</v>
+        <v>1333</v>
       </c>
       <c r="C567" s="2" t="s">
-        <v>1328</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="568" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A568" s="2" t="s">
-        <v>1576</v>
+        <v>1582</v>
       </c>
       <c r="B568" s="2" t="s">
-        <v>1577</v>
+        <v>4</v>
       </c>
       <c r="C568" s="2" t="s">
-        <v>1578</v>
+        <v>5</v>
       </c>
     </row>
     <row r="569" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A569" s="2" t="s">
-        <v>1579</v>
+        <v>1583</v>
       </c>
       <c r="B569" s="2" t="s">
-        <v>1580</v>
+        <v>1324</v>
       </c>
       <c r="C569" s="2" t="s">
-        <v>1581</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="570" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A570" s="2" t="s">
-        <v>1582</v>
+        <v>1584</v>
       </c>
       <c r="B570" s="2" t="s">
-        <v>1330</v>
+        <v>1336</v>
       </c>
       <c r="C570" s="2" t="s">
-        <v>1331</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="571" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A571" s="2" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
       <c r="B571" s="2" t="s">
-        <v>1584</v>
+        <v>1586</v>
       </c>
       <c r="C571" s="2" t="s">
-        <v>1585</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="572" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A572" s="2" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="B572" s="2" t="s">
-        <v>1333</v>
+        <v>1589</v>
       </c>
       <c r="C572" s="2" t="s">
-        <v>1587</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="573" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A573" s="2" t="s">
-        <v>1588</v>
+        <v>1591</v>
       </c>
       <c r="B573" s="2" t="s">
-        <v>1282</v>
+        <v>1339</v>
       </c>
       <c r="C573" s="2" t="s">
-        <v>1589</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="574" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A574" s="2" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
       <c r="B574" s="2" t="s">
-        <v>1591</v>
+        <v>1593</v>
       </c>
       <c r="C574" s="2" t="s">
-        <v>1592</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="575" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A575" s="2" t="s">
-        <v>1593</v>
+        <v>1595</v>
       </c>
       <c r="B575" s="2" t="s">
-        <v>1594</v>
+        <v>1342</v>
       </c>
       <c r="C575" s="2" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="576" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A576" s="2" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="B576" s="2" t="s">
-        <v>1597</v>
+        <v>1291</v>
       </c>
       <c r="C576" s="2" t="s">
         <v>1598</v>
@@ -13436,65 +13469,65 @@
         <v>1617</v>
       </c>
       <c r="B583" s="2" t="s">
-        <v>1324</v>
+        <v>1618</v>
       </c>
       <c r="C583" s="2" t="s">
-        <v>1325</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="584" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A584" s="2" t="s">
-        <v>1618</v>
+        <v>1620</v>
       </c>
       <c r="B584" s="2" t="s">
-        <v>4</v>
+        <v>1621</v>
       </c>
       <c r="C584" s="2" t="s">
-        <v>5</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="585" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A585" s="2" t="s">
-        <v>1619</v>
+        <v>1623</v>
       </c>
       <c r="B585" s="2" t="s">
-        <v>1330</v>
+        <v>1624</v>
       </c>
       <c r="C585" s="2" t="s">
-        <v>1331</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="586" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A586" s="2" t="s">
-        <v>1620</v>
+        <v>1626</v>
       </c>
       <c r="B586" s="2" t="s">
-        <v>1621</v>
+        <v>1333</v>
       </c>
       <c r="C586" s="2" t="s">
-        <v>1622</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="587" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A587" s="2" t="s">
-        <v>1623</v>
+        <v>1627</v>
       </c>
       <c r="B587" s="2" t="s">
-        <v>1624</v>
+        <v>4</v>
       </c>
       <c r="C587" s="2" t="s">
-        <v>1625</v>
+        <v>5</v>
       </c>
     </row>
     <row r="588" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A588" s="2" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
       <c r="B588" s="2" t="s">
-        <v>1627</v>
+        <v>1339</v>
       </c>
       <c r="C588" s="2" t="s">
-        <v>1628</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="589" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13502,76 +13535,76 @@
         <v>1629</v>
       </c>
       <c r="B589" s="2" t="s">
-        <v>1600</v>
+        <v>1630</v>
       </c>
       <c r="C589" s="2" t="s">
-        <v>1601</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="590" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A590" s="2" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="B590" s="2" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
       <c r="C590" s="2" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="591" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A591" s="2" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
       <c r="B591" s="2" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="C591" s="2" t="s">
-        <v>1635</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="592" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A592" s="2" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
       <c r="B592" s="2" t="s">
-        <v>1454</v>
+        <v>1609</v>
       </c>
       <c r="C592" s="2" t="s">
-        <v>1455</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="593" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A593" s="2" t="s">
-        <v>1637</v>
+        <v>1639</v>
       </c>
       <c r="B593" s="2" t="s">
-        <v>1638</v>
+        <v>1640</v>
       </c>
       <c r="C593" s="2" t="s">
-        <v>1639</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="594" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A594" s="2" t="s">
-        <v>1640</v>
+        <v>1642</v>
       </c>
       <c r="B594" s="2" t="s">
-        <v>1641</v>
+        <v>1643</v>
       </c>
       <c r="C594" s="2" t="s">
-        <v>1642</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="595" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A595" s="2" t="s">
-        <v>1643</v>
+        <v>1645</v>
       </c>
       <c r="B595" s="2" t="s">
-        <v>1644</v>
+        <v>1463</v>
       </c>
       <c r="C595" s="2" t="s">
-        <v>1645</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="596" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13626,40 +13659,40 @@
         <v>1659</v>
       </c>
       <c r="C600" s="2" t="s">
-        <v>603</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="601" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A601" s="2" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="B601" s="2" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="C601" s="2" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="602" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A602" s="2" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="B602" s="2" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="C602" s="2" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="603" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A603" s="2" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="B603" s="2" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="C603" s="2" t="s">
-        <v>1668</v>
+        <v>612</v>
       </c>
     </row>
     <row r="604" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13722,76 +13755,76 @@
         <v>1684</v>
       </c>
       <c r="B609" s="2" t="s">
-        <v>602</v>
+        <v>1685</v>
       </c>
       <c r="C609" s="2" t="s">
-        <v>603</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="610" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A610" s="2" t="s">
-        <v>1685</v>
+        <v>1687</v>
       </c>
       <c r="B610" s="2" t="s">
-        <v>1686</v>
+        <v>1688</v>
       </c>
       <c r="C610" s="2" t="s">
-        <v>1687</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="611" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A611" s="2" t="s">
-        <v>1688</v>
+        <v>1690</v>
       </c>
       <c r="B611" s="2" t="s">
-        <v>1689</v>
+        <v>1691</v>
       </c>
       <c r="C611" s="2" t="s">
-        <v>1690</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="612" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A612" s="2" t="s">
-        <v>1691</v>
+        <v>1693</v>
       </c>
       <c r="B612" s="2" t="s">
-        <v>303</v>
+        <v>611</v>
       </c>
       <c r="C612" s="2" t="s">
-        <v>304</v>
+        <v>612</v>
       </c>
     </row>
     <row r="613" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A613" s="2" t="s">
-        <v>1692</v>
+        <v>1694</v>
       </c>
       <c r="B613" s="2" t="s">
-        <v>1693</v>
+        <v>1695</v>
       </c>
       <c r="C613" s="2" t="s">
-        <v>1694</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="614" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A614" s="2" t="s">
-        <v>1695</v>
+        <v>1697</v>
       </c>
       <c r="B614" s="2" t="s">
-        <v>1696</v>
+        <v>1698</v>
       </c>
       <c r="C614" s="2" t="s">
-        <v>1697</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="615" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A615" s="2" t="s">
-        <v>1698</v>
+        <v>1700</v>
       </c>
       <c r="B615" s="2" t="s">
-        <v>1699</v>
+        <v>306</v>
       </c>
       <c r="C615" s="2" t="s">
-        <v>1700</v>
+        <v>307</v>
       </c>
     </row>
     <row r="616" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13898,76 +13931,76 @@
         <v>1728</v>
       </c>
       <c r="B625" s="2" t="s">
-        <v>297</v>
+        <v>1729</v>
       </c>
       <c r="C625" s="2" t="s">
-        <v>298</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="626" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A626" s="2" t="s">
-        <v>1729</v>
+        <v>1731</v>
       </c>
       <c r="B626" s="2" t="s">
-        <v>1730</v>
+        <v>1732</v>
       </c>
       <c r="C626" s="2" t="s">
-        <v>1174</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="627" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A627" s="2" t="s">
-        <v>1731</v>
+        <v>1734</v>
       </c>
       <c r="B627" s="2" t="s">
-        <v>1732</v>
+        <v>1735</v>
       </c>
       <c r="C627" s="2" t="s">
-        <v>1733</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="628" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A628" s="2" t="s">
-        <v>1734</v>
+        <v>1737</v>
       </c>
       <c r="B628" s="2" t="s">
-        <v>1553</v>
+        <v>300</v>
       </c>
       <c r="C628" s="2" t="s">
-        <v>1554</v>
+        <v>301</v>
       </c>
     </row>
     <row r="629" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A629" s="2" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
       <c r="B629" s="2" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
       <c r="C629" s="2" t="s">
-        <v>1737</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="630" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A630" s="2" t="s">
-        <v>1738</v>
+        <v>1740</v>
       </c>
       <c r="B630" s="2" t="s">
-        <v>1739</v>
+        <v>1741</v>
       </c>
       <c r="C630" s="2" t="s">
-        <v>1740</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="631" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A631" s="2" t="s">
-        <v>1741</v>
+        <v>1743</v>
       </c>
       <c r="B631" s="2" t="s">
-        <v>1742</v>
+        <v>1562</v>
       </c>
       <c r="C631" s="2" t="s">
-        <v>1743</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="632" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13997,87 +14030,87 @@
         <v>1750</v>
       </c>
       <c r="B634" s="2" t="s">
-        <v>197</v>
+        <v>1751</v>
       </c>
       <c r="C634" s="2" t="s">
-        <v>198</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="635" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A635" s="2" t="s">
-        <v>1751</v>
+        <v>1753</v>
       </c>
       <c r="B635" s="2" t="s">
-        <v>1171</v>
+        <v>1754</v>
       </c>
       <c r="C635" s="2" t="s">
-        <v>712</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="636" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A636" s="2" t="s">
-        <v>1752</v>
+        <v>1756</v>
       </c>
       <c r="B636" s="2" t="s">
-        <v>1180</v>
+        <v>1757</v>
       </c>
       <c r="C636" s="2" t="s">
-        <v>1753</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="637" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A637" s="2" t="s">
-        <v>1754</v>
+        <v>1759</v>
       </c>
       <c r="B637" s="2" t="s">
-        <v>1755</v>
+        <v>200</v>
       </c>
       <c r="C637" s="2" t="s">
-        <v>1756</v>
+        <v>201</v>
       </c>
     </row>
     <row r="638" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A638" s="2" t="s">
-        <v>1757</v>
+        <v>1760</v>
       </c>
       <c r="B638" s="2" t="s">
-        <v>297</v>
+        <v>1180</v>
       </c>
       <c r="C638" s="2" t="s">
-        <v>298</v>
+        <v>721</v>
       </c>
     </row>
     <row r="639" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A639" s="2" t="s">
-        <v>1758</v>
+        <v>1761</v>
       </c>
       <c r="B639" s="2" t="s">
-        <v>1759</v>
+        <v>1189</v>
       </c>
       <c r="C639" s="2" t="s">
-        <v>1760</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="640" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A640" s="2" t="s">
-        <v>1761</v>
+        <v>1763</v>
       </c>
       <c r="B640" s="2" t="s">
-        <v>1762</v>
+        <v>1764</v>
       </c>
       <c r="C640" s="2" t="s">
-        <v>1763</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="641" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A641" s="2" t="s">
-        <v>1764</v>
+        <v>1766</v>
       </c>
       <c r="B641" s="2" t="s">
-        <v>1765</v>
+        <v>300</v>
       </c>
       <c r="C641" s="2" t="s">
-        <v>1766</v>
+        <v>301</v>
       </c>
     </row>
     <row r="642" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14096,43 +14129,43 @@
         <v>1770</v>
       </c>
       <c r="B643" s="2" t="s">
-        <v>303</v>
+        <v>1771</v>
       </c>
       <c r="C643" s="2" t="s">
-        <v>304</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="644" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A644" s="2" t="s">
-        <v>1771</v>
+        <v>1773</v>
       </c>
       <c r="B644" s="2" t="s">
-        <v>1772</v>
+        <v>1774</v>
       </c>
       <c r="C644" s="2" t="s">
-        <v>1773</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="645" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A645" s="2" t="s">
-        <v>1774</v>
+        <v>1776</v>
       </c>
       <c r="B645" s="2" t="s">
-        <v>1775</v>
+        <v>1777</v>
       </c>
       <c r="C645" s="2" t="s">
-        <v>1776</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="646" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A646" s="2" t="s">
-        <v>1777</v>
+        <v>1779</v>
       </c>
       <c r="B646" s="2" t="s">
-        <v>1778</v>
+        <v>306</v>
       </c>
       <c r="C646" s="2" t="s">
-        <v>1779</v>
+        <v>307</v>
       </c>
     </row>
     <row r="647" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14162,43 +14195,43 @@
         <v>1786</v>
       </c>
       <c r="B649" s="2" t="s">
-        <v>602</v>
+        <v>1787</v>
       </c>
       <c r="C649" s="2" t="s">
-        <v>603</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="650" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A650" s="2" t="s">
-        <v>1787</v>
+        <v>1789</v>
       </c>
       <c r="B650" s="2" t="s">
-        <v>1788</v>
+        <v>1790</v>
       </c>
       <c r="C650" s="2" t="s">
-        <v>1789</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="651" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A651" s="2" t="s">
-        <v>1790</v>
+        <v>1792</v>
       </c>
       <c r="B651" s="2" t="s">
-        <v>1791</v>
+        <v>1793</v>
       </c>
       <c r="C651" s="2" t="s">
-        <v>1792</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="652" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A652" s="2" t="s">
-        <v>1793</v>
+        <v>1795</v>
       </c>
       <c r="B652" s="2" t="s">
-        <v>1794</v>
+        <v>611</v>
       </c>
       <c r="C652" s="2" t="s">
-        <v>1795</v>
+        <v>612</v>
       </c>
     </row>
     <row r="653" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14272,43 +14305,43 @@
         <v>1814</v>
       </c>
       <c r="B659" s="2" t="s">
-        <v>19</v>
+        <v>1815</v>
       </c>
       <c r="C659" s="2" t="s">
-        <v>20</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="660" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A660" s="2" t="s">
-        <v>1815</v>
+        <v>1817</v>
       </c>
       <c r="B660" s="2" t="s">
-        <v>1816</v>
+        <v>1818</v>
       </c>
       <c r="C660" s="2" t="s">
-        <v>1817</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="661" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A661" s="2" t="s">
-        <v>1818</v>
+        <v>1820</v>
       </c>
       <c r="B661" s="2" t="s">
-        <v>1819</v>
+        <v>1821</v>
       </c>
       <c r="C661" s="2" t="s">
-        <v>1820</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="662" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A662" s="2" t="s">
-        <v>1821</v>
+        <v>1823</v>
       </c>
       <c r="B662" s="2" t="s">
-        <v>1822</v>
+        <v>19</v>
       </c>
       <c r="C662" s="2" t="s">
-        <v>1823</v>
+        <v>20</v>
       </c>
     </row>
     <row r="663" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14338,43 +14371,43 @@
         <v>1830</v>
       </c>
       <c r="B665" s="2" t="s">
-        <v>282</v>
+        <v>1831</v>
       </c>
       <c r="C665" s="2" t="s">
-        <v>283</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="666" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A666" s="2" t="s">
-        <v>1831</v>
+        <v>1833</v>
       </c>
       <c r="B666" s="2" t="s">
-        <v>1832</v>
+        <v>1834</v>
       </c>
       <c r="C666" s="2" t="s">
-        <v>1833</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="667" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A667" s="2" t="s">
-        <v>1834</v>
+        <v>1836</v>
       </c>
       <c r="B667" s="2" t="s">
-        <v>1835</v>
+        <v>1837</v>
       </c>
       <c r="C667" s="2" t="s">
-        <v>1836</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="668" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A668" s="2" t="s">
-        <v>1837</v>
+        <v>1839</v>
       </c>
       <c r="B668" s="2" t="s">
-        <v>1838</v>
+        <v>285</v>
       </c>
       <c r="C668" s="2" t="s">
-        <v>1839</v>
+        <v>286</v>
       </c>
     </row>
     <row r="669" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14437,40 +14470,40 @@
         <v>1855</v>
       </c>
       <c r="B674" s="2" t="s">
-        <v>814</v>
+        <v>1856</v>
       </c>
       <c r="C674" s="2" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="675" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A675" s="2" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="B675" s="2" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="C675" s="2" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="676" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A676" s="2" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
       <c r="B676" s="2" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="C676" s="2" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="677" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A677" s="2" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="B677" s="2" t="s">
-        <v>1864</v>
+        <v>823</v>
       </c>
       <c r="C677" s="2" t="s">
         <v>1865</v>
@@ -14539,161 +14572,161 @@
         <v>1882</v>
       </c>
       <c r="C683" s="2" t="s">
-        <v>476</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="684" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A684" s="2" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="B684" s="2" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
       <c r="C684" s="2" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="685" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A685" s="2" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
       <c r="B685" s="2" t="s">
-        <v>1887</v>
+        <v>1888</v>
       </c>
       <c r="C685" s="2" t="s">
-        <v>1888</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="686" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A686" s="2" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
       <c r="B686" s="2" t="s">
-        <v>297</v>
+        <v>1891</v>
       </c>
       <c r="C686" s="2" t="s">
-        <v>298</v>
+        <v>479</v>
       </c>
     </row>
     <row r="687" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A687" s="2" t="s">
-        <v>1890</v>
+        <v>1892</v>
       </c>
       <c r="B687" s="2" t="s">
-        <v>1891</v>
+        <v>1893</v>
       </c>
       <c r="C687" s="2" t="s">
-        <v>195</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="688" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A688" s="2" t="s">
-        <v>1892</v>
+        <v>1895</v>
       </c>
       <c r="B688" s="2" t="s">
-        <v>1893</v>
+        <v>1896</v>
       </c>
       <c r="C688" s="2" t="s">
-        <v>1894</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="689" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A689" s="2" t="s">
-        <v>1895</v>
+        <v>1898</v>
       </c>
       <c r="B689" s="2" t="s">
-        <v>1896</v>
+        <v>300</v>
       </c>
       <c r="C689" s="2" t="s">
-        <v>476</v>
+        <v>301</v>
       </c>
     </row>
     <row r="690" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A690" s="2" t="s">
-        <v>1897</v>
+        <v>1899</v>
       </c>
       <c r="B690" s="2" t="s">
-        <v>1898</v>
+        <v>1900</v>
       </c>
       <c r="C690" s="2" t="s">
-        <v>1899</v>
+        <v>198</v>
       </c>
     </row>
     <row r="691" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A691" s="2" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="B691" s="2" t="s">
-        <v>927</v>
+        <v>1902</v>
       </c>
       <c r="C691" s="2" t="s">
-        <v>928</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="692" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A692" s="2" t="s">
-        <v>1901</v>
+        <v>1904</v>
       </c>
       <c r="B692" s="2" t="s">
-        <v>4</v>
+        <v>1905</v>
       </c>
       <c r="C692" s="2" t="s">
-        <v>5</v>
+        <v>479</v>
       </c>
     </row>
     <row r="693" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A693" s="2" t="s">
-        <v>1902</v>
+        <v>1906</v>
       </c>
       <c r="B693" s="2" t="s">
-        <v>303</v>
+        <v>1907</v>
       </c>
       <c r="C693" s="2" t="s">
-        <v>304</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="694" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A694" s="2" t="s">
-        <v>1903</v>
+        <v>1909</v>
       </c>
       <c r="B694" s="2" t="s">
-        <v>1898</v>
+        <v>936</v>
       </c>
       <c r="C694" s="2" t="s">
-        <v>1899</v>
+        <v>937</v>
       </c>
     </row>
     <row r="695" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A695" s="2" t="s">
-        <v>1904</v>
+        <v>1910</v>
       </c>
       <c r="B695" s="2" t="s">
-        <v>1905</v>
+        <v>4</v>
       </c>
       <c r="C695" s="2" t="s">
-        <v>1906</v>
+        <v>5</v>
       </c>
     </row>
     <row r="696" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A696" s="2" t="s">
-        <v>1907</v>
+        <v>1911</v>
       </c>
       <c r="B696" s="2" t="s">
-        <v>1908</v>
+        <v>306</v>
       </c>
       <c r="C696" s="2" t="s">
-        <v>1909</v>
+        <v>307</v>
       </c>
     </row>
     <row r="697" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A697" s="2" t="s">
-        <v>1910</v>
+        <v>1912</v>
       </c>
       <c r="B697" s="2" t="s">
-        <v>1911</v>
+        <v>1907</v>
       </c>
       <c r="C697" s="2" t="s">
-        <v>1912</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="698" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14756,65 +14789,65 @@
         <v>1928</v>
       </c>
       <c r="B703" s="2" t="s">
-        <v>19</v>
+        <v>1929</v>
       </c>
       <c r="C703" s="2" t="s">
-        <v>20</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="704" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A704" s="2" t="s">
-        <v>1929</v>
+        <v>1931</v>
       </c>
       <c r="B704" s="2" t="s">
-        <v>13</v>
+        <v>1932</v>
       </c>
       <c r="C704" s="2" t="s">
-        <v>14</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="705" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A705" s="2" t="s">
-        <v>1930</v>
+        <v>1934</v>
       </c>
       <c r="B705" s="2" t="s">
-        <v>16</v>
+        <v>1935</v>
       </c>
       <c r="C705" s="2" t="s">
-        <v>17</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="706" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A706" s="2" t="s">
-        <v>1931</v>
+        <v>1937</v>
       </c>
       <c r="B706" s="2" t="s">
-        <v>1932</v>
+        <v>19</v>
       </c>
       <c r="C706" s="2" t="s">
-        <v>1933</v>
+        <v>20</v>
       </c>
     </row>
     <row r="707" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A707" s="2" t="s">
-        <v>1934</v>
+        <v>1938</v>
       </c>
       <c r="B707" s="2" t="s">
-        <v>1935</v>
+        <v>13</v>
       </c>
       <c r="C707" s="2" t="s">
-        <v>1936</v>
+        <v>14</v>
       </c>
     </row>
     <row r="708" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A708" s="2" t="s">
-        <v>1937</v>
+        <v>1939</v>
       </c>
       <c r="B708" s="2" t="s">
-        <v>1938</v>
+        <v>16</v>
       </c>
       <c r="C708" s="2" t="s">
-        <v>1939</v>
+        <v>17</v>
       </c>
     </row>
     <row r="709" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14833,186 +14866,186 @@
         <v>1943</v>
       </c>
       <c r="B710" s="2" t="s">
-        <v>1841</v>
+        <v>1944</v>
       </c>
       <c r="C710" s="2" t="s">
-        <v>1842</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="711" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A711" s="2" t="s">
-        <v>1944</v>
+        <v>1946</v>
       </c>
       <c r="B711" s="2" t="s">
-        <v>1844</v>
+        <v>1947</v>
       </c>
       <c r="C711" s="2" t="s">
-        <v>1845</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="712" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A712" s="2" t="s">
-        <v>1945</v>
+        <v>1949</v>
       </c>
       <c r="B712" s="2" t="s">
-        <v>1946</v>
+        <v>1950</v>
       </c>
       <c r="C712" s="2" t="s">
-        <v>1334</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="713" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A713" s="2" t="s">
-        <v>1947</v>
+        <v>1952</v>
       </c>
       <c r="B713" s="2" t="s">
-        <v>1948</v>
+        <v>1850</v>
       </c>
       <c r="C713" s="2" t="s">
-        <v>1949</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="714" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A714" s="2" t="s">
-        <v>1950</v>
+        <v>1953</v>
       </c>
       <c r="B714" s="2" t="s">
-        <v>1183</v>
+        <v>1853</v>
       </c>
       <c r="C714" s="2" t="s">
-        <v>1184</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="715" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A715" s="2" t="s">
-        <v>1951</v>
+        <v>1954</v>
       </c>
       <c r="B715" s="2" t="s">
-        <v>1952</v>
+        <v>1955</v>
       </c>
       <c r="C715" s="2" t="s">
-        <v>1854</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="716" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A716" s="2" t="s">
-        <v>1953</v>
+        <v>1956</v>
       </c>
       <c r="B716" s="2" t="s">
-        <v>814</v>
+        <v>1957</v>
       </c>
       <c r="C716" s="2" t="s">
-        <v>1856</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="717" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A717" s="2" t="s">
-        <v>1954</v>
+        <v>1959</v>
       </c>
       <c r="B717" s="2" t="s">
-        <v>1955</v>
+        <v>1192</v>
       </c>
       <c r="C717" s="2" t="s">
-        <v>1956</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="718" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A718" s="2" t="s">
-        <v>1957</v>
+        <v>1960</v>
       </c>
       <c r="B718" s="2" t="s">
-        <v>1958</v>
+        <v>1961</v>
       </c>
       <c r="C718" s="2" t="s">
-        <v>1949</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="719" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A719" s="2" t="s">
-        <v>1959</v>
+        <v>1962</v>
       </c>
       <c r="B719" s="2" t="s">
-        <v>911</v>
+        <v>823</v>
       </c>
       <c r="C719" s="2" t="s">
-        <v>1960</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="720" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A720" s="2" t="s">
-        <v>1961</v>
+        <v>1963</v>
       </c>
       <c r="B720" s="2" t="s">
-        <v>923</v>
+        <v>1964</v>
       </c>
       <c r="C720" s="2" t="s">
-        <v>1962</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="721" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A721" s="2" t="s">
-        <v>1963</v>
+        <v>1966</v>
       </c>
       <c r="B721" s="2" t="s">
-        <v>605</v>
+        <v>1967</v>
       </c>
       <c r="C721" s="2" t="s">
-        <v>476</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="722" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A722" s="2" t="s">
-        <v>1964</v>
+        <v>1968</v>
       </c>
       <c r="B722" s="2" t="s">
-        <v>927</v>
+        <v>920</v>
       </c>
       <c r="C722" s="2" t="s">
-        <v>928</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="723" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A723" s="2" t="s">
-        <v>1965</v>
+        <v>1970</v>
       </c>
       <c r="B723" s="2" t="s">
-        <v>303</v>
+        <v>932</v>
       </c>
       <c r="C723" s="2" t="s">
-        <v>304</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="724" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A724" s="2" t="s">
-        <v>1966</v>
+        <v>1972</v>
       </c>
       <c r="B724" s="2" t="s">
-        <v>1967</v>
+        <v>614</v>
       </c>
       <c r="C724" s="2" t="s">
-        <v>1968</v>
+        <v>479</v>
       </c>
     </row>
     <row r="725" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A725" s="2" t="s">
-        <v>1969</v>
+        <v>1973</v>
       </c>
       <c r="B725" s="2" t="s">
-        <v>1970</v>
+        <v>936</v>
       </c>
       <c r="C725" s="2" t="s">
-        <v>1971</v>
+        <v>937</v>
       </c>
     </row>
     <row r="726" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A726" s="2" t="s">
-        <v>1972</v>
+        <v>1974</v>
       </c>
       <c r="B726" s="2" t="s">
-        <v>1973</v>
+        <v>306</v>
       </c>
       <c r="C726" s="2" t="s">
-        <v>1974</v>
+        <v>307</v>
       </c>
     </row>
     <row r="727" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15020,106 +15053,106 @@
         <v>1975</v>
       </c>
       <c r="B727" s="2" t="s">
-        <v>955</v>
+        <v>1976</v>
       </c>
       <c r="C727" s="2" t="s">
-        <v>956</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="728" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A728" s="2" t="s">
-        <v>1976</v>
+        <v>1978</v>
       </c>
       <c r="B728" s="2" t="s">
-        <v>923</v>
+        <v>1979</v>
       </c>
       <c r="C728" s="2" t="s">
-        <v>1962</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="729" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A729" s="2" t="s">
-        <v>1977</v>
+        <v>1981</v>
       </c>
       <c r="B729" s="2" t="s">
-        <v>959</v>
+        <v>1982</v>
       </c>
       <c r="C729" s="2" t="s">
-        <v>960</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="730" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A730" s="2" t="s">
-        <v>1978</v>
+        <v>1984</v>
       </c>
       <c r="B730" s="2" t="s">
-        <v>1979</v>
+        <v>964</v>
       </c>
       <c r="C730" s="2" t="s">
-        <v>1980</v>
+        <v>965</v>
       </c>
     </row>
     <row r="731" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A731" s="2" t="s">
-        <v>1981</v>
+        <v>1985</v>
       </c>
       <c r="B731" s="2" t="s">
-        <v>965</v>
+        <v>932</v>
       </c>
       <c r="C731" s="2" t="s">
-        <v>1982</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="732" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A732" s="2" t="s">
-        <v>1983</v>
+        <v>1986</v>
       </c>
       <c r="B732" s="2" t="s">
-        <v>1984</v>
+        <v>968</v>
       </c>
       <c r="C732" s="2" t="s">
-        <v>1985</v>
+        <v>969</v>
       </c>
     </row>
     <row r="733" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A733" s="2" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="B733" s="2" t="s">
-        <v>971</v>
+        <v>1988</v>
       </c>
       <c r="C733" s="2" t="s">
-        <v>1987</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="734" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A734" s="2" t="s">
-        <v>1988</v>
+        <v>1990</v>
       </c>
       <c r="B734" s="2" t="s">
-        <v>1989</v>
+        <v>974</v>
       </c>
       <c r="C734" s="2" t="s">
-        <v>1990</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="735" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A735" s="2" t="s">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="B735" s="2" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="C735" s="2" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="736" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A736" s="2" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="B736" s="2" t="s">
-        <v>1995</v>
+        <v>980</v>
       </c>
       <c r="C736" s="2" t="s">
         <v>1996</v>
@@ -15130,120 +15163,120 @@
         <v>1997</v>
       </c>
       <c r="B737" s="2" t="s">
-        <v>795</v>
+        <v>1998</v>
       </c>
       <c r="C737" s="2" t="s">
-        <v>796</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="738" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A738" s="2" t="s">
-        <v>1998</v>
+        <v>2000</v>
       </c>
       <c r="B738" s="2" t="s">
-        <v>981</v>
+        <v>2001</v>
       </c>
       <c r="C738" s="2" t="s">
-        <v>982</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="739" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A739" s="2" t="s">
-        <v>1999</v>
+        <v>2003</v>
       </c>
       <c r="B739" s="2" t="s">
-        <v>984</v>
+        <v>2004</v>
       </c>
       <c r="C739" s="2" t="s">
-        <v>2000</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="740" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A740" s="2" t="s">
-        <v>2001</v>
+        <v>2006</v>
       </c>
       <c r="B740" s="2" t="s">
-        <v>987</v>
+        <v>804</v>
       </c>
       <c r="C740" s="2" t="s">
-        <v>2002</v>
+        <v>805</v>
       </c>
     </row>
     <row r="741" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A741" s="2" t="s">
-        <v>2003</v>
+        <v>2007</v>
       </c>
       <c r="B741" s="2" t="s">
         <v>990</v>
       </c>
       <c r="C741" s="2" t="s">
-        <v>2004</v>
+        <v>991</v>
       </c>
     </row>
     <row r="742" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A742" s="2" t="s">
-        <v>2005</v>
+        <v>2008</v>
       </c>
       <c r="B742" s="2" t="s">
-        <v>2006</v>
+        <v>993</v>
       </c>
       <c r="C742" s="2" t="s">
-        <v>2007</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="743" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A743" s="2" t="s">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="B743" s="2" t="s">
-        <v>1841</v>
+        <v>996</v>
       </c>
       <c r="C743" s="2" t="s">
-        <v>1842</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="744" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A744" s="2" t="s">
-        <v>2009</v>
+        <v>2012</v>
       </c>
       <c r="B744" s="2" t="s">
-        <v>1844</v>
+        <v>999</v>
       </c>
       <c r="C744" s="2" t="s">
-        <v>1845</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="745" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A745" s="2" t="s">
-        <v>2010</v>
+        <v>2014</v>
       </c>
       <c r="B745" s="2" t="s">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="C745" s="2" t="s">
-        <v>2012</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="746" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A746" s="2" t="s">
-        <v>2013</v>
+        <v>2017</v>
       </c>
       <c r="B746" s="2" t="s">
-        <v>2014</v>
+        <v>1850</v>
       </c>
       <c r="C746" s="2" t="s">
-        <v>2015</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="747" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A747" s="2" t="s">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="B747" s="2" t="s">
-        <v>2017</v>
+        <v>1853</v>
       </c>
       <c r="C747" s="2" t="s">
-        <v>2018</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="748" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15284,106 +15317,106 @@
         <v>2028</v>
       </c>
       <c r="B751" s="2" t="s">
-        <v>454</v>
+        <v>2029</v>
       </c>
       <c r="C751" s="2" t="s">
-        <v>455</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="752" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A752" s="2" t="s">
-        <v>2029</v>
+        <v>2031</v>
       </c>
       <c r="B752" s="2" t="s">
-        <v>2030</v>
+        <v>2032</v>
       </c>
       <c r="C752" s="2" t="s">
-        <v>2031</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="753" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A753" s="2" t="s">
-        <v>2032</v>
+        <v>2034</v>
       </c>
       <c r="B753" s="2" t="s">
-        <v>2033</v>
+        <v>2035</v>
       </c>
       <c r="C753" s="2" t="s">
-        <v>2034</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="754" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A754" s="2" t="s">
-        <v>2035</v>
+        <v>2037</v>
       </c>
       <c r="B754" s="2" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="C754" s="2" t="s">
-        <v>603</v>
+        <v>458</v>
       </c>
     </row>
     <row r="755" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A755" s="2" t="s">
-        <v>2036</v>
+        <v>2038</v>
       </c>
       <c r="B755" s="2" t="s">
-        <v>472</v>
+        <v>2039</v>
       </c>
       <c r="C755" s="2" t="s">
-        <v>2037</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="756" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A756" s="2" t="s">
-        <v>2038</v>
+        <v>2041</v>
       </c>
       <c r="B756" s="2" t="s">
-        <v>505</v>
+        <v>2042</v>
       </c>
       <c r="C756" s="2" t="s">
-        <v>2039</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="757" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A757" s="2" t="s">
-        <v>2040</v>
+        <v>2044</v>
       </c>
       <c r="B757" s="2" t="s">
-        <v>508</v>
+        <v>469</v>
       </c>
       <c r="C757" s="2" t="s">
-        <v>2041</v>
+        <v>612</v>
       </c>
     </row>
     <row r="758" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A758" s="2" t="s">
-        <v>2042</v>
+        <v>2045</v>
       </c>
       <c r="B758" s="2" t="s">
-        <v>2043</v>
+        <v>475</v>
       </c>
       <c r="C758" s="2" t="s">
-        <v>2044</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="759" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A759" s="2" t="s">
-        <v>2045</v>
+        <v>2047</v>
       </c>
       <c r="B759" s="2" t="s">
-        <v>2046</v>
+        <v>508</v>
       </c>
       <c r="C759" s="2" t="s">
-        <v>2047</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="760" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A760" s="2" t="s">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="B760" s="2" t="s">
-        <v>2049</v>
+        <v>511</v>
       </c>
       <c r="C760" s="2" t="s">
         <v>2050</v>
@@ -15394,252 +15427,252 @@
         <v>2051</v>
       </c>
       <c r="B761" s="2" t="s">
-        <v>475</v>
+        <v>2052</v>
       </c>
       <c r="C761" s="2" t="s">
-        <v>476</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="762" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A762" s="2" t="s">
-        <v>2052</v>
+        <v>2054</v>
       </c>
       <c r="B762" s="2" t="s">
-        <v>2053</v>
+        <v>2055</v>
       </c>
       <c r="C762" s="2" t="s">
-        <v>2054</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="763" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A763" s="2" t="s">
-        <v>2055</v>
+        <v>2057</v>
       </c>
       <c r="B763" s="2" t="s">
-        <v>487</v>
+        <v>2058</v>
       </c>
       <c r="C763" s="2" t="s">
-        <v>488</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="764" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A764" s="2" t="s">
-        <v>2056</v>
+        <v>2060</v>
       </c>
       <c r="B764" s="2" t="s">
-        <v>493</v>
+        <v>478</v>
       </c>
       <c r="C764" s="2" t="s">
-        <v>494</v>
+        <v>479</v>
       </c>
     </row>
     <row r="765" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A765" s="2" t="s">
-        <v>2057</v>
+        <v>2061</v>
       </c>
       <c r="B765" s="2" t="s">
-        <v>2058</v>
+        <v>2062</v>
       </c>
       <c r="C765" s="2" t="s">
-        <v>2059</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="766" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A766" s="2" t="s">
-        <v>2060</v>
+        <v>2064</v>
       </c>
       <c r="B766" s="2" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="C766" s="2" t="s">
-        <v>221</v>
+        <v>491</v>
       </c>
     </row>
     <row r="767" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A767" s="2" t="s">
-        <v>2061</v>
+        <v>2065</v>
       </c>
       <c r="B767" s="2" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="C767" s="2" t="s">
-        <v>2062</v>
+        <v>497</v>
       </c>
     </row>
     <row r="768" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A768" s="2" t="s">
-        <v>2063</v>
+        <v>2066</v>
       </c>
       <c r="B768" s="2" t="s">
-        <v>541</v>
+        <v>2067</v>
       </c>
       <c r="C768" s="2" t="s">
-        <v>2064</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="769" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A769" s="2" t="s">
-        <v>2065</v>
+        <v>2069</v>
       </c>
       <c r="B769" s="2" t="s">
-        <v>2066</v>
+        <v>499</v>
       </c>
       <c r="C769" s="2" t="s">
-        <v>2067</v>
+        <v>224</v>
       </c>
     </row>
     <row r="770" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A770" s="2" t="s">
-        <v>2068</v>
+        <v>2070</v>
       </c>
       <c r="B770" s="2" t="s">
-        <v>523</v>
+        <v>502</v>
       </c>
       <c r="C770" s="2" t="s">
-        <v>524</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="771" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A771" s="2" t="s">
-        <v>2069</v>
+        <v>2072</v>
       </c>
       <c r="B771" s="2" t="s">
-        <v>2070</v>
+        <v>544</v>
       </c>
       <c r="C771" s="2" t="s">
-        <v>2071</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="772" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A772" s="2" t="s">
-        <v>2072</v>
+        <v>2074</v>
       </c>
       <c r="B772" s="2" t="s">
-        <v>2073</v>
+        <v>2075</v>
       </c>
       <c r="C772" s="2" t="s">
-        <v>2074</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="773" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A773" s="2" t="s">
-        <v>2075</v>
+        <v>2077</v>
       </c>
       <c r="B773" s="2" t="s">
-        <v>2076</v>
+        <v>526</v>
       </c>
       <c r="C773" s="2" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
     </row>
     <row r="774" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A774" s="2" t="s">
-        <v>2077</v>
+        <v>2078</v>
       </c>
       <c r="B774" s="2" t="s">
-        <v>2078</v>
+        <v>2079</v>
       </c>
       <c r="C774" s="2" t="s">
-        <v>536</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="775" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A775" s="2" t="s">
-        <v>2079</v>
+        <v>2081</v>
       </c>
       <c r="B775" s="2" t="s">
-        <v>2080</v>
+        <v>2082</v>
       </c>
       <c r="C775" s="2" t="s">
-        <v>2081</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="776" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A776" s="2" t="s">
-        <v>2082</v>
+        <v>2084</v>
       </c>
       <c r="B776" s="2" t="s">
-        <v>2083</v>
+        <v>2085</v>
       </c>
       <c r="C776" s="2" t="s">
-        <v>2084</v>
+        <v>536</v>
       </c>
     </row>
     <row r="777" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A777" s="2" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="B777" s="2" t="s">
-        <v>547</v>
+        <v>2087</v>
       </c>
       <c r="C777" s="2" t="s">
-        <v>548</v>
+        <v>539</v>
       </c>
     </row>
     <row r="778" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A778" s="2" t="s">
-        <v>2086</v>
+        <v>2088</v>
       </c>
       <c r="B778" s="2" t="s">
-        <v>2087</v>
+        <v>2089</v>
       </c>
       <c r="C778" s="2" t="s">
-        <v>2088</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="779" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A779" s="2" t="s">
-        <v>2089</v>
+        <v>2091</v>
       </c>
       <c r="B779" s="2" t="s">
-        <v>553</v>
+        <v>2092</v>
       </c>
       <c r="C779" s="2" t="s">
-        <v>554</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="780" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A780" s="2" t="s">
-        <v>2090</v>
+        <v>2094</v>
       </c>
       <c r="B780" s="2" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="C780" s="2" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
     </row>
     <row r="781" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A781" s="2" t="s">
-        <v>2091</v>
+        <v>2095</v>
       </c>
       <c r="B781" s="2" t="s">
-        <v>2092</v>
+        <v>2096</v>
       </c>
       <c r="C781" s="2" t="s">
-        <v>2093</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="782" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A782" s="2" t="s">
-        <v>2094</v>
+        <v>2098</v>
       </c>
       <c r="B782" s="2" t="s">
-        <v>2095</v>
+        <v>556</v>
       </c>
       <c r="C782" s="2" t="s">
-        <v>2096</v>
+        <v>557</v>
       </c>
     </row>
     <row r="783" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A783" s="2" t="s">
-        <v>2097</v>
+        <v>2099</v>
       </c>
       <c r="B783" s="2" t="s">
-        <v>2098</v>
+        <v>559</v>
       </c>
       <c r="C783" s="2" t="s">
-        <v>2099</v>
+        <v>560</v>
       </c>
     </row>
     <row r="784" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15658,10 +15691,10 @@
         <v>2103</v>
       </c>
       <c r="B785" s="2" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="C785" s="2" t="s">
-        <v>575</v>
+        <v>566</v>
       </c>
     </row>
     <row r="786" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15669,21 +15702,21 @@
         <v>2104</v>
       </c>
       <c r="B786" s="2" t="s">
-        <v>2105</v>
+        <v>568</v>
       </c>
       <c r="C786" s="2" t="s">
-        <v>2106</v>
+        <v>569</v>
       </c>
     </row>
     <row r="787" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A787" s="2" t="s">
+        <v>2105</v>
+      </c>
+      <c r="B787" s="2" t="s">
+        <v>2106</v>
+      </c>
+      <c r="C787" s="2" t="s">
         <v>2107</v>
-      </c>
-      <c r="B787" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="C787" s="2" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="788" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15691,98 +15724,98 @@
         <v>2108</v>
       </c>
       <c r="B788" s="2" t="s">
-        <v>568</v>
+        <v>2109</v>
       </c>
       <c r="C788" s="2" t="s">
-        <v>569</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="789" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A789" s="2" t="s">
-        <v>2109</v>
+        <v>2111</v>
       </c>
       <c r="B789" s="2" t="s">
-        <v>581</v>
+        <v>2112</v>
       </c>
       <c r="C789" s="2" t="s">
-        <v>582</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="790" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A790" s="2" t="s">
-        <v>2110</v>
+        <v>2114</v>
       </c>
       <c r="B790" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="C790" s="2" t="s">
         <v>584</v>
-      </c>
-      <c r="C790" s="2" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="791" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A791" s="2" t="s">
-        <v>2111</v>
+        <v>2115</v>
       </c>
       <c r="B791" s="2" t="s">
-        <v>587</v>
+        <v>2116</v>
       </c>
       <c r="C791" s="2" t="s">
-        <v>587</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="792" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A792" s="2" t="s">
-        <v>2112</v>
+        <v>2118</v>
       </c>
       <c r="B792" s="2" t="s">
-        <v>589</v>
+        <v>574</v>
       </c>
       <c r="C792" s="2" t="s">
-        <v>590</v>
+        <v>575</v>
       </c>
     </row>
     <row r="793" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A793" s="2" t="s">
-        <v>2113</v>
+        <v>2119</v>
       </c>
       <c r="B793" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="C793" s="2" t="s">
         <v>578</v>
-      </c>
-      <c r="C793" s="2" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="794" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A794" s="2" t="s">
-        <v>2114</v>
+        <v>2120</v>
       </c>
       <c r="B794" s="2" t="s">
-        <v>2115</v>
+        <v>590</v>
       </c>
       <c r="C794" s="2" t="s">
-        <v>2116</v>
+        <v>591</v>
       </c>
     </row>
     <row r="795" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A795" s="2" t="s">
-        <v>2117</v>
+        <v>2121</v>
       </c>
       <c r="B795" s="2" t="s">
-        <v>2118</v>
+        <v>593</v>
       </c>
       <c r="C795" s="2" t="s">
-        <v>2119</v>
+        <v>594</v>
       </c>
     </row>
     <row r="796" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A796" s="2" t="s">
-        <v>2120</v>
+        <v>2122</v>
       </c>
       <c r="B796" s="2" t="s">
-        <v>2121</v>
+        <v>596</v>
       </c>
       <c r="C796" s="2" t="s">
-        <v>2122</v>
+        <v>596</v>
       </c>
     </row>
     <row r="797" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15790,219 +15823,219 @@
         <v>2123</v>
       </c>
       <c r="B797" s="2" t="s">
-        <v>2124</v>
+        <v>598</v>
       </c>
       <c r="C797" s="2" t="s">
-        <v>2125</v>
+        <v>599</v>
       </c>
     </row>
     <row r="798" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A798" s="2" t="s">
-        <v>2126</v>
+        <v>2124</v>
       </c>
       <c r="B798" s="2" t="s">
-        <v>2127</v>
+        <v>587</v>
       </c>
       <c r="C798" s="2" t="s">
-        <v>2128</v>
+        <v>588</v>
       </c>
     </row>
     <row r="799" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A799" s="2" t="s">
-        <v>2129</v>
+        <v>2125</v>
       </c>
       <c r="B799" s="2" t="s">
-        <v>2130</v>
+        <v>2126</v>
       </c>
       <c r="C799" s="2" t="s">
-        <v>1763</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="800" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A800" s="2" t="s">
-        <v>2131</v>
+        <v>2128</v>
       </c>
       <c r="B800" s="2" t="s">
-        <v>2132</v>
+        <v>2129</v>
       </c>
       <c r="C800" s="2" t="s">
-        <v>2133</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="801" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A801" s="2" t="s">
-        <v>2134</v>
+        <v>2131</v>
       </c>
       <c r="B801" s="2" t="s">
-        <v>2135</v>
+        <v>2132</v>
       </c>
       <c r="C801" s="2" t="s">
-        <v>2136</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="802" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A802" s="2" t="s">
-        <v>2137</v>
+        <v>2134</v>
       </c>
       <c r="B802" s="2" t="s">
-        <v>2138</v>
+        <v>2135</v>
       </c>
       <c r="C802" s="2" t="s">
-        <v>2139</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="803" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A803" s="2" t="s">
-        <v>2140</v>
+        <v>2137</v>
       </c>
       <c r="B803" s="2" t="s">
-        <v>2141</v>
+        <v>2138</v>
       </c>
       <c r="C803" s="2" t="s">
-        <v>229</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="804" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A804" s="2" t="s">
-        <v>2142</v>
+        <v>2140</v>
       </c>
       <c r="B804" s="2" t="s">
-        <v>2143</v>
+        <v>2141</v>
       </c>
       <c r="C804" s="2" t="s">
-        <v>2144</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="805" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A805" s="2" t="s">
-        <v>2145</v>
+        <v>2142</v>
       </c>
       <c r="B805" s="2" t="s">
-        <v>2146</v>
+        <v>2143</v>
       </c>
       <c r="C805" s="2" t="s">
-        <v>2147</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="806" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A806" s="2" t="s">
-        <v>2148</v>
+        <v>2145</v>
       </c>
       <c r="B806" s="2" t="s">
-        <v>2149</v>
+        <v>2146</v>
       </c>
       <c r="C806" s="2" t="s">
-        <v>2150</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="807" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A807" s="2" t="s">
-        <v>2151</v>
+        <v>2148</v>
       </c>
       <c r="B807" s="2" t="s">
-        <v>2152</v>
+        <v>2149</v>
       </c>
       <c r="C807" s="2" t="s">
-        <v>2153</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="808" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A808" s="2" t="s">
-        <v>2154</v>
+        <v>2151</v>
       </c>
       <c r="B808" s="2" t="s">
-        <v>2155</v>
+        <v>2152</v>
       </c>
       <c r="C808" s="2" t="s">
-        <v>2156</v>
+        <v>232</v>
       </c>
     </row>
     <row r="809" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A809" s="2" t="s">
-        <v>2157</v>
+        <v>2153</v>
       </c>
       <c r="B809" s="2" t="s">
-        <v>2158</v>
+        <v>2154</v>
       </c>
       <c r="C809" s="2" t="s">
-        <v>2159</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="810" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A810" s="2" t="s">
-        <v>2160</v>
+        <v>2156</v>
       </c>
       <c r="B810" s="2" t="s">
-        <v>2161</v>
+        <v>2157</v>
       </c>
       <c r="C810" s="2" t="s">
-        <v>2162</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="811" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A811" s="2" t="s">
-        <v>2163</v>
+        <v>2159</v>
       </c>
       <c r="B811" s="2" t="s">
-        <v>2164</v>
+        <v>2160</v>
       </c>
       <c r="C811" s="2" t="s">
-        <v>2165</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="812" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A812" s="2" t="s">
-        <v>2166</v>
+        <v>2162</v>
       </c>
       <c r="B812" s="2" t="s">
-        <v>2167</v>
+        <v>2163</v>
       </c>
       <c r="C812" s="2" t="s">
-        <v>2168</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="813" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A813" s="2" t="s">
-        <v>2169</v>
+        <v>2165</v>
       </c>
       <c r="B813" s="2" t="s">
-        <v>2170</v>
+        <v>2166</v>
       </c>
       <c r="C813" s="2" t="s">
-        <v>2171</v>
+        <v>2167</v>
       </c>
     </row>
     <row r="814" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A814" s="2" t="s">
-        <v>2172</v>
+        <v>2168</v>
       </c>
       <c r="B814" s="2" t="s">
-        <v>2173</v>
+        <v>2169</v>
       </c>
       <c r="C814" s="2" t="s">
-        <v>2174</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="815" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A815" s="2" t="s">
-        <v>2175</v>
+        <v>2171</v>
       </c>
       <c r="B815" s="2" t="s">
-        <v>677</v>
+        <v>2172</v>
       </c>
       <c r="C815" s="2" t="s">
-        <v>678</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="816" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A816" s="2" t="s">
+        <v>2174</v>
+      </c>
+      <c r="B816" s="2" t="s">
+        <v>2175</v>
+      </c>
+      <c r="C816" s="2" t="s">
         <v>2176</v>
-      </c>
-      <c r="B816" s="2" t="s">
-        <v>680</v>
-      </c>
-      <c r="C816" s="2" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="817" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -16043,87 +16076,142 @@
         <v>2186</v>
       </c>
       <c r="B820" s="2" t="s">
-        <v>2187</v>
+        <v>686</v>
       </c>
       <c r="C820" s="2" t="s">
-        <v>2188</v>
+        <v>687</v>
       </c>
     </row>
     <row r="821" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A821" s="2" t="s">
-        <v>2189</v>
+        <v>2187</v>
       </c>
       <c r="B821" s="2" t="s">
-        <v>2190</v>
+        <v>689</v>
       </c>
       <c r="C821" s="2" t="s">
-        <v>2191</v>
+        <v>690</v>
       </c>
     </row>
     <row r="822" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A822" s="2" t="s">
-        <v>2192</v>
+        <v>2188</v>
       </c>
       <c r="B822" s="2" t="s">
-        <v>2193</v>
+        <v>2189</v>
       </c>
       <c r="C822" s="2" t="s">
-        <v>2194</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="823" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A823" s="2" t="s">
-        <v>2195</v>
+        <v>2191</v>
       </c>
       <c r="B823" s="2" t="s">
-        <v>2196</v>
+        <v>2192</v>
       </c>
       <c r="C823" s="2" t="s">
-        <v>2197</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="824" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A824" s="2" t="s">
-        <v>2198</v>
+        <v>2194</v>
       </c>
       <c r="B824" s="2" t="s">
-        <v>184</v>
+        <v>2195</v>
       </c>
       <c r="C824" s="2" t="s">
-        <v>185</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="825" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A825" s="2" t="s">
+        <v>2197</v>
+      </c>
+      <c r="B825" s="2" t="s">
+        <v>2198</v>
+      </c>
+      <c r="C825" s="2" t="s">
         <v>2199</v>
-      </c>
-      <c r="B825" s="2" t="s">
-        <v>2200</v>
-      </c>
-      <c r="C825" s="2" t="s">
-        <v>2201</v>
       </c>
     </row>
     <row r="826" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A826" s="2" t="s">
+        <v>2200</v>
+      </c>
+      <c r="B826" s="2" t="s">
+        <v>2201</v>
+      </c>
+      <c r="C826" s="2" t="s">
         <v>2202</v>
-      </c>
-      <c r="B826" s="2" t="s">
-        <v>2203</v>
-      </c>
-      <c r="C826" s="2" t="s">
-        <v>2204</v>
       </c>
     </row>
     <row r="827" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A827" s="2" t="s">
+        <v>2203</v>
+      </c>
+      <c r="B827" s="2" t="s">
+        <v>2204</v>
+      </c>
+      <c r="C827" s="2" t="s">
         <v>2205</v>
       </c>
-      <c r="B827" s="2" t="s">
+    </row>
+    <row r="828" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A828" s="2" t="s">
         <v>2206</v>
       </c>
-      <c r="C827" s="2" t="s">
+      <c r="B828" s="2" t="s">
         <v>2207</v>
+      </c>
+      <c r="C828" s="2" t="s">
+        <v>2208</v>
+      </c>
+    </row>
+    <row r="829" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A829" s="2" t="s">
+        <v>2209</v>
+      </c>
+      <c r="B829" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C829" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="830" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A830" s="2" t="s">
+        <v>2210</v>
+      </c>
+      <c r="B830" s="2" t="s">
+        <v>2211</v>
+      </c>
+      <c r="C830" s="2" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="831" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A831" s="2" t="s">
+        <v>2213</v>
+      </c>
+      <c r="B831" s="2" t="s">
+        <v>2214</v>
+      </c>
+      <c r="C831" s="2" t="s">
+        <v>2215</v>
+      </c>
+    </row>
+    <row r="832" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A832" s="2" t="s">
+        <v>2216</v>
+      </c>
+      <c r="B832" s="2" t="s">
+        <v>2217</v>
+      </c>
+      <c r="C832" s="2" t="s">
+        <v>2218</v>
       </c>
     </row>
   </sheetData>

--- a/apps/workspace-web/i18n.xlsx
+++ b/apps/workspace-web/i18n.xlsx
@@ -5449,21 +5449,19 @@
     <t>legalDocs.highlightsPlaceholder</t>
   </si>
   <si>
-    <t xml:space="preserve">每行一則，以第一個「|」分隔標題與描述，例如：
-作品永遠是你的|上架不會轉移著作權，創作者僅授權平台展示與銷售作品。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One per line, title and description split by the first "|", e.g.:
-Your work stays yours|Listing never transfers copyright — creators only license us to display and sell their work.</t>
+    <t>每行一則，格式：標題|描述</t>
+  </si>
+  <si>
+    <t>One per line, format: title|description</t>
   </si>
   <si>
     <t>legalDocs.highlightsHint</t>
   </si>
   <si>
-    <t>選填，最多 6 則；顯示於前台條款頁頂部的 30 秒摘要卡，留空則前台改用預設文案。</t>
-  </si>
-  <si>
-    <t>Optional, up to 6 items; shown as the 30-second summary cards atop the public legal page. Leave empty to fall back to the default copy.</t>
+    <t>選填，最多 6 則；顯示於前台條款頁頂部的 30 秒摘要卡，留空則前台改用預設文案。例如：作品永遠是你的|上架不會轉移著作權，創作者僅授權平台展示與銷售作品。</t>
+  </si>
+  <si>
+    <t>Optional, up to 6 items; shown as the 30-second summary cards atop the public legal page. Leave empty to fall back to the default copy. E.g.: Your work stays yours|Listing never transfers copyright — creators only license us to display and sell their work.</t>
   </si>
   <si>
     <t>legalDocs.valHighlightsFormat</t>

--- a/apps/workspace-web/i18n.xlsx
+++ b/apps/workspace-web/i18n.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2496" uniqueCount="2219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2637" uniqueCount="2331">
   <si>
     <t>key</t>
   </si>
@@ -409,6 +409,15 @@
     <t>Failed to load orders, please try again later.</t>
   </si>
   <si>
+    <t>storeError.loadDashboardFailed</t>
+  </si>
+  <si>
+    <t>載入儀表板資料失敗，請稍後再試。</t>
+  </si>
+  <si>
+    <t>Failed to load dashboard data, please try again later.</t>
+  </si>
+  <si>
     <t>storeError.loadCatalogFailed</t>
   </si>
   <si>
@@ -571,6 +580,15 @@
     <t>Failed to create version.</t>
   </si>
   <si>
+    <t>storeError.notifyBuyersFailed</t>
+  </si>
+  <si>
+    <t>通知買家失敗。</t>
+  </si>
+  <si>
+    <t>Failed to notify buyers.</t>
+  </si>
+  <si>
     <t>storeError.uploadFileFailed</t>
   </si>
   <si>
@@ -598,6 +616,15 @@
     <t>Failed to delete product.</t>
   </si>
   <si>
+    <t>storeError.loadPaymentsFailed</t>
+  </si>
+  <si>
+    <t>付款紀錄載入失敗</t>
+  </si>
+  <si>
+    <t>Failed to load payments</t>
+  </si>
+  <si>
     <t>catalogStatus.all</t>
   </si>
   <si>
@@ -1528,10 +1555,19 @@
     <t>upload.platformFee</t>
   </si>
   <si>
-    <t>平台抽成 3%</t>
-  </si>
-  <si>
-    <t>3% platform fee</t>
+    <t>平台抽成 10% + 每筆 NT$12</t>
+  </si>
+  <si>
+    <t>10% + NT$12 platform fee</t>
+  </si>
+  <si>
+    <t>upload.minPriceHint</t>
+  </si>
+  <si>
+    <t>付費商品最低定價 ${min}。</t>
+  </si>
+  <si>
+    <t>Paid items start at ${min}.</t>
   </si>
   <si>
     <t>upload.blurbLabel</t>
@@ -1915,10 +1951,10 @@
     <t>upload.copyrightNote</t>
   </si>
   <si>
-    <t>你保留作品 100% 著作權，平台僅收取 3% 交易手續費。</t>
-  </si>
-  <si>
-    <t>You keep 100% of the copyright; the platform takes only a 3% transaction fee.</t>
+    <t>你保留作品 100% 著作權，平台僅收取售價 10% 加每筆 NT$12 交易手續費。</t>
+  </si>
+  <si>
+    <t>You keep 100% of the copyright; the platform takes only 10% of the sale price plus NT$12 per transaction.</t>
   </si>
   <si>
     <t>upload.prevStep</t>
@@ -2770,6 +2806,24 @@
     <t>The Stripe setup link has expired. Please click the button to try again.</t>
   </si>
   <si>
+    <t>payouts.actionDashboard</t>
+  </si>
+  <si>
+    <t>前往 Stripe 儀表板</t>
+  </si>
+  <si>
+    <t>Open Stripe dashboard</t>
+  </si>
+  <si>
+    <t>payouts.msgDashboardFailed</t>
+  </si>
+  <si>
+    <t>無法開啟 Stripe 儀表板，請稍後再試</t>
+  </si>
+  <si>
+    <t>Couldn't open the Stripe dashboard. Please try again later.</t>
+  </si>
+  <si>
     <t>catalogCategories.searchPlaceholder</t>
   </si>
   <si>
@@ -3091,15 +3145,6 @@
     <t>This category still has subcategories or product references and can’t be deleted.</t>
   </si>
   <si>
-    <t>catalogCategories.systemDeleteBlocked</t>
-  </si>
-  <si>
-    <t>系統預設分類，不允許刪除。</t>
-  </si>
-  <si>
-    <t>System default category — deletion is not allowed.</t>
-  </si>
-  <si>
     <t>auditLog.subStats</t>
   </si>
   <si>
@@ -4000,6 +4045,18 @@
     <t>Search buyer email</t>
   </si>
   <si>
+    <t>orders.searchKeyword</t>
+  </si>
+  <si>
+    <t>orders.searchKeywordPlaceholder</t>
+  </si>
+  <si>
+    <t>搜尋買家 Email 或訂單編號</t>
+  </si>
+  <si>
+    <t>Search buyer email or order number</t>
+  </si>
+  <si>
     <t>orders.orderStatus</t>
   </si>
   <si>
@@ -4381,6 +4438,15 @@
     <t>FAQ</t>
   </si>
   <si>
+    <t>route.adminPayments</t>
+  </si>
+  <si>
+    <t>金流付款</t>
+  </si>
+  <si>
+    <t>Payments</t>
+  </si>
+  <si>
     <t>header.openMenu</t>
   </si>
   <si>
@@ -4678,6 +4744,33 @@
     <t>{sales} sold · {views} views</t>
   </si>
   <si>
+    <t>overview.categoryOther</t>
+  </si>
+  <si>
+    <t>其他</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>overview.payoutEstimate</t>
+  </si>
+  <si>
+    <t>本期預估</t>
+  </si>
+  <si>
+    <t>This cycle (est.)</t>
+  </si>
+  <si>
+    <t>overview.emptyProducts</t>
+  </si>
+  <si>
+    <t>尚無商品資料</t>
+  </si>
+  <si>
+    <t>overview.emptyOrders</t>
+  </si>
+  <si>
     <t>orderStatus.all</t>
   </si>
   <si>
@@ -4882,6 +4975,24 @@
     <t>Order created</t>
   </si>
   <si>
+    <t>orderModal.platformFee</t>
+  </si>
+  <si>
+    <t>平台服務費</t>
+  </si>
+  <si>
+    <t>Platform fee</t>
+  </si>
+  <si>
+    <t>orderModal.netAmount</t>
+  </si>
+  <si>
+    <t>賣家實收</t>
+  </si>
+  <si>
+    <t>Seller net payout</t>
+  </si>
+  <si>
     <t>purchaseModal.title</t>
   </si>
   <si>
@@ -4987,6 +5098,15 @@
     <t>{storeName} released a new product "{catalogName}"</t>
   </si>
   <si>
+    <t>notifications.catalogVersionReleased</t>
+  </si>
+  <si>
+    <t>你買過的「{catalogName}」發布了新版本 {version}</t>
+  </si>
+  <si>
+    <t>"{catalogName}" you bought released version {version}</t>
+  </si>
+  <si>
     <t>notifications.storeAnnouncement</t>
   </si>
   <si>
@@ -6229,6 +6349,9 @@
     <t>Give away free</t>
   </si>
   <si>
+    <t>productEdit.minPriceHint</t>
+  </si>
+  <si>
     <t>productEdit.coverHueLabel</t>
   </si>
   <si>
@@ -6535,6 +6658,51 @@
     <t>Buyers will no longer be able to get this file. Delete it?</t>
   </si>
   <si>
+    <t>productEdit.notifyBuyers</t>
+  </si>
+  <si>
+    <t>通知買家</t>
+  </si>
+  <si>
+    <t>Notify buyers</t>
+  </si>
+  <si>
+    <t>productEdit.notifyBuyersConfirm</t>
+  </si>
+  <si>
+    <t>將寄信並推播給所有買過這件商品的買家，每個版本只能通知一次。確定要送出嗎？</t>
+  </si>
+  <si>
+    <t>This will email and notify everyone who bought this product. Each version can only be announced once. Send it?</t>
+  </si>
+  <si>
+    <t>productEdit.buyersNotifiedAt</t>
+  </si>
+  <si>
+    <t>已於 {date} 通知買家</t>
+  </si>
+  <si>
+    <t>Buyers notified on {date}</t>
+  </si>
+  <si>
+    <t>productEdit.msgBuyersNotified</t>
+  </si>
+  <si>
+    <t>已送出買家通知。</t>
+  </si>
+  <si>
+    <t>Buyer notification sent.</t>
+  </si>
+  <si>
+    <t>productEdit.msgNotifyBuyersFailed</t>
+  </si>
+  <si>
+    <t>通知買家失敗</t>
+  </si>
+  <si>
+    <t>Failed to notify buyers</t>
+  </si>
+  <si>
     <t>productEdit.notFoundTitle</t>
   </si>
   <si>
@@ -6668,6 +6836,174 @@
   </si>
   <si>
     <t>Failed to get download link</t>
+  </si>
+  <si>
+    <t>paymentStatus.all</t>
+  </si>
+  <si>
+    <t>paymentStatus.pending</t>
+  </si>
+  <si>
+    <t>paymentStatus.processing</t>
+  </si>
+  <si>
+    <t>處理中</t>
+  </si>
+  <si>
+    <t>Processing</t>
+  </si>
+  <si>
+    <t>paymentStatus.succeeded</t>
+  </si>
+  <si>
+    <t>Succeeded</t>
+  </si>
+  <si>
+    <t>paymentStatus.failed</t>
+  </si>
+  <si>
+    <t>付款失敗</t>
+  </si>
+  <si>
+    <t>paymentStatus.cancelled</t>
+  </si>
+  <si>
+    <t>paymentStatus.expired</t>
+  </si>
+  <si>
+    <t>已過期</t>
+  </si>
+  <si>
+    <t>Expired</t>
+  </si>
+  <si>
+    <t>paymentStatus.unknown</t>
+  </si>
+  <si>
+    <t>payments.buyerEmail</t>
+  </si>
+  <si>
+    <t>payments.buyerEmailPlaceholder</t>
+  </si>
+  <si>
+    <t>輸入信箱搜尋</t>
+  </si>
+  <si>
+    <t>Search by email</t>
+  </si>
+  <si>
+    <t>payments.paymentStatus</t>
+  </si>
+  <si>
+    <t>付款狀態</t>
+  </si>
+  <si>
+    <t>Payment status</t>
+  </si>
+  <si>
+    <t>payments.colCreatedAt</t>
+  </si>
+  <si>
+    <t>payments.colBuyer</t>
+  </si>
+  <si>
+    <t>payments.colOrder</t>
+  </si>
+  <si>
+    <t>訂單</t>
+  </si>
+  <si>
+    <t>payments.colAmount</t>
+  </si>
+  <si>
+    <t>payments.colFee</t>
+  </si>
+  <si>
+    <t>平台抽成</t>
+  </si>
+  <si>
+    <t>payments.colDetail</t>
+  </si>
+  <si>
+    <t>詳情</t>
+  </si>
+  <si>
+    <t>Detail</t>
+  </si>
+  <si>
+    <t>payments.emptyTitle</t>
+  </si>
+  <si>
+    <t>沒有付款紀錄</t>
+  </si>
+  <si>
+    <t>No payments</t>
+  </si>
+  <si>
+    <t>payments.emptyDesc</t>
+  </si>
+  <si>
+    <t>目前沒有符合條件的付款</t>
+  </si>
+  <si>
+    <t>No payments match the current filters</t>
+  </si>
+  <si>
+    <t>payments.modalTitle</t>
+  </si>
+  <si>
+    <t>付款詳情</t>
+  </si>
+  <si>
+    <t>Payment details</t>
+  </si>
+  <si>
+    <t>payments.orderId</t>
+  </si>
+  <si>
+    <t>訂單 ID</t>
+  </si>
+  <si>
+    <t>Order ID</t>
+  </si>
+  <si>
+    <t>payments.storeId</t>
+  </si>
+  <si>
+    <t>商店 ID</t>
+  </si>
+  <si>
+    <t>Store ID</t>
+  </si>
+  <si>
+    <t>payments.netAmount</t>
+  </si>
+  <si>
+    <t>Seller net</t>
+  </si>
+  <si>
+    <t>payments.paidAt</t>
+  </si>
+  <si>
+    <t>付款時間</t>
+  </si>
+  <si>
+    <t>Paid at</t>
+  </si>
+  <si>
+    <t>payments.checkoutSession</t>
+  </si>
+  <si>
+    <t>Checkout Session</t>
+  </si>
+  <si>
+    <t>payments.openInStripe</t>
+  </si>
+  <si>
+    <t>在 Stripe Dashboard 開啟</t>
+  </si>
+  <si>
+    <t>Open in Stripe Dashboard</t>
   </si>
 </sst>
 </file>
@@ -7053,7 +7389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C832"/>
+  <dimension ref="A1:C879"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -7780,43 +8116,43 @@
         <v>195</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>43</v>
+        <v>196</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>44</v>
+        <v>197</v>
       </c>
     </row>
     <row r="67" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="68" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="69" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>203</v>
+        <v>43</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>204</v>
+        <v>44</v>
       </c>
     </row>
     <row r="70" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7838,37 +8174,37 @@
         <v>209</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="72" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="73" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="74" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>218</v>
@@ -7915,40 +8251,40 @@
         <v>229</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
     </row>
     <row r="79" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="80" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="81" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>238</v>
+        <v>207</v>
       </c>
     </row>
     <row r="82" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8286,43 +8622,43 @@
         <v>329</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>28</v>
+        <v>330</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>29</v>
+        <v>331</v>
       </c>
     </row>
     <row r="113" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="114" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="115" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>337</v>
+        <v>28</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>338</v>
+        <v>29</v>
       </c>
     </row>
     <row r="116" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8440,43 +8776,43 @@
         <v>369</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>306</v>
+        <v>370</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>307</v>
+        <v>371</v>
       </c>
     </row>
     <row r="127" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="128" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="129" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>377</v>
+        <v>315</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>378</v>
+        <v>316</v>
       </c>
     </row>
     <row r="130" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8726,43 +9062,43 @@
         <v>445</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>392</v>
+        <v>446</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>393</v>
+        <v>447</v>
       </c>
     </row>
     <row r="153" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="154" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="155" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>453</v>
+        <v>401</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>454</v>
+        <v>402</v>
       </c>
     </row>
     <row r="156" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8770,43 +9106,43 @@
         <v>455</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>318</v>
+        <v>456</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>319</v>
+        <v>457</v>
       </c>
     </row>
     <row r="157" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="158" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="159" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>463</v>
+        <v>327</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>464</v>
+        <v>328</v>
       </c>
     </row>
     <row r="160" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9254,120 +9590,120 @@
         <v>585</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>178</v>
+        <v>586</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>179</v>
+        <v>587</v>
       </c>
     </row>
     <row r="201" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="202" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="203" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="204" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>596</v>
+        <v>181</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>596</v>
+        <v>182</v>
       </c>
     </row>
     <row r="205" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="206" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>550</v>
+        <v>602</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>551</v>
+        <v>603</v>
       </c>
     </row>
     <row r="207" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
     </row>
     <row r="208" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="209" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="210" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>611</v>
+        <v>562</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>612</v>
+        <v>563</v>
       </c>
     </row>
     <row r="211" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9378,106 +9714,106 @@
         <v>614</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>479</v>
+        <v>615</v>
       </c>
     </row>
     <row r="212" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>490</v>
+        <v>617</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>491</v>
+        <v>618</v>
       </c>
     </row>
     <row r="213" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>499</v>
+        <v>620</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>224</v>
+        <v>621</v>
       </c>
     </row>
     <row r="214" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
     </row>
     <row r="215" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>622</v>
+        <v>488</v>
       </c>
     </row>
     <row r="216" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>526</v>
+        <v>499</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>527</v>
+        <v>500</v>
       </c>
     </row>
     <row r="217" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>625</v>
+        <v>508</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>626</v>
+        <v>233</v>
       </c>
     </row>
     <row r="218" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="219" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="220" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>634</v>
+        <v>538</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>635</v>
+        <v>539</v>
       </c>
     </row>
     <row r="221" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9496,54 +9832,54 @@
         <v>639</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>22</v>
+        <v>640</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>23</v>
+        <v>641</v>
       </c>
     </row>
     <row r="223" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="224" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
     </row>
     <row r="225" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="226" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>650</v>
+        <v>22</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>651</v>
+        <v>23</v>
       </c>
     </row>
     <row r="227" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9562,51 +9898,51 @@
         <v>655</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>490</v>
+        <v>656</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="229" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="230" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="231" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="232" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>667</v>
+        <v>499</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>668</v>
@@ -9672,54 +10008,54 @@
         <v>684</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>187</v>
+        <v>685</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>188</v>
+        <v>686</v>
       </c>
     </row>
     <row r="239" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
     </row>
     <row r="240" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="241" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
     <row r="242" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>695</v>
+        <v>193</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>696</v>
+        <v>194</v>
       </c>
     </row>
     <row r="243" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9804,76 +10140,76 @@
         <v>718</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>209</v>
+        <v>719</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>209</v>
+        <v>720</v>
       </c>
     </row>
     <row r="251" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
     </row>
     <row r="252" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>206</v>
+        <v>725</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>207</v>
+        <v>726</v>
       </c>
     </row>
     <row r="253" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
     </row>
     <row r="254" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>727</v>
+        <v>218</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>728</v>
+        <v>218</v>
       </c>
     </row>
     <row r="255" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
     </row>
     <row r="256" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>733</v>
+        <v>215</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>734</v>
+        <v>216</v>
       </c>
     </row>
     <row r="257" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9925,76 +10261,76 @@
         <v>747</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>358</v>
+        <v>748</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>359</v>
+        <v>749</v>
       </c>
     </row>
     <row r="262" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
     </row>
     <row r="263" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>361</v>
+        <v>754</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>362</v>
+        <v>755</v>
       </c>
     </row>
     <row r="264" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
     </row>
     <row r="265" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>756</v>
+        <v>367</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>757</v>
+        <v>368</v>
       </c>
     </row>
     <row r="266" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
     </row>
     <row r="267" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>762</v>
+        <v>370</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>763</v>
+        <v>371</v>
       </c>
     </row>
     <row r="268" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10112,76 +10448,76 @@
         <v>794</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>358</v>
+        <v>795</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>359</v>
+        <v>796</v>
       </c>
     </row>
     <row r="279" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>749</v>
+        <v>798</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>750</v>
+        <v>799</v>
       </c>
     </row>
     <row r="280" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>361</v>
+        <v>801</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>362</v>
+        <v>802</v>
       </c>
     </row>
     <row r="281" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
-        <v>797</v>
+        <v>803</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>798</v>
+        <v>804</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>799</v>
+        <v>805</v>
       </c>
     </row>
     <row r="282" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
-        <v>800</v>
+        <v>806</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>801</v>
+        <v>367</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>802</v>
+        <v>368</v>
       </c>
     </row>
     <row r="283" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>804</v>
+        <v>761</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>805</v>
+        <v>762</v>
       </c>
     </row>
     <row r="284" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>807</v>
+        <v>370</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>808</v>
+        <v>371</v>
       </c>
     </row>
     <row r="285" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10222,54 +10558,54 @@
         <v>818</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>701</v>
+        <v>819</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>702</v>
+        <v>820</v>
       </c>
     </row>
     <row r="289" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
     </row>
     <row r="290" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
     </row>
     <row r="291" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
     </row>
     <row r="292" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>829</v>
+        <v>713</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>830</v>
+        <v>714</v>
       </c>
     </row>
     <row r="293" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10332,54 +10668,54 @@
         <v>846</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>22</v>
+        <v>847</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>23</v>
+        <v>848</v>
       </c>
     </row>
     <row r="299" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
     </row>
     <row r="300" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
     </row>
     <row r="301" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
     </row>
     <row r="302" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>857</v>
+        <v>22</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>858</v>
+        <v>23</v>
       </c>
     </row>
     <row r="303" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10662,98 +10998,98 @@
         <v>934</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>614</v>
+        <v>935</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>479</v>
+        <v>936</v>
       </c>
     </row>
     <row r="329" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
     </row>
     <row r="330" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>306</v>
+        <v>941</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>307</v>
+        <v>942</v>
       </c>
     </row>
     <row r="331" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
-        <v>939</v>
+        <v>943</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>941</v>
+        <v>945</v>
       </c>
     </row>
     <row r="332" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
-        <v>942</v>
+        <v>946</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
     </row>
     <row r="333" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>947</v>
+        <v>951</v>
       </c>
     </row>
     <row r="334" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>949</v>
+        <v>626</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>950</v>
+        <v>488</v>
       </c>
     </row>
     <row r="335" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
     </row>
     <row r="336" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>955</v>
+        <v>315</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>956</v>
+        <v>316</v>
       </c>
     </row>
     <row r="337" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10794,76 +11130,76 @@
         <v>966</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>932</v>
+        <v>967</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>933</v>
+        <v>968</v>
       </c>
     </row>
     <row r="341" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
     </row>
     <row r="342" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
     </row>
     <row r="343" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
     </row>
     <row r="344" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
     </row>
     <row r="345" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
     </row>
     <row r="346" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>983</v>
+        <v>950</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>984</v>
+        <v>951</v>
       </c>
     </row>
     <row r="347" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10882,142 +11218,142 @@
         <v>988</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>804</v>
+        <v>989</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>805</v>
+        <v>990</v>
       </c>
     </row>
     <row r="349" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
     </row>
     <row r="350" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
     </row>
     <row r="351" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
     </row>
     <row r="352" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="353" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="354" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>52</v>
+        <v>816</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>53</v>
+        <v>817</v>
       </c>
     </row>
     <row r="355" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="356" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="357" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="358" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="359" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="360" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>1021</v>
+        <v>52</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>1022</v>
+        <v>53</v>
       </c>
     </row>
     <row r="361" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11149,73 +11485,73 @@
         <v>1057</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="373" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>440</v>
+        <v>1060</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>441</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="374" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
-        <v>1059</v>
+        <v>1062</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>1060</v>
+        <v>1063</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="375" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>1063</v>
+        <v>1066</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="376" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A376" s="2" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="C376" s="2" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="377" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A377" s="2" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="C377" s="2" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="378" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>1072</v>
+        <v>449</v>
       </c>
       <c r="C378" s="2" t="s">
-        <v>1073</v>
+        <v>450</v>
       </c>
     </row>
     <row r="379" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11270,59 +11606,59 @@
         <v>1087</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="384" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A384" s="2" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="385" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A385" s="2" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="C385" s="2" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="386" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A386" s="2" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="387" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A387" s="2" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="C387" s="2" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="388" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A388" s="2" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="C388" s="2" t="s">
         <v>1102</v>
@@ -11608,109 +11944,109 @@
         <v>1178</v>
       </c>
       <c r="B414" s="2" t="s">
-        <v>318</v>
+        <v>1179</v>
       </c>
       <c r="C414" s="2" t="s">
-        <v>319</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="415" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A415" s="2" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="C415" s="2" t="s">
-        <v>721</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="416" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A416" s="2" t="s">
-        <v>1181</v>
+        <v>1184</v>
       </c>
       <c r="B416" s="2" t="s">
-        <v>1182</v>
+        <v>1185</v>
       </c>
       <c r="C416" s="2" t="s">
-        <v>1183</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="417" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A417" s="2" t="s">
-        <v>1184</v>
+        <v>1187</v>
       </c>
       <c r="B417" s="2" t="s">
-        <v>1185</v>
+        <v>1188</v>
       </c>
       <c r="C417" s="2" t="s">
-        <v>1186</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="418" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A418" s="2" t="s">
-        <v>1187</v>
+        <v>1190</v>
       </c>
       <c r="B418" s="2" t="s">
-        <v>206</v>
+        <v>1191</v>
       </c>
       <c r="C418" s="2" t="s">
-        <v>207</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="419" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A419" s="2" t="s">
-        <v>1188</v>
+        <v>1193</v>
       </c>
       <c r="B419" s="2" t="s">
-        <v>1189</v>
+        <v>327</v>
       </c>
       <c r="C419" s="2" t="s">
-        <v>1190</v>
+        <v>328</v>
       </c>
     </row>
     <row r="420" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A420" s="2" t="s">
-        <v>1191</v>
+        <v>1194</v>
       </c>
       <c r="B420" s="2" t="s">
-        <v>1192</v>
+        <v>1195</v>
       </c>
       <c r="C420" s="2" t="s">
-        <v>1193</v>
+        <v>733</v>
       </c>
     </row>
     <row r="421" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A421" s="2" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="B421" s="2" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="C421" s="2" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="422" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A422" s="2" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="B422" s="2" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="C422" s="2" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="423" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A423" s="2" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>1201</v>
+        <v>215</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>1202</v>
+        <v>216</v>
       </c>
     </row>
     <row r="424" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11751,76 +12087,76 @@
         <v>1212</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>300</v>
+        <v>1213</v>
       </c>
       <c r="C427" s="2" t="s">
-        <v>301</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="428" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A428" s="2" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="B428" s="2" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="C428" s="2" t="s">
-        <v>1199</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="429" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A429" s="2" t="s">
-        <v>1215</v>
+        <v>1218</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>1216</v>
+        <v>1219</v>
       </c>
       <c r="C429" s="2" t="s">
-        <v>1217</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="430" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A430" s="2" t="s">
-        <v>1218</v>
+        <v>1221</v>
       </c>
       <c r="B430" s="2" t="s">
-        <v>1219</v>
+        <v>1222</v>
       </c>
       <c r="C430" s="2" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="431" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A431" s="2" t="s">
-        <v>1221</v>
+        <v>1224</v>
       </c>
       <c r="B431" s="2" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="C431" s="2" t="s">
-        <v>1223</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="432" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A432" s="2" t="s">
-        <v>1224</v>
+        <v>1227</v>
       </c>
       <c r="B432" s="2" t="s">
-        <v>1225</v>
+        <v>309</v>
       </c>
       <c r="C432" s="2" t="s">
-        <v>1226</v>
+        <v>310</v>
       </c>
     </row>
     <row r="433" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A433" s="2" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="C433" s="2" t="s">
-        <v>1229</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="434" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11828,65 +12164,65 @@
         <v>1230</v>
       </c>
       <c r="B434" s="2" t="s">
-        <v>318</v>
+        <v>1231</v>
       </c>
       <c r="C434" s="2" t="s">
-        <v>319</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="435" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A435" s="2" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="B435" s="2" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="C435" s="2" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="436" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A436" s="2" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="B436" s="2" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="C436" s="2" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="437" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A437" s="2" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="B437" s="2" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="C437" s="2" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="438" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A438" s="2" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="B438" s="2" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="C438" s="2" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="439" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A439" s="2" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="B439" s="2" t="s">
-        <v>1244</v>
+        <v>327</v>
       </c>
       <c r="C439" s="2" t="s">
-        <v>1245</v>
+        <v>328</v>
       </c>
     </row>
     <row r="440" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12015,62 +12351,62 @@
         <v>1279</v>
       </c>
       <c r="B451" s="2" t="s">
-        <v>374</v>
+        <v>1280</v>
       </c>
       <c r="C451" s="2" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="452" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A452" s="2" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B452" s="2" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="C452" s="2" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="453" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A453" s="2" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="C453" s="2" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="454" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A454" s="2" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="C454" s="2" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="455" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A455" s="2" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="C455" s="2" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="456" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A456" s="2" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="B456" s="2" t="s">
-        <v>1294</v>
+        <v>383</v>
       </c>
       <c r="C456" s="2" t="s">
         <v>1295</v>
@@ -12257,10 +12593,10 @@
         <v>1344</v>
       </c>
       <c r="B473" s="2" t="s">
-        <v>1060</v>
+        <v>7</v>
       </c>
       <c r="C473" s="2" t="s">
-        <v>1061</v>
+        <v>8</v>
       </c>
     </row>
     <row r="474" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12293,268 +12629,268 @@
         <v>1352</v>
       </c>
       <c r="C476" s="2" t="s">
-        <v>198</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="477" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A477" s="2" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B477" s="2" t="s">
-        <v>200</v>
+        <v>1355</v>
       </c>
       <c r="C477" s="2" t="s">
-        <v>201</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="478" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A478" s="2" t="s">
-        <v>1354</v>
+        <v>1357</v>
       </c>
       <c r="B478" s="2" t="s">
-        <v>1355</v>
+        <v>1358</v>
       </c>
       <c r="C478" s="2" t="s">
-        <v>1356</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="479" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A479" s="2" t="s">
-        <v>1357</v>
+        <v>1360</v>
       </c>
       <c r="B479" s="2" t="s">
-        <v>206</v>
+        <v>1361</v>
       </c>
       <c r="C479" s="2" t="s">
-        <v>207</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="480" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A480" s="2" t="s">
-        <v>1358</v>
+        <v>1363</v>
       </c>
       <c r="B480" s="2" t="s">
-        <v>1359</v>
+        <v>1075</v>
       </c>
       <c r="C480" s="2" t="s">
-        <v>1360</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="481" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A481" s="2" t="s">
-        <v>1361</v>
+        <v>1364</v>
       </c>
       <c r="B481" s="2" t="s">
-        <v>306</v>
+        <v>1365</v>
       </c>
       <c r="C481" s="2" t="s">
-        <v>307</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="482" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A482" s="2" t="s">
-        <v>1362</v>
+        <v>1367</v>
       </c>
       <c r="B482" s="2" t="s">
-        <v>1363</v>
+        <v>1368</v>
       </c>
       <c r="C482" s="2" t="s">
-        <v>1364</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="483" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A483" s="2" t="s">
-        <v>1365</v>
+        <v>1370</v>
       </c>
       <c r="B483" s="2" t="s">
-        <v>1173</v>
+        <v>1371</v>
       </c>
       <c r="C483" s="2" t="s">
-        <v>1366</v>
+        <v>207</v>
       </c>
     </row>
     <row r="484" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A484" s="2" t="s">
-        <v>1367</v>
+        <v>1372</v>
       </c>
       <c r="B484" s="2" t="s">
-        <v>327</v>
+        <v>209</v>
       </c>
       <c r="C484" s="2" t="s">
-        <v>328</v>
+        <v>210</v>
       </c>
     </row>
     <row r="485" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A485" s="2" t="s">
-        <v>1368</v>
+        <v>1373</v>
       </c>
       <c r="B485" s="2" t="s">
-        <v>321</v>
+        <v>1374</v>
       </c>
       <c r="C485" s="2" t="s">
-        <v>322</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="486" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A486" s="2" t="s">
-        <v>1369</v>
+        <v>1376</v>
       </c>
       <c r="B486" s="2" t="s">
-        <v>1370</v>
+        <v>215</v>
       </c>
       <c r="C486" s="2" t="s">
-        <v>1371</v>
+        <v>216</v>
       </c>
     </row>
     <row r="487" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A487" s="2" t="s">
-        <v>1372</v>
+        <v>1377</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>1373</v>
+        <v>1378</v>
       </c>
       <c r="C487" s="2" t="s">
-        <v>1374</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="488" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A488" s="2" t="s">
-        <v>1375</v>
+        <v>1380</v>
       </c>
       <c r="B488" s="2" t="s">
-        <v>337</v>
+        <v>315</v>
       </c>
       <c r="C488" s="2" t="s">
-        <v>338</v>
+        <v>316</v>
       </c>
     </row>
     <row r="489" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A489" s="2" t="s">
-        <v>1376</v>
+        <v>1381</v>
       </c>
       <c r="B489" s="2" t="s">
-        <v>1377</v>
+        <v>1382</v>
       </c>
       <c r="C489" s="2" t="s">
-        <v>1378</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="490" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A490" s="2" t="s">
-        <v>1379</v>
+        <v>1384</v>
       </c>
       <c r="B490" s="2" t="s">
-        <v>343</v>
+        <v>1188</v>
       </c>
       <c r="C490" s="2" t="s">
-        <v>344</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="491" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A491" s="2" t="s">
-        <v>1380</v>
+        <v>1386</v>
       </c>
       <c r="B491" s="2" t="s">
-        <v>1381</v>
+        <v>336</v>
       </c>
       <c r="C491" s="2" t="s">
-        <v>1382</v>
+        <v>337</v>
       </c>
     </row>
     <row r="492" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A492" s="2" t="s">
-        <v>1383</v>
+        <v>1387</v>
       </c>
       <c r="B492" s="2" t="s">
-        <v>1384</v>
+        <v>330</v>
       </c>
       <c r="C492" s="2" t="s">
-        <v>1384</v>
+        <v>331</v>
       </c>
     </row>
     <row r="493" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A493" s="2" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="B493" s="2" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="C493" s="2" t="s">
-        <v>1386</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="494" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A494" s="2" t="s">
-        <v>1387</v>
+        <v>1391</v>
       </c>
       <c r="B494" s="2" t="s">
-        <v>1388</v>
+        <v>1392</v>
       </c>
       <c r="C494" s="2" t="s">
-        <v>1389</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="495" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A495" s="2" t="s">
-        <v>1390</v>
+        <v>1394</v>
       </c>
       <c r="B495" s="2" t="s">
-        <v>1388</v>
+        <v>346</v>
       </c>
       <c r="C495" s="2" t="s">
-        <v>1389</v>
+        <v>347</v>
       </c>
     </row>
     <row r="496" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A496" s="2" t="s">
-        <v>1391</v>
+        <v>1395</v>
       </c>
       <c r="B496" s="2" t="s">
-        <v>1392</v>
+        <v>1396</v>
       </c>
       <c r="C496" s="2" t="s">
-        <v>1393</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="497" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A497" s="2" t="s">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="B497" s="2" t="s">
-        <v>1395</v>
+        <v>352</v>
       </c>
       <c r="C497" s="2" t="s">
-        <v>1396</v>
+        <v>353</v>
       </c>
     </row>
     <row r="498" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A498" s="2" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>1398</v>
+        <v>1400</v>
       </c>
       <c r="C498" s="2" t="s">
-        <v>1399</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="499" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A499" s="2" t="s">
-        <v>1400</v>
+        <v>1402</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="C499" s="2" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="500" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A500" s="2" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="B500" s="2" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="C500" s="2" t="s">
         <v>1405</v>
@@ -12576,120 +12912,120 @@
         <v>1409</v>
       </c>
       <c r="B502" s="2" t="s">
-        <v>1410</v>
+        <v>1407</v>
       </c>
       <c r="C502" s="2" t="s">
-        <v>1411</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="503" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A503" s="2" t="s">
+        <v>1410</v>
+      </c>
+      <c r="B503" s="2" t="s">
+        <v>1411</v>
+      </c>
+      <c r="C503" s="2" t="s">
         <v>1412</v>
-      </c>
-      <c r="B503" s="2" t="s">
-        <v>1413</v>
-      </c>
-      <c r="C503" s="2" t="s">
-        <v>1414</v>
       </c>
     </row>
     <row r="504" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A504" s="2" t="s">
+        <v>1413</v>
+      </c>
+      <c r="B504" s="2" t="s">
+        <v>1414</v>
+      </c>
+      <c r="C504" s="2" t="s">
         <v>1415</v>
-      </c>
-      <c r="B504" s="2" t="s">
-        <v>1416</v>
-      </c>
-      <c r="C504" s="2" t="s">
-        <v>1417</v>
       </c>
     </row>
     <row r="505" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A505" s="2" t="s">
+        <v>1416</v>
+      </c>
+      <c r="B505" s="2" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C505" s="2" t="s">
         <v>1418</v>
-      </c>
-      <c r="B505" s="2" t="s">
-        <v>1419</v>
-      </c>
-      <c r="C505" s="2" t="s">
-        <v>1420</v>
       </c>
     </row>
     <row r="506" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A506" s="2" t="s">
+        <v>1419</v>
+      </c>
+      <c r="B506" s="2" t="s">
+        <v>1420</v>
+      </c>
+      <c r="C506" s="2" t="s">
         <v>1421</v>
-      </c>
-      <c r="B506" s="2" t="s">
-        <v>1422</v>
-      </c>
-      <c r="C506" s="2" t="s">
-        <v>1423</v>
       </c>
     </row>
     <row r="507" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A507" s="2" t="s">
+        <v>1422</v>
+      </c>
+      <c r="B507" s="2" t="s">
+        <v>1423</v>
+      </c>
+      <c r="C507" s="2" t="s">
         <v>1424</v>
-      </c>
-      <c r="B507" s="2" t="s">
-        <v>1425</v>
-      </c>
-      <c r="C507" s="2" t="s">
-        <v>1426</v>
       </c>
     </row>
     <row r="508" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A508" s="2" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B508" s="2" t="s">
+        <v>1426</v>
+      </c>
+      <c r="C508" s="2" t="s">
         <v>1427</v>
-      </c>
-      <c r="B508" s="2" t="s">
-        <v>1428</v>
-      </c>
-      <c r="C508" s="2" t="s">
-        <v>1429</v>
       </c>
     </row>
     <row r="509" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A509" s="2" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B509" s="2" t="s">
+        <v>1429</v>
+      </c>
+      <c r="C509" s="2" t="s">
         <v>1430</v>
-      </c>
-      <c r="B509" s="2" t="s">
-        <v>1431</v>
-      </c>
-      <c r="C509" s="2" t="s">
-        <v>1408</v>
       </c>
     </row>
     <row r="510" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A510" s="2" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B510" s="2" t="s">
         <v>1432</v>
       </c>
-      <c r="B510" s="2" t="s">
+      <c r="C510" s="2" t="s">
         <v>1433</v>
-      </c>
-      <c r="C510" s="2" t="s">
-        <v>1434</v>
       </c>
     </row>
     <row r="511" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A511" s="2" t="s">
+        <v>1434</v>
+      </c>
+      <c r="B511" s="2" t="s">
         <v>1435</v>
       </c>
-      <c r="B511" s="2" t="s">
+      <c r="C511" s="2" t="s">
         <v>1436</v>
-      </c>
-      <c r="C511" s="2" t="s">
-        <v>1437</v>
       </c>
     </row>
     <row r="512" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A512" s="2" t="s">
+        <v>1437</v>
+      </c>
+      <c r="B512" s="2" t="s">
         <v>1438</v>
       </c>
-      <c r="B512" s="2" t="s">
+      <c r="C512" s="2" t="s">
         <v>1439</v>
-      </c>
-      <c r="C512" s="2" t="s">
-        <v>1414</v>
       </c>
     </row>
     <row r="513" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12730,43 +13066,43 @@
         <v>1449</v>
       </c>
       <c r="B516" s="2" t="s">
-        <v>1301</v>
+        <v>1450</v>
       </c>
       <c r="C516" s="2" t="s">
-        <v>1301</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="517" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A517" s="2" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="B517" s="2" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="C517" s="2" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="518" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A518" s="2" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="B518" s="2" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="C518" s="2" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="519" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A519" s="2" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="B519" s="2" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="C519" s="2" t="s">
-        <v>1458</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="520" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12807,32 +13143,32 @@
         <v>1468</v>
       </c>
       <c r="B523" s="2" t="s">
-        <v>1469</v>
+        <v>1316</v>
       </c>
       <c r="C523" s="2" t="s">
-        <v>1470</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="524" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A524" s="2" t="s">
+        <v>1469</v>
+      </c>
+      <c r="B524" s="2" t="s">
+        <v>1470</v>
+      </c>
+      <c r="C524" s="2" t="s">
         <v>1471</v>
-      </c>
-      <c r="B524" s="2" t="s">
-        <v>1472</v>
-      </c>
-      <c r="C524" s="2" t="s">
-        <v>1473</v>
       </c>
     </row>
     <row r="525" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A525" s="2" t="s">
+        <v>1472</v>
+      </c>
+      <c r="B525" s="2" t="s">
+        <v>1473</v>
+      </c>
+      <c r="C525" s="2" t="s">
         <v>1474</v>
-      </c>
-      <c r="B525" s="2" t="s">
-        <v>1336</v>
-      </c>
-      <c r="C525" s="2" t="s">
-        <v>1337</v>
       </c>
     </row>
     <row r="526" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12909,117 +13245,117 @@
         <v>1494</v>
       </c>
       <c r="C532" s="2" t="s">
-        <v>232</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="533" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A533" s="2" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="B533" s="2" t="s">
-        <v>200</v>
+        <v>1355</v>
       </c>
       <c r="C533" s="2" t="s">
-        <v>201</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="534" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A534" s="2" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="B534" s="2" t="s">
-        <v>203</v>
+        <v>1498</v>
       </c>
       <c r="C534" s="2" t="s">
-        <v>204</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="535" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A535" s="2" t="s">
-        <v>1497</v>
+        <v>1500</v>
       </c>
       <c r="B535" s="2" t="s">
-        <v>707</v>
+        <v>1501</v>
       </c>
       <c r="C535" s="2" t="s">
-        <v>708</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="536" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A536" s="2" t="s">
-        <v>1498</v>
+        <v>1503</v>
       </c>
       <c r="B536" s="2" t="s">
-        <v>1499</v>
+        <v>1504</v>
       </c>
       <c r="C536" s="2" t="s">
-        <v>1500</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="537" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A537" s="2" t="s">
-        <v>1501</v>
+        <v>1506</v>
       </c>
       <c r="B537" s="2" t="s">
-        <v>1502</v>
+        <v>1507</v>
       </c>
       <c r="C537" s="2" t="s">
-        <v>1503</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="538" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A538" s="2" t="s">
-        <v>1504</v>
+        <v>1509</v>
       </c>
       <c r="B538" s="2" t="s">
-        <v>1505</v>
+        <v>1510</v>
       </c>
       <c r="C538" s="2" t="s">
-        <v>1506</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="539" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A539" s="2" t="s">
-        <v>1507</v>
+        <v>1512</v>
       </c>
       <c r="B539" s="2" t="s">
-        <v>1508</v>
+        <v>1513</v>
       </c>
       <c r="C539" s="2" t="s">
-        <v>1509</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="540" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A540" s="2" t="s">
-        <v>1510</v>
+        <v>1515</v>
       </c>
       <c r="B540" s="2" t="s">
-        <v>1511</v>
+        <v>1516</v>
       </c>
       <c r="C540" s="2" t="s">
-        <v>1512</v>
+        <v>241</v>
       </c>
     </row>
     <row r="541" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A541" s="2" t="s">
-        <v>1513</v>
+        <v>1517</v>
       </c>
       <c r="B541" s="2" t="s">
-        <v>1514</v>
+        <v>209</v>
       </c>
       <c r="C541" s="2" t="s">
-        <v>1515</v>
+        <v>210</v>
       </c>
     </row>
     <row r="542" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A542" s="2" t="s">
-        <v>1516</v>
+        <v>1518</v>
       </c>
       <c r="B542" s="2" t="s">
-        <v>1517</v>
+        <v>212</v>
       </c>
       <c r="C542" s="2" t="s">
-        <v>1518</v>
+        <v>213</v>
       </c>
     </row>
     <row r="543" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13027,142 +13363,142 @@
         <v>1519</v>
       </c>
       <c r="B543" s="2" t="s">
-        <v>1520</v>
+        <v>719</v>
       </c>
       <c r="C543" s="2" t="s">
-        <v>1521</v>
+        <v>720</v>
       </c>
     </row>
     <row r="544" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A544" s="2" t="s">
+        <v>1520</v>
+      </c>
+      <c r="B544" s="2" t="s">
+        <v>1521</v>
+      </c>
+      <c r="C544" s="2" t="s">
         <v>1522</v>
-      </c>
-      <c r="B544" s="2" t="s">
-        <v>1523</v>
-      </c>
-      <c r="C544" s="2" t="s">
-        <v>1524</v>
       </c>
     </row>
     <row r="545" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A545" s="2" t="s">
+        <v>1523</v>
+      </c>
+      <c r="B545" s="2" t="s">
+        <v>1524</v>
+      </c>
+      <c r="C545" s="2" t="s">
         <v>1525</v>
-      </c>
-      <c r="B545" s="2" t="s">
-        <v>1526</v>
-      </c>
-      <c r="C545" s="2" t="s">
-        <v>1527</v>
       </c>
     </row>
     <row r="546" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A546" s="2" t="s">
+        <v>1526</v>
+      </c>
+      <c r="B546" s="2" t="s">
+        <v>1527</v>
+      </c>
+      <c r="C546" s="2" t="s">
         <v>1528</v>
-      </c>
-      <c r="B546" s="2" t="s">
-        <v>1529</v>
-      </c>
-      <c r="C546" s="2" t="s">
-        <v>1530</v>
       </c>
     </row>
     <row r="547" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A547" s="2" t="s">
+        <v>1529</v>
+      </c>
+      <c r="B547" s="2" t="s">
+        <v>1530</v>
+      </c>
+      <c r="C547" s="2" t="s">
         <v>1531</v>
-      </c>
-      <c r="B547" s="2" t="s">
-        <v>1532</v>
-      </c>
-      <c r="C547" s="2" t="s">
-        <v>1533</v>
       </c>
     </row>
     <row r="548" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A548" s="2" t="s">
+        <v>1532</v>
+      </c>
+      <c r="B548" s="2" t="s">
+        <v>1533</v>
+      </c>
+      <c r="C548" s="2" t="s">
         <v>1534</v>
-      </c>
-      <c r="B548" s="2" t="s">
-        <v>1535</v>
-      </c>
-      <c r="C548" s="2" t="s">
-        <v>1536</v>
       </c>
     </row>
     <row r="549" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A549" s="2" t="s">
+        <v>1535</v>
+      </c>
+      <c r="B549" s="2" t="s">
+        <v>1536</v>
+      </c>
+      <c r="C549" s="2" t="s">
         <v>1537</v>
-      </c>
-      <c r="B549" s="2" t="s">
-        <v>1538</v>
-      </c>
-      <c r="C549" s="2" t="s">
-        <v>1539</v>
       </c>
     </row>
     <row r="550" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A550" s="2" t="s">
+        <v>1538</v>
+      </c>
+      <c r="B550" s="2" t="s">
+        <v>1539</v>
+      </c>
+      <c r="C550" s="2" t="s">
         <v>1540</v>
-      </c>
-      <c r="B550" s="2" t="s">
-        <v>1541</v>
-      </c>
-      <c r="C550" s="2" t="s">
-        <v>1542</v>
       </c>
     </row>
     <row r="551" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A551" s="2" t="s">
+        <v>1541</v>
+      </c>
+      <c r="B551" s="2" t="s">
+        <v>1542</v>
+      </c>
+      <c r="C551" s="2" t="s">
         <v>1543</v>
-      </c>
-      <c r="B551" s="2" t="s">
-        <v>1544</v>
-      </c>
-      <c r="C551" s="2" t="s">
-        <v>1545</v>
       </c>
     </row>
     <row r="552" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A552" s="2" t="s">
+        <v>1544</v>
+      </c>
+      <c r="B552" s="2" t="s">
+        <v>1545</v>
+      </c>
+      <c r="C552" s="2" t="s">
         <v>1546</v>
-      </c>
-      <c r="B552" s="2" t="s">
-        <v>1547</v>
-      </c>
-      <c r="C552" s="2" t="s">
-        <v>1548</v>
       </c>
     </row>
     <row r="553" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A553" s="2" t="s">
+        <v>1547</v>
+      </c>
+      <c r="B553" s="2" t="s">
+        <v>1548</v>
+      </c>
+      <c r="C553" s="2" t="s">
         <v>1549</v>
-      </c>
-      <c r="B553" s="2" t="s">
-        <v>1550</v>
-      </c>
-      <c r="C553" s="2" t="s">
-        <v>1551</v>
       </c>
     </row>
     <row r="554" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A554" s="2" t="s">
+        <v>1550</v>
+      </c>
+      <c r="B554" s="2" t="s">
+        <v>1551</v>
+      </c>
+      <c r="C554" s="2" t="s">
         <v>1552</v>
-      </c>
-      <c r="B554" s="2" t="s">
-        <v>1553</v>
-      </c>
-      <c r="C554" s="2" t="s">
-        <v>1554</v>
       </c>
     </row>
     <row r="555" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A555" s="2" t="s">
+        <v>1553</v>
+      </c>
+      <c r="B555" s="2" t="s">
+        <v>1554</v>
+      </c>
+      <c r="C555" s="2" t="s">
         <v>1555</v>
-      </c>
-      <c r="B555" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C555" s="2" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="556" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13173,348 +13509,348 @@
         <v>1557</v>
       </c>
       <c r="C556" s="2" t="s">
-        <v>1183</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="557" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A557" s="2" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="B557" s="2" t="s">
-        <v>1499</v>
+        <v>1560</v>
       </c>
       <c r="C557" s="2" t="s">
-        <v>1500</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="558" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A558" s="2" t="s">
-        <v>1559</v>
+        <v>1562</v>
       </c>
       <c r="B558" s="2" t="s">
-        <v>1560</v>
+        <v>1563</v>
       </c>
       <c r="C558" s="2" t="s">
-        <v>1292</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="559" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A559" s="2" t="s">
-        <v>1561</v>
+        <v>1565</v>
       </c>
       <c r="B559" s="2" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="C559" s="2" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="560" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A560" s="2" t="s">
-        <v>1564</v>
+        <v>1568</v>
       </c>
       <c r="B560" s="2" t="s">
-        <v>1502</v>
+        <v>1569</v>
       </c>
       <c r="C560" s="2" t="s">
-        <v>1503</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="561" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A561" s="2" t="s">
-        <v>1565</v>
+        <v>1571</v>
       </c>
       <c r="B561" s="2" t="s">
-        <v>209</v>
+        <v>1572</v>
       </c>
       <c r="C561" s="2" t="s">
-        <v>209</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="562" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A562" s="2" t="s">
-        <v>1566</v>
+        <v>1574</v>
       </c>
       <c r="B562" s="2" t="s">
-        <v>1567</v>
+        <v>1575</v>
       </c>
       <c r="C562" s="2" t="s">
-        <v>1568</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="563" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A563" s="2" t="s">
-        <v>1569</v>
+        <v>1577</v>
       </c>
       <c r="B563" s="2" t="s">
-        <v>1570</v>
+        <v>1578</v>
       </c>
       <c r="C563" s="2" t="s">
-        <v>1571</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="564" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A564" s="2" t="s">
-        <v>1572</v>
+        <v>1580</v>
       </c>
       <c r="B564" s="2" t="s">
-        <v>1573</v>
+        <v>1581</v>
       </c>
       <c r="C564" s="2" t="s">
-        <v>1574</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="565" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A565" s="2" t="s">
-        <v>1575</v>
+        <v>1583</v>
       </c>
       <c r="B565" s="2" t="s">
-        <v>1576</v>
+        <v>1584</v>
       </c>
       <c r="C565" s="2" t="s">
-        <v>1577</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="566" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A566" s="2" t="s">
-        <v>1578</v>
+        <v>1585</v>
       </c>
       <c r="B566" s="2" t="s">
-        <v>1579</v>
+        <v>1365</v>
       </c>
       <c r="C566" s="2" t="s">
-        <v>1580</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="567" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A567" s="2" t="s">
-        <v>1581</v>
+        <v>1586</v>
       </c>
       <c r="B567" s="2" t="s">
-        <v>1333</v>
+        <v>43</v>
       </c>
       <c r="C567" s="2" t="s">
-        <v>1334</v>
+        <v>44</v>
       </c>
     </row>
     <row r="568" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A568" s="2" t="s">
-        <v>1582</v>
+        <v>1587</v>
       </c>
       <c r="B568" s="2" t="s">
-        <v>4</v>
+        <v>1588</v>
       </c>
       <c r="C568" s="2" t="s">
-        <v>5</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="569" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A569" s="2" t="s">
-        <v>1583</v>
+        <v>1589</v>
       </c>
       <c r="B569" s="2" t="s">
-        <v>1324</v>
+        <v>1521</v>
       </c>
       <c r="C569" s="2" t="s">
-        <v>1325</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="570" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A570" s="2" t="s">
-        <v>1584</v>
+        <v>1590</v>
       </c>
       <c r="B570" s="2" t="s">
-        <v>1336</v>
+        <v>1591</v>
       </c>
       <c r="C570" s="2" t="s">
-        <v>1337</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="571" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A571" s="2" t="s">
-        <v>1585</v>
+        <v>1592</v>
       </c>
       <c r="B571" s="2" t="s">
-        <v>1586</v>
+        <v>1593</v>
       </c>
       <c r="C571" s="2" t="s">
-        <v>1587</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="572" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A572" s="2" t="s">
-        <v>1588</v>
+        <v>1595</v>
       </c>
       <c r="B572" s="2" t="s">
-        <v>1589</v>
+        <v>1524</v>
       </c>
       <c r="C572" s="2" t="s">
-        <v>1590</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="573" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A573" s="2" t="s">
-        <v>1591</v>
+        <v>1596</v>
       </c>
       <c r="B573" s="2" t="s">
-        <v>1339</v>
+        <v>218</v>
       </c>
       <c r="C573" s="2" t="s">
-        <v>1340</v>
+        <v>218</v>
       </c>
     </row>
     <row r="574" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A574" s="2" t="s">
-        <v>1592</v>
+        <v>1597</v>
       </c>
       <c r="B574" s="2" t="s">
-        <v>1593</v>
+        <v>1598</v>
       </c>
       <c r="C574" s="2" t="s">
-        <v>1594</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="575" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A575" s="2" t="s">
-        <v>1595</v>
+        <v>1600</v>
       </c>
       <c r="B575" s="2" t="s">
-        <v>1342</v>
+        <v>1601</v>
       </c>
       <c r="C575" s="2" t="s">
-        <v>1596</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="576" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A576" s="2" t="s">
-        <v>1597</v>
+        <v>1603</v>
       </c>
       <c r="B576" s="2" t="s">
-        <v>1291</v>
+        <v>1604</v>
       </c>
       <c r="C576" s="2" t="s">
-        <v>1598</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="577" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A577" s="2" t="s">
-        <v>1599</v>
+        <v>1606</v>
       </c>
       <c r="B577" s="2" t="s">
-        <v>1600</v>
+        <v>1607</v>
       </c>
       <c r="C577" s="2" t="s">
-        <v>1601</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="578" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A578" s="2" t="s">
-        <v>1602</v>
+        <v>1609</v>
       </c>
       <c r="B578" s="2" t="s">
-        <v>1603</v>
+        <v>1610</v>
       </c>
       <c r="C578" s="2" t="s">
-        <v>1604</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="579" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A579" s="2" t="s">
-        <v>1605</v>
+        <v>1612</v>
       </c>
       <c r="B579" s="2" t="s">
-        <v>1606</v>
+        <v>1352</v>
       </c>
       <c r="C579" s="2" t="s">
-        <v>1607</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="580" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A580" s="2" t="s">
-        <v>1608</v>
+        <v>1613</v>
       </c>
       <c r="B580" s="2" t="s">
-        <v>1609</v>
+        <v>4</v>
       </c>
       <c r="C580" s="2" t="s">
-        <v>1610</v>
+        <v>5</v>
       </c>
     </row>
     <row r="581" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A581" s="2" t="s">
-        <v>1611</v>
+        <v>1614</v>
       </c>
       <c r="B581" s="2" t="s">
-        <v>1612</v>
+        <v>1339</v>
       </c>
       <c r="C581" s="2" t="s">
-        <v>1613</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="582" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A582" s="2" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="B582" s="2" t="s">
-        <v>1615</v>
+        <v>1355</v>
       </c>
       <c r="C582" s="2" t="s">
-        <v>1616</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="583" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A583" s="2" t="s">
+        <v>1616</v>
+      </c>
+      <c r="B583" s="2" t="s">
         <v>1617</v>
       </c>
-      <c r="B583" s="2" t="s">
+      <c r="C583" s="2" t="s">
         <v>1618</v>
-      </c>
-      <c r="C583" s="2" t="s">
-        <v>1619</v>
       </c>
     </row>
     <row r="584" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A584" s="2" t="s">
+        <v>1619</v>
+      </c>
+      <c r="B584" s="2" t="s">
         <v>1620</v>
       </c>
-      <c r="B584" s="2" t="s">
+      <c r="C584" s="2" t="s">
         <v>1621</v>
-      </c>
-      <c r="C584" s="2" t="s">
-        <v>1622</v>
       </c>
     </row>
     <row r="585" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A585" s="2" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="B585" s="2" t="s">
-        <v>1624</v>
+        <v>1358</v>
       </c>
       <c r="C585" s="2" t="s">
-        <v>1625</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="586" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A586" s="2" t="s">
-        <v>1626</v>
+        <v>1623</v>
       </c>
       <c r="B586" s="2" t="s">
-        <v>1333</v>
+        <v>1624</v>
       </c>
       <c r="C586" s="2" t="s">
-        <v>1334</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="587" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A587" s="2" t="s">
+        <v>1626</v>
+      </c>
+      <c r="B587" s="2" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C587" s="2" t="s">
         <v>1627</v>
-      </c>
-      <c r="B587" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C587" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="588" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13522,175 +13858,175 @@
         <v>1628</v>
       </c>
       <c r="B588" s="2" t="s">
-        <v>1339</v>
+        <v>1306</v>
       </c>
       <c r="C588" s="2" t="s">
-        <v>1340</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="589" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A589" s="2" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="B589" s="2" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="C589" s="2" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="590" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A590" s="2" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="B590" s="2" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="C590" s="2" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="591" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A591" s="2" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="B591" s="2" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="C591" s="2" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="592" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A592" s="2" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="B592" s="2" t="s">
-        <v>1609</v>
+        <v>1640</v>
       </c>
       <c r="C592" s="2" t="s">
-        <v>1610</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="593" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A593" s="2" t="s">
-        <v>1639</v>
+        <v>1642</v>
       </c>
       <c r="B593" s="2" t="s">
-        <v>1640</v>
+        <v>1643</v>
       </c>
       <c r="C593" s="2" t="s">
-        <v>1641</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="594" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A594" s="2" t="s">
-        <v>1642</v>
+        <v>1645</v>
       </c>
       <c r="B594" s="2" t="s">
-        <v>1643</v>
+        <v>1646</v>
       </c>
       <c r="C594" s="2" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="595" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A595" s="2" t="s">
-        <v>1645</v>
+        <v>1648</v>
       </c>
       <c r="B595" s="2" t="s">
-        <v>1463</v>
+        <v>1649</v>
       </c>
       <c r="C595" s="2" t="s">
-        <v>1464</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="596" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A596" s="2" t="s">
-        <v>1646</v>
+        <v>1651</v>
       </c>
       <c r="B596" s="2" t="s">
-        <v>1647</v>
+        <v>1652</v>
       </c>
       <c r="C596" s="2" t="s">
-        <v>1648</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="597" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A597" s="2" t="s">
-        <v>1649</v>
+        <v>1654</v>
       </c>
       <c r="B597" s="2" t="s">
-        <v>1650</v>
+        <v>1655</v>
       </c>
       <c r="C597" s="2" t="s">
-        <v>1651</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="598" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A598" s="2" t="s">
-        <v>1652</v>
+        <v>1657</v>
       </c>
       <c r="B598" s="2" t="s">
-        <v>1653</v>
+        <v>1658</v>
       </c>
       <c r="C598" s="2" t="s">
-        <v>1654</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="599" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A599" s="2" t="s">
-        <v>1655</v>
+        <v>1660</v>
       </c>
       <c r="B599" s="2" t="s">
-        <v>1656</v>
+        <v>1661</v>
       </c>
       <c r="C599" s="2" t="s">
-        <v>1657</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="600" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A600" s="2" t="s">
-        <v>1658</v>
+        <v>1663</v>
       </c>
       <c r="B600" s="2" t="s">
-        <v>1659</v>
+        <v>1352</v>
       </c>
       <c r="C600" s="2" t="s">
-        <v>1660</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="601" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A601" s="2" t="s">
-        <v>1661</v>
+        <v>1664</v>
       </c>
       <c r="B601" s="2" t="s">
-        <v>1662</v>
+        <v>4</v>
       </c>
       <c r="C601" s="2" t="s">
-        <v>1663</v>
+        <v>5</v>
       </c>
     </row>
     <row r="602" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A602" s="2" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="B602" s="2" t="s">
-        <v>1665</v>
+        <v>1358</v>
       </c>
       <c r="C602" s="2" t="s">
-        <v>1666</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="603" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A603" s="2" t="s">
+        <v>1666</v>
+      </c>
+      <c r="B603" s="2" t="s">
         <v>1667</v>
       </c>
-      <c r="B603" s="2" t="s">
+      <c r="C603" s="2" t="s">
         <v>1668</v>
-      </c>
-      <c r="C603" s="2" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="604" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13720,109 +14056,109 @@
         <v>1675</v>
       </c>
       <c r="B606" s="2" t="s">
-        <v>1676</v>
+        <v>1640</v>
       </c>
       <c r="C606" s="2" t="s">
-        <v>1677</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="607" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A607" s="2" t="s">
+        <v>1676</v>
+      </c>
+      <c r="B607" s="2" t="s">
+        <v>1677</v>
+      </c>
+      <c r="C607" s="2" t="s">
         <v>1678</v>
-      </c>
-      <c r="B607" s="2" t="s">
-        <v>1679</v>
-      </c>
-      <c r="C607" s="2" t="s">
-        <v>1680</v>
       </c>
     </row>
     <row r="608" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A608" s="2" t="s">
+        <v>1679</v>
+      </c>
+      <c r="B608" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="C608" s="2" t="s">
         <v>1681</v>
-      </c>
-      <c r="B608" s="2" t="s">
-        <v>1682</v>
-      </c>
-      <c r="C608" s="2" t="s">
-        <v>1683</v>
       </c>
     </row>
     <row r="609" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A609" s="2" t="s">
-        <v>1684</v>
+        <v>1682</v>
       </c>
       <c r="B609" s="2" t="s">
-        <v>1685</v>
+        <v>1485</v>
       </c>
       <c r="C609" s="2" t="s">
-        <v>1686</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="610" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A610" s="2" t="s">
-        <v>1687</v>
+        <v>1683</v>
       </c>
       <c r="B610" s="2" t="s">
-        <v>1688</v>
+        <v>1684</v>
       </c>
       <c r="C610" s="2" t="s">
-        <v>1689</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="611" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A611" s="2" t="s">
-        <v>1690</v>
+        <v>1686</v>
       </c>
       <c r="B611" s="2" t="s">
-        <v>1691</v>
+        <v>1687</v>
       </c>
       <c r="C611" s="2" t="s">
-        <v>1692</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="612" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A612" s="2" t="s">
-        <v>1693</v>
+        <v>1689</v>
       </c>
       <c r="B612" s="2" t="s">
-        <v>611</v>
+        <v>1690</v>
       </c>
       <c r="C612" s="2" t="s">
-        <v>612</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="613" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A613" s="2" t="s">
+        <v>1692</v>
+      </c>
+      <c r="B613" s="2" t="s">
+        <v>1693</v>
+      </c>
+      <c r="C613" s="2" t="s">
         <v>1694</v>
-      </c>
-      <c r="B613" s="2" t="s">
-        <v>1695</v>
-      </c>
-      <c r="C613" s="2" t="s">
-        <v>1696</v>
       </c>
     </row>
     <row r="614" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A614" s="2" t="s">
+        <v>1695</v>
+      </c>
+      <c r="B614" s="2" t="s">
+        <v>1696</v>
+      </c>
+      <c r="C614" s="2" t="s">
         <v>1697</v>
-      </c>
-      <c r="B614" s="2" t="s">
-        <v>1698</v>
-      </c>
-      <c r="C614" s="2" t="s">
-        <v>1699</v>
       </c>
     </row>
     <row r="615" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A615" s="2" t="s">
+        <v>1698</v>
+      </c>
+      <c r="B615" s="2" t="s">
+        <v>1699</v>
+      </c>
+      <c r="C615" s="2" t="s">
         <v>1700</v>
-      </c>
-      <c r="B615" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="C615" s="2" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="616" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13855,128 +14191,128 @@
         <v>1708</v>
       </c>
       <c r="C618" s="2" t="s">
-        <v>1709</v>
+        <v>624</v>
       </c>
     </row>
     <row r="619" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A619" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="B619" s="2" t="s">
         <v>1710</v>
       </c>
-      <c r="B619" s="2" t="s">
+      <c r="C619" s="2" t="s">
         <v>1711</v>
-      </c>
-      <c r="C619" s="2" t="s">
-        <v>1712</v>
       </c>
     </row>
     <row r="620" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A620" s="2" t="s">
+        <v>1712</v>
+      </c>
+      <c r="B620" s="2" t="s">
         <v>1713</v>
       </c>
-      <c r="B620" s="2" t="s">
+      <c r="C620" s="2" t="s">
         <v>1714</v>
-      </c>
-      <c r="C620" s="2" t="s">
-        <v>1715</v>
       </c>
     </row>
     <row r="621" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A621" s="2" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B621" s="2" t="s">
         <v>1716</v>
       </c>
-      <c r="B621" s="2" t="s">
+      <c r="C621" s="2" t="s">
         <v>1717</v>
-      </c>
-      <c r="C621" s="2" t="s">
-        <v>1718</v>
       </c>
     </row>
     <row r="622" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A622" s="2" t="s">
+        <v>1718</v>
+      </c>
+      <c r="B622" s="2" t="s">
         <v>1719</v>
       </c>
-      <c r="B622" s="2" t="s">
+      <c r="C622" s="2" t="s">
         <v>1720</v>
-      </c>
-      <c r="C622" s="2" t="s">
-        <v>1721</v>
       </c>
     </row>
     <row r="623" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A623" s="2" t="s">
+        <v>1721</v>
+      </c>
+      <c r="B623" s="2" t="s">
         <v>1722</v>
       </c>
-      <c r="B623" s="2" t="s">
+      <c r="C623" s="2" t="s">
         <v>1723</v>
-      </c>
-      <c r="C623" s="2" t="s">
-        <v>1724</v>
       </c>
     </row>
     <row r="624" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A624" s="2" t="s">
+        <v>1724</v>
+      </c>
+      <c r="B624" s="2" t="s">
         <v>1725</v>
       </c>
-      <c r="B624" s="2" t="s">
+      <c r="C624" s="2" t="s">
         <v>1726</v>
-      </c>
-      <c r="C624" s="2" t="s">
-        <v>1727</v>
       </c>
     </row>
     <row r="625" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A625" s="2" t="s">
+        <v>1727</v>
+      </c>
+      <c r="B625" s="2" t="s">
         <v>1728</v>
       </c>
-      <c r="B625" s="2" t="s">
+      <c r="C625" s="2" t="s">
         <v>1729</v>
-      </c>
-      <c r="C625" s="2" t="s">
-        <v>1730</v>
       </c>
     </row>
     <row r="626" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A626" s="2" t="s">
+        <v>1730</v>
+      </c>
+      <c r="B626" s="2" t="s">
         <v>1731</v>
       </c>
-      <c r="B626" s="2" t="s">
+      <c r="C626" s="2" t="s">
         <v>1732</v>
-      </c>
-      <c r="C626" s="2" t="s">
-        <v>1733</v>
       </c>
     </row>
     <row r="627" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A627" s="2" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="B627" s="2" t="s">
-        <v>1735</v>
+        <v>623</v>
       </c>
       <c r="C627" s="2" t="s">
-        <v>1736</v>
+        <v>624</v>
       </c>
     </row>
     <row r="628" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A628" s="2" t="s">
-        <v>1737</v>
+        <v>1734</v>
       </c>
       <c r="B628" s="2" t="s">
-        <v>300</v>
+        <v>1735</v>
       </c>
       <c r="C628" s="2" t="s">
-        <v>301</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="629" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A629" s="2" t="s">
+        <v>1737</v>
+      </c>
+      <c r="B629" s="2" t="s">
         <v>1738</v>
       </c>
-      <c r="B629" s="2" t="s">
+      <c r="C629" s="2" t="s">
         <v>1739</v>
-      </c>
-      <c r="C629" s="2" t="s">
-        <v>1183</v>
       </c>
     </row>
     <row r="630" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13984,21 +14320,21 @@
         <v>1740</v>
       </c>
       <c r="B630" s="2" t="s">
-        <v>1741</v>
+        <v>315</v>
       </c>
       <c r="C630" s="2" t="s">
-        <v>1742</v>
+        <v>316</v>
       </c>
     </row>
     <row r="631" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A631" s="2" t="s">
+        <v>1741</v>
+      </c>
+      <c r="B631" s="2" t="s">
+        <v>1742</v>
+      </c>
+      <c r="C631" s="2" t="s">
         <v>1743</v>
-      </c>
-      <c r="B631" s="2" t="s">
-        <v>1562</v>
-      </c>
-      <c r="C631" s="2" t="s">
-        <v>1563</v>
       </c>
     </row>
     <row r="632" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14061,593 +14397,593 @@
         <v>1759</v>
       </c>
       <c r="B637" s="2" t="s">
-        <v>200</v>
+        <v>1760</v>
       </c>
       <c r="C637" s="2" t="s">
-        <v>201</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="638" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A638" s="2" t="s">
-        <v>1760</v>
+        <v>1762</v>
       </c>
       <c r="B638" s="2" t="s">
-        <v>1180</v>
+        <v>1763</v>
       </c>
       <c r="C638" s="2" t="s">
-        <v>721</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="639" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A639" s="2" t="s">
-        <v>1761</v>
+        <v>1765</v>
       </c>
       <c r="B639" s="2" t="s">
-        <v>1189</v>
+        <v>1766</v>
       </c>
       <c r="C639" s="2" t="s">
-        <v>1762</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="640" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A640" s="2" t="s">
-        <v>1763</v>
+        <v>1768</v>
       </c>
       <c r="B640" s="2" t="s">
-        <v>1764</v>
+        <v>1769</v>
       </c>
       <c r="C640" s="2" t="s">
-        <v>1765</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="641" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A641" s="2" t="s">
-        <v>1766</v>
+        <v>1771</v>
       </c>
       <c r="B641" s="2" t="s">
-        <v>300</v>
+        <v>1772</v>
       </c>
       <c r="C641" s="2" t="s">
-        <v>301</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="642" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A642" s="2" t="s">
-        <v>1767</v>
+        <v>1774</v>
       </c>
       <c r="B642" s="2" t="s">
-        <v>1768</v>
+        <v>1775</v>
       </c>
       <c r="C642" s="2" t="s">
-        <v>1769</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="643" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A643" s="2" t="s">
-        <v>1770</v>
+        <v>1777</v>
       </c>
       <c r="B643" s="2" t="s">
-        <v>1771</v>
+        <v>309</v>
       </c>
       <c r="C643" s="2" t="s">
-        <v>1772</v>
+        <v>310</v>
       </c>
     </row>
     <row r="644" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A644" s="2" t="s">
-        <v>1773</v>
+        <v>1778</v>
       </c>
       <c r="B644" s="2" t="s">
-        <v>1774</v>
+        <v>1779</v>
       </c>
       <c r="C644" s="2" t="s">
-        <v>1775</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="645" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A645" s="2" t="s">
-        <v>1776</v>
+        <v>1780</v>
       </c>
       <c r="B645" s="2" t="s">
-        <v>1777</v>
+        <v>1781</v>
       </c>
       <c r="C645" s="2" t="s">
-        <v>1778</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="646" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A646" s="2" t="s">
-        <v>1779</v>
+        <v>1783</v>
       </c>
       <c r="B646" s="2" t="s">
-        <v>306</v>
+        <v>1593</v>
       </c>
       <c r="C646" s="2" t="s">
-        <v>307</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="647" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A647" s="2" t="s">
-        <v>1780</v>
+        <v>1784</v>
       </c>
       <c r="B647" s="2" t="s">
-        <v>1781</v>
+        <v>1785</v>
       </c>
       <c r="C647" s="2" t="s">
-        <v>1782</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="648" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A648" s="2" t="s">
-        <v>1783</v>
+        <v>1787</v>
       </c>
       <c r="B648" s="2" t="s">
-        <v>1784</v>
+        <v>1788</v>
       </c>
       <c r="C648" s="2" t="s">
-        <v>1785</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="649" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A649" s="2" t="s">
-        <v>1786</v>
+        <v>1790</v>
       </c>
       <c r="B649" s="2" t="s">
-        <v>1787</v>
+        <v>1791</v>
       </c>
       <c r="C649" s="2" t="s">
-        <v>1788</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="650" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A650" s="2" t="s">
-        <v>1789</v>
+        <v>1793</v>
       </c>
       <c r="B650" s="2" t="s">
-        <v>1790</v>
+        <v>1794</v>
       </c>
       <c r="C650" s="2" t="s">
-        <v>1791</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="651" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A651" s="2" t="s">
-        <v>1792</v>
+        <v>1796</v>
       </c>
       <c r="B651" s="2" t="s">
-        <v>1793</v>
+        <v>1797</v>
       </c>
       <c r="C651" s="2" t="s">
-        <v>1794</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="652" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A652" s="2" t="s">
-        <v>1795</v>
+        <v>1799</v>
       </c>
       <c r="B652" s="2" t="s">
-        <v>611</v>
+        <v>209</v>
       </c>
       <c r="C652" s="2" t="s">
-        <v>612</v>
+        <v>210</v>
       </c>
     </row>
     <row r="653" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A653" s="2" t="s">
-        <v>1796</v>
+        <v>1800</v>
       </c>
       <c r="B653" s="2" t="s">
-        <v>1797</v>
+        <v>1195</v>
       </c>
       <c r="C653" s="2" t="s">
-        <v>1798</v>
+        <v>733</v>
       </c>
     </row>
     <row r="654" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A654" s="2" t="s">
-        <v>1799</v>
+        <v>1801</v>
       </c>
       <c r="B654" s="2" t="s">
-        <v>1800</v>
+        <v>1204</v>
       </c>
       <c r="C654" s="2" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="655" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A655" s="2" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="B655" s="2" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="C655" s="2" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="656" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A656" s="2" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="B656" s="2" t="s">
-        <v>1806</v>
+        <v>309</v>
       </c>
       <c r="C656" s="2" t="s">
-        <v>1807</v>
+        <v>310</v>
       </c>
     </row>
     <row r="657" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A657" s="2" t="s">
+        <v>1807</v>
+      </c>
+      <c r="B657" s="2" t="s">
         <v>1808</v>
       </c>
-      <c r="B657" s="2" t="s">
+      <c r="C657" s="2" t="s">
         <v>1809</v>
-      </c>
-      <c r="C657" s="2" t="s">
-        <v>1810</v>
       </c>
     </row>
     <row r="658" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A658" s="2" t="s">
+        <v>1810</v>
+      </c>
+      <c r="B658" s="2" t="s">
         <v>1811</v>
       </c>
-      <c r="B658" s="2" t="s">
+      <c r="C658" s="2" t="s">
         <v>1812</v>
-      </c>
-      <c r="C658" s="2" t="s">
-        <v>1813</v>
       </c>
     </row>
     <row r="659" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A659" s="2" t="s">
+        <v>1813</v>
+      </c>
+      <c r="B659" s="2" t="s">
         <v>1814</v>
       </c>
-      <c r="B659" s="2" t="s">
+      <c r="C659" s="2" t="s">
         <v>1815</v>
-      </c>
-      <c r="C659" s="2" t="s">
-        <v>1816</v>
       </c>
     </row>
     <row r="660" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A660" s="2" t="s">
+        <v>1816</v>
+      </c>
+      <c r="B660" s="2" t="s">
         <v>1817</v>
       </c>
-      <c r="B660" s="2" t="s">
+      <c r="C660" s="2" t="s">
         <v>1818</v>
-      </c>
-      <c r="C660" s="2" t="s">
-        <v>1819</v>
       </c>
     </row>
     <row r="661" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A661" s="2" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="B661" s="2" t="s">
-        <v>1821</v>
+        <v>315</v>
       </c>
       <c r="C661" s="2" t="s">
-        <v>1822</v>
+        <v>316</v>
       </c>
     </row>
     <row r="662" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A662" s="2" t="s">
-        <v>1823</v>
+        <v>1820</v>
       </c>
       <c r="B662" s="2" t="s">
-        <v>19</v>
+        <v>1821</v>
       </c>
       <c r="C662" s="2" t="s">
-        <v>20</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="663" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A663" s="2" t="s">
+        <v>1823</v>
+      </c>
+      <c r="B663" s="2" t="s">
         <v>1824</v>
       </c>
-      <c r="B663" s="2" t="s">
+      <c r="C663" s="2" t="s">
         <v>1825</v>
-      </c>
-      <c r="C663" s="2" t="s">
-        <v>1826</v>
       </c>
     </row>
     <row r="664" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A664" s="2" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B664" s="2" t="s">
         <v>1827</v>
       </c>
-      <c r="B664" s="2" t="s">
+      <c r="C664" s="2" t="s">
         <v>1828</v>
-      </c>
-      <c r="C664" s="2" t="s">
-        <v>1829</v>
       </c>
     </row>
     <row r="665" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A665" s="2" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B665" s="2" t="s">
         <v>1830</v>
       </c>
-      <c r="B665" s="2" t="s">
+      <c r="C665" s="2" t="s">
         <v>1831</v>
-      </c>
-      <c r="C665" s="2" t="s">
-        <v>1832</v>
       </c>
     </row>
     <row r="666" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A666" s="2" t="s">
+        <v>1832</v>
+      </c>
+      <c r="B666" s="2" t="s">
         <v>1833</v>
       </c>
-      <c r="B666" s="2" t="s">
+      <c r="C666" s="2" t="s">
         <v>1834</v>
-      </c>
-      <c r="C666" s="2" t="s">
-        <v>1835</v>
       </c>
     </row>
     <row r="667" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A667" s="2" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="B667" s="2" t="s">
-        <v>1837</v>
+        <v>623</v>
       </c>
       <c r="C667" s="2" t="s">
-        <v>1838</v>
+        <v>624</v>
       </c>
     </row>
     <row r="668" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A668" s="2" t="s">
-        <v>1839</v>
+        <v>1836</v>
       </c>
       <c r="B668" s="2" t="s">
-        <v>285</v>
+        <v>1837</v>
       </c>
       <c r="C668" s="2" t="s">
-        <v>286</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="669" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A669" s="2" t="s">
+        <v>1839</v>
+      </c>
+      <c r="B669" s="2" t="s">
         <v>1840</v>
       </c>
-      <c r="B669" s="2" t="s">
+      <c r="C669" s="2" t="s">
         <v>1841</v>
-      </c>
-      <c r="C669" s="2" t="s">
-        <v>1842</v>
       </c>
     </row>
     <row r="670" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A670" s="2" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B670" s="2" t="s">
         <v>1843</v>
       </c>
-      <c r="B670" s="2" t="s">
+      <c r="C670" s="2" t="s">
         <v>1844</v>
-      </c>
-      <c r="C670" s="2" t="s">
-        <v>1845</v>
       </c>
     </row>
     <row r="671" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A671" s="2" t="s">
+        <v>1845</v>
+      </c>
+      <c r="B671" s="2" t="s">
         <v>1846</v>
       </c>
-      <c r="B671" s="2" t="s">
+      <c r="C671" s="2" t="s">
         <v>1847</v>
-      </c>
-      <c r="C671" s="2" t="s">
-        <v>1848</v>
       </c>
     </row>
     <row r="672" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A672" s="2" t="s">
+        <v>1848</v>
+      </c>
+      <c r="B672" s="2" t="s">
         <v>1849</v>
       </c>
-      <c r="B672" s="2" t="s">
+      <c r="C672" s="2" t="s">
         <v>1850</v>
-      </c>
-      <c r="C672" s="2" t="s">
-        <v>1851</v>
       </c>
     </row>
     <row r="673" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A673" s="2" t="s">
+        <v>1851</v>
+      </c>
+      <c r="B673" s="2" t="s">
         <v>1852</v>
       </c>
-      <c r="B673" s="2" t="s">
+      <c r="C673" s="2" t="s">
         <v>1853</v>
-      </c>
-      <c r="C673" s="2" t="s">
-        <v>1854</v>
       </c>
     </row>
     <row r="674" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A674" s="2" t="s">
+        <v>1854</v>
+      </c>
+      <c r="B674" s="2" t="s">
         <v>1855</v>
       </c>
-      <c r="B674" s="2" t="s">
+      <c r="C674" s="2" t="s">
         <v>1856</v>
-      </c>
-      <c r="C674" s="2" t="s">
-        <v>1857</v>
       </c>
     </row>
     <row r="675" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A675" s="2" t="s">
+        <v>1857</v>
+      </c>
+      <c r="B675" s="2" t="s">
         <v>1858</v>
       </c>
-      <c r="B675" s="2" t="s">
+      <c r="C675" s="2" t="s">
         <v>1859</v>
-      </c>
-      <c r="C675" s="2" t="s">
-        <v>1860</v>
       </c>
     </row>
     <row r="676" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A676" s="2" t="s">
+        <v>1860</v>
+      </c>
+      <c r="B676" s="2" t="s">
         <v>1861</v>
       </c>
-      <c r="B676" s="2" t="s">
+      <c r="C676" s="2" t="s">
         <v>1862</v>
-      </c>
-      <c r="C676" s="2" t="s">
-        <v>1863</v>
       </c>
     </row>
     <row r="677" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A677" s="2" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="B677" s="2" t="s">
-        <v>823</v>
+        <v>19</v>
       </c>
       <c r="C677" s="2" t="s">
-        <v>1865</v>
+        <v>20</v>
       </c>
     </row>
     <row r="678" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A678" s="2" t="s">
+        <v>1864</v>
+      </c>
+      <c r="B678" s="2" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C678" s="2" t="s">
         <v>1866</v>
-      </c>
-      <c r="B678" s="2" t="s">
-        <v>1867</v>
-      </c>
-      <c r="C678" s="2" t="s">
-        <v>1868</v>
       </c>
     </row>
     <row r="679" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A679" s="2" t="s">
+        <v>1867</v>
+      </c>
+      <c r="B679" s="2" t="s">
+        <v>1868</v>
+      </c>
+      <c r="C679" s="2" t="s">
         <v>1869</v>
-      </c>
-      <c r="B679" s="2" t="s">
-        <v>1870</v>
-      </c>
-      <c r="C679" s="2" t="s">
-        <v>1871</v>
       </c>
     </row>
     <row r="680" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A680" s="2" t="s">
+        <v>1870</v>
+      </c>
+      <c r="B680" s="2" t="s">
+        <v>1871</v>
+      </c>
+      <c r="C680" s="2" t="s">
         <v>1872</v>
-      </c>
-      <c r="B680" s="2" t="s">
-        <v>1873</v>
-      </c>
-      <c r="C680" s="2" t="s">
-        <v>1874</v>
       </c>
     </row>
     <row r="681" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A681" s="2" t="s">
+        <v>1873</v>
+      </c>
+      <c r="B681" s="2" t="s">
+        <v>1874</v>
+      </c>
+      <c r="C681" s="2" t="s">
         <v>1875</v>
-      </c>
-      <c r="B681" s="2" t="s">
-        <v>1876</v>
-      </c>
-      <c r="C681" s="2" t="s">
-        <v>1877</v>
       </c>
     </row>
     <row r="682" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A682" s="2" t="s">
+        <v>1876</v>
+      </c>
+      <c r="B682" s="2" t="s">
+        <v>1877</v>
+      </c>
+      <c r="C682" s="2" t="s">
         <v>1878</v>
-      </c>
-      <c r="B682" s="2" t="s">
-        <v>1879</v>
-      </c>
-      <c r="C682" s="2" t="s">
-        <v>1880</v>
       </c>
     </row>
     <row r="683" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A683" s="2" t="s">
-        <v>1881</v>
+        <v>1879</v>
       </c>
       <c r="B683" s="2" t="s">
-        <v>1882</v>
+        <v>294</v>
       </c>
       <c r="C683" s="2" t="s">
-        <v>1883</v>
+        <v>295</v>
       </c>
     </row>
     <row r="684" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A684" s="2" t="s">
-        <v>1884</v>
+        <v>1880</v>
       </c>
       <c r="B684" s="2" t="s">
-        <v>1885</v>
+        <v>1881</v>
       </c>
       <c r="C684" s="2" t="s">
-        <v>1886</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="685" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A685" s="2" t="s">
-        <v>1887</v>
+        <v>1883</v>
       </c>
       <c r="B685" s="2" t="s">
-        <v>1888</v>
+        <v>1884</v>
       </c>
       <c r="C685" s="2" t="s">
-        <v>1889</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="686" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A686" s="2" t="s">
-        <v>1890</v>
+        <v>1886</v>
       </c>
       <c r="B686" s="2" t="s">
-        <v>1891</v>
+        <v>1887</v>
       </c>
       <c r="C686" s="2" t="s">
-        <v>479</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="687" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A687" s="2" t="s">
-        <v>1892</v>
+        <v>1889</v>
       </c>
       <c r="B687" s="2" t="s">
-        <v>1893</v>
+        <v>1890</v>
       </c>
       <c r="C687" s="2" t="s">
-        <v>1894</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="688" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A688" s="2" t="s">
-        <v>1895</v>
+        <v>1892</v>
       </c>
       <c r="B688" s="2" t="s">
-        <v>1896</v>
+        <v>1893</v>
       </c>
       <c r="C688" s="2" t="s">
-        <v>1897</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="689" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A689" s="2" t="s">
-        <v>1898</v>
+        <v>1895</v>
       </c>
       <c r="B689" s="2" t="s">
-        <v>300</v>
+        <v>1896</v>
       </c>
       <c r="C689" s="2" t="s">
-        <v>301</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="690" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A690" s="2" t="s">
+        <v>1898</v>
+      </c>
+      <c r="B690" s="2" t="s">
         <v>1899</v>
       </c>
-      <c r="B690" s="2" t="s">
+      <c r="C690" s="2" t="s">
         <v>1900</v>
-      </c>
-      <c r="C690" s="2" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="691" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14666,10 +15002,10 @@
         <v>1904</v>
       </c>
       <c r="B692" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="C692" s="2" t="s">
         <v>1905</v>
-      </c>
-      <c r="C692" s="2" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="693" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14688,1528 +15024,2045 @@
         <v>1909</v>
       </c>
       <c r="B694" s="2" t="s">
-        <v>936</v>
+        <v>1910</v>
       </c>
       <c r="C694" s="2" t="s">
-        <v>937</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="695" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A695" s="2" t="s">
-        <v>1910</v>
+        <v>1912</v>
       </c>
       <c r="B695" s="2" t="s">
-        <v>4</v>
+        <v>1913</v>
       </c>
       <c r="C695" s="2" t="s">
-        <v>5</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="696" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A696" s="2" t="s">
-        <v>1911</v>
+        <v>1915</v>
       </c>
       <c r="B696" s="2" t="s">
-        <v>306</v>
+        <v>1916</v>
       </c>
       <c r="C696" s="2" t="s">
-        <v>307</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="697" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A697" s="2" t="s">
-        <v>1912</v>
+        <v>1918</v>
       </c>
       <c r="B697" s="2" t="s">
-        <v>1907</v>
+        <v>1919</v>
       </c>
       <c r="C697" s="2" t="s">
-        <v>1908</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="698" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A698" s="2" t="s">
-        <v>1913</v>
+        <v>1921</v>
       </c>
       <c r="B698" s="2" t="s">
-        <v>1914</v>
+        <v>1922</v>
       </c>
       <c r="C698" s="2" t="s">
-        <v>1915</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="699" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A699" s="2" t="s">
-        <v>1916</v>
+        <v>1924</v>
       </c>
       <c r="B699" s="2" t="s">
-        <v>1917</v>
+        <v>1925</v>
       </c>
       <c r="C699" s="2" t="s">
-        <v>1918</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="700" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A700" s="2" t="s">
-        <v>1919</v>
+        <v>1927</v>
       </c>
       <c r="B700" s="2" t="s">
-        <v>1920</v>
+        <v>1928</v>
       </c>
       <c r="C700" s="2" t="s">
-        <v>1921</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="701" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A701" s="2" t="s">
-        <v>1922</v>
+        <v>1930</v>
       </c>
       <c r="B701" s="2" t="s">
-        <v>1923</v>
+        <v>1931</v>
       </c>
       <c r="C701" s="2" t="s">
-        <v>1924</v>
+        <v>488</v>
       </c>
     </row>
     <row r="702" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A702" s="2" t="s">
-        <v>1925</v>
+        <v>1932</v>
       </c>
       <c r="B702" s="2" t="s">
-        <v>1926</v>
+        <v>1933</v>
       </c>
       <c r="C702" s="2" t="s">
-        <v>1927</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="703" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A703" s="2" t="s">
-        <v>1928</v>
+        <v>1935</v>
       </c>
       <c r="B703" s="2" t="s">
-        <v>1929</v>
+        <v>1936</v>
       </c>
       <c r="C703" s="2" t="s">
-        <v>1930</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="704" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A704" s="2" t="s">
-        <v>1931</v>
+        <v>1938</v>
       </c>
       <c r="B704" s="2" t="s">
-        <v>1932</v>
+        <v>309</v>
       </c>
       <c r="C704" s="2" t="s">
-        <v>1933</v>
+        <v>310</v>
       </c>
     </row>
     <row r="705" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A705" s="2" t="s">
-        <v>1934</v>
+        <v>1939</v>
       </c>
       <c r="B705" s="2" t="s">
-        <v>1935</v>
+        <v>1940</v>
       </c>
       <c r="C705" s="2" t="s">
-        <v>1936</v>
+        <v>207</v>
       </c>
     </row>
     <row r="706" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A706" s="2" t="s">
-        <v>1937</v>
+        <v>1941</v>
       </c>
       <c r="B706" s="2" t="s">
-        <v>19</v>
+        <v>1942</v>
       </c>
       <c r="C706" s="2" t="s">
-        <v>20</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="707" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A707" s="2" t="s">
-        <v>1938</v>
+        <v>1944</v>
       </c>
       <c r="B707" s="2" t="s">
-        <v>13</v>
+        <v>1945</v>
       </c>
       <c r="C707" s="2" t="s">
-        <v>14</v>
+        <v>488</v>
       </c>
     </row>
     <row r="708" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A708" s="2" t="s">
-        <v>1939</v>
+        <v>1946</v>
       </c>
       <c r="B708" s="2" t="s">
-        <v>16</v>
+        <v>1947</v>
       </c>
       <c r="C708" s="2" t="s">
-        <v>17</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="709" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A709" s="2" t="s">
-        <v>1940</v>
+        <v>1949</v>
       </c>
       <c r="B709" s="2" t="s">
-        <v>1941</v>
+        <v>954</v>
       </c>
       <c r="C709" s="2" t="s">
-        <v>1942</v>
+        <v>955</v>
       </c>
     </row>
     <row r="710" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A710" s="2" t="s">
-        <v>1943</v>
+        <v>1950</v>
       </c>
       <c r="B710" s="2" t="s">
-        <v>1944</v>
+        <v>4</v>
       </c>
       <c r="C710" s="2" t="s">
-        <v>1945</v>
+        <v>5</v>
       </c>
     </row>
     <row r="711" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A711" s="2" t="s">
-        <v>1946</v>
+        <v>1951</v>
       </c>
       <c r="B711" s="2" t="s">
-        <v>1947</v>
+        <v>315</v>
       </c>
       <c r="C711" s="2" t="s">
-        <v>1948</v>
+        <v>316</v>
       </c>
     </row>
     <row r="712" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A712" s="2" t="s">
-        <v>1949</v>
+        <v>1952</v>
       </c>
       <c r="B712" s="2" t="s">
-        <v>1950</v>
+        <v>1947</v>
       </c>
       <c r="C712" s="2" t="s">
-        <v>1951</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="713" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A713" s="2" t="s">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="B713" s="2" t="s">
-        <v>1850</v>
+        <v>1954</v>
       </c>
       <c r="C713" s="2" t="s">
-        <v>1851</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="714" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A714" s="2" t="s">
-        <v>1953</v>
+        <v>1956</v>
       </c>
       <c r="B714" s="2" t="s">
-        <v>1853</v>
+        <v>1957</v>
       </c>
       <c r="C714" s="2" t="s">
-        <v>1854</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="715" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A715" s="2" t="s">
-        <v>1954</v>
+        <v>1959</v>
       </c>
       <c r="B715" s="2" t="s">
-        <v>1955</v>
+        <v>1960</v>
       </c>
       <c r="C715" s="2" t="s">
-        <v>1343</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="716" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A716" s="2" t="s">
-        <v>1956</v>
+        <v>1962</v>
       </c>
       <c r="B716" s="2" t="s">
-        <v>1957</v>
+        <v>1963</v>
       </c>
       <c r="C716" s="2" t="s">
-        <v>1958</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="717" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A717" s="2" t="s">
-        <v>1959</v>
+        <v>1965</v>
       </c>
       <c r="B717" s="2" t="s">
-        <v>1192</v>
+        <v>1966</v>
       </c>
       <c r="C717" s="2" t="s">
-        <v>1193</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="718" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A718" s="2" t="s">
-        <v>1960</v>
+        <v>1968</v>
       </c>
       <c r="B718" s="2" t="s">
-        <v>1961</v>
+        <v>1969</v>
       </c>
       <c r="C718" s="2" t="s">
-        <v>1863</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="719" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A719" s="2" t="s">
-        <v>1962</v>
+        <v>1971</v>
       </c>
       <c r="B719" s="2" t="s">
-        <v>823</v>
+        <v>1972</v>
       </c>
       <c r="C719" s="2" t="s">
-        <v>1865</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="720" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A720" s="2" t="s">
-        <v>1963</v>
+        <v>1974</v>
       </c>
       <c r="B720" s="2" t="s">
-        <v>1964</v>
+        <v>1975</v>
       </c>
       <c r="C720" s="2" t="s">
-        <v>1965</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="721" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A721" s="2" t="s">
-        <v>1966</v>
+        <v>1977</v>
       </c>
       <c r="B721" s="2" t="s">
-        <v>1967</v>
+        <v>19</v>
       </c>
       <c r="C721" s="2" t="s">
-        <v>1958</v>
+        <v>20</v>
       </c>
     </row>
     <row r="722" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A722" s="2" t="s">
-        <v>1968</v>
+        <v>1978</v>
       </c>
       <c r="B722" s="2" t="s">
-        <v>920</v>
+        <v>13</v>
       </c>
       <c r="C722" s="2" t="s">
-        <v>1969</v>
+        <v>14</v>
       </c>
     </row>
     <row r="723" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A723" s="2" t="s">
-        <v>1970</v>
+        <v>1979</v>
       </c>
       <c r="B723" s="2" t="s">
-        <v>932</v>
+        <v>16</v>
       </c>
       <c r="C723" s="2" t="s">
-        <v>1971</v>
+        <v>17</v>
       </c>
     </row>
     <row r="724" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A724" s="2" t="s">
-        <v>1972</v>
+        <v>1980</v>
       </c>
       <c r="B724" s="2" t="s">
-        <v>614</v>
+        <v>1981</v>
       </c>
       <c r="C724" s="2" t="s">
-        <v>479</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="725" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A725" s="2" t="s">
-        <v>1973</v>
+        <v>1983</v>
       </c>
       <c r="B725" s="2" t="s">
-        <v>936</v>
+        <v>1984</v>
       </c>
       <c r="C725" s="2" t="s">
-        <v>937</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="726" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A726" s="2" t="s">
-        <v>1974</v>
+        <v>1986</v>
       </c>
       <c r="B726" s="2" t="s">
-        <v>306</v>
+        <v>1987</v>
       </c>
       <c r="C726" s="2" t="s">
-        <v>307</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="727" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A727" s="2" t="s">
-        <v>1975</v>
+        <v>1989</v>
       </c>
       <c r="B727" s="2" t="s">
-        <v>1976</v>
+        <v>1990</v>
       </c>
       <c r="C727" s="2" t="s">
-        <v>1977</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="728" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A728" s="2" t="s">
-        <v>1978</v>
+        <v>1992</v>
       </c>
       <c r="B728" s="2" t="s">
-        <v>1979</v>
+        <v>1890</v>
       </c>
       <c r="C728" s="2" t="s">
-        <v>1980</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="729" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A729" s="2" t="s">
-        <v>1981</v>
+        <v>1993</v>
       </c>
       <c r="B729" s="2" t="s">
-        <v>1982</v>
+        <v>1893</v>
       </c>
       <c r="C729" s="2" t="s">
-        <v>1983</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="730" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A730" s="2" t="s">
-        <v>1984</v>
+        <v>1994</v>
       </c>
       <c r="B730" s="2" t="s">
-        <v>964</v>
+        <v>1995</v>
       </c>
       <c r="C730" s="2" t="s">
-        <v>965</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="731" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A731" s="2" t="s">
-        <v>1985</v>
+        <v>1996</v>
       </c>
       <c r="B731" s="2" t="s">
-        <v>932</v>
+        <v>1997</v>
       </c>
       <c r="C731" s="2" t="s">
-        <v>1971</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="732" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A732" s="2" t="s">
-        <v>1986</v>
+        <v>1999</v>
       </c>
       <c r="B732" s="2" t="s">
-        <v>968</v>
+        <v>1207</v>
       </c>
       <c r="C732" s="2" t="s">
-        <v>969</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="733" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A733" s="2" t="s">
-        <v>1987</v>
+        <v>2000</v>
       </c>
       <c r="B733" s="2" t="s">
-        <v>1988</v>
+        <v>2001</v>
       </c>
       <c r="C733" s="2" t="s">
-        <v>1989</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="734" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A734" s="2" t="s">
-        <v>1990</v>
+        <v>2002</v>
       </c>
       <c r="B734" s="2" t="s">
-        <v>974</v>
+        <v>835</v>
       </c>
       <c r="C734" s="2" t="s">
-        <v>1991</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="735" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A735" s="2" t="s">
-        <v>1992</v>
+        <v>2003</v>
       </c>
       <c r="B735" s="2" t="s">
-        <v>1993</v>
+        <v>2004</v>
       </c>
       <c r="C735" s="2" t="s">
-        <v>1994</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="736" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A736" s="2" t="s">
-        <v>1995</v>
+        <v>2006</v>
       </c>
       <c r="B736" s="2" t="s">
-        <v>980</v>
+        <v>2007</v>
       </c>
       <c r="C736" s="2" t="s">
-        <v>1996</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="737" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A737" s="2" t="s">
-        <v>1997</v>
+        <v>2008</v>
       </c>
       <c r="B737" s="2" t="s">
-        <v>1998</v>
+        <v>938</v>
       </c>
       <c r="C737" s="2" t="s">
-        <v>1999</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="738" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A738" s="2" t="s">
-        <v>2000</v>
+        <v>2010</v>
       </c>
       <c r="B738" s="2" t="s">
-        <v>2001</v>
+        <v>950</v>
       </c>
       <c r="C738" s="2" t="s">
-        <v>2002</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="739" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A739" s="2" t="s">
-        <v>2003</v>
+        <v>2012</v>
       </c>
       <c r="B739" s="2" t="s">
-        <v>2004</v>
+        <v>626</v>
       </c>
       <c r="C739" s="2" t="s">
-        <v>2005</v>
+        <v>488</v>
       </c>
     </row>
     <row r="740" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A740" s="2" t="s">
-        <v>2006</v>
+        <v>2013</v>
       </c>
       <c r="B740" s="2" t="s">
-        <v>804</v>
+        <v>954</v>
       </c>
       <c r="C740" s="2" t="s">
-        <v>805</v>
+        <v>955</v>
       </c>
     </row>
     <row r="741" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A741" s="2" t="s">
-        <v>2007</v>
+        <v>2014</v>
       </c>
       <c r="B741" s="2" t="s">
-        <v>990</v>
+        <v>315</v>
       </c>
       <c r="C741" s="2" t="s">
-        <v>991</v>
+        <v>316</v>
       </c>
     </row>
     <row r="742" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A742" s="2" t="s">
-        <v>2008</v>
+        <v>2015</v>
       </c>
       <c r="B742" s="2" t="s">
-        <v>993</v>
+        <v>2016</v>
       </c>
       <c r="C742" s="2" t="s">
-        <v>2009</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="743" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A743" s="2" t="s">
-        <v>2010</v>
+        <v>2018</v>
       </c>
       <c r="B743" s="2" t="s">
-        <v>996</v>
+        <v>2019</v>
       </c>
       <c r="C743" s="2" t="s">
-        <v>2011</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="744" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A744" s="2" t="s">
-        <v>2012</v>
+        <v>2021</v>
       </c>
       <c r="B744" s="2" t="s">
-        <v>999</v>
+        <v>2022</v>
       </c>
       <c r="C744" s="2" t="s">
-        <v>2013</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="745" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A745" s="2" t="s">
-        <v>2014</v>
+        <v>2024</v>
       </c>
       <c r="B745" s="2" t="s">
-        <v>2015</v>
+        <v>982</v>
       </c>
       <c r="C745" s="2" t="s">
-        <v>2016</v>
+        <v>983</v>
       </c>
     </row>
     <row r="746" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A746" s="2" t="s">
-        <v>2017</v>
+        <v>2025</v>
       </c>
       <c r="B746" s="2" t="s">
-        <v>1850</v>
+        <v>950</v>
       </c>
       <c r="C746" s="2" t="s">
-        <v>1851</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="747" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A747" s="2" t="s">
-        <v>2018</v>
+        <v>2026</v>
       </c>
       <c r="B747" s="2" t="s">
-        <v>1853</v>
+        <v>986</v>
       </c>
       <c r="C747" s="2" t="s">
-        <v>1854</v>
+        <v>987</v>
       </c>
     </row>
     <row r="748" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A748" s="2" t="s">
-        <v>2019</v>
+        <v>2027</v>
       </c>
       <c r="B748" s="2" t="s">
-        <v>2020</v>
+        <v>2028</v>
       </c>
       <c r="C748" s="2" t="s">
-        <v>2021</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="749" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A749" s="2" t="s">
-        <v>2022</v>
+        <v>2030</v>
       </c>
       <c r="B749" s="2" t="s">
-        <v>2023</v>
+        <v>992</v>
       </c>
       <c r="C749" s="2" t="s">
-        <v>2024</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="750" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A750" s="2" t="s">
-        <v>2025</v>
+        <v>2032</v>
       </c>
       <c r="B750" s="2" t="s">
-        <v>2026</v>
+        <v>2033</v>
       </c>
       <c r="C750" s="2" t="s">
-        <v>2027</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="751" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A751" s="2" t="s">
-        <v>2028</v>
+        <v>2035</v>
       </c>
       <c r="B751" s="2" t="s">
-        <v>2029</v>
+        <v>998</v>
       </c>
       <c r="C751" s="2" t="s">
-        <v>2030</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="752" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A752" s="2" t="s">
-        <v>2031</v>
+        <v>2037</v>
       </c>
       <c r="B752" s="2" t="s">
-        <v>2032</v>
+        <v>2038</v>
       </c>
       <c r="C752" s="2" t="s">
-        <v>2033</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="753" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A753" s="2" t="s">
-        <v>2034</v>
+        <v>2040</v>
       </c>
       <c r="B753" s="2" t="s">
-        <v>2035</v>
+        <v>2041</v>
       </c>
       <c r="C753" s="2" t="s">
-        <v>2036</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="754" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A754" s="2" t="s">
-        <v>2037</v>
+        <v>2043</v>
       </c>
       <c r="B754" s="2" t="s">
-        <v>457</v>
+        <v>2044</v>
       </c>
       <c r="C754" s="2" t="s">
-        <v>458</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="755" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A755" s="2" t="s">
-        <v>2038</v>
+        <v>2046</v>
       </c>
       <c r="B755" s="2" t="s">
-        <v>2039</v>
+        <v>816</v>
       </c>
       <c r="C755" s="2" t="s">
-        <v>2040</v>
+        <v>817</v>
       </c>
     </row>
     <row r="756" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A756" s="2" t="s">
-        <v>2041</v>
+        <v>2047</v>
       </c>
       <c r="B756" s="2" t="s">
-        <v>2042</v>
+        <v>1008</v>
       </c>
       <c r="C756" s="2" t="s">
-        <v>2043</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="757" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A757" s="2" t="s">
-        <v>2044</v>
+        <v>2048</v>
       </c>
       <c r="B757" s="2" t="s">
-        <v>469</v>
+        <v>1011</v>
       </c>
       <c r="C757" s="2" t="s">
-        <v>612</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="758" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A758" s="2" t="s">
-        <v>2045</v>
+        <v>2050</v>
       </c>
       <c r="B758" s="2" t="s">
-        <v>475</v>
+        <v>1014</v>
       </c>
       <c r="C758" s="2" t="s">
-        <v>2046</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="759" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A759" s="2" t="s">
-        <v>2047</v>
+        <v>2052</v>
       </c>
       <c r="B759" s="2" t="s">
-        <v>508</v>
+        <v>1017</v>
       </c>
       <c r="C759" s="2" t="s">
-        <v>2048</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="760" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A760" s="2" t="s">
-        <v>2049</v>
+        <v>2054</v>
       </c>
       <c r="B760" s="2" t="s">
-        <v>511</v>
+        <v>2055</v>
       </c>
       <c r="C760" s="2" t="s">
-        <v>2050</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="761" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A761" s="2" t="s">
-        <v>2051</v>
+        <v>2057</v>
       </c>
       <c r="B761" s="2" t="s">
-        <v>2052</v>
+        <v>1890</v>
       </c>
       <c r="C761" s="2" t="s">
-        <v>2053</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="762" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A762" s="2" t="s">
-        <v>2054</v>
+        <v>2058</v>
       </c>
       <c r="B762" s="2" t="s">
-        <v>2055</v>
+        <v>1893</v>
       </c>
       <c r="C762" s="2" t="s">
-        <v>2056</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="763" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A763" s="2" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="B763" s="2" t="s">
-        <v>2058</v>
+        <v>2060</v>
       </c>
       <c r="C763" s="2" t="s">
-        <v>2059</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="764" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A764" s="2" t="s">
-        <v>2060</v>
+        <v>2062</v>
       </c>
       <c r="B764" s="2" t="s">
-        <v>478</v>
+        <v>2063</v>
       </c>
       <c r="C764" s="2" t="s">
-        <v>479</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="765" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A765" s="2" t="s">
-        <v>2061</v>
+        <v>2065</v>
       </c>
       <c r="B765" s="2" t="s">
-        <v>2062</v>
+        <v>2066</v>
       </c>
       <c r="C765" s="2" t="s">
-        <v>2063</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="766" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A766" s="2" t="s">
-        <v>2064</v>
+        <v>2068</v>
       </c>
       <c r="B766" s="2" t="s">
-        <v>490</v>
+        <v>2069</v>
       </c>
       <c r="C766" s="2" t="s">
-        <v>491</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="767" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A767" s="2" t="s">
-        <v>2065</v>
+        <v>2071</v>
       </c>
       <c r="B767" s="2" t="s">
-        <v>496</v>
+        <v>2072</v>
       </c>
       <c r="C767" s="2" t="s">
-        <v>497</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="768" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A768" s="2" t="s">
-        <v>2066</v>
+        <v>2074</v>
       </c>
       <c r="B768" s="2" t="s">
-        <v>2067</v>
+        <v>2075</v>
       </c>
       <c r="C768" s="2" t="s">
-        <v>2068</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="769" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A769" s="2" t="s">
-        <v>2069</v>
+        <v>2077</v>
       </c>
       <c r="B769" s="2" t="s">
-        <v>499</v>
+        <v>466</v>
       </c>
       <c r="C769" s="2" t="s">
-        <v>224</v>
+        <v>467</v>
       </c>
     </row>
     <row r="770" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A770" s="2" t="s">
-        <v>2070</v>
+        <v>2078</v>
       </c>
       <c r="B770" s="2" t="s">
-        <v>502</v>
+        <v>2079</v>
       </c>
       <c r="C770" s="2" t="s">
-        <v>2071</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="771" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A771" s="2" t="s">
-        <v>2072</v>
+        <v>2081</v>
       </c>
       <c r="B771" s="2" t="s">
-        <v>544</v>
+        <v>2082</v>
       </c>
       <c r="C771" s="2" t="s">
-        <v>2073</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="772" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A772" s="2" t="s">
-        <v>2074</v>
+        <v>2084</v>
       </c>
       <c r="B772" s="2" t="s">
-        <v>2075</v>
+        <v>478</v>
       </c>
       <c r="C772" s="2" t="s">
-        <v>2076</v>
+        <v>624</v>
       </c>
     </row>
     <row r="773" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A773" s="2" t="s">
-        <v>2077</v>
+        <v>2085</v>
       </c>
       <c r="B773" s="2" t="s">
-        <v>526</v>
+        <v>484</v>
       </c>
       <c r="C773" s="2" t="s">
-        <v>527</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="774" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A774" s="2" t="s">
-        <v>2078</v>
+        <v>2087</v>
       </c>
       <c r="B774" s="2" t="s">
-        <v>2079</v>
+        <v>520</v>
       </c>
       <c r="C774" s="2" t="s">
-        <v>2080</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="775" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A775" s="2" t="s">
-        <v>2081</v>
+        <v>2089</v>
       </c>
       <c r="B775" s="2" t="s">
-        <v>2082</v>
+        <v>523</v>
       </c>
       <c r="C775" s="2" t="s">
-        <v>2083</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="776" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A776" s="2" t="s">
-        <v>2084</v>
+        <v>2091</v>
       </c>
       <c r="B776" s="2" t="s">
-        <v>2085</v>
+        <v>2092</v>
       </c>
       <c r="C776" s="2" t="s">
-        <v>536</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="777" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A777" s="2" t="s">
-        <v>2086</v>
+        <v>2094</v>
       </c>
       <c r="B777" s="2" t="s">
-        <v>2087</v>
+        <v>2095</v>
       </c>
       <c r="C777" s="2" t="s">
-        <v>539</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="778" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A778" s="2" t="s">
-        <v>2088</v>
+        <v>2097</v>
       </c>
       <c r="B778" s="2" t="s">
-        <v>2089</v>
+        <v>2098</v>
       </c>
       <c r="C778" s="2" t="s">
-        <v>2090</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="779" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A779" s="2" t="s">
-        <v>2091</v>
+        <v>2100</v>
       </c>
       <c r="B779" s="2" t="s">
-        <v>2092</v>
+        <v>487</v>
       </c>
       <c r="C779" s="2" t="s">
-        <v>2093</v>
+        <v>488</v>
       </c>
     </row>
     <row r="780" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A780" s="2" t="s">
-        <v>2094</v>
+        <v>2101</v>
       </c>
       <c r="B780" s="2" t="s">
-        <v>550</v>
+        <v>2102</v>
       </c>
       <c r="C780" s="2" t="s">
-        <v>551</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="781" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A781" s="2" t="s">
-        <v>2095</v>
+        <v>2104</v>
       </c>
       <c r="B781" s="2" t="s">
-        <v>2096</v>
+        <v>499</v>
       </c>
       <c r="C781" s="2" t="s">
-        <v>2097</v>
+        <v>500</v>
       </c>
     </row>
     <row r="782" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A782" s="2" t="s">
-        <v>2098</v>
+        <v>2105</v>
       </c>
       <c r="B782" s="2" t="s">
-        <v>556</v>
+        <v>505</v>
       </c>
       <c r="C782" s="2" t="s">
-        <v>557</v>
+        <v>506</v>
       </c>
     </row>
     <row r="783" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A783" s="2" t="s">
-        <v>2099</v>
+        <v>2106</v>
       </c>
       <c r="B783" s="2" t="s">
-        <v>559</v>
+        <v>2107</v>
       </c>
       <c r="C783" s="2" t="s">
-        <v>560</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="784" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A784" s="2" t="s">
-        <v>2100</v>
+        <v>2109</v>
       </c>
       <c r="B784" s="2" t="s">
-        <v>2101</v>
+        <v>508</v>
       </c>
       <c r="C784" s="2" t="s">
-        <v>2102</v>
+        <v>233</v>
       </c>
     </row>
     <row r="785" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A785" s="2" t="s">
-        <v>2103</v>
+        <v>2110</v>
       </c>
       <c r="B785" s="2" t="s">
-        <v>565</v>
+        <v>511</v>
       </c>
       <c r="C785" s="2" t="s">
-        <v>566</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="786" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A786" s="2" t="s">
-        <v>2104</v>
+        <v>2112</v>
       </c>
       <c r="B786" s="2" t="s">
-        <v>568</v>
+        <v>517</v>
       </c>
       <c r="C786" s="2" t="s">
-        <v>569</v>
+        <v>518</v>
       </c>
     </row>
     <row r="787" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A787" s="2" t="s">
-        <v>2105</v>
+        <v>2113</v>
       </c>
       <c r="B787" s="2" t="s">
-        <v>2106</v>
+        <v>556</v>
       </c>
       <c r="C787" s="2" t="s">
-        <v>2107</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="788" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A788" s="2" t="s">
-        <v>2108</v>
+        <v>2115</v>
       </c>
       <c r="B788" s="2" t="s">
-        <v>2109</v>
+        <v>2116</v>
       </c>
       <c r="C788" s="2" t="s">
-        <v>2110</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="789" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A789" s="2" t="s">
-        <v>2111</v>
+        <v>2118</v>
       </c>
       <c r="B789" s="2" t="s">
-        <v>2112</v>
+        <v>538</v>
       </c>
       <c r="C789" s="2" t="s">
-        <v>2113</v>
+        <v>539</v>
       </c>
     </row>
     <row r="790" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A790" s="2" t="s">
-        <v>2114</v>
+        <v>2119</v>
       </c>
       <c r="B790" s="2" t="s">
-        <v>583</v>
+        <v>2120</v>
       </c>
       <c r="C790" s="2" t="s">
-        <v>584</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="791" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A791" s="2" t="s">
-        <v>2115</v>
+        <v>2122</v>
       </c>
       <c r="B791" s="2" t="s">
-        <v>2116</v>
+        <v>2123</v>
       </c>
       <c r="C791" s="2" t="s">
-        <v>2117</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="792" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A792" s="2" t="s">
-        <v>2118</v>
+        <v>2125</v>
       </c>
       <c r="B792" s="2" t="s">
-        <v>574</v>
+        <v>2126</v>
       </c>
       <c r="C792" s="2" t="s">
-        <v>575</v>
+        <v>548</v>
       </c>
     </row>
     <row r="793" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A793" s="2" t="s">
-        <v>2119</v>
+        <v>2127</v>
       </c>
       <c r="B793" s="2" t="s">
-        <v>577</v>
+        <v>2128</v>
       </c>
       <c r="C793" s="2" t="s">
-        <v>578</v>
+        <v>551</v>
       </c>
     </row>
     <row r="794" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A794" s="2" t="s">
-        <v>2120</v>
+        <v>2129</v>
       </c>
       <c r="B794" s="2" t="s">
-        <v>590</v>
+        <v>2130</v>
       </c>
       <c r="C794" s="2" t="s">
-        <v>591</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="795" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A795" s="2" t="s">
-        <v>2121</v>
+        <v>2132</v>
       </c>
       <c r="B795" s="2" t="s">
-        <v>593</v>
+        <v>2133</v>
       </c>
       <c r="C795" s="2" t="s">
-        <v>594</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="796" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A796" s="2" t="s">
-        <v>2122</v>
+        <v>2135</v>
       </c>
       <c r="B796" s="2" t="s">
-        <v>596</v>
+        <v>562</v>
       </c>
       <c r="C796" s="2" t="s">
-        <v>596</v>
+        <v>563</v>
       </c>
     </row>
     <row r="797" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A797" s="2" t="s">
-        <v>2123</v>
+        <v>2136</v>
       </c>
       <c r="B797" s="2" t="s">
-        <v>598</v>
+        <v>2137</v>
       </c>
       <c r="C797" s="2" t="s">
-        <v>599</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="798" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A798" s="2" t="s">
-        <v>2124</v>
+        <v>2139</v>
       </c>
       <c r="B798" s="2" t="s">
-        <v>587</v>
+        <v>568</v>
       </c>
       <c r="C798" s="2" t="s">
-        <v>588</v>
+        <v>569</v>
       </c>
     </row>
     <row r="799" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A799" s="2" t="s">
-        <v>2125</v>
+        <v>2140</v>
       </c>
       <c r="B799" s="2" t="s">
-        <v>2126</v>
+        <v>571</v>
       </c>
       <c r="C799" s="2" t="s">
-        <v>2127</v>
+        <v>572</v>
       </c>
     </row>
     <row r="800" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A800" s="2" t="s">
-        <v>2128</v>
+        <v>2141</v>
       </c>
       <c r="B800" s="2" t="s">
-        <v>2129</v>
+        <v>2142</v>
       </c>
       <c r="C800" s="2" t="s">
-        <v>2130</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="801" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A801" s="2" t="s">
-        <v>2131</v>
+        <v>2144</v>
       </c>
       <c r="B801" s="2" t="s">
-        <v>2132</v>
+        <v>577</v>
       </c>
       <c r="C801" s="2" t="s">
-        <v>2133</v>
+        <v>578</v>
       </c>
     </row>
     <row r="802" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A802" s="2" t="s">
-        <v>2134</v>
+        <v>2145</v>
       </c>
       <c r="B802" s="2" t="s">
-        <v>2135</v>
+        <v>580</v>
       </c>
       <c r="C802" s="2" t="s">
-        <v>2136</v>
+        <v>581</v>
       </c>
     </row>
     <row r="803" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A803" s="2" t="s">
-        <v>2137</v>
+        <v>2146</v>
       </c>
       <c r="B803" s="2" t="s">
-        <v>2138</v>
+        <v>2147</v>
       </c>
       <c r="C803" s="2" t="s">
-        <v>2139</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="804" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A804" s="2" t="s">
-        <v>2140</v>
+        <v>2149</v>
       </c>
       <c r="B804" s="2" t="s">
-        <v>2141</v>
+        <v>2150</v>
       </c>
       <c r="C804" s="2" t="s">
-        <v>1772</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="805" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A805" s="2" t="s">
-        <v>2142</v>
+        <v>2152</v>
       </c>
       <c r="B805" s="2" t="s">
-        <v>2143</v>
+        <v>2153</v>
       </c>
       <c r="C805" s="2" t="s">
-        <v>2144</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="806" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A806" s="2" t="s">
-        <v>2145</v>
+        <v>2155</v>
       </c>
       <c r="B806" s="2" t="s">
-        <v>2146</v>
+        <v>595</v>
       </c>
       <c r="C806" s="2" t="s">
-        <v>2147</v>
+        <v>596</v>
       </c>
     </row>
     <row r="807" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A807" s="2" t="s">
-        <v>2148</v>
+        <v>2156</v>
       </c>
       <c r="B807" s="2" t="s">
-        <v>2149</v>
+        <v>2157</v>
       </c>
       <c r="C807" s="2" t="s">
-        <v>2150</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="808" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A808" s="2" t="s">
-        <v>2151</v>
+        <v>2159</v>
       </c>
       <c r="B808" s="2" t="s">
-        <v>2152</v>
+        <v>586</v>
       </c>
       <c r="C808" s="2" t="s">
-        <v>232</v>
+        <v>587</v>
       </c>
     </row>
     <row r="809" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A809" s="2" t="s">
-        <v>2153</v>
+        <v>2160</v>
       </c>
       <c r="B809" s="2" t="s">
-        <v>2154</v>
+        <v>589</v>
       </c>
       <c r="C809" s="2" t="s">
-        <v>2155</v>
+        <v>590</v>
       </c>
     </row>
     <row r="810" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A810" s="2" t="s">
-        <v>2156</v>
+        <v>2161</v>
       </c>
       <c r="B810" s="2" t="s">
-        <v>2157</v>
+        <v>602</v>
       </c>
       <c r="C810" s="2" t="s">
-        <v>2158</v>
+        <v>603</v>
       </c>
     </row>
     <row r="811" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A811" s="2" t="s">
-        <v>2159</v>
+        <v>2162</v>
       </c>
       <c r="B811" s="2" t="s">
-        <v>2160</v>
+        <v>605</v>
       </c>
       <c r="C811" s="2" t="s">
-        <v>2161</v>
+        <v>606</v>
       </c>
     </row>
     <row r="812" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A812" s="2" t="s">
-        <v>2162</v>
+        <v>2163</v>
       </c>
       <c r="B812" s="2" t="s">
-        <v>2163</v>
+        <v>608</v>
       </c>
       <c r="C812" s="2" t="s">
-        <v>2164</v>
+        <v>608</v>
       </c>
     </row>
     <row r="813" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A813" s="2" t="s">
-        <v>2165</v>
+        <v>2164</v>
       </c>
       <c r="B813" s="2" t="s">
-        <v>2166</v>
+        <v>610</v>
       </c>
       <c r="C813" s="2" t="s">
-        <v>2167</v>
+        <v>611</v>
       </c>
     </row>
     <row r="814" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A814" s="2" t="s">
-        <v>2168</v>
+        <v>2165</v>
       </c>
       <c r="B814" s="2" t="s">
-        <v>2169</v>
+        <v>599</v>
       </c>
       <c r="C814" s="2" t="s">
-        <v>2170</v>
+        <v>600</v>
       </c>
     </row>
     <row r="815" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A815" s="2" t="s">
-        <v>2171</v>
+        <v>2166</v>
       </c>
       <c r="B815" s="2" t="s">
-        <v>2172</v>
+        <v>2167</v>
       </c>
       <c r="C815" s="2" t="s">
-        <v>2173</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="816" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A816" s="2" t="s">
-        <v>2174</v>
+        <v>2169</v>
       </c>
       <c r="B816" s="2" t="s">
-        <v>2175</v>
+        <v>2170</v>
       </c>
       <c r="C816" s="2" t="s">
-        <v>2176</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="817" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A817" s="2" t="s">
-        <v>2177</v>
+        <v>2172</v>
       </c>
       <c r="B817" s="2" t="s">
-        <v>2178</v>
+        <v>2173</v>
       </c>
       <c r="C817" s="2" t="s">
-        <v>2179</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="818" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A818" s="2" t="s">
-        <v>2180</v>
+        <v>2175</v>
       </c>
       <c r="B818" s="2" t="s">
-        <v>2181</v>
+        <v>2176</v>
       </c>
       <c r="C818" s="2" t="s">
-        <v>2182</v>
+        <v>2177</v>
       </c>
     </row>
     <row r="819" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A819" s="2" t="s">
-        <v>2183</v>
+        <v>2178</v>
       </c>
       <c r="B819" s="2" t="s">
-        <v>2184</v>
+        <v>2179</v>
       </c>
       <c r="C819" s="2" t="s">
-        <v>2185</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="820" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A820" s="2" t="s">
-        <v>2186</v>
+        <v>2181</v>
       </c>
       <c r="B820" s="2" t="s">
-        <v>686</v>
+        <v>2182</v>
       </c>
       <c r="C820" s="2" t="s">
-        <v>687</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="821" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A821" s="2" t="s">
-        <v>2187</v>
+        <v>2183</v>
       </c>
       <c r="B821" s="2" t="s">
-        <v>689</v>
+        <v>2184</v>
       </c>
       <c r="C821" s="2" t="s">
-        <v>690</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="822" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A822" s="2" t="s">
+        <v>2186</v>
+      </c>
+      <c r="B822" s="2" t="s">
+        <v>2187</v>
+      </c>
+      <c r="C822" s="2" t="s">
         <v>2188</v>
-      </c>
-      <c r="B822" s="2" t="s">
-        <v>2189</v>
-      </c>
-      <c r="C822" s="2" t="s">
-        <v>2190</v>
       </c>
     </row>
     <row r="823" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A823" s="2" t="s">
+        <v>2189</v>
+      </c>
+      <c r="B823" s="2" t="s">
+        <v>2190</v>
+      </c>
+      <c r="C823" s="2" t="s">
         <v>2191</v>
-      </c>
-      <c r="B823" s="2" t="s">
-        <v>2192</v>
-      </c>
-      <c r="C823" s="2" t="s">
-        <v>2193</v>
       </c>
     </row>
     <row r="824" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A824" s="2" t="s">
-        <v>2194</v>
+        <v>2192</v>
       </c>
       <c r="B824" s="2" t="s">
-        <v>2195</v>
+        <v>2193</v>
       </c>
       <c r="C824" s="2" t="s">
-        <v>2196</v>
+        <v>241</v>
       </c>
     </row>
     <row r="825" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A825" s="2" t="s">
-        <v>2197</v>
+        <v>2194</v>
       </c>
       <c r="B825" s="2" t="s">
-        <v>2198</v>
+        <v>2195</v>
       </c>
       <c r="C825" s="2" t="s">
-        <v>2199</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="826" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A826" s="2" t="s">
-        <v>2200</v>
+        <v>2197</v>
       </c>
       <c r="B826" s="2" t="s">
-        <v>2201</v>
+        <v>2198</v>
       </c>
       <c r="C826" s="2" t="s">
-        <v>2202</v>
+        <v>2199</v>
       </c>
     </row>
     <row r="827" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A827" s="2" t="s">
-        <v>2203</v>
+        <v>2200</v>
       </c>
       <c r="B827" s="2" t="s">
-        <v>2204</v>
+        <v>2201</v>
       </c>
       <c r="C827" s="2" t="s">
-        <v>2205</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="828" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A828" s="2" t="s">
-        <v>2206</v>
+        <v>2203</v>
       </c>
       <c r="B828" s="2" t="s">
-        <v>2207</v>
+        <v>2204</v>
       </c>
       <c r="C828" s="2" t="s">
-        <v>2208</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="829" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A829" s="2" t="s">
-        <v>2209</v>
+        <v>2206</v>
       </c>
       <c r="B829" s="2" t="s">
-        <v>187</v>
+        <v>2207</v>
       </c>
       <c r="C829" s="2" t="s">
-        <v>188</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="830" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A830" s="2" t="s">
+        <v>2209</v>
+      </c>
+      <c r="B830" s="2" t="s">
         <v>2210</v>
       </c>
-      <c r="B830" s="2" t="s">
+      <c r="C830" s="2" t="s">
         <v>2211</v>
-      </c>
-      <c r="C830" s="2" t="s">
-        <v>2212</v>
       </c>
     </row>
     <row r="831" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A831" s="2" t="s">
+        <v>2212</v>
+      </c>
+      <c r="B831" s="2" t="s">
         <v>2213</v>
       </c>
-      <c r="B831" s="2" t="s">
+      <c r="C831" s="2" t="s">
         <v>2214</v>
-      </c>
-      <c r="C831" s="2" t="s">
-        <v>2215</v>
       </c>
     </row>
     <row r="832" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A832" s="2" t="s">
+        <v>2215</v>
+      </c>
+      <c r="B832" s="2" t="s">
         <v>2216</v>
       </c>
-      <c r="B832" s="2" t="s">
+      <c r="C832" s="2" t="s">
         <v>2217</v>
       </c>
-      <c r="C832" s="2" t="s">
+    </row>
+    <row r="833" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A833" s="2" t="s">
         <v>2218</v>
+      </c>
+      <c r="B833" s="2" t="s">
+        <v>2219</v>
+      </c>
+      <c r="C833" s="2" t="s">
+        <v>2220</v>
+      </c>
+    </row>
+    <row r="834" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A834" s="2" t="s">
+        <v>2221</v>
+      </c>
+      <c r="B834" s="2" t="s">
+        <v>2222</v>
+      </c>
+      <c r="C834" s="2" t="s">
+        <v>2223</v>
+      </c>
+    </row>
+    <row r="835" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A835" s="2" t="s">
+        <v>2224</v>
+      </c>
+      <c r="B835" s="2" t="s">
+        <v>2225</v>
+      </c>
+      <c r="C835" s="2" t="s">
+        <v>2226</v>
+      </c>
+    </row>
+    <row r="836" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A836" s="2" t="s">
+        <v>2227</v>
+      </c>
+      <c r="B836" s="2" t="s">
+        <v>2228</v>
+      </c>
+      <c r="C836" s="2" t="s">
+        <v>2229</v>
+      </c>
+    </row>
+    <row r="837" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A837" s="2" t="s">
+        <v>2230</v>
+      </c>
+      <c r="B837" s="2" t="s">
+        <v>2231</v>
+      </c>
+      <c r="C837" s="2" t="s">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="838" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A838" s="2" t="s">
+        <v>2233</v>
+      </c>
+      <c r="B838" s="2" t="s">
+        <v>2234</v>
+      </c>
+      <c r="C838" s="2" t="s">
+        <v>2235</v>
+      </c>
+    </row>
+    <row r="839" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A839" s="2" t="s">
+        <v>2236</v>
+      </c>
+      <c r="B839" s="2" t="s">
+        <v>2237</v>
+      </c>
+      <c r="C839" s="2" t="s">
+        <v>2238</v>
+      </c>
+    </row>
+    <row r="840" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A840" s="2" t="s">
+        <v>2239</v>
+      </c>
+      <c r="B840" s="2" t="s">
+        <v>2240</v>
+      </c>
+      <c r="C840" s="2" t="s">
+        <v>2241</v>
+      </c>
+    </row>
+    <row r="841" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A841" s="2" t="s">
+        <v>2242</v>
+      </c>
+      <c r="B841" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="C841" s="2" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="842" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A842" s="2" t="s">
+        <v>2243</v>
+      </c>
+      <c r="B842" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="C842" s="2" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="843" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A843" s="2" t="s">
+        <v>2244</v>
+      </c>
+      <c r="B843" s="2" t="s">
+        <v>2245</v>
+      </c>
+      <c r="C843" s="2" t="s">
+        <v>2246</v>
+      </c>
+    </row>
+    <row r="844" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A844" s="2" t="s">
+        <v>2247</v>
+      </c>
+      <c r="B844" s="2" t="s">
+        <v>2248</v>
+      </c>
+      <c r="C844" s="2" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="845" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A845" s="2" t="s">
+        <v>2250</v>
+      </c>
+      <c r="B845" s="2" t="s">
+        <v>2251</v>
+      </c>
+      <c r="C845" s="2" t="s">
+        <v>2252</v>
+      </c>
+    </row>
+    <row r="846" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A846" s="2" t="s">
+        <v>2253</v>
+      </c>
+      <c r="B846" s="2" t="s">
+        <v>2254</v>
+      </c>
+      <c r="C846" s="2" t="s">
+        <v>2255</v>
+      </c>
+    </row>
+    <row r="847" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A847" s="2" t="s">
+        <v>2256</v>
+      </c>
+      <c r="B847" s="2" t="s">
+        <v>2257</v>
+      </c>
+      <c r="C847" s="2" t="s">
+        <v>2258</v>
+      </c>
+    </row>
+    <row r="848" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A848" s="2" t="s">
+        <v>2259</v>
+      </c>
+      <c r="B848" s="2" t="s">
+        <v>2260</v>
+      </c>
+      <c r="C848" s="2" t="s">
+        <v>2261</v>
+      </c>
+    </row>
+    <row r="849" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A849" s="2" t="s">
+        <v>2262</v>
+      </c>
+      <c r="B849" s="2" t="s">
+        <v>2263</v>
+      </c>
+      <c r="C849" s="2" t="s">
+        <v>2264</v>
+      </c>
+    </row>
+    <row r="850" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A850" s="2" t="s">
+        <v>2265</v>
+      </c>
+      <c r="B850" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C850" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="851" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A851" s="2" t="s">
+        <v>2266</v>
+      </c>
+      <c r="B851" s="2" t="s">
+        <v>2267</v>
+      </c>
+      <c r="C851" s="2" t="s">
+        <v>2268</v>
+      </c>
+    </row>
+    <row r="852" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A852" s="2" t="s">
+        <v>2269</v>
+      </c>
+      <c r="B852" s="2" t="s">
+        <v>2270</v>
+      </c>
+      <c r="C852" s="2" t="s">
+        <v>2271</v>
+      </c>
+    </row>
+    <row r="853" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A853" s="2" t="s">
+        <v>2272</v>
+      </c>
+      <c r="B853" s="2" t="s">
+        <v>2273</v>
+      </c>
+      <c r="C853" s="2" t="s">
+        <v>2274</v>
+      </c>
+    </row>
+    <row r="854" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A854" s="2" t="s">
+        <v>2275</v>
+      </c>
+      <c r="B854" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="C854" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="855" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A855" s="2" t="s">
+        <v>2276</v>
+      </c>
+      <c r="B855" s="2" t="s">
+        <v>1588</v>
+      </c>
+      <c r="C855" s="2" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="856" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A856" s="2" t="s">
+        <v>2277</v>
+      </c>
+      <c r="B856" s="2" t="s">
+        <v>2278</v>
+      </c>
+      <c r="C856" s="2" t="s">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="857" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A857" s="2" t="s">
+        <v>2280</v>
+      </c>
+      <c r="B857" s="2" t="s">
+        <v>1521</v>
+      </c>
+      <c r="C857" s="2" t="s">
+        <v>2281</v>
+      </c>
+    </row>
+    <row r="858" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A858" s="2" t="s">
+        <v>2282</v>
+      </c>
+      <c r="B858" s="2" t="s">
+        <v>2283</v>
+      </c>
+      <c r="C858" s="2" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="859" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A859" s="2" t="s">
+        <v>2284</v>
+      </c>
+      <c r="B859" s="2" t="s">
+        <v>1593</v>
+      </c>
+      <c r="C859" s="2" t="s">
+        <v>1594</v>
+      </c>
+    </row>
+    <row r="860" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A860" s="2" t="s">
+        <v>2285</v>
+      </c>
+      <c r="B860" s="2" t="s">
+        <v>2286</v>
+      </c>
+      <c r="C860" s="2" t="s">
+        <v>2287</v>
+      </c>
+    </row>
+    <row r="861" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A861" s="2" t="s">
+        <v>2288</v>
+      </c>
+      <c r="B861" s="2" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C861" s="2" t="s">
+        <v>1789</v>
+      </c>
+    </row>
+    <row r="862" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A862" s="2" t="s">
+        <v>2289</v>
+      </c>
+      <c r="B862" s="2" t="s">
+        <v>1339</v>
+      </c>
+      <c r="C862" s="2" t="s">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="863" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A863" s="2" t="s">
+        <v>2290</v>
+      </c>
+      <c r="B863" s="2" t="s">
+        <v>2291</v>
+      </c>
+      <c r="C863" s="2" t="s">
+        <v>2292</v>
+      </c>
+    </row>
+    <row r="864" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A864" s="2" t="s">
+        <v>2293</v>
+      </c>
+      <c r="B864" s="2" t="s">
+        <v>2294</v>
+      </c>
+      <c r="C864" s="2" t="s">
+        <v>2295</v>
+      </c>
+    </row>
+    <row r="865" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A865" s="2" t="s">
+        <v>2296</v>
+      </c>
+      <c r="B865" s="2" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C865" s="2" t="s">
+        <v>1627</v>
+      </c>
+    </row>
+    <row r="866" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A866" s="2" t="s">
+        <v>2297</v>
+      </c>
+      <c r="B866" s="2" t="s">
+        <v>1355</v>
+      </c>
+      <c r="C866" s="2" t="s">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="867" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A867" s="2" t="s">
+        <v>2298</v>
+      </c>
+      <c r="B867" s="2" t="s">
+        <v>2299</v>
+      </c>
+      <c r="C867" s="2" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="868" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A868" s="2" t="s">
+        <v>2300</v>
+      </c>
+      <c r="B868" s="2" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C868" s="2" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="869" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A869" s="2" t="s">
+        <v>2301</v>
+      </c>
+      <c r="B869" s="2" t="s">
+        <v>2302</v>
+      </c>
+      <c r="C869" s="2" t="s">
+        <v>1656</v>
+      </c>
+    </row>
+    <row r="870" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A870" s="2" t="s">
+        <v>2303</v>
+      </c>
+      <c r="B870" s="2" t="s">
+        <v>2304</v>
+      </c>
+      <c r="C870" s="2" t="s">
+        <v>2305</v>
+      </c>
+    </row>
+    <row r="871" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A871" s="2" t="s">
+        <v>2306</v>
+      </c>
+      <c r="B871" s="2" t="s">
+        <v>2307</v>
+      </c>
+      <c r="C871" s="2" t="s">
+        <v>2308</v>
+      </c>
+    </row>
+    <row r="872" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A872" s="2" t="s">
+        <v>2309</v>
+      </c>
+      <c r="B872" s="2" t="s">
+        <v>2310</v>
+      </c>
+      <c r="C872" s="2" t="s">
+        <v>2311</v>
+      </c>
+    </row>
+    <row r="873" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A873" s="2" t="s">
+        <v>2312</v>
+      </c>
+      <c r="B873" s="2" t="s">
+        <v>2313</v>
+      </c>
+      <c r="C873" s="2" t="s">
+        <v>2314</v>
+      </c>
+    </row>
+    <row r="874" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A874" s="2" t="s">
+        <v>2315</v>
+      </c>
+      <c r="B874" s="2" t="s">
+        <v>2316</v>
+      </c>
+      <c r="C874" s="2" t="s">
+        <v>2317</v>
+      </c>
+    </row>
+    <row r="875" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A875" s="2" t="s">
+        <v>2318</v>
+      </c>
+      <c r="B875" s="2" t="s">
+        <v>2319</v>
+      </c>
+      <c r="C875" s="2" t="s">
+        <v>2320</v>
+      </c>
+    </row>
+    <row r="876" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A876" s="2" t="s">
+        <v>2321</v>
+      </c>
+      <c r="B876" s="2" t="s">
+        <v>1658</v>
+      </c>
+      <c r="C876" s="2" t="s">
+        <v>2322</v>
+      </c>
+    </row>
+    <row r="877" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A877" s="2" t="s">
+        <v>2323</v>
+      </c>
+      <c r="B877" s="2" t="s">
+        <v>2324</v>
+      </c>
+      <c r="C877" s="2" t="s">
+        <v>2325</v>
+      </c>
+    </row>
+    <row r="878" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A878" s="2" t="s">
+        <v>2326</v>
+      </c>
+      <c r="B878" s="2" t="s">
+        <v>2327</v>
+      </c>
+      <c r="C878" s="2" t="s">
+        <v>2327</v>
+      </c>
+    </row>
+    <row r="879" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A879" s="2" t="s">
+        <v>2328</v>
+      </c>
+      <c r="B879" s="2" t="s">
+        <v>2329</v>
+      </c>
+      <c r="C879" s="2" t="s">
+        <v>2330</v>
       </c>
     </row>
   </sheetData>

--- a/apps/workspace-web/i18n.xlsx
+++ b/apps/workspace-web/i18n.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2637" uniqueCount="2331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2652" uniqueCount="2345">
   <si>
     <t>key</t>
   </si>
@@ -166,6 +166,15 @@
     <t>/ page</t>
   </si>
   <si>
+    <t>common.payoutRequired</t>
+  </si>
+  <si>
+    <t>商店尚未完成收款設定，無法上架付費商品。請先於「收款設定」完成 Stripe 設定。</t>
+  </si>
+  <si>
+    <t>Payouts are not set up yet, so paid products cannot be published. Complete Stripe setup in "Payouts" first.</t>
+  </si>
+  <si>
     <t>storeError.actionFailed</t>
   </si>
   <si>
@@ -6836,6 +6845,39 @@
   </si>
   <si>
     <t>Failed to get download link</t>
+  </si>
+  <si>
+    <t>productEdit.publish</t>
+  </si>
+  <si>
+    <t>上架商品</t>
+  </si>
+  <si>
+    <t>productEdit.publishNeedVersionHint</t>
+  </si>
+  <si>
+    <t>需先建立版本並上傳可下載檔，才能上架商品。</t>
+  </si>
+  <si>
+    <t>Create a version and upload downloadable files before publishing.</t>
+  </si>
+  <si>
+    <t>productEdit.msgPublished</t>
+  </si>
+  <si>
+    <t>已上架，商品現已對外販售。</t>
+  </si>
+  <si>
+    <t>Published. The product is now live.</t>
+  </si>
+  <si>
+    <t>productEdit.msgPublishFailed</t>
+  </si>
+  <si>
+    <t>上架失敗</t>
+  </si>
+  <si>
+    <t>Failed to publish</t>
   </si>
   <si>
     <t>paymentStatus.all</t>
@@ -7389,7 +7431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C879"/>
+  <dimension ref="A1:C884"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
@@ -8149,21 +8191,21 @@
         <v>204</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>43</v>
+        <v>205</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>44</v>
+        <v>206</v>
       </c>
     </row>
     <row r="70" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>206</v>
+        <v>43</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>207</v>
+        <v>44</v>
       </c>
     </row>
     <row r="71" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8207,15 +8249,15 @@
         <v>218</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="75" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>221</v>
@@ -8284,18 +8326,18 @@
         <v>238</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>207</v>
+        <v>239</v>
       </c>
     </row>
     <row r="82" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>241</v>
+        <v>210</v>
       </c>
     </row>
     <row r="83" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8655,21 +8697,21 @@
         <v>338</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>28</v>
+        <v>339</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>29</v>
+        <v>340</v>
       </c>
     </row>
     <row r="116" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>340</v>
+        <v>28</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>341</v>
+        <v>29</v>
       </c>
     </row>
     <row r="117" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -8809,21 +8851,21 @@
         <v>378</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>315</v>
+        <v>379</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>316</v>
+        <v>380</v>
       </c>
     </row>
     <row r="130" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>380</v>
+        <v>318</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>381</v>
+        <v>319</v>
       </c>
     </row>
     <row r="131" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9095,21 +9137,21 @@
         <v>454</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>401</v>
+        <v>455</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>402</v>
+        <v>456</v>
       </c>
     </row>
     <row r="156" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>456</v>
+        <v>404</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>457</v>
+        <v>405</v>
       </c>
     </row>
     <row r="157" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9139,21 +9181,21 @@
         <v>464</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>327</v>
+        <v>465</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>328</v>
+        <v>466</v>
       </c>
     </row>
     <row r="160" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>466</v>
+        <v>330</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>467</v>
+        <v>331</v>
       </c>
     </row>
     <row r="161" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9634,21 +9676,21 @@
         <v>597</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>181</v>
+        <v>598</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>182</v>
+        <v>599</v>
       </c>
     </row>
     <row r="205" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>599</v>
+        <v>184</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>600</v>
+        <v>185</v>
       </c>
     </row>
     <row r="206" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9681,15 +9723,15 @@
         <v>608</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="209" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C209" s="2" t="s">
         <v>611</v>
@@ -9700,21 +9742,21 @@
         <v>612</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>562</v>
+        <v>613</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>563</v>
+        <v>614</v>
       </c>
     </row>
     <row r="211" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>614</v>
+        <v>565</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>615</v>
+        <v>566</v>
       </c>
     </row>
     <row r="212" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9758,40 +9800,40 @@
         <v>626</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>488</v>
+        <v>627</v>
       </c>
     </row>
     <row r="216" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>499</v>
+        <v>629</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
     </row>
     <row r="217" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>233</v>
+        <v>503</v>
       </c>
     </row>
     <row r="218" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>630</v>
+        <v>511</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>631</v>
+        <v>236</v>
       </c>
     </row>
     <row r="219" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9810,21 +9852,21 @@
         <v>635</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>538</v>
+        <v>636</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>539</v>
+        <v>637</v>
       </c>
     </row>
     <row r="221" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>637</v>
+        <v>541</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>638</v>
+        <v>542</v>
       </c>
     </row>
     <row r="222" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9876,21 +9918,21 @@
         <v>651</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>22</v>
+        <v>652</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>23</v>
+        <v>653</v>
       </c>
     </row>
     <row r="227" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>653</v>
+        <v>22</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>654</v>
+        <v>23</v>
       </c>
     </row>
     <row r="228" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -9942,18 +9984,18 @@
         <v>667</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>499</v>
+        <v>668</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="233" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>670</v>
+        <v>502</v>
       </c>
       <c r="C233" s="2" t="s">
         <v>671</v>
@@ -10052,21 +10094,21 @@
         <v>696</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>193</v>
+        <v>697</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>194</v>
+        <v>698</v>
       </c>
     </row>
     <row r="243" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>698</v>
+        <v>196</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>699</v>
+        <v>197</v>
       </c>
     </row>
     <row r="244" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10184,21 +10226,21 @@
         <v>730</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>218</v>
+        <v>731</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>218</v>
+        <v>732</v>
       </c>
     </row>
     <row r="255" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>732</v>
+        <v>221</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>733</v>
+        <v>221</v>
       </c>
     </row>
     <row r="256" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10206,21 +10248,21 @@
         <v>734</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>215</v>
+        <v>735</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>216</v>
+        <v>736</v>
       </c>
     </row>
     <row r="257" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>736</v>
+        <v>218</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>737</v>
+        <v>219</v>
       </c>
     </row>
     <row r="258" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10305,21 +10347,21 @@
         <v>759</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>367</v>
+        <v>760</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>368</v>
+        <v>761</v>
       </c>
     </row>
     <row r="266" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>761</v>
+        <v>370</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>762</v>
+        <v>371</v>
       </c>
     </row>
     <row r="267" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10327,21 +10369,21 @@
         <v>763</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>370</v>
+        <v>764</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>371</v>
+        <v>765</v>
       </c>
     </row>
     <row r="268" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>765</v>
+        <v>373</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>766</v>
+        <v>374</v>
       </c>
     </row>
     <row r="269" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10492,43 +10534,43 @@
         <v>806</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>367</v>
+        <v>807</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>368</v>
+        <v>808</v>
       </c>
     </row>
     <row r="283" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>761</v>
+        <v>370</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>762</v>
+        <v>371</v>
       </c>
     </row>
     <row r="284" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>370</v>
+        <v>764</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>371</v>
+        <v>765</v>
       </c>
     </row>
     <row r="285" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>810</v>
+        <v>373</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>811</v>
+        <v>374</v>
       </c>
     </row>
     <row r="286" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10602,21 +10644,21 @@
         <v>830</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>713</v>
+        <v>831</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>714</v>
+        <v>832</v>
       </c>
     </row>
     <row r="293" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>832</v>
+        <v>716</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>833</v>
+        <v>717</v>
       </c>
     </row>
     <row r="294" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -10712,21 +10754,21 @@
         <v>858</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>22</v>
+        <v>859</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>23</v>
+        <v>860</v>
       </c>
     </row>
     <row r="303" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>860</v>
+        <v>22</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>861</v>
+        <v>23</v>
       </c>
     </row>
     <row r="304" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11064,21 +11106,21 @@
         <v>952</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>626</v>
+        <v>953</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>488</v>
+        <v>954</v>
       </c>
     </row>
     <row r="335" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>954</v>
+        <v>629</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>955</v>
+        <v>491</v>
       </c>
     </row>
     <row r="336" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11086,21 +11128,21 @@
         <v>956</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>315</v>
+        <v>957</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>316</v>
+        <v>958</v>
       </c>
     </row>
     <row r="337" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>958</v>
+        <v>318</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>959</v>
+        <v>319</v>
       </c>
     </row>
     <row r="338" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11196,21 +11238,21 @@
         <v>984</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>950</v>
+        <v>985</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>951</v>
+        <v>986</v>
       </c>
     </row>
     <row r="347" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>986</v>
+        <v>953</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>987</v>
+        <v>954</v>
       </c>
     </row>
     <row r="348" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11284,21 +11326,21 @@
         <v>1006</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>816</v>
+        <v>1007</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>817</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="355" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>1008</v>
+        <v>819</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>1009</v>
+        <v>820</v>
       </c>
     </row>
     <row r="356" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11350,21 +11392,21 @@
         <v>1022</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>52</v>
+        <v>1023</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>53</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="361" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>1024</v>
+        <v>55</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>1025</v>
+        <v>56</v>
       </c>
     </row>
     <row r="362" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11540,29 +11582,29 @@
         <v>1072</v>
       </c>
       <c r="C377" s="2" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="378" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>449</v>
+        <v>1075</v>
       </c>
       <c r="C378" s="2" t="s">
-        <v>450</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="379" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A379" s="2" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>1075</v>
+        <v>452</v>
       </c>
       <c r="C379" s="2" t="s">
-        <v>1076</v>
+        <v>453</v>
       </c>
     </row>
     <row r="380" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -11661,15 +11703,15 @@
         <v>1102</v>
       </c>
       <c r="C388" s="2" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="389" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A389" s="2" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B389" s="2" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="C389" s="2" t="s">
         <v>1105</v>
@@ -11999,32 +12041,32 @@
         <v>1193</v>
       </c>
       <c r="B419" s="2" t="s">
-        <v>327</v>
+        <v>1194</v>
       </c>
       <c r="C419" s="2" t="s">
-        <v>328</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="420" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A420" s="2" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="B420" s="2" t="s">
-        <v>1195</v>
+        <v>330</v>
       </c>
       <c r="C420" s="2" t="s">
-        <v>733</v>
+        <v>331</v>
       </c>
     </row>
     <row r="421" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A421" s="2" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B421" s="2" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="C421" s="2" t="s">
-        <v>1198</v>
+        <v>736</v>
       </c>
     </row>
     <row r="422" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12043,21 +12085,21 @@
         <v>1202</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>215</v>
+        <v>1203</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>216</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="424" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A424" s="2" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="B424" s="2" t="s">
-        <v>1204</v>
+        <v>218</v>
       </c>
       <c r="C424" s="2" t="s">
-        <v>1205</v>
+        <v>219</v>
       </c>
     </row>
     <row r="425" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12142,32 +12184,32 @@
         <v>1227</v>
       </c>
       <c r="B432" s="2" t="s">
-        <v>309</v>
+        <v>1228</v>
       </c>
       <c r="C432" s="2" t="s">
-        <v>310</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="433" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A433" s="2" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>1229</v>
+        <v>312</v>
       </c>
       <c r="C433" s="2" t="s">
-        <v>1214</v>
+        <v>313</v>
       </c>
     </row>
     <row r="434" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A434" s="2" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="B434" s="2" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="C434" s="2" t="s">
-        <v>1232</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="435" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12219,21 +12261,21 @@
         <v>1245</v>
       </c>
       <c r="B439" s="2" t="s">
-        <v>327</v>
+        <v>1246</v>
       </c>
       <c r="C439" s="2" t="s">
-        <v>328</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="440" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A440" s="2" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="B440" s="2" t="s">
-        <v>1247</v>
+        <v>330</v>
       </c>
       <c r="C440" s="2" t="s">
-        <v>1248</v>
+        <v>331</v>
       </c>
     </row>
     <row r="441" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12406,18 +12448,18 @@
         <v>1294</v>
       </c>
       <c r="B456" s="2" t="s">
-        <v>383</v>
+        <v>1295</v>
       </c>
       <c r="C456" s="2" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="457" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A457" s="2" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="B457" s="2" t="s">
-        <v>1297</v>
+        <v>386</v>
       </c>
       <c r="C457" s="2" t="s">
         <v>1298</v>
@@ -12593,21 +12635,21 @@
         <v>1344</v>
       </c>
       <c r="B473" s="2" t="s">
-        <v>7</v>
+        <v>1345</v>
       </c>
       <c r="C473" s="2" t="s">
-        <v>8</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="474" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A474" s="2" t="s">
-        <v>1345</v>
+        <v>1347</v>
       </c>
       <c r="B474" s="2" t="s">
-        <v>1346</v>
+        <v>7</v>
       </c>
       <c r="C474" s="2" t="s">
-        <v>1347</v>
+        <v>8</v>
       </c>
     </row>
     <row r="475" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12670,21 +12712,21 @@
         <v>1363</v>
       </c>
       <c r="B480" s="2" t="s">
-        <v>1075</v>
+        <v>1364</v>
       </c>
       <c r="C480" s="2" t="s">
-        <v>1076</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="481" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A481" s="2" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="B481" s="2" t="s">
-        <v>1365</v>
+        <v>1078</v>
       </c>
       <c r="C481" s="2" t="s">
-        <v>1366</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="482" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12706,15 +12748,15 @@
         <v>1371</v>
       </c>
       <c r="C483" s="2" t="s">
-        <v>207</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="484" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A484" s="2" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="B484" s="2" t="s">
-        <v>209</v>
+        <v>1374</v>
       </c>
       <c r="C484" s="2" t="s">
         <v>210</v>
@@ -12722,13 +12764,13 @@
     </row>
     <row r="485" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A485" s="2" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="B485" s="2" t="s">
-        <v>1374</v>
+        <v>212</v>
       </c>
       <c r="C485" s="2" t="s">
-        <v>1375</v>
+        <v>213</v>
       </c>
     </row>
     <row r="486" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12736,21 +12778,21 @@
         <v>1376</v>
       </c>
       <c r="B486" s="2" t="s">
-        <v>215</v>
+        <v>1377</v>
       </c>
       <c r="C486" s="2" t="s">
-        <v>216</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="487" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A487" s="2" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>1378</v>
+        <v>218</v>
       </c>
       <c r="C487" s="2" t="s">
-        <v>1379</v>
+        <v>219</v>
       </c>
     </row>
     <row r="488" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12758,21 +12800,21 @@
         <v>1380</v>
       </c>
       <c r="B488" s="2" t="s">
-        <v>315</v>
+        <v>1381</v>
       </c>
       <c r="C488" s="2" t="s">
-        <v>316</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="489" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A489" s="2" t="s">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="B489" s="2" t="s">
-        <v>1382</v>
+        <v>318</v>
       </c>
       <c r="C489" s="2" t="s">
-        <v>1383</v>
+        <v>319</v>
       </c>
     </row>
     <row r="490" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12780,43 +12822,43 @@
         <v>1384</v>
       </c>
       <c r="B490" s="2" t="s">
-        <v>1188</v>
+        <v>1385</v>
       </c>
       <c r="C490" s="2" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="491" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A491" s="2" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="B491" s="2" t="s">
-        <v>336</v>
+        <v>1191</v>
       </c>
       <c r="C491" s="2" t="s">
-        <v>337</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="492" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A492" s="2" t="s">
-        <v>1387</v>
+        <v>1389</v>
       </c>
       <c r="B492" s="2" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="C492" s="2" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
     </row>
     <row r="493" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A493" s="2" t="s">
-        <v>1388</v>
+        <v>1390</v>
       </c>
       <c r="B493" s="2" t="s">
-        <v>1389</v>
+        <v>333</v>
       </c>
       <c r="C493" s="2" t="s">
-        <v>1390</v>
+        <v>334</v>
       </c>
     </row>
     <row r="494" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12835,21 +12877,21 @@
         <v>1394</v>
       </c>
       <c r="B495" s="2" t="s">
-        <v>346</v>
+        <v>1395</v>
       </c>
       <c r="C495" s="2" t="s">
-        <v>347</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="496" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A496" s="2" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="B496" s="2" t="s">
-        <v>1396</v>
+        <v>349</v>
       </c>
       <c r="C496" s="2" t="s">
-        <v>1397</v>
+        <v>350</v>
       </c>
     </row>
     <row r="497" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12857,21 +12899,21 @@
         <v>1398</v>
       </c>
       <c r="B497" s="2" t="s">
-        <v>352</v>
+        <v>1399</v>
       </c>
       <c r="C497" s="2" t="s">
-        <v>353</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="498" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A498" s="2" t="s">
-        <v>1399</v>
+        <v>1401</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>1400</v>
+        <v>355</v>
       </c>
       <c r="C498" s="2" t="s">
-        <v>1401</v>
+        <v>356</v>
       </c>
     </row>
     <row r="499" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -12882,26 +12924,26 @@
         <v>1403</v>
       </c>
       <c r="C499" s="2" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="500" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A500" s="2" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="B500" s="2" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="C500" s="2" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="501" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A501" s="2" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="B501" s="2" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="C501" s="2" t="s">
         <v>1408</v>
@@ -12912,21 +12954,21 @@
         <v>1409</v>
       </c>
       <c r="B502" s="2" t="s">
-        <v>1407</v>
+        <v>1410</v>
       </c>
       <c r="C502" s="2" t="s">
-        <v>1408</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="503" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A503" s="2" t="s">
+        <v>1412</v>
+      </c>
+      <c r="B503" s="2" t="s">
         <v>1410</v>
       </c>
-      <c r="B503" s="2" t="s">
+      <c r="C503" s="2" t="s">
         <v>1411</v>
-      </c>
-      <c r="C503" s="2" t="s">
-        <v>1412</v>
       </c>
     </row>
     <row r="504" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13069,18 +13111,18 @@
         <v>1450</v>
       </c>
       <c r="C516" s="2" t="s">
-        <v>1427</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="517" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A517" s="2" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="B517" s="2" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="C517" s="2" t="s">
-        <v>1453</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="518" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13102,18 +13144,18 @@
         <v>1458</v>
       </c>
       <c r="C519" s="2" t="s">
-        <v>1433</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="520" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A520" s="2" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="B520" s="2" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="C520" s="2" t="s">
-        <v>1461</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="521" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13143,21 +13185,21 @@
         <v>1468</v>
       </c>
       <c r="B523" s="2" t="s">
-        <v>1316</v>
+        <v>1469</v>
       </c>
       <c r="C523" s="2" t="s">
-        <v>1316</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="524" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A524" s="2" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="B524" s="2" t="s">
-        <v>1470</v>
+        <v>1319</v>
       </c>
       <c r="C524" s="2" t="s">
-        <v>1471</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="525" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13253,21 +13295,21 @@
         <v>1496</v>
       </c>
       <c r="B533" s="2" t="s">
-        <v>1355</v>
+        <v>1497</v>
       </c>
       <c r="C533" s="2" t="s">
-        <v>1356</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="534" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A534" s="2" t="s">
-        <v>1497</v>
+        <v>1499</v>
       </c>
       <c r="B534" s="2" t="s">
-        <v>1498</v>
+        <v>1358</v>
       </c>
       <c r="C534" s="2" t="s">
-        <v>1499</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="535" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13333,23 +13375,23 @@
         <v>1516</v>
       </c>
       <c r="C540" s="2" t="s">
-        <v>241</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="541" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A541" s="2" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="B541" s="2" t="s">
-        <v>209</v>
+        <v>1519</v>
       </c>
       <c r="C541" s="2" t="s">
-        <v>210</v>
+        <v>244</v>
       </c>
     </row>
     <row r="542" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A542" s="2" t="s">
-        <v>1518</v>
+        <v>1520</v>
       </c>
       <c r="B542" s="2" t="s">
         <v>212</v>
@@ -13360,24 +13402,24 @@
     </row>
     <row r="543" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A543" s="2" t="s">
-        <v>1519</v>
+        <v>1521</v>
       </c>
       <c r="B543" s="2" t="s">
-        <v>719</v>
+        <v>215</v>
       </c>
       <c r="C543" s="2" t="s">
-        <v>720</v>
+        <v>216</v>
       </c>
     </row>
     <row r="544" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A544" s="2" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
       <c r="B544" s="2" t="s">
-        <v>1521</v>
+        <v>722</v>
       </c>
       <c r="C544" s="2" t="s">
-        <v>1522</v>
+        <v>723</v>
       </c>
     </row>
     <row r="545" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13608,73 +13650,73 @@
         <v>1584</v>
       </c>
       <c r="C565" s="2" t="s">
-        <v>1186</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="566" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A566" s="2" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="B566" s="2" t="s">
-        <v>1365</v>
+        <v>1587</v>
       </c>
       <c r="C566" s="2" t="s">
-        <v>1366</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="567" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A567" s="2" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="B567" s="2" t="s">
-        <v>43</v>
+        <v>1368</v>
       </c>
       <c r="C567" s="2" t="s">
-        <v>44</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="568" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A568" s="2" t="s">
-        <v>1587</v>
+        <v>1589</v>
       </c>
       <c r="B568" s="2" t="s">
-        <v>1588</v>
+        <v>43</v>
       </c>
       <c r="C568" s="2" t="s">
-        <v>1198</v>
+        <v>44</v>
       </c>
     </row>
     <row r="569" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A569" s="2" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="B569" s="2" t="s">
-        <v>1521</v>
+        <v>1591</v>
       </c>
       <c r="C569" s="2" t="s">
-        <v>1522</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="570" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A570" s="2" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
       <c r="B570" s="2" t="s">
-        <v>1591</v>
+        <v>1524</v>
       </c>
       <c r="C570" s="2" t="s">
-        <v>1307</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="571" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A571" s="2" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="B571" s="2" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="C571" s="2" t="s">
-        <v>1594</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="572" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13682,32 +13724,32 @@
         <v>1595</v>
       </c>
       <c r="B572" s="2" t="s">
-        <v>1524</v>
+        <v>1596</v>
       </c>
       <c r="C572" s="2" t="s">
-        <v>1525</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="573" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A573" s="2" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
       <c r="B573" s="2" t="s">
-        <v>218</v>
+        <v>1527</v>
       </c>
       <c r="C573" s="2" t="s">
-        <v>218</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="574" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A574" s="2" t="s">
-        <v>1597</v>
+        <v>1599</v>
       </c>
       <c r="B574" s="2" t="s">
-        <v>1598</v>
+        <v>221</v>
       </c>
       <c r="C574" s="2" t="s">
-        <v>1599</v>
+        <v>221</v>
       </c>
     </row>
     <row r="575" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13759,54 +13801,54 @@
         <v>1612</v>
       </c>
       <c r="B579" s="2" t="s">
-        <v>1352</v>
+        <v>1613</v>
       </c>
       <c r="C579" s="2" t="s">
-        <v>1353</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="580" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A580" s="2" t="s">
-        <v>1613</v>
+        <v>1615</v>
       </c>
       <c r="B580" s="2" t="s">
-        <v>4</v>
+        <v>1355</v>
       </c>
       <c r="C580" s="2" t="s">
-        <v>5</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="581" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A581" s="2" t="s">
-        <v>1614</v>
+        <v>1616</v>
       </c>
       <c r="B581" s="2" t="s">
-        <v>1339</v>
+        <v>4</v>
       </c>
       <c r="C581" s="2" t="s">
-        <v>1340</v>
+        <v>5</v>
       </c>
     </row>
     <row r="582" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A582" s="2" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="B582" s="2" t="s">
-        <v>1355</v>
+        <v>1342</v>
       </c>
       <c r="C582" s="2" t="s">
-        <v>1356</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="583" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A583" s="2" t="s">
-        <v>1616</v>
+        <v>1618</v>
       </c>
       <c r="B583" s="2" t="s">
-        <v>1617</v>
+        <v>1358</v>
       </c>
       <c r="C583" s="2" t="s">
-        <v>1618</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="584" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13825,21 +13867,21 @@
         <v>1622</v>
       </c>
       <c r="B585" s="2" t="s">
-        <v>1358</v>
+        <v>1623</v>
       </c>
       <c r="C585" s="2" t="s">
-        <v>1359</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="586" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A586" s="2" t="s">
-        <v>1623</v>
+        <v>1625</v>
       </c>
       <c r="B586" s="2" t="s">
-        <v>1624</v>
+        <v>1361</v>
       </c>
       <c r="C586" s="2" t="s">
-        <v>1625</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="587" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -13847,29 +13889,29 @@
         <v>1626</v>
       </c>
       <c r="B587" s="2" t="s">
-        <v>1361</v>
+        <v>1627</v>
       </c>
       <c r="C587" s="2" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="588" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A588" s="2" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="B588" s="2" t="s">
-        <v>1306</v>
+        <v>1364</v>
       </c>
       <c r="C588" s="2" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="589" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A589" s="2" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="B589" s="2" t="s">
-        <v>1631</v>
+        <v>1309</v>
       </c>
       <c r="C589" s="2" t="s">
         <v>1632</v>
@@ -13990,43 +14032,43 @@
         <v>1663</v>
       </c>
       <c r="B600" s="2" t="s">
-        <v>1352</v>
+        <v>1664</v>
       </c>
       <c r="C600" s="2" t="s">
-        <v>1353</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="601" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A601" s="2" t="s">
-        <v>1664</v>
+        <v>1666</v>
       </c>
       <c r="B601" s="2" t="s">
-        <v>4</v>
+        <v>1355</v>
       </c>
       <c r="C601" s="2" t="s">
-        <v>5</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="602" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A602" s="2" t="s">
-        <v>1665</v>
+        <v>1667</v>
       </c>
       <c r="B602" s="2" t="s">
-        <v>1358</v>
+        <v>4</v>
       </c>
       <c r="C602" s="2" t="s">
-        <v>1359</v>
+        <v>5</v>
       </c>
     </row>
     <row r="603" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A603" s="2" t="s">
-        <v>1666</v>
+        <v>1668</v>
       </c>
       <c r="B603" s="2" t="s">
-        <v>1667</v>
+        <v>1361</v>
       </c>
       <c r="C603" s="2" t="s">
-        <v>1668</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="604" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14056,21 +14098,21 @@
         <v>1675</v>
       </c>
       <c r="B606" s="2" t="s">
-        <v>1640</v>
+        <v>1676</v>
       </c>
       <c r="C606" s="2" t="s">
-        <v>1641</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="607" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A607" s="2" t="s">
-        <v>1676</v>
+        <v>1678</v>
       </c>
       <c r="B607" s="2" t="s">
-        <v>1677</v>
+        <v>1643</v>
       </c>
       <c r="C607" s="2" t="s">
-        <v>1678</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="608" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14089,21 +14131,21 @@
         <v>1682</v>
       </c>
       <c r="B609" s="2" t="s">
-        <v>1485</v>
+        <v>1683</v>
       </c>
       <c r="C609" s="2" t="s">
-        <v>1486</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="610" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A610" s="2" t="s">
-        <v>1683</v>
+        <v>1685</v>
       </c>
       <c r="B610" s="2" t="s">
-        <v>1684</v>
+        <v>1488</v>
       </c>
       <c r="C610" s="2" t="s">
-        <v>1685</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="611" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14191,18 +14233,18 @@
         <v>1708</v>
       </c>
       <c r="C618" s="2" t="s">
-        <v>624</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="619" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A619" s="2" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="B619" s="2" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="C619" s="2" t="s">
-        <v>1711</v>
+        <v>627</v>
       </c>
     </row>
     <row r="620" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14287,21 +14329,21 @@
         <v>1733</v>
       </c>
       <c r="B627" s="2" t="s">
-        <v>623</v>
+        <v>1734</v>
       </c>
       <c r="C627" s="2" t="s">
-        <v>624</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="628" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A628" s="2" t="s">
-        <v>1734</v>
+        <v>1736</v>
       </c>
       <c r="B628" s="2" t="s">
-        <v>1735</v>
+        <v>626</v>
       </c>
       <c r="C628" s="2" t="s">
-        <v>1736</v>
+        <v>627</v>
       </c>
     </row>
     <row r="629" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14320,21 +14362,21 @@
         <v>1740</v>
       </c>
       <c r="B630" s="2" t="s">
-        <v>315</v>
+        <v>1741</v>
       </c>
       <c r="C630" s="2" t="s">
-        <v>316</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="631" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A631" s="2" t="s">
-        <v>1741</v>
+        <v>1743</v>
       </c>
       <c r="B631" s="2" t="s">
-        <v>1742</v>
+        <v>318</v>
       </c>
       <c r="C631" s="2" t="s">
-        <v>1743</v>
+        <v>319</v>
       </c>
     </row>
     <row r="632" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14463,32 +14505,32 @@
         <v>1777</v>
       </c>
       <c r="B643" s="2" t="s">
-        <v>309</v>
+        <v>1778</v>
       </c>
       <c r="C643" s="2" t="s">
-        <v>310</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="644" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A644" s="2" t="s">
-        <v>1778</v>
+        <v>1780</v>
       </c>
       <c r="B644" s="2" t="s">
-        <v>1779</v>
+        <v>312</v>
       </c>
       <c r="C644" s="2" t="s">
-        <v>1198</v>
+        <v>313</v>
       </c>
     </row>
     <row r="645" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A645" s="2" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="B645" s="2" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="C645" s="2" t="s">
-        <v>1782</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="646" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14496,21 +14538,21 @@
         <v>1783</v>
       </c>
       <c r="B646" s="2" t="s">
-        <v>1593</v>
+        <v>1784</v>
       </c>
       <c r="C646" s="2" t="s">
-        <v>1594</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="647" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A647" s="2" t="s">
-        <v>1784</v>
+        <v>1786</v>
       </c>
       <c r="B647" s="2" t="s">
-        <v>1785</v>
+        <v>1596</v>
       </c>
       <c r="C647" s="2" t="s">
-        <v>1786</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="648" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14562,40 +14604,40 @@
         <v>1799</v>
       </c>
       <c r="B652" s="2" t="s">
-        <v>209</v>
+        <v>1800</v>
       </c>
       <c r="C652" s="2" t="s">
-        <v>210</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="653" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A653" s="2" t="s">
-        <v>1800</v>
+        <v>1802</v>
       </c>
       <c r="B653" s="2" t="s">
-        <v>1195</v>
+        <v>212</v>
       </c>
       <c r="C653" s="2" t="s">
-        <v>733</v>
+        <v>213</v>
       </c>
     </row>
     <row r="654" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A654" s="2" t="s">
-        <v>1801</v>
+        <v>1803</v>
       </c>
       <c r="B654" s="2" t="s">
-        <v>1204</v>
+        <v>1198</v>
       </c>
       <c r="C654" s="2" t="s">
-        <v>1802</v>
+        <v>736</v>
       </c>
     </row>
     <row r="655" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A655" s="2" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="B655" s="2" t="s">
-        <v>1804</v>
+        <v>1207</v>
       </c>
       <c r="C655" s="2" t="s">
         <v>1805</v>
@@ -14606,21 +14648,21 @@
         <v>1806</v>
       </c>
       <c r="B656" s="2" t="s">
-        <v>309</v>
+        <v>1807</v>
       </c>
       <c r="C656" s="2" t="s">
-        <v>310</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="657" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A657" s="2" t="s">
-        <v>1807</v>
+        <v>1809</v>
       </c>
       <c r="B657" s="2" t="s">
-        <v>1808</v>
+        <v>312</v>
       </c>
       <c r="C657" s="2" t="s">
-        <v>1809</v>
+        <v>313</v>
       </c>
     </row>
     <row r="658" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14661,21 +14703,21 @@
         <v>1819</v>
       </c>
       <c r="B661" s="2" t="s">
-        <v>315</v>
+        <v>1820</v>
       </c>
       <c r="C661" s="2" t="s">
-        <v>316</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="662" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A662" s="2" t="s">
-        <v>1820</v>
+        <v>1822</v>
       </c>
       <c r="B662" s="2" t="s">
-        <v>1821</v>
+        <v>318</v>
       </c>
       <c r="C662" s="2" t="s">
-        <v>1822</v>
+        <v>319</v>
       </c>
     </row>
     <row r="663" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14727,21 +14769,21 @@
         <v>1835</v>
       </c>
       <c r="B667" s="2" t="s">
-        <v>623</v>
+        <v>1836</v>
       </c>
       <c r="C667" s="2" t="s">
-        <v>624</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="668" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A668" s="2" t="s">
-        <v>1836</v>
+        <v>1838</v>
       </c>
       <c r="B668" s="2" t="s">
-        <v>1837</v>
+        <v>626</v>
       </c>
       <c r="C668" s="2" t="s">
-        <v>1838</v>
+        <v>627</v>
       </c>
     </row>
     <row r="669" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14837,21 +14879,21 @@
         <v>1863</v>
       </c>
       <c r="B677" s="2" t="s">
-        <v>19</v>
+        <v>1864</v>
       </c>
       <c r="C677" s="2" t="s">
-        <v>20</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="678" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A678" s="2" t="s">
-        <v>1864</v>
+        <v>1866</v>
       </c>
       <c r="B678" s="2" t="s">
-        <v>1865</v>
+        <v>19</v>
       </c>
       <c r="C678" s="2" t="s">
-        <v>1866</v>
+        <v>20</v>
       </c>
     </row>
     <row r="679" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -14903,21 +14945,21 @@
         <v>1879</v>
       </c>
       <c r="B683" s="2" t="s">
-        <v>294</v>
+        <v>1880</v>
       </c>
       <c r="C683" s="2" t="s">
-        <v>295</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="684" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A684" s="2" t="s">
-        <v>1880</v>
+        <v>1882</v>
       </c>
       <c r="B684" s="2" t="s">
-        <v>1881</v>
+        <v>297</v>
       </c>
       <c r="C684" s="2" t="s">
-        <v>1882</v>
+        <v>298</v>
       </c>
     </row>
     <row r="685" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15002,18 +15044,18 @@
         <v>1904</v>
       </c>
       <c r="B692" s="2" t="s">
-        <v>835</v>
+        <v>1905</v>
       </c>
       <c r="C692" s="2" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="693" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A693" s="2" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="B693" s="2" t="s">
-        <v>1907</v>
+        <v>838</v>
       </c>
       <c r="C693" s="2" t="s">
         <v>1908</v>
@@ -15104,18 +15146,18 @@
         <v>1931</v>
       </c>
       <c r="C701" s="2" t="s">
-        <v>488</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="702" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A702" s="2" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="B702" s="2" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="C702" s="2" t="s">
-        <v>1934</v>
+        <v>491</v>
       </c>
     </row>
     <row r="703" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15134,32 +15176,32 @@
         <v>1938</v>
       </c>
       <c r="B704" s="2" t="s">
-        <v>309</v>
+        <v>1939</v>
       </c>
       <c r="C704" s="2" t="s">
-        <v>310</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="705" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A705" s="2" t="s">
-        <v>1939</v>
+        <v>1941</v>
       </c>
       <c r="B705" s="2" t="s">
-        <v>1940</v>
+        <v>312</v>
       </c>
       <c r="C705" s="2" t="s">
-        <v>207</v>
+        <v>313</v>
       </c>
     </row>
     <row r="706" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A706" s="2" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="B706" s="2" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="C706" s="2" t="s">
-        <v>1943</v>
+        <v>210</v>
       </c>
     </row>
     <row r="707" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15170,18 +15212,18 @@
         <v>1945</v>
       </c>
       <c r="C707" s="2" t="s">
-        <v>488</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="708" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A708" s="2" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="B708" s="2" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="C708" s="2" t="s">
-        <v>1948</v>
+        <v>491</v>
       </c>
     </row>
     <row r="709" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15189,54 +15231,54 @@
         <v>1949</v>
       </c>
       <c r="B709" s="2" t="s">
-        <v>954</v>
+        <v>1950</v>
       </c>
       <c r="C709" s="2" t="s">
-        <v>955</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="710" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A710" s="2" t="s">
-        <v>1950</v>
+        <v>1952</v>
       </c>
       <c r="B710" s="2" t="s">
-        <v>4</v>
+        <v>957</v>
       </c>
       <c r="C710" s="2" t="s">
-        <v>5</v>
+        <v>958</v>
       </c>
     </row>
     <row r="711" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A711" s="2" t="s">
-        <v>1951</v>
+        <v>1953</v>
       </c>
       <c r="B711" s="2" t="s">
-        <v>315</v>
+        <v>4</v>
       </c>
       <c r="C711" s="2" t="s">
-        <v>316</v>
+        <v>5</v>
       </c>
     </row>
     <row r="712" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A712" s="2" t="s">
-        <v>1952</v>
+        <v>1954</v>
       </c>
       <c r="B712" s="2" t="s">
-        <v>1947</v>
+        <v>318</v>
       </c>
       <c r="C712" s="2" t="s">
-        <v>1948</v>
+        <v>319</v>
       </c>
     </row>
     <row r="713" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A713" s="2" t="s">
-        <v>1953</v>
+        <v>1955</v>
       </c>
       <c r="B713" s="2" t="s">
-        <v>1954</v>
+        <v>1950</v>
       </c>
       <c r="C713" s="2" t="s">
-        <v>1955</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="714" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15321,43 +15363,43 @@
         <v>1977</v>
       </c>
       <c r="B721" s="2" t="s">
-        <v>19</v>
+        <v>1978</v>
       </c>
       <c r="C721" s="2" t="s">
-        <v>20</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="722" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A722" s="2" t="s">
-        <v>1978</v>
+        <v>1980</v>
       </c>
       <c r="B722" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C722" s="2" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="723" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A723" s="2" t="s">
-        <v>1979</v>
+        <v>1981</v>
       </c>
       <c r="B723" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C723" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="724" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A724" s="2" t="s">
-        <v>1980</v>
+        <v>1982</v>
       </c>
       <c r="B724" s="2" t="s">
-        <v>1981</v>
+        <v>16</v>
       </c>
       <c r="C724" s="2" t="s">
-        <v>1982</v>
+        <v>17</v>
       </c>
     </row>
     <row r="725" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15398,15 +15440,15 @@
         <v>1992</v>
       </c>
       <c r="B728" s="2" t="s">
-        <v>1890</v>
+        <v>1993</v>
       </c>
       <c r="C728" s="2" t="s">
-        <v>1891</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="729" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A729" s="2" t="s">
-        <v>1993</v>
+        <v>1995</v>
       </c>
       <c r="B729" s="2" t="s">
         <v>1893</v>
@@ -15417,24 +15459,24 @@
     </row>
     <row r="730" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A730" s="2" t="s">
-        <v>1994</v>
+        <v>1996</v>
       </c>
       <c r="B730" s="2" t="s">
-        <v>1995</v>
+        <v>1896</v>
       </c>
       <c r="C730" s="2" t="s">
-        <v>1362</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="731" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A731" s="2" t="s">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="B731" s="2" t="s">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="C731" s="2" t="s">
-        <v>1998</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="732" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15442,43 +15484,43 @@
         <v>1999</v>
       </c>
       <c r="B732" s="2" t="s">
-        <v>1207</v>
+        <v>2000</v>
       </c>
       <c r="C732" s="2" t="s">
-        <v>1208</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="733" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A733" s="2" t="s">
-        <v>2000</v>
+        <v>2002</v>
       </c>
       <c r="B733" s="2" t="s">
-        <v>2001</v>
+        <v>1210</v>
       </c>
       <c r="C733" s="2" t="s">
-        <v>1903</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="734" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A734" s="2" t="s">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="B734" s="2" t="s">
-        <v>835</v>
+        <v>2004</v>
       </c>
       <c r="C734" s="2" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="735" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A735" s="2" t="s">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="B735" s="2" t="s">
-        <v>2004</v>
+        <v>838</v>
       </c>
       <c r="C735" s="2" t="s">
-        <v>2005</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="736" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15489,73 +15531,73 @@
         <v>2007</v>
       </c>
       <c r="C736" s="2" t="s">
-        <v>1998</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="737" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A737" s="2" t="s">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="B737" s="2" t="s">
-        <v>938</v>
+        <v>2010</v>
       </c>
       <c r="C737" s="2" t="s">
-        <v>2009</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="738" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A738" s="2" t="s">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="B738" s="2" t="s">
-        <v>950</v>
+        <v>941</v>
       </c>
       <c r="C738" s="2" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="739" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A739" s="2" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="B739" s="2" t="s">
-        <v>626</v>
+        <v>953</v>
       </c>
       <c r="C739" s="2" t="s">
-        <v>488</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="740" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A740" s="2" t="s">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="B740" s="2" t="s">
-        <v>954</v>
+        <v>629</v>
       </c>
       <c r="C740" s="2" t="s">
-        <v>955</v>
+        <v>491</v>
       </c>
     </row>
     <row r="741" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A741" s="2" t="s">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="B741" s="2" t="s">
-        <v>315</v>
+        <v>957</v>
       </c>
       <c r="C741" s="2" t="s">
-        <v>316</v>
+        <v>958</v>
       </c>
     </row>
     <row r="742" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A742" s="2" t="s">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="B742" s="2" t="s">
-        <v>2016</v>
+        <v>318</v>
       </c>
       <c r="C742" s="2" t="s">
-        <v>2017</v>
+        <v>319</v>
       </c>
     </row>
     <row r="743" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15585,43 +15627,43 @@
         <v>2024</v>
       </c>
       <c r="B745" s="2" t="s">
-        <v>982</v>
+        <v>2025</v>
       </c>
       <c r="C745" s="2" t="s">
-        <v>983</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="746" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A746" s="2" t="s">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="B746" s="2" t="s">
-        <v>950</v>
+        <v>985</v>
       </c>
       <c r="C746" s="2" t="s">
-        <v>2011</v>
+        <v>986</v>
       </c>
     </row>
     <row r="747" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A747" s="2" t="s">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="B747" s="2" t="s">
-        <v>986</v>
+        <v>953</v>
       </c>
       <c r="C747" s="2" t="s">
-        <v>987</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="748" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A748" s="2" t="s">
-        <v>2027</v>
+        <v>2029</v>
       </c>
       <c r="B748" s="2" t="s">
-        <v>2028</v>
+        <v>989</v>
       </c>
       <c r="C748" s="2" t="s">
-        <v>2029</v>
+        <v>990</v>
       </c>
     </row>
     <row r="749" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15629,18 +15671,18 @@
         <v>2030</v>
       </c>
       <c r="B749" s="2" t="s">
-        <v>992</v>
+        <v>2031</v>
       </c>
       <c r="C749" s="2" t="s">
-        <v>2031</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="750" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A750" s="2" t="s">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="B750" s="2" t="s">
-        <v>2033</v>
+        <v>995</v>
       </c>
       <c r="C750" s="2" t="s">
         <v>2034</v>
@@ -15651,18 +15693,18 @@
         <v>2035</v>
       </c>
       <c r="B751" s="2" t="s">
-        <v>998</v>
+        <v>2036</v>
       </c>
       <c r="C751" s="2" t="s">
-        <v>2036</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="752" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A752" s="2" t="s">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="B752" s="2" t="s">
-        <v>2038</v>
+        <v>1001</v>
       </c>
       <c r="C752" s="2" t="s">
         <v>2039</v>
@@ -15695,62 +15737,62 @@
         <v>2046</v>
       </c>
       <c r="B755" s="2" t="s">
-        <v>816</v>
+        <v>2047</v>
       </c>
       <c r="C755" s="2" t="s">
-        <v>817</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="756" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A756" s="2" t="s">
-        <v>2047</v>
+        <v>2049</v>
       </c>
       <c r="B756" s="2" t="s">
-        <v>1008</v>
+        <v>819</v>
       </c>
       <c r="C756" s="2" t="s">
-        <v>1009</v>
+        <v>820</v>
       </c>
     </row>
     <row r="757" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A757" s="2" t="s">
-        <v>2048</v>
+        <v>2050</v>
       </c>
       <c r="B757" s="2" t="s">
         <v>1011</v>
       </c>
       <c r="C757" s="2" t="s">
-        <v>2049</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="758" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A758" s="2" t="s">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="B758" s="2" t="s">
         <v>1014</v>
       </c>
       <c r="C758" s="2" t="s">
-        <v>2051</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="759" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A759" s="2" t="s">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="B759" s="2" t="s">
         <v>1017</v>
       </c>
       <c r="C759" s="2" t="s">
-        <v>2053</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="760" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A760" s="2" t="s">
-        <v>2054</v>
+        <v>2055</v>
       </c>
       <c r="B760" s="2" t="s">
-        <v>2055</v>
+        <v>1020</v>
       </c>
       <c r="C760" s="2" t="s">
         <v>2056</v>
@@ -15761,15 +15803,15 @@
         <v>2057</v>
       </c>
       <c r="B761" s="2" t="s">
-        <v>1890</v>
+        <v>2058</v>
       </c>
       <c r="C761" s="2" t="s">
-        <v>1891</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="762" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A762" s="2" t="s">
-        <v>2058</v>
+        <v>2060</v>
       </c>
       <c r="B762" s="2" t="s">
         <v>1893</v>
@@ -15780,13 +15822,13 @@
     </row>
     <row r="763" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A763" s="2" t="s">
-        <v>2059</v>
+        <v>2061</v>
       </c>
       <c r="B763" s="2" t="s">
-        <v>2060</v>
+        <v>1896</v>
       </c>
       <c r="C763" s="2" t="s">
-        <v>2061</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="764" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15849,21 +15891,21 @@
         <v>2077</v>
       </c>
       <c r="B769" s="2" t="s">
-        <v>466</v>
+        <v>2078</v>
       </c>
       <c r="C769" s="2" t="s">
-        <v>467</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="770" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A770" s="2" t="s">
-        <v>2078</v>
+        <v>2080</v>
       </c>
       <c r="B770" s="2" t="s">
-        <v>2079</v>
+        <v>469</v>
       </c>
       <c r="C770" s="2" t="s">
-        <v>2080</v>
+        <v>470</v>
       </c>
     </row>
     <row r="771" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15882,51 +15924,51 @@
         <v>2084</v>
       </c>
       <c r="B772" s="2" t="s">
-        <v>478</v>
+        <v>2085</v>
       </c>
       <c r="C772" s="2" t="s">
-        <v>624</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="773" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A773" s="2" t="s">
-        <v>2085</v>
+        <v>2087</v>
       </c>
       <c r="B773" s="2" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C773" s="2" t="s">
-        <v>2086</v>
+        <v>627</v>
       </c>
     </row>
     <row r="774" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A774" s="2" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="B774" s="2" t="s">
-        <v>520</v>
+        <v>487</v>
       </c>
       <c r="C774" s="2" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="775" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A775" s="2" t="s">
-        <v>2089</v>
+        <v>2090</v>
       </c>
       <c r="B775" s="2" t="s">
         <v>523</v>
       </c>
       <c r="C775" s="2" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="776" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A776" s="2" t="s">
-        <v>2091</v>
+        <v>2092</v>
       </c>
       <c r="B776" s="2" t="s">
-        <v>2092</v>
+        <v>526</v>
       </c>
       <c r="C776" s="2" t="s">
         <v>2093</v>
@@ -15959,21 +16001,21 @@
         <v>2100</v>
       </c>
       <c r="B779" s="2" t="s">
-        <v>487</v>
+        <v>2101</v>
       </c>
       <c r="C779" s="2" t="s">
-        <v>488</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="780" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A780" s="2" t="s">
-        <v>2101</v>
+        <v>2103</v>
       </c>
       <c r="B780" s="2" t="s">
-        <v>2102</v>
+        <v>490</v>
       </c>
       <c r="C780" s="2" t="s">
-        <v>2103</v>
+        <v>491</v>
       </c>
     </row>
     <row r="781" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -15981,32 +16023,32 @@
         <v>2104</v>
       </c>
       <c r="B781" s="2" t="s">
-        <v>499</v>
+        <v>2105</v>
       </c>
       <c r="C781" s="2" t="s">
-        <v>500</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="782" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A782" s="2" t="s">
-        <v>2105</v>
+        <v>2107</v>
       </c>
       <c r="B782" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="C782" s="2" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
     </row>
     <row r="783" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A783" s="2" t="s">
-        <v>2106</v>
+        <v>2108</v>
       </c>
       <c r="B783" s="2" t="s">
-        <v>2107</v>
+        <v>508</v>
       </c>
       <c r="C783" s="2" t="s">
-        <v>2108</v>
+        <v>509</v>
       </c>
     </row>
     <row r="784" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -16014,51 +16056,51 @@
         <v>2109</v>
       </c>
       <c r="B784" s="2" t="s">
-        <v>508</v>
+        <v>2110</v>
       </c>
       <c r="C784" s="2" t="s">
-        <v>233</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="785" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A785" s="2" t="s">
-        <v>2110</v>
+        <v>2112</v>
       </c>
       <c r="B785" s="2" t="s">
         <v>511</v>
       </c>
       <c r="C785" s="2" t="s">
-        <v>2111</v>
+        <v>236</v>
       </c>
     </row>
     <row r="786" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A786" s="2" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="B786" s="2" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="C786" s="2" t="s">
-        <v>518</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="787" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A787" s="2" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="B787" s="2" t="s">
-        <v>556</v>
+        <v>520</v>
       </c>
       <c r="C787" s="2" t="s">
-        <v>2114</v>
+        <v>521</v>
       </c>
     </row>
     <row r="788" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A788" s="2" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="B788" s="2" t="s">
-        <v>2116</v>
+        <v>559</v>
       </c>
       <c r="C788" s="2" t="s">
         <v>2117</v>
@@ -16069,21 +16111,21 @@
         <v>2118</v>
       </c>
       <c r="B789" s="2" t="s">
-        <v>538</v>
+        <v>2119</v>
       </c>
       <c r="C789" s="2" t="s">
-        <v>539</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="790" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A790" s="2" t="s">
-        <v>2119</v>
+        <v>2121</v>
       </c>
       <c r="B790" s="2" t="s">
-        <v>2120</v>
+        <v>541</v>
       </c>
       <c r="C790" s="2" t="s">
-        <v>2121</v>
+        <v>542</v>
       </c>
     </row>
     <row r="791" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -16105,15 +16147,15 @@
         <v>2126</v>
       </c>
       <c r="C792" s="2" t="s">
-        <v>548</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="793" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A793" s="2" t="s">
-        <v>2127</v>
+        <v>2128</v>
       </c>
       <c r="B793" s="2" t="s">
-        <v>2128</v>
+        <v>2129</v>
       </c>
       <c r="C793" s="2" t="s">
         <v>551</v>
@@ -16121,13 +16163,13 @@
     </row>
     <row r="794" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A794" s="2" t="s">
-        <v>2129</v>
+        <v>2130</v>
       </c>
       <c r="B794" s="2" t="s">
-        <v>2130</v>
+        <v>2131</v>
       </c>
       <c r="C794" s="2" t="s">
-        <v>2131</v>
+        <v>554</v>
       </c>
     </row>
     <row r="795" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -16146,21 +16188,21 @@
         <v>2135</v>
       </c>
       <c r="B796" s="2" t="s">
-        <v>562</v>
+        <v>2136</v>
       </c>
       <c r="C796" s="2" t="s">
-        <v>563</v>
+        <v>2137</v>
       </c>
     </row>
     <row r="797" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A797" s="2" t="s">
-        <v>2136</v>
+        <v>2138</v>
       </c>
       <c r="B797" s="2" t="s">
-        <v>2137</v>
+        <v>565</v>
       </c>
       <c r="C797" s="2" t="s">
-        <v>2138</v>
+        <v>566</v>
       </c>
     </row>
     <row r="798" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -16168,15 +16210,15 @@
         <v>2139</v>
       </c>
       <c r="B798" s="2" t="s">
-        <v>568</v>
+        <v>2140</v>
       </c>
       <c r="C798" s="2" t="s">
-        <v>569</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="799" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A799" s="2" t="s">
-        <v>2140</v>
+        <v>2142</v>
       </c>
       <c r="B799" s="2" t="s">
         <v>571</v>
@@ -16187,13 +16229,13 @@
     </row>
     <row r="800" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A800" s="2" t="s">
-        <v>2141</v>
+        <v>2143</v>
       </c>
       <c r="B800" s="2" t="s">
-        <v>2142</v>
+        <v>574</v>
       </c>
       <c r="C800" s="2" t="s">
-        <v>2143</v>
+        <v>575</v>
       </c>
     </row>
     <row r="801" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -16201,15 +16243,15 @@
         <v>2144</v>
       </c>
       <c r="B801" s="2" t="s">
-        <v>577</v>
+        <v>2145</v>
       </c>
       <c r="C801" s="2" t="s">
-        <v>578</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="802" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A802" s="2" t="s">
-        <v>2145</v>
+        <v>2147</v>
       </c>
       <c r="B802" s="2" t="s">
         <v>580</v>
@@ -16220,13 +16262,13 @@
     </row>
     <row r="803" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A803" s="2" t="s">
-        <v>2146</v>
+        <v>2148</v>
       </c>
       <c r="B803" s="2" t="s">
-        <v>2147</v>
+        <v>583</v>
       </c>
       <c r="C803" s="2" t="s">
-        <v>2148</v>
+        <v>584</v>
       </c>
     </row>
     <row r="804" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -16256,21 +16298,21 @@
         <v>2155</v>
       </c>
       <c r="B806" s="2" t="s">
-        <v>595</v>
+        <v>2156</v>
       </c>
       <c r="C806" s="2" t="s">
-        <v>596</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="807" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A807" s="2" t="s">
-        <v>2156</v>
+        <v>2158</v>
       </c>
       <c r="B807" s="2" t="s">
-        <v>2157</v>
+        <v>598</v>
       </c>
       <c r="C807" s="2" t="s">
-        <v>2158</v>
+        <v>599</v>
       </c>
     </row>
     <row r="808" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -16278,15 +16320,15 @@
         <v>2159</v>
       </c>
       <c r="B808" s="2" t="s">
-        <v>586</v>
+        <v>2160</v>
       </c>
       <c r="C808" s="2" t="s">
-        <v>587</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="809" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A809" s="2" t="s">
-        <v>2160</v>
+        <v>2162</v>
       </c>
       <c r="B809" s="2" t="s">
         <v>589</v>
@@ -16297,18 +16339,18 @@
     </row>
     <row r="810" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A810" s="2" t="s">
-        <v>2161</v>
+        <v>2163</v>
       </c>
       <c r="B810" s="2" t="s">
-        <v>602</v>
+        <v>592</v>
       </c>
       <c r="C810" s="2" t="s">
-        <v>603</v>
+        <v>593</v>
       </c>
     </row>
     <row r="811" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A811" s="2" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="B811" s="2" t="s">
         <v>605</v>
@@ -16319,21 +16361,21 @@
     </row>
     <row r="812" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A812" s="2" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="B812" s="2" t="s">
         <v>608</v>
       </c>
       <c r="C812" s="2" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="813" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A813" s="2" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="B813" s="2" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C813" s="2" t="s">
         <v>611</v>
@@ -16341,24 +16383,24 @@
     </row>
     <row r="814" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A814" s="2" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="B814" s="2" t="s">
-        <v>599</v>
+        <v>613</v>
       </c>
       <c r="C814" s="2" t="s">
-        <v>600</v>
+        <v>614</v>
       </c>
     </row>
     <row r="815" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A815" s="2" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="B815" s="2" t="s">
-        <v>2167</v>
+        <v>602</v>
       </c>
       <c r="C815" s="2" t="s">
-        <v>2168</v>
+        <v>603</v>
       </c>
     </row>
     <row r="816" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -16413,18 +16455,18 @@
         <v>2182</v>
       </c>
       <c r="C820" s="2" t="s">
-        <v>1812</v>
+        <v>2183</v>
       </c>
     </row>
     <row r="821" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A821" s="2" t="s">
-        <v>2183</v>
+        <v>2184</v>
       </c>
       <c r="B821" s="2" t="s">
-        <v>2184</v>
+        <v>2185</v>
       </c>
       <c r="C821" s="2" t="s">
-        <v>2185</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="822" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -16457,18 +16499,18 @@
         <v>2193</v>
       </c>
       <c r="C824" s="2" t="s">
-        <v>241</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="825" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A825" s="2" t="s">
-        <v>2194</v>
+        <v>2195</v>
       </c>
       <c r="B825" s="2" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="C825" s="2" t="s">
-        <v>2196</v>
+        <v>244</v>
       </c>
     </row>
     <row r="826" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -16641,15 +16683,15 @@
         <v>2242</v>
       </c>
       <c r="B841" s="2" t="s">
-        <v>698</v>
+        <v>2243</v>
       </c>
       <c r="C841" s="2" t="s">
-        <v>699</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="842" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A842" s="2" t="s">
-        <v>2243</v>
+        <v>2245</v>
       </c>
       <c r="B842" s="2" t="s">
         <v>701</v>
@@ -16660,13 +16702,13 @@
     </row>
     <row r="843" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A843" s="2" t="s">
-        <v>2244</v>
+        <v>2246</v>
       </c>
       <c r="B843" s="2" t="s">
-        <v>2245</v>
+        <v>704</v>
       </c>
       <c r="C843" s="2" t="s">
-        <v>2246</v>
+        <v>705</v>
       </c>
     </row>
     <row r="844" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -16740,21 +16782,21 @@
         <v>2265</v>
       </c>
       <c r="B850" s="2" t="s">
-        <v>193</v>
+        <v>2266</v>
       </c>
       <c r="C850" s="2" t="s">
-        <v>194</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="851" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A851" s="2" t="s">
-        <v>2266</v>
+        <v>2268</v>
       </c>
       <c r="B851" s="2" t="s">
-        <v>2267</v>
+        <v>196</v>
       </c>
       <c r="C851" s="2" t="s">
-        <v>2268</v>
+        <v>197</v>
       </c>
     </row>
     <row r="852" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -16784,219 +16826,219 @@
         <v>2275</v>
       </c>
       <c r="B854" s="2" t="s">
-        <v>309</v>
+        <v>2276</v>
       </c>
       <c r="C854" s="2" t="s">
-        <v>310</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="855" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A855" s="2" t="s">
-        <v>2276</v>
+        <v>2278</v>
       </c>
       <c r="B855" s="2" t="s">
-        <v>1588</v>
+        <v>2279</v>
       </c>
       <c r="C855" s="2" t="s">
-        <v>1198</v>
+        <v>663</v>
       </c>
     </row>
     <row r="856" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A856" s="2" t="s">
-        <v>2277</v>
+        <v>2280</v>
       </c>
       <c r="B856" s="2" t="s">
-        <v>2278</v>
+        <v>2281</v>
       </c>
       <c r="C856" s="2" t="s">
-        <v>2279</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="857" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A857" s="2" t="s">
-        <v>2280</v>
+        <v>2283</v>
       </c>
       <c r="B857" s="2" t="s">
-        <v>1521</v>
+        <v>2284</v>
       </c>
       <c r="C857" s="2" t="s">
-        <v>2281</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="858" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A858" s="2" t="s">
-        <v>2282</v>
+        <v>2286</v>
       </c>
       <c r="B858" s="2" t="s">
-        <v>2283</v>
+        <v>2287</v>
       </c>
       <c r="C858" s="2" t="s">
-        <v>1786</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="859" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A859" s="2" t="s">
-        <v>2284</v>
+        <v>2289</v>
       </c>
       <c r="B859" s="2" t="s">
-        <v>1593</v>
+        <v>312</v>
       </c>
       <c r="C859" s="2" t="s">
-        <v>1594</v>
+        <v>313</v>
       </c>
     </row>
     <row r="860" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A860" s="2" t="s">
-        <v>2285</v>
+        <v>2290</v>
       </c>
       <c r="B860" s="2" t="s">
-        <v>2286</v>
+        <v>1591</v>
       </c>
       <c r="C860" s="2" t="s">
-        <v>2287</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="861" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A861" s="2" t="s">
-        <v>2288</v>
+        <v>2291</v>
       </c>
       <c r="B861" s="2" t="s">
-        <v>1788</v>
+        <v>2292</v>
       </c>
       <c r="C861" s="2" t="s">
-        <v>1789</v>
+        <v>2293</v>
       </c>
     </row>
     <row r="862" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A862" s="2" t="s">
-        <v>2289</v>
+        <v>2294</v>
       </c>
       <c r="B862" s="2" t="s">
-        <v>1339</v>
+        <v>1524</v>
       </c>
       <c r="C862" s="2" t="s">
-        <v>1340</v>
+        <v>2295</v>
       </c>
     </row>
     <row r="863" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A863" s="2" t="s">
-        <v>2290</v>
+        <v>2296</v>
       </c>
       <c r="B863" s="2" t="s">
-        <v>2291</v>
+        <v>2297</v>
       </c>
       <c r="C863" s="2" t="s">
-        <v>2292</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="864" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A864" s="2" t="s">
-        <v>2293</v>
+        <v>2298</v>
       </c>
       <c r="B864" s="2" t="s">
-        <v>2294</v>
+        <v>1596</v>
       </c>
       <c r="C864" s="2" t="s">
-        <v>2295</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="865" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A865" s="2" t="s">
-        <v>2296</v>
+        <v>2299</v>
       </c>
       <c r="B865" s="2" t="s">
-        <v>1361</v>
+        <v>2300</v>
       </c>
       <c r="C865" s="2" t="s">
-        <v>1627</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="866" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A866" s="2" t="s">
-        <v>2297</v>
+        <v>2302</v>
       </c>
       <c r="B866" s="2" t="s">
-        <v>1355</v>
+        <v>1791</v>
       </c>
       <c r="C866" s="2" t="s">
-        <v>1356</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="867" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A867" s="2" t="s">
-        <v>2298</v>
+        <v>2303</v>
       </c>
       <c r="B867" s="2" t="s">
-        <v>2299</v>
+        <v>1342</v>
       </c>
       <c r="C867" s="2" t="s">
-        <v>955</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="868" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A868" s="2" t="s">
-        <v>2300</v>
+        <v>2304</v>
       </c>
       <c r="B868" s="2" t="s">
-        <v>1358</v>
+        <v>2305</v>
       </c>
       <c r="C868" s="2" t="s">
-        <v>1359</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="869" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A869" s="2" t="s">
-        <v>2301</v>
+        <v>2307</v>
       </c>
       <c r="B869" s="2" t="s">
-        <v>2302</v>
+        <v>2308</v>
       </c>
       <c r="C869" s="2" t="s">
-        <v>1656</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="870" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A870" s="2" t="s">
-        <v>2303</v>
+        <v>2310</v>
       </c>
       <c r="B870" s="2" t="s">
-        <v>2304</v>
+        <v>1364</v>
       </c>
       <c r="C870" s="2" t="s">
-        <v>2305</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="871" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A871" s="2" t="s">
-        <v>2306</v>
+        <v>2311</v>
       </c>
       <c r="B871" s="2" t="s">
-        <v>2307</v>
+        <v>1358</v>
       </c>
       <c r="C871" s="2" t="s">
-        <v>2308</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="872" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A872" s="2" t="s">
-        <v>2309</v>
+        <v>2312</v>
       </c>
       <c r="B872" s="2" t="s">
-        <v>2310</v>
+        <v>2313</v>
       </c>
       <c r="C872" s="2" t="s">
-        <v>2311</v>
+        <v>958</v>
       </c>
     </row>
     <row r="873" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A873" s="2" t="s">
-        <v>2312</v>
+        <v>2314</v>
       </c>
       <c r="B873" s="2" t="s">
-        <v>2313</v>
+        <v>1361</v>
       </c>
       <c r="C873" s="2" t="s">
-        <v>2314</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="874" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -17007,26 +17049,26 @@
         <v>2316</v>
       </c>
       <c r="C874" s="2" t="s">
-        <v>2317</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="875" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A875" s="2" t="s">
+        <v>2317</v>
+      </c>
+      <c r="B875" s="2" t="s">
         <v>2318</v>
       </c>
-      <c r="B875" s="2" t="s">
+      <c r="C875" s="2" t="s">
         <v>2319</v>
-      </c>
-      <c r="C875" s="2" t="s">
-        <v>2320</v>
       </c>
     </row>
     <row r="876" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A876" s="2" t="s">
+        <v>2320</v>
+      </c>
+      <c r="B876" s="2" t="s">
         <v>2321</v>
-      </c>
-      <c r="B876" s="2" t="s">
-        <v>1658</v>
       </c>
       <c r="C876" s="2" t="s">
         <v>2322</v>
@@ -17051,18 +17093,73 @@
         <v>2327</v>
       </c>
       <c r="C878" s="2" t="s">
-        <v>2327</v>
+        <v>2328</v>
       </c>
     </row>
     <row r="879" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A879" s="2" t="s">
-        <v>2328</v>
+        <v>2329</v>
       </c>
       <c r="B879" s="2" t="s">
-        <v>2329</v>
+        <v>2330</v>
       </c>
       <c r="C879" s="2" t="s">
-        <v>2330</v>
+        <v>2331</v>
+      </c>
+    </row>
+    <row r="880" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A880" s="2" t="s">
+        <v>2332</v>
+      </c>
+      <c r="B880" s="2" t="s">
+        <v>2333</v>
+      </c>
+      <c r="C880" s="2" t="s">
+        <v>2334</v>
+      </c>
+    </row>
+    <row r="881" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A881" s="2" t="s">
+        <v>2335</v>
+      </c>
+      <c r="B881" s="2" t="s">
+        <v>1661</v>
+      </c>
+      <c r="C881" s="2" t="s">
+        <v>2336</v>
+      </c>
+    </row>
+    <row r="882" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A882" s="2" t="s">
+        <v>2337</v>
+      </c>
+      <c r="B882" s="2" t="s">
+        <v>2338</v>
+      </c>
+      <c r="C882" s="2" t="s">
+        <v>2339</v>
+      </c>
+    </row>
+    <row r="883" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A883" s="2" t="s">
+        <v>2340</v>
+      </c>
+      <c r="B883" s="2" t="s">
+        <v>2341</v>
+      </c>
+      <c r="C883" s="2" t="s">
+        <v>2341</v>
+      </c>
+    </row>
+    <row r="884" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A884" s="2" t="s">
+        <v>2342</v>
+      </c>
+      <c r="B884" s="2" t="s">
+        <v>2343</v>
+      </c>
+      <c r="C884" s="2" t="s">
+        <v>2344</v>
       </c>
     </row>
   </sheetData>
